--- a/assets/excel/en/national_sdg_indicators.xlsx
+++ b/assets/excel/en/national_sdg_indicators.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sidwab\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\niewiadomskaew\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB40B393-588E-432D-AC71-0727C0694142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C71AA6B-4515-4FEE-9913-0C70DEA597B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SDGs_1-17" sheetId="1" r:id="rId1"/>
@@ -1264,7 +1264,7 @@
     <t>The Ministry of Economic Development and Technology / The Chancellery of the  Prime Minister</t>
   </si>
   <si>
-    <t>Last update: 10-02-2026, 09:34</t>
+    <t>Last update: 24-02-2026, 08:37</t>
   </si>
 </sst>
 </file>
@@ -2085,7 +2085,7 @@
         <v>36</v>
       </c>
       <c r="U6" s="4">
-        <v>42.7</v>
+        <v>41.8</v>
       </c>
       <c r="V6" s="3"/>
       <c r="W6" s="2" t="s">
@@ -2549,7 +2549,7 @@
         <v>0.06</v>
       </c>
       <c r="R13" s="5">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="S13" s="5">
         <v>0.05</v>
@@ -2557,7 +2557,9 @@
       <c r="T13" s="5">
         <v>0.05</v>
       </c>
-      <c r="U13" s="3"/>
+      <c r="U13" s="5">
+        <v>0.05</v>
+      </c>
       <c r="V13" s="3"/>
       <c r="W13" s="2" t="s">
         <v>30</v>
@@ -8226,7 +8228,9 @@
       <c r="T114" s="4">
         <v>7.9</v>
       </c>
-      <c r="U114" s="3"/>
+      <c r="U114" s="4">
+        <v>4.0999999999999996</v>
+      </c>
       <c r="V114" s="3"/>
       <c r="W114" s="2" t="s">
         <v>30</v>
@@ -8870,7 +8874,7 @@
         <v>36</v>
       </c>
       <c r="U125" s="4">
-        <v>42.7</v>
+        <v>41.8</v>
       </c>
       <c r="V125" s="3"/>
       <c r="W125" s="2" t="s">
@@ -9754,7 +9758,9 @@
       <c r="T138" s="5">
         <v>16.559999999999999</v>
       </c>
-      <c r="U138" s="3"/>
+      <c r="U138" s="5">
+        <v>17.77</v>
+      </c>
       <c r="V138" s="3"/>
       <c r="W138" s="2" t="s">
         <v>181</v>
@@ -9951,7 +9957,9 @@
       <c r="T141" s="4">
         <v>9.5</v>
       </c>
-      <c r="U141" s="3"/>
+      <c r="U141" s="4">
+        <v>10.6</v>
+      </c>
       <c r="V141" s="3"/>
       <c r="W141" s="2" t="s">
         <v>30</v>
@@ -13351,7 +13359,9 @@
       <c r="T191" s="4">
         <v>13.2</v>
       </c>
-      <c r="U191" s="3"/>
+      <c r="U191" s="4">
+        <v>12.5</v>
+      </c>
       <c r="V191" s="3"/>
       <c r="W191" s="2" t="s">
         <v>30</v>
@@ -13404,21 +13414,23 @@
         <v>71.7</v>
       </c>
       <c r="P192" s="4">
-        <v>77.099999999999994</v>
+        <v>71.5</v>
       </c>
       <c r="Q192" s="4">
-        <v>78.3</v>
+        <v>72.3</v>
       </c>
       <c r="R192" s="4">
-        <v>80.400000000000006</v>
+        <v>74.5</v>
       </c>
       <c r="S192" s="4">
-        <v>81.2</v>
+        <v>74.400000000000006</v>
       </c>
       <c r="T192" s="4">
-        <v>83.3</v>
-      </c>
-      <c r="U192" s="3"/>
+        <v>76.400000000000006</v>
+      </c>
+      <c r="U192" s="4">
+        <v>77.5</v>
+      </c>
       <c r="V192" s="3"/>
       <c r="W192" s="2" t="s">
         <v>30</v>
@@ -14316,7 +14328,9 @@
       <c r="T208" s="4">
         <v>21.6</v>
       </c>
-      <c r="U208" s="3"/>
+      <c r="U208" s="4">
+        <v>24.2</v>
+      </c>
       <c r="V208" s="3"/>
       <c r="W208" s="2" t="s">
         <v>30</v>
@@ -15698,7 +15712,9 @@
       <c r="T230" s="6">
         <v>26</v>
       </c>
-      <c r="U230" s="3"/>
+      <c r="U230" s="6">
+        <v>21</v>
+      </c>
       <c r="V230" s="3"/>
       <c r="W230" s="2" t="s">
         <v>99</v>
@@ -15901,9 +15917,11 @@
         <v>6.7</v>
       </c>
       <c r="T233" s="4">
-        <v>7.5</v>
-      </c>
-      <c r="U233" s="3"/>
+        <v>7.8</v>
+      </c>
+      <c r="U233" s="4">
+        <v>7.7</v>
+      </c>
       <c r="V233" s="3"/>
       <c r="W233" s="2" t="s">
         <v>181</v>
@@ -16167,7 +16185,9 @@
       <c r="T237" s="5">
         <v>16.559999999999999</v>
       </c>
-      <c r="U237" s="3"/>
+      <c r="U237" s="5">
+        <v>17.77</v>
+      </c>
       <c r="V237" s="3"/>
       <c r="W237" s="2" t="s">
         <v>181</v>
@@ -18228,16 +18248,16 @@
         <v>36</v>
       </c>
       <c r="G269" s="5">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="H269" s="5">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="I269" s="5">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="J269" s="5">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="K269" s="5">
         <v>1.86</v>
@@ -19472,7 +19492,9 @@
       <c r="T288" s="4">
         <v>5.0999999999999996</v>
       </c>
-      <c r="U288" s="3"/>
+      <c r="U288" s="4">
+        <v>4.8</v>
+      </c>
       <c r="V288" s="3"/>
       <c r="W288" s="2" t="s">
         <v>30</v>
@@ -20054,7 +20076,7 @@
     <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.39370078740157499" right="0.39370078740157499" top="0.39370078740157499" bottom="0.39370078740157499" header="0.39370078740157499" footer="0.39370078740157499"/>
-  <pageSetup paperSize="9" scale="59" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="58" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId3"/>
 </worksheet>

--- a/assets/excel/en/national_sdg_indicators.xlsx
+++ b/assets/excel/en/national_sdg_indicators.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\niewiadomskaew\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dregerj\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C71AA6B-4515-4FEE-9913-0C70DEA597B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD9D553B-625C-4730-8315-27F5A3584FEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SDGs_1-17" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2083" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="413">
   <si>
     <t>sdg.gov.pl/en</t>
   </si>
@@ -853,6 +853,9 @@
     <t>Supporting cities in dealing with sudden changes, crises, both socio-economic and environmental, and guaranteeing safety and high quality of life for inhabitants</t>
   </si>
   <si>
+    <t>11.2.a Housing deficit for low-income households per 1 thous. population in urban areas</t>
+  </si>
+  <si>
     <t>11.2.b Share of inhabitants using sewage systems in urban areas</t>
   </si>
   <si>
@@ -1264,7 +1267,7 @@
     <t>The Ministry of Economic Development and Technology / The Chancellery of the  Prime Minister</t>
   </si>
   <si>
-    <t>Last update: 24-02-2026, 08:37</t>
+    <t>Last update: 10-03-2026, 12:35</t>
   </si>
 </sst>
 </file>
@@ -1810,6 +1813,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:W300"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2008,18 +2014,20 @@
         <v>115.4</v>
       </c>
       <c r="Q5" s="4">
-        <v>115.1</v>
+        <v>115.8</v>
       </c>
       <c r="R5" s="4">
-        <v>121.5</v>
+        <v>122.2</v>
       </c>
       <c r="S5" s="4">
-        <v>132.5</v>
+        <v>127.2</v>
       </c>
       <c r="T5" s="4">
         <v>130.4</v>
       </c>
-      <c r="U5" s="3"/>
+      <c r="U5" s="4">
+        <v>135.69999999999999</v>
+      </c>
       <c r="V5" s="3"/>
       <c r="W5" s="2" t="s">
         <v>30</v>
@@ -2490,7 +2498,9 @@
       <c r="T12" s="5">
         <v>0.57999999999999996</v>
       </c>
-      <c r="U12" s="3"/>
+      <c r="U12" s="5">
+        <v>0.55000000000000004</v>
+      </c>
       <c r="V12" s="3"/>
       <c r="W12" s="2" t="s">
         <v>46</v>
@@ -3200,7 +3210,9 @@
       <c r="T24" s="4">
         <v>61.3</v>
       </c>
-      <c r="U24" s="3"/>
+      <c r="U24" s="4">
+        <v>61.6</v>
+      </c>
       <c r="V24" s="3"/>
       <c r="W24" s="2" t="s">
         <v>30</v>
@@ -3267,7 +3279,9 @@
       <c r="T25" s="4">
         <v>64.599999999999994</v>
       </c>
-      <c r="U25" s="3"/>
+      <c r="U25" s="4">
+        <v>65.3</v>
+      </c>
       <c r="V25" s="3"/>
       <c r="W25" s="2" t="s">
         <v>30</v>
@@ -3334,7 +3348,9 @@
       <c r="T26" s="4">
         <v>400.4</v>
       </c>
-      <c r="U26" s="3"/>
+      <c r="U26" s="4">
+        <v>400.1</v>
+      </c>
       <c r="V26" s="3"/>
       <c r="W26" s="2" t="s">
         <v>30</v>
@@ -3401,7 +3417,9 @@
       <c r="T27" s="4">
         <v>381.8</v>
       </c>
-      <c r="U27" s="3"/>
+      <c r="U27" s="4">
+        <v>377.8</v>
+      </c>
       <c r="V27" s="3"/>
       <c r="W27" s="2" t="s">
         <v>30</v>
@@ -3468,7 +3486,9 @@
       <c r="T28" s="4">
         <v>417.8</v>
       </c>
-      <c r="U28" s="3"/>
+      <c r="U28" s="4">
+        <v>421.1</v>
+      </c>
       <c r="V28" s="3"/>
       <c r="W28" s="2" t="s">
         <v>30</v>
@@ -3535,7 +3555,9 @@
       <c r="T29" s="4">
         <v>407.7</v>
       </c>
-      <c r="U29" s="3"/>
+      <c r="U29" s="4">
+        <v>409.1</v>
+      </c>
       <c r="V29" s="3"/>
       <c r="W29" s="2" t="s">
         <v>30</v>
@@ -3602,7 +3624,9 @@
       <c r="T30" s="4">
         <v>389.8</v>
       </c>
-      <c r="U30" s="3"/>
+      <c r="U30" s="4">
+        <v>387.1</v>
+      </c>
       <c r="V30" s="3"/>
       <c r="W30" s="2" t="s">
         <v>30</v>
@@ -3669,7 +3693,9 @@
       <c r="T31" s="4">
         <v>264.39999999999998</v>
       </c>
-      <c r="U31" s="3"/>
+      <c r="U31" s="4">
+        <v>265.39999999999998</v>
+      </c>
       <c r="V31" s="3"/>
       <c r="W31" s="2" t="s">
         <v>30</v>
@@ -3736,7 +3762,9 @@
       <c r="T32" s="4">
         <v>292.8</v>
       </c>
-      <c r="U32" s="3"/>
+      <c r="U32" s="4">
+        <v>294.5</v>
+      </c>
       <c r="V32" s="3"/>
       <c r="W32" s="2" t="s">
         <v>30</v>
@@ -3803,7 +3831,9 @@
       <c r="T33" s="4">
         <v>237.9</v>
       </c>
-      <c r="U33" s="3"/>
+      <c r="U33" s="4">
+        <v>238.3</v>
+      </c>
       <c r="V33" s="3"/>
       <c r="W33" s="2" t="s">
         <v>30</v>
@@ -3870,7 +3900,9 @@
       <c r="T34" s="4">
         <v>287.7</v>
       </c>
-      <c r="U34" s="3"/>
+      <c r="U34" s="4">
+        <v>289.8</v>
+      </c>
       <c r="V34" s="3"/>
       <c r="W34" s="2" t="s">
         <v>30</v>
@@ -3937,7 +3969,9 @@
       <c r="T35" s="4">
         <v>230.2</v>
       </c>
-      <c r="U35" s="3"/>
+      <c r="U35" s="4">
+        <v>229.6</v>
+      </c>
       <c r="V35" s="3"/>
       <c r="W35" s="2" t="s">
         <v>30</v>
@@ -4004,7 +4038,9 @@
       <c r="T36" s="4">
         <v>25.7</v>
       </c>
-      <c r="U36" s="3"/>
+      <c r="U36" s="4">
+        <v>24.3</v>
+      </c>
       <c r="V36" s="3"/>
       <c r="W36" s="2" t="s">
         <v>30</v>
@@ -4071,7 +4107,9 @@
       <c r="T37" s="4">
         <v>24</v>
       </c>
-      <c r="U37" s="3"/>
+      <c r="U37" s="4">
+        <v>23.2</v>
+      </c>
       <c r="V37" s="3"/>
       <c r="W37" s="2" t="s">
         <v>30</v>
@@ -4138,7 +4176,9 @@
       <c r="T38" s="4">
         <v>27.3</v>
       </c>
-      <c r="U38" s="3"/>
+      <c r="U38" s="4">
+        <v>25.4</v>
+      </c>
       <c r="V38" s="3"/>
       <c r="W38" s="2" t="s">
         <v>30</v>
@@ -4205,7 +4245,9 @@
       <c r="T39" s="4">
         <v>26.2</v>
       </c>
-      <c r="U39" s="3"/>
+      <c r="U39" s="4">
+        <v>24.7</v>
+      </c>
       <c r="V39" s="3"/>
       <c r="W39" s="2" t="s">
         <v>30</v>
@@ -4272,7 +4314,9 @@
       <c r="T40" s="4">
         <v>24.4</v>
       </c>
-      <c r="U40" s="3"/>
+      <c r="U40" s="4">
+        <v>23.9</v>
+      </c>
       <c r="V40" s="3"/>
       <c r="W40" s="2" t="s">
         <v>30</v>
@@ -4331,15 +4375,17 @@
         <v>22.9</v>
       </c>
       <c r="R41" s="4">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="S41" s="4">
         <v>26.6</v>
       </c>
       <c r="T41" s="4">
-        <v>25.7</v>
-      </c>
-      <c r="U41" s="3"/>
+        <v>25.8</v>
+      </c>
+      <c r="U41" s="4">
+        <v>25.3</v>
+      </c>
       <c r="V41" s="3"/>
       <c r="W41" s="2" t="s">
         <v>30</v>
@@ -4395,7 +4441,7 @@
         <v>27.5</v>
       </c>
       <c r="Q42" s="4">
-        <v>28.4</v>
+        <v>28.5</v>
       </c>
       <c r="R42" s="4">
         <v>30</v>
@@ -4406,7 +4452,9 @@
       <c r="T42" s="4">
         <v>29.8</v>
       </c>
-      <c r="U42" s="3"/>
+      <c r="U42" s="4">
+        <v>29.3</v>
+      </c>
       <c r="V42" s="3"/>
       <c r="W42" s="2" t="s">
         <v>30</v>
@@ -4465,15 +4513,17 @@
         <v>17.7</v>
       </c>
       <c r="R43" s="4">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="S43" s="4">
         <v>22.2</v>
       </c>
       <c r="T43" s="4">
-        <v>21.9</v>
-      </c>
-      <c r="U43" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="U43" s="4">
+        <v>21.7</v>
+      </c>
       <c r="V43" s="3"/>
       <c r="W43" s="2" t="s">
         <v>30</v>
@@ -4535,12 +4585,14 @@
         <v>25.5</v>
       </c>
       <c r="S44" s="4">
-        <v>27.9</v>
+        <v>28</v>
       </c>
       <c r="T44" s="4">
         <v>26.9</v>
       </c>
-      <c r="U44" s="3"/>
+      <c r="U44" s="4">
+        <v>26.6</v>
+      </c>
       <c r="V44" s="3"/>
       <c r="W44" s="2" t="s">
         <v>30</v>
@@ -4602,12 +4654,14 @@
         <v>25.3</v>
       </c>
       <c r="S45" s="4">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="T45" s="4">
         <v>24.1</v>
       </c>
-      <c r="U45" s="3"/>
+      <c r="U45" s="4">
+        <v>23.5</v>
+      </c>
       <c r="V45" s="3"/>
       <c r="W45" s="2" t="s">
         <v>30</v>
@@ -4654,9 +4708,11 @@
         <v>34.799999999999997</v>
       </c>
       <c r="T46" s="4">
-        <v>37.6</v>
-      </c>
-      <c r="U46" s="3"/>
+        <v>36.5</v>
+      </c>
+      <c r="U46" s="4">
+        <v>37.700000000000003</v>
+      </c>
       <c r="V46" s="3"/>
       <c r="W46" s="2" t="s">
         <v>30</v>
@@ -4705,7 +4761,9 @@
       <c r="T47" s="4">
         <v>65</v>
       </c>
-      <c r="U47" s="3"/>
+      <c r="U47" s="4">
+        <v>66.2</v>
+      </c>
       <c r="V47" s="3"/>
       <c r="W47" s="2" t="s">
         <v>30</v>
@@ -5409,9 +5467,11 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="S62" s="4">
-        <v>4.7</v>
-      </c>
-      <c r="T62" s="3"/>
+        <v>4.8</v>
+      </c>
+      <c r="T62" s="4">
+        <v>5.5</v>
+      </c>
       <c r="U62" s="3"/>
       <c r="V62" s="3"/>
       <c r="W62" s="2" t="s">
@@ -5470,7 +5530,9 @@
       <c r="S63" s="4">
         <v>4.5</v>
       </c>
-      <c r="T63" s="3"/>
+      <c r="T63" s="4">
+        <v>5.2</v>
+      </c>
       <c r="U63" s="3"/>
       <c r="V63" s="3"/>
       <c r="W63" s="2" t="s">
@@ -5527,9 +5589,11 @@
         <v>0.3</v>
       </c>
       <c r="S64" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="T64" s="3"/>
+        <v>0.3</v>
+      </c>
+      <c r="T64" s="4">
+        <v>0.3</v>
+      </c>
       <c r="U64" s="3"/>
       <c r="V64" s="3"/>
       <c r="W64" s="2" t="s">
@@ -7387,17 +7451,19 @@
       <c r="O96" s="3"/>
       <c r="P96" s="3"/>
       <c r="Q96" s="3"/>
-      <c r="R96" s="6">
+      <c r="R96" s="4">
         <v>21</v>
       </c>
       <c r="S96" s="3"/>
-      <c r="T96" s="6">
+      <c r="T96" s="4">
         <v>20</v>
       </c>
-      <c r="U96" s="6">
+      <c r="U96" s="4">
         <v>22</v>
       </c>
-      <c r="V96" s="3"/>
+      <c r="V96" s="4">
+        <v>23.5</v>
+      </c>
       <c r="W96" s="2" t="s">
         <v>30</v>
       </c>
@@ -7432,17 +7498,19 @@
       <c r="O97" s="3"/>
       <c r="P97" s="3"/>
       <c r="Q97" s="3"/>
-      <c r="R97" s="6">
+      <c r="R97" s="4">
         <v>20</v>
       </c>
       <c r="S97" s="3"/>
-      <c r="T97" s="6">
+      <c r="T97" s="4">
         <v>19</v>
       </c>
-      <c r="U97" s="6">
+      <c r="U97" s="4">
         <v>20</v>
       </c>
-      <c r="V97" s="3"/>
+      <c r="V97" s="4">
+        <v>23.5</v>
+      </c>
       <c r="W97" s="2" t="s">
         <v>30</v>
       </c>
@@ -7477,17 +7545,19 @@
       <c r="O98" s="3"/>
       <c r="P98" s="3"/>
       <c r="Q98" s="3"/>
-      <c r="R98" s="6">
+      <c r="R98" s="4">
         <v>22</v>
       </c>
       <c r="S98" s="3"/>
-      <c r="T98" s="6">
+      <c r="T98" s="4">
         <v>21</v>
       </c>
-      <c r="U98" s="6">
+      <c r="U98" s="4">
         <v>25</v>
       </c>
-      <c r="V98" s="3"/>
+      <c r="V98" s="4">
+        <v>23.6</v>
+      </c>
       <c r="W98" s="2" t="s">
         <v>30</v>
       </c>
@@ -7612,17 +7682,19 @@
       <c r="O101" s="3"/>
       <c r="P101" s="3"/>
       <c r="Q101" s="3"/>
-      <c r="R101" s="6">
+      <c r="R101" s="4">
         <v>36</v>
       </c>
       <c r="S101" s="3"/>
-      <c r="T101" s="6">
+      <c r="T101" s="4">
         <v>31</v>
       </c>
-      <c r="U101" s="6">
+      <c r="U101" s="4">
         <v>36</v>
       </c>
-      <c r="V101" s="3"/>
+      <c r="V101" s="4">
+        <v>38.6</v>
+      </c>
       <c r="W101" s="2" t="s">
         <v>30</v>
       </c>
@@ -7667,7 +7739,9 @@
       <c r="U102" s="6">
         <v>37</v>
       </c>
-      <c r="V102" s="3"/>
+      <c r="V102" s="6">
+        <v>41</v>
+      </c>
       <c r="W102" s="2" t="s">
         <v>30</v>
       </c>
@@ -7702,17 +7776,19 @@
       <c r="O103" s="3"/>
       <c r="P103" s="3"/>
       <c r="Q103" s="3"/>
-      <c r="R103" s="6">
+      <c r="R103" s="4">
         <v>28</v>
       </c>
       <c r="S103" s="3"/>
-      <c r="T103" s="6">
+      <c r="T103" s="4">
         <v>27</v>
       </c>
-      <c r="U103" s="6">
+      <c r="U103" s="4">
         <v>31</v>
       </c>
-      <c r="V103" s="3"/>
+      <c r="V103" s="4">
+        <v>32.200000000000003</v>
+      </c>
       <c r="W103" s="2" t="s">
         <v>30</v>
       </c>
@@ -7747,17 +7823,19 @@
       <c r="O104" s="3"/>
       <c r="P104" s="3"/>
       <c r="Q104" s="3"/>
-      <c r="R104" s="6">
+      <c r="R104" s="4">
         <v>17</v>
       </c>
       <c r="S104" s="3"/>
-      <c r="T104" s="6">
+      <c r="T104" s="4">
         <v>18</v>
       </c>
-      <c r="U104" s="6">
+      <c r="U104" s="4">
         <v>19</v>
       </c>
-      <c r="V104" s="3"/>
+      <c r="V104" s="4">
+        <v>20.9</v>
+      </c>
       <c r="W104" s="2" t="s">
         <v>30</v>
       </c>
@@ -7792,17 +7870,19 @@
       <c r="O105" s="3"/>
       <c r="P105" s="3"/>
       <c r="Q105" s="3"/>
-      <c r="R105" s="6">
+      <c r="R105" s="4">
         <v>8</v>
       </c>
       <c r="S105" s="3"/>
-      <c r="T105" s="6">
+      <c r="T105" s="4">
         <v>9</v>
       </c>
-      <c r="U105" s="6">
+      <c r="U105" s="4">
         <v>12</v>
       </c>
-      <c r="V105" s="3"/>
+      <c r="V105" s="4">
+        <v>8.8000000000000007</v>
+      </c>
       <c r="W105" s="2" t="s">
         <v>30</v>
       </c>
@@ -7837,17 +7917,19 @@
       <c r="O106" s="3"/>
       <c r="P106" s="3"/>
       <c r="Q106" s="3"/>
-      <c r="R106" s="6">
+      <c r="R106" s="4">
         <v>3</v>
       </c>
       <c r="S106" s="3"/>
-      <c r="T106" s="6">
+      <c r="T106" s="4">
         <v>3</v>
       </c>
-      <c r="U106" s="6">
+      <c r="U106" s="4">
         <v>3</v>
       </c>
-      <c r="V106" s="3"/>
+      <c r="V106" s="4">
+        <v>2.7</v>
+      </c>
       <c r="W106" s="2" t="s">
         <v>30</v>
       </c>
@@ -8226,7 +8308,7 @@
         <v>7.9</v>
       </c>
       <c r="T114" s="4">
-        <v>7.9</v>
+        <v>6</v>
       </c>
       <c r="U114" s="4">
         <v>4.0999999999999996</v>
@@ -14698,56 +14780,28 @@
         <v>28</v>
       </c>
       <c r="F214" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G214" s="4">
-        <v>88</v>
-      </c>
-      <c r="H214" s="4">
-        <v>88.4</v>
-      </c>
-      <c r="I214" s="4">
-        <v>91.7</v>
-      </c>
-      <c r="J214" s="4">
-        <v>93.3</v>
-      </c>
-      <c r="K214" s="4">
-        <v>93.9</v>
-      </c>
-      <c r="L214" s="4">
-        <v>94.6</v>
-      </c>
-      <c r="M214" s="4">
-        <v>94.8</v>
-      </c>
-      <c r="N214" s="4">
-        <v>94.5</v>
-      </c>
-      <c r="O214" s="4">
-        <v>94.6</v>
-      </c>
-      <c r="P214" s="4">
-        <v>94.8</v>
-      </c>
-      <c r="Q214" s="4">
-        <v>94.7</v>
-      </c>
-      <c r="R214" s="4">
-        <v>94.6</v>
-      </c>
-      <c r="S214" s="4">
-        <v>95</v>
-      </c>
-      <c r="T214" s="4">
-        <v>94.8</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="G214" s="3"/>
+      <c r="H214" s="3"/>
+      <c r="I214" s="3"/>
+      <c r="J214" s="3"/>
+      <c r="K214" s="3"/>
+      <c r="L214" s="3"/>
+      <c r="M214" s="3"/>
+      <c r="N214" s="3"/>
+      <c r="O214" s="3"/>
+      <c r="P214" s="3"/>
+      <c r="Q214" s="3"/>
+      <c r="R214" s="3"/>
+      <c r="S214" s="3"/>
+      <c r="T214" s="3"/>
       <c r="U214" s="4">
-        <v>94.6</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="V214" s="3"/>
       <c r="W214" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="215" spans="1:23" ht="36" x14ac:dyDescent="0.25">
@@ -14770,49 +14824,49 @@
         <v>36</v>
       </c>
       <c r="G215" s="4">
-        <v>95.3</v>
+        <v>88</v>
       </c>
       <c r="H215" s="4">
-        <v>95.4</v>
+        <v>88.4</v>
       </c>
       <c r="I215" s="4">
-        <v>95.4</v>
+        <v>91.7</v>
       </c>
       <c r="J215" s="4">
-        <v>95.5</v>
+        <v>93.3</v>
       </c>
       <c r="K215" s="4">
-        <v>96.4</v>
+        <v>93.9</v>
       </c>
       <c r="L215" s="4">
-        <v>96.5</v>
+        <v>94.6</v>
       </c>
       <c r="M215" s="4">
-        <v>96.5</v>
+        <v>94.8</v>
       </c>
       <c r="N215" s="4">
-        <v>96.6</v>
+        <v>94.5</v>
       </c>
       <c r="O215" s="4">
-        <v>96.6</v>
+        <v>94.6</v>
       </c>
       <c r="P215" s="4">
-        <v>96.6</v>
+        <v>94.8</v>
       </c>
       <c r="Q215" s="4">
-        <v>96.7</v>
+        <v>94.7</v>
       </c>
       <c r="R215" s="4">
-        <v>96.7</v>
+        <v>94.6</v>
       </c>
       <c r="S215" s="4">
-        <v>96.7</v>
+        <v>95</v>
       </c>
       <c r="T215" s="4">
-        <v>96.8</v>
+        <v>94.8</v>
       </c>
       <c r="U215" s="4">
-        <v>96.8</v>
+        <v>94.6</v>
       </c>
       <c r="V215" s="3"/>
       <c r="W215" s="2" t="s">
@@ -14838,29 +14892,51 @@
       <c r="F216" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G216" s="3"/>
-      <c r="H216" s="3"/>
-      <c r="I216" s="3"/>
-      <c r="J216" s="3"/>
-      <c r="K216" s="3"/>
-      <c r="L216" s="3"/>
-      <c r="M216" s="3"/>
-      <c r="N216" s="3"/>
-      <c r="O216" s="3"/>
-      <c r="P216" s="3"/>
+      <c r="G216" s="4">
+        <v>95.3</v>
+      </c>
+      <c r="H216" s="4">
+        <v>95.4</v>
+      </c>
+      <c r="I216" s="4">
+        <v>95.4</v>
+      </c>
+      <c r="J216" s="4">
+        <v>95.5</v>
+      </c>
+      <c r="K216" s="4">
+        <v>96.4</v>
+      </c>
+      <c r="L216" s="4">
+        <v>96.5</v>
+      </c>
+      <c r="M216" s="4">
+        <v>96.5</v>
+      </c>
+      <c r="N216" s="4">
+        <v>96.6</v>
+      </c>
+      <c r="O216" s="4">
+        <v>96.6</v>
+      </c>
+      <c r="P216" s="4">
+        <v>96.6</v>
+      </c>
       <c r="Q216" s="4">
-        <v>15.7</v>
+        <v>96.7</v>
       </c>
       <c r="R216" s="4">
-        <v>14.8</v>
+        <v>96.7</v>
       </c>
       <c r="S216" s="4">
-        <v>14.8</v>
+        <v>96.7</v>
       </c>
       <c r="T216" s="4">
-        <v>14.3</v>
-      </c>
-      <c r="U216" s="3"/>
+        <v>96.8</v>
+      </c>
+      <c r="U216" s="4">
+        <v>96.8</v>
+      </c>
       <c r="V216" s="3"/>
       <c r="W216" s="2" t="s">
         <v>30</v>
@@ -14896,16 +14972,16 @@
       <c r="O217" s="3"/>
       <c r="P217" s="3"/>
       <c r="Q217" s="4">
-        <v>13.3</v>
+        <v>15.7</v>
       </c>
       <c r="R217" s="4">
-        <v>13.5</v>
+        <v>14.8</v>
       </c>
       <c r="S217" s="4">
-        <v>13.1</v>
+        <v>14.8</v>
       </c>
       <c r="T217" s="4">
-        <v>13.3</v>
+        <v>14.3</v>
       </c>
       <c r="U217" s="3"/>
       <c r="V217" s="3"/>
@@ -14913,15 +14989,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="218" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>259</v>
       </c>
       <c r="B218" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C218" s="2" t="s">
         <v>278</v>
-      </c>
-      <c r="C218" s="2" t="s">
-        <v>279</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>27</v>
@@ -14932,47 +15008,27 @@
       <c r="F218" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G218" s="4">
-        <v>41.6</v>
-      </c>
-      <c r="H218" s="4">
-        <v>44.7</v>
-      </c>
-      <c r="I218" s="4">
-        <v>46.5</v>
-      </c>
-      <c r="J218" s="4">
-        <v>48.2</v>
-      </c>
-      <c r="K218" s="4">
-        <v>49.6</v>
-      </c>
-      <c r="L218" s="4">
-        <v>49.8</v>
-      </c>
-      <c r="M218" s="4">
-        <v>50.6</v>
-      </c>
-      <c r="N218" s="4">
-        <v>51.2</v>
-      </c>
-      <c r="O218" s="4">
-        <v>52.4</v>
-      </c>
-      <c r="P218" s="4">
-        <v>53.4</v>
-      </c>
+      <c r="G218" s="3"/>
+      <c r="H218" s="3"/>
+      <c r="I218" s="3"/>
+      <c r="J218" s="3"/>
+      <c r="K218" s="3"/>
+      <c r="L218" s="3"/>
+      <c r="M218" s="3"/>
+      <c r="N218" s="3"/>
+      <c r="O218" s="3"/>
+      <c r="P218" s="3"/>
       <c r="Q218" s="4">
-        <v>53.9</v>
+        <v>13.3</v>
       </c>
       <c r="R218" s="4">
-        <v>54.8</v>
+        <v>13.5</v>
       </c>
       <c r="S218" s="4">
-        <v>55.8</v>
+        <v>13.1</v>
       </c>
       <c r="T218" s="4">
-        <v>53.6</v>
+        <v>13.3</v>
       </c>
       <c r="U218" s="3"/>
       <c r="V218" s="3"/>
@@ -14985,7 +15041,7 @@
         <v>259</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C219" s="2" t="s">
         <v>280</v>
@@ -14999,46 +15055,50 @@
       <c r="F219" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G219" s="3"/>
-      <c r="H219" s="3"/>
+      <c r="G219" s="4">
+        <v>41.6</v>
+      </c>
+      <c r="H219" s="4">
+        <v>44.7</v>
+      </c>
       <c r="I219" s="4">
-        <v>29.8</v>
+        <v>46.5</v>
       </c>
       <c r="J219" s="4">
-        <v>31.1</v>
+        <v>48.2</v>
       </c>
       <c r="K219" s="4">
-        <v>30.3</v>
+        <v>49.6</v>
       </c>
       <c r="L219" s="4">
-        <v>32.299999999999997</v>
+        <v>49.8</v>
       </c>
       <c r="M219" s="4">
-        <v>34.700000000000003</v>
+        <v>50.6</v>
       </c>
       <c r="N219" s="4">
-        <v>35.6</v>
+        <v>51.2</v>
       </c>
       <c r="O219" s="4">
-        <v>37.5</v>
+        <v>52.4</v>
       </c>
       <c r="P219" s="4">
-        <v>35.9</v>
+        <v>53.4</v>
       </c>
       <c r="Q219" s="4">
-        <v>36.6</v>
+        <v>53.9</v>
       </c>
       <c r="R219" s="4">
-        <v>36.1</v>
+        <v>54.8</v>
       </c>
       <c r="S219" s="4">
-        <v>35.4</v>
+        <v>55.8</v>
       </c>
       <c r="T219" s="4">
-        <v>35.6</v>
+        <v>53.6</v>
       </c>
       <c r="U219" s="4">
-        <v>35.4</v>
+        <v>54.5</v>
       </c>
       <c r="V219" s="3"/>
       <c r="W219" s="2" t="s">
@@ -15050,7 +15110,7 @@
         <v>259</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C220" s="2" t="s">
         <v>281</v>
@@ -15062,39 +15122,63 @@
         <v>28</v>
       </c>
       <c r="F220" s="3" t="s">
-        <v>282</v>
+        <v>36</v>
       </c>
       <c r="G220" s="3"/>
       <c r="H220" s="3"/>
-      <c r="I220" s="3"/>
-      <c r="J220" s="3"/>
-      <c r="K220" s="3"/>
-      <c r="L220" s="3"/>
-      <c r="M220" s="3"/>
-      <c r="N220" s="3"/>
-      <c r="O220" s="3"/>
-      <c r="P220" s="3"/>
-      <c r="Q220" s="5">
-        <v>83.49</v>
-      </c>
-      <c r="R220" s="3"/>
-      <c r="S220" s="3"/>
-      <c r="T220" s="3"/>
-      <c r="U220" s="3"/>
+      <c r="I220" s="4">
+        <v>29.8</v>
+      </c>
+      <c r="J220" s="4">
+        <v>31.1</v>
+      </c>
+      <c r="K220" s="4">
+        <v>30.3</v>
+      </c>
+      <c r="L220" s="4">
+        <v>32.299999999999997</v>
+      </c>
+      <c r="M220" s="4">
+        <v>34.700000000000003</v>
+      </c>
+      <c r="N220" s="4">
+        <v>35.6</v>
+      </c>
+      <c r="O220" s="4">
+        <v>37.5</v>
+      </c>
+      <c r="P220" s="4">
+        <v>35.9</v>
+      </c>
+      <c r="Q220" s="4">
+        <v>36.6</v>
+      </c>
+      <c r="R220" s="4">
+        <v>36.1</v>
+      </c>
+      <c r="S220" s="4">
+        <v>35.4</v>
+      </c>
+      <c r="T220" s="4">
+        <v>35.6</v>
+      </c>
+      <c r="U220" s="4">
+        <v>35.4</v>
+      </c>
       <c r="V220" s="3"/>
       <c r="W220" s="2" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="221" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="221" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>259</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>27</v>
@@ -15103,52 +15187,28 @@
         <v>28</v>
       </c>
       <c r="F221" s="3" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="G221" s="3"/>
       <c r="H221" s="3"/>
-      <c r="I221" s="5">
-        <v>1.39</v>
-      </c>
-      <c r="J221" s="5">
-        <v>1.41</v>
-      </c>
-      <c r="K221" s="5">
-        <v>1.43</v>
-      </c>
-      <c r="L221" s="5">
-        <v>1.48</v>
-      </c>
-      <c r="M221" s="5">
-        <v>1.47</v>
-      </c>
-      <c r="N221" s="5">
-        <v>1.5</v>
-      </c>
-      <c r="O221" s="5">
-        <v>1.53</v>
-      </c>
-      <c r="P221" s="5">
-        <v>1.57</v>
-      </c>
+      <c r="I221" s="3"/>
+      <c r="J221" s="3"/>
+      <c r="K221" s="3"/>
+      <c r="L221" s="3"/>
+      <c r="M221" s="3"/>
+      <c r="N221" s="3"/>
+      <c r="O221" s="3"/>
+      <c r="P221" s="3"/>
       <c r="Q221" s="5">
-        <v>1.58</v>
-      </c>
-      <c r="R221" s="5">
-        <v>1.58</v>
-      </c>
-      <c r="S221" s="5">
-        <v>1.54</v>
-      </c>
-      <c r="T221" s="5">
-        <v>1.57</v>
-      </c>
-      <c r="U221" s="5">
-        <v>1.62</v>
-      </c>
+        <v>83.49</v>
+      </c>
+      <c r="R221" s="3"/>
+      <c r="S221" s="3"/>
+      <c r="T221" s="3"/>
+      <c r="U221" s="3"/>
       <c r="V221" s="3"/>
       <c r="W221" s="2" t="s">
-        <v>30</v>
+        <v>284</v>
       </c>
     </row>
     <row r="222" spans="1:23" ht="27" x14ac:dyDescent="0.25">
@@ -15156,10 +15216,10 @@
         <v>259</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>27</v>
@@ -15168,44 +15228,52 @@
         <v>28</v>
       </c>
       <c r="F222" s="3" t="s">
-        <v>32</v>
+        <v>287</v>
       </c>
       <c r="G222" s="3"/>
       <c r="H222" s="3"/>
-      <c r="I222" s="3"/>
-      <c r="J222" s="3"/>
-      <c r="K222" s="3"/>
-      <c r="L222" s="4">
-        <v>12.1</v>
-      </c>
-      <c r="M222" s="4">
-        <v>12.7</v>
-      </c>
-      <c r="N222" s="4">
-        <v>11.6</v>
-      </c>
-      <c r="O222" s="4">
-        <v>11.4</v>
-      </c>
-      <c r="P222" s="4">
-        <v>10.6</v>
-      </c>
-      <c r="Q222" s="4">
-        <v>9</v>
-      </c>
-      <c r="R222" s="4">
-        <v>7.7</v>
-      </c>
-      <c r="S222" s="4">
-        <v>7.6</v>
-      </c>
-      <c r="T222" s="4">
-        <v>7.6</v>
-      </c>
-      <c r="U222" s="3"/>
+      <c r="I222" s="5">
+        <v>1.39</v>
+      </c>
+      <c r="J222" s="5">
+        <v>1.41</v>
+      </c>
+      <c r="K222" s="5">
+        <v>1.43</v>
+      </c>
+      <c r="L222" s="5">
+        <v>1.48</v>
+      </c>
+      <c r="M222" s="5">
+        <v>1.47</v>
+      </c>
+      <c r="N222" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="O222" s="5">
+        <v>1.53</v>
+      </c>
+      <c r="P222" s="5">
+        <v>1.57</v>
+      </c>
+      <c r="Q222" s="5">
+        <v>1.58</v>
+      </c>
+      <c r="R222" s="5">
+        <v>1.58</v>
+      </c>
+      <c r="S222" s="5">
+        <v>1.54</v>
+      </c>
+      <c r="T222" s="5">
+        <v>1.57</v>
+      </c>
+      <c r="U222" s="5">
+        <v>1.62</v>
+      </c>
       <c r="V222" s="3"/>
       <c r="W222" s="2" t="s">
-        <v>288</v>
+        <v>30</v>
       </c>
     </row>
     <row r="223" spans="1:23" ht="27" x14ac:dyDescent="0.25">
@@ -15213,10 +15281,10 @@
         <v>259</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>27</v>
@@ -15227,52 +15295,42 @@
       <c r="F223" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G223" s="4">
-        <v>166.5</v>
-      </c>
-      <c r="H223" s="4">
-        <v>166.2</v>
-      </c>
-      <c r="I223" s="4">
-        <v>165.6</v>
-      </c>
-      <c r="J223" s="4">
-        <v>155.5</v>
-      </c>
-      <c r="K223" s="4">
-        <v>159.69999999999999</v>
-      </c>
+      <c r="G223" s="3"/>
+      <c r="H223" s="3"/>
+      <c r="I223" s="3"/>
+      <c r="J223" s="3"/>
+      <c r="K223" s="3"/>
       <c r="L223" s="4">
-        <v>158.30000000000001</v>
+        <v>12.1</v>
       </c>
       <c r="M223" s="4">
-        <v>162.69999999999999</v>
+        <v>12.7</v>
       </c>
       <c r="N223" s="4">
-        <v>161.69999999999999</v>
+        <v>11.6</v>
       </c>
       <c r="O223" s="4">
-        <v>163.4</v>
+        <v>11.4</v>
       </c>
       <c r="P223" s="4">
-        <v>167.6</v>
+        <v>10.6</v>
       </c>
       <c r="Q223" s="4">
-        <v>99.3</v>
+        <v>9</v>
       </c>
       <c r="R223" s="4">
-        <v>110.1</v>
+        <v>7.7</v>
       </c>
       <c r="S223" s="4">
-        <v>135.6</v>
+        <v>7.6</v>
       </c>
       <c r="T223" s="4">
-        <v>144.6</v>
+        <v>7.6</v>
       </c>
       <c r="U223" s="3"/>
       <c r="V223" s="3"/>
       <c r="W223" s="2" t="s">
-        <v>170</v>
+        <v>289</v>
       </c>
     </row>
     <row r="224" spans="1:23" ht="27" x14ac:dyDescent="0.25">
@@ -15280,10 +15338,10 @@
         <v>259</v>
       </c>
       <c r="B224" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C224" s="2" t="s">
         <v>290</v>
-      </c>
-      <c r="C224" s="2" t="s">
-        <v>291</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>27</v>
@@ -15292,56 +15350,56 @@
         <v>28</v>
       </c>
       <c r="F224" s="3" t="s">
-        <v>257</v>
+        <v>32</v>
       </c>
       <c r="G224" s="4">
-        <v>3.7</v>
+        <v>166.5</v>
       </c>
       <c r="H224" s="4">
-        <v>3.4</v>
+        <v>166.2</v>
       </c>
       <c r="I224" s="4">
-        <v>4.0999999999999996</v>
+        <v>165.6</v>
       </c>
       <c r="J224" s="4">
-        <v>3.8</v>
+        <v>155.5</v>
       </c>
       <c r="K224" s="4">
-        <v>3.9</v>
+        <v>159.69999999999999</v>
       </c>
       <c r="L224" s="4">
-        <v>3.9</v>
+        <v>158.30000000000001</v>
       </c>
       <c r="M224" s="4">
-        <v>4.5999999999999996</v>
+        <v>162.69999999999999</v>
       </c>
       <c r="N224" s="4">
-        <v>5.0999999999999996</v>
+        <v>161.69999999999999</v>
       </c>
       <c r="O224" s="4">
-        <v>5.4</v>
+        <v>163.4</v>
       </c>
       <c r="P224" s="4">
-        <v>6.1</v>
+        <v>167.6</v>
       </c>
       <c r="Q224" s="4">
-        <v>6.5</v>
+        <v>99.3</v>
       </c>
       <c r="R224" s="4">
-        <v>6.6</v>
+        <v>110.1</v>
       </c>
       <c r="S224" s="4">
-        <v>6.6</v>
+        <v>135.6</v>
       </c>
       <c r="T224" s="4">
-        <v>6.3</v>
+        <v>144.6</v>
       </c>
       <c r="U224" s="4">
-        <v>5.8</v>
+        <v>152.19999999999999</v>
       </c>
       <c r="V224" s="3"/>
       <c r="W224" s="2" t="s">
-        <v>30</v>
+        <v>170</v>
       </c>
     </row>
     <row r="225" spans="1:23" ht="27" x14ac:dyDescent="0.25">
@@ -15349,7 +15407,7 @@
         <v>259</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>292</v>
@@ -15363,50 +15421,50 @@
       <c r="F225" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="G225" s="5">
-        <v>0.26</v>
-      </c>
-      <c r="H225" s="5">
-        <v>0.18</v>
-      </c>
-      <c r="I225" s="5">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="J225" s="5">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="K225" s="5">
-        <v>0.16</v>
-      </c>
-      <c r="L225" s="5">
-        <v>0.11</v>
-      </c>
-      <c r="M225" s="5">
-        <v>0.12</v>
-      </c>
-      <c r="N225" s="5">
-        <v>0.13</v>
-      </c>
-      <c r="O225" s="5">
-        <v>0.13</v>
-      </c>
-      <c r="P225" s="5">
-        <v>0.18</v>
-      </c>
-      <c r="Q225" s="5">
-        <v>0.11</v>
-      </c>
-      <c r="R225" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="S225" s="5">
-        <v>0.09</v>
-      </c>
-      <c r="T225" s="5">
-        <v>0.13</v>
-      </c>
-      <c r="U225" s="5">
-        <v>0.18</v>
+      <c r="G225" s="4">
+        <v>3.7</v>
+      </c>
+      <c r="H225" s="4">
+        <v>3.4</v>
+      </c>
+      <c r="I225" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="J225" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="K225" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="L225" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="M225" s="4">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="N225" s="4">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="O225" s="4">
+        <v>5.4</v>
+      </c>
+      <c r="P225" s="4">
+        <v>6.1</v>
+      </c>
+      <c r="Q225" s="4">
+        <v>6.5</v>
+      </c>
+      <c r="R225" s="4">
+        <v>6.6</v>
+      </c>
+      <c r="S225" s="4">
+        <v>6.6</v>
+      </c>
+      <c r="T225" s="4">
+        <v>6.3</v>
+      </c>
+      <c r="U225" s="4">
+        <v>5.8</v>
       </c>
       <c r="V225" s="3"/>
       <c r="W225" s="2" t="s">
@@ -15418,7 +15476,7 @@
         <v>259</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>293</v>
@@ -15432,31 +15490,51 @@
       <c r="F226" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="G226" s="3"/>
-      <c r="H226" s="3"/>
-      <c r="I226" s="3"/>
-      <c r="J226" s="3"/>
-      <c r="K226" s="3"/>
-      <c r="L226" s="3"/>
-      <c r="M226" s="3"/>
-      <c r="N226" s="3"/>
-      <c r="O226" s="3"/>
-      <c r="P226" s="6">
-        <v>74110</v>
-      </c>
-      <c r="Q226" s="6">
-        <v>68436</v>
-      </c>
-      <c r="R226" s="6">
-        <v>65117</v>
-      </c>
-      <c r="S226" s="6">
-        <v>64070</v>
-      </c>
-      <c r="T226" s="6">
-        <v>61349</v>
-      </c>
-      <c r="U226" s="3"/>
+      <c r="G226" s="5">
+        <v>0.26</v>
+      </c>
+      <c r="H226" s="5">
+        <v>0.18</v>
+      </c>
+      <c r="I226" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J226" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="K226" s="5">
+        <v>0.16</v>
+      </c>
+      <c r="L226" s="5">
+        <v>0.11</v>
+      </c>
+      <c r="M226" s="5">
+        <v>0.12</v>
+      </c>
+      <c r="N226" s="5">
+        <v>0.13</v>
+      </c>
+      <c r="O226" s="5">
+        <v>0.13</v>
+      </c>
+      <c r="P226" s="5">
+        <v>0.18</v>
+      </c>
+      <c r="Q226" s="5">
+        <v>0.11</v>
+      </c>
+      <c r="R226" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="S226" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="T226" s="5">
+        <v>0.13</v>
+      </c>
+      <c r="U226" s="5">
+        <v>0.18</v>
+      </c>
       <c r="V226" s="3"/>
       <c r="W226" s="2" t="s">
         <v>30</v>
@@ -15467,7 +15545,7 @@
         <v>259</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C227" s="2" t="s">
         <v>294</v>
@@ -15484,30 +15562,30 @@
       <c r="G227" s="3"/>
       <c r="H227" s="3"/>
       <c r="I227" s="3"/>
-      <c r="J227" s="6">
-        <v>546870</v>
-      </c>
+      <c r="J227" s="3"/>
       <c r="K227" s="3"/>
-      <c r="L227" s="6">
-        <v>512116</v>
-      </c>
-      <c r="M227" s="6">
-        <v>501544</v>
-      </c>
+      <c r="L227" s="3"/>
+      <c r="M227" s="3"/>
       <c r="N227" s="3"/>
-      <c r="O227" s="6">
-        <v>487452</v>
-      </c>
-      <c r="P227" s="3"/>
+      <c r="O227" s="3"/>
+      <c r="P227" s="6">
+        <v>74110</v>
+      </c>
       <c r="Q227" s="6">
-        <v>469607</v>
-      </c>
-      <c r="R227" s="3"/>
+        <v>68436</v>
+      </c>
+      <c r="R227" s="6">
+        <v>65117</v>
+      </c>
       <c r="S227" s="6">
-        <v>457891</v>
-      </c>
-      <c r="T227" s="3"/>
-      <c r="U227" s="3"/>
+        <v>64070</v>
+      </c>
+      <c r="T227" s="6">
+        <v>61349</v>
+      </c>
+      <c r="U227" s="6">
+        <v>59560</v>
+      </c>
       <c r="V227" s="3"/>
       <c r="W227" s="2" t="s">
         <v>30</v>
@@ -15518,10 +15596,10 @@
         <v>259</v>
       </c>
       <c r="B228" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C228" s="2" t="s">
         <v>295</v>
-      </c>
-      <c r="C228" s="2" t="s">
-        <v>296</v>
       </c>
       <c r="D228" s="2" t="s">
         <v>27</v>
@@ -15530,52 +15608,36 @@
         <v>28</v>
       </c>
       <c r="F228" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="G228" s="6">
-        <v>22795</v>
-      </c>
-      <c r="H228" s="6">
-        <v>21359</v>
-      </c>
-      <c r="I228" s="6">
-        <v>20022</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="G228" s="3"/>
+      <c r="H228" s="3"/>
+      <c r="I228" s="3"/>
       <c r="J228" s="6">
-        <v>19636</v>
-      </c>
-      <c r="K228" s="6">
-        <v>18137</v>
-      </c>
+        <v>546870</v>
+      </c>
+      <c r="K228" s="3"/>
       <c r="L228" s="6">
-        <v>16793</v>
+        <v>512116</v>
       </c>
       <c r="M228" s="6">
-        <v>15086</v>
-      </c>
-      <c r="N228" s="6">
-        <v>14505</v>
-      </c>
+        <v>501544</v>
+      </c>
+      <c r="N228" s="3"/>
       <c r="O228" s="6">
-        <v>14165</v>
-      </c>
-      <c r="P228" s="6">
-        <v>11466</v>
-      </c>
+        <v>487452</v>
+      </c>
+      <c r="P228" s="3"/>
       <c r="Q228" s="6">
-        <v>8767</v>
-      </c>
-      <c r="R228" s="6">
-        <v>8374</v>
-      </c>
+        <v>469607</v>
+      </c>
+      <c r="R228" s="3"/>
       <c r="S228" s="6">
-        <v>7344</v>
-      </c>
-      <c r="T228" s="6">
-        <v>5553</v>
-      </c>
+        <v>457891</v>
+      </c>
+      <c r="T228" s="3"/>
       <c r="U228" s="6">
-        <v>5297</v>
+        <v>446959</v>
       </c>
       <c r="V228" s="3"/>
       <c r="W228" s="2" t="s">
@@ -15587,10 +15649,10 @@
         <v>259</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D229" s="2" t="s">
         <v>27</v>
@@ -15599,64 +15661,64 @@
         <v>28</v>
       </c>
       <c r="F229" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G229" s="6">
-        <v>961</v>
+        <v>22795</v>
       </c>
       <c r="H229" s="6">
-        <v>136730</v>
+        <v>21359</v>
       </c>
       <c r="I229" s="6">
-        <v>11553</v>
+        <v>20022</v>
       </c>
       <c r="J229" s="6">
-        <v>15701</v>
+        <v>19636</v>
       </c>
       <c r="K229" s="6">
-        <v>2758</v>
+        <v>18137</v>
       </c>
       <c r="L229" s="6">
-        <v>69422</v>
+        <v>16793</v>
       </c>
       <c r="M229" s="6">
-        <v>44764</v>
+        <v>15086</v>
       </c>
       <c r="N229" s="6">
-        <v>78118</v>
+        <v>14505</v>
       </c>
       <c r="O229" s="6">
-        <v>14958</v>
+        <v>14165</v>
       </c>
       <c r="P229" s="6">
-        <v>68943</v>
+        <v>11466</v>
       </c>
       <c r="Q229" s="6">
-        <v>57788</v>
+        <v>8767</v>
       </c>
       <c r="R229" s="6">
-        <v>27276</v>
+        <v>8374</v>
       </c>
       <c r="S229" s="6">
-        <v>256675</v>
+        <v>7344</v>
       </c>
       <c r="T229" s="6">
-        <v>211015</v>
+        <v>5553</v>
       </c>
       <c r="U229" s="6">
-        <v>1435</v>
+        <v>5297</v>
       </c>
       <c r="V229" s="3"/>
       <c r="W229" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="230" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>259</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C230" s="2" t="s">
         <v>299</v>
@@ -15668,67 +15730,67 @@
         <v>28</v>
       </c>
       <c r="F230" s="3" t="s">
-        <v>257</v>
+        <v>298</v>
       </c>
       <c r="G230" s="6">
-        <v>6</v>
+        <v>961</v>
       </c>
       <c r="H230" s="6">
-        <v>8</v>
+        <v>136730</v>
       </c>
       <c r="I230" s="6">
-        <v>8</v>
+        <v>11553</v>
       </c>
       <c r="J230" s="6">
-        <v>10</v>
+        <v>15701</v>
       </c>
       <c r="K230" s="6">
-        <v>9</v>
+        <v>2758</v>
       </c>
       <c r="L230" s="6">
-        <v>10</v>
+        <v>69422</v>
       </c>
       <c r="M230" s="6">
-        <v>11</v>
+        <v>44764</v>
       </c>
       <c r="N230" s="6">
-        <v>13</v>
+        <v>78118</v>
       </c>
       <c r="O230" s="6">
-        <v>12</v>
+        <v>14958</v>
       </c>
       <c r="P230" s="6">
-        <v>16</v>
+        <v>68943</v>
       </c>
       <c r="Q230" s="6">
-        <v>21</v>
+        <v>57788</v>
       </c>
       <c r="R230" s="6">
-        <v>24</v>
+        <v>27276</v>
       </c>
       <c r="S230" s="6">
-        <v>25</v>
+        <v>256675</v>
       </c>
       <c r="T230" s="6">
-        <v>26</v>
+        <v>211015</v>
       </c>
       <c r="U230" s="6">
-        <v>21</v>
+        <v>1435</v>
       </c>
       <c r="V230" s="3"/>
       <c r="W230" s="2" t="s">
-        <v>99</v>
+        <v>30</v>
       </c>
     </row>
     <row r="231" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C231" s="2" t="s">
         <v>300</v>
-      </c>
-      <c r="B231" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="C231" s="2" t="s">
-        <v>302</v>
       </c>
       <c r="D231" s="2" t="s">
         <v>27</v>
@@ -15737,67 +15799,67 @@
         <v>28</v>
       </c>
       <c r="F231" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="G231" s="5">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="H231" s="5">
-        <v>0.49</v>
-      </c>
-      <c r="I231" s="5">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="J231" s="5">
-        <v>0.61</v>
-      </c>
-      <c r="K231" s="5">
-        <v>0.65</v>
-      </c>
-      <c r="L231" s="5">
-        <v>0.69</v>
-      </c>
-      <c r="M231" s="5">
-        <v>0.67</v>
-      </c>
-      <c r="N231" s="5">
-        <v>0.69</v>
-      </c>
-      <c r="O231" s="5">
-        <v>0.72</v>
-      </c>
-      <c r="P231" s="5">
-        <v>0.81</v>
-      </c>
-      <c r="Q231" s="5">
-        <v>0.81</v>
-      </c>
-      <c r="R231" s="5">
-        <v>0.86</v>
-      </c>
-      <c r="S231" s="5">
-        <v>0.98</v>
-      </c>
-      <c r="T231" s="5">
-        <v>1.18</v>
-      </c>
-      <c r="U231" s="5">
-        <v>1.38</v>
+        <v>257</v>
+      </c>
+      <c r="G231" s="6">
+        <v>6</v>
+      </c>
+      <c r="H231" s="6">
+        <v>8</v>
+      </c>
+      <c r="I231" s="6">
+        <v>8</v>
+      </c>
+      <c r="J231" s="6">
+        <v>10</v>
+      </c>
+      <c r="K231" s="6">
+        <v>9</v>
+      </c>
+      <c r="L231" s="6">
+        <v>10</v>
+      </c>
+      <c r="M231" s="6">
+        <v>11</v>
+      </c>
+      <c r="N231" s="6">
+        <v>13</v>
+      </c>
+      <c r="O231" s="6">
+        <v>12</v>
+      </c>
+      <c r="P231" s="6">
+        <v>16</v>
+      </c>
+      <c r="Q231" s="6">
+        <v>21</v>
+      </c>
+      <c r="R231" s="6">
+        <v>24</v>
+      </c>
+      <c r="S231" s="6">
+        <v>25</v>
+      </c>
+      <c r="T231" s="6">
+        <v>26</v>
+      </c>
+      <c r="U231" s="6">
+        <v>21</v>
       </c>
       <c r="V231" s="3"/>
       <c r="W231" s="2" t="s">
-        <v>181</v>
+        <v>99</v>
       </c>
     </row>
     <row r="232" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D232" s="2" t="s">
         <v>27</v>
@@ -15806,52 +15868,52 @@
         <v>28</v>
       </c>
       <c r="F232" s="3" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="G232" s="5">
-        <v>16.5</v>
+        <v>0.59</v>
       </c>
       <c r="H232" s="5">
-        <v>20.43</v>
+        <v>0.5</v>
       </c>
       <c r="I232" s="5">
-        <v>17.52</v>
+        <v>0.59</v>
       </c>
       <c r="J232" s="5">
-        <v>16.72</v>
+        <v>0.63</v>
       </c>
       <c r="K232" s="5">
-        <v>16.579999999999998</v>
+        <v>0.66</v>
       </c>
       <c r="L232" s="5">
-        <v>16.47</v>
+        <v>0.69</v>
       </c>
       <c r="M232" s="5">
-        <v>16.920000000000002</v>
+        <v>0.69</v>
       </c>
       <c r="N232" s="5">
-        <v>18.010000000000002</v>
+        <v>0.69</v>
       </c>
       <c r="O232" s="5">
-        <v>18.47</v>
+        <v>0.71</v>
       </c>
       <c r="P232" s="5">
-        <v>17.59</v>
+        <v>0.78</v>
       </c>
       <c r="Q232" s="5">
-        <v>17.579999999999998</v>
+        <v>0.77</v>
       </c>
       <c r="R232" s="5">
-        <v>18.25</v>
+        <v>0.81</v>
       </c>
       <c r="S232" s="5">
-        <v>18.309999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="T232" s="5">
-        <v>17.34</v>
+        <v>0.9</v>
       </c>
       <c r="U232" s="5">
-        <v>16.68</v>
+        <v>0.97</v>
       </c>
       <c r="V232" s="3"/>
       <c r="W232" s="2" t="s">
@@ -15860,10 +15922,10 @@
     </row>
     <row r="233" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C233" s="2" t="s">
         <v>305</v>
@@ -15875,67 +15937,67 @@
         <v>28</v>
       </c>
       <c r="F233" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G233" s="4">
-        <v>11.1</v>
-      </c>
-      <c r="H233" s="4">
-        <v>9.4</v>
-      </c>
-      <c r="I233" s="4">
-        <v>11</v>
-      </c>
-      <c r="J233" s="4">
-        <v>12.2</v>
-      </c>
-      <c r="K233" s="4">
-        <v>13</v>
-      </c>
-      <c r="L233" s="4">
-        <v>11.9</v>
-      </c>
-      <c r="M233" s="4">
-        <v>10.6</v>
-      </c>
-      <c r="N233" s="4">
-        <v>10.4</v>
-      </c>
-      <c r="O233" s="4">
-        <v>10.5</v>
-      </c>
-      <c r="P233" s="4">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="Q233" s="4">
-        <v>7.4</v>
-      </c>
-      <c r="R233" s="4">
-        <v>7</v>
-      </c>
-      <c r="S233" s="4">
-        <v>6.7</v>
-      </c>
-      <c r="T233" s="4">
-        <v>7.8</v>
-      </c>
-      <c r="U233" s="4">
-        <v>7.7</v>
+        <v>298</v>
+      </c>
+      <c r="G233" s="5">
+        <v>16.5</v>
+      </c>
+      <c r="H233" s="5">
+        <v>20.43</v>
+      </c>
+      <c r="I233" s="5">
+        <v>17.52</v>
+      </c>
+      <c r="J233" s="5">
+        <v>16.72</v>
+      </c>
+      <c r="K233" s="5">
+        <v>16.579999999999998</v>
+      </c>
+      <c r="L233" s="5">
+        <v>16.47</v>
+      </c>
+      <c r="M233" s="5">
+        <v>16.920000000000002</v>
+      </c>
+      <c r="N233" s="5">
+        <v>18.010000000000002</v>
+      </c>
+      <c r="O233" s="5">
+        <v>18.47</v>
+      </c>
+      <c r="P233" s="5">
+        <v>17.59</v>
+      </c>
+      <c r="Q233" s="5">
+        <v>17.579999999999998</v>
+      </c>
+      <c r="R233" s="5">
+        <v>18.25</v>
+      </c>
+      <c r="S233" s="5">
+        <v>18.309999999999999</v>
+      </c>
+      <c r="T233" s="5">
+        <v>17.34</v>
+      </c>
+      <c r="U233" s="5">
+        <v>16.68</v>
       </c>
       <c r="V233" s="3"/>
       <c r="W233" s="2" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="234" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B234" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C234" s="2" t="s">
         <v>306</v>
-      </c>
-      <c r="C234" s="2" t="s">
-        <v>307</v>
       </c>
       <c r="D234" s="2" t="s">
         <v>27</v>
@@ -15946,59 +16008,65 @@
       <c r="F234" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G234" s="5">
-        <v>2.0699999999999998</v>
-      </c>
-      <c r="H234" s="5">
-        <v>2.48</v>
-      </c>
-      <c r="I234" s="5">
-        <v>3.05</v>
-      </c>
-      <c r="J234" s="5">
-        <v>3.37</v>
-      </c>
-      <c r="K234" s="5">
-        <v>3.82</v>
-      </c>
-      <c r="L234" s="5">
-        <v>3.45</v>
-      </c>
-      <c r="M234" s="5">
-        <v>2.96</v>
-      </c>
-      <c r="N234" s="5">
-        <v>2.62</v>
-      </c>
-      <c r="O234" s="5">
-        <v>2.48</v>
-      </c>
-      <c r="P234" s="5">
-        <v>2.66</v>
-      </c>
-      <c r="Q234" s="5">
-        <v>2.68</v>
-      </c>
-      <c r="R234" s="3"/>
-      <c r="S234" s="3"/>
-      <c r="T234" s="5">
-        <v>3.1</v>
-      </c>
-      <c r="U234" s="3"/>
+      <c r="G234" s="4">
+        <v>11.1</v>
+      </c>
+      <c r="H234" s="4">
+        <v>9.4</v>
+      </c>
+      <c r="I234" s="4">
+        <v>11</v>
+      </c>
+      <c r="J234" s="4">
+        <v>12.2</v>
+      </c>
+      <c r="K234" s="4">
+        <v>13</v>
+      </c>
+      <c r="L234" s="4">
+        <v>11.9</v>
+      </c>
+      <c r="M234" s="4">
+        <v>10.6</v>
+      </c>
+      <c r="N234" s="4">
+        <v>10.4</v>
+      </c>
+      <c r="O234" s="4">
+        <v>10.5</v>
+      </c>
+      <c r="P234" s="4">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="Q234" s="4">
+        <v>7.4</v>
+      </c>
+      <c r="R234" s="4">
+        <v>7</v>
+      </c>
+      <c r="S234" s="4">
+        <v>6.7</v>
+      </c>
+      <c r="T234" s="4">
+        <v>7.8</v>
+      </c>
+      <c r="U234" s="4">
+        <v>7.7</v>
+      </c>
       <c r="V234" s="3"/>
       <c r="W234" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="235" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="235" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C235" s="2" t="s">
         <v>308</v>
-      </c>
-      <c r="B235" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="C235" s="2" t="s">
-        <v>310</v>
       </c>
       <c r="D235" s="2" t="s">
         <v>27</v>
@@ -16007,65 +16075,61 @@
         <v>28</v>
       </c>
       <c r="F235" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="G235" s="4">
-        <v>100</v>
-      </c>
-      <c r="H235" s="4">
-        <v>99.8</v>
-      </c>
-      <c r="I235" s="4">
-        <v>97.5</v>
-      </c>
-      <c r="J235" s="4">
-        <v>96.3</v>
-      </c>
-      <c r="K235" s="4">
-        <v>92.6</v>
-      </c>
-      <c r="L235" s="4">
-        <v>93.6</v>
-      </c>
-      <c r="M235" s="4">
-        <v>96.8</v>
-      </c>
-      <c r="N235" s="4">
-        <v>100.7</v>
-      </c>
-      <c r="O235" s="4">
-        <v>100.5</v>
-      </c>
-      <c r="P235" s="4">
-        <v>95</v>
-      </c>
-      <c r="Q235" s="4">
-        <v>90.5</v>
-      </c>
-      <c r="R235" s="4">
-        <v>99</v>
-      </c>
-      <c r="S235" s="4">
-        <v>94.2</v>
-      </c>
-      <c r="T235" s="4">
-        <v>84.8</v>
+        <v>36</v>
+      </c>
+      <c r="G235" s="5">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="H235" s="5">
+        <v>2.48</v>
+      </c>
+      <c r="I235" s="5">
+        <v>3.05</v>
+      </c>
+      <c r="J235" s="5">
+        <v>3.37</v>
+      </c>
+      <c r="K235" s="5">
+        <v>3.82</v>
+      </c>
+      <c r="L235" s="5">
+        <v>3.45</v>
+      </c>
+      <c r="M235" s="5">
+        <v>2.96</v>
+      </c>
+      <c r="N235" s="5">
+        <v>2.62</v>
+      </c>
+      <c r="O235" s="5">
+        <v>2.48</v>
+      </c>
+      <c r="P235" s="5">
+        <v>2.66</v>
+      </c>
+      <c r="Q235" s="5">
+        <v>2.68</v>
+      </c>
+      <c r="R235" s="3"/>
+      <c r="S235" s="3"/>
+      <c r="T235" s="5">
+        <v>3.1</v>
       </c>
       <c r="U235" s="3"/>
       <c r="V235" s="3"/>
       <c r="W235" s="2" t="s">
-        <v>312</v>
+        <v>51</v>
       </c>
     </row>
     <row r="236" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D236" s="2" t="s">
         <v>27</v>
@@ -16074,65 +16138,65 @@
         <v>28</v>
       </c>
       <c r="F236" s="3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="G236" s="4">
         <v>100</v>
       </c>
       <c r="H236" s="4">
-        <v>99.6</v>
+        <v>99.8</v>
       </c>
       <c r="I236" s="4">
-        <v>97.8</v>
+        <v>97.5</v>
       </c>
       <c r="J236" s="4">
+        <v>96.3</v>
+      </c>
+      <c r="K236" s="4">
+        <v>92.6</v>
+      </c>
+      <c r="L236" s="4">
+        <v>93.6</v>
+      </c>
+      <c r="M236" s="4">
         <v>96.8</v>
       </c>
-      <c r="K236" s="4">
-        <v>93.7</v>
-      </c>
-      <c r="L236" s="4">
-        <v>94.4</v>
-      </c>
-      <c r="M236" s="4">
-        <v>97</v>
-      </c>
       <c r="N236" s="4">
-        <v>100.6</v>
+        <v>100.7</v>
       </c>
       <c r="O236" s="4">
-        <v>100.6</v>
+        <v>100.5</v>
       </c>
       <c r="P236" s="4">
-        <v>95.1</v>
+        <v>95</v>
       </c>
       <c r="Q236" s="4">
-        <v>91.5</v>
+        <v>90.5</v>
       </c>
       <c r="R236" s="4">
-        <v>98.4</v>
+        <v>99</v>
       </c>
       <c r="S236" s="4">
-        <v>93.8</v>
+        <v>94.2</v>
       </c>
       <c r="T236" s="4">
-        <v>85.8</v>
+        <v>84.8</v>
       </c>
       <c r="U236" s="3"/>
       <c r="V236" s="3"/>
       <c r="W236" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="237" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="237" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D237" s="2" t="s">
         <v>27</v>
@@ -16141,64 +16205,62 @@
         <v>28</v>
       </c>
       <c r="F237" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G237" s="5">
-        <v>9.2799999999999994</v>
-      </c>
-      <c r="H237" s="5">
-        <v>10.34</v>
-      </c>
-      <c r="I237" s="5">
-        <v>10.96</v>
-      </c>
-      <c r="J237" s="5">
-        <v>11.45</v>
-      </c>
-      <c r="K237" s="5">
-        <v>11.61</v>
-      </c>
-      <c r="L237" s="5">
-        <v>11.88</v>
-      </c>
-      <c r="M237" s="5">
-        <v>11.4</v>
-      </c>
-      <c r="N237" s="5">
-        <v>11.06</v>
-      </c>
-      <c r="O237" s="5">
-        <v>14.94</v>
-      </c>
-      <c r="P237" s="5">
-        <v>15.38</v>
-      </c>
-      <c r="Q237" s="5">
-        <v>16.100000000000001</v>
-      </c>
-      <c r="R237" s="5">
-        <v>15.6</v>
-      </c>
-      <c r="S237" s="5">
-        <v>16.63</v>
-      </c>
-      <c r="T237" s="5">
-        <v>16.559999999999999</v>
-      </c>
-      <c r="U237" s="5">
-        <v>17.77</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="G237" s="4">
+        <v>100</v>
+      </c>
+      <c r="H237" s="4">
+        <v>99.6</v>
+      </c>
+      <c r="I237" s="4">
+        <v>97.8</v>
+      </c>
+      <c r="J237" s="4">
+        <v>96.8</v>
+      </c>
+      <c r="K237" s="4">
+        <v>93.7</v>
+      </c>
+      <c r="L237" s="4">
+        <v>94.4</v>
+      </c>
+      <c r="M237" s="4">
+        <v>97</v>
+      </c>
+      <c r="N237" s="4">
+        <v>100.6</v>
+      </c>
+      <c r="O237" s="4">
+        <v>100.6</v>
+      </c>
+      <c r="P237" s="4">
+        <v>95.1</v>
+      </c>
+      <c r="Q237" s="4">
+        <v>91.5</v>
+      </c>
+      <c r="R237" s="4">
+        <v>98.4</v>
+      </c>
+      <c r="S237" s="4">
+        <v>93.8</v>
+      </c>
+      <c r="T237" s="4">
+        <v>85.8</v>
+      </c>
+      <c r="U237" s="3"/>
       <c r="V237" s="3"/>
       <c r="W237" s="2" t="s">
-        <v>181</v>
+        <v>313</v>
       </c>
     </row>
     <row r="238" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>317</v>
@@ -16210,65 +16272,67 @@
         <v>28</v>
       </c>
       <c r="F238" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="G238" s="6">
-        <v>563</v>
-      </c>
-      <c r="H238" s="6">
-        <v>531</v>
-      </c>
-      <c r="I238" s="6">
-        <v>661</v>
-      </c>
-      <c r="J238" s="6">
-        <v>778</v>
-      </c>
-      <c r="K238" s="6">
-        <v>847</v>
-      </c>
-      <c r="L238" s="6">
-        <v>909</v>
-      </c>
-      <c r="M238" s="6">
-        <v>930</v>
-      </c>
-      <c r="N238" s="6">
-        <v>946</v>
-      </c>
-      <c r="O238" s="6">
-        <v>991</v>
-      </c>
-      <c r="P238" s="6">
-        <v>1050</v>
-      </c>
-      <c r="Q238" s="6">
-        <v>1073</v>
-      </c>
-      <c r="R238" s="6">
-        <v>1189</v>
-      </c>
-      <c r="S238" s="6">
-        <v>1318</v>
-      </c>
-      <c r="T238" s="6">
-        <v>1372</v>
-      </c>
-      <c r="U238" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="G238" s="5">
+        <v>9.2799999999999994</v>
+      </c>
+      <c r="H238" s="5">
+        <v>10.34</v>
+      </c>
+      <c r="I238" s="5">
+        <v>10.96</v>
+      </c>
+      <c r="J238" s="5">
+        <v>11.45</v>
+      </c>
+      <c r="K238" s="5">
+        <v>11.61</v>
+      </c>
+      <c r="L238" s="5">
+        <v>11.88</v>
+      </c>
+      <c r="M238" s="5">
+        <v>11.4</v>
+      </c>
+      <c r="N238" s="5">
+        <v>11.06</v>
+      </c>
+      <c r="O238" s="5">
+        <v>14.94</v>
+      </c>
+      <c r="P238" s="5">
+        <v>15.38</v>
+      </c>
+      <c r="Q238" s="5">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="R238" s="5">
+        <v>15.6</v>
+      </c>
+      <c r="S238" s="5">
+        <v>16.63</v>
+      </c>
+      <c r="T238" s="5">
+        <v>16.559999999999999</v>
+      </c>
+      <c r="U238" s="5">
+        <v>17.77</v>
+      </c>
       <c r="V238" s="3"/>
       <c r="W238" s="2" t="s">
-        <v>30</v>
+        <v>181</v>
       </c>
     </row>
     <row r="239" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D239" s="2" t="s">
         <v>27</v>
@@ -16277,67 +16341,67 @@
         <v>28</v>
       </c>
       <c r="F239" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G239" s="6">
-        <v>2218</v>
+        <v>563</v>
       </c>
       <c r="H239" s="6">
-        <v>3117</v>
+        <v>531</v>
       </c>
       <c r="I239" s="6">
-        <v>4139</v>
+        <v>661</v>
       </c>
       <c r="J239" s="6">
-        <v>5205</v>
+        <v>778</v>
       </c>
       <c r="K239" s="6">
-        <v>5793</v>
+        <v>847</v>
       </c>
       <c r="L239" s="6">
-        <v>7105</v>
+        <v>909</v>
       </c>
       <c r="M239" s="6">
-        <v>8017</v>
+        <v>930</v>
       </c>
       <c r="N239" s="6">
-        <v>8195</v>
+        <v>946</v>
       </c>
       <c r="O239" s="6">
-        <v>8486</v>
+        <v>991</v>
       </c>
       <c r="P239" s="6">
-        <v>9547</v>
+        <v>1050</v>
       </c>
       <c r="Q239" s="6">
-        <v>12490</v>
+        <v>1073</v>
       </c>
       <c r="R239" s="6">
-        <v>16935</v>
+        <v>1189</v>
       </c>
       <c r="S239" s="6">
-        <v>22670</v>
+        <v>1318</v>
       </c>
       <c r="T239" s="6">
-        <v>28779</v>
+        <v>1372</v>
       </c>
       <c r="U239" s="6">
-        <v>33623</v>
+        <v>1556</v>
       </c>
       <c r="V239" s="3"/>
       <c r="W239" s="2" t="s">
-        <v>321</v>
+        <v>30</v>
       </c>
     </row>
     <row r="240" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D240" s="2" t="s">
         <v>27</v>
@@ -16346,62 +16410,64 @@
         <v>28</v>
       </c>
       <c r="F240" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G240" s="4">
-        <v>91.3</v>
-      </c>
-      <c r="H240" s="4">
-        <v>91.3</v>
-      </c>
-      <c r="I240" s="4">
-        <v>84.8</v>
-      </c>
-      <c r="J240" s="4">
-        <v>80.400000000000006</v>
-      </c>
-      <c r="K240" s="4">
-        <v>93.5</v>
-      </c>
-      <c r="L240" s="4">
-        <v>87</v>
-      </c>
-      <c r="M240" s="4">
-        <v>78.3</v>
-      </c>
-      <c r="N240" s="4">
-        <v>76.099999999999994</v>
-      </c>
-      <c r="O240" s="4">
-        <v>84.8</v>
-      </c>
-      <c r="P240" s="4">
-        <v>47.8</v>
-      </c>
-      <c r="Q240" s="4">
-        <v>35.6</v>
-      </c>
-      <c r="R240" s="4">
-        <v>54.4</v>
-      </c>
-      <c r="S240" s="4">
-        <v>30.4</v>
-      </c>
-      <c r="T240" s="4">
-        <v>4.3</v>
-      </c>
-      <c r="U240" s="3"/>
+        <v>321</v>
+      </c>
+      <c r="G240" s="6">
+        <v>2218</v>
+      </c>
+      <c r="H240" s="6">
+        <v>3117</v>
+      </c>
+      <c r="I240" s="6">
+        <v>4139</v>
+      </c>
+      <c r="J240" s="6">
+        <v>5205</v>
+      </c>
+      <c r="K240" s="6">
+        <v>5793</v>
+      </c>
+      <c r="L240" s="6">
+        <v>7105</v>
+      </c>
+      <c r="M240" s="6">
+        <v>8017</v>
+      </c>
+      <c r="N240" s="6">
+        <v>8195</v>
+      </c>
+      <c r="O240" s="6">
+        <v>8486</v>
+      </c>
+      <c r="P240" s="6">
+        <v>9547</v>
+      </c>
+      <c r="Q240" s="6">
+        <v>12490</v>
+      </c>
+      <c r="R240" s="6">
+        <v>16935</v>
+      </c>
+      <c r="S240" s="6">
+        <v>22670</v>
+      </c>
+      <c r="T240" s="6">
+        <v>28779</v>
+      </c>
+      <c r="U240" s="6">
+        <v>33623</v>
+      </c>
       <c r="V240" s="3"/>
       <c r="W240" s="2" t="s">
-        <v>99</v>
+        <v>322</v>
       </c>
     </row>
     <row r="241" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>324</v>
@@ -16413,53 +16479,51 @@
         <v>28</v>
       </c>
       <c r="F241" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="G241" s="6">
-        <v>28</v>
-      </c>
-      <c r="H241" s="6">
-        <v>27</v>
-      </c>
-      <c r="I241" s="6">
-        <v>26</v>
-      </c>
-      <c r="J241" s="6">
-        <v>25</v>
-      </c>
-      <c r="K241" s="6">
-        <v>24</v>
-      </c>
-      <c r="L241" s="6">
-        <v>23</v>
-      </c>
-      <c r="M241" s="6">
-        <v>22</v>
-      </c>
-      <c r="N241" s="6">
-        <v>22</v>
-      </c>
-      <c r="O241" s="6">
-        <v>22</v>
-      </c>
-      <c r="P241" s="6">
-        <v>21</v>
-      </c>
-      <c r="Q241" s="6">
-        <v>19</v>
-      </c>
-      <c r="R241" s="6">
-        <v>17</v>
-      </c>
-      <c r="S241" s="6">
-        <v>16</v>
-      </c>
-      <c r="T241" s="6">
-        <v>16</v>
-      </c>
-      <c r="U241" s="6">
-        <v>15</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G241" s="4">
+        <v>91.3</v>
+      </c>
+      <c r="H241" s="4">
+        <v>91.3</v>
+      </c>
+      <c r="I241" s="4">
+        <v>84.8</v>
+      </c>
+      <c r="J241" s="4">
+        <v>80.400000000000006</v>
+      </c>
+      <c r="K241" s="4">
+        <v>93.5</v>
+      </c>
+      <c r="L241" s="4">
+        <v>87</v>
+      </c>
+      <c r="M241" s="4">
+        <v>78.3</v>
+      </c>
+      <c r="N241" s="4">
+        <v>76.099999999999994</v>
+      </c>
+      <c r="O241" s="4">
+        <v>84.8</v>
+      </c>
+      <c r="P241" s="4">
+        <v>47.8</v>
+      </c>
+      <c r="Q241" s="4">
+        <v>35.6</v>
+      </c>
+      <c r="R241" s="4">
+        <v>54.4</v>
+      </c>
+      <c r="S241" s="4">
+        <v>30.4</v>
+      </c>
+      <c r="T241" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="U241" s="3"/>
       <c r="V241" s="3"/>
       <c r="W241" s="2" t="s">
         <v>99</v>
@@ -16467,10 +16531,10 @@
     </row>
     <row r="242" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>325</v>
@@ -16482,63 +16546,67 @@
         <v>28</v>
       </c>
       <c r="F242" s="3" t="s">
-        <v>326</v>
+        <v>98</v>
       </c>
       <c r="G242" s="6">
-        <v>2186</v>
+        <v>28</v>
       </c>
       <c r="H242" s="6">
-        <v>1721</v>
+        <v>27</v>
       </c>
       <c r="I242" s="6">
-        <v>2035</v>
+        <v>26</v>
       </c>
       <c r="J242" s="6">
-        <v>2174</v>
+        <v>25</v>
       </c>
       <c r="K242" s="6">
-        <v>1981</v>
+        <v>24</v>
       </c>
       <c r="L242" s="6">
-        <v>1725</v>
+        <v>23</v>
       </c>
       <c r="M242" s="6">
-        <v>1826</v>
+        <v>22</v>
       </c>
       <c r="N242" s="6">
-        <v>1792</v>
+        <v>22</v>
       </c>
       <c r="O242" s="6">
-        <v>1744</v>
+        <v>22</v>
       </c>
       <c r="P242" s="6">
-        <v>1494</v>
+        <v>21</v>
       </c>
       <c r="Q242" s="6">
-        <v>1820</v>
+        <v>19</v>
       </c>
       <c r="R242" s="6">
-        <v>2205</v>
+        <v>17</v>
       </c>
       <c r="S242" s="6">
-        <v>1959</v>
-      </c>
-      <c r="T242" s="3"/>
-      <c r="U242" s="3"/>
+        <v>16</v>
+      </c>
+      <c r="T242" s="6">
+        <v>16</v>
+      </c>
+      <c r="U242" s="6">
+        <v>15</v>
+      </c>
       <c r="V242" s="3"/>
       <c r="W242" s="2" t="s">
-        <v>327</v>
+        <v>99</v>
       </c>
     </row>
     <row r="243" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D243" s="2" t="s">
         <v>27</v>
@@ -16547,63 +16615,65 @@
         <v>28</v>
       </c>
       <c r="F243" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G243" s="6">
-        <v>48641</v>
+        <v>2186</v>
       </c>
       <c r="H243" s="6">
-        <v>48212</v>
+        <v>1721</v>
       </c>
       <c r="I243" s="6">
-        <v>46053</v>
+        <v>2035</v>
       </c>
       <c r="J243" s="6">
-        <v>43064</v>
+        <v>2174</v>
       </c>
       <c r="K243" s="6">
-        <v>43315</v>
+        <v>1981</v>
       </c>
       <c r="L243" s="6">
-        <v>46834</v>
+        <v>1725</v>
       </c>
       <c r="M243" s="6">
-        <v>52332</v>
+        <v>1826</v>
       </c>
       <c r="N243" s="6">
-        <v>62146</v>
+        <v>1792</v>
       </c>
       <c r="O243" s="6">
-        <v>63975</v>
+        <v>1744</v>
       </c>
       <c r="P243" s="6">
-        <v>64742</v>
+        <v>1494</v>
       </c>
       <c r="Q243" s="6">
-        <v>61823</v>
+        <v>1820</v>
       </c>
       <c r="R243" s="6">
-        <v>66958</v>
+        <v>2205</v>
       </c>
       <c r="S243" s="6">
-        <v>68339</v>
-      </c>
-      <c r="T243" s="3"/>
+        <v>1959</v>
+      </c>
+      <c r="T243" s="6">
+        <v>1801</v>
+      </c>
       <c r="U243" s="3"/>
       <c r="V243" s="3"/>
       <c r="W243" s="2" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="244" spans="1:23" ht="18" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="244" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B244" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C244" s="2" t="s">
         <v>329</v>
-      </c>
-      <c r="C244" s="2" t="s">
-        <v>330</v>
       </c>
       <c r="D244" s="2" t="s">
         <v>27</v>
@@ -16612,64 +16682,62 @@
         <v>28</v>
       </c>
       <c r="F244" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G244" s="5">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="H244" s="5">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="I244" s="5">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="J244" s="5">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="K244" s="5">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="L244" s="5">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="M244" s="5">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="N244" s="5">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="O244" s="5">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="P244" s="5">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="Q244" s="5">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="R244" s="5">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="S244" s="5">
-        <v>0.59</v>
-      </c>
-      <c r="T244" s="5">
-        <v>0.59</v>
-      </c>
-      <c r="U244" s="5">
-        <v>0.59</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="G244" s="6">
+        <v>48641</v>
+      </c>
+      <c r="H244" s="6">
+        <v>48212</v>
+      </c>
+      <c r="I244" s="6">
+        <v>46053</v>
+      </c>
+      <c r="J244" s="6">
+        <v>43064</v>
+      </c>
+      <c r="K244" s="6">
+        <v>43315</v>
+      </c>
+      <c r="L244" s="6">
+        <v>47177</v>
+      </c>
+      <c r="M244" s="6">
+        <v>52332</v>
+      </c>
+      <c r="N244" s="6">
+        <v>62146</v>
+      </c>
+      <c r="O244" s="6">
+        <v>63975</v>
+      </c>
+      <c r="P244" s="6">
+        <v>64742</v>
+      </c>
+      <c r="Q244" s="6">
+        <v>62093</v>
+      </c>
+      <c r="R244" s="6">
+        <v>66958</v>
+      </c>
+      <c r="S244" s="6">
+        <v>68530</v>
+      </c>
+      <c r="T244" s="6">
+        <v>67711</v>
+      </c>
+      <c r="U244" s="3"/>
       <c r="V244" s="3"/>
       <c r="W244" s="2" t="s">
-        <v>30</v>
+        <v>328</v>
       </c>
     </row>
     <row r="245" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C245" s="2" t="s">
         <v>331</v>
@@ -16681,65 +16749,67 @@
         <v>28</v>
       </c>
       <c r="F245" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="G245" s="4">
-        <v>732401.6</v>
-      </c>
-      <c r="H245" s="4">
-        <v>740630</v>
-      </c>
-      <c r="I245" s="4">
-        <v>753624</v>
-      </c>
-      <c r="J245" s="4">
-        <v>752240.3</v>
-      </c>
-      <c r="K245" s="4">
-        <v>804401.8</v>
-      </c>
-      <c r="L245" s="4">
-        <v>830309.8</v>
-      </c>
-      <c r="M245" s="4">
-        <v>826034.2</v>
-      </c>
-      <c r="N245" s="3"/>
-      <c r="O245" s="4">
-        <v>846693.5</v>
-      </c>
-      <c r="P245" s="4">
-        <v>839607.4</v>
-      </c>
-      <c r="Q245" s="4">
-        <v>852978.8</v>
-      </c>
-      <c r="R245" s="4">
-        <v>855928.1</v>
-      </c>
-      <c r="S245" s="4">
-        <v>859996.9</v>
-      </c>
-      <c r="T245" s="4">
-        <v>870987.2</v>
-      </c>
-      <c r="U245" s="4">
-        <v>881284.3</v>
+        <v>36</v>
+      </c>
+      <c r="G245" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="H245" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="I245" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J245" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="K245" s="5">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="L245" s="5">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="M245" s="5">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="N245" s="5">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="O245" s="5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="P245" s="5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="Q245" s="5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="R245" s="5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="S245" s="5">
+        <v>0.59</v>
+      </c>
+      <c r="T245" s="5">
+        <v>0.59</v>
+      </c>
+      <c r="U245" s="5">
+        <v>0.59</v>
       </c>
       <c r="V245" s="3"/>
       <c r="W245" s="2" t="s">
-        <v>170</v>
+        <v>30</v>
       </c>
     </row>
     <row r="246" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D246" s="2" t="s">
         <v>27</v>
@@ -16748,39 +16818,51 @@
         <v>28</v>
       </c>
       <c r="F246" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="G246" s="3"/>
-      <c r="H246" s="3"/>
-      <c r="I246" s="3"/>
-      <c r="J246" s="3"/>
-      <c r="K246" s="3"/>
-      <c r="L246" s="5">
-        <v>6.6</v>
-      </c>
-      <c r="M246" s="5">
-        <v>7.58</v>
-      </c>
-      <c r="N246" s="5">
-        <v>7.54</v>
-      </c>
-      <c r="O246" s="5">
-        <v>10.15</v>
-      </c>
-      <c r="P246" s="5">
-        <v>12.38</v>
-      </c>
-      <c r="Q246" s="5">
-        <v>12.53</v>
-      </c>
-      <c r="R246" s="5">
-        <v>5.95</v>
-      </c>
-      <c r="S246" s="5">
-        <v>4.7300000000000004</v>
-      </c>
-      <c r="T246" s="3"/>
-      <c r="U246" s="3"/>
+        <v>333</v>
+      </c>
+      <c r="G246" s="4">
+        <v>732401.6</v>
+      </c>
+      <c r="H246" s="4">
+        <v>740630</v>
+      </c>
+      <c r="I246" s="4">
+        <v>753624</v>
+      </c>
+      <c r="J246" s="4">
+        <v>752240.3</v>
+      </c>
+      <c r="K246" s="4">
+        <v>804401.8</v>
+      </c>
+      <c r="L246" s="4">
+        <v>830309.8</v>
+      </c>
+      <c r="M246" s="4">
+        <v>826034.2</v>
+      </c>
+      <c r="N246" s="3"/>
+      <c r="O246" s="4">
+        <v>846693.5</v>
+      </c>
+      <c r="P246" s="4">
+        <v>839607.4</v>
+      </c>
+      <c r="Q246" s="4">
+        <v>852978.8</v>
+      </c>
+      <c r="R246" s="4">
+        <v>855928.1</v>
+      </c>
+      <c r="S246" s="4">
+        <v>859996.9</v>
+      </c>
+      <c r="T246" s="4">
+        <v>870987.2</v>
+      </c>
+      <c r="U246" s="4">
+        <v>881284.3</v>
+      </c>
       <c r="V246" s="3"/>
       <c r="W246" s="2" t="s">
         <v>170</v>
@@ -16788,13 +16870,13 @@
     </row>
     <row r="247" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D247" s="2" t="s">
         <v>27</v>
@@ -16803,51 +16885,53 @@
         <v>28</v>
       </c>
       <c r="F247" s="3" t="s">
-        <v>36</v>
+        <v>335</v>
       </c>
       <c r="G247" s="3"/>
       <c r="H247" s="3"/>
       <c r="I247" s="3"/>
       <c r="J247" s="3"/>
       <c r="K247" s="3"/>
-      <c r="L247" s="3"/>
-      <c r="M247" s="3"/>
-      <c r="N247" s="3"/>
-      <c r="O247" s="6">
-        <v>1</v>
-      </c>
-      <c r="P247" s="6">
-        <v>54</v>
-      </c>
-      <c r="Q247" s="6">
-        <v>63</v>
-      </c>
-      <c r="R247" s="6">
-        <v>66</v>
-      </c>
-      <c r="S247" s="6">
-        <v>70</v>
-      </c>
-      <c r="T247" s="6">
-        <v>75</v>
-      </c>
-      <c r="U247" s="6">
-        <v>80</v>
-      </c>
+      <c r="L247" s="5">
+        <v>6.6</v>
+      </c>
+      <c r="M247" s="5">
+        <v>7.58</v>
+      </c>
+      <c r="N247" s="5">
+        <v>7.54</v>
+      </c>
+      <c r="O247" s="5">
+        <v>10.15</v>
+      </c>
+      <c r="P247" s="5">
+        <v>12.38</v>
+      </c>
+      <c r="Q247" s="5">
+        <v>12.53</v>
+      </c>
+      <c r="R247" s="5">
+        <v>5.95</v>
+      </c>
+      <c r="S247" s="5">
+        <v>4.7300000000000004</v>
+      </c>
+      <c r="T247" s="3"/>
+      <c r="U247" s="3"/>
       <c r="V247" s="3"/>
       <c r="W247" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="248" spans="1:23" ht="18" x14ac:dyDescent="0.25">
+      <c r="A248" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="C248" s="2" t="s">
         <v>337</v>
-      </c>
-    </row>
-    <row r="248" spans="1:23" ht="135" x14ac:dyDescent="0.25">
-      <c r="A248" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="B248" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="C248" s="2" t="s">
-        <v>339</v>
       </c>
       <c r="D248" s="2" t="s">
         <v>27</v>
@@ -16856,7 +16940,7 @@
         <v>28</v>
       </c>
       <c r="F248" s="3" t="s">
-        <v>257</v>
+        <v>36</v>
       </c>
       <c r="G248" s="3"/>
       <c r="H248" s="3"/>
@@ -16866,35 +16950,41 @@
       <c r="L248" s="3"/>
       <c r="M248" s="3"/>
       <c r="N248" s="3"/>
-      <c r="O248" s="3"/>
-      <c r="P248" s="3"/>
-      <c r="Q248" s="3"/>
-      <c r="R248" s="3"/>
+      <c r="O248" s="6">
+        <v>1</v>
+      </c>
+      <c r="P248" s="6">
+        <v>54</v>
+      </c>
+      <c r="Q248" s="6">
+        <v>63</v>
+      </c>
+      <c r="R248" s="6">
+        <v>66</v>
+      </c>
       <c r="S248" s="6">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="T248" s="6">
-        <v>7</v>
+        <v>75</v>
       </c>
       <c r="U248" s="6">
-        <v>6</v>
-      </c>
-      <c r="V248" s="6">
-        <v>4</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="V248" s="3"/>
       <c r="W248" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="249" spans="1:23" ht="135" x14ac:dyDescent="0.25">
+      <c r="A249" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B249" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="C249" s="2" t="s">
         <v>340</v>
-      </c>
-    </row>
-    <row r="249" spans="1:23" ht="36" x14ac:dyDescent="0.25">
-      <c r="A249" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="B249" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="C249" s="2" t="s">
-        <v>341</v>
       </c>
       <c r="D249" s="2" t="s">
         <v>27</v>
@@ -16903,7 +16993,7 @@
         <v>28</v>
       </c>
       <c r="F249" s="3" t="s">
-        <v>342</v>
+        <v>257</v>
       </c>
       <c r="G249" s="3"/>
       <c r="H249" s="3"/>
@@ -16916,107 +17006,85 @@
       <c r="O249" s="3"/>
       <c r="P249" s="3"/>
       <c r="Q249" s="3"/>
-      <c r="R249" s="6">
+      <c r="R249" s="3"/>
+      <c r="S249" s="6">
+        <v>16</v>
+      </c>
+      <c r="T249" s="6">
+        <v>7</v>
+      </c>
+      <c r="U249" s="6">
+        <v>6</v>
+      </c>
+      <c r="V249" s="6">
+        <v>4</v>
+      </c>
+      <c r="W249" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="250" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+      <c r="A250" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="C250" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="D250" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E250" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F250" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="G250" s="3"/>
+      <c r="H250" s="3"/>
+      <c r="I250" s="3"/>
+      <c r="J250" s="3"/>
+      <c r="K250" s="3"/>
+      <c r="L250" s="3"/>
+      <c r="M250" s="3"/>
+      <c r="N250" s="3"/>
+      <c r="O250" s="3"/>
+      <c r="P250" s="3"/>
+      <c r="Q250" s="3"/>
+      <c r="R250" s="6">
         <v>133</v>
       </c>
-      <c r="S249" s="6">
+      <c r="S250" s="6">
         <v>80</v>
       </c>
-      <c r="T249" s="6">
+      <c r="T250" s="6">
         <v>97</v>
       </c>
-      <c r="U249" s="6">
+      <c r="U250" s="6">
         <v>44</v>
-      </c>
-      <c r="V249" s="3"/>
-      <c r="W249" s="2" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="250" spans="1:23" ht="72" x14ac:dyDescent="0.25">
-      <c r="A250" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="B250" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C250" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="D250" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="E250" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="F250" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G250" s="6">
-        <v>40</v>
-      </c>
-      <c r="H250" s="6">
-        <v>60</v>
-      </c>
-      <c r="I250" s="6">
-        <v>40</v>
-      </c>
-      <c r="J250" s="6">
-        <v>40</v>
-      </c>
-      <c r="K250" s="6">
-        <v>40</v>
-      </c>
-      <c r="L250" s="6">
-        <v>40</v>
-      </c>
-      <c r="M250" s="6">
-        <v>60</v>
-      </c>
-      <c r="N250" s="6">
-        <v>40</v>
-      </c>
-      <c r="O250" s="6">
-        <v>40</v>
-      </c>
-      <c r="P250" s="6">
-        <v>40</v>
-      </c>
-      <c r="Q250" s="6">
-        <v>60</v>
-      </c>
-      <c r="R250" s="6">
-        <v>67</v>
-      </c>
-      <c r="S250" s="6">
-        <v>50</v>
-      </c>
-      <c r="T250" s="6">
-        <v>67</v>
-      </c>
-      <c r="U250" s="6">
-        <v>67</v>
       </c>
       <c r="V250" s="3"/>
       <c r="W250" s="2" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
     </row>
     <row r="251" spans="1:23" ht="72" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E251" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F251" s="3" t="s">
         <v>36</v>
@@ -17028,13 +17096,13 @@
         <v>60</v>
       </c>
       <c r="I251" s="6">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="J251" s="6">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K251" s="6">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L251" s="6">
         <v>40</v>
@@ -17046,43 +17114,43 @@
         <v>40</v>
       </c>
       <c r="O251" s="6">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="P251" s="6">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="Q251" s="6">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="R251" s="6">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="S251" s="6">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="T251" s="6">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="U251" s="6">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="V251" s="3"/>
       <c r="W251" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="252" spans="1:23" ht="72" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E252" s="3" t="s">
         <v>351</v>
@@ -17091,10 +17159,10 @@
         <v>36</v>
       </c>
       <c r="G252" s="6">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H252" s="6">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I252" s="6">
         <v>20</v>
@@ -17106,52 +17174,52 @@
         <v>20</v>
       </c>
       <c r="L252" s="6">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M252" s="6">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N252" s="6">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="O252" s="6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="P252" s="6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Q252" s="6">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="R252" s="6">
         <v>17</v>
       </c>
       <c r="S252" s="6">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="T252" s="6">
         <v>17</v>
       </c>
       <c r="U252" s="6">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="V252" s="3"/>
       <c r="W252" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="253" spans="1:23" ht="72" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E253" s="3" t="s">
         <v>352</v>
@@ -17160,133 +17228,133 @@
         <v>36</v>
       </c>
       <c r="G253" s="6">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H253" s="6">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I253" s="6">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="J253" s="6">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="K253" s="6">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="L253" s="6">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M253" s="6">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="N253" s="6">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="O253" s="6">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="P253" s="6">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="Q253" s="6">
         <v>40</v>
       </c>
       <c r="R253" s="6">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="S253" s="6">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="T253" s="6">
         <v>17</v>
       </c>
       <c r="U253" s="6">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="V253" s="3"/>
       <c r="W253" s="2" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="254" spans="1:23" ht="18" x14ac:dyDescent="0.25">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="254" spans="1:23" ht="72" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B254" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="C254" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D254" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="E254" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="C254" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="D254" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E254" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="F254" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="G254" s="4">
-        <v>100</v>
-      </c>
-      <c r="H254" s="4">
-        <v>100.8</v>
-      </c>
-      <c r="I254" s="4">
-        <v>99.9</v>
-      </c>
-      <c r="J254" s="4">
-        <v>101.8</v>
-      </c>
-      <c r="K254" s="4">
-        <v>104.9</v>
-      </c>
-      <c r="L254" s="4">
-        <v>106</v>
-      </c>
-      <c r="M254" s="4">
-        <v>119.9</v>
-      </c>
-      <c r="N254" s="4">
-        <v>119.4</v>
-      </c>
-      <c r="O254" s="4">
-        <v>130</v>
-      </c>
-      <c r="P254" s="4">
-        <v>189.5</v>
-      </c>
-      <c r="Q254" s="4">
-        <v>186.6</v>
-      </c>
-      <c r="R254" s="4">
-        <v>190.1</v>
-      </c>
-      <c r="S254" s="4">
-        <v>200.8</v>
-      </c>
-      <c r="T254" s="4">
-        <v>205.6</v>
-      </c>
-      <c r="U254" s="4">
-        <v>208.5</v>
+        <v>36</v>
+      </c>
+      <c r="G254" s="6">
+        <v>60</v>
+      </c>
+      <c r="H254" s="6">
+        <v>40</v>
+      </c>
+      <c r="I254" s="6">
+        <v>60</v>
+      </c>
+      <c r="J254" s="6">
+        <v>60</v>
+      </c>
+      <c r="K254" s="6">
+        <v>60</v>
+      </c>
+      <c r="L254" s="6">
+        <v>60</v>
+      </c>
+      <c r="M254" s="6">
+        <v>40</v>
+      </c>
+      <c r="N254" s="6">
+        <v>60</v>
+      </c>
+      <c r="O254" s="6">
+        <v>75</v>
+      </c>
+      <c r="P254" s="6">
+        <v>75</v>
+      </c>
+      <c r="Q254" s="6">
+        <v>40</v>
+      </c>
+      <c r="R254" s="6">
+        <v>33</v>
+      </c>
+      <c r="S254" s="6">
+        <v>50</v>
+      </c>
+      <c r="T254" s="6">
+        <v>17</v>
+      </c>
+      <c r="U254" s="6">
+        <v>25</v>
       </c>
       <c r="V254" s="3"/>
       <c r="W254" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="255" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="255" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B255" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="C255" s="2" t="s">
         <v>355</v>
-      </c>
-      <c r="C255" s="2" t="s">
-        <v>356</v>
       </c>
       <c r="D255" s="2" t="s">
         <v>27</v>
@@ -17295,67 +17363,67 @@
         <v>28</v>
       </c>
       <c r="F255" s="3" t="s">
-        <v>357</v>
+        <v>315</v>
       </c>
       <c r="G255" s="4">
-        <v>59.5</v>
+        <v>100</v>
       </c>
       <c r="H255" s="4">
-        <v>57.7</v>
+        <v>100.8</v>
       </c>
       <c r="I255" s="4">
-        <v>58.8</v>
+        <v>99.9</v>
       </c>
       <c r="J255" s="4">
-        <v>64.3</v>
+        <v>101.8</v>
       </c>
       <c r="K255" s="4">
-        <v>68.7</v>
+        <v>104.9</v>
       </c>
       <c r="L255" s="4">
-        <v>69.5</v>
+        <v>106</v>
       </c>
       <c r="M255" s="4">
-        <v>72.900000000000006</v>
+        <v>119.9</v>
       </c>
       <c r="N255" s="4">
-        <v>78.099999999999994</v>
+        <v>119.4</v>
       </c>
       <c r="O255" s="4">
-        <v>91.8</v>
+        <v>130</v>
       </c>
       <c r="P255" s="4">
-        <v>93.9</v>
+        <v>189.5</v>
       </c>
       <c r="Q255" s="4">
-        <v>88.5</v>
+        <v>186.6</v>
       </c>
       <c r="R255" s="4">
-        <v>96.7</v>
+        <v>190.1</v>
       </c>
       <c r="S255" s="4">
-        <v>119</v>
+        <v>200.8</v>
       </c>
       <c r="T255" s="4">
-        <v>136.4</v>
+        <v>205.6</v>
       </c>
       <c r="U255" s="4">
-        <v>124.2</v>
+        <v>208.5</v>
       </c>
       <c r="V255" s="3"/>
       <c r="W255" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="256" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="D256" s="2" t="s">
         <v>27</v>
@@ -17364,67 +17432,67 @@
         <v>28</v>
       </c>
       <c r="F256" s="3" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="G256" s="4">
-        <v>90.8</v>
+        <v>59.5</v>
       </c>
       <c r="H256" s="4">
-        <v>88.8</v>
+        <v>57.7</v>
       </c>
       <c r="I256" s="4">
-        <v>86.5</v>
+        <v>58.8</v>
       </c>
       <c r="J256" s="4">
-        <v>87</v>
+        <v>64.3</v>
       </c>
       <c r="K256" s="4">
-        <v>85</v>
+        <v>68.7</v>
       </c>
       <c r="L256" s="4">
-        <v>87.4</v>
+        <v>69.5</v>
       </c>
       <c r="M256" s="4">
-        <v>88.7</v>
+        <v>72.900000000000006</v>
       </c>
       <c r="N256" s="4">
-        <v>84.6</v>
+        <v>78.099999999999994</v>
       </c>
       <c r="O256" s="4">
-        <v>77.3</v>
+        <v>91.8</v>
       </c>
       <c r="P256" s="4">
-        <v>79.7</v>
+        <v>93.9</v>
       </c>
       <c r="Q256" s="4">
-        <v>81.900000000000006</v>
+        <v>88.5</v>
       </c>
       <c r="R256" s="4">
-        <v>74.8</v>
+        <v>96.7</v>
       </c>
       <c r="S256" s="4">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="T256" s="4">
-        <v>77.2</v>
+        <v>136.4</v>
       </c>
       <c r="U256" s="4">
-        <v>76.3</v>
+        <v>124.2</v>
       </c>
       <c r="V256" s="3"/>
       <c r="W256" s="2" t="s">
-        <v>362</v>
+        <v>30</v>
       </c>
     </row>
     <row r="257" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D257" s="2" t="s">
         <v>27</v>
@@ -17433,67 +17501,67 @@
         <v>28</v>
       </c>
       <c r="F257" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G257" s="7">
-        <v>0.19600000000000001</v>
-      </c>
-      <c r="H257" s="7">
-        <v>0.20499999999999999</v>
-      </c>
-      <c r="I257" s="7">
-        <v>0.20599999999999999</v>
-      </c>
-      <c r="J257" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="K257" s="7">
-        <v>0.20100000000000001</v>
-      </c>
-      <c r="L257" s="7">
-        <v>0.20300000000000001</v>
-      </c>
-      <c r="M257" s="7">
-        <v>0.20699999999999999</v>
-      </c>
-      <c r="N257" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="O257" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="P257" s="7">
-        <v>0.19900000000000001</v>
-      </c>
-      <c r="Q257" s="7">
-        <v>0.2</v>
-      </c>
-      <c r="R257" s="7">
-        <v>0.19900000000000001</v>
-      </c>
-      <c r="S257" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="T257" s="7">
-        <v>0.192</v>
-      </c>
-      <c r="U257" s="7">
-        <v>0.192</v>
+        <v>362</v>
+      </c>
+      <c r="G257" s="4">
+        <v>90.8</v>
+      </c>
+      <c r="H257" s="4">
+        <v>88.8</v>
+      </c>
+      <c r="I257" s="4">
+        <v>86.5</v>
+      </c>
+      <c r="J257" s="4">
+        <v>87</v>
+      </c>
+      <c r="K257" s="4">
+        <v>85</v>
+      </c>
+      <c r="L257" s="4">
+        <v>87.4</v>
+      </c>
+      <c r="M257" s="4">
+        <v>88.7</v>
+      </c>
+      <c r="N257" s="4">
+        <v>84.6</v>
+      </c>
+      <c r="O257" s="4">
+        <v>77.3</v>
+      </c>
+      <c r="P257" s="4">
+        <v>79.7</v>
+      </c>
+      <c r="Q257" s="4">
+        <v>81.900000000000006</v>
+      </c>
+      <c r="R257" s="4">
+        <v>74.8</v>
+      </c>
+      <c r="S257" s="4">
+        <v>77</v>
+      </c>
+      <c r="T257" s="4">
+        <v>77.2</v>
+      </c>
+      <c r="U257" s="4">
+        <v>76.3</v>
       </c>
       <c r="V257" s="3"/>
       <c r="W257" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="258" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D258" s="2" t="s">
         <v>27</v>
@@ -17504,65 +17572,65 @@
       <c r="F258" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G258" s="4">
-        <v>30.5</v>
-      </c>
-      <c r="H258" s="4">
-        <v>30.5</v>
-      </c>
-      <c r="I258" s="4">
-        <v>30.6</v>
-      </c>
-      <c r="J258" s="4">
-        <v>30.6</v>
-      </c>
-      <c r="K258" s="4">
-        <v>30.7</v>
-      </c>
-      <c r="L258" s="4">
-        <v>30.8</v>
-      </c>
-      <c r="M258" s="4">
-        <v>30.8</v>
-      </c>
-      <c r="N258" s="4">
-        <v>30.9</v>
-      </c>
-      <c r="O258" s="4">
-        <v>30.9</v>
-      </c>
-      <c r="P258" s="4">
-        <v>30.9</v>
-      </c>
-      <c r="Q258" s="4">
-        <v>30.9</v>
-      </c>
-      <c r="R258" s="4">
-        <v>30.9</v>
-      </c>
-      <c r="S258" s="4">
-        <v>31</v>
-      </c>
-      <c r="T258" s="4">
-        <v>31</v>
-      </c>
-      <c r="U258" s="4">
-        <v>31</v>
+      <c r="G258" s="7">
+        <v>0.19600000000000001</v>
+      </c>
+      <c r="H258" s="7">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="I258" s="7">
+        <v>0.20599999999999999</v>
+      </c>
+      <c r="J258" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="K258" s="7">
+        <v>0.20100000000000001</v>
+      </c>
+      <c r="L258" s="7">
+        <v>0.20300000000000001</v>
+      </c>
+      <c r="M258" s="7">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="N258" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="O258" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="P258" s="7">
+        <v>0.19900000000000001</v>
+      </c>
+      <c r="Q258" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="R258" s="7">
+        <v>0.19900000000000001</v>
+      </c>
+      <c r="S258" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="T258" s="7">
+        <v>0.192</v>
+      </c>
+      <c r="U258" s="7">
+        <v>0.192</v>
       </c>
       <c r="V258" s="3"/>
       <c r="W258" s="2" t="s">
-        <v>30</v>
+        <v>365</v>
       </c>
     </row>
     <row r="259" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B259" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="C259" s="2" t="s">
         <v>366</v>
-      </c>
-      <c r="C259" s="2" t="s">
-        <v>367</v>
       </c>
       <c r="D259" s="2" t="s">
         <v>27</v>
@@ -17571,190 +17639,190 @@
         <v>28</v>
       </c>
       <c r="F259" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="G259" s="6">
-        <v>28</v>
-      </c>
-      <c r="H259" s="6">
-        <v>27</v>
-      </c>
-      <c r="I259" s="6">
-        <v>26</v>
-      </c>
-      <c r="J259" s="6">
-        <v>25</v>
-      </c>
-      <c r="K259" s="6">
-        <v>24</v>
-      </c>
-      <c r="L259" s="6">
-        <v>23</v>
-      </c>
-      <c r="M259" s="6">
-        <v>22</v>
-      </c>
-      <c r="N259" s="6">
-        <v>22</v>
-      </c>
-      <c r="O259" s="6">
-        <v>22</v>
-      </c>
-      <c r="P259" s="6">
-        <v>21</v>
-      </c>
-      <c r="Q259" s="6">
-        <v>19</v>
-      </c>
-      <c r="R259" s="6">
-        <v>17</v>
-      </c>
-      <c r="S259" s="6">
-        <v>16</v>
-      </c>
-      <c r="T259" s="6">
-        <v>16</v>
-      </c>
-      <c r="U259" s="6">
-        <v>15</v>
+        <v>36</v>
+      </c>
+      <c r="G259" s="4">
+        <v>30.5</v>
+      </c>
+      <c r="H259" s="4">
+        <v>30.5</v>
+      </c>
+      <c r="I259" s="4">
+        <v>30.6</v>
+      </c>
+      <c r="J259" s="4">
+        <v>30.6</v>
+      </c>
+      <c r="K259" s="4">
+        <v>30.7</v>
+      </c>
+      <c r="L259" s="4">
+        <v>30.8</v>
+      </c>
+      <c r="M259" s="4">
+        <v>30.8</v>
+      </c>
+      <c r="N259" s="4">
+        <v>30.9</v>
+      </c>
+      <c r="O259" s="4">
+        <v>30.9</v>
+      </c>
+      <c r="P259" s="4">
+        <v>30.9</v>
+      </c>
+      <c r="Q259" s="4">
+        <v>30.9</v>
+      </c>
+      <c r="R259" s="4">
+        <v>30.9</v>
+      </c>
+      <c r="S259" s="4">
+        <v>31</v>
+      </c>
+      <c r="T259" s="4">
+        <v>31</v>
+      </c>
+      <c r="U259" s="4">
+        <v>31</v>
       </c>
       <c r="V259" s="3"/>
       <c r="W259" s="2" t="s">
-        <v>99</v>
+        <v>30</v>
       </c>
     </row>
     <row r="260" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C260" s="2" t="s">
         <v>368</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E260" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F260" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G260" s="4">
-        <v>64.7</v>
-      </c>
-      <c r="H260" s="4">
-        <v>65.7</v>
-      </c>
-      <c r="I260" s="4">
-        <v>68.599999999999994</v>
-      </c>
-      <c r="J260" s="4">
-        <v>70.3</v>
-      </c>
-      <c r="K260" s="4">
-        <v>71.5</v>
-      </c>
-      <c r="L260" s="4">
-        <v>72.7</v>
-      </c>
-      <c r="M260" s="4">
-        <v>73.5</v>
-      </c>
-      <c r="N260" s="4">
-        <v>73.599999999999994</v>
-      </c>
-      <c r="O260" s="4">
-        <v>74</v>
-      </c>
-      <c r="P260" s="4">
-        <v>74.5</v>
-      </c>
-      <c r="Q260" s="4">
-        <v>74.900000000000006</v>
-      </c>
-      <c r="R260" s="4">
-        <v>75.2</v>
-      </c>
-      <c r="S260" s="4">
-        <v>75.7</v>
-      </c>
-      <c r="T260" s="4">
-        <v>75.900000000000006</v>
-      </c>
-      <c r="U260" s="4">
-        <v>76.2</v>
+        <v>98</v>
+      </c>
+      <c r="G260" s="6">
+        <v>28</v>
+      </c>
+      <c r="H260" s="6">
+        <v>27</v>
+      </c>
+      <c r="I260" s="6">
+        <v>26</v>
+      </c>
+      <c r="J260" s="6">
+        <v>25</v>
+      </c>
+      <c r="K260" s="6">
+        <v>24</v>
+      </c>
+      <c r="L260" s="6">
+        <v>23</v>
+      </c>
+      <c r="M260" s="6">
+        <v>22</v>
+      </c>
+      <c r="N260" s="6">
+        <v>22</v>
+      </c>
+      <c r="O260" s="6">
+        <v>22</v>
+      </c>
+      <c r="P260" s="6">
+        <v>21</v>
+      </c>
+      <c r="Q260" s="6">
+        <v>19</v>
+      </c>
+      <c r="R260" s="6">
+        <v>17</v>
+      </c>
+      <c r="S260" s="6">
+        <v>16</v>
+      </c>
+      <c r="T260" s="6">
+        <v>16</v>
+      </c>
+      <c r="U260" s="6">
+        <v>15</v>
       </c>
       <c r="V260" s="3"/>
       <c r="W260" s="2" t="s">
-        <v>30</v>
+        <v>99</v>
       </c>
     </row>
     <row r="261" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D261" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E261" s="3" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F261" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G261" s="4">
-        <v>88</v>
+        <v>64.7</v>
       </c>
       <c r="H261" s="4">
-        <v>88.4</v>
+        <v>65.7</v>
       </c>
       <c r="I261" s="4">
-        <v>91.7</v>
+        <v>68.599999999999994</v>
       </c>
       <c r="J261" s="4">
-        <v>93.3</v>
+        <v>70.3</v>
       </c>
       <c r="K261" s="4">
-        <v>93.9</v>
+        <v>71.5</v>
       </c>
       <c r="L261" s="4">
-        <v>94.6</v>
+        <v>72.7</v>
       </c>
       <c r="M261" s="4">
-        <v>94.8</v>
+        <v>73.5</v>
       </c>
       <c r="N261" s="4">
-        <v>94.5</v>
+        <v>73.599999999999994</v>
       </c>
       <c r="O261" s="4">
-        <v>94.6</v>
+        <v>74</v>
       </c>
       <c r="P261" s="4">
-        <v>94.8</v>
+        <v>74.5</v>
       </c>
       <c r="Q261" s="4">
-        <v>94.7</v>
+        <v>74.900000000000006</v>
       </c>
       <c r="R261" s="4">
-        <v>94.6</v>
+        <v>75.2</v>
       </c>
       <c r="S261" s="4">
-        <v>95</v>
+        <v>75.7</v>
       </c>
       <c r="T261" s="4">
-        <v>94.8</v>
+        <v>75.900000000000006</v>
       </c>
       <c r="U261" s="4">
-        <v>94.6</v>
+        <v>76.2</v>
       </c>
       <c r="V261" s="3"/>
       <c r="W261" s="2" t="s">
@@ -17763,67 +17831,67 @@
     </row>
     <row r="262" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D262" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E262" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F262" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G262" s="4">
-        <v>28.5</v>
+        <v>88</v>
       </c>
       <c r="H262" s="4">
-        <v>30.6</v>
+        <v>88.4</v>
       </c>
       <c r="I262" s="4">
-        <v>33.1</v>
+        <v>91.7</v>
       </c>
       <c r="J262" s="4">
-        <v>35.299999999999997</v>
+        <v>93.3</v>
       </c>
       <c r="K262" s="4">
-        <v>37.4</v>
+        <v>93.9</v>
       </c>
       <c r="L262" s="4">
-        <v>39.6</v>
+        <v>94.6</v>
       </c>
       <c r="M262" s="4">
-        <v>41.2</v>
+        <v>94.8</v>
       </c>
       <c r="N262" s="4">
-        <v>42</v>
+        <v>94.5</v>
       </c>
       <c r="O262" s="4">
-        <v>42.9</v>
+        <v>94.6</v>
       </c>
       <c r="P262" s="4">
-        <v>44</v>
+        <v>94.8</v>
       </c>
       <c r="Q262" s="4">
-        <v>45.4</v>
+        <v>94.7</v>
       </c>
       <c r="R262" s="4">
-        <v>46.5</v>
+        <v>94.6</v>
       </c>
       <c r="S262" s="4">
-        <v>47.2</v>
+        <v>95</v>
       </c>
       <c r="T262" s="4">
-        <v>48.2</v>
+        <v>94.8</v>
       </c>
       <c r="U262" s="4">
-        <v>49.3</v>
+        <v>94.6</v>
       </c>
       <c r="V262" s="3"/>
       <c r="W262" s="2" t="s">
@@ -17832,82 +17900,82 @@
     </row>
     <row r="263" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C263" s="2" t="s">
         <v>369</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E263" s="3" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F263" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G263" s="4">
-        <v>65.7</v>
+        <v>28.5</v>
       </c>
       <c r="H263" s="4">
-        <v>64.8</v>
+        <v>30.6</v>
       </c>
       <c r="I263" s="4">
-        <v>67.400000000000006</v>
+        <v>33.1</v>
       </c>
       <c r="J263" s="4">
-        <v>69.8</v>
+        <v>35.299999999999997</v>
       </c>
       <c r="K263" s="4">
-        <v>70.5</v>
+        <v>37.4</v>
       </c>
       <c r="L263" s="4">
-        <v>70.900000000000006</v>
+        <v>39.6</v>
       </c>
       <c r="M263" s="4">
-        <v>71.400000000000006</v>
+        <v>41.2</v>
       </c>
       <c r="N263" s="4">
-        <v>72.5</v>
+        <v>42</v>
       </c>
       <c r="O263" s="4">
-        <v>73.2</v>
+        <v>42.9</v>
       </c>
       <c r="P263" s="4">
-        <v>73.900000000000006</v>
+        <v>44</v>
       </c>
       <c r="Q263" s="4">
-        <v>73.3</v>
+        <v>45.4</v>
       </c>
       <c r="R263" s="4">
-        <v>72.8</v>
+        <v>46.5</v>
       </c>
       <c r="S263" s="4">
-        <v>76.3</v>
+        <v>47.2</v>
       </c>
       <c r="T263" s="4">
-        <v>78.099999999999994</v>
+        <v>48.2</v>
       </c>
       <c r="U263" s="4">
-        <v>78.599999999999994</v>
+        <v>49.3</v>
       </c>
       <c r="V263" s="3"/>
       <c r="W263" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="264" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B264" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="C264" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="C264" s="2" t="s">
-        <v>371</v>
       </c>
       <c r="D264" s="2" t="s">
         <v>27</v>
@@ -17916,52 +17984,52 @@
         <v>28</v>
       </c>
       <c r="F264" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="G264" s="6">
-        <v>70108</v>
-      </c>
-      <c r="H264" s="6">
-        <v>248240</v>
-      </c>
-      <c r="I264" s="6">
-        <v>168221</v>
-      </c>
-      <c r="J264" s="6">
-        <v>72837</v>
-      </c>
-      <c r="K264" s="6">
-        <v>64283</v>
-      </c>
-      <c r="L264" s="6">
-        <v>68694</v>
-      </c>
-      <c r="M264" s="6">
-        <v>60135</v>
-      </c>
-      <c r="N264" s="6">
-        <v>46337</v>
-      </c>
-      <c r="O264" s="6">
-        <v>50289</v>
-      </c>
-      <c r="P264" s="6">
-        <v>104107</v>
-      </c>
-      <c r="Q264" s="6">
-        <v>201963</v>
-      </c>
-      <c r="R264" s="6">
-        <v>84506</v>
-      </c>
-      <c r="S264" s="6">
-        <v>295948</v>
-      </c>
-      <c r="T264" s="6">
-        <v>123796</v>
-      </c>
-      <c r="U264" s="6">
-        <v>104040</v>
+        <v>36</v>
+      </c>
+      <c r="G264" s="4">
+        <v>65.7</v>
+      </c>
+      <c r="H264" s="4">
+        <v>64.8</v>
+      </c>
+      <c r="I264" s="4">
+        <v>67.400000000000006</v>
+      </c>
+      <c r="J264" s="4">
+        <v>69.8</v>
+      </c>
+      <c r="K264" s="4">
+        <v>70.5</v>
+      </c>
+      <c r="L264" s="4">
+        <v>70.900000000000006</v>
+      </c>
+      <c r="M264" s="4">
+        <v>71.400000000000006</v>
+      </c>
+      <c r="N264" s="4">
+        <v>72.5</v>
+      </c>
+      <c r="O264" s="4">
+        <v>73.2</v>
+      </c>
+      <c r="P264" s="4">
+        <v>73.900000000000006</v>
+      </c>
+      <c r="Q264" s="4">
+        <v>73.3</v>
+      </c>
+      <c r="R264" s="4">
+        <v>72.8</v>
+      </c>
+      <c r="S264" s="4">
+        <v>76.3</v>
+      </c>
+      <c r="T264" s="4">
+        <v>78.099999999999994</v>
+      </c>
+      <c r="U264" s="4">
+        <v>78.599999999999994</v>
       </c>
       <c r="V264" s="3"/>
       <c r="W264" s="2" t="s">
@@ -17970,13 +18038,13 @@
     </row>
     <row r="265" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D265" s="2" t="s">
         <v>27</v>
@@ -17985,52 +18053,52 @@
         <v>28</v>
       </c>
       <c r="F265" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G265" s="4">
-        <v>2.9</v>
-      </c>
-      <c r="H265" s="4">
-        <v>3.8</v>
-      </c>
-      <c r="I265" s="4">
-        <v>6</v>
-      </c>
-      <c r="J265" s="4">
-        <v>4.3</v>
-      </c>
-      <c r="K265" s="4">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="L265" s="4">
-        <v>4.2</v>
-      </c>
-      <c r="M265" s="4">
-        <v>3.1</v>
-      </c>
-      <c r="N265" s="4">
-        <v>3</v>
-      </c>
-      <c r="O265" s="4">
-        <v>3.2</v>
-      </c>
-      <c r="P265" s="4">
-        <v>3.4</v>
-      </c>
-      <c r="Q265" s="4">
-        <v>3.2</v>
-      </c>
-      <c r="R265" s="4">
-        <v>4.5</v>
-      </c>
-      <c r="S265" s="4">
-        <v>6.6</v>
-      </c>
-      <c r="T265" s="4">
-        <v>5.8</v>
-      </c>
-      <c r="U265" s="4">
-        <v>4.5</v>
+        <v>373</v>
+      </c>
+      <c r="G265" s="6">
+        <v>70108</v>
+      </c>
+      <c r="H265" s="6">
+        <v>248240</v>
+      </c>
+      <c r="I265" s="6">
+        <v>168221</v>
+      </c>
+      <c r="J265" s="6">
+        <v>72837</v>
+      </c>
+      <c r="K265" s="6">
+        <v>64283</v>
+      </c>
+      <c r="L265" s="6">
+        <v>68694</v>
+      </c>
+      <c r="M265" s="6">
+        <v>60135</v>
+      </c>
+      <c r="N265" s="6">
+        <v>46337</v>
+      </c>
+      <c r="O265" s="6">
+        <v>50289</v>
+      </c>
+      <c r="P265" s="6">
+        <v>104107</v>
+      </c>
+      <c r="Q265" s="6">
+        <v>201963</v>
+      </c>
+      <c r="R265" s="6">
+        <v>84506</v>
+      </c>
+      <c r="S265" s="6">
+        <v>295948</v>
+      </c>
+      <c r="T265" s="6">
+        <v>123796</v>
+      </c>
+      <c r="U265" s="6">
+        <v>104040</v>
       </c>
       <c r="V265" s="3"/>
       <c r="W265" s="2" t="s">
@@ -18039,13 +18107,13 @@
     </row>
     <row r="266" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B266" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C266" s="2" t="s">
         <v>374</v>
-      </c>
-      <c r="B266" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="C266" s="2" t="s">
-        <v>376</v>
       </c>
       <c r="D266" s="2" t="s">
         <v>27</v>
@@ -18056,65 +18124,65 @@
       <c r="F266" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G266" s="6">
-        <v>70</v>
-      </c>
-      <c r="H266" s="6">
-        <v>75</v>
-      </c>
-      <c r="I266" s="6">
-        <v>66</v>
-      </c>
-      <c r="J266" s="6">
-        <v>64</v>
-      </c>
-      <c r="K266" s="6">
-        <v>70</v>
-      </c>
-      <c r="L266" s="6">
-        <v>66</v>
-      </c>
-      <c r="M266" s="6">
-        <v>80</v>
-      </c>
-      <c r="N266" s="6">
-        <v>89</v>
-      </c>
-      <c r="O266" s="6">
-        <v>86</v>
-      </c>
-      <c r="P266" s="6">
-        <v>89</v>
-      </c>
-      <c r="Q266" s="6">
-        <v>85</v>
-      </c>
-      <c r="R266" s="6">
-        <v>82</v>
-      </c>
-      <c r="S266" s="6">
-        <v>83</v>
-      </c>
-      <c r="T266" s="6">
-        <v>88</v>
-      </c>
-      <c r="U266" s="6">
-        <v>88</v>
+      <c r="G266" s="4">
+        <v>2.9</v>
+      </c>
+      <c r="H266" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="I266" s="4">
+        <v>6</v>
+      </c>
+      <c r="J266" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="K266" s="4">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="L266" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="M266" s="4">
+        <v>3.1</v>
+      </c>
+      <c r="N266" s="4">
+        <v>3</v>
+      </c>
+      <c r="O266" s="4">
+        <v>3.2</v>
+      </c>
+      <c r="P266" s="4">
+        <v>3.4</v>
+      </c>
+      <c r="Q266" s="4">
+        <v>3.2</v>
+      </c>
+      <c r="R266" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="S266" s="4">
+        <v>6.6</v>
+      </c>
+      <c r="T266" s="4">
+        <v>5.8</v>
+      </c>
+      <c r="U266" s="4">
+        <v>4.5</v>
       </c>
       <c r="V266" s="3"/>
       <c r="W266" s="2" t="s">
-        <v>377</v>
+        <v>30</v>
       </c>
     </row>
     <row r="267" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D267" s="2" t="s">
         <v>27</v>
@@ -18126,50 +18194,66 @@
         <v>36</v>
       </c>
       <c r="G267" s="6">
-        <v>55</v>
-      </c>
-      <c r="H267" s="3"/>
+        <v>70</v>
+      </c>
+      <c r="H267" s="6">
+        <v>75</v>
+      </c>
       <c r="I267" s="6">
-        <v>58</v>
-      </c>
-      <c r="J267" s="3"/>
+        <v>66</v>
+      </c>
+      <c r="J267" s="6">
+        <v>64</v>
+      </c>
       <c r="K267" s="6">
-        <v>60</v>
-      </c>
-      <c r="L267" s="3"/>
+        <v>70</v>
+      </c>
+      <c r="L267" s="6">
+        <v>66</v>
+      </c>
       <c r="M267" s="6">
-        <v>64</v>
-      </c>
-      <c r="N267" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="N267" s="6">
+        <v>89</v>
+      </c>
       <c r="O267" s="6">
-        <v>65</v>
-      </c>
-      <c r="P267" s="3"/>
+        <v>86</v>
+      </c>
+      <c r="P267" s="6">
+        <v>89</v>
+      </c>
       <c r="Q267" s="6">
-        <v>74</v>
-      </c>
-      <c r="R267" s="3"/>
+        <v>85</v>
+      </c>
+      <c r="R267" s="6">
+        <v>82</v>
+      </c>
       <c r="S267" s="6">
-        <v>63</v>
-      </c>
-      <c r="T267" s="3"/>
+        <v>83</v>
+      </c>
+      <c r="T267" s="6">
+        <v>88</v>
+      </c>
       <c r="U267" s="6">
-        <v>71</v>
-      </c>
-      <c r="V267" s="3"/>
+        <v>88</v>
+      </c>
+      <c r="V267" s="6">
+        <v>86</v>
+      </c>
       <c r="W267" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="268" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B268" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="C268" s="2" t="s">
         <v>379</v>
-      </c>
-      <c r="C268" s="2" t="s">
-        <v>380</v>
       </c>
       <c r="D268" s="2" t="s">
         <v>27</v>
@@ -18178,65 +18262,53 @@
         <v>28</v>
       </c>
       <c r="F268" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="G268" s="5">
-        <v>1.02</v>
-      </c>
-      <c r="H268" s="5">
-        <v>0.96</v>
-      </c>
-      <c r="I268" s="5">
-        <v>1</v>
-      </c>
-      <c r="J268" s="5">
-        <v>1.05</v>
-      </c>
-      <c r="K268" s="5">
-        <v>1.06</v>
-      </c>
-      <c r="L268" s="5">
-        <v>0.95</v>
-      </c>
-      <c r="M268" s="5">
-        <v>0.91</v>
-      </c>
-      <c r="N268" s="5">
-        <v>0.81</v>
-      </c>
-      <c r="O268" s="5">
-        <v>0.87</v>
-      </c>
-      <c r="P268" s="5">
-        <v>1.01</v>
-      </c>
-      <c r="Q268" s="5">
-        <v>0.85</v>
-      </c>
-      <c r="R268" s="5">
-        <v>0.83</v>
-      </c>
-      <c r="S268" s="5">
-        <v>0.72</v>
-      </c>
-      <c r="T268" s="5">
-        <v>0.78</v>
-      </c>
-      <c r="U268" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="G268" s="6">
+        <v>55</v>
+      </c>
+      <c r="H268" s="3"/>
+      <c r="I268" s="6">
+        <v>58</v>
+      </c>
+      <c r="J268" s="3"/>
+      <c r="K268" s="6">
+        <v>60</v>
+      </c>
+      <c r="L268" s="3"/>
+      <c r="M268" s="6">
+        <v>64</v>
+      </c>
+      <c r="N268" s="3"/>
+      <c r="O268" s="6">
+        <v>65</v>
+      </c>
+      <c r="P268" s="3"/>
+      <c r="Q268" s="6">
+        <v>74</v>
+      </c>
+      <c r="R268" s="3"/>
+      <c r="S268" s="6">
+        <v>63</v>
+      </c>
+      <c r="T268" s="3"/>
+      <c r="U268" s="6">
+        <v>71</v>
+      </c>
       <c r="V268" s="3"/>
       <c r="W268" s="2" t="s">
-        <v>198</v>
+        <v>378</v>
       </c>
     </row>
     <row r="269" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B269" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="C269" s="2" t="s">
         <v>381</v>
-      </c>
-      <c r="C269" s="2" t="s">
-        <v>382</v>
       </c>
       <c r="D269" s="2" t="s">
         <v>27</v>
@@ -18245,70 +18317,70 @@
         <v>28</v>
       </c>
       <c r="F269" s="3" t="s">
-        <v>36</v>
+        <v>246</v>
       </c>
       <c r="G269" s="5">
-        <v>1.84</v>
+        <v>1.02</v>
       </c>
       <c r="H269" s="5">
-        <v>1.79</v>
+        <v>0.96</v>
       </c>
       <c r="I269" s="5">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J269" s="5">
-        <v>1.79</v>
+        <v>1.05</v>
       </c>
       <c r="K269" s="5">
-        <v>1.86</v>
+        <v>1.06</v>
       </c>
       <c r="L269" s="5">
-        <v>2.21</v>
+        <v>0.95</v>
       </c>
       <c r="M269" s="5">
-        <v>1.99</v>
+        <v>0.91</v>
       </c>
       <c r="N269" s="5">
-        <v>1.88</v>
+        <v>0.81</v>
       </c>
       <c r="O269" s="5">
-        <v>2</v>
+        <v>0.87</v>
       </c>
       <c r="P269" s="5">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="Q269" s="5">
-        <v>2.21</v>
+        <v>0.85</v>
       </c>
       <c r="R269" s="5">
-        <v>2.19</v>
+        <v>0.83</v>
       </c>
       <c r="S269" s="5">
-        <v>2.21</v>
+        <v>0.72</v>
       </c>
       <c r="T269" s="5">
-        <v>3.27</v>
+        <v>0.78</v>
       </c>
       <c r="U269" s="5">
-        <v>4.07</v>
+        <v>0.69</v>
       </c>
       <c r="V269" s="3"/>
       <c r="W269" s="2" t="s">
-        <v>383</v>
+        <v>198</v>
       </c>
     </row>
     <row r="270" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="E270" s="3" t="s">
         <v>28</v>
@@ -18316,65 +18388,71 @@
       <c r="F270" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G270" s="6">
-        <v>10</v>
-      </c>
-      <c r="H270" s="6">
-        <v>9</v>
-      </c>
-      <c r="I270" s="6">
-        <v>11</v>
-      </c>
-      <c r="J270" s="6">
-        <v>11</v>
-      </c>
-      <c r="K270" s="6">
-        <v>15</v>
-      </c>
-      <c r="L270" s="6">
-        <v>16</v>
-      </c>
-      <c r="M270" s="6">
-        <v>19</v>
-      </c>
-      <c r="N270" s="6">
-        <v>21</v>
-      </c>
-      <c r="O270" s="6">
-        <v>25</v>
-      </c>
-      <c r="P270" s="6">
-        <v>31</v>
-      </c>
-      <c r="Q270" s="6">
-        <v>34</v>
-      </c>
-      <c r="R270" s="6">
-        <v>40</v>
-      </c>
-      <c r="S270" s="3"/>
-      <c r="T270" s="3"/>
-      <c r="U270" s="3"/>
+      <c r="G270" s="5">
+        <v>1.84</v>
+      </c>
+      <c r="H270" s="5">
+        <v>1.79</v>
+      </c>
+      <c r="I270" s="5">
+        <v>1.8</v>
+      </c>
+      <c r="J270" s="5">
+        <v>1.79</v>
+      </c>
+      <c r="K270" s="5">
+        <v>1.86</v>
+      </c>
+      <c r="L270" s="5">
+        <v>2.21</v>
+      </c>
+      <c r="M270" s="5">
+        <v>1.99</v>
+      </c>
+      <c r="N270" s="5">
+        <v>1.88</v>
+      </c>
+      <c r="O270" s="5">
+        <v>2</v>
+      </c>
+      <c r="P270" s="5">
+        <v>1.96</v>
+      </c>
+      <c r="Q270" s="5">
+        <v>2.21</v>
+      </c>
+      <c r="R270" s="5">
+        <v>2.19</v>
+      </c>
+      <c r="S270" s="5">
+        <v>2.21</v>
+      </c>
+      <c r="T270" s="5">
+        <v>3.27</v>
+      </c>
+      <c r="U270" s="5">
+        <v>4.07</v>
+      </c>
       <c r="V270" s="3"/>
       <c r="W270" s="2" t="s">
-        <v>30</v>
+        <v>384</v>
       </c>
     </row>
     <row r="271" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D271" s="2" t="s">
         <v>62</v>
       </c>
       <c r="E271" s="3" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="F271" s="3" t="s">
         <v>36</v>
@@ -18389,13 +18467,13 @@
         <v>11</v>
       </c>
       <c r="J271" s="6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K271" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L271" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M271" s="6">
         <v>19</v>
@@ -18404,16 +18482,16 @@
         <v>21</v>
       </c>
       <c r="O271" s="6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P271" s="6">
         <v>31</v>
       </c>
       <c r="Q271" s="6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R271" s="6">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S271" s="3"/>
       <c r="T271" s="3"/>
@@ -18425,19 +18503,19 @@
     </row>
     <row r="272" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D272" s="2" t="s">
         <v>62</v>
       </c>
       <c r="E272" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F272" s="3" t="s">
         <v>36</v>
@@ -18449,16 +18527,16 @@
         <v>9</v>
       </c>
       <c r="I272" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J272" s="6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K272" s="6">
+        <v>14</v>
+      </c>
+      <c r="L272" s="6">
         <v>15</v>
-      </c>
-      <c r="L272" s="6">
-        <v>16</v>
       </c>
       <c r="M272" s="6">
         <v>19</v>
@@ -18467,16 +18545,16 @@
         <v>21</v>
       </c>
       <c r="O272" s="6">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="P272" s="6">
+        <v>31</v>
+      </c>
+      <c r="Q272" s="6">
         <v>32</v>
       </c>
-      <c r="Q272" s="6">
-        <v>35</v>
-      </c>
       <c r="R272" s="6">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="S272" s="3"/>
       <c r="T272" s="3"/>
@@ -18488,58 +18566,58 @@
     </row>
     <row r="273" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="E273" s="3" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="F273" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G273" s="6">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H273" s="6">
+        <v>9</v>
+      </c>
+      <c r="I273" s="6">
+        <v>10</v>
+      </c>
+      <c r="J273" s="6">
         <v>11</v>
       </c>
-      <c r="I273" s="6">
-        <v>13</v>
-      </c>
-      <c r="J273" s="6">
+      <c r="K273" s="6">
         <v>15</v>
       </c>
-      <c r="K273" s="6">
-        <v>18</v>
-      </c>
       <c r="L273" s="6">
+        <v>16</v>
+      </c>
+      <c r="M273" s="6">
         <v>19</v>
       </c>
-      <c r="M273" s="6">
-        <v>23</v>
-      </c>
       <c r="N273" s="6">
+        <v>21</v>
+      </c>
+      <c r="O273" s="6">
         <v>26</v>
       </c>
-      <c r="O273" s="6">
-        <v>30</v>
-      </c>
       <c r="P273" s="6">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="Q273" s="6">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="R273" s="6">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="S273" s="3"/>
       <c r="T273" s="3"/>
@@ -18551,58 +18629,58 @@
     </row>
     <row r="274" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D274" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E274" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F274" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G274" s="6">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H274" s="6">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I274" s="6">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J274" s="6">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="K274" s="6">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="L274" s="6">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="M274" s="6">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="N274" s="6">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="O274" s="6">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="P274" s="6">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="Q274" s="6">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="R274" s="6">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="S274" s="3"/>
       <c r="T274" s="3"/>
@@ -18614,58 +18692,58 @@
     </row>
     <row r="275" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="E275" s="3" t="s">
-        <v>139</v>
+        <v>39</v>
       </c>
       <c r="F275" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G275" s="6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H275" s="6">
+        <v>5</v>
+      </c>
+      <c r="I275" s="6">
         <v>6</v>
       </c>
-      <c r="I275" s="6">
-        <v>8</v>
-      </c>
       <c r="J275" s="6">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K275" s="6">
         <v>9</v>
       </c>
       <c r="L275" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M275" s="6">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="N275" s="6">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O275" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P275" s="6">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Q275" s="6">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="R275" s="6">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="S275" s="3"/>
       <c r="T275" s="3"/>
@@ -18677,58 +18755,58 @@
     </row>
     <row r="276" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D276" s="2" t="s">
         <v>80</v>
       </c>
       <c r="E276" s="3" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="F276" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G276" s="6">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H276" s="6">
+        <v>6</v>
+      </c>
+      <c r="I276" s="6">
+        <v>8</v>
+      </c>
+      <c r="J276" s="6">
+        <v>9</v>
+      </c>
+      <c r="K276" s="6">
+        <v>9</v>
+      </c>
+      <c r="L276" s="6">
+        <v>8</v>
+      </c>
+      <c r="M276" s="6">
+        <v>9</v>
+      </c>
+      <c r="N276" s="6">
+        <v>11</v>
+      </c>
+      <c r="O276" s="6">
         <v>16</v>
       </c>
-      <c r="I276" s="6">
-        <v>19</v>
-      </c>
-      <c r="J276" s="6">
-        <v>20</v>
-      </c>
-      <c r="K276" s="6">
-        <v>28</v>
-      </c>
-      <c r="L276" s="6">
-        <v>28</v>
-      </c>
-      <c r="M276" s="6">
-        <v>32</v>
-      </c>
-      <c r="N276" s="6">
-        <v>35</v>
-      </c>
-      <c r="O276" s="6">
-        <v>39</v>
-      </c>
       <c r="P276" s="6">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="Q276" s="6">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="R276" s="6">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="S276" s="3"/>
       <c r="T276" s="3"/>
@@ -18740,58 +18818,58 @@
     </row>
     <row r="277" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D277" s="2" t="s">
         <v>80</v>
       </c>
       <c r="E277" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F277" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G277" s="6">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H277" s="6">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I277" s="6">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J277" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K277" s="6">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="L277" s="6">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M277" s="6">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="N277" s="6">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="O277" s="6">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="P277" s="6">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q277" s="6">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="R277" s="6">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="S277" s="3"/>
       <c r="T277" s="3"/>
@@ -18803,58 +18881,58 @@
     </row>
     <row r="278" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D278" s="2" t="s">
         <v>80</v>
       </c>
       <c r="E278" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F278" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G278" s="6">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H278" s="6">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I278" s="6">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="J278" s="6">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="K278" s="6">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="L278" s="6">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="M278" s="6">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="N278" s="6">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="O278" s="6">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="P278" s="6">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="Q278" s="6">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="R278" s="6">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="S278" s="3"/>
       <c r="T278" s="3"/>
@@ -18866,58 +18944,58 @@
     </row>
     <row r="279" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D279" s="2" t="s">
         <v>80</v>
       </c>
       <c r="E279" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F279" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G279" s="6">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H279" s="6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I279" s="6">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J279" s="6">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K279" s="6">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="L279" s="6">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M279" s="6">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="N279" s="6">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="O279" s="6">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="P279" s="6">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="Q279" s="6">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R279" s="6">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="S279" s="3"/>
       <c r="T279" s="3"/>
@@ -18929,58 +19007,58 @@
     </row>
     <row r="280" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D280" s="2" t="s">
         <v>80</v>
       </c>
       <c r="E280" s="3" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="F280" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G280" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H280" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I280" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J280" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K280" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L280" s="6">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M280" s="6">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="N280" s="6">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="O280" s="6">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="P280" s="6">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="Q280" s="6">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="R280" s="6">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="S280" s="3"/>
       <c r="T280" s="3"/>
@@ -18992,58 +19070,58 @@
     </row>
     <row r="281" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>141</v>
+        <v>80</v>
       </c>
       <c r="E281" s="3" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="F281" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G281" s="6">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="H281" s="6">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="I281" s="6">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="J281" s="6">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="K281" s="6">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="L281" s="6">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="M281" s="6">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="N281" s="6">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="O281" s="6">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="P281" s="6">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="Q281" s="6">
-        <v>62</v>
+        <v>9</v>
       </c>
       <c r="R281" s="6">
-        <v>71</v>
+        <v>11</v>
       </c>
       <c r="S281" s="3"/>
       <c r="T281" s="3"/>
@@ -19055,58 +19133,58 @@
     </row>
     <row r="282" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D282" s="2" t="s">
         <v>141</v>
       </c>
       <c r="E282" s="3" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="F282" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G282" s="6">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="H282" s="6">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="I282" s="6">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="J282" s="6">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="K282" s="6">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="L282" s="6">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="M282" s="6">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="N282" s="6">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="O282" s="6">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="P282" s="6">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="Q282" s="6">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="R282" s="6">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="S282" s="3"/>
       <c r="T282" s="3"/>
@@ -19118,58 +19196,58 @@
     </row>
     <row r="283" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D283" s="2" t="s">
         <v>141</v>
       </c>
       <c r="E283" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F283" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G283" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H283" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I283" s="6">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J283" s="6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K283" s="6">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L283" s="6">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="M283" s="6">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="N283" s="6">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="O283" s="6">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="P283" s="6">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="Q283" s="6">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="R283" s="6">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="S283" s="3"/>
       <c r="T283" s="3"/>
@@ -19181,58 +19259,58 @@
     </row>
     <row r="284" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E284" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F284" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G284" s="6">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H284" s="6">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I284" s="6">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="J284" s="6">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="K284" s="6">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="L284" s="6">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="M284" s="6">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="N284" s="6">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="O284" s="6">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="P284" s="6">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="Q284" s="6">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="R284" s="6">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="S284" s="3"/>
       <c r="T284" s="3"/>
@@ -19244,58 +19322,58 @@
     </row>
     <row r="285" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D285" s="2" t="s">
         <v>144</v>
       </c>
       <c r="E285" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F285" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G285" s="6">
+        <v>14</v>
+      </c>
+      <c r="H285" s="6">
+        <v>13</v>
+      </c>
+      <c r="I285" s="6">
         <v>15</v>
       </c>
-      <c r="H285" s="6">
-        <v>14</v>
-      </c>
-      <c r="I285" s="6">
-        <v>16</v>
-      </c>
       <c r="J285" s="6">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K285" s="6">
+        <v>21</v>
+      </c>
+      <c r="L285" s="6">
         <v>23</v>
       </c>
-      <c r="L285" s="6">
+      <c r="M285" s="6">
         <v>25</v>
       </c>
-      <c r="M285" s="6">
-        <v>27</v>
-      </c>
       <c r="N285" s="6">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O285" s="6">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P285" s="6">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q285" s="6">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="R285" s="6">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="S285" s="3"/>
       <c r="T285" s="3"/>
@@ -19307,58 +19385,58 @@
     </row>
     <row r="286" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D286" s="2" t="s">
         <v>144</v>
       </c>
       <c r="E286" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F286" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G286" s="6">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H286" s="6">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I286" s="6">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J286" s="6">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="K286" s="6">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="L286" s="6">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="M286" s="6">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="N286" s="6">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="O286" s="6">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="P286" s="6">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="Q286" s="6">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="R286" s="6">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="S286" s="3"/>
       <c r="T286" s="3"/>
@@ -19370,58 +19448,58 @@
     </row>
     <row r="287" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D287" s="2" t="s">
         <v>144</v>
       </c>
       <c r="E287" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F287" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G287" s="6">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H287" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I287" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J287" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K287" s="6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L287" s="6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M287" s="6">
         <v>7</v>
       </c>
       <c r="N287" s="6">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O287" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P287" s="6">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="Q287" s="6">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="R287" s="6">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="S287" s="3"/>
       <c r="T287" s="3"/>
@@ -19433,82 +19511,76 @@
     </row>
     <row r="288" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B288" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C288" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="C288" s="2" t="s">
-        <v>387</v>
-      </c>
       <c r="D288" s="2" t="s">
-        <v>27</v>
+        <v>144</v>
       </c>
       <c r="E288" s="3" t="s">
-        <v>28</v>
+        <v>148</v>
       </c>
       <c r="F288" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G288" s="4">
-        <v>5.7</v>
-      </c>
-      <c r="H288" s="4">
-        <v>6</v>
-      </c>
-      <c r="I288" s="4">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="J288" s="4">
-        <v>4.3</v>
-      </c>
-      <c r="K288" s="4">
-        <v>4.7</v>
-      </c>
-      <c r="L288" s="4">
-        <v>4.5</v>
-      </c>
-      <c r="M288" s="4">
-        <v>3.3</v>
-      </c>
-      <c r="N288" s="4">
-        <v>3.8</v>
-      </c>
-      <c r="O288" s="4">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="P288" s="4">
-        <v>4.3</v>
-      </c>
-      <c r="Q288" s="4">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="R288" s="4">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="S288" s="4">
-        <v>3.8</v>
-      </c>
-      <c r="T288" s="4">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="U288" s="4">
-        <v>4.8</v>
-      </c>
+      <c r="G288" s="6">
+        <v>4</v>
+      </c>
+      <c r="H288" s="6">
+        <v>3</v>
+      </c>
+      <c r="I288" s="6">
+        <v>5</v>
+      </c>
+      <c r="J288" s="6">
+        <v>4</v>
+      </c>
+      <c r="K288" s="6">
+        <v>5</v>
+      </c>
+      <c r="L288" s="6">
+        <v>5</v>
+      </c>
+      <c r="M288" s="6">
+        <v>7</v>
+      </c>
+      <c r="N288" s="6">
+        <v>8</v>
+      </c>
+      <c r="O288" s="6">
+        <v>9</v>
+      </c>
+      <c r="P288" s="6">
+        <v>12</v>
+      </c>
+      <c r="Q288" s="6">
+        <v>14</v>
+      </c>
+      <c r="R288" s="6">
+        <v>17</v>
+      </c>
+      <c r="S288" s="3"/>
+      <c r="T288" s="3"/>
+      <c r="U288" s="3"/>
       <c r="V288" s="3"/>
       <c r="W288" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="289" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B289" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C289" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="B289" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="C289" s="2" t="s">
-        <v>390</v>
       </c>
       <c r="D289" s="2" t="s">
         <v>27</v>
@@ -19517,67 +19589,67 @@
         <v>28</v>
       </c>
       <c r="F289" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="G289" s="5">
-        <v>377.75</v>
-      </c>
-      <c r="H289" s="5">
-        <v>417.47</v>
-      </c>
-      <c r="I289" s="5">
-        <v>421.06</v>
-      </c>
-      <c r="J289" s="5">
-        <v>487.12</v>
-      </c>
-      <c r="K289" s="5">
-        <v>451.84</v>
-      </c>
-      <c r="L289" s="5">
-        <v>440.89</v>
-      </c>
-      <c r="M289" s="5">
-        <v>662.95</v>
-      </c>
-      <c r="N289" s="5">
-        <v>679.46</v>
-      </c>
-      <c r="O289" s="5">
-        <v>766.04</v>
-      </c>
-      <c r="P289" s="5">
-        <v>776.56</v>
-      </c>
-      <c r="Q289" s="5">
-        <v>829.27</v>
-      </c>
-      <c r="R289" s="5">
-        <v>983.51</v>
-      </c>
-      <c r="S289" s="5">
-        <v>3494.39</v>
-      </c>
-      <c r="T289" s="5">
-        <v>2580.38</v>
-      </c>
-      <c r="U289" s="5">
-        <v>1840.15</v>
+        <v>36</v>
+      </c>
+      <c r="G289" s="4">
+        <v>5.7</v>
+      </c>
+      <c r="H289" s="4">
+        <v>6</v>
+      </c>
+      <c r="I289" s="4">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="J289" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="K289" s="4">
+        <v>4.7</v>
+      </c>
+      <c r="L289" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="M289" s="4">
+        <v>3.3</v>
+      </c>
+      <c r="N289" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="O289" s="4">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="P289" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="Q289" s="4">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="R289" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="S289" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="T289" s="4">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="U289" s="4">
+        <v>4.8</v>
       </c>
       <c r="V289" s="3"/>
       <c r="W289" s="2" t="s">
-        <v>392</v>
+        <v>30</v>
       </c>
     </row>
     <row r="290" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="D290" s="2" t="s">
         <v>27</v>
@@ -19586,67 +19658,67 @@
         <v>28</v>
       </c>
       <c r="F290" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="G290" s="5">
-        <v>96.04</v>
+        <v>377.75</v>
       </c>
       <c r="H290" s="5">
-        <v>90.68</v>
+        <v>417.47</v>
       </c>
       <c r="I290" s="5">
-        <v>111.55</v>
+        <v>421.06</v>
       </c>
       <c r="J290" s="5">
-        <v>127.11</v>
+        <v>487.12</v>
       </c>
       <c r="K290" s="5">
-        <v>82.28</v>
+        <v>451.84</v>
       </c>
       <c r="L290" s="5">
-        <v>100.19</v>
+        <v>440.89</v>
       </c>
       <c r="M290" s="5">
-        <v>148.99</v>
+        <v>662.95</v>
       </c>
       <c r="N290" s="5">
-        <v>222.11</v>
+        <v>679.46</v>
       </c>
       <c r="O290" s="5">
-        <v>244.93</v>
+        <v>766.04</v>
       </c>
       <c r="P290" s="5">
-        <v>223.31</v>
+        <v>776.56</v>
       </c>
       <c r="Q290" s="5">
-        <v>225.08</v>
+        <v>829.27</v>
       </c>
       <c r="R290" s="5">
-        <v>296.20999999999998</v>
+        <v>983.51</v>
       </c>
       <c r="S290" s="5">
-        <v>2661.32</v>
+        <v>3494.39</v>
       </c>
       <c r="T290" s="5">
-        <v>1701.94</v>
+        <v>2580.38</v>
       </c>
       <c r="U290" s="5">
-        <v>705.25</v>
+        <v>1840.15</v>
       </c>
       <c r="V290" s="3"/>
       <c r="W290" s="2" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="291" spans="1:23" ht="72" x14ac:dyDescent="0.25">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="291" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B291" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="C291" s="2" t="s">
         <v>395</v>
-      </c>
-      <c r="C291" s="2" t="s">
-        <v>396</v>
       </c>
       <c r="D291" s="2" t="s">
         <v>27</v>
@@ -19655,67 +19727,67 @@
         <v>28</v>
       </c>
       <c r="F291" s="3" t="s">
-        <v>36</v>
+        <v>392</v>
       </c>
       <c r="G291" s="5">
-        <v>0.08</v>
+        <v>96.04</v>
       </c>
       <c r="H291" s="5">
-        <v>0.08</v>
+        <v>90.68</v>
       </c>
       <c r="I291" s="5">
-        <v>0.09</v>
+        <v>111.55</v>
       </c>
       <c r="J291" s="5">
-        <v>0.1</v>
+        <v>127.11</v>
       </c>
       <c r="K291" s="5">
-        <v>0.09</v>
+        <v>82.28</v>
       </c>
       <c r="L291" s="5">
-        <v>0.1</v>
+        <v>100.19</v>
       </c>
       <c r="M291" s="5">
-        <v>0.15</v>
+        <v>148.99</v>
       </c>
       <c r="N291" s="5">
-        <v>0.13</v>
+        <v>222.11</v>
       </c>
       <c r="O291" s="5">
-        <v>0.14000000000000001</v>
+        <v>244.93</v>
       </c>
       <c r="P291" s="5">
-        <v>0.14000000000000001</v>
+        <v>223.31</v>
       </c>
       <c r="Q291" s="5">
-        <v>0.14000000000000001</v>
+        <v>225.08</v>
       </c>
       <c r="R291" s="5">
-        <v>0.15</v>
+        <v>296.20999999999998</v>
       </c>
       <c r="S291" s="5">
-        <v>0.53</v>
+        <v>2661.32</v>
       </c>
       <c r="T291" s="5">
-        <v>0.33</v>
+        <v>1701.94</v>
       </c>
       <c r="U291" s="5">
-        <v>0.21</v>
+        <v>705.25</v>
       </c>
       <c r="V291" s="3"/>
       <c r="W291" s="2" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="292" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="292" spans="1:23" ht="72" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B292" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="C292" s="2" t="s">
         <v>397</v>
-      </c>
-      <c r="C292" s="2" t="s">
-        <v>398</v>
       </c>
       <c r="D292" s="2" t="s">
         <v>27</v>
@@ -19724,61 +19796,67 @@
         <v>28</v>
       </c>
       <c r="F292" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="G292" s="3"/>
-      <c r="H292" s="3"/>
-      <c r="I292" s="3"/>
-      <c r="J292" s="7">
-        <v>2.2850000000000001</v>
-      </c>
-      <c r="K292" s="7">
-        <v>1.1160000000000001</v>
-      </c>
-      <c r="L292" s="7">
-        <v>1.55</v>
-      </c>
-      <c r="M292" s="7">
-        <v>3.7469999999999999</v>
-      </c>
-      <c r="N292" s="7">
-        <v>3.8530000000000002</v>
-      </c>
-      <c r="O292" s="7">
-        <v>3.367</v>
-      </c>
-      <c r="P292" s="7">
-        <v>6.8940000000000001</v>
-      </c>
-      <c r="Q292" s="7">
-        <v>4.077</v>
-      </c>
-      <c r="R292" s="7">
-        <v>4.49</v>
-      </c>
-      <c r="S292" s="7">
-        <v>11.999000000000001</v>
-      </c>
-      <c r="T292" s="7">
-        <v>16.606000000000002</v>
-      </c>
-      <c r="U292" s="7">
-        <v>20.382000000000001</v>
+        <v>36</v>
+      </c>
+      <c r="G292" s="5">
+        <v>0.08</v>
+      </c>
+      <c r="H292" s="5">
+        <v>0.08</v>
+      </c>
+      <c r="I292" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="J292" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="K292" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="L292" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="M292" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="N292" s="5">
+        <v>0.13</v>
+      </c>
+      <c r="O292" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="P292" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="Q292" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="R292" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="S292" s="5">
+        <v>0.53</v>
+      </c>
+      <c r="T292" s="5">
+        <v>0.33</v>
+      </c>
+      <c r="U292" s="5">
+        <v>0.21</v>
       </c>
       <c r="V292" s="3"/>
       <c r="W292" s="2" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
     </row>
     <row r="293" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D293" s="2" t="s">
         <v>27</v>
@@ -19787,61 +19865,61 @@
         <v>28</v>
       </c>
       <c r="F293" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="G293" s="3"/>
       <c r="H293" s="3"/>
       <c r="I293" s="3"/>
-      <c r="J293" s="5">
-        <v>8.07</v>
-      </c>
-      <c r="K293" s="5">
-        <v>3.54</v>
-      </c>
-      <c r="L293" s="5">
-        <v>2.98</v>
-      </c>
-      <c r="M293" s="5">
-        <v>2.44</v>
-      </c>
-      <c r="N293" s="5">
-        <v>2.25</v>
-      </c>
-      <c r="O293" s="5">
-        <v>63.36</v>
-      </c>
-      <c r="P293" s="5">
-        <v>7.61</v>
-      </c>
-      <c r="Q293" s="5">
-        <v>6.64</v>
-      </c>
-      <c r="R293" s="5">
-        <v>3.65</v>
-      </c>
-      <c r="S293" s="5">
-        <v>9.59</v>
-      </c>
-      <c r="T293" s="5">
-        <v>4.2699999999999996</v>
-      </c>
-      <c r="U293" s="5">
-        <v>8.32</v>
+      <c r="J293" s="7">
+        <v>2.2850000000000001</v>
+      </c>
+      <c r="K293" s="7">
+        <v>1.1160000000000001</v>
+      </c>
+      <c r="L293" s="7">
+        <v>1.55</v>
+      </c>
+      <c r="M293" s="7">
+        <v>3.7469999999999999</v>
+      </c>
+      <c r="N293" s="7">
+        <v>3.8530000000000002</v>
+      </c>
+      <c r="O293" s="7">
+        <v>3.367</v>
+      </c>
+      <c r="P293" s="7">
+        <v>6.8940000000000001</v>
+      </c>
+      <c r="Q293" s="7">
+        <v>4.077</v>
+      </c>
+      <c r="R293" s="7">
+        <v>4.49</v>
+      </c>
+      <c r="S293" s="7">
+        <v>11.999000000000001</v>
+      </c>
+      <c r="T293" s="7">
+        <v>16.606000000000002</v>
+      </c>
+      <c r="U293" s="7">
+        <v>20.382000000000001</v>
       </c>
       <c r="V293" s="3"/>
       <c r="W293" s="2" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
     </row>
     <row r="294" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B294" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="C294" s="2" t="s">
         <v>401</v>
-      </c>
-      <c r="C294" s="2" t="s">
-        <v>402</v>
       </c>
       <c r="D294" s="2" t="s">
         <v>27</v>
@@ -19850,53 +19928,61 @@
         <v>28</v>
       </c>
       <c r="F294" s="3" t="s">
-        <v>257</v>
+        <v>392</v>
       </c>
       <c r="G294" s="3"/>
       <c r="H294" s="3"/>
       <c r="I294" s="3"/>
-      <c r="J294" s="3"/>
-      <c r="K294" s="6">
-        <v>1</v>
-      </c>
-      <c r="L294" s="6">
-        <v>1</v>
-      </c>
-      <c r="M294" s="6">
-        <v>8</v>
-      </c>
-      <c r="N294" s="6">
-        <v>2</v>
-      </c>
-      <c r="O294" s="3"/>
-      <c r="P294" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q294" s="6">
-        <v>2</v>
-      </c>
-      <c r="R294" s="3"/>
-      <c r="S294" s="3"/>
-      <c r="T294" s="6">
-        <v>8</v>
-      </c>
-      <c r="U294" s="6">
-        <v>7</v>
+      <c r="J294" s="5">
+        <v>8.07</v>
+      </c>
+      <c r="K294" s="5">
+        <v>3.54</v>
+      </c>
+      <c r="L294" s="5">
+        <v>2.98</v>
+      </c>
+      <c r="M294" s="5">
+        <v>2.44</v>
+      </c>
+      <c r="N294" s="5">
+        <v>2.25</v>
+      </c>
+      <c r="O294" s="5">
+        <v>63.36</v>
+      </c>
+      <c r="P294" s="5">
+        <v>7.61</v>
+      </c>
+      <c r="Q294" s="5">
+        <v>6.64</v>
+      </c>
+      <c r="R294" s="5">
+        <v>3.65</v>
+      </c>
+      <c r="S294" s="5">
+        <v>9.59</v>
+      </c>
+      <c r="T294" s="5">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="U294" s="5">
+        <v>8.32</v>
       </c>
       <c r="V294" s="3"/>
       <c r="W294" s="2" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
     </row>
     <row r="295" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D295" s="2" t="s">
         <v>27</v>
@@ -19909,12 +19995,8 @@
       </c>
       <c r="G295" s="3"/>
       <c r="H295" s="3"/>
-      <c r="I295" s="6">
-        <v>2</v>
-      </c>
-      <c r="J295" s="6">
-        <v>2</v>
-      </c>
+      <c r="I295" s="3"/>
+      <c r="J295" s="3"/>
       <c r="K295" s="6">
         <v>1</v>
       </c>
@@ -19922,46 +20004,40 @@
         <v>1</v>
       </c>
       <c r="M295" s="6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N295" s="6">
-        <v>1</v>
-      </c>
-      <c r="O295" s="6">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="O295" s="3"/>
       <c r="P295" s="6">
         <v>1</v>
       </c>
       <c r="Q295" s="6">
-        <v>4</v>
-      </c>
-      <c r="R295" s="6">
-        <v>1</v>
-      </c>
-      <c r="S295" s="6">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="R295" s="3"/>
+      <c r="S295" s="3"/>
       <c r="T295" s="6">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U295" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V295" s="3"/>
       <c r="W295" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="296" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B296" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="C296" s="2" t="s">
         <v>406</v>
-      </c>
-      <c r="C296" s="2" t="s">
-        <v>407</v>
       </c>
       <c r="D296" s="2" t="s">
         <v>27</v>
@@ -19970,59 +20046,63 @@
         <v>28</v>
       </c>
       <c r="F296" s="3" t="s">
-        <v>32</v>
+        <v>257</v>
       </c>
       <c r="G296" s="3"/>
       <c r="H296" s="3"/>
-      <c r="I296" s="3"/>
-      <c r="J296" s="3"/>
+      <c r="I296" s="6">
+        <v>2</v>
+      </c>
+      <c r="J296" s="6">
+        <v>2</v>
+      </c>
       <c r="K296" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L296" s="6">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="M296" s="6">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="N296" s="6">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="O296" s="6">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="P296" s="6">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="Q296" s="6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="R296" s="6">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="S296" s="6">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="T296" s="6">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="U296" s="6">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="V296" s="3"/>
       <c r="W296" s="2" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="297" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="297" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B297" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C297" s="2" t="s">
         <v>408</v>
-      </c>
-      <c r="C297" s="2" t="s">
-        <v>409</v>
       </c>
       <c r="D297" s="2" t="s">
         <v>27</v>
@@ -20037,31 +20117,91 @@
       <c r="H297" s="3"/>
       <c r="I297" s="3"/>
       <c r="J297" s="3"/>
-      <c r="K297" s="3"/>
-      <c r="L297" s="3"/>
-      <c r="M297" s="3"/>
-      <c r="N297" s="3"/>
-      <c r="O297" s="3"/>
-      <c r="P297" s="3"/>
-      <c r="Q297" s="3"/>
-      <c r="R297" s="3"/>
-      <c r="S297" s="3"/>
+      <c r="K297" s="6">
+        <v>5</v>
+      </c>
+      <c r="L297" s="6">
+        <v>13</v>
+      </c>
+      <c r="M297" s="6">
+        <v>19</v>
+      </c>
+      <c r="N297" s="6">
+        <v>18</v>
+      </c>
+      <c r="O297" s="6">
+        <v>15</v>
+      </c>
+      <c r="P297" s="6">
+        <v>15</v>
+      </c>
+      <c r="Q297" s="6">
+        <v>8</v>
+      </c>
+      <c r="R297" s="6">
+        <v>28</v>
+      </c>
+      <c r="S297" s="6">
+        <v>53</v>
+      </c>
       <c r="T297" s="6">
-        <v>114</v>
+        <v>65</v>
       </c>
       <c r="U297" s="6">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="V297" s="3"/>
       <c r="W297" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="298" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+      <c r="A298" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B298" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="C298" s="2" t="s">
         <v>410</v>
       </c>
-    </row>
-    <row r="298" spans="1:23" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="D298" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E298" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F298" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G298" s="3"/>
+      <c r="H298" s="3"/>
+      <c r="I298" s="3"/>
+      <c r="J298" s="3"/>
+      <c r="K298" s="3"/>
+      <c r="L298" s="3"/>
+      <c r="M298" s="3"/>
+      <c r="N298" s="3"/>
+      <c r="O298" s="3"/>
+      <c r="P298" s="3"/>
+      <c r="Q298" s="3"/>
+      <c r="R298" s="3"/>
+      <c r="S298" s="3"/>
+      <c r="T298" s="6">
+        <v>114</v>
+      </c>
+      <c r="U298" s="6">
+        <v>61</v>
+      </c>
+      <c r="V298" s="3"/>
+      <c r="W298" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
     <row r="299" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="300" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="10" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B300" s="8"/>
     </row>
@@ -20076,7 +20216,7 @@
     <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.39370078740157499" right="0.39370078740157499" top="0.39370078740157499" bottom="0.39370078740157499" header="0.39370078740157499" footer="0.39370078740157499"/>
-  <pageSetup paperSize="9" scale="58" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="59" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId3"/>
 </worksheet>

--- a/assets/excel/en/national_sdg_indicators.xlsx
+++ b/assets/excel/en/national_sdg_indicators.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dregerj\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD9D553B-625C-4730-8315-27F5A3584FEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB930A99-E258-425D-89E3-3E38EAC9349C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -943,7 +943,7 @@
     <t>12.1.a Resource productivity</t>
   </si>
   <si>
-    <t>euro/kg</t>
+    <t>Euro per kilogram, chain linked volumes (2015)</t>
   </si>
   <si>
     <t>12.1.b Domestic material consumption (DMC) per capita</t>
@@ -1267,7 +1267,7 @@
     <t>The Ministry of Economic Development and Technology / The Chancellery of the  Prime Minister</t>
   </si>
   <si>
-    <t>Last update: 10-03-2026, 12:35</t>
+    <t>Last update: 17-03-2026, 07:50</t>
   </si>
 </sst>
 </file>
@@ -1813,9 +1813,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
   <dimension ref="A1:W300"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3349,7 +3346,7 @@
         <v>400.4</v>
       </c>
       <c r="U26" s="4">
-        <v>400.1</v>
+        <v>400.2</v>
       </c>
       <c r="V26" s="3"/>
       <c r="W26" s="2" t="s">
@@ -4762,7 +4759,7 @@
         <v>65</v>
       </c>
       <c r="U47" s="4">
-        <v>66.2</v>
+        <v>66.3</v>
       </c>
       <c r="V47" s="3"/>
       <c r="W47" s="2" t="s">
@@ -9835,10 +9832,10 @@
         <v>15.6</v>
       </c>
       <c r="S138" s="5">
-        <v>16.63</v>
+        <v>16.64</v>
       </c>
       <c r="T138" s="5">
-        <v>16.559999999999999</v>
+        <v>16.649999999999999</v>
       </c>
       <c r="U138" s="5">
         <v>17.77</v>
@@ -13248,7 +13245,9 @@
       <c r="T188" s="4">
         <v>15.8</v>
       </c>
-      <c r="U188" s="3"/>
+      <c r="U188" s="4">
+        <v>15.2</v>
+      </c>
       <c r="V188" s="3"/>
       <c r="W188" s="2" t="s">
         <v>30</v>
@@ -14972,18 +14971,20 @@
       <c r="O217" s="3"/>
       <c r="P217" s="3"/>
       <c r="Q217" s="4">
-        <v>15.7</v>
+        <v>5.4</v>
       </c>
       <c r="R217" s="4">
-        <v>14.8</v>
+        <v>5.3</v>
       </c>
       <c r="S217" s="4">
-        <v>14.8</v>
+        <v>5.2</v>
       </c>
       <c r="T217" s="4">
-        <v>14.3</v>
-      </c>
-      <c r="U217" s="3"/>
+        <v>6.6</v>
+      </c>
+      <c r="U217" s="4">
+        <v>10.7</v>
+      </c>
       <c r="V217" s="3"/>
       <c r="W217" s="2" t="s">
         <v>30</v>
@@ -15019,18 +15020,20 @@
       <c r="O218" s="3"/>
       <c r="P218" s="3"/>
       <c r="Q218" s="4">
-        <v>13.3</v>
+        <v>3.9</v>
       </c>
       <c r="R218" s="4">
-        <v>13.5</v>
+        <v>4.5</v>
       </c>
       <c r="S218" s="4">
-        <v>13.1</v>
+        <v>5</v>
       </c>
       <c r="T218" s="4">
-        <v>13.3</v>
-      </c>
-      <c r="U218" s="3"/>
+        <v>7.3</v>
+      </c>
+      <c r="U218" s="4">
+        <v>14.5</v>
+      </c>
       <c r="V218" s="3"/>
       <c r="W218" s="2" t="s">
         <v>30</v>
@@ -16311,10 +16314,10 @@
         <v>15.6</v>
       </c>
       <c r="S238" s="5">
-        <v>16.63</v>
+        <v>16.64</v>
       </c>
       <c r="T238" s="5">
-        <v>16.559999999999999</v>
+        <v>16.649999999999999</v>
       </c>
       <c r="U238" s="5">
         <v>17.77</v>
@@ -20216,7 +20219,7 @@
     <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.39370078740157499" right="0.39370078740157499" top="0.39370078740157499" bottom="0.39370078740157499" header="0.39370078740157499" footer="0.39370078740157499"/>
-  <pageSetup paperSize="9" scale="59" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="59" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId3"/>
 </worksheet>

--- a/assets/excel/en/national_sdg_indicators.xlsx
+++ b/assets/excel/en/national_sdg_indicators.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dregerj\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sidwab\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB930A99-E258-425D-89E3-3E38EAC9349C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2EF6D31-E2C5-4043-AECF-C8E48B344757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="412">
   <si>
     <t>sdg.gov.pl/en</t>
   </si>
@@ -1030,9 +1030,6 @@
     <t>13.4.b Capacity of small water retention facilities</t>
   </si>
   <si>
-    <t>dam&lt;sub&gt;3&lt;/sub&gt;</t>
-  </si>
-  <si>
     <t>13.4.c Length of the coastline protected during a year from the sea erosion and flood</t>
   </si>
   <si>
@@ -1054,7 +1051,7 @@
     <t>13.6.a Number of conducted educational campaigns promoting issues related to the problem of invasive alien species entering the natural environment</t>
   </si>
   <si>
-    <t>&lt;p&gt;Ministry of Climate and Environment&lt;/p&gt; &lt;p&gt;General Directorate for  Environmental Protection&lt;/p&gt; &lt;p&gt;Regional directorates of environmental  protection&lt;/p&gt; &lt;p&gt;Ministry of Internal Affairs and Administration&lt;/p&gt;  &lt;p&gt;Ministry of Agriculture and Rural Development (cooperating institution)&lt;/p&gt;</t>
+    <t>Ministry of Climate and Environment / General Directorate for Environmental Protection / Regional directorates of environmental protection / Ministry of Internal Affairs and Administration / Ministry of Agriculture and Rural Development (cooperating institution)</t>
   </si>
   <si>
     <t>13.6.b Extent of implemented educational and informational projects</t>
@@ -1267,7 +1264,7 @@
     <t>The Ministry of Economic Development and Technology / The Chancellery of the  Prime Minister</t>
   </si>
   <si>
-    <t>Last update: 17-03-2026, 07:50</t>
+    <t>Last update: 24-03-2026, 11:45</t>
   </si>
 </sst>
 </file>
@@ -2092,7 +2089,9 @@
       <c r="U6" s="4">
         <v>41.8</v>
       </c>
-      <c r="V6" s="3"/>
+      <c r="V6" s="4">
+        <v>44.2</v>
+      </c>
       <c r="W6" s="2" t="s">
         <v>37</v>
       </c>
@@ -2157,7 +2156,9 @@
       <c r="U7" s="4">
         <v>60.4</v>
       </c>
-      <c r="V7" s="3"/>
+      <c r="V7" s="4">
+        <v>60.5</v>
+      </c>
       <c r="W7" s="2" t="s">
         <v>37</v>
       </c>
@@ -2222,7 +2223,9 @@
       <c r="U8" s="4">
         <v>21</v>
       </c>
-      <c r="V8" s="3"/>
+      <c r="V8" s="4">
+        <v>23.5</v>
+      </c>
       <c r="W8" s="2" t="s">
         <v>37</v>
       </c>
@@ -2750,11 +2753,21 @@
       <c r="Q16" s="4">
         <v>16.5</v>
       </c>
-      <c r="R16" s="3"/>
-      <c r="S16" s="3"/>
-      <c r="T16" s="3"/>
-      <c r="U16" s="3"/>
-      <c r="V16" s="3"/>
+      <c r="R16" s="4">
+        <v>15.3</v>
+      </c>
+      <c r="S16" s="4">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="T16" s="4">
+        <v>22.2</v>
+      </c>
+      <c r="U16" s="4">
+        <v>16.7</v>
+      </c>
+      <c r="V16" s="4">
+        <v>15.7</v>
+      </c>
       <c r="W16" s="2" t="s">
         <v>53</v>
       </c>
@@ -5645,7 +5658,9 @@
       <c r="U65" s="4">
         <v>84.3</v>
       </c>
-      <c r="V65" s="3"/>
+      <c r="V65" s="4">
+        <v>87.5</v>
+      </c>
       <c r="W65" s="2" t="s">
         <v>95</v>
       </c>
@@ -8955,7 +8970,9 @@
       <c r="U125" s="4">
         <v>41.8</v>
       </c>
-      <c r="V125" s="3"/>
+      <c r="V125" s="4">
+        <v>44.2</v>
+      </c>
       <c r="W125" s="2" t="s">
         <v>37</v>
       </c>
@@ -9020,7 +9037,9 @@
       <c r="U126" s="4">
         <v>60.4</v>
       </c>
-      <c r="V126" s="3"/>
+      <c r="V126" s="4">
+        <v>60.5</v>
+      </c>
       <c r="W126" s="2" t="s">
         <v>37</v>
       </c>
@@ -9085,7 +9104,9 @@
       <c r="U127" s="4">
         <v>21</v>
       </c>
-      <c r="V127" s="3"/>
+      <c r="V127" s="4">
+        <v>23.5</v>
+      </c>
       <c r="W127" s="2" t="s">
         <v>37</v>
       </c>
@@ -11719,10 +11740,10 @@
         <v>56</v>
       </c>
       <c r="P166" s="4">
-        <v>56</v>
+        <v>56.2</v>
       </c>
       <c r="Q166" s="4">
-        <v>55.8</v>
+        <v>56.2</v>
       </c>
       <c r="R166" s="4">
         <v>58.2</v>
@@ -15322,7 +15343,7 @@
         <v>9</v>
       </c>
       <c r="R223" s="4">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="S223" s="4">
         <v>7.6</v>
@@ -15330,7 +15351,9 @@
       <c r="T223" s="4">
         <v>7.6</v>
       </c>
-      <c r="U223" s="3"/>
+      <c r="U223" s="4">
+        <v>7.7</v>
+      </c>
       <c r="V223" s="3"/>
       <c r="W223" s="2" t="s">
         <v>289</v>
@@ -15402,7 +15425,7 @@
       </c>
       <c r="V224" s="3"/>
       <c r="W224" s="2" t="s">
-        <v>170</v>
+        <v>30</v>
       </c>
     </row>
     <row r="225" spans="1:23" ht="27" x14ac:dyDescent="0.25">
@@ -16821,7 +16844,7 @@
         <v>28</v>
       </c>
       <c r="F246" s="3" t="s">
-        <v>333</v>
+        <v>169</v>
       </c>
       <c r="G246" s="4">
         <v>732401.6</v>
@@ -16879,7 +16902,7 @@
         <v>330</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D247" s="2" t="s">
         <v>27</v>
@@ -16888,7 +16911,7 @@
         <v>28</v>
       </c>
       <c r="F247" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G247" s="3"/>
       <c r="H247" s="3"/>
@@ -16931,10 +16954,10 @@
         <v>309</v>
       </c>
       <c r="B248" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C248" s="2" t="s">
         <v>336</v>
-      </c>
-      <c r="C248" s="2" t="s">
-        <v>337</v>
       </c>
       <c r="D248" s="2" t="s">
         <v>27</v>
@@ -16976,18 +16999,18 @@
       </c>
       <c r="V248" s="3"/>
       <c r="W248" s="2" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="249" spans="1:23" ht="135" x14ac:dyDescent="0.25">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="249" spans="1:23" ht="99" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
         <v>309</v>
       </c>
       <c r="B249" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C249" s="2" t="s">
         <v>339</v>
-      </c>
-      <c r="C249" s="2" t="s">
-        <v>340</v>
       </c>
       <c r="D249" s="2" t="s">
         <v>27</v>
@@ -17023,7 +17046,7 @@
         <v>4</v>
       </c>
       <c r="W249" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="250" spans="1:23" ht="36" x14ac:dyDescent="0.25">
@@ -17031,10 +17054,10 @@
         <v>309</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D250" s="2" t="s">
         <v>27</v>
@@ -17043,7 +17066,7 @@
         <v>28</v>
       </c>
       <c r="F250" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G250" s="3"/>
       <c r="H250" s="3"/>
@@ -17070,24 +17093,24 @@
       </c>
       <c r="V250" s="3"/>
       <c r="W250" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="251" spans="1:23" ht="72" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B251" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="B251" s="2" t="s">
+      <c r="C251" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="C251" s="2" t="s">
+      <c r="D251" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="D251" s="2" t="s">
+      <c r="E251" s="3" t="s">
         <v>348</v>
-      </c>
-      <c r="E251" s="3" t="s">
-        <v>349</v>
       </c>
       <c r="F251" s="3" t="s">
         <v>36</v>
@@ -17139,24 +17162,24 @@
       </c>
       <c r="V251" s="3"/>
       <c r="W251" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="252" spans="1:23" ht="72" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B252" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="B252" s="2" t="s">
+      <c r="C252" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="C252" s="2" t="s">
+      <c r="D252" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="D252" s="2" t="s">
-        <v>348</v>
-      </c>
       <c r="E252" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F252" s="3" t="s">
         <v>36</v>
@@ -17208,24 +17231,24 @@
       </c>
       <c r="V252" s="3"/>
       <c r="W252" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="253" spans="1:23" ht="72" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B253" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="B253" s="2" t="s">
+      <c r="C253" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="C253" s="2" t="s">
+      <c r="D253" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="D253" s="2" t="s">
-        <v>348</v>
-      </c>
       <c r="E253" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F253" s="3" t="s">
         <v>36</v>
@@ -17277,24 +17300,24 @@
       </c>
       <c r="V253" s="3"/>
       <c r="W253" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="254" spans="1:23" ht="72" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B254" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="B254" s="2" t="s">
+      <c r="C254" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="C254" s="2" t="s">
+      <c r="D254" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="D254" s="2" t="s">
-        <v>348</v>
-      </c>
       <c r="E254" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F254" s="3" t="s">
         <v>36</v>
@@ -17346,18 +17369,18 @@
       </c>
       <c r="V254" s="3"/>
       <c r="W254" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="255" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B255" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="C255" s="2" t="s">
         <v>354</v>
-      </c>
-      <c r="C255" s="2" t="s">
-        <v>355</v>
       </c>
       <c r="D255" s="2" t="s">
         <v>27</v>
@@ -17420,13 +17443,13 @@
     </row>
     <row r="256" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B256" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="C256" s="2" t="s">
         <v>356</v>
-      </c>
-      <c r="C256" s="2" t="s">
-        <v>357</v>
       </c>
       <c r="D256" s="2" t="s">
         <v>27</v>
@@ -17435,7 +17458,7 @@
         <v>28</v>
       </c>
       <c r="F256" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G256" s="4">
         <v>59.5</v>
@@ -17489,13 +17512,13 @@
     </row>
     <row r="257" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B257" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="B257" s="2" t="s">
+      <c r="C257" s="2" t="s">
         <v>360</v>
-      </c>
-      <c r="C257" s="2" t="s">
-        <v>361</v>
       </c>
       <c r="D257" s="2" t="s">
         <v>27</v>
@@ -17504,7 +17527,7 @@
         <v>28</v>
       </c>
       <c r="F257" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G257" s="4">
         <v>90.8</v>
@@ -17553,18 +17576,18 @@
       </c>
       <c r="V257" s="3"/>
       <c r="W257" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="258" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B258" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="B258" s="2" t="s">
-        <v>360</v>
-      </c>
       <c r="C258" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D258" s="2" t="s">
         <v>27</v>
@@ -17622,18 +17645,18 @@
       </c>
       <c r="V258" s="3"/>
       <c r="W258" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="259" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B259" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="B259" s="2" t="s">
-        <v>360</v>
-      </c>
       <c r="C259" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D259" s="2" t="s">
         <v>27</v>
@@ -17696,13 +17719,13 @@
     </row>
     <row r="260" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B260" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="C260" s="2" t="s">
         <v>367</v>
-      </c>
-      <c r="C260" s="2" t="s">
-        <v>368</v>
       </c>
       <c r="D260" s="2" t="s">
         <v>27</v>
@@ -17765,13 +17788,13 @@
     </row>
     <row r="261" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D261" s="2" t="s">
         <v>35</v>
@@ -17834,13 +17857,13 @@
     </row>
     <row r="262" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D262" s="2" t="s">
         <v>35</v>
@@ -17903,13 +17926,13 @@
     </row>
     <row r="263" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D263" s="2" t="s">
         <v>35</v>
@@ -17972,13 +17995,13 @@
     </row>
     <row r="264" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D264" s="2" t="s">
         <v>27</v>
@@ -18041,13 +18064,13 @@
     </row>
     <row r="265" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B265" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="C265" s="2" t="s">
         <v>371</v>
-      </c>
-      <c r="C265" s="2" t="s">
-        <v>372</v>
       </c>
       <c r="D265" s="2" t="s">
         <v>27</v>
@@ -18056,7 +18079,7 @@
         <v>28</v>
       </c>
       <c r="F265" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G265" s="6">
         <v>70108</v>
@@ -18110,13 +18133,13 @@
     </row>
     <row r="266" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D266" s="2" t="s">
         <v>27</v>
@@ -18179,13 +18202,13 @@
     </row>
     <row r="267" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B267" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="B267" s="2" t="s">
+      <c r="C267" s="2" t="s">
         <v>376</v>
-      </c>
-      <c r="C267" s="2" t="s">
-        <v>377</v>
       </c>
       <c r="D267" s="2" t="s">
         <v>27</v>
@@ -18245,18 +18268,18 @@
         <v>86</v>
       </c>
       <c r="W267" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="268" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B268" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="B268" s="2" t="s">
-        <v>376</v>
-      </c>
       <c r="C268" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D268" s="2" t="s">
         <v>27</v>
@@ -18300,18 +18323,18 @@
       </c>
       <c r="V268" s="3"/>
       <c r="W268" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="269" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B269" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="C269" s="2" t="s">
         <v>380</v>
-      </c>
-      <c r="C269" s="2" t="s">
-        <v>381</v>
       </c>
       <c r="D269" s="2" t="s">
         <v>27</v>
@@ -18374,13 +18397,13 @@
     </row>
     <row r="270" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B270" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="C270" s="2" t="s">
         <v>382</v>
-      </c>
-      <c r="C270" s="2" t="s">
-        <v>383</v>
       </c>
       <c r="D270" s="2" t="s">
         <v>27</v>
@@ -18438,18 +18461,18 @@
       </c>
       <c r="V270" s="3"/>
       <c r="W270" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="271" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B271" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C271" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="C271" s="2" t="s">
-        <v>386</v>
       </c>
       <c r="D271" s="2" t="s">
         <v>62</v>
@@ -18506,13 +18529,13 @@
     </row>
     <row r="272" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B272" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C272" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="C272" s="2" t="s">
-        <v>386</v>
       </c>
       <c r="D272" s="2" t="s">
         <v>62</v>
@@ -18569,13 +18592,13 @@
     </row>
     <row r="273" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B273" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C273" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="C273" s="2" t="s">
-        <v>386</v>
       </c>
       <c r="D273" s="2" t="s">
         <v>62</v>
@@ -18632,13 +18655,13 @@
     </row>
     <row r="274" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B274" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C274" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="C274" s="2" t="s">
-        <v>386</v>
       </c>
       <c r="D274" s="2" t="s">
         <v>35</v>
@@ -18695,13 +18718,13 @@
     </row>
     <row r="275" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B275" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C275" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="C275" s="2" t="s">
-        <v>386</v>
       </c>
       <c r="D275" s="2" t="s">
         <v>35</v>
@@ -18758,13 +18781,13 @@
     </row>
     <row r="276" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B276" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C276" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="C276" s="2" t="s">
-        <v>386</v>
       </c>
       <c r="D276" s="2" t="s">
         <v>80</v>
@@ -18821,13 +18844,13 @@
     </row>
     <row r="277" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B277" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C277" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="C277" s="2" t="s">
-        <v>386</v>
       </c>
       <c r="D277" s="2" t="s">
         <v>80</v>
@@ -18884,13 +18907,13 @@
     </row>
     <row r="278" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B278" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C278" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="C278" s="2" t="s">
-        <v>386</v>
       </c>
       <c r="D278" s="2" t="s">
         <v>80</v>
@@ -18947,13 +18970,13 @@
     </row>
     <row r="279" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B279" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C279" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="C279" s="2" t="s">
-        <v>386</v>
       </c>
       <c r="D279" s="2" t="s">
         <v>80</v>
@@ -19010,13 +19033,13 @@
     </row>
     <row r="280" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B280" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C280" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="C280" s="2" t="s">
-        <v>386</v>
       </c>
       <c r="D280" s="2" t="s">
         <v>80</v>
@@ -19073,13 +19096,13 @@
     </row>
     <row r="281" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B281" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C281" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="C281" s="2" t="s">
-        <v>386</v>
       </c>
       <c r="D281" s="2" t="s">
         <v>80</v>
@@ -19136,13 +19159,13 @@
     </row>
     <row r="282" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B282" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C282" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="C282" s="2" t="s">
-        <v>386</v>
       </c>
       <c r="D282" s="2" t="s">
         <v>141</v>
@@ -19199,13 +19222,13 @@
     </row>
     <row r="283" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B283" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C283" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="C283" s="2" t="s">
-        <v>386</v>
       </c>
       <c r="D283" s="2" t="s">
         <v>141</v>
@@ -19262,13 +19285,13 @@
     </row>
     <row r="284" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B284" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C284" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="C284" s="2" t="s">
-        <v>386</v>
       </c>
       <c r="D284" s="2" t="s">
         <v>141</v>
@@ -19325,13 +19348,13 @@
     </row>
     <row r="285" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B285" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C285" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="C285" s="2" t="s">
-        <v>386</v>
       </c>
       <c r="D285" s="2" t="s">
         <v>144</v>
@@ -19388,13 +19411,13 @@
     </row>
     <row r="286" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B286" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C286" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="C286" s="2" t="s">
-        <v>386</v>
       </c>
       <c r="D286" s="2" t="s">
         <v>144</v>
@@ -19451,13 +19474,13 @@
     </row>
     <row r="287" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B287" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C287" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="C287" s="2" t="s">
-        <v>386</v>
       </c>
       <c r="D287" s="2" t="s">
         <v>144</v>
@@ -19514,13 +19537,13 @@
     </row>
     <row r="288" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B288" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C288" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="C288" s="2" t="s">
-        <v>386</v>
       </c>
       <c r="D288" s="2" t="s">
         <v>144</v>
@@ -19577,13 +19600,13 @@
     </row>
     <row r="289" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B289" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="C289" s="2" t="s">
         <v>387</v>
-      </c>
-      <c r="C289" s="2" t="s">
-        <v>388</v>
       </c>
       <c r="D289" s="2" t="s">
         <v>27</v>
@@ -19646,13 +19669,13 @@
     </row>
     <row r="290" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B290" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="B290" s="2" t="s">
+      <c r="C290" s="2" t="s">
         <v>390</v>
-      </c>
-      <c r="C290" s="2" t="s">
-        <v>391</v>
       </c>
       <c r="D290" s="2" t="s">
         <v>27</v>
@@ -19661,7 +19684,7 @@
         <v>28</v>
       </c>
       <c r="F290" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G290" s="5">
         <v>377.75</v>
@@ -19710,18 +19733,18 @@
       </c>
       <c r="V290" s="3"/>
       <c r="W290" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="291" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B291" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="C291" s="2" t="s">
         <v>394</v>
-      </c>
-      <c r="C291" s="2" t="s">
-        <v>395</v>
       </c>
       <c r="D291" s="2" t="s">
         <v>27</v>
@@ -19730,7 +19753,7 @@
         <v>28</v>
       </c>
       <c r="F291" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G291" s="5">
         <v>96.04</v>
@@ -19779,18 +19802,18 @@
       </c>
       <c r="V291" s="3"/>
       <c r="W291" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="292" spans="1:23" ht="72" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B292" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C292" s="2" t="s">
         <v>396</v>
-      </c>
-      <c r="C292" s="2" t="s">
-        <v>397</v>
       </c>
       <c r="D292" s="2" t="s">
         <v>27</v>
@@ -19848,18 +19871,18 @@
       </c>
       <c r="V292" s="3"/>
       <c r="W292" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="293" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B293" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C293" s="2" t="s">
         <v>398</v>
-      </c>
-      <c r="C293" s="2" t="s">
-        <v>399</v>
       </c>
       <c r="D293" s="2" t="s">
         <v>27</v>
@@ -19868,7 +19891,7 @@
         <v>28</v>
       </c>
       <c r="F293" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G293" s="3"/>
       <c r="H293" s="3"/>
@@ -19911,18 +19934,18 @@
       </c>
       <c r="V293" s="3"/>
       <c r="W293" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="294" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D294" s="2" t="s">
         <v>27</v>
@@ -19931,7 +19954,7 @@
         <v>28</v>
       </c>
       <c r="F294" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G294" s="3"/>
       <c r="H294" s="3"/>
@@ -19974,18 +19997,18 @@
       </c>
       <c r="V294" s="3"/>
       <c r="W294" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="295" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B295" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="C295" s="2" t="s">
         <v>402</v>
-      </c>
-      <c r="C295" s="2" t="s">
-        <v>403</v>
       </c>
       <c r="D295" s="2" t="s">
         <v>27</v>
@@ -20027,20 +20050,22 @@
       <c r="U295" s="6">
         <v>7</v>
       </c>
-      <c r="V295" s="3"/>
+      <c r="V295" s="6">
+        <v>2</v>
+      </c>
       <c r="W295" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="296" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B296" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="C296" s="2" t="s">
         <v>405</v>
-      </c>
-      <c r="C296" s="2" t="s">
-        <v>406</v>
       </c>
       <c r="D296" s="2" t="s">
         <v>27</v>
@@ -20092,20 +20117,22 @@
       <c r="U296" s="6">
         <v>4</v>
       </c>
-      <c r="V296" s="3"/>
+      <c r="V296" s="6">
+        <v>2</v>
+      </c>
       <c r="W296" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="297" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B297" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="C297" s="2" t="s">
         <v>407</v>
-      </c>
-      <c r="C297" s="2" t="s">
-        <v>408</v>
       </c>
       <c r="D297" s="2" t="s">
         <v>27</v>
@@ -20153,20 +20180,22 @@
       <c r="U297" s="6">
         <v>70</v>
       </c>
-      <c r="V297" s="3"/>
+      <c r="V297" s="6">
+        <v>69</v>
+      </c>
       <c r="W297" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="298" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B298" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="C298" s="2" t="s">
         <v>409</v>
-      </c>
-      <c r="C298" s="2" t="s">
-        <v>410</v>
       </c>
       <c r="D298" s="2" t="s">
         <v>27</v>
@@ -20196,15 +20225,17 @@
       <c r="U298" s="6">
         <v>61</v>
       </c>
-      <c r="V298" s="3"/>
+      <c r="V298" s="6">
+        <v>97</v>
+      </c>
       <c r="W298" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="299" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="300" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="10" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B300" s="8"/>
     </row>
@@ -20219,7 +20250,7 @@
     <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.39370078740157499" right="0.39370078740157499" top="0.39370078740157499" bottom="0.39370078740157499" header="0.39370078740157499" footer="0.39370078740157499"/>
-  <pageSetup paperSize="9" scale="59" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="58" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId3"/>
 </worksheet>

--- a/assets/excel/en/national_sdg_indicators.xlsx
+++ b/assets/excel/en/national_sdg_indicators.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sidwab\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dregerj\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2EF6D31-E2C5-4043-AECF-C8E48B344757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53329364-CB59-4AEB-9E58-5C0F53FED924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="413">
   <si>
     <t>sdg.gov.pl/en</t>
   </si>
@@ -1240,6 +1240,9 @@
     <t>17.4.a Participation of National Revenue Administration in twinning projects, activities financed from Taiex and from domestic resources</t>
   </si>
   <si>
+    <t>-</t>
+  </si>
+  <si>
     <t>Ministry of Finance</t>
   </si>
   <si>
@@ -1264,7 +1267,7 @@
     <t>The Ministry of Economic Development and Technology / The Chancellery of the  Prime Minister</t>
   </si>
   <si>
-    <t>Last update: 24-03-2026, 11:45</t>
+    <t>Last update: 21-04-2026, 11:39</t>
   </si>
 </sst>
 </file>
@@ -2087,7 +2090,7 @@
         <v>36</v>
       </c>
       <c r="U6" s="4">
-        <v>41.8</v>
+        <v>41.1</v>
       </c>
       <c r="V6" s="4">
         <v>44.2</v>
@@ -2154,7 +2157,7 @@
         <v>51.4</v>
       </c>
       <c r="U7" s="4">
-        <v>60.4</v>
+        <v>58.2</v>
       </c>
       <c r="V7" s="4">
         <v>60.5</v>
@@ -2221,7 +2224,7 @@
         <v>15.1</v>
       </c>
       <c r="U8" s="4">
-        <v>21</v>
+        <v>19.8</v>
       </c>
       <c r="V8" s="4">
         <v>23.5</v>
@@ -6216,7 +6219,9 @@
       <c r="U75" s="4">
         <v>95.4</v>
       </c>
-      <c r="V75" s="3"/>
+      <c r="V75" s="4">
+        <v>95.1</v>
+      </c>
       <c r="W75" s="2" t="s">
         <v>117</v>
       </c>
@@ -8968,7 +8973,7 @@
         <v>36</v>
       </c>
       <c r="U125" s="4">
-        <v>41.8</v>
+        <v>41.1</v>
       </c>
       <c r="V125" s="4">
         <v>44.2</v>
@@ -9035,7 +9040,7 @@
         <v>51.4</v>
       </c>
       <c r="U126" s="4">
-        <v>60.4</v>
+        <v>58.2</v>
       </c>
       <c r="V126" s="4">
         <v>60.5</v>
@@ -9102,7 +9107,7 @@
         <v>15.1</v>
       </c>
       <c r="U127" s="4">
-        <v>21</v>
+        <v>19.8</v>
       </c>
       <c r="V127" s="4">
         <v>23.5</v>
@@ -13269,7 +13274,9 @@
       <c r="U188" s="4">
         <v>15.2</v>
       </c>
-      <c r="V188" s="3"/>
+      <c r="V188" s="4">
+        <v>15.9</v>
+      </c>
       <c r="W188" s="2" t="s">
         <v>30</v>
       </c>
@@ -14171,7 +14178,9 @@
       <c r="U204" s="6">
         <v>294</v>
       </c>
-      <c r="V204" s="3"/>
+      <c r="V204" s="6">
+        <v>372</v>
+      </c>
       <c r="W204" s="2" t="s">
         <v>258</v>
       </c>
@@ -16197,7 +16206,7 @@
         <v>95</v>
       </c>
       <c r="Q236" s="4">
-        <v>90.5</v>
+        <v>90.4</v>
       </c>
       <c r="R236" s="4">
         <v>99</v>
@@ -16206,9 +16215,11 @@
         <v>94.2</v>
       </c>
       <c r="T236" s="4">
-        <v>84.8</v>
-      </c>
-      <c r="U236" s="3"/>
+        <v>84.9</v>
+      </c>
+      <c r="U236" s="4">
+        <v>83.4</v>
+      </c>
       <c r="V236" s="3"/>
       <c r="W236" s="2" t="s">
         <v>313</v>
@@ -16237,45 +16248,47 @@
         <v>100</v>
       </c>
       <c r="H237" s="4">
-        <v>99.6</v>
+        <v>99.7</v>
       </c>
       <c r="I237" s="4">
         <v>97.8</v>
       </c>
       <c r="J237" s="4">
-        <v>96.8</v>
+        <v>96.7</v>
       </c>
       <c r="K237" s="4">
-        <v>93.7</v>
+        <v>93.6</v>
       </c>
       <c r="L237" s="4">
-        <v>94.4</v>
+        <v>94.3</v>
       </c>
       <c r="M237" s="4">
-        <v>97</v>
+        <v>96.9</v>
       </c>
       <c r="N237" s="4">
-        <v>100.6</v>
+        <v>100.5</v>
       </c>
       <c r="O237" s="4">
-        <v>100.6</v>
+        <v>100.4</v>
       </c>
       <c r="P237" s="4">
-        <v>95.1</v>
+        <v>94.9</v>
       </c>
       <c r="Q237" s="4">
-        <v>91.5</v>
+        <v>91.2</v>
       </c>
       <c r="R237" s="4">
-        <v>98.4</v>
+        <v>98.2</v>
       </c>
       <c r="S237" s="4">
-        <v>93.8</v>
+        <v>93.6</v>
       </c>
       <c r="T237" s="4">
-        <v>85.8</v>
-      </c>
-      <c r="U237" s="3"/>
+        <v>85.7</v>
+      </c>
+      <c r="U237" s="4">
+        <v>84.2</v>
+      </c>
       <c r="V237" s="3"/>
       <c r="W237" s="2" t="s">
         <v>313</v>
@@ -16483,7 +16496,9 @@
       <c r="U240" s="6">
         <v>33623</v>
       </c>
-      <c r="V240" s="3"/>
+      <c r="V240" s="6">
+        <v>37777</v>
+      </c>
       <c r="W240" s="2" t="s">
         <v>322</v>
       </c>
@@ -16997,7 +17012,9 @@
       <c r="U248" s="6">
         <v>80</v>
       </c>
-      <c r="V248" s="3"/>
+      <c r="V248" s="6">
+        <v>86</v>
+      </c>
       <c r="W248" s="2" t="s">
         <v>337</v>
       </c>
@@ -17091,7 +17108,9 @@
       <c r="U250" s="6">
         <v>44</v>
       </c>
-      <c r="V250" s="3"/>
+      <c r="V250" s="6">
+        <v>89</v>
+      </c>
       <c r="W250" s="2" t="s">
         <v>343</v>
       </c>
@@ -20017,7 +20036,7 @@
         <v>28</v>
       </c>
       <c r="F295" s="3" t="s">
-        <v>257</v>
+        <v>403</v>
       </c>
       <c r="G295" s="3"/>
       <c r="H295" s="3"/>
@@ -20054,7 +20073,7 @@
         <v>2</v>
       </c>
       <c r="W295" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="296" spans="1:23" ht="27" x14ac:dyDescent="0.25">
@@ -20062,10 +20081,10 @@
         <v>388</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D296" s="2" t="s">
         <v>27</v>
@@ -20074,7 +20093,7 @@
         <v>28</v>
       </c>
       <c r="F296" s="3" t="s">
-        <v>257</v>
+        <v>403</v>
       </c>
       <c r="G296" s="3"/>
       <c r="H296" s="3"/>
@@ -20121,7 +20140,7 @@
         <v>2</v>
       </c>
       <c r="W296" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="297" spans="1:23" ht="27" x14ac:dyDescent="0.25">
@@ -20129,10 +20148,10 @@
         <v>388</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D297" s="2" t="s">
         <v>27</v>
@@ -20184,7 +20203,7 @@
         <v>69</v>
       </c>
       <c r="W297" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="298" spans="1:23" ht="45" x14ac:dyDescent="0.25">
@@ -20192,10 +20211,10 @@
         <v>388</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D298" s="2" t="s">
         <v>27</v>
@@ -20229,13 +20248,13 @@
         <v>97</v>
       </c>
       <c r="W298" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="299" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="300" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="10" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B300" s="8"/>
     </row>
@@ -20250,7 +20269,7 @@
     <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.39370078740157499" right="0.39370078740157499" top="0.39370078740157499" bottom="0.39370078740157499" header="0.39370078740157499" footer="0.39370078740157499"/>
-  <pageSetup paperSize="9" scale="58" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="59" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId3"/>
 </worksheet>

--- a/assets/excel/en/national_sdg_indicators.xlsx
+++ b/assets/excel/en/national_sdg_indicators.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dregerj\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\niewiadomskaew\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53329364-CB59-4AEB-9E58-5C0F53FED924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C355B6A8-230A-4697-AC3D-BF530BC6C5F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1267,7 +1267,7 @@
     <t>The Ministry of Economic Development and Technology / The Chancellery of the  Prime Minister</t>
   </si>
   <si>
-    <t>Last update: 21-04-2026, 11:39</t>
+    <t>Last update: 28-04-2026, 10:51</t>
   </si>
 </sst>
 </file>
@@ -5801,7 +5801,9 @@
       <c r="U67" s="4">
         <v>34.9</v>
       </c>
-      <c r="V67" s="3"/>
+      <c r="V67" s="4">
+        <v>32.799999999999997</v>
+      </c>
       <c r="W67" s="2" t="s">
         <v>30</v>
       </c>
@@ -6428,7 +6430,9 @@
       <c r="U78" s="4">
         <v>4.0999999999999996</v>
       </c>
-      <c r="V78" s="3"/>
+      <c r="V78" s="4">
+        <v>4</v>
+      </c>
       <c r="W78" s="2" t="s">
         <v>30</v>
       </c>
@@ -6635,7 +6639,9 @@
       <c r="U81" s="4">
         <v>10</v>
       </c>
-      <c r="V81" s="3"/>
+      <c r="V81" s="4">
+        <v>8.8000000000000007</v>
+      </c>
       <c r="W81" s="2" t="s">
         <v>30</v>
       </c>
@@ -8399,7 +8405,9 @@
       <c r="U115" s="4">
         <v>8.5</v>
       </c>
-      <c r="V115" s="3"/>
+      <c r="V115" s="4">
+        <v>8</v>
+      </c>
       <c r="W115" s="2" t="s">
         <v>30</v>
       </c>
@@ -16957,9 +16965,15 @@
       <c r="S247" s="5">
         <v>4.7300000000000004</v>
       </c>
-      <c r="T247" s="3"/>
-      <c r="U247" s="3"/>
-      <c r="V247" s="3"/>
+      <c r="T247" s="5">
+        <v>6.25</v>
+      </c>
+      <c r="U247" s="5">
+        <v>5.6</v>
+      </c>
+      <c r="V247" s="5">
+        <v>5.95</v>
+      </c>
       <c r="W247" s="2" t="s">
         <v>170</v>
       </c>
@@ -19951,7 +19965,9 @@
       <c r="U293" s="7">
         <v>20.382000000000001</v>
       </c>
-      <c r="V293" s="3"/>
+      <c r="V293" s="7">
+        <v>5.3920000000000003</v>
+      </c>
       <c r="W293" s="2" t="s">
         <v>399</v>
       </c>
@@ -20269,7 +20285,7 @@
     <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.39370078740157499" right="0.39370078740157499" top="0.39370078740157499" bottom="0.39370078740157499" header="0.39370078740157499" footer="0.39370078740157499"/>
-  <pageSetup paperSize="9" scale="59" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="58" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId3"/>
 </worksheet>

--- a/assets/excel/en/national_sdg_indicators.xlsx
+++ b/assets/excel/en/national_sdg_indicators.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sidwab\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3B24D5F-67E2-440D-B0FF-54F5F0D15586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CA763E3-23B7-4D3E-B9C8-34C22AC91AE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2118" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2139" uniqueCount="418">
   <si>
     <t>sdg.gov.pl/en</t>
   </si>
@@ -1018,6 +1018,24 @@
     <t>Energy Market Agency S.A</t>
   </si>
   <si>
+    <t>Enhancement of the role of adaptation to climate change as a means of combating climate change equivalent to mitigation</t>
+  </si>
+  <si>
+    <t>13.3.a Investments in climate change mitigation in relation to GDP</t>
+  </si>
+  <si>
+    <t>13.3.b Climate related economic losses</t>
+  </si>
+  <si>
+    <t>per capita (at constant prices)</t>
+  </si>
+  <si>
+    <t>euro</t>
+  </si>
+  <si>
+    <t>in mln (at constant prices)</t>
+  </si>
+  <si>
     <t>Increasing the country's resilience to the effects of climate change</t>
   </si>
   <si>
@@ -1264,7 +1282,7 @@
     <t>The Ministry of Economic Development and Technology / The Chancellery of the  Prime Minister</t>
   </si>
   <si>
-    <t>Last update: 12-05-2026, 12:02</t>
+    <t>Last update: 20-05-2026, 10:30</t>
   </si>
 </sst>
 </file>
@@ -1810,7 +1828,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W304"/>
+  <dimension ref="A1:W307"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" customWidth="1"/>
@@ -9895,21 +9913,51 @@
       <c r="F139" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G139" s="3"/>
-      <c r="H139" s="3"/>
-      <c r="I139" s="3"/>
-      <c r="J139" s="3"/>
-      <c r="K139" s="3"/>
-      <c r="L139" s="3"/>
-      <c r="M139" s="3"/>
-      <c r="N139" s="3"/>
-      <c r="O139" s="3"/>
-      <c r="P139" s="3"/>
-      <c r="Q139" s="3"/>
-      <c r="R139" s="3"/>
-      <c r="S139" s="3"/>
-      <c r="T139" s="3"/>
-      <c r="U139" s="3"/>
+      <c r="G139" s="7">
+        <v>6.64</v>
+      </c>
+      <c r="H139" s="7">
+        <v>6.9180000000000001</v>
+      </c>
+      <c r="I139" s="7">
+        <v>6.5330000000000004</v>
+      </c>
+      <c r="J139" s="7">
+        <v>6.6660000000000004</v>
+      </c>
+      <c r="K139" s="7">
+        <v>6.319</v>
+      </c>
+      <c r="L139" s="7">
+        <v>5.6859999999999999</v>
+      </c>
+      <c r="M139" s="7">
+        <v>3.9740000000000002</v>
+      </c>
+      <c r="N139" s="7">
+        <v>4.2320000000000002</v>
+      </c>
+      <c r="O139" s="7">
+        <v>5.72</v>
+      </c>
+      <c r="P139" s="7">
+        <v>6.2</v>
+      </c>
+      <c r="Q139" s="7">
+        <v>6.5750000000000002</v>
+      </c>
+      <c r="R139" s="7">
+        <v>5.6740000000000004</v>
+      </c>
+      <c r="S139" s="7">
+        <v>5.7910000000000004</v>
+      </c>
+      <c r="T139" s="7">
+        <v>6.3390000000000004</v>
+      </c>
+      <c r="U139" s="7">
+        <v>6.0330000000000004</v>
+      </c>
       <c r="V139" s="3"/>
       <c r="W139" s="2" t="s">
         <v>182</v>
@@ -9934,21 +9982,51 @@
       <c r="F140" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G140" s="3"/>
-      <c r="H140" s="3"/>
-      <c r="I140" s="3"/>
-      <c r="J140" s="3"/>
-      <c r="K140" s="3"/>
-      <c r="L140" s="3"/>
-      <c r="M140" s="3"/>
-      <c r="N140" s="3"/>
-      <c r="O140" s="3"/>
-      <c r="P140" s="3"/>
-      <c r="Q140" s="3"/>
-      <c r="R140" s="3"/>
-      <c r="S140" s="3"/>
-      <c r="T140" s="3"/>
-      <c r="U140" s="3"/>
+      <c r="G140" s="7">
+        <v>6.5490000000000004</v>
+      </c>
+      <c r="H140" s="7">
+        <v>8.0779999999999994</v>
+      </c>
+      <c r="I140" s="7">
+        <v>10.61</v>
+      </c>
+      <c r="J140" s="7">
+        <v>10.676</v>
+      </c>
+      <c r="K140" s="7">
+        <v>12.36</v>
+      </c>
+      <c r="L140" s="7">
+        <v>13.401</v>
+      </c>
+      <c r="M140" s="7">
+        <v>13.342000000000001</v>
+      </c>
+      <c r="N140" s="7">
+        <v>13.082000000000001</v>
+      </c>
+      <c r="O140" s="7">
+        <v>13.026999999999999</v>
+      </c>
+      <c r="P140" s="7">
+        <v>14.356</v>
+      </c>
+      <c r="Q140" s="7">
+        <v>16.236999999999998</v>
+      </c>
+      <c r="R140" s="7">
+        <v>17.167000000000002</v>
+      </c>
+      <c r="S140" s="7">
+        <v>21.009</v>
+      </c>
+      <c r="T140" s="7">
+        <v>25.792999999999999</v>
+      </c>
+      <c r="U140" s="7">
+        <v>30.37</v>
+      </c>
       <c r="V140" s="3"/>
       <c r="W140" s="2" t="s">
         <v>182</v>
@@ -9973,21 +10051,51 @@
       <c r="F141" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G141" s="3"/>
-      <c r="H141" s="3"/>
-      <c r="I141" s="3"/>
-      <c r="J141" s="3"/>
-      <c r="K141" s="3"/>
-      <c r="L141" s="3"/>
-      <c r="M141" s="3"/>
-      <c r="N141" s="3"/>
-      <c r="O141" s="3"/>
-      <c r="P141" s="3"/>
-      <c r="Q141" s="3"/>
-      <c r="R141" s="3"/>
-      <c r="S141" s="3"/>
-      <c r="T141" s="3"/>
-      <c r="U141" s="3"/>
+      <c r="G141" s="7">
+        <v>11.811999999999999</v>
+      </c>
+      <c r="H141" s="7">
+        <v>13.24</v>
+      </c>
+      <c r="I141" s="7">
+        <v>13.497</v>
+      </c>
+      <c r="J141" s="7">
+        <v>14.265000000000001</v>
+      </c>
+      <c r="K141" s="7">
+        <v>14.237</v>
+      </c>
+      <c r="L141" s="7">
+        <v>14.795</v>
+      </c>
+      <c r="M141" s="7">
+        <v>14.919</v>
+      </c>
+      <c r="N141" s="7">
+        <v>14.779</v>
+      </c>
+      <c r="O141" s="7">
+        <v>21.472999999999999</v>
+      </c>
+      <c r="P141" s="7">
+        <v>22.004999999999999</v>
+      </c>
+      <c r="Q141" s="7">
+        <v>22.143000000000001</v>
+      </c>
+      <c r="R141" s="7">
+        <v>20.978000000000002</v>
+      </c>
+      <c r="S141" s="7">
+        <v>22.094999999999999</v>
+      </c>
+      <c r="T141" s="7">
+        <v>20.61</v>
+      </c>
+      <c r="U141" s="7">
+        <v>21.286999999999999</v>
+      </c>
       <c r="V141" s="3"/>
       <c r="W141" s="2" t="s">
         <v>182</v>
@@ -16504,21 +16612,51 @@
       <c r="F242" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G242" s="3"/>
-      <c r="H242" s="3"/>
-      <c r="I242" s="3"/>
-      <c r="J242" s="3"/>
-      <c r="K242" s="3"/>
-      <c r="L242" s="3"/>
-      <c r="M242" s="3"/>
-      <c r="N242" s="3"/>
-      <c r="O242" s="3"/>
-      <c r="P242" s="3"/>
-      <c r="Q242" s="3"/>
-      <c r="R242" s="3"/>
-      <c r="S242" s="3"/>
-      <c r="T242" s="3"/>
-      <c r="U242" s="3"/>
+      <c r="G242" s="7">
+        <v>6.64</v>
+      </c>
+      <c r="H242" s="7">
+        <v>6.9180000000000001</v>
+      </c>
+      <c r="I242" s="7">
+        <v>6.5330000000000004</v>
+      </c>
+      <c r="J242" s="7">
+        <v>6.6660000000000004</v>
+      </c>
+      <c r="K242" s="7">
+        <v>6.319</v>
+      </c>
+      <c r="L242" s="7">
+        <v>5.6859999999999999</v>
+      </c>
+      <c r="M242" s="7">
+        <v>3.9740000000000002</v>
+      </c>
+      <c r="N242" s="7">
+        <v>4.2320000000000002</v>
+      </c>
+      <c r="O242" s="7">
+        <v>5.72</v>
+      </c>
+      <c r="P242" s="7">
+        <v>6.2</v>
+      </c>
+      <c r="Q242" s="7">
+        <v>6.5750000000000002</v>
+      </c>
+      <c r="R242" s="7">
+        <v>5.6740000000000004</v>
+      </c>
+      <c r="S242" s="7">
+        <v>5.7910000000000004</v>
+      </c>
+      <c r="T242" s="7">
+        <v>6.3390000000000004</v>
+      </c>
+      <c r="U242" s="7">
+        <v>6.0330000000000004</v>
+      </c>
       <c r="V242" s="3"/>
       <c r="W242" s="2" t="s">
         <v>182</v>
@@ -16543,21 +16681,51 @@
       <c r="F243" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G243" s="3"/>
-      <c r="H243" s="3"/>
-      <c r="I243" s="3"/>
-      <c r="J243" s="3"/>
-      <c r="K243" s="3"/>
-      <c r="L243" s="3"/>
-      <c r="M243" s="3"/>
-      <c r="N243" s="3"/>
-      <c r="O243" s="3"/>
-      <c r="P243" s="3"/>
-      <c r="Q243" s="3"/>
-      <c r="R243" s="3"/>
-      <c r="S243" s="3"/>
-      <c r="T243" s="3"/>
-      <c r="U243" s="3"/>
+      <c r="G243" s="7">
+        <v>6.5490000000000004</v>
+      </c>
+      <c r="H243" s="7">
+        <v>8.0779999999999994</v>
+      </c>
+      <c r="I243" s="7">
+        <v>10.61</v>
+      </c>
+      <c r="J243" s="7">
+        <v>10.676</v>
+      </c>
+      <c r="K243" s="7">
+        <v>12.36</v>
+      </c>
+      <c r="L243" s="7">
+        <v>13.401</v>
+      </c>
+      <c r="M243" s="7">
+        <v>13.342000000000001</v>
+      </c>
+      <c r="N243" s="7">
+        <v>13.082000000000001</v>
+      </c>
+      <c r="O243" s="7">
+        <v>13.026999999999999</v>
+      </c>
+      <c r="P243" s="7">
+        <v>14.356</v>
+      </c>
+      <c r="Q243" s="7">
+        <v>16.236999999999998</v>
+      </c>
+      <c r="R243" s="7">
+        <v>17.167000000000002</v>
+      </c>
+      <c r="S243" s="7">
+        <v>21.009</v>
+      </c>
+      <c r="T243" s="7">
+        <v>25.792999999999999</v>
+      </c>
+      <c r="U243" s="7">
+        <v>30.37</v>
+      </c>
       <c r="V243" s="3"/>
       <c r="W243" s="2" t="s">
         <v>182</v>
@@ -16582,21 +16750,51 @@
       <c r="F244" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G244" s="3"/>
-      <c r="H244" s="3"/>
-      <c r="I244" s="3"/>
-      <c r="J244" s="3"/>
-      <c r="K244" s="3"/>
-      <c r="L244" s="3"/>
-      <c r="M244" s="3"/>
-      <c r="N244" s="3"/>
-      <c r="O244" s="3"/>
-      <c r="P244" s="3"/>
-      <c r="Q244" s="3"/>
-      <c r="R244" s="3"/>
-      <c r="S244" s="3"/>
-      <c r="T244" s="3"/>
-      <c r="U244" s="3"/>
+      <c r="G244" s="7">
+        <v>11.811999999999999</v>
+      </c>
+      <c r="H244" s="7">
+        <v>13.24</v>
+      </c>
+      <c r="I244" s="7">
+        <v>13.497</v>
+      </c>
+      <c r="J244" s="7">
+        <v>14.265000000000001</v>
+      </c>
+      <c r="K244" s="7">
+        <v>14.237</v>
+      </c>
+      <c r="L244" s="7">
+        <v>14.795</v>
+      </c>
+      <c r="M244" s="7">
+        <v>14.919</v>
+      </c>
+      <c r="N244" s="7">
+        <v>14.779</v>
+      </c>
+      <c r="O244" s="7">
+        <v>21.472999999999999</v>
+      </c>
+      <c r="P244" s="7">
+        <v>22.004999999999999</v>
+      </c>
+      <c r="Q244" s="7">
+        <v>22.143000000000001</v>
+      </c>
+      <c r="R244" s="7">
+        <v>20.978000000000002</v>
+      </c>
+      <c r="S244" s="7">
+        <v>22.094999999999999</v>
+      </c>
+      <c r="T244" s="7">
+        <v>20.61</v>
+      </c>
+      <c r="U244" s="7">
+        <v>21.286999999999999</v>
+      </c>
       <c r="V244" s="3"/>
       <c r="W244" s="2" t="s">
         <v>182</v>
@@ -16690,21 +16888,51 @@
       <c r="F246" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="G246" s="3"/>
-      <c r="H246" s="3"/>
-      <c r="I246" s="3"/>
-      <c r="J246" s="3"/>
-      <c r="K246" s="3"/>
-      <c r="L246" s="3"/>
-      <c r="M246" s="3"/>
-      <c r="N246" s="3"/>
-      <c r="O246" s="3"/>
-      <c r="P246" s="3"/>
-      <c r="Q246" s="3"/>
-      <c r="R246" s="3"/>
-      <c r="S246" s="3"/>
-      <c r="T246" s="3"/>
-      <c r="U246" s="3"/>
+      <c r="G246" s="6">
+        <v>440</v>
+      </c>
+      <c r="H246" s="6">
+        <v>101</v>
+      </c>
+      <c r="I246" s="6">
+        <v>151</v>
+      </c>
+      <c r="J246" s="6">
+        <v>217</v>
+      </c>
+      <c r="K246" s="6">
+        <v>239</v>
+      </c>
+      <c r="L246" s="6">
+        <v>674</v>
+      </c>
+      <c r="M246" s="6">
+        <v>705</v>
+      </c>
+      <c r="N246" s="6">
+        <v>712</v>
+      </c>
+      <c r="O246" s="6">
+        <v>743</v>
+      </c>
+      <c r="P246" s="6">
+        <v>788</v>
+      </c>
+      <c r="Q246" s="6">
+        <v>805</v>
+      </c>
+      <c r="R246" s="6">
+        <v>892</v>
+      </c>
+      <c r="S246" s="6">
+        <v>988</v>
+      </c>
+      <c r="T246" s="6">
+        <v>1029</v>
+      </c>
+      <c r="U246" s="6">
+        <v>1167</v>
+      </c>
       <c r="V246" s="3"/>
       <c r="W246" s="2" t="s">
         <v>30</v>
@@ -16729,21 +16957,51 @@
       <c r="F247" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="G247" s="3"/>
-      <c r="H247" s="3"/>
-      <c r="I247" s="3"/>
-      <c r="J247" s="3"/>
-      <c r="K247" s="3"/>
-      <c r="L247" s="3"/>
-      <c r="M247" s="3"/>
-      <c r="N247" s="3"/>
-      <c r="O247" s="3"/>
-      <c r="P247" s="3"/>
-      <c r="Q247" s="3"/>
-      <c r="R247" s="3"/>
-      <c r="S247" s="3"/>
-      <c r="T247" s="3"/>
-      <c r="U247" s="3"/>
+      <c r="G247" s="6">
+        <v>123</v>
+      </c>
+      <c r="H247" s="6">
+        <v>101</v>
+      </c>
+      <c r="I247" s="6">
+        <v>151</v>
+      </c>
+      <c r="J247" s="6">
+        <v>217</v>
+      </c>
+      <c r="K247" s="6">
+        <v>239</v>
+      </c>
+      <c r="L247" s="6">
+        <v>235</v>
+      </c>
+      <c r="M247" s="6">
+        <v>225</v>
+      </c>
+      <c r="N247" s="6">
+        <v>234</v>
+      </c>
+      <c r="O247" s="6">
+        <v>248</v>
+      </c>
+      <c r="P247" s="6">
+        <v>263</v>
+      </c>
+      <c r="Q247" s="6">
+        <v>268</v>
+      </c>
+      <c r="R247" s="6">
+        <v>297</v>
+      </c>
+      <c r="S247" s="6">
+        <v>329</v>
+      </c>
+      <c r="T247" s="6">
+        <v>343</v>
+      </c>
+      <c r="U247" s="6">
+        <v>389</v>
+      </c>
       <c r="V247" s="3"/>
       <c r="W247" s="2" t="s">
         <v>30</v>
@@ -16820,7 +17078,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="249" spans="1:23" ht="18" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
         <v>313</v>
       </c>
@@ -16839,57 +17097,55 @@
       <c r="F249" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G249" s="5">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="H249" s="5">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="I249" s="5">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="J249" s="5">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="K249" s="5">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="L249" s="5">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="M249" s="5">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="N249" s="5">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="O249" s="5">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="P249" s="5">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="Q249" s="5">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="R249" s="5">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="S249" s="5">
-        <v>0.59</v>
-      </c>
-      <c r="T249" s="5">
-        <v>0.59</v>
-      </c>
-      <c r="U249" s="5">
-        <v>0.59</v>
-      </c>
+      <c r="G249" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="H249" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="I249" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="J249" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="K249" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="L249" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="M249" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="N249" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="O249" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="P249" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="Q249" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="R249" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="S249" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="T249" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="U249" s="3"/>
       <c r="V249" s="3"/>
       <c r="W249" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="250" spans="1:23" ht="18" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="250" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>313</v>
       </c>
@@ -16903,60 +17159,62 @@
         <v>27</v>
       </c>
       <c r="E250" s="3" t="s">
-        <v>28</v>
+        <v>332</v>
       </c>
       <c r="F250" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="G250" s="4">
-        <v>732401.6</v>
-      </c>
-      <c r="H250" s="4">
-        <v>740630</v>
-      </c>
-      <c r="I250" s="4">
-        <v>753624</v>
-      </c>
-      <c r="J250" s="4">
-        <v>752240.3</v>
-      </c>
-      <c r="K250" s="4">
-        <v>804401.8</v>
-      </c>
-      <c r="L250" s="4">
-        <v>830309.8</v>
-      </c>
-      <c r="M250" s="4">
-        <v>826034.2</v>
-      </c>
-      <c r="N250" s="3"/>
-      <c r="O250" s="4">
-        <v>846693.5</v>
-      </c>
-      <c r="P250" s="4">
-        <v>839607.4</v>
-      </c>
-      <c r="Q250" s="4">
-        <v>852978.8</v>
-      </c>
-      <c r="R250" s="4">
-        <v>855928.1</v>
-      </c>
-      <c r="S250" s="4">
-        <v>859996.9</v>
-      </c>
-      <c r="T250" s="4">
-        <v>870987.2</v>
-      </c>
-      <c r="U250" s="4">
-        <v>881284.3</v>
+        <v>333</v>
+      </c>
+      <c r="G250" s="5">
+        <v>137.94999999999999</v>
+      </c>
+      <c r="H250" s="5">
+        <v>0</v>
+      </c>
+      <c r="I250" s="5">
+        <v>0.18</v>
+      </c>
+      <c r="J250" s="5">
+        <v>0</v>
+      </c>
+      <c r="K250" s="5">
+        <v>0</v>
+      </c>
+      <c r="L250" s="5">
+        <v>0</v>
+      </c>
+      <c r="M250" s="5">
+        <v>0</v>
+      </c>
+      <c r="N250" s="5">
+        <v>2.29</v>
+      </c>
+      <c r="O250" s="5">
+        <v>25.44</v>
+      </c>
+      <c r="P250" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q250" s="5">
+        <v>12.02</v>
+      </c>
+      <c r="R250" s="5">
+        <v>0.89</v>
+      </c>
+      <c r="S250" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="T250" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="U250" s="5">
+        <v>80.36</v>
       </c>
       <c r="V250" s="3"/>
       <c r="W250" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="251" spans="1:23" ht="18" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="251" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
         <v>313</v>
       </c>
@@ -16964,57 +17222,65 @@
         <v>329</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D251" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E251" s="3" t="s">
-        <v>28</v>
+        <v>334</v>
       </c>
       <c r="F251" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="G251" s="3"/>
-      <c r="H251" s="3"/>
-      <c r="I251" s="3"/>
-      <c r="J251" s="3"/>
-      <c r="K251" s="3"/>
-      <c r="L251" s="5">
-        <v>6.6</v>
-      </c>
-      <c r="M251" s="5">
-        <v>7.58</v>
-      </c>
-      <c r="N251" s="5">
-        <v>7.54</v>
-      </c>
-      <c r="O251" s="5">
-        <v>10.15</v>
-      </c>
-      <c r="P251" s="5">
-        <v>12.38</v>
-      </c>
-      <c r="Q251" s="5">
-        <v>12.53</v>
-      </c>
-      <c r="R251" s="5">
-        <v>5.95</v>
-      </c>
-      <c r="S251" s="5">
-        <v>4.7300000000000004</v>
-      </c>
-      <c r="T251" s="5">
-        <v>6.25</v>
-      </c>
-      <c r="U251" s="5">
-        <v>5.6</v>
-      </c>
-      <c r="V251" s="5">
-        <v>5.95</v>
-      </c>
+      <c r="G251" s="6">
+        <v>5248</v>
+      </c>
+      <c r="H251" s="6">
+        <v>0</v>
+      </c>
+      <c r="I251" s="6">
+        <v>7</v>
+      </c>
+      <c r="J251" s="6">
+        <v>0</v>
+      </c>
+      <c r="K251" s="6">
+        <v>0</v>
+      </c>
+      <c r="L251" s="6">
+        <v>0</v>
+      </c>
+      <c r="M251" s="6">
+        <v>0</v>
+      </c>
+      <c r="N251" s="6">
+        <v>87</v>
+      </c>
+      <c r="O251" s="6">
+        <v>966</v>
+      </c>
+      <c r="P251" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q251" s="6">
+        <v>451</v>
+      </c>
+      <c r="R251" s="6">
+        <v>33</v>
+      </c>
+      <c r="S251" s="6">
+        <v>1</v>
+      </c>
+      <c r="T251" s="6">
+        <v>1</v>
+      </c>
+      <c r="U251" s="6">
+        <v>2938</v>
+      </c>
+      <c r="V251" s="3"/>
       <c r="W251" s="2" t="s">
-        <v>170</v>
+        <v>27</v>
       </c>
     </row>
     <row r="252" spans="1:23" ht="18" x14ac:dyDescent="0.25">
@@ -17022,10 +17288,10 @@
         <v>313</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D252" s="2" t="s">
         <v>27</v>
@@ -17036,51 +17302,65 @@
       <c r="F252" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G252" s="3"/>
-      <c r="H252" s="3"/>
-      <c r="I252" s="3"/>
-      <c r="J252" s="3"/>
-      <c r="K252" s="3"/>
-      <c r="L252" s="3"/>
-      <c r="M252" s="3"/>
-      <c r="N252" s="3"/>
-      <c r="O252" s="6">
-        <v>1</v>
-      </c>
-      <c r="P252" s="6">
-        <v>54</v>
-      </c>
-      <c r="Q252" s="6">
-        <v>63</v>
-      </c>
-      <c r="R252" s="6">
-        <v>66</v>
-      </c>
-      <c r="S252" s="6">
-        <v>70</v>
-      </c>
-      <c r="T252" s="6">
-        <v>75</v>
-      </c>
-      <c r="U252" s="6">
-        <v>80</v>
-      </c>
-      <c r="V252" s="6">
-        <v>86</v>
-      </c>
+      <c r="G252" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="H252" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="I252" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J252" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="K252" s="5">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="L252" s="5">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="M252" s="5">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="N252" s="5">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="O252" s="5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="P252" s="5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="Q252" s="5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="R252" s="5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="S252" s="5">
+        <v>0.59</v>
+      </c>
+      <c r="T252" s="5">
+        <v>0.59</v>
+      </c>
+      <c r="U252" s="5">
+        <v>0.59</v>
+      </c>
+      <c r="V252" s="3"/>
       <c r="W252" s="2" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="253" spans="1:23" ht="99" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="253" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>313</v>
       </c>
       <c r="B253" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C253" s="2" t="s">
         <v>337</v>
-      </c>
-      <c r="C253" s="2" t="s">
-        <v>338</v>
       </c>
       <c r="D253" s="2" t="s">
         <v>27</v>
@@ -17089,45 +17369,65 @@
         <v>28</v>
       </c>
       <c r="F253" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="G253" s="3"/>
-      <c r="H253" s="3"/>
-      <c r="I253" s="3"/>
-      <c r="J253" s="3"/>
-      <c r="K253" s="3"/>
-      <c r="L253" s="3"/>
-      <c r="M253" s="3"/>
+        <v>169</v>
+      </c>
+      <c r="G253" s="4">
+        <v>732401.6</v>
+      </c>
+      <c r="H253" s="4">
+        <v>740630</v>
+      </c>
+      <c r="I253" s="4">
+        <v>753624</v>
+      </c>
+      <c r="J253" s="4">
+        <v>752240.3</v>
+      </c>
+      <c r="K253" s="4">
+        <v>804401.8</v>
+      </c>
+      <c r="L253" s="4">
+        <v>830309.8</v>
+      </c>
+      <c r="M253" s="4">
+        <v>826034.2</v>
+      </c>
       <c r="N253" s="3"/>
-      <c r="O253" s="3"/>
-      <c r="P253" s="3"/>
-      <c r="Q253" s="3"/>
-      <c r="R253" s="3"/>
-      <c r="S253" s="6">
-        <v>16</v>
-      </c>
-      <c r="T253" s="6">
-        <v>7</v>
-      </c>
-      <c r="U253" s="6">
-        <v>6</v>
-      </c>
-      <c r="V253" s="6">
-        <v>4</v>
-      </c>
+      <c r="O253" s="4">
+        <v>846693.5</v>
+      </c>
+      <c r="P253" s="4">
+        <v>839607.4</v>
+      </c>
+      <c r="Q253" s="4">
+        <v>852978.8</v>
+      </c>
+      <c r="R253" s="4">
+        <v>855928.1</v>
+      </c>
+      <c r="S253" s="4">
+        <v>859996.9</v>
+      </c>
+      <c r="T253" s="4">
+        <v>870987.2</v>
+      </c>
+      <c r="U253" s="4">
+        <v>881284.3</v>
+      </c>
+      <c r="V253" s="3"/>
       <c r="W253" s="2" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="254" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="254" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
         <v>313</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D254" s="2" t="s">
         <v>27</v>
@@ -17136,530 +17436,486 @@
         <v>28</v>
       </c>
       <c r="F254" s="3" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G254" s="3"/>
       <c r="H254" s="3"/>
       <c r="I254" s="3"/>
       <c r="J254" s="3"/>
       <c r="K254" s="3"/>
-      <c r="L254" s="3"/>
-      <c r="M254" s="3"/>
-      <c r="N254" s="3"/>
-      <c r="O254" s="3"/>
-      <c r="P254" s="3"/>
-      <c r="Q254" s="3"/>
-      <c r="R254" s="6">
+      <c r="L254" s="5">
+        <v>6.6</v>
+      </c>
+      <c r="M254" s="5">
+        <v>7.58</v>
+      </c>
+      <c r="N254" s="5">
+        <v>7.54</v>
+      </c>
+      <c r="O254" s="5">
+        <v>10.15</v>
+      </c>
+      <c r="P254" s="5">
+        <v>12.38</v>
+      </c>
+      <c r="Q254" s="5">
+        <v>12.53</v>
+      </c>
+      <c r="R254" s="5">
+        <v>5.95</v>
+      </c>
+      <c r="S254" s="5">
+        <v>4.7300000000000004</v>
+      </c>
+      <c r="T254" s="5">
+        <v>6.25</v>
+      </c>
+      <c r="U254" s="5">
+        <v>5.6</v>
+      </c>
+      <c r="V254" s="5">
+        <v>5.95</v>
+      </c>
+      <c r="W254" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="255" spans="1:23" ht="18" x14ac:dyDescent="0.25">
+      <c r="A255" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B255" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C255" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D255" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E255" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F255" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G255" s="3"/>
+      <c r="H255" s="3"/>
+      <c r="I255" s="3"/>
+      <c r="J255" s="3"/>
+      <c r="K255" s="3"/>
+      <c r="L255" s="3"/>
+      <c r="M255" s="3"/>
+      <c r="N255" s="3"/>
+      <c r="O255" s="6">
+        <v>1</v>
+      </c>
+      <c r="P255" s="6">
+        <v>54</v>
+      </c>
+      <c r="Q255" s="6">
+        <v>63</v>
+      </c>
+      <c r="R255" s="6">
+        <v>66</v>
+      </c>
+      <c r="S255" s="6">
+        <v>70</v>
+      </c>
+      <c r="T255" s="6">
+        <v>75</v>
+      </c>
+      <c r="U255" s="6">
+        <v>80</v>
+      </c>
+      <c r="V255" s="6">
+        <v>86</v>
+      </c>
+      <c r="W255" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="256" spans="1:23" ht="99" x14ac:dyDescent="0.25">
+      <c r="A256" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B256" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C256" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="D256" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E256" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F256" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="G256" s="3"/>
+      <c r="H256" s="3"/>
+      <c r="I256" s="3"/>
+      <c r="J256" s="3"/>
+      <c r="K256" s="3"/>
+      <c r="L256" s="3"/>
+      <c r="M256" s="3"/>
+      <c r="N256" s="3"/>
+      <c r="O256" s="3"/>
+      <c r="P256" s="3"/>
+      <c r="Q256" s="3"/>
+      <c r="R256" s="3"/>
+      <c r="S256" s="6">
+        <v>16</v>
+      </c>
+      <c r="T256" s="6">
+        <v>7</v>
+      </c>
+      <c r="U256" s="6">
+        <v>6</v>
+      </c>
+      <c r="V256" s="6">
+        <v>4</v>
+      </c>
+      <c r="W256" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="257" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+      <c r="A257" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B257" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C257" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D257" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E257" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F257" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="G257" s="3"/>
+      <c r="H257" s="3"/>
+      <c r="I257" s="3"/>
+      <c r="J257" s="3"/>
+      <c r="K257" s="3"/>
+      <c r="L257" s="3"/>
+      <c r="M257" s="3"/>
+      <c r="N257" s="3"/>
+      <c r="O257" s="3"/>
+      <c r="P257" s="3"/>
+      <c r="Q257" s="3"/>
+      <c r="R257" s="6">
         <v>133</v>
       </c>
-      <c r="S254" s="6">
+      <c r="S257" s="6">
         <v>80</v>
       </c>
-      <c r="T254" s="6">
+      <c r="T257" s="6">
         <v>97</v>
       </c>
-      <c r="U254" s="6">
+      <c r="U257" s="6">
         <v>44</v>
       </c>
-      <c r="V254" s="6">
+      <c r="V257" s="6">
         <v>89</v>
       </c>
-      <c r="W254" s="2" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="255" spans="1:23" ht="72" x14ac:dyDescent="0.25">
-      <c r="A255" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="B255" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="C255" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="D255" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="E255" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="F255" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G255" s="6">
-        <v>40</v>
-      </c>
-      <c r="H255" s="6">
-        <v>60</v>
-      </c>
-      <c r="I255" s="6">
-        <v>40</v>
-      </c>
-      <c r="J255" s="6">
-        <v>40</v>
-      </c>
-      <c r="K255" s="6">
-        <v>40</v>
-      </c>
-      <c r="L255" s="6">
-        <v>40</v>
-      </c>
-      <c r="M255" s="6">
-        <v>60</v>
-      </c>
-      <c r="N255" s="6">
-        <v>40</v>
-      </c>
-      <c r="O255" s="6">
-        <v>40</v>
-      </c>
-      <c r="P255" s="6">
-        <v>40</v>
-      </c>
-      <c r="Q255" s="6">
-        <v>60</v>
-      </c>
-      <c r="R255" s="6">
-        <v>67</v>
-      </c>
-      <c r="S255" s="6">
-        <v>50</v>
-      </c>
-      <c r="T255" s="6">
-        <v>67</v>
-      </c>
-      <c r="U255" s="6">
-        <v>67</v>
-      </c>
-      <c r="V255" s="3"/>
-      <c r="W255" s="2" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="256" spans="1:23" ht="72" x14ac:dyDescent="0.25">
-      <c r="A256" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="B256" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="C256" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="D256" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="E256" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="F256" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G256" s="6">
-        <v>40</v>
-      </c>
-      <c r="H256" s="6">
-        <v>60</v>
-      </c>
-      <c r="I256" s="6">
-        <v>20</v>
-      </c>
-      <c r="J256" s="6">
-        <v>20</v>
-      </c>
-      <c r="K256" s="6">
-        <v>20</v>
-      </c>
-      <c r="L256" s="6">
-        <v>40</v>
-      </c>
-      <c r="M256" s="6">
-        <v>60</v>
-      </c>
-      <c r="N256" s="6">
-        <v>40</v>
-      </c>
-      <c r="O256" s="6">
-        <v>25</v>
-      </c>
-      <c r="P256" s="6">
-        <v>25</v>
-      </c>
-      <c r="Q256" s="6">
-        <v>20</v>
-      </c>
-      <c r="R256" s="6">
-        <v>17</v>
-      </c>
-      <c r="S256" s="6">
-        <v>0</v>
-      </c>
-      <c r="T256" s="6">
-        <v>17</v>
-      </c>
-      <c r="U256" s="6">
-        <v>0</v>
-      </c>
-      <c r="V256" s="3"/>
-      <c r="W256" s="2" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="257" spans="1:23" ht="72" x14ac:dyDescent="0.25">
-      <c r="A257" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="B257" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="C257" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="D257" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="E257" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="F257" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G257" s="6">
-        <v>0</v>
-      </c>
-      <c r="H257" s="6">
-        <v>0</v>
-      </c>
-      <c r="I257" s="6">
-        <v>20</v>
-      </c>
-      <c r="J257" s="6">
-        <v>20</v>
-      </c>
-      <c r="K257" s="6">
-        <v>20</v>
-      </c>
-      <c r="L257" s="6">
-        <v>0</v>
-      </c>
-      <c r="M257" s="6">
-        <v>0</v>
-      </c>
-      <c r="N257" s="6">
-        <v>0</v>
-      </c>
-      <c r="O257" s="6">
-        <v>0</v>
-      </c>
-      <c r="P257" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q257" s="6">
-        <v>40</v>
-      </c>
-      <c r="R257" s="6">
-        <v>17</v>
-      </c>
-      <c r="S257" s="6">
-        <v>17</v>
-      </c>
-      <c r="T257" s="6">
-        <v>17</v>
-      </c>
-      <c r="U257" s="6">
-        <v>50</v>
-      </c>
-      <c r="V257" s="3"/>
       <c r="W257" s="2" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="258" spans="1:23" ht="72" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="E258" s="3" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F258" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G258" s="6">
+        <v>40</v>
+      </c>
+      <c r="H258" s="6">
         <v>60</v>
       </c>
-      <c r="H258" s="6">
+      <c r="I258" s="6">
         <v>40</v>
       </c>
-      <c r="I258" s="6">
+      <c r="J258" s="6">
+        <v>40</v>
+      </c>
+      <c r="K258" s="6">
+        <v>40</v>
+      </c>
+      <c r="L258" s="6">
+        <v>40</v>
+      </c>
+      <c r="M258" s="6">
         <v>60</v>
       </c>
-      <c r="J258" s="6">
+      <c r="N258" s="6">
+        <v>40</v>
+      </c>
+      <c r="O258" s="6">
+        <v>40</v>
+      </c>
+      <c r="P258" s="6">
+        <v>40</v>
+      </c>
+      <c r="Q258" s="6">
         <v>60</v>
       </c>
-      <c r="K258" s="6">
-        <v>60</v>
-      </c>
-      <c r="L258" s="6">
-        <v>60</v>
-      </c>
-      <c r="M258" s="6">
-        <v>40</v>
-      </c>
-      <c r="N258" s="6">
-        <v>60</v>
-      </c>
-      <c r="O258" s="6">
-        <v>75</v>
-      </c>
-      <c r="P258" s="6">
-        <v>75</v>
-      </c>
-      <c r="Q258" s="6">
-        <v>40</v>
-      </c>
       <c r="R258" s="6">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="S258" s="6">
         <v>50</v>
       </c>
       <c r="T258" s="6">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="U258" s="6">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="V258" s="3"/>
       <c r="W258" s="2" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="259" spans="1:23" ht="18" x14ac:dyDescent="0.25">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="259" spans="1:23" ht="72" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="B259" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C259" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="D259" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="C259" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="D259" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="E259" s="3" t="s">
-        <v>28</v>
+        <v>355</v>
       </c>
       <c r="F259" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="G259" s="4">
-        <v>100</v>
-      </c>
-      <c r="H259" s="4">
-        <v>100.8</v>
-      </c>
-      <c r="I259" s="4">
-        <v>99.9</v>
-      </c>
-      <c r="J259" s="4">
-        <v>101.8</v>
-      </c>
-      <c r="K259" s="4">
-        <v>104.9</v>
-      </c>
-      <c r="L259" s="4">
-        <v>106</v>
-      </c>
-      <c r="M259" s="4">
-        <v>119.9</v>
-      </c>
-      <c r="N259" s="4">
-        <v>119.4</v>
-      </c>
-      <c r="O259" s="4">
-        <v>130</v>
-      </c>
-      <c r="P259" s="4">
-        <v>189.5</v>
-      </c>
-      <c r="Q259" s="4">
-        <v>186.6</v>
-      </c>
-      <c r="R259" s="4">
-        <v>190.1</v>
-      </c>
-      <c r="S259" s="4">
-        <v>200.8</v>
-      </c>
-      <c r="T259" s="4">
-        <v>205.6</v>
-      </c>
-      <c r="U259" s="4">
-        <v>208.5</v>
+        <v>36</v>
+      </c>
+      <c r="G259" s="6">
+        <v>40</v>
+      </c>
+      <c r="H259" s="6">
+        <v>60</v>
+      </c>
+      <c r="I259" s="6">
+        <v>20</v>
+      </c>
+      <c r="J259" s="6">
+        <v>20</v>
+      </c>
+      <c r="K259" s="6">
+        <v>20</v>
+      </c>
+      <c r="L259" s="6">
+        <v>40</v>
+      </c>
+      <c r="M259" s="6">
+        <v>60</v>
+      </c>
+      <c r="N259" s="6">
+        <v>40</v>
+      </c>
+      <c r="O259" s="6">
+        <v>25</v>
+      </c>
+      <c r="P259" s="6">
+        <v>25</v>
+      </c>
+      <c r="Q259" s="6">
+        <v>20</v>
+      </c>
+      <c r="R259" s="6">
+        <v>17</v>
+      </c>
+      <c r="S259" s="6">
+        <v>0</v>
+      </c>
+      <c r="T259" s="6">
+        <v>17</v>
+      </c>
+      <c r="U259" s="6">
+        <v>0</v>
       </c>
       <c r="V259" s="3"/>
       <c r="W259" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="260" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="260" spans="1:23" ht="72" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>27</v>
+        <v>352</v>
       </c>
       <c r="E260" s="3" t="s">
-        <v>28</v>
+        <v>356</v>
       </c>
       <c r="F260" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="G260" s="4">
-        <v>59.5</v>
-      </c>
-      <c r="H260" s="4">
-        <v>57.7</v>
-      </c>
-      <c r="I260" s="4">
-        <v>58.8</v>
-      </c>
-      <c r="J260" s="4">
-        <v>64.3</v>
-      </c>
-      <c r="K260" s="4">
-        <v>68.7</v>
-      </c>
-      <c r="L260" s="4">
-        <v>69.5</v>
-      </c>
-      <c r="M260" s="4">
-        <v>72.900000000000006</v>
-      </c>
-      <c r="N260" s="4">
-        <v>78.099999999999994</v>
-      </c>
-      <c r="O260" s="4">
-        <v>91.8</v>
-      </c>
-      <c r="P260" s="4">
-        <v>93.9</v>
-      </c>
-      <c r="Q260" s="4">
-        <v>88.5</v>
-      </c>
-      <c r="R260" s="4">
-        <v>96.7</v>
-      </c>
-      <c r="S260" s="4">
-        <v>119</v>
-      </c>
-      <c r="T260" s="4">
-        <v>136.4</v>
-      </c>
-      <c r="U260" s="4">
-        <v>124.2</v>
+        <v>36</v>
+      </c>
+      <c r="G260" s="6">
+        <v>0</v>
+      </c>
+      <c r="H260" s="6">
+        <v>0</v>
+      </c>
+      <c r="I260" s="6">
+        <v>20</v>
+      </c>
+      <c r="J260" s="6">
+        <v>20</v>
+      </c>
+      <c r="K260" s="6">
+        <v>20</v>
+      </c>
+      <c r="L260" s="6">
+        <v>0</v>
+      </c>
+      <c r="M260" s="6">
+        <v>0</v>
+      </c>
+      <c r="N260" s="6">
+        <v>0</v>
+      </c>
+      <c r="O260" s="6">
+        <v>0</v>
+      </c>
+      <c r="P260" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q260" s="6">
+        <v>40</v>
+      </c>
+      <c r="R260" s="6">
+        <v>17</v>
+      </c>
+      <c r="S260" s="6">
+        <v>17</v>
+      </c>
+      <c r="T260" s="6">
+        <v>17</v>
+      </c>
+      <c r="U260" s="6">
+        <v>50</v>
       </c>
       <c r="V260" s="3"/>
       <c r="W260" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="261" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="261" spans="1:23" ht="72" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C261" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="D261" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E261" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="B261" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C261" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="D261" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E261" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="F261" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="G261" s="4">
-        <v>90.8</v>
-      </c>
-      <c r="H261" s="4">
-        <v>88.8</v>
-      </c>
-      <c r="I261" s="4">
-        <v>86.5</v>
-      </c>
-      <c r="J261" s="4">
-        <v>87</v>
-      </c>
-      <c r="K261" s="4">
-        <v>85</v>
-      </c>
-      <c r="L261" s="4">
-        <v>87.4</v>
-      </c>
-      <c r="M261" s="4">
-        <v>88.7</v>
-      </c>
-      <c r="N261" s="4">
-        <v>84.6</v>
-      </c>
-      <c r="O261" s="4">
-        <v>77.3</v>
-      </c>
-      <c r="P261" s="4">
-        <v>79.7</v>
-      </c>
-      <c r="Q261" s="4">
-        <v>81.900000000000006</v>
-      </c>
-      <c r="R261" s="4">
-        <v>74.8</v>
-      </c>
-      <c r="S261" s="4">
-        <v>77</v>
-      </c>
-      <c r="T261" s="4">
-        <v>77.2</v>
-      </c>
-      <c r="U261" s="4">
-        <v>76.3</v>
+        <v>36</v>
+      </c>
+      <c r="G261" s="6">
+        <v>60</v>
+      </c>
+      <c r="H261" s="6">
+        <v>40</v>
+      </c>
+      <c r="I261" s="6">
+        <v>60</v>
+      </c>
+      <c r="J261" s="6">
+        <v>60</v>
+      </c>
+      <c r="K261" s="6">
+        <v>60</v>
+      </c>
+      <c r="L261" s="6">
+        <v>60</v>
+      </c>
+      <c r="M261" s="6">
+        <v>40</v>
+      </c>
+      <c r="N261" s="6">
+        <v>60</v>
+      </c>
+      <c r="O261" s="6">
+        <v>75</v>
+      </c>
+      <c r="P261" s="6">
+        <v>75</v>
+      </c>
+      <c r="Q261" s="6">
+        <v>40</v>
+      </c>
+      <c r="R261" s="6">
+        <v>33</v>
+      </c>
+      <c r="S261" s="6">
+        <v>50</v>
+      </c>
+      <c r="T261" s="6">
+        <v>17</v>
+      </c>
+      <c r="U261" s="6">
+        <v>25</v>
       </c>
       <c r="V261" s="3"/>
       <c r="W261" s="2" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="262" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="262" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="B262" s="2" t="s">
         <v>358</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="D262" s="2" t="s">
         <v>27</v>
@@ -17668,67 +17924,67 @@
         <v>28</v>
       </c>
       <c r="F262" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G262" s="7">
-        <v>0.19600000000000001</v>
-      </c>
-      <c r="H262" s="7">
-        <v>0.20499999999999999</v>
-      </c>
-      <c r="I262" s="7">
-        <v>0.20599999999999999</v>
-      </c>
-      <c r="J262" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="K262" s="7">
-        <v>0.20100000000000001</v>
-      </c>
-      <c r="L262" s="7">
-        <v>0.20300000000000001</v>
-      </c>
-      <c r="M262" s="7">
-        <v>0.20699999999999999</v>
-      </c>
-      <c r="N262" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="O262" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="P262" s="7">
-        <v>0.19900000000000001</v>
-      </c>
-      <c r="Q262" s="7">
-        <v>0.2</v>
-      </c>
-      <c r="R262" s="7">
-        <v>0.19900000000000001</v>
-      </c>
-      <c r="S262" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="T262" s="7">
-        <v>0.192</v>
-      </c>
-      <c r="U262" s="7">
-        <v>0.192</v>
+        <v>319</v>
+      </c>
+      <c r="G262" s="4">
+        <v>100</v>
+      </c>
+      <c r="H262" s="4">
+        <v>100.8</v>
+      </c>
+      <c r="I262" s="4">
+        <v>99.9</v>
+      </c>
+      <c r="J262" s="4">
+        <v>101.8</v>
+      </c>
+      <c r="K262" s="4">
+        <v>104.9</v>
+      </c>
+      <c r="L262" s="4">
+        <v>106</v>
+      </c>
+      <c r="M262" s="4">
+        <v>119.9</v>
+      </c>
+      <c r="N262" s="4">
+        <v>119.4</v>
+      </c>
+      <c r="O262" s="4">
+        <v>130</v>
+      </c>
+      <c r="P262" s="4">
+        <v>189.5</v>
+      </c>
+      <c r="Q262" s="4">
+        <v>186.6</v>
+      </c>
+      <c r="R262" s="4">
+        <v>190.1</v>
+      </c>
+      <c r="S262" s="4">
+        <v>200.8</v>
+      </c>
+      <c r="T262" s="4">
+        <v>205.6</v>
+      </c>
+      <c r="U262" s="4">
+        <v>208.5</v>
       </c>
       <c r="V262" s="3"/>
       <c r="W262" s="2" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="263" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="263" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="D263" s="2" t="s">
         <v>27</v>
@@ -17737,52 +17993,52 @@
         <v>28</v>
       </c>
       <c r="F263" s="3" t="s">
-        <v>36</v>
+        <v>362</v>
       </c>
       <c r="G263" s="4">
-        <v>30.5</v>
+        <v>59.5</v>
       </c>
       <c r="H263" s="4">
-        <v>30.5</v>
+        <v>57.7</v>
       </c>
       <c r="I263" s="4">
-        <v>30.6</v>
+        <v>58.8</v>
       </c>
       <c r="J263" s="4">
-        <v>30.6</v>
+        <v>64.3</v>
       </c>
       <c r="K263" s="4">
-        <v>30.7</v>
+        <v>68.7</v>
       </c>
       <c r="L263" s="4">
-        <v>30.8</v>
+        <v>69.5</v>
       </c>
       <c r="M263" s="4">
-        <v>30.8</v>
+        <v>72.900000000000006</v>
       </c>
       <c r="N263" s="4">
-        <v>30.9</v>
+        <v>78.099999999999994</v>
       </c>
       <c r="O263" s="4">
-        <v>30.9</v>
+        <v>91.8</v>
       </c>
       <c r="P263" s="4">
-        <v>30.9</v>
+        <v>93.9</v>
       </c>
       <c r="Q263" s="4">
-        <v>30.9</v>
+        <v>88.5</v>
       </c>
       <c r="R263" s="4">
-        <v>30.9</v>
+        <v>96.7</v>
       </c>
       <c r="S263" s="4">
-        <v>31</v>
+        <v>119</v>
       </c>
       <c r="T263" s="4">
-        <v>31</v>
+        <v>136.4</v>
       </c>
       <c r="U263" s="4">
-        <v>31</v>
+        <v>124.2</v>
       </c>
       <c r="V263" s="3"/>
       <c r="W263" s="2" t="s">
@@ -17791,13 +18047,13 @@
     </row>
     <row r="264" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="B264" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="C264" s="2" t="s">
         <v>365</v>
-      </c>
-      <c r="C264" s="2" t="s">
-        <v>366</v>
       </c>
       <c r="D264" s="2" t="s">
         <v>27</v>
@@ -17806,70 +18062,70 @@
         <v>28</v>
       </c>
       <c r="F264" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="G264" s="6">
-        <v>28</v>
-      </c>
-      <c r="H264" s="6">
-        <v>27</v>
-      </c>
-      <c r="I264" s="6">
-        <v>26</v>
-      </c>
-      <c r="J264" s="6">
-        <v>25</v>
-      </c>
-      <c r="K264" s="6">
-        <v>24</v>
-      </c>
-      <c r="L264" s="6">
-        <v>23</v>
-      </c>
-      <c r="M264" s="6">
-        <v>22</v>
-      </c>
-      <c r="N264" s="6">
-        <v>22</v>
-      </c>
-      <c r="O264" s="6">
-        <v>22</v>
-      </c>
-      <c r="P264" s="6">
-        <v>21</v>
-      </c>
-      <c r="Q264" s="6">
-        <v>19</v>
-      </c>
-      <c r="R264" s="6">
-        <v>17</v>
-      </c>
-      <c r="S264" s="6">
-        <v>16</v>
-      </c>
-      <c r="T264" s="6">
-        <v>16</v>
-      </c>
-      <c r="U264" s="6">
-        <v>15</v>
+        <v>366</v>
+      </c>
+      <c r="G264" s="4">
+        <v>90.8</v>
+      </c>
+      <c r="H264" s="4">
+        <v>88.8</v>
+      </c>
+      <c r="I264" s="4">
+        <v>86.5</v>
+      </c>
+      <c r="J264" s="4">
+        <v>87</v>
+      </c>
+      <c r="K264" s="4">
+        <v>85</v>
+      </c>
+      <c r="L264" s="4">
+        <v>87.4</v>
+      </c>
+      <c r="M264" s="4">
+        <v>88.7</v>
+      </c>
+      <c r="N264" s="4">
+        <v>84.6</v>
+      </c>
+      <c r="O264" s="4">
+        <v>77.3</v>
+      </c>
+      <c r="P264" s="4">
+        <v>79.7</v>
+      </c>
+      <c r="Q264" s="4">
+        <v>81.900000000000006</v>
+      </c>
+      <c r="R264" s="4">
+        <v>74.8</v>
+      </c>
+      <c r="S264" s="4">
+        <v>77</v>
+      </c>
+      <c r="T264" s="4">
+        <v>77.2</v>
+      </c>
+      <c r="U264" s="4">
+        <v>76.3</v>
       </c>
       <c r="V264" s="3"/>
       <c r="W264" s="2" t="s">
-        <v>99</v>
+        <v>367</v>
       </c>
     </row>
     <row r="265" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E265" s="3" t="s">
         <v>28</v>
@@ -17877,119 +18133,119 @@
       <c r="F265" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G265" s="4">
-        <v>64.7</v>
-      </c>
-      <c r="H265" s="4">
-        <v>65.7</v>
-      </c>
-      <c r="I265" s="4">
-        <v>68.599999999999994</v>
-      </c>
-      <c r="J265" s="4">
-        <v>70.3</v>
-      </c>
-      <c r="K265" s="4">
-        <v>71.5</v>
-      </c>
-      <c r="L265" s="4">
-        <v>72.7</v>
-      </c>
-      <c r="M265" s="4">
-        <v>73.5</v>
-      </c>
-      <c r="N265" s="4">
-        <v>73.599999999999994</v>
-      </c>
-      <c r="O265" s="4">
-        <v>74</v>
-      </c>
-      <c r="P265" s="4">
-        <v>74.5</v>
-      </c>
-      <c r="Q265" s="4">
-        <v>74.900000000000006</v>
-      </c>
-      <c r="R265" s="4">
-        <v>75.2</v>
-      </c>
-      <c r="S265" s="4">
-        <v>75.7</v>
-      </c>
-      <c r="T265" s="4">
-        <v>75.900000000000006</v>
-      </c>
-      <c r="U265" s="4">
-        <v>76.2</v>
+      <c r="G265" s="7">
+        <v>0.19600000000000001</v>
+      </c>
+      <c r="H265" s="7">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="I265" s="7">
+        <v>0.20599999999999999</v>
+      </c>
+      <c r="J265" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="K265" s="7">
+        <v>0.20100000000000001</v>
+      </c>
+      <c r="L265" s="7">
+        <v>0.20300000000000001</v>
+      </c>
+      <c r="M265" s="7">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="N265" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="O265" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="P265" s="7">
+        <v>0.19900000000000001</v>
+      </c>
+      <c r="Q265" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="R265" s="7">
+        <v>0.19900000000000001</v>
+      </c>
+      <c r="S265" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="T265" s="7">
+        <v>0.192</v>
+      </c>
+      <c r="U265" s="7">
+        <v>0.192</v>
       </c>
       <c r="V265" s="3"/>
       <c r="W265" s="2" t="s">
-        <v>30</v>
+        <v>369</v>
       </c>
     </row>
     <row r="266" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E266" s="3" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F266" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G266" s="4">
-        <v>88</v>
+        <v>30.5</v>
       </c>
       <c r="H266" s="4">
-        <v>88.4</v>
+        <v>30.5</v>
       </c>
       <c r="I266" s="4">
-        <v>91.7</v>
+        <v>30.6</v>
       </c>
       <c r="J266" s="4">
-        <v>93.3</v>
+        <v>30.6</v>
       </c>
       <c r="K266" s="4">
-        <v>93.9</v>
+        <v>30.7</v>
       </c>
       <c r="L266" s="4">
-        <v>94.6</v>
+        <v>30.8</v>
       </c>
       <c r="M266" s="4">
-        <v>94.8</v>
+        <v>30.8</v>
       </c>
       <c r="N266" s="4">
-        <v>94.5</v>
+        <v>30.9</v>
       </c>
       <c r="O266" s="4">
-        <v>94.6</v>
+        <v>30.9</v>
       </c>
       <c r="P266" s="4">
-        <v>94.8</v>
+        <v>30.9</v>
       </c>
       <c r="Q266" s="4">
-        <v>94.7</v>
+        <v>30.9</v>
       </c>
       <c r="R266" s="4">
-        <v>94.6</v>
+        <v>30.9</v>
       </c>
       <c r="S266" s="4">
-        <v>95</v>
+        <v>31</v>
       </c>
       <c r="T266" s="4">
-        <v>94.8</v>
+        <v>31</v>
       </c>
       <c r="U266" s="4">
-        <v>94.6</v>
+        <v>31</v>
       </c>
       <c r="V266" s="3"/>
       <c r="W266" s="2" t="s">
@@ -17998,85 +18254,85 @@
     </row>
     <row r="267" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E267" s="3" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="F267" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G267" s="4">
-        <v>28.5</v>
-      </c>
-      <c r="H267" s="4">
-        <v>30.6</v>
-      </c>
-      <c r="I267" s="4">
-        <v>33.1</v>
-      </c>
-      <c r="J267" s="4">
-        <v>35.299999999999997</v>
-      </c>
-      <c r="K267" s="4">
-        <v>37.4</v>
-      </c>
-      <c r="L267" s="4">
-        <v>39.6</v>
-      </c>
-      <c r="M267" s="4">
-        <v>41.2</v>
-      </c>
-      <c r="N267" s="4">
-        <v>42</v>
-      </c>
-      <c r="O267" s="4">
-        <v>42.9</v>
-      </c>
-      <c r="P267" s="4">
-        <v>44</v>
-      </c>
-      <c r="Q267" s="4">
-        <v>45.4</v>
-      </c>
-      <c r="R267" s="4">
-        <v>46.5</v>
-      </c>
-      <c r="S267" s="4">
-        <v>47.2</v>
-      </c>
-      <c r="T267" s="4">
-        <v>48.2</v>
-      </c>
-      <c r="U267" s="4">
-        <v>49.3</v>
+        <v>98</v>
+      </c>
+      <c r="G267" s="6">
+        <v>28</v>
+      </c>
+      <c r="H267" s="6">
+        <v>27</v>
+      </c>
+      <c r="I267" s="6">
+        <v>26</v>
+      </c>
+      <c r="J267" s="6">
+        <v>25</v>
+      </c>
+      <c r="K267" s="6">
+        <v>24</v>
+      </c>
+      <c r="L267" s="6">
+        <v>23</v>
+      </c>
+      <c r="M267" s="6">
+        <v>22</v>
+      </c>
+      <c r="N267" s="6">
+        <v>22</v>
+      </c>
+      <c r="O267" s="6">
+        <v>22</v>
+      </c>
+      <c r="P267" s="6">
+        <v>21</v>
+      </c>
+      <c r="Q267" s="6">
+        <v>19</v>
+      </c>
+      <c r="R267" s="6">
+        <v>17</v>
+      </c>
+      <c r="S267" s="6">
+        <v>16</v>
+      </c>
+      <c r="T267" s="6">
+        <v>16</v>
+      </c>
+      <c r="U267" s="6">
+        <v>15</v>
       </c>
       <c r="V267" s="3"/>
       <c r="W267" s="2" t="s">
-        <v>30</v>
+        <v>99</v>
       </c>
     </row>
     <row r="268" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E268" s="3" t="s">
         <v>28</v>
@@ -18085,202 +18341,202 @@
         <v>36</v>
       </c>
       <c r="G268" s="4">
+        <v>64.7</v>
+      </c>
+      <c r="H268" s="4">
         <v>65.7</v>
       </c>
-      <c r="H268" s="4">
-        <v>64.8</v>
-      </c>
       <c r="I268" s="4">
-        <v>67.400000000000006</v>
+        <v>68.599999999999994</v>
       </c>
       <c r="J268" s="4">
-        <v>69.8</v>
+        <v>70.3</v>
       </c>
       <c r="K268" s="4">
-        <v>70.5</v>
+        <v>71.5</v>
       </c>
       <c r="L268" s="4">
-        <v>70.900000000000006</v>
+        <v>72.7</v>
       </c>
       <c r="M268" s="4">
-        <v>71.400000000000006</v>
+        <v>73.5</v>
       </c>
       <c r="N268" s="4">
-        <v>72.5</v>
+        <v>73.599999999999994</v>
       </c>
       <c r="O268" s="4">
-        <v>73.2</v>
+        <v>74</v>
       </c>
       <c r="P268" s="4">
-        <v>73.900000000000006</v>
+        <v>74.5</v>
       </c>
       <c r="Q268" s="4">
-        <v>73.3</v>
+        <v>74.900000000000006</v>
       </c>
       <c r="R268" s="4">
-        <v>72.8</v>
+        <v>75.2</v>
       </c>
       <c r="S268" s="4">
-        <v>76.3</v>
+        <v>75.7</v>
       </c>
       <c r="T268" s="4">
-        <v>78.099999999999994</v>
+        <v>75.900000000000006</v>
       </c>
       <c r="U268" s="4">
-        <v>78.599999999999994</v>
+        <v>76.2</v>
       </c>
       <c r="V268" s="3"/>
       <c r="W268" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="269" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E269" s="3" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="F269" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="G269" s="6">
-        <v>70108</v>
-      </c>
-      <c r="H269" s="6">
-        <v>248240</v>
-      </c>
-      <c r="I269" s="6">
-        <v>168221</v>
-      </c>
-      <c r="J269" s="6">
-        <v>72837</v>
-      </c>
-      <c r="K269" s="6">
-        <v>64283</v>
-      </c>
-      <c r="L269" s="6">
-        <v>68694</v>
-      </c>
-      <c r="M269" s="6">
-        <v>60135</v>
-      </c>
-      <c r="N269" s="6">
-        <v>46337</v>
-      </c>
-      <c r="O269" s="6">
-        <v>50289</v>
-      </c>
-      <c r="P269" s="6">
-        <v>104107</v>
-      </c>
-      <c r="Q269" s="6">
-        <v>201963</v>
-      </c>
-      <c r="R269" s="6">
-        <v>84506</v>
-      </c>
-      <c r="S269" s="6">
-        <v>295948</v>
-      </c>
-      <c r="T269" s="6">
-        <v>123796</v>
-      </c>
-      <c r="U269" s="6">
-        <v>104040</v>
+        <v>36</v>
+      </c>
+      <c r="G269" s="4">
+        <v>88</v>
+      </c>
+      <c r="H269" s="4">
+        <v>88.4</v>
+      </c>
+      <c r="I269" s="4">
+        <v>91.7</v>
+      </c>
+      <c r="J269" s="4">
+        <v>93.3</v>
+      </c>
+      <c r="K269" s="4">
+        <v>93.9</v>
+      </c>
+      <c r="L269" s="4">
+        <v>94.6</v>
+      </c>
+      <c r="M269" s="4">
+        <v>94.8</v>
+      </c>
+      <c r="N269" s="4">
+        <v>94.5</v>
+      </c>
+      <c r="O269" s="4">
+        <v>94.6</v>
+      </c>
+      <c r="P269" s="4">
+        <v>94.8</v>
+      </c>
+      <c r="Q269" s="4">
+        <v>94.7</v>
+      </c>
+      <c r="R269" s="4">
+        <v>94.6</v>
+      </c>
+      <c r="S269" s="4">
+        <v>95</v>
+      </c>
+      <c r="T269" s="4">
+        <v>94.8</v>
+      </c>
+      <c r="U269" s="4">
+        <v>94.6</v>
       </c>
       <c r="V269" s="3"/>
       <c r="W269" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="270" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E270" s="3" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F270" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G270" s="4">
-        <v>2.9</v>
+        <v>28.5</v>
       </c>
       <c r="H270" s="4">
-        <v>3.8</v>
+        <v>30.6</v>
       </c>
       <c r="I270" s="4">
-        <v>6</v>
+        <v>33.1</v>
       </c>
       <c r="J270" s="4">
-        <v>4.3</v>
+        <v>35.299999999999997</v>
       </c>
       <c r="K270" s="4">
-        <v>4.5999999999999996</v>
+        <v>37.4</v>
       </c>
       <c r="L270" s="4">
-        <v>4.2</v>
+        <v>39.6</v>
       </c>
       <c r="M270" s="4">
-        <v>3.1</v>
+        <v>41.2</v>
       </c>
       <c r="N270" s="4">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="O270" s="4">
-        <v>3.2</v>
+        <v>42.9</v>
       </c>
       <c r="P270" s="4">
-        <v>3.4</v>
+        <v>44</v>
       </c>
       <c r="Q270" s="4">
-        <v>3.2</v>
+        <v>45.4</v>
       </c>
       <c r="R270" s="4">
-        <v>4.5</v>
+        <v>46.5</v>
       </c>
       <c r="S270" s="4">
-        <v>6.6</v>
+        <v>47.2</v>
       </c>
       <c r="T270" s="4">
-        <v>5.8</v>
+        <v>48.2</v>
       </c>
       <c r="U270" s="4">
-        <v>4.5</v>
+        <v>49.3</v>
       </c>
       <c r="V270" s="3"/>
       <c r="W270" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="271" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="B271" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C271" s="2" t="s">
         <v>374</v>
-      </c>
-      <c r="C271" s="2" t="s">
-        <v>375</v>
       </c>
       <c r="D271" s="2" t="s">
         <v>27</v>
@@ -18291,67 +18547,65 @@
       <c r="F271" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G271" s="6">
-        <v>70</v>
-      </c>
-      <c r="H271" s="6">
-        <v>75</v>
-      </c>
-      <c r="I271" s="6">
-        <v>66</v>
-      </c>
-      <c r="J271" s="6">
-        <v>64</v>
-      </c>
-      <c r="K271" s="6">
-        <v>70</v>
-      </c>
-      <c r="L271" s="6">
-        <v>66</v>
-      </c>
-      <c r="M271" s="6">
-        <v>80</v>
-      </c>
-      <c r="N271" s="6">
-        <v>89</v>
-      </c>
-      <c r="O271" s="6">
-        <v>86</v>
-      </c>
-      <c r="P271" s="6">
-        <v>89</v>
-      </c>
-      <c r="Q271" s="6">
-        <v>85</v>
-      </c>
-      <c r="R271" s="6">
-        <v>82</v>
-      </c>
-      <c r="S271" s="6">
-        <v>83</v>
-      </c>
-      <c r="T271" s="6">
-        <v>88</v>
-      </c>
-      <c r="U271" s="6">
-        <v>88</v>
-      </c>
-      <c r="V271" s="6">
-        <v>86</v>
-      </c>
+      <c r="G271" s="4">
+        <v>65.7</v>
+      </c>
+      <c r="H271" s="4">
+        <v>64.8</v>
+      </c>
+      <c r="I271" s="4">
+        <v>67.400000000000006</v>
+      </c>
+      <c r="J271" s="4">
+        <v>69.8</v>
+      </c>
+      <c r="K271" s="4">
+        <v>70.5</v>
+      </c>
+      <c r="L271" s="4">
+        <v>70.900000000000006</v>
+      </c>
+      <c r="M271" s="4">
+        <v>71.400000000000006</v>
+      </c>
+      <c r="N271" s="4">
+        <v>72.5</v>
+      </c>
+      <c r="O271" s="4">
+        <v>73.2</v>
+      </c>
+      <c r="P271" s="4">
+        <v>73.900000000000006</v>
+      </c>
+      <c r="Q271" s="4">
+        <v>73.3</v>
+      </c>
+      <c r="R271" s="4">
+        <v>72.8</v>
+      </c>
+      <c r="S271" s="4">
+        <v>76.3</v>
+      </c>
+      <c r="T271" s="4">
+        <v>78.099999999999994</v>
+      </c>
+      <c r="U271" s="4">
+        <v>78.599999999999994</v>
+      </c>
+      <c r="V271" s="3"/>
       <c r="W271" s="2" t="s">
-        <v>376</v>
+        <v>30</v>
       </c>
     </row>
     <row r="272" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D272" s="2" t="s">
         <v>27</v>
@@ -18360,53 +18614,67 @@
         <v>28</v>
       </c>
       <c r="F272" s="3" t="s">
-        <v>36</v>
+        <v>377</v>
       </c>
       <c r="G272" s="6">
-        <v>55</v>
-      </c>
-      <c r="H272" s="3"/>
+        <v>70108</v>
+      </c>
+      <c r="H272" s="6">
+        <v>248240</v>
+      </c>
       <c r="I272" s="6">
-        <v>58</v>
-      </c>
-      <c r="J272" s="3"/>
+        <v>168221</v>
+      </c>
+      <c r="J272" s="6">
+        <v>72837</v>
+      </c>
       <c r="K272" s="6">
-        <v>60</v>
-      </c>
-      <c r="L272" s="3"/>
+        <v>64283</v>
+      </c>
+      <c r="L272" s="6">
+        <v>68694</v>
+      </c>
       <c r="M272" s="6">
-        <v>64</v>
-      </c>
-      <c r="N272" s="3"/>
+        <v>60135</v>
+      </c>
+      <c r="N272" s="6">
+        <v>46337</v>
+      </c>
       <c r="O272" s="6">
-        <v>65</v>
-      </c>
-      <c r="P272" s="3"/>
+        <v>50289</v>
+      </c>
+      <c r="P272" s="6">
+        <v>104107</v>
+      </c>
       <c r="Q272" s="6">
-        <v>74</v>
-      </c>
-      <c r="R272" s="3"/>
+        <v>201963</v>
+      </c>
+      <c r="R272" s="6">
+        <v>84506</v>
+      </c>
       <c r="S272" s="6">
-        <v>63</v>
-      </c>
-      <c r="T272" s="3"/>
+        <v>295948</v>
+      </c>
+      <c r="T272" s="6">
+        <v>123796</v>
+      </c>
       <c r="U272" s="6">
-        <v>71</v>
+        <v>104040</v>
       </c>
       <c r="V272" s="3"/>
       <c r="W272" s="2" t="s">
-        <v>376</v>
+        <v>30</v>
       </c>
     </row>
     <row r="273" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="B273" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="C273" s="2" t="s">
         <v>378</v>
-      </c>
-      <c r="C273" s="2" t="s">
-        <v>379</v>
       </c>
       <c r="D273" s="2" t="s">
         <v>27</v>
@@ -18415,61 +18683,61 @@
         <v>28</v>
       </c>
       <c r="F273" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="G273" s="5">
-        <v>1.02</v>
-      </c>
-      <c r="H273" s="5">
-        <v>0.96</v>
-      </c>
-      <c r="I273" s="5">
-        <v>1</v>
-      </c>
-      <c r="J273" s="5">
-        <v>1.05</v>
-      </c>
-      <c r="K273" s="5">
-        <v>1.06</v>
-      </c>
-      <c r="L273" s="5">
-        <v>0.95</v>
-      </c>
-      <c r="M273" s="5">
-        <v>0.91</v>
-      </c>
-      <c r="N273" s="5">
-        <v>0.81</v>
-      </c>
-      <c r="O273" s="5">
-        <v>0.87</v>
-      </c>
-      <c r="P273" s="5">
-        <v>1.01</v>
-      </c>
-      <c r="Q273" s="5">
-        <v>0.85</v>
-      </c>
-      <c r="R273" s="5">
-        <v>0.83</v>
-      </c>
-      <c r="S273" s="5">
-        <v>0.72</v>
-      </c>
-      <c r="T273" s="5">
-        <v>0.78</v>
-      </c>
-      <c r="U273" s="5">
-        <v>0.69</v>
+        <v>36</v>
+      </c>
+      <c r="G273" s="4">
+        <v>2.9</v>
+      </c>
+      <c r="H273" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="I273" s="4">
+        <v>6</v>
+      </c>
+      <c r="J273" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="K273" s="4">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="L273" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="M273" s="4">
+        <v>3.1</v>
+      </c>
+      <c r="N273" s="4">
+        <v>3</v>
+      </c>
+      <c r="O273" s="4">
+        <v>3.2</v>
+      </c>
+      <c r="P273" s="4">
+        <v>3.4</v>
+      </c>
+      <c r="Q273" s="4">
+        <v>3.2</v>
+      </c>
+      <c r="R273" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="S273" s="4">
+        <v>6.6</v>
+      </c>
+      <c r="T273" s="4">
+        <v>5.8</v>
+      </c>
+      <c r="U273" s="4">
+        <v>4.5</v>
       </c>
       <c r="V273" s="3"/>
       <c r="W273" s="2" t="s">
-        <v>202</v>
+        <v>30</v>
       </c>
     </row>
     <row r="274" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B274" s="2" t="s">
         <v>380</v>
@@ -18486,68 +18754,70 @@
       <c r="F274" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G274" s="5">
-        <v>1.84</v>
-      </c>
-      <c r="H274" s="5">
-        <v>1.79</v>
-      </c>
-      <c r="I274" s="5">
-        <v>1.8</v>
-      </c>
-      <c r="J274" s="5">
-        <v>1.79</v>
-      </c>
-      <c r="K274" s="5">
-        <v>1.86</v>
-      </c>
-      <c r="L274" s="5">
-        <v>2.21</v>
-      </c>
-      <c r="M274" s="5">
-        <v>1.99</v>
-      </c>
-      <c r="N274" s="5">
-        <v>1.88</v>
-      </c>
-      <c r="O274" s="5">
-        <v>2</v>
-      </c>
-      <c r="P274" s="5">
-        <v>1.96</v>
-      </c>
-      <c r="Q274" s="5">
-        <v>2.21</v>
-      </c>
-      <c r="R274" s="5">
-        <v>2.19</v>
-      </c>
-      <c r="S274" s="5">
-        <v>2.21</v>
-      </c>
-      <c r="T274" s="5">
-        <v>3.27</v>
-      </c>
-      <c r="U274" s="5">
-        <v>4.07</v>
-      </c>
-      <c r="V274" s="3"/>
+      <c r="G274" s="6">
+        <v>70</v>
+      </c>
+      <c r="H274" s="6">
+        <v>75</v>
+      </c>
+      <c r="I274" s="6">
+        <v>66</v>
+      </c>
+      <c r="J274" s="6">
+        <v>64</v>
+      </c>
+      <c r="K274" s="6">
+        <v>70</v>
+      </c>
+      <c r="L274" s="6">
+        <v>66</v>
+      </c>
+      <c r="M274" s="6">
+        <v>80</v>
+      </c>
+      <c r="N274" s="6">
+        <v>89</v>
+      </c>
+      <c r="O274" s="6">
+        <v>86</v>
+      </c>
+      <c r="P274" s="6">
+        <v>89</v>
+      </c>
+      <c r="Q274" s="6">
+        <v>85</v>
+      </c>
+      <c r="R274" s="6">
+        <v>82</v>
+      </c>
+      <c r="S274" s="6">
+        <v>83</v>
+      </c>
+      <c r="T274" s="6">
+        <v>88</v>
+      </c>
+      <c r="U274" s="6">
+        <v>88</v>
+      </c>
+      <c r="V274" s="6">
+        <v>86</v>
+      </c>
       <c r="W274" s="2" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="275" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B275" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="C275" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="C275" s="2" t="s">
-        <v>384</v>
-      </c>
       <c r="D275" s="2" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="E275" s="3" t="s">
         <v>28</v>
@@ -18556,229 +18826,233 @@
         <v>36</v>
       </c>
       <c r="G275" s="6">
-        <v>10</v>
-      </c>
-      <c r="H275" s="6">
-        <v>9</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="H275" s="3"/>
       <c r="I275" s="6">
-        <v>11</v>
-      </c>
-      <c r="J275" s="6">
-        <v>11</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="J275" s="3"/>
       <c r="K275" s="6">
-        <v>15</v>
-      </c>
-      <c r="L275" s="6">
-        <v>16</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="L275" s="3"/>
       <c r="M275" s="6">
-        <v>19</v>
-      </c>
-      <c r="N275" s="6">
-        <v>21</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="N275" s="3"/>
       <c r="O275" s="6">
-        <v>25</v>
-      </c>
-      <c r="P275" s="6">
-        <v>31</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="P275" s="3"/>
       <c r="Q275" s="6">
-        <v>34</v>
-      </c>
-      <c r="R275" s="6">
-        <v>40</v>
-      </c>
-      <c r="S275" s="3"/>
+        <v>74</v>
+      </c>
+      <c r="R275" s="3"/>
+      <c r="S275" s="6">
+        <v>63</v>
+      </c>
       <c r="T275" s="3"/>
-      <c r="U275" s="3"/>
+      <c r="U275" s="6">
+        <v>71</v>
+      </c>
       <c r="V275" s="3"/>
       <c r="W275" s="2" t="s">
-        <v>30</v>
+        <v>382</v>
       </c>
     </row>
     <row r="276" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="E276" s="3" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="F276" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G276" s="6">
-        <v>10</v>
-      </c>
-      <c r="H276" s="6">
-        <v>9</v>
-      </c>
-      <c r="I276" s="6">
-        <v>11</v>
-      </c>
-      <c r="J276" s="6">
-        <v>12</v>
-      </c>
-      <c r="K276" s="6">
-        <v>14</v>
-      </c>
-      <c r="L276" s="6">
-        <v>15</v>
-      </c>
-      <c r="M276" s="6">
-        <v>19</v>
-      </c>
-      <c r="N276" s="6">
-        <v>21</v>
-      </c>
-      <c r="O276" s="6">
-        <v>24</v>
-      </c>
-      <c r="P276" s="6">
-        <v>31</v>
-      </c>
-      <c r="Q276" s="6">
-        <v>32</v>
-      </c>
-      <c r="R276" s="6">
-        <v>39</v>
-      </c>
-      <c r="S276" s="3"/>
-      <c r="T276" s="3"/>
-      <c r="U276" s="3"/>
+        <v>250</v>
+      </c>
+      <c r="G276" s="5">
+        <v>1.02</v>
+      </c>
+      <c r="H276" s="5">
+        <v>0.96</v>
+      </c>
+      <c r="I276" s="5">
+        <v>1</v>
+      </c>
+      <c r="J276" s="5">
+        <v>1.05</v>
+      </c>
+      <c r="K276" s="5">
+        <v>1.06</v>
+      </c>
+      <c r="L276" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="M276" s="5">
+        <v>0.91</v>
+      </c>
+      <c r="N276" s="5">
+        <v>0.81</v>
+      </c>
+      <c r="O276" s="5">
+        <v>0.87</v>
+      </c>
+      <c r="P276" s="5">
+        <v>1.01</v>
+      </c>
+      <c r="Q276" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="R276" s="5">
+        <v>0.83</v>
+      </c>
+      <c r="S276" s="5">
+        <v>0.72</v>
+      </c>
+      <c r="T276" s="5">
+        <v>0.78</v>
+      </c>
+      <c r="U276" s="5">
+        <v>0.69</v>
+      </c>
       <c r="V276" s="3"/>
       <c r="W276" s="2" t="s">
-        <v>30</v>
+        <v>202</v>
       </c>
     </row>
     <row r="277" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="E277" s="3" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="F277" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G277" s="6">
-        <v>10</v>
-      </c>
-      <c r="H277" s="6">
-        <v>9</v>
-      </c>
-      <c r="I277" s="6">
-        <v>10</v>
-      </c>
-      <c r="J277" s="6">
-        <v>11</v>
-      </c>
-      <c r="K277" s="6">
-        <v>15</v>
-      </c>
-      <c r="L277" s="6">
-        <v>16</v>
-      </c>
-      <c r="M277" s="6">
-        <v>19</v>
-      </c>
-      <c r="N277" s="6">
-        <v>21</v>
-      </c>
-      <c r="O277" s="6">
-        <v>26</v>
-      </c>
-      <c r="P277" s="6">
-        <v>32</v>
-      </c>
-      <c r="Q277" s="6">
-        <v>35</v>
-      </c>
-      <c r="R277" s="6">
-        <v>41</v>
-      </c>
-      <c r="S277" s="3"/>
-      <c r="T277" s="3"/>
-      <c r="U277" s="3"/>
+      <c r="G277" s="5">
+        <v>1.84</v>
+      </c>
+      <c r="H277" s="5">
+        <v>1.79</v>
+      </c>
+      <c r="I277" s="5">
+        <v>1.8</v>
+      </c>
+      <c r="J277" s="5">
+        <v>1.79</v>
+      </c>
+      <c r="K277" s="5">
+        <v>1.86</v>
+      </c>
+      <c r="L277" s="5">
+        <v>2.21</v>
+      </c>
+      <c r="M277" s="5">
+        <v>1.99</v>
+      </c>
+      <c r="N277" s="5">
+        <v>1.88</v>
+      </c>
+      <c r="O277" s="5">
+        <v>2</v>
+      </c>
+      <c r="P277" s="5">
+        <v>1.96</v>
+      </c>
+      <c r="Q277" s="5">
+        <v>2.21</v>
+      </c>
+      <c r="R277" s="5">
+        <v>2.19</v>
+      </c>
+      <c r="S277" s="5">
+        <v>2.21</v>
+      </c>
+      <c r="T277" s="5">
+        <v>3.27</v>
+      </c>
+      <c r="U277" s="5">
+        <v>4.07</v>
+      </c>
       <c r="V277" s="3"/>
       <c r="W277" s="2" t="s">
-        <v>30</v>
+        <v>388</v>
       </c>
     </row>
     <row r="278" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="E278" s="3" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F278" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G278" s="6">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H278" s="6">
+        <v>9</v>
+      </c>
+      <c r="I278" s="6">
         <v>11</v>
       </c>
-      <c r="I278" s="6">
-        <v>13</v>
-      </c>
       <c r="J278" s="6">
+        <v>11</v>
+      </c>
+      <c r="K278" s="6">
         <v>15</v>
       </c>
-      <c r="K278" s="6">
-        <v>18</v>
-      </c>
       <c r="L278" s="6">
+        <v>16</v>
+      </c>
+      <c r="M278" s="6">
         <v>19</v>
       </c>
-      <c r="M278" s="6">
-        <v>23</v>
-      </c>
       <c r="N278" s="6">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O278" s="6">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P278" s="6">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="Q278" s="6">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R278" s="6">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="S278" s="3"/>
       <c r="T278" s="3"/>
@@ -18790,58 +19064,58 @@
     </row>
     <row r="279" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="E279" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F279" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G279" s="6">
+        <v>10</v>
+      </c>
+      <c r="H279" s="6">
+        <v>9</v>
+      </c>
+      <c r="I279" s="6">
+        <v>11</v>
+      </c>
+      <c r="J279" s="6">
+        <v>12</v>
+      </c>
+      <c r="K279" s="6">
+        <v>14</v>
+      </c>
+      <c r="L279" s="6">
+        <v>15</v>
+      </c>
+      <c r="M279" s="6">
+        <v>19</v>
+      </c>
+      <c r="N279" s="6">
+        <v>21</v>
+      </c>
+      <c r="O279" s="6">
+        <v>24</v>
+      </c>
+      <c r="P279" s="6">
+        <v>31</v>
+      </c>
+      <c r="Q279" s="6">
+        <v>32</v>
+      </c>
+      <c r="R279" s="6">
         <v>39</v>
-      </c>
-      <c r="F279" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G279" s="6">
-        <v>6</v>
-      </c>
-      <c r="H279" s="6">
-        <v>5</v>
-      </c>
-      <c r="I279" s="6">
-        <v>6</v>
-      </c>
-      <c r="J279" s="6">
-        <v>6</v>
-      </c>
-      <c r="K279" s="6">
-        <v>9</v>
-      </c>
-      <c r="L279" s="6">
-        <v>10</v>
-      </c>
-      <c r="M279" s="6">
-        <v>12</v>
-      </c>
-      <c r="N279" s="6">
-        <v>13</v>
-      </c>
-      <c r="O279" s="6">
-        <v>17</v>
-      </c>
-      <c r="P279" s="6">
-        <v>23</v>
-      </c>
-      <c r="Q279" s="6">
-        <v>25</v>
-      </c>
-      <c r="R279" s="6">
-        <v>31</v>
       </c>
       <c r="S279" s="3"/>
       <c r="T279" s="3"/>
@@ -18853,19 +19127,19 @@
     </row>
     <row r="280" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="E280" s="3" t="s">
-        <v>139</v>
+        <v>64</v>
       </c>
       <c r="F280" s="3" t="s">
         <v>36</v>
@@ -18874,37 +19148,37 @@
         <v>10</v>
       </c>
       <c r="H280" s="6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I280" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J280" s="6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K280" s="6">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L280" s="6">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="M280" s="6">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="N280" s="6">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="O280" s="6">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="P280" s="6">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="Q280" s="6">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="R280" s="6">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="S280" s="3"/>
       <c r="T280" s="3"/>
@@ -18916,58 +19190,58 @@
     </row>
     <row r="281" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="E281" s="3" t="s">
-        <v>122</v>
+        <v>38</v>
       </c>
       <c r="F281" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G281" s="6">
+        <v>12</v>
+      </c>
+      <c r="H281" s="6">
+        <v>11</v>
+      </c>
+      <c r="I281" s="6">
+        <v>13</v>
+      </c>
+      <c r="J281" s="6">
+        <v>15</v>
+      </c>
+      <c r="K281" s="6">
         <v>18</v>
       </c>
-      <c r="H281" s="6">
-        <v>16</v>
-      </c>
-      <c r="I281" s="6">
+      <c r="L281" s="6">
         <v>19</v>
       </c>
-      <c r="J281" s="6">
-        <v>20</v>
-      </c>
-      <c r="K281" s="6">
-        <v>28</v>
-      </c>
-      <c r="L281" s="6">
-        <v>28</v>
-      </c>
       <c r="M281" s="6">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N281" s="6">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="O281" s="6">
+        <v>30</v>
+      </c>
+      <c r="P281" s="6">
+        <v>37</v>
+      </c>
+      <c r="Q281" s="6">
         <v>39</v>
       </c>
-      <c r="P281" s="6">
-        <v>47</v>
-      </c>
-      <c r="Q281" s="6">
-        <v>53</v>
-      </c>
       <c r="R281" s="6">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="S281" s="3"/>
       <c r="T281" s="3"/>
@@ -18979,58 +19253,58 @@
     </row>
     <row r="282" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="E282" s="3" t="s">
-        <v>125</v>
+        <v>39</v>
       </c>
       <c r="F282" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G282" s="6">
+        <v>6</v>
+      </c>
+      <c r="H282" s="6">
+        <v>5</v>
+      </c>
+      <c r="I282" s="6">
+        <v>6</v>
+      </c>
+      <c r="J282" s="6">
+        <v>6</v>
+      </c>
+      <c r="K282" s="6">
+        <v>9</v>
+      </c>
+      <c r="L282" s="6">
+        <v>10</v>
+      </c>
+      <c r="M282" s="6">
+        <v>12</v>
+      </c>
+      <c r="N282" s="6">
         <v>13</v>
       </c>
-      <c r="H282" s="6">
-        <v>13</v>
-      </c>
-      <c r="I282" s="6">
-        <v>16</v>
-      </c>
-      <c r="J282" s="6">
-        <v>19</v>
-      </c>
-      <c r="K282" s="6">
-        <v>24</v>
-      </c>
-      <c r="L282" s="6">
+      <c r="O282" s="6">
+        <v>17</v>
+      </c>
+      <c r="P282" s="6">
+        <v>23</v>
+      </c>
+      <c r="Q282" s="6">
         <v>25</v>
       </c>
-      <c r="M282" s="6">
-        <v>27</v>
-      </c>
-      <c r="N282" s="6">
-        <v>33</v>
-      </c>
-      <c r="O282" s="6">
-        <v>36</v>
-      </c>
-      <c r="P282" s="6">
-        <v>46</v>
-      </c>
-      <c r="Q282" s="6">
-        <v>48</v>
-      </c>
       <c r="R282" s="6">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="S282" s="3"/>
       <c r="T282" s="3"/>
@@ -19042,58 +19316,58 @@
     </row>
     <row r="283" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="D283" s="2" t="s">
         <v>80</v>
       </c>
       <c r="E283" s="3" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="F283" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G283" s="6">
+        <v>10</v>
+      </c>
+      <c r="H283" s="6">
+        <v>6</v>
+      </c>
+      <c r="I283" s="6">
+        <v>8</v>
+      </c>
+      <c r="J283" s="6">
         <v>9</v>
       </c>
-      <c r="H283" s="6">
+      <c r="K283" s="6">
         <v>9</v>
       </c>
-      <c r="I283" s="6">
+      <c r="L283" s="6">
+        <v>8</v>
+      </c>
+      <c r="M283" s="6">
+        <v>9</v>
+      </c>
+      <c r="N283" s="6">
         <v>11</v>
       </c>
-      <c r="J283" s="6">
-        <v>12</v>
-      </c>
-      <c r="K283" s="6">
-        <v>15</v>
-      </c>
-      <c r="L283" s="6">
-        <v>15</v>
-      </c>
-      <c r="M283" s="6">
-        <v>18</v>
-      </c>
-      <c r="N283" s="6">
-        <v>19</v>
-      </c>
       <c r="O283" s="6">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="P283" s="6">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="Q283" s="6">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="R283" s="6">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="S283" s="3"/>
       <c r="T283" s="3"/>
@@ -19105,58 +19379,58 @@
     </row>
     <row r="284" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="D284" s="2" t="s">
         <v>80</v>
       </c>
       <c r="E284" s="3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="F284" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G284" s="6">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="H284" s="6">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I284" s="6">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="J284" s="6">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="K284" s="6">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="L284" s="6">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="M284" s="6">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="N284" s="6">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="O284" s="6">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="P284" s="6">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="Q284" s="6">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="R284" s="6">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="S284" s="3"/>
       <c r="T284" s="3"/>
@@ -19168,58 +19442,58 @@
     </row>
     <row r="285" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="D285" s="2" t="s">
         <v>80</v>
       </c>
       <c r="E285" s="3" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="F285" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G285" s="6">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H285" s="6">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I285" s="6">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J285" s="6">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="K285" s="6">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="L285" s="6">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="M285" s="6">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="N285" s="6">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="O285" s="6">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="P285" s="6">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="Q285" s="6">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="R285" s="6">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="S285" s="3"/>
       <c r="T285" s="3"/>
@@ -19231,58 +19505,58 @@
     </row>
     <row r="286" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>141</v>
+        <v>80</v>
       </c>
       <c r="E286" s="3" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="F286" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G286" s="6">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="H286" s="6">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="I286" s="6">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="J286" s="6">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="K286" s="6">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="L286" s="6">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="M286" s="6">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="N286" s="6">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="O286" s="6">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="P286" s="6">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="Q286" s="6">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="R286" s="6">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="S286" s="3"/>
       <c r="T286" s="3"/>
@@ -19294,37 +19568,37 @@
     </row>
     <row r="287" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>141</v>
+        <v>80</v>
       </c>
       <c r="E287" s="3" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="F287" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G287" s="6">
+        <v>4</v>
+      </c>
+      <c r="H287" s="6">
+        <v>5</v>
+      </c>
+      <c r="I287" s="6">
+        <v>6</v>
+      </c>
+      <c r="J287" s="6">
+        <v>6</v>
+      </c>
+      <c r="K287" s="6">
         <v>7</v>
-      </c>
-      <c r="H287" s="6">
-        <v>6</v>
-      </c>
-      <c r="I287" s="6">
-        <v>8</v>
-      </c>
-      <c r="J287" s="6">
-        <v>8</v>
-      </c>
-      <c r="K287" s="6">
-        <v>10</v>
       </c>
       <c r="L287" s="6">
         <v>10</v>
@@ -19333,16 +19607,16 @@
         <v>12</v>
       </c>
       <c r="N287" s="6">
+        <v>12</v>
+      </c>
+      <c r="O287" s="6">
         <v>14</v>
       </c>
-      <c r="O287" s="6">
-        <v>17</v>
-      </c>
       <c r="P287" s="6">
+        <v>21</v>
+      </c>
+      <c r="Q287" s="6">
         <v>23</v>
-      </c>
-      <c r="Q287" s="6">
-        <v>25</v>
       </c>
       <c r="R287" s="6">
         <v>29</v>
@@ -19357,19 +19631,19 @@
     </row>
     <row r="288" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>141</v>
+        <v>80</v>
       </c>
       <c r="E288" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F288" s="3" t="s">
         <v>36</v>
@@ -19378,37 +19652,37 @@
         <v>2</v>
       </c>
       <c r="H288" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I288" s="6">
         <v>2</v>
       </c>
       <c r="J288" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K288" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L288" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M288" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N288" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O288" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P288" s="6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q288" s="6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="R288" s="6">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="S288" s="3"/>
       <c r="T288" s="3"/>
@@ -19420,58 +19694,58 @@
     </row>
     <row r="289" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E289" s="3" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="F289" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G289" s="6">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="H289" s="6">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="I289" s="6">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="J289" s="6">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="K289" s="6">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="L289" s="6">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="M289" s="6">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="N289" s="6">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="O289" s="6">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="P289" s="6">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="Q289" s="6">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="R289" s="6">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="S289" s="3"/>
       <c r="T289" s="3"/>
@@ -19483,58 +19757,58 @@
     </row>
     <row r="290" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E290" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="F290" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G290" s="6">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="H290" s="6">
+        <v>6</v>
+      </c>
+      <c r="I290" s="6">
+        <v>8</v>
+      </c>
+      <c r="J290" s="6">
+        <v>8</v>
+      </c>
+      <c r="K290" s="6">
+        <v>10</v>
+      </c>
+      <c r="L290" s="6">
+        <v>10</v>
+      </c>
+      <c r="M290" s="6">
+        <v>12</v>
+      </c>
+      <c r="N290" s="6">
         <v>14</v>
       </c>
-      <c r="I290" s="6">
-        <v>16</v>
-      </c>
-      <c r="J290" s="6">
-        <v>18</v>
-      </c>
-      <c r="K290" s="6">
+      <c r="O290" s="6">
+        <v>17</v>
+      </c>
+      <c r="P290" s="6">
         <v>23</v>
       </c>
-      <c r="L290" s="6">
+      <c r="Q290" s="6">
         <v>25</v>
       </c>
-      <c r="M290" s="6">
-        <v>27</v>
-      </c>
-      <c r="N290" s="6">
-        <v>30</v>
-      </c>
-      <c r="O290" s="6">
-        <v>35</v>
-      </c>
-      <c r="P290" s="6">
-        <v>44</v>
-      </c>
-      <c r="Q290" s="6">
-        <v>46</v>
-      </c>
       <c r="R290" s="6">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="S290" s="3"/>
       <c r="T290" s="3"/>
@@ -19546,58 +19820,58 @@
     </row>
     <row r="291" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E291" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F291" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G291" s="6">
+        <v>2</v>
+      </c>
+      <c r="H291" s="6">
+        <v>1</v>
+      </c>
+      <c r="I291" s="6">
+        <v>2</v>
+      </c>
+      <c r="J291" s="6">
+        <v>1</v>
+      </c>
+      <c r="K291" s="6">
+        <v>1</v>
+      </c>
+      <c r="L291" s="6">
+        <v>2</v>
+      </c>
+      <c r="M291" s="6">
+        <v>2</v>
+      </c>
+      <c r="N291" s="6">
+        <v>2</v>
+      </c>
+      <c r="O291" s="6">
+        <v>4</v>
+      </c>
+      <c r="P291" s="6">
+        <v>5</v>
+      </c>
+      <c r="Q291" s="6">
+        <v>5</v>
+      </c>
+      <c r="R291" s="6">
         <v>8</v>
-      </c>
-      <c r="H291" s="6">
-        <v>5</v>
-      </c>
-      <c r="I291" s="6">
-        <v>6</v>
-      </c>
-      <c r="J291" s="6">
-        <v>7</v>
-      </c>
-      <c r="K291" s="6">
-        <v>7</v>
-      </c>
-      <c r="L291" s="6">
-        <v>7</v>
-      </c>
-      <c r="M291" s="6">
-        <v>7</v>
-      </c>
-      <c r="N291" s="6">
-        <v>11</v>
-      </c>
-      <c r="O291" s="6">
-        <v>10</v>
-      </c>
-      <c r="P291" s="6">
-        <v>17</v>
-      </c>
-      <c r="Q291" s="6">
-        <v>25</v>
-      </c>
-      <c r="R291" s="6">
-        <v>22</v>
       </c>
       <c r="S291" s="3"/>
       <c r="T291" s="3"/>
@@ -19609,58 +19883,58 @@
     </row>
     <row r="292" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="D292" s="2" t="s">
         <v>144</v>
       </c>
       <c r="E292" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F292" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G292" s="6">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H292" s="6">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I292" s="6">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J292" s="6">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="K292" s="6">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="L292" s="6">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="M292" s="6">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="N292" s="6">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="O292" s="6">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="P292" s="6">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="Q292" s="6">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="R292" s="6">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="S292" s="3"/>
       <c r="T292" s="3"/>
@@ -19672,222 +19946,202 @@
     </row>
     <row r="293" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="D293" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E293" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="F293" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G293" s="6">
+        <v>15</v>
+      </c>
+      <c r="H293" s="6">
+        <v>14</v>
+      </c>
+      <c r="I293" s="6">
+        <v>16</v>
+      </c>
+      <c r="J293" s="6">
+        <v>18</v>
+      </c>
+      <c r="K293" s="6">
+        <v>23</v>
+      </c>
+      <c r="L293" s="6">
+        <v>25</v>
+      </c>
+      <c r="M293" s="6">
         <v>27</v>
       </c>
-      <c r="E293" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F293" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G293" s="4">
-        <v>5.7</v>
-      </c>
-      <c r="H293" s="4">
+      <c r="N293" s="6">
+        <v>30</v>
+      </c>
+      <c r="O293" s="6">
+        <v>35</v>
+      </c>
+      <c r="P293" s="6">
+        <v>44</v>
+      </c>
+      <c r="Q293" s="6">
+        <v>46</v>
+      </c>
+      <c r="R293" s="6">
+        <v>54</v>
+      </c>
+      <c r="S293" s="3"/>
+      <c r="T293" s="3"/>
+      <c r="U293" s="3"/>
+      <c r="V293" s="3"/>
+      <c r="W293" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="294" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+      <c r="A294" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B294" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C294" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="D294" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E294" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F294" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G294" s="6">
+        <v>8</v>
+      </c>
+      <c r="H294" s="6">
+        <v>5</v>
+      </c>
+      <c r="I294" s="6">
         <v>6</v>
       </c>
-      <c r="I293" s="4">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="J293" s="4">
-        <v>4.3</v>
-      </c>
-      <c r="K293" s="4">
-        <v>4.7</v>
-      </c>
-      <c r="L293" s="4">
-        <v>4.5</v>
-      </c>
-      <c r="M293" s="4">
-        <v>3.3</v>
-      </c>
-      <c r="N293" s="4">
-        <v>3.8</v>
-      </c>
-      <c r="O293" s="4">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="P293" s="4">
-        <v>4.3</v>
-      </c>
-      <c r="Q293" s="4">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="R293" s="4">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="S293" s="4">
-        <v>3.8</v>
-      </c>
-      <c r="T293" s="4">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="U293" s="4">
-        <v>4.8</v>
-      </c>
-      <c r="V293" s="4">
-        <v>5.2</v>
-      </c>
-      <c r="W293" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="294" spans="1:23" ht="36" x14ac:dyDescent="0.25">
-      <c r="A294" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="B294" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C294" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="D294" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E294" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F294" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="G294" s="5">
-        <v>377.75</v>
-      </c>
-      <c r="H294" s="5">
-        <v>417.47</v>
-      </c>
-      <c r="I294" s="5">
-        <v>421.06</v>
-      </c>
-      <c r="J294" s="5">
-        <v>487.12</v>
-      </c>
-      <c r="K294" s="5">
-        <v>451.84</v>
-      </c>
-      <c r="L294" s="5">
-        <v>440.89</v>
-      </c>
-      <c r="M294" s="5">
-        <v>662.95</v>
-      </c>
-      <c r="N294" s="5">
-        <v>679.46</v>
-      </c>
-      <c r="O294" s="5">
-        <v>766.04</v>
-      </c>
-      <c r="P294" s="5">
-        <v>776.56</v>
-      </c>
-      <c r="Q294" s="5">
-        <v>829.27</v>
-      </c>
-      <c r="R294" s="5">
-        <v>983.51</v>
-      </c>
-      <c r="S294" s="5">
-        <v>3494.39</v>
-      </c>
-      <c r="T294" s="5">
-        <v>2580.38</v>
-      </c>
-      <c r="U294" s="5">
-        <v>1840.15</v>
-      </c>
+      <c r="J294" s="6">
+        <v>7</v>
+      </c>
+      <c r="K294" s="6">
+        <v>7</v>
+      </c>
+      <c r="L294" s="6">
+        <v>7</v>
+      </c>
+      <c r="M294" s="6">
+        <v>7</v>
+      </c>
+      <c r="N294" s="6">
+        <v>11</v>
+      </c>
+      <c r="O294" s="6">
+        <v>10</v>
+      </c>
+      <c r="P294" s="6">
+        <v>17</v>
+      </c>
+      <c r="Q294" s="6">
+        <v>25</v>
+      </c>
+      <c r="R294" s="6">
+        <v>22</v>
+      </c>
+      <c r="S294" s="3"/>
+      <c r="T294" s="3"/>
+      <c r="U294" s="3"/>
       <c r="V294" s="3"/>
       <c r="W294" s="2" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="295" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="295" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>27</v>
+        <v>144</v>
       </c>
       <c r="E295" s="3" t="s">
-        <v>28</v>
+        <v>148</v>
       </c>
       <c r="F295" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="G295" s="5">
-        <v>96.04</v>
-      </c>
-      <c r="H295" s="5">
-        <v>90.68</v>
-      </c>
-      <c r="I295" s="5">
-        <v>111.55</v>
-      </c>
-      <c r="J295" s="5">
-        <v>127.11</v>
-      </c>
-      <c r="K295" s="5">
-        <v>82.28</v>
-      </c>
-      <c r="L295" s="5">
-        <v>100.19</v>
-      </c>
-      <c r="M295" s="5">
-        <v>148.99</v>
-      </c>
-      <c r="N295" s="5">
-        <v>222.11</v>
-      </c>
-      <c r="O295" s="5">
-        <v>244.93</v>
-      </c>
-      <c r="P295" s="5">
-        <v>223.31</v>
-      </c>
-      <c r="Q295" s="5">
-        <v>225.08</v>
-      </c>
-      <c r="R295" s="5">
-        <v>296.20999999999998</v>
-      </c>
-      <c r="S295" s="5">
-        <v>2661.32</v>
-      </c>
-      <c r="T295" s="5">
-        <v>1701.94</v>
-      </c>
-      <c r="U295" s="5">
-        <v>705.25</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G295" s="6">
+        <v>4</v>
+      </c>
+      <c r="H295" s="6">
+        <v>3</v>
+      </c>
+      <c r="I295" s="6">
+        <v>5</v>
+      </c>
+      <c r="J295" s="6">
+        <v>4</v>
+      </c>
+      <c r="K295" s="6">
+        <v>5</v>
+      </c>
+      <c r="L295" s="6">
+        <v>5</v>
+      </c>
+      <c r="M295" s="6">
+        <v>7</v>
+      </c>
+      <c r="N295" s="6">
+        <v>8</v>
+      </c>
+      <c r="O295" s="6">
+        <v>9</v>
+      </c>
+      <c r="P295" s="6">
+        <v>12</v>
+      </c>
+      <c r="Q295" s="6">
+        <v>14</v>
+      </c>
+      <c r="R295" s="6">
+        <v>17</v>
+      </c>
+      <c r="S295" s="3"/>
+      <c r="T295" s="3"/>
+      <c r="U295" s="3"/>
       <c r="V295" s="3"/>
       <c r="W295" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="296" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+      <c r="A296" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B296" s="2" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="296" spans="1:23" ht="72" x14ac:dyDescent="0.25">
-      <c r="A296" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="B296" s="2" t="s">
-        <v>394</v>
-      </c>
       <c r="C296" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D296" s="2" t="s">
         <v>27</v>
@@ -19898,65 +20152,67 @@
       <c r="F296" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G296" s="5">
-        <v>0.08</v>
-      </c>
-      <c r="H296" s="5">
-        <v>0.08</v>
-      </c>
-      <c r="I296" s="5">
-        <v>0.09</v>
-      </c>
-      <c r="J296" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="K296" s="5">
-        <v>0.09</v>
-      </c>
-      <c r="L296" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="M296" s="5">
-        <v>0.15</v>
-      </c>
-      <c r="N296" s="5">
-        <v>0.13</v>
-      </c>
-      <c r="O296" s="5">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="P296" s="5">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="Q296" s="5">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="R296" s="5">
-        <v>0.15</v>
-      </c>
-      <c r="S296" s="5">
-        <v>0.53</v>
-      </c>
-      <c r="T296" s="5">
-        <v>0.33</v>
-      </c>
-      <c r="U296" s="5">
-        <v>0.21</v>
-      </c>
-      <c r="V296" s="3"/>
+      <c r="G296" s="4">
+        <v>5.7</v>
+      </c>
+      <c r="H296" s="4">
+        <v>6</v>
+      </c>
+      <c r="I296" s="4">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="J296" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="K296" s="4">
+        <v>4.7</v>
+      </c>
+      <c r="L296" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="M296" s="4">
+        <v>3.3</v>
+      </c>
+      <c r="N296" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="O296" s="4">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="P296" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="Q296" s="4">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="R296" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="S296" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="T296" s="4">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="U296" s="4">
+        <v>4.8</v>
+      </c>
+      <c r="V296" s="4">
+        <v>5.2</v>
+      </c>
       <c r="W296" s="2" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="297" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="297" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D297" s="2" t="s">
         <v>27</v>
@@ -19965,60 +20221,64 @@
         <v>28</v>
       </c>
       <c r="F297" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="G297" s="3"/>
-      <c r="H297" s="3"/>
-      <c r="I297" s="3"/>
-      <c r="J297" s="7">
-        <v>2.2850000000000001</v>
-      </c>
-      <c r="K297" s="7">
-        <v>1.1160000000000001</v>
-      </c>
-      <c r="L297" s="7">
-        <v>1.55</v>
-      </c>
-      <c r="M297" s="7">
-        <v>3.7469999999999999</v>
-      </c>
-      <c r="N297" s="7">
-        <v>3.8530000000000002</v>
-      </c>
-      <c r="O297" s="7">
-        <v>3.367</v>
-      </c>
-      <c r="P297" s="7">
-        <v>6.8940000000000001</v>
-      </c>
-      <c r="Q297" s="7">
-        <v>4.077</v>
-      </c>
-      <c r="R297" s="7">
-        <v>4.49</v>
-      </c>
-      <c r="S297" s="7">
-        <v>11.999000000000001</v>
-      </c>
-      <c r="T297" s="7">
-        <v>16.606000000000002</v>
-      </c>
-      <c r="U297" s="7">
-        <v>20.382000000000001</v>
-      </c>
-      <c r="V297" s="7">
-        <v>5.3920000000000003</v>
-      </c>
+        <v>396</v>
+      </c>
+      <c r="G297" s="5">
+        <v>377.75</v>
+      </c>
+      <c r="H297" s="5">
+        <v>417.47</v>
+      </c>
+      <c r="I297" s="5">
+        <v>421.06</v>
+      </c>
+      <c r="J297" s="5">
+        <v>487.12</v>
+      </c>
+      <c r="K297" s="5">
+        <v>451.84</v>
+      </c>
+      <c r="L297" s="5">
+        <v>440.89</v>
+      </c>
+      <c r="M297" s="5">
+        <v>662.95</v>
+      </c>
+      <c r="N297" s="5">
+        <v>679.46</v>
+      </c>
+      <c r="O297" s="5">
+        <v>766.04</v>
+      </c>
+      <c r="P297" s="5">
+        <v>776.56</v>
+      </c>
+      <c r="Q297" s="5">
+        <v>829.27</v>
+      </c>
+      <c r="R297" s="5">
+        <v>983.51</v>
+      </c>
+      <c r="S297" s="5">
+        <v>3494.39</v>
+      </c>
+      <c r="T297" s="5">
+        <v>2580.38</v>
+      </c>
+      <c r="U297" s="5">
+        <v>1840.15</v>
+      </c>
+      <c r="V297" s="3"/>
       <c r="W297" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="298" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+      <c r="A298" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B298" s="2" t="s">
         <v>398</v>
-      </c>
-    </row>
-    <row r="298" spans="1:23" ht="27" x14ac:dyDescent="0.25">
-      <c r="A298" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="B298" s="2" t="s">
-        <v>396</v>
       </c>
       <c r="C298" s="2" t="s">
         <v>399</v>
@@ -20030,55 +20290,61 @@
         <v>28</v>
       </c>
       <c r="F298" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="G298" s="3"/>
-      <c r="H298" s="3"/>
-      <c r="I298" s="3"/>
+        <v>396</v>
+      </c>
+      <c r="G298" s="5">
+        <v>96.04</v>
+      </c>
+      <c r="H298" s="5">
+        <v>90.68</v>
+      </c>
+      <c r="I298" s="5">
+        <v>111.55</v>
+      </c>
       <c r="J298" s="5">
-        <v>8.07</v>
+        <v>127.11</v>
       </c>
       <c r="K298" s="5">
-        <v>3.54</v>
+        <v>82.28</v>
       </c>
       <c r="L298" s="5">
-        <v>2.98</v>
+        <v>100.19</v>
       </c>
       <c r="M298" s="5">
-        <v>2.44</v>
+        <v>148.99</v>
       </c>
       <c r="N298" s="5">
-        <v>2.25</v>
+        <v>222.11</v>
       </c>
       <c r="O298" s="5">
-        <v>63.36</v>
+        <v>244.93</v>
       </c>
       <c r="P298" s="5">
-        <v>7.61</v>
+        <v>223.31</v>
       </c>
       <c r="Q298" s="5">
-        <v>6.64</v>
+        <v>225.08</v>
       </c>
       <c r="R298" s="5">
-        <v>3.65</v>
+        <v>296.20999999999998</v>
       </c>
       <c r="S298" s="5">
-        <v>9.59</v>
+        <v>2661.32</v>
       </c>
       <c r="T298" s="5">
-        <v>4.2699999999999996</v>
+        <v>1701.94</v>
       </c>
       <c r="U298" s="5">
-        <v>8.32</v>
+        <v>705.25</v>
       </c>
       <c r="V298" s="3"/>
       <c r="W298" s="2" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="299" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="299" spans="1:23" ht="72" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="B299" s="2" t="s">
         <v>400</v>
@@ -20093,55 +20359,67 @@
         <v>28</v>
       </c>
       <c r="F299" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="G299" s="3"/>
-      <c r="H299" s="3"/>
-      <c r="I299" s="3"/>
-      <c r="J299" s="3"/>
-      <c r="K299" s="6">
-        <v>1</v>
-      </c>
-      <c r="L299" s="6">
-        <v>1</v>
-      </c>
-      <c r="M299" s="6">
-        <v>8</v>
-      </c>
-      <c r="N299" s="6">
-        <v>2</v>
-      </c>
-      <c r="O299" s="3"/>
-      <c r="P299" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q299" s="6">
-        <v>2</v>
-      </c>
-      <c r="R299" s="3"/>
-      <c r="S299" s="3"/>
-      <c r="T299" s="6">
-        <v>8</v>
-      </c>
-      <c r="U299" s="6">
-        <v>7</v>
-      </c>
-      <c r="V299" s="6">
-        <v>2</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G299" s="5">
+        <v>0.08</v>
+      </c>
+      <c r="H299" s="5">
+        <v>0.08</v>
+      </c>
+      <c r="I299" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="J299" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="K299" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="L299" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="M299" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="N299" s="5">
+        <v>0.13</v>
+      </c>
+      <c r="O299" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="P299" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="Q299" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="R299" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="S299" s="5">
+        <v>0.53</v>
+      </c>
+      <c r="T299" s="5">
+        <v>0.33</v>
+      </c>
+      <c r="U299" s="5">
+        <v>0.21</v>
+      </c>
+      <c r="V299" s="3"/>
       <c r="W299" s="2" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
     </row>
     <row r="300" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D300" s="2" t="s">
         <v>27</v>
@@ -20150,65 +20428,63 @@
         <v>28</v>
       </c>
       <c r="F300" s="3" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="G300" s="3"/>
       <c r="H300" s="3"/>
-      <c r="I300" s="6">
-        <v>2</v>
-      </c>
-      <c r="J300" s="6">
-        <v>2</v>
-      </c>
-      <c r="K300" s="6">
-        <v>1</v>
-      </c>
-      <c r="L300" s="6">
-        <v>1</v>
-      </c>
-      <c r="M300" s="6">
-        <v>1</v>
-      </c>
-      <c r="N300" s="6">
-        <v>1</v>
-      </c>
-      <c r="O300" s="6">
-        <v>1</v>
-      </c>
-      <c r="P300" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q300" s="6">
-        <v>4</v>
-      </c>
-      <c r="R300" s="6">
-        <v>1</v>
-      </c>
-      <c r="S300" s="6">
-        <v>1</v>
-      </c>
-      <c r="T300" s="6">
-        <v>0</v>
-      </c>
-      <c r="U300" s="6">
-        <v>4</v>
-      </c>
-      <c r="V300" s="6">
-        <v>2</v>
+      <c r="I300" s="3"/>
+      <c r="J300" s="7">
+        <v>2.2850000000000001</v>
+      </c>
+      <c r="K300" s="7">
+        <v>1.1160000000000001</v>
+      </c>
+      <c r="L300" s="7">
+        <v>1.55</v>
+      </c>
+      <c r="M300" s="7">
+        <v>3.7469999999999999</v>
+      </c>
+      <c r="N300" s="7">
+        <v>3.8530000000000002</v>
+      </c>
+      <c r="O300" s="7">
+        <v>3.367</v>
+      </c>
+      <c r="P300" s="7">
+        <v>6.8940000000000001</v>
+      </c>
+      <c r="Q300" s="7">
+        <v>4.077</v>
+      </c>
+      <c r="R300" s="7">
+        <v>4.49</v>
+      </c>
+      <c r="S300" s="7">
+        <v>11.999000000000001</v>
+      </c>
+      <c r="T300" s="7">
+        <v>16.606000000000002</v>
+      </c>
+      <c r="U300" s="7">
+        <v>20.382000000000001</v>
+      </c>
+      <c r="V300" s="7">
+        <v>5.3920000000000003</v>
       </c>
       <c r="W300" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="301" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D301" s="2" t="s">
         <v>27</v>
@@ -20217,61 +20493,61 @@
         <v>28</v>
       </c>
       <c r="F301" s="3" t="s">
-        <v>32</v>
+        <v>396</v>
       </c>
       <c r="G301" s="3"/>
       <c r="H301" s="3"/>
       <c r="I301" s="3"/>
-      <c r="J301" s="3"/>
-      <c r="K301" s="6">
-        <v>5</v>
-      </c>
-      <c r="L301" s="6">
-        <v>13</v>
-      </c>
-      <c r="M301" s="6">
-        <v>19</v>
-      </c>
-      <c r="N301" s="6">
-        <v>18</v>
-      </c>
-      <c r="O301" s="6">
-        <v>15</v>
-      </c>
-      <c r="P301" s="6">
-        <v>15</v>
-      </c>
-      <c r="Q301" s="6">
-        <v>8</v>
-      </c>
-      <c r="R301" s="6">
-        <v>28</v>
-      </c>
-      <c r="S301" s="6">
-        <v>53</v>
-      </c>
-      <c r="T301" s="6">
-        <v>65</v>
-      </c>
-      <c r="U301" s="6">
-        <v>70</v>
-      </c>
-      <c r="V301" s="6">
-        <v>69</v>
-      </c>
+      <c r="J301" s="5">
+        <v>8.07</v>
+      </c>
+      <c r="K301" s="5">
+        <v>3.54</v>
+      </c>
+      <c r="L301" s="5">
+        <v>2.98</v>
+      </c>
+      <c r="M301" s="5">
+        <v>2.44</v>
+      </c>
+      <c r="N301" s="5">
+        <v>2.25</v>
+      </c>
+      <c r="O301" s="5">
+        <v>63.36</v>
+      </c>
+      <c r="P301" s="5">
+        <v>7.61</v>
+      </c>
+      <c r="Q301" s="5">
+        <v>6.64</v>
+      </c>
+      <c r="R301" s="5">
+        <v>3.65</v>
+      </c>
+      <c r="S301" s="5">
+        <v>9.59</v>
+      </c>
+      <c r="T301" s="5">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="U301" s="5">
+        <v>8.32</v>
+      </c>
+      <c r="V301" s="3"/>
       <c r="W301" s="2" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="302" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="302" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D302" s="2" t="s">
         <v>27</v>
@@ -20280,47 +20556,234 @@
         <v>28</v>
       </c>
       <c r="F302" s="3" t="s">
-        <v>32</v>
+        <v>408</v>
       </c>
       <c r="G302" s="3"/>
       <c r="H302" s="3"/>
       <c r="I302" s="3"/>
       <c r="J302" s="3"/>
-      <c r="K302" s="3"/>
-      <c r="L302" s="3"/>
-      <c r="M302" s="3"/>
-      <c r="N302" s="3"/>
+      <c r="K302" s="6">
+        <v>1</v>
+      </c>
+      <c r="L302" s="6">
+        <v>1</v>
+      </c>
+      <c r="M302" s="6">
+        <v>8</v>
+      </c>
+      <c r="N302" s="6">
+        <v>2</v>
+      </c>
       <c r="O302" s="3"/>
-      <c r="P302" s="3"/>
-      <c r="Q302" s="3"/>
+      <c r="P302" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q302" s="6">
+        <v>2</v>
+      </c>
       <c r="R302" s="3"/>
       <c r="S302" s="3"/>
       <c r="T302" s="6">
+        <v>8</v>
+      </c>
+      <c r="U302" s="6">
+        <v>7</v>
+      </c>
+      <c r="V302" s="6">
+        <v>2</v>
+      </c>
+      <c r="W302" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="303" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+      <c r="A303" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B303" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="C303" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="D303" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E303" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F303" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="G303" s="3"/>
+      <c r="H303" s="3"/>
+      <c r="I303" s="6">
+        <v>2</v>
+      </c>
+      <c r="J303" s="6">
+        <v>2</v>
+      </c>
+      <c r="K303" s="6">
+        <v>1</v>
+      </c>
+      <c r="L303" s="6">
+        <v>1</v>
+      </c>
+      <c r="M303" s="6">
+        <v>1</v>
+      </c>
+      <c r="N303" s="6">
+        <v>1</v>
+      </c>
+      <c r="O303" s="6">
+        <v>1</v>
+      </c>
+      <c r="P303" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q303" s="6">
+        <v>4</v>
+      </c>
+      <c r="R303" s="6">
+        <v>1</v>
+      </c>
+      <c r="S303" s="6">
+        <v>1</v>
+      </c>
+      <c r="T303" s="6">
+        <v>0</v>
+      </c>
+      <c r="U303" s="6">
+        <v>4</v>
+      </c>
+      <c r="V303" s="6">
+        <v>2</v>
+      </c>
+      <c r="W303" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="304" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+      <c r="A304" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B304" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="C304" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="D304" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E304" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F304" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G304" s="3"/>
+      <c r="H304" s="3"/>
+      <c r="I304" s="3"/>
+      <c r="J304" s="3"/>
+      <c r="K304" s="6">
+        <v>5</v>
+      </c>
+      <c r="L304" s="6">
+        <v>13</v>
+      </c>
+      <c r="M304" s="6">
+        <v>19</v>
+      </c>
+      <c r="N304" s="6">
+        <v>18</v>
+      </c>
+      <c r="O304" s="6">
+        <v>15</v>
+      </c>
+      <c r="P304" s="6">
+        <v>15</v>
+      </c>
+      <c r="Q304" s="6">
+        <v>8</v>
+      </c>
+      <c r="R304" s="6">
+        <v>28</v>
+      </c>
+      <c r="S304" s="6">
+        <v>53</v>
+      </c>
+      <c r="T304" s="6">
+        <v>65</v>
+      </c>
+      <c r="U304" s="6">
+        <v>70</v>
+      </c>
+      <c r="V304" s="6">
+        <v>69</v>
+      </c>
+      <c r="W304" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="305" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+      <c r="A305" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B305" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="C305" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="D305" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E305" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F305" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G305" s="3"/>
+      <c r="H305" s="3"/>
+      <c r="I305" s="3"/>
+      <c r="J305" s="3"/>
+      <c r="K305" s="3"/>
+      <c r="L305" s="3"/>
+      <c r="M305" s="3"/>
+      <c r="N305" s="3"/>
+      <c r="O305" s="3"/>
+      <c r="P305" s="3"/>
+      <c r="Q305" s="3"/>
+      <c r="R305" s="3"/>
+      <c r="S305" s="3"/>
+      <c r="T305" s="6">
         <v>114</v>
       </c>
-      <c r="U302" s="6">
+      <c r="U305" s="6">
         <v>61</v>
       </c>
-      <c r="V302" s="6">
+      <c r="V305" s="6">
         <v>97</v>
       </c>
-      <c r="W302" s="2" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="303" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="304" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A304" s="10" t="s">
-        <v>411</v>
-      </c>
-      <c r="B304" s="8"/>
+      <c r="W305" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="306" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A307" s="10" t="s">
+        <v>417</v>
+      </c>
+      <c r="B307" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:C3" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A304:B304"/>
+    <mergeCell ref="A307:B307"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>

--- a/assets/excel/en/national_sdg_indicators.xlsx
+++ b/assets/excel/en/national_sdg_indicators.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sidwab\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\niewiadomskaew\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CA763E3-23B7-4D3E-B9C8-34C22AC91AE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67E58836-893A-4CAB-9549-A33A21353932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2139" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2146" uniqueCount="418">
   <si>
     <t>sdg.gov.pl/en</t>
   </si>
@@ -1282,7 +1282,7 @@
     <t>The Ministry of Economic Development and Technology / The Chancellery of the  Prime Minister</t>
   </si>
   <si>
-    <t>Last update: 20-05-2026, 10:30</t>
+    <t>Last update: 26-05-2026, 10:02</t>
   </si>
 </sst>
 </file>
@@ -1828,7 +1828,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W307"/>
+  <dimension ref="A1:W310"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" customWidth="1"/>
@@ -7489,18 +7489,18 @@
       <c r="O96" s="3"/>
       <c r="P96" s="3"/>
       <c r="Q96" s="3"/>
-      <c r="R96" s="4">
+      <c r="R96" s="6">
         <v>21</v>
       </c>
       <c r="S96" s="3"/>
-      <c r="T96" s="4">
+      <c r="T96" s="6">
         <v>20</v>
       </c>
-      <c r="U96" s="4">
+      <c r="U96" s="6">
         <v>22</v>
       </c>
-      <c r="V96" s="4">
-        <v>23.5</v>
+      <c r="V96" s="6">
+        <v>24</v>
       </c>
       <c r="W96" s="2" t="s">
         <v>30</v>
@@ -7536,18 +7536,18 @@
       <c r="O97" s="3"/>
       <c r="P97" s="3"/>
       <c r="Q97" s="3"/>
-      <c r="R97" s="4">
+      <c r="R97" s="6">
         <v>20</v>
       </c>
       <c r="S97" s="3"/>
-      <c r="T97" s="4">
+      <c r="T97" s="6">
         <v>19</v>
       </c>
-      <c r="U97" s="4">
+      <c r="U97" s="6">
         <v>20</v>
       </c>
-      <c r="V97" s="4">
-        <v>23.5</v>
+      <c r="V97" s="6">
+        <v>24</v>
       </c>
       <c r="W97" s="2" t="s">
         <v>30</v>
@@ -7583,18 +7583,18 @@
       <c r="O98" s="3"/>
       <c r="P98" s="3"/>
       <c r="Q98" s="3"/>
-      <c r="R98" s="4">
+      <c r="R98" s="6">
         <v>22</v>
       </c>
       <c r="S98" s="3"/>
-      <c r="T98" s="4">
+      <c r="T98" s="6">
         <v>21</v>
       </c>
-      <c r="U98" s="4">
+      <c r="U98" s="6">
         <v>25</v>
       </c>
-      <c r="V98" s="4">
-        <v>23.6</v>
+      <c r="V98" s="6">
+        <v>24</v>
       </c>
       <c r="W98" s="2" t="s">
         <v>30</v>
@@ -7720,18 +7720,18 @@
       <c r="O101" s="3"/>
       <c r="P101" s="3"/>
       <c r="Q101" s="3"/>
-      <c r="R101" s="4">
+      <c r="R101" s="6">
         <v>36</v>
       </c>
       <c r="S101" s="3"/>
-      <c r="T101" s="4">
+      <c r="T101" s="6">
         <v>31</v>
       </c>
-      <c r="U101" s="4">
+      <c r="U101" s="6">
         <v>36</v>
       </c>
-      <c r="V101" s="4">
-        <v>38.6</v>
+      <c r="V101" s="6">
+        <v>39</v>
       </c>
       <c r="W101" s="2" t="s">
         <v>30</v>
@@ -7814,18 +7814,18 @@
       <c r="O103" s="3"/>
       <c r="P103" s="3"/>
       <c r="Q103" s="3"/>
-      <c r="R103" s="4">
+      <c r="R103" s="6">
         <v>28</v>
       </c>
       <c r="S103" s="3"/>
-      <c r="T103" s="4">
+      <c r="T103" s="6">
         <v>27</v>
       </c>
-      <c r="U103" s="4">
+      <c r="U103" s="6">
         <v>31</v>
       </c>
-      <c r="V103" s="4">
-        <v>32.200000000000003</v>
+      <c r="V103" s="6">
+        <v>32</v>
       </c>
       <c r="W103" s="2" t="s">
         <v>30</v>
@@ -7861,18 +7861,18 @@
       <c r="O104" s="3"/>
       <c r="P104" s="3"/>
       <c r="Q104" s="3"/>
-      <c r="R104" s="4">
+      <c r="R104" s="6">
         <v>17</v>
       </c>
       <c r="S104" s="3"/>
-      <c r="T104" s="4">
+      <c r="T104" s="6">
         <v>18</v>
       </c>
-      <c r="U104" s="4">
+      <c r="U104" s="6">
         <v>19</v>
       </c>
-      <c r="V104" s="4">
-        <v>20.9</v>
+      <c r="V104" s="6">
+        <v>21</v>
       </c>
       <c r="W104" s="2" t="s">
         <v>30</v>
@@ -7908,18 +7908,18 @@
       <c r="O105" s="3"/>
       <c r="P105" s="3"/>
       <c r="Q105" s="3"/>
-      <c r="R105" s="4">
+      <c r="R105" s="6">
         <v>8</v>
       </c>
       <c r="S105" s="3"/>
-      <c r="T105" s="4">
+      <c r="T105" s="6">
         <v>9</v>
       </c>
-      <c r="U105" s="4">
+      <c r="U105" s="6">
         <v>12</v>
       </c>
-      <c r="V105" s="4">
-        <v>8.8000000000000007</v>
+      <c r="V105" s="6">
+        <v>9</v>
       </c>
       <c r="W105" s="2" t="s">
         <v>30</v>
@@ -7955,18 +7955,18 @@
       <c r="O106" s="3"/>
       <c r="P106" s="3"/>
       <c r="Q106" s="3"/>
-      <c r="R106" s="4">
+      <c r="R106" s="6">
         <v>3</v>
       </c>
       <c r="S106" s="3"/>
-      <c r="T106" s="4">
+      <c r="T106" s="6">
         <v>3</v>
       </c>
-      <c r="U106" s="4">
+      <c r="U106" s="6">
         <v>3</v>
       </c>
-      <c r="V106" s="4">
-        <v>2.7</v>
+      <c r="V106" s="6">
+        <v>3</v>
       </c>
       <c r="W106" s="2" t="s">
         <v>30</v>
@@ -12941,10 +12941,10 @@
         <v>8.8000000000000007</v>
       </c>
       <c r="P183" s="4">
-        <v>8.1999999999999993</v>
+        <v>7.9</v>
       </c>
       <c r="Q183" s="4">
-        <v>8.8000000000000007</v>
+        <v>8.6</v>
       </c>
       <c r="R183" s="4">
         <v>11.2</v>
@@ -12958,7 +12958,9 @@
       <c r="U183" s="4">
         <v>7</v>
       </c>
-      <c r="V183" s="3"/>
+      <c r="V183" s="4">
+        <v>7.1</v>
+      </c>
       <c r="W183" s="2" t="s">
         <v>30</v>
       </c>
@@ -13010,10 +13012,10 @@
         <v>10.1</v>
       </c>
       <c r="P184" s="4">
-        <v>9.5</v>
+        <v>9.1</v>
       </c>
       <c r="Q184" s="4">
-        <v>9.6</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="R184" s="4">
         <v>11.8</v>
@@ -13027,7 +13029,9 @@
       <c r="U184" s="4">
         <v>6.9</v>
       </c>
-      <c r="V184" s="3"/>
+      <c r="V184" s="4">
+        <v>7.6</v>
+      </c>
       <c r="W184" s="2" t="s">
         <v>30</v>
       </c>
@@ -13079,10 +13083,10 @@
         <v>7.4</v>
       </c>
       <c r="P185" s="4">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="Q185" s="4">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="R185" s="4">
         <v>10.6</v>
@@ -13096,7 +13100,9 @@
       <c r="U185" s="4">
         <v>7</v>
       </c>
-      <c r="V185" s="3"/>
+      <c r="V185" s="4">
+        <v>6.7</v>
+      </c>
       <c r="W185" s="2" t="s">
         <v>30</v>
       </c>
@@ -15731,7 +15737,9 @@
       <c r="U228" s="4">
         <v>5.8</v>
       </c>
-      <c r="V228" s="3"/>
+      <c r="V228" s="4">
+        <v>6</v>
+      </c>
       <c r="W228" s="2" t="s">
         <v>30</v>
       </c>
@@ -15800,7 +15808,9 @@
       <c r="U229" s="5">
         <v>0.18</v>
       </c>
-      <c r="V229" s="3"/>
+      <c r="V229" s="5">
+        <v>0.25</v>
+      </c>
       <c r="W229" s="2" t="s">
         <v>30</v>
       </c>
@@ -17228,128 +17238,128 @@
         <v>27</v>
       </c>
       <c r="E251" s="3" t="s">
-        <v>334</v>
+        <v>28</v>
       </c>
       <c r="F251" s="3" t="s">
         <v>333</v>
       </c>
       <c r="G251" s="6">
-        <v>5248</v>
+        <v>28</v>
       </c>
       <c r="H251" s="6">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="I251" s="6">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="J251" s="6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K251" s="6">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L251" s="6">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="M251" s="6">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N251" s="6">
-        <v>87</v>
+        <v>22</v>
       </c>
       <c r="O251" s="6">
-        <v>966</v>
+        <v>22</v>
       </c>
       <c r="P251" s="6">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Q251" s="6">
-        <v>451</v>
+        <v>19</v>
       </c>
       <c r="R251" s="6">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="S251" s="6">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="T251" s="6">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="U251" s="6">
-        <v>2938</v>
+        <v>15</v>
       </c>
       <c r="V251" s="3"/>
       <c r="W251" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="252" spans="1:23" ht="18" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
         <v>313</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="D252" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E252" s="3" t="s">
-        <v>28</v>
+        <v>334</v>
       </c>
       <c r="F252" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G252" s="5">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="H252" s="5">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="I252" s="5">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="J252" s="5">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="K252" s="5">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="L252" s="5">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="M252" s="5">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="N252" s="5">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="O252" s="5">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="P252" s="5">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="Q252" s="5">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="R252" s="5">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="S252" s="5">
-        <v>0.59</v>
-      </c>
-      <c r="T252" s="5">
-        <v>0.59</v>
-      </c>
-      <c r="U252" s="5">
-        <v>0.59</v>
+        <v>333</v>
+      </c>
+      <c r="G252" s="6">
+        <v>5248</v>
+      </c>
+      <c r="H252" s="6">
+        <v>0</v>
+      </c>
+      <c r="I252" s="6">
+        <v>7</v>
+      </c>
+      <c r="J252" s="6">
+        <v>0</v>
+      </c>
+      <c r="K252" s="6">
+        <v>0</v>
+      </c>
+      <c r="L252" s="6">
+        <v>0</v>
+      </c>
+      <c r="M252" s="6">
+        <v>0</v>
+      </c>
+      <c r="N252" s="6">
+        <v>87</v>
+      </c>
+      <c r="O252" s="6">
+        <v>966</v>
+      </c>
+      <c r="P252" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q252" s="6">
+        <v>451</v>
+      </c>
+      <c r="R252" s="6">
+        <v>33</v>
+      </c>
+      <c r="S252" s="6">
+        <v>1</v>
+      </c>
+      <c r="T252" s="6">
+        <v>1</v>
+      </c>
+      <c r="U252" s="6">
+        <v>2938</v>
       </c>
       <c r="V252" s="3"/>
       <c r="W252" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="253" spans="1:23" ht="18" x14ac:dyDescent="0.25">
@@ -17360,7 +17370,7 @@
         <v>335</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D253" s="2" t="s">
         <v>27</v>
@@ -17369,54 +17379,56 @@
         <v>28</v>
       </c>
       <c r="F253" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="G253" s="4">
-        <v>732401.6</v>
-      </c>
-      <c r="H253" s="4">
-        <v>740630</v>
-      </c>
-      <c r="I253" s="4">
-        <v>753624</v>
-      </c>
-      <c r="J253" s="4">
-        <v>752240.3</v>
-      </c>
-      <c r="K253" s="4">
-        <v>804401.8</v>
-      </c>
-      <c r="L253" s="4">
-        <v>830309.8</v>
-      </c>
-      <c r="M253" s="4">
-        <v>826034.2</v>
-      </c>
-      <c r="N253" s="3"/>
-      <c r="O253" s="4">
-        <v>846693.5</v>
-      </c>
-      <c r="P253" s="4">
-        <v>839607.4</v>
-      </c>
-      <c r="Q253" s="4">
-        <v>852978.8</v>
-      </c>
-      <c r="R253" s="4">
-        <v>855928.1</v>
-      </c>
-      <c r="S253" s="4">
-        <v>859996.9</v>
-      </c>
-      <c r="T253" s="4">
-        <v>870987.2</v>
-      </c>
-      <c r="U253" s="4">
-        <v>881284.3</v>
+        <v>36</v>
+      </c>
+      <c r="G253" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="H253" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="I253" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J253" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="K253" s="5">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="L253" s="5">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="M253" s="5">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="N253" s="5">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="O253" s="5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="P253" s="5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="Q253" s="5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="R253" s="5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="S253" s="5">
+        <v>0.59</v>
+      </c>
+      <c r="T253" s="5">
+        <v>0.59</v>
+      </c>
+      <c r="U253" s="5">
+        <v>0.59</v>
       </c>
       <c r="V253" s="3"/>
       <c r="W253" s="2" t="s">
-        <v>170</v>
+        <v>30</v>
       </c>
     </row>
     <row r="254" spans="1:23" ht="18" x14ac:dyDescent="0.25">
@@ -17427,7 +17439,7 @@
         <v>335</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D254" s="2" t="s">
         <v>27</v>
@@ -17436,46 +17448,52 @@
         <v>28</v>
       </c>
       <c r="F254" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="G254" s="3"/>
-      <c r="H254" s="3"/>
-      <c r="I254" s="3"/>
-      <c r="J254" s="3"/>
-      <c r="K254" s="3"/>
-      <c r="L254" s="5">
-        <v>6.6</v>
-      </c>
-      <c r="M254" s="5">
-        <v>7.58</v>
-      </c>
-      <c r="N254" s="5">
-        <v>7.54</v>
-      </c>
-      <c r="O254" s="5">
-        <v>10.15</v>
-      </c>
-      <c r="P254" s="5">
-        <v>12.38</v>
-      </c>
-      <c r="Q254" s="5">
-        <v>12.53</v>
-      </c>
-      <c r="R254" s="5">
-        <v>5.95</v>
-      </c>
-      <c r="S254" s="5">
-        <v>4.7300000000000004</v>
-      </c>
-      <c r="T254" s="5">
-        <v>6.25</v>
-      </c>
-      <c r="U254" s="5">
-        <v>5.6</v>
-      </c>
-      <c r="V254" s="5">
-        <v>5.95</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="G254" s="4">
+        <v>732401.6</v>
+      </c>
+      <c r="H254" s="4">
+        <v>740630</v>
+      </c>
+      <c r="I254" s="4">
+        <v>753624</v>
+      </c>
+      <c r="J254" s="4">
+        <v>752240.3</v>
+      </c>
+      <c r="K254" s="4">
+        <v>804401.8</v>
+      </c>
+      <c r="L254" s="4">
+        <v>830309.8</v>
+      </c>
+      <c r="M254" s="4">
+        <v>826034.2</v>
+      </c>
+      <c r="N254" s="3"/>
+      <c r="O254" s="4">
+        <v>846693.5</v>
+      </c>
+      <c r="P254" s="4">
+        <v>839607.4</v>
+      </c>
+      <c r="Q254" s="4">
+        <v>852978.8</v>
+      </c>
+      <c r="R254" s="4">
+        <v>855928.1</v>
+      </c>
+      <c r="S254" s="4">
+        <v>859996.9</v>
+      </c>
+      <c r="T254" s="4">
+        <v>870987.2</v>
+      </c>
+      <c r="U254" s="4">
+        <v>881284.3</v>
+      </c>
+      <c r="V254" s="3"/>
       <c r="W254" s="2" t="s">
         <v>170</v>
       </c>
@@ -17485,10 +17503,10 @@
         <v>313</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="D255" s="2" t="s">
         <v>27</v>
@@ -17497,53 +17515,59 @@
         <v>28</v>
       </c>
       <c r="F255" s="3" t="s">
-        <v>36</v>
+        <v>339</v>
       </c>
       <c r="G255" s="3"/>
       <c r="H255" s="3"/>
       <c r="I255" s="3"/>
       <c r="J255" s="3"/>
       <c r="K255" s="3"/>
-      <c r="L255" s="3"/>
-      <c r="M255" s="3"/>
-      <c r="N255" s="3"/>
-      <c r="O255" s="6">
-        <v>1</v>
-      </c>
-      <c r="P255" s="6">
-        <v>54</v>
-      </c>
-      <c r="Q255" s="6">
-        <v>63</v>
-      </c>
-      <c r="R255" s="6">
-        <v>66</v>
-      </c>
-      <c r="S255" s="6">
-        <v>70</v>
-      </c>
-      <c r="T255" s="6">
-        <v>75</v>
-      </c>
-      <c r="U255" s="6">
-        <v>80</v>
-      </c>
-      <c r="V255" s="6">
-        <v>86</v>
+      <c r="L255" s="5">
+        <v>6.6</v>
+      </c>
+      <c r="M255" s="5">
+        <v>7.58</v>
+      </c>
+      <c r="N255" s="5">
+        <v>7.54</v>
+      </c>
+      <c r="O255" s="5">
+        <v>10.15</v>
+      </c>
+      <c r="P255" s="5">
+        <v>12.38</v>
+      </c>
+      <c r="Q255" s="5">
+        <v>12.53</v>
+      </c>
+      <c r="R255" s="5">
+        <v>5.95</v>
+      </c>
+      <c r="S255" s="5">
+        <v>4.7300000000000004</v>
+      </c>
+      <c r="T255" s="5">
+        <v>6.25</v>
+      </c>
+      <c r="U255" s="5">
+        <v>5.6</v>
+      </c>
+      <c r="V255" s="5">
+        <v>5.95</v>
       </c>
       <c r="W255" s="2" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="256" spans="1:23" ht="99" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="256" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
         <v>313</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D256" s="2" t="s">
         <v>27</v>
@@ -17552,7 +17576,7 @@
         <v>28</v>
       </c>
       <c r="F256" s="3" t="s">
-        <v>261</v>
+        <v>36</v>
       </c>
       <c r="G256" s="3"/>
       <c r="H256" s="3"/>
@@ -17562,27 +17586,35 @@
       <c r="L256" s="3"/>
       <c r="M256" s="3"/>
       <c r="N256" s="3"/>
-      <c r="O256" s="3"/>
-      <c r="P256" s="3"/>
-      <c r="Q256" s="3"/>
-      <c r="R256" s="3"/>
+      <c r="O256" s="6">
+        <v>1</v>
+      </c>
+      <c r="P256" s="6">
+        <v>54</v>
+      </c>
+      <c r="Q256" s="6">
+        <v>63</v>
+      </c>
+      <c r="R256" s="6">
+        <v>66</v>
+      </c>
       <c r="S256" s="6">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="T256" s="6">
-        <v>7</v>
+        <v>75</v>
       </c>
       <c r="U256" s="6">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="V256" s="6">
-        <v>4</v>
+        <v>86</v>
       </c>
       <c r="W256" s="2" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="257" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="257" spans="1:23" ht="99" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
         <v>313</v>
       </c>
@@ -17590,7 +17622,7 @@
         <v>343</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D257" s="2" t="s">
         <v>27</v>
@@ -17599,7 +17631,7 @@
         <v>28</v>
       </c>
       <c r="F257" s="3" t="s">
-        <v>347</v>
+        <v>261</v>
       </c>
       <c r="G257" s="3"/>
       <c r="H257" s="3"/>
@@ -17612,92 +17644,70 @@
       <c r="O257" s="3"/>
       <c r="P257" s="3"/>
       <c r="Q257" s="3"/>
-      <c r="R257" s="6">
+      <c r="R257" s="3"/>
+      <c r="S257" s="6">
+        <v>16</v>
+      </c>
+      <c r="T257" s="6">
+        <v>7</v>
+      </c>
+      <c r="U257" s="6">
+        <v>6</v>
+      </c>
+      <c r="V257" s="6">
+        <v>4</v>
+      </c>
+      <c r="W257" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="258" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+      <c r="A258" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D258" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E258" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F258" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="G258" s="3"/>
+      <c r="H258" s="3"/>
+      <c r="I258" s="3"/>
+      <c r="J258" s="3"/>
+      <c r="K258" s="3"/>
+      <c r="L258" s="3"/>
+      <c r="M258" s="3"/>
+      <c r="N258" s="3"/>
+      <c r="O258" s="3"/>
+      <c r="P258" s="3"/>
+      <c r="Q258" s="3"/>
+      <c r="R258" s="6">
         <v>133</v>
       </c>
-      <c r="S257" s="6">
+      <c r="S258" s="6">
         <v>80</v>
       </c>
-      <c r="T257" s="6">
+      <c r="T258" s="6">
         <v>97</v>
       </c>
-      <c r="U257" s="6">
+      <c r="U258" s="6">
         <v>44</v>
       </c>
-      <c r="V257" s="6">
+      <c r="V258" s="6">
         <v>89</v>
       </c>
-      <c r="W257" s="2" t="s">
+      <c r="W258" s="2" t="s">
         <v>348</v>
-      </c>
-    </row>
-    <row r="258" spans="1:23" ht="72" x14ac:dyDescent="0.25">
-      <c r="A258" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="B258" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="C258" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="D258" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="E258" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="F258" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G258" s="6">
-        <v>40</v>
-      </c>
-      <c r="H258" s="6">
-        <v>60</v>
-      </c>
-      <c r="I258" s="6">
-        <v>40</v>
-      </c>
-      <c r="J258" s="6">
-        <v>40</v>
-      </c>
-      <c r="K258" s="6">
-        <v>40</v>
-      </c>
-      <c r="L258" s="6">
-        <v>40</v>
-      </c>
-      <c r="M258" s="6">
-        <v>60</v>
-      </c>
-      <c r="N258" s="6">
-        <v>40</v>
-      </c>
-      <c r="O258" s="6">
-        <v>40</v>
-      </c>
-      <c r="P258" s="6">
-        <v>40</v>
-      </c>
-      <c r="Q258" s="6">
-        <v>60</v>
-      </c>
-      <c r="R258" s="6">
-        <v>67</v>
-      </c>
-      <c r="S258" s="6">
-        <v>50</v>
-      </c>
-      <c r="T258" s="6">
-        <v>67</v>
-      </c>
-      <c r="U258" s="6">
-        <v>67</v>
-      </c>
-      <c r="V258" s="3"/>
-      <c r="W258" s="2" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="259" spans="1:23" ht="72" x14ac:dyDescent="0.25">
@@ -17714,7 +17724,7 @@
         <v>352</v>
       </c>
       <c r="E259" s="3" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="F259" s="3" t="s">
         <v>36</v>
@@ -17726,13 +17736,13 @@
         <v>60</v>
       </c>
       <c r="I259" s="6">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="J259" s="6">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K259" s="6">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L259" s="6">
         <v>40</v>
@@ -17744,25 +17754,25 @@
         <v>40</v>
       </c>
       <c r="O259" s="6">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="P259" s="6">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="Q259" s="6">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="R259" s="6">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="S259" s="6">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="T259" s="6">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="U259" s="6">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="V259" s="3"/>
       <c r="W259" s="2" t="s">
@@ -17783,16 +17793,16 @@
         <v>352</v>
       </c>
       <c r="E260" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F260" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G260" s="6">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H260" s="6">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I260" s="6">
         <v>20</v>
@@ -17804,34 +17814,34 @@
         <v>20</v>
       </c>
       <c r="L260" s="6">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M260" s="6">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N260" s="6">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="O260" s="6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="P260" s="6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Q260" s="6">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="R260" s="6">
         <v>17</v>
       </c>
       <c r="S260" s="6">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="T260" s="6">
         <v>17</v>
       </c>
       <c r="U260" s="6">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="V260" s="3"/>
       <c r="W260" s="2" t="s">
@@ -17852,139 +17862,139 @@
         <v>352</v>
       </c>
       <c r="E261" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F261" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G261" s="6">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H261" s="6">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I261" s="6">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="J261" s="6">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="K261" s="6">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="L261" s="6">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M261" s="6">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="N261" s="6">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="O261" s="6">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="P261" s="6">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="Q261" s="6">
         <v>40</v>
       </c>
       <c r="R261" s="6">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="S261" s="6">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="T261" s="6">
         <v>17</v>
       </c>
       <c r="U261" s="6">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="V261" s="3"/>
       <c r="W261" s="2" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="262" spans="1:23" ht="18" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:23" ht="72" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
         <v>349</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>27</v>
+        <v>352</v>
       </c>
       <c r="E262" s="3" t="s">
-        <v>28</v>
+        <v>357</v>
       </c>
       <c r="F262" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="G262" s="4">
-        <v>100</v>
-      </c>
-      <c r="H262" s="4">
-        <v>100.8</v>
-      </c>
-      <c r="I262" s="4">
-        <v>99.9</v>
-      </c>
-      <c r="J262" s="4">
-        <v>101.8</v>
-      </c>
-      <c r="K262" s="4">
-        <v>104.9</v>
-      </c>
-      <c r="L262" s="4">
-        <v>106</v>
-      </c>
-      <c r="M262" s="4">
-        <v>119.9</v>
-      </c>
-      <c r="N262" s="4">
-        <v>119.4</v>
-      </c>
-      <c r="O262" s="4">
-        <v>130</v>
-      </c>
-      <c r="P262" s="4">
-        <v>189.5</v>
-      </c>
-      <c r="Q262" s="4">
-        <v>186.6</v>
-      </c>
-      <c r="R262" s="4">
-        <v>190.1</v>
-      </c>
-      <c r="S262" s="4">
-        <v>200.8</v>
-      </c>
-      <c r="T262" s="4">
-        <v>205.6</v>
-      </c>
-      <c r="U262" s="4">
-        <v>208.5</v>
+        <v>36</v>
+      </c>
+      <c r="G262" s="6">
+        <v>60</v>
+      </c>
+      <c r="H262" s="6">
+        <v>40</v>
+      </c>
+      <c r="I262" s="6">
+        <v>60</v>
+      </c>
+      <c r="J262" s="6">
+        <v>60</v>
+      </c>
+      <c r="K262" s="6">
+        <v>60</v>
+      </c>
+      <c r="L262" s="6">
+        <v>60</v>
+      </c>
+      <c r="M262" s="6">
+        <v>40</v>
+      </c>
+      <c r="N262" s="6">
+        <v>60</v>
+      </c>
+      <c r="O262" s="6">
+        <v>75</v>
+      </c>
+      <c r="P262" s="6">
+        <v>75</v>
+      </c>
+      <c r="Q262" s="6">
+        <v>40</v>
+      </c>
+      <c r="R262" s="6">
+        <v>33</v>
+      </c>
+      <c r="S262" s="6">
+        <v>50</v>
+      </c>
+      <c r="T262" s="6">
+        <v>17</v>
+      </c>
+      <c r="U262" s="6">
+        <v>25</v>
       </c>
       <c r="V262" s="3"/>
       <c r="W262" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="263" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="263" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
         <v>349</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D263" s="2" t="s">
         <v>27</v>
@@ -17993,67 +18003,67 @@
         <v>28</v>
       </c>
       <c r="F263" s="3" t="s">
-        <v>362</v>
+        <v>319</v>
       </c>
       <c r="G263" s="4">
-        <v>59.5</v>
+        <v>100</v>
       </c>
       <c r="H263" s="4">
-        <v>57.7</v>
+        <v>100.8</v>
       </c>
       <c r="I263" s="4">
-        <v>58.8</v>
+        <v>99.9</v>
       </c>
       <c r="J263" s="4">
-        <v>64.3</v>
+        <v>101.8</v>
       </c>
       <c r="K263" s="4">
-        <v>68.7</v>
+        <v>104.9</v>
       </c>
       <c r="L263" s="4">
-        <v>69.5</v>
+        <v>106</v>
       </c>
       <c r="M263" s="4">
-        <v>72.900000000000006</v>
+        <v>119.9</v>
       </c>
       <c r="N263" s="4">
-        <v>78.099999999999994</v>
+        <v>119.4</v>
       </c>
       <c r="O263" s="4">
-        <v>91.8</v>
+        <v>130</v>
       </c>
       <c r="P263" s="4">
-        <v>93.9</v>
+        <v>189.5</v>
       </c>
       <c r="Q263" s="4">
-        <v>88.5</v>
+        <v>186.6</v>
       </c>
       <c r="R263" s="4">
-        <v>96.7</v>
+        <v>190.1</v>
       </c>
       <c r="S263" s="4">
-        <v>119</v>
+        <v>200.8</v>
       </c>
       <c r="T263" s="4">
-        <v>136.4</v>
+        <v>205.6</v>
       </c>
       <c r="U263" s="4">
-        <v>124.2</v>
+        <v>208.5</v>
       </c>
       <c r="V263" s="3"/>
       <c r="W263" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="264" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="D264" s="2" t="s">
         <v>27</v>
@@ -18062,56 +18072,56 @@
         <v>28</v>
       </c>
       <c r="F264" s="3" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="G264" s="4">
-        <v>90.8</v>
+        <v>59.5</v>
       </c>
       <c r="H264" s="4">
-        <v>88.8</v>
+        <v>57.7</v>
       </c>
       <c r="I264" s="4">
-        <v>86.5</v>
+        <v>58.8</v>
       </c>
       <c r="J264" s="4">
-        <v>87</v>
+        <v>64.3</v>
       </c>
       <c r="K264" s="4">
-        <v>85</v>
+        <v>68.7</v>
       </c>
       <c r="L264" s="4">
-        <v>87.4</v>
+        <v>69.5</v>
       </c>
       <c r="M264" s="4">
-        <v>88.7</v>
+        <v>72.900000000000006</v>
       </c>
       <c r="N264" s="4">
-        <v>84.6</v>
+        <v>78.099999999999994</v>
       </c>
       <c r="O264" s="4">
-        <v>77.3</v>
+        <v>91.8</v>
       </c>
       <c r="P264" s="4">
-        <v>79.7</v>
+        <v>93.9</v>
       </c>
       <c r="Q264" s="4">
-        <v>81.900000000000006</v>
+        <v>88.5</v>
       </c>
       <c r="R264" s="4">
-        <v>74.8</v>
+        <v>96.7</v>
       </c>
       <c r="S264" s="4">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="T264" s="4">
-        <v>77.2</v>
+        <v>136.4</v>
       </c>
       <c r="U264" s="4">
-        <v>76.3</v>
+        <v>124.2</v>
       </c>
       <c r="V264" s="3"/>
       <c r="W264" s="2" t="s">
-        <v>367</v>
+        <v>30</v>
       </c>
     </row>
     <row r="265" spans="1:23" ht="36" x14ac:dyDescent="0.25">
@@ -18122,7 +18132,7 @@
         <v>364</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="D265" s="2" t="s">
         <v>27</v>
@@ -18131,56 +18141,56 @@
         <v>28</v>
       </c>
       <c r="F265" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G265" s="7">
-        <v>0.19600000000000001</v>
-      </c>
-      <c r="H265" s="7">
-        <v>0.20499999999999999</v>
-      </c>
-      <c r="I265" s="7">
-        <v>0.20599999999999999</v>
-      </c>
-      <c r="J265" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="K265" s="7">
-        <v>0.20100000000000001</v>
-      </c>
-      <c r="L265" s="7">
-        <v>0.20300000000000001</v>
-      </c>
-      <c r="M265" s="7">
-        <v>0.20699999999999999</v>
-      </c>
-      <c r="N265" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="O265" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="P265" s="7">
-        <v>0.19900000000000001</v>
-      </c>
-      <c r="Q265" s="7">
-        <v>0.2</v>
-      </c>
-      <c r="R265" s="7">
-        <v>0.19900000000000001</v>
-      </c>
-      <c r="S265" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="T265" s="7">
-        <v>0.192</v>
-      </c>
-      <c r="U265" s="7">
-        <v>0.192</v>
+        <v>366</v>
+      </c>
+      <c r="G265" s="4">
+        <v>90.8</v>
+      </c>
+      <c r="H265" s="4">
+        <v>88.8</v>
+      </c>
+      <c r="I265" s="4">
+        <v>86.5</v>
+      </c>
+      <c r="J265" s="4">
+        <v>87</v>
+      </c>
+      <c r="K265" s="4">
+        <v>85</v>
+      </c>
+      <c r="L265" s="4">
+        <v>87.4</v>
+      </c>
+      <c r="M265" s="4">
+        <v>88.7</v>
+      </c>
+      <c r="N265" s="4">
+        <v>84.6</v>
+      </c>
+      <c r="O265" s="4">
+        <v>77.3</v>
+      </c>
+      <c r="P265" s="4">
+        <v>79.7</v>
+      </c>
+      <c r="Q265" s="4">
+        <v>81.900000000000006</v>
+      </c>
+      <c r="R265" s="4">
+        <v>74.8</v>
+      </c>
+      <c r="S265" s="4">
+        <v>77</v>
+      </c>
+      <c r="T265" s="4">
+        <v>77.2</v>
+      </c>
+      <c r="U265" s="4">
+        <v>76.3</v>
       </c>
       <c r="V265" s="3"/>
       <c r="W265" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="266" spans="1:23" ht="36" x14ac:dyDescent="0.25">
@@ -18191,7 +18201,7 @@
         <v>364</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D266" s="2" t="s">
         <v>27</v>
@@ -18202,54 +18212,54 @@
       <c r="F266" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G266" s="4">
-        <v>30.5</v>
-      </c>
-      <c r="H266" s="4">
-        <v>30.5</v>
-      </c>
-      <c r="I266" s="4">
-        <v>30.6</v>
-      </c>
-      <c r="J266" s="4">
-        <v>30.6</v>
-      </c>
-      <c r="K266" s="4">
-        <v>30.7</v>
-      </c>
-      <c r="L266" s="4">
-        <v>30.8</v>
-      </c>
-      <c r="M266" s="4">
-        <v>30.8</v>
-      </c>
-      <c r="N266" s="4">
-        <v>30.9</v>
-      </c>
-      <c r="O266" s="4">
-        <v>30.9</v>
-      </c>
-      <c r="P266" s="4">
-        <v>30.9</v>
-      </c>
-      <c r="Q266" s="4">
-        <v>30.9</v>
-      </c>
-      <c r="R266" s="4">
-        <v>30.9</v>
-      </c>
-      <c r="S266" s="4">
-        <v>31</v>
-      </c>
-      <c r="T266" s="4">
-        <v>31</v>
-      </c>
-      <c r="U266" s="4">
-        <v>31</v>
+      <c r="G266" s="7">
+        <v>0.19600000000000001</v>
+      </c>
+      <c r="H266" s="7">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="I266" s="7">
+        <v>0.20599999999999999</v>
+      </c>
+      <c r="J266" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="K266" s="7">
+        <v>0.20100000000000001</v>
+      </c>
+      <c r="L266" s="7">
+        <v>0.20300000000000001</v>
+      </c>
+      <c r="M266" s="7">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="N266" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="O266" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="P266" s="7">
+        <v>0.19900000000000001</v>
+      </c>
+      <c r="Q266" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="R266" s="7">
+        <v>0.19900000000000001</v>
+      </c>
+      <c r="S266" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="T266" s="7">
+        <v>0.192</v>
+      </c>
+      <c r="U266" s="7">
+        <v>0.192</v>
       </c>
       <c r="V266" s="3"/>
       <c r="W266" s="2" t="s">
-        <v>30</v>
+        <v>369</v>
       </c>
     </row>
     <row r="267" spans="1:23" ht="36" x14ac:dyDescent="0.25">
@@ -18257,10 +18267,10 @@
         <v>363</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D267" s="2" t="s">
         <v>27</v>
@@ -18269,56 +18279,56 @@
         <v>28</v>
       </c>
       <c r="F267" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="G267" s="6">
-        <v>28</v>
-      </c>
-      <c r="H267" s="6">
-        <v>27</v>
-      </c>
-      <c r="I267" s="6">
-        <v>26</v>
-      </c>
-      <c r="J267" s="6">
-        <v>25</v>
-      </c>
-      <c r="K267" s="6">
-        <v>24</v>
-      </c>
-      <c r="L267" s="6">
-        <v>23</v>
-      </c>
-      <c r="M267" s="6">
-        <v>22</v>
-      </c>
-      <c r="N267" s="6">
-        <v>22</v>
-      </c>
-      <c r="O267" s="6">
-        <v>22</v>
-      </c>
-      <c r="P267" s="6">
-        <v>21</v>
-      </c>
-      <c r="Q267" s="6">
-        <v>19</v>
-      </c>
-      <c r="R267" s="6">
-        <v>17</v>
-      </c>
-      <c r="S267" s="6">
-        <v>16</v>
-      </c>
-      <c r="T267" s="6">
-        <v>16</v>
-      </c>
-      <c r="U267" s="6">
-        <v>15</v>
+        <v>36</v>
+      </c>
+      <c r="G267" s="4">
+        <v>30.5</v>
+      </c>
+      <c r="H267" s="4">
+        <v>30.5</v>
+      </c>
+      <c r="I267" s="4">
+        <v>30.6</v>
+      </c>
+      <c r="J267" s="4">
+        <v>30.6</v>
+      </c>
+      <c r="K267" s="4">
+        <v>30.7</v>
+      </c>
+      <c r="L267" s="4">
+        <v>30.8</v>
+      </c>
+      <c r="M267" s="4">
+        <v>30.8</v>
+      </c>
+      <c r="N267" s="4">
+        <v>30.9</v>
+      </c>
+      <c r="O267" s="4">
+        <v>30.9</v>
+      </c>
+      <c r="P267" s="4">
+        <v>30.9</v>
+      </c>
+      <c r="Q267" s="4">
+        <v>30.9</v>
+      </c>
+      <c r="R267" s="4">
+        <v>30.9</v>
+      </c>
+      <c r="S267" s="4">
+        <v>31</v>
+      </c>
+      <c r="T267" s="4">
+        <v>31</v>
+      </c>
+      <c r="U267" s="4">
+        <v>31</v>
       </c>
       <c r="V267" s="3"/>
       <c r="W267" s="2" t="s">
-        <v>99</v>
+        <v>30</v>
       </c>
     </row>
     <row r="268" spans="1:23" ht="36" x14ac:dyDescent="0.25">
@@ -18329,65 +18339,65 @@
         <v>371</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E268" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F268" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G268" s="4">
-        <v>64.7</v>
-      </c>
-      <c r="H268" s="4">
-        <v>65.7</v>
-      </c>
-      <c r="I268" s="4">
-        <v>68.599999999999994</v>
-      </c>
-      <c r="J268" s="4">
-        <v>70.3</v>
-      </c>
-      <c r="K268" s="4">
-        <v>71.5</v>
-      </c>
-      <c r="L268" s="4">
-        <v>72.7</v>
-      </c>
-      <c r="M268" s="4">
-        <v>73.5</v>
-      </c>
-      <c r="N268" s="4">
-        <v>73.599999999999994</v>
-      </c>
-      <c r="O268" s="4">
-        <v>74</v>
-      </c>
-      <c r="P268" s="4">
-        <v>74.5</v>
-      </c>
-      <c r="Q268" s="4">
-        <v>74.900000000000006</v>
-      </c>
-      <c r="R268" s="4">
-        <v>75.2</v>
-      </c>
-      <c r="S268" s="4">
-        <v>75.7</v>
-      </c>
-      <c r="T268" s="4">
-        <v>75.900000000000006</v>
-      </c>
-      <c r="U268" s="4">
-        <v>76.2</v>
+        <v>98</v>
+      </c>
+      <c r="G268" s="6">
+        <v>28</v>
+      </c>
+      <c r="H268" s="6">
+        <v>27</v>
+      </c>
+      <c r="I268" s="6">
+        <v>26</v>
+      </c>
+      <c r="J268" s="6">
+        <v>25</v>
+      </c>
+      <c r="K268" s="6">
+        <v>24</v>
+      </c>
+      <c r="L268" s="6">
+        <v>23</v>
+      </c>
+      <c r="M268" s="6">
+        <v>22</v>
+      </c>
+      <c r="N268" s="6">
+        <v>22</v>
+      </c>
+      <c r="O268" s="6">
+        <v>22</v>
+      </c>
+      <c r="P268" s="6">
+        <v>21</v>
+      </c>
+      <c r="Q268" s="6">
+        <v>19</v>
+      </c>
+      <c r="R268" s="6">
+        <v>17</v>
+      </c>
+      <c r="S268" s="6">
+        <v>16</v>
+      </c>
+      <c r="T268" s="6">
+        <v>16</v>
+      </c>
+      <c r="U268" s="6">
+        <v>15</v>
       </c>
       <c r="V268" s="3"/>
       <c r="W268" s="2" t="s">
-        <v>30</v>
+        <v>99</v>
       </c>
     </row>
     <row r="269" spans="1:23" ht="36" x14ac:dyDescent="0.25">
@@ -18404,55 +18414,55 @@
         <v>35</v>
       </c>
       <c r="E269" s="3" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F269" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G269" s="4">
-        <v>88</v>
+        <v>64.7</v>
       </c>
       <c r="H269" s="4">
-        <v>88.4</v>
+        <v>65.7</v>
       </c>
       <c r="I269" s="4">
-        <v>91.7</v>
+        <v>68.599999999999994</v>
       </c>
       <c r="J269" s="4">
-        <v>93.3</v>
+        <v>70.3</v>
       </c>
       <c r="K269" s="4">
-        <v>93.9</v>
+        <v>71.5</v>
       </c>
       <c r="L269" s="4">
-        <v>94.6</v>
+        <v>72.7</v>
       </c>
       <c r="M269" s="4">
-        <v>94.8</v>
+        <v>73.5</v>
       </c>
       <c r="N269" s="4">
-        <v>94.5</v>
+        <v>73.599999999999994</v>
       </c>
       <c r="O269" s="4">
-        <v>94.6</v>
+        <v>74</v>
       </c>
       <c r="P269" s="4">
-        <v>94.8</v>
+        <v>74.5</v>
       </c>
       <c r="Q269" s="4">
-        <v>94.7</v>
+        <v>74.900000000000006</v>
       </c>
       <c r="R269" s="4">
-        <v>94.6</v>
+        <v>75.2</v>
       </c>
       <c r="S269" s="4">
-        <v>95</v>
+        <v>75.7</v>
       </c>
       <c r="T269" s="4">
-        <v>94.8</v>
+        <v>75.900000000000006</v>
       </c>
       <c r="U269" s="4">
-        <v>94.6</v>
+        <v>76.2</v>
       </c>
       <c r="V269" s="3"/>
       <c r="W269" s="2" t="s">
@@ -18473,55 +18483,55 @@
         <v>35</v>
       </c>
       <c r="E270" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F270" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G270" s="4">
-        <v>28.5</v>
+        <v>88</v>
       </c>
       <c r="H270" s="4">
-        <v>30.6</v>
+        <v>88.4</v>
       </c>
       <c r="I270" s="4">
-        <v>33.1</v>
+        <v>91.7</v>
       </c>
       <c r="J270" s="4">
-        <v>35.299999999999997</v>
+        <v>93.3</v>
       </c>
       <c r="K270" s="4">
-        <v>37.4</v>
+        <v>93.9</v>
       </c>
       <c r="L270" s="4">
-        <v>39.6</v>
+        <v>94.6</v>
       </c>
       <c r="M270" s="4">
-        <v>41.2</v>
+        <v>94.8</v>
       </c>
       <c r="N270" s="4">
-        <v>42</v>
+        <v>94.5</v>
       </c>
       <c r="O270" s="4">
-        <v>42.9</v>
+        <v>94.6</v>
       </c>
       <c r="P270" s="4">
-        <v>44</v>
+        <v>94.8</v>
       </c>
       <c r="Q270" s="4">
-        <v>45.4</v>
+        <v>94.7</v>
       </c>
       <c r="R270" s="4">
-        <v>46.5</v>
+        <v>94.6</v>
       </c>
       <c r="S270" s="4">
-        <v>47.2</v>
+        <v>95</v>
       </c>
       <c r="T270" s="4">
-        <v>48.2</v>
+        <v>94.8</v>
       </c>
       <c r="U270" s="4">
-        <v>49.3</v>
+        <v>94.6</v>
       </c>
       <c r="V270" s="3"/>
       <c r="W270" s="2" t="s">
@@ -18536,76 +18546,76 @@
         <v>371</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E271" s="3" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F271" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G271" s="4">
-        <v>65.7</v>
+        <v>28.5</v>
       </c>
       <c r="H271" s="4">
-        <v>64.8</v>
+        <v>30.6</v>
       </c>
       <c r="I271" s="4">
-        <v>67.400000000000006</v>
+        <v>33.1</v>
       </c>
       <c r="J271" s="4">
-        <v>69.8</v>
+        <v>35.299999999999997</v>
       </c>
       <c r="K271" s="4">
-        <v>70.5</v>
+        <v>37.4</v>
       </c>
       <c r="L271" s="4">
-        <v>70.900000000000006</v>
+        <v>39.6</v>
       </c>
       <c r="M271" s="4">
-        <v>71.400000000000006</v>
+        <v>41.2</v>
       </c>
       <c r="N271" s="4">
-        <v>72.5</v>
+        <v>42</v>
       </c>
       <c r="O271" s="4">
-        <v>73.2</v>
+        <v>42.9</v>
       </c>
       <c r="P271" s="4">
-        <v>73.900000000000006</v>
+        <v>44</v>
       </c>
       <c r="Q271" s="4">
-        <v>73.3</v>
+        <v>45.4</v>
       </c>
       <c r="R271" s="4">
-        <v>72.8</v>
+        <v>46.5</v>
       </c>
       <c r="S271" s="4">
-        <v>76.3</v>
+        <v>47.2</v>
       </c>
       <c r="T271" s="4">
-        <v>78.099999999999994</v>
+        <v>48.2</v>
       </c>
       <c r="U271" s="4">
-        <v>78.599999999999994</v>
+        <v>49.3</v>
       </c>
       <c r="V271" s="3"/>
       <c r="W271" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="272" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
         <v>363</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D272" s="2" t="s">
         <v>27</v>
@@ -18614,52 +18624,52 @@
         <v>28</v>
       </c>
       <c r="F272" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="G272" s="6">
-        <v>70108</v>
-      </c>
-      <c r="H272" s="6">
-        <v>248240</v>
-      </c>
-      <c r="I272" s="6">
-        <v>168221</v>
-      </c>
-      <c r="J272" s="6">
-        <v>72837</v>
-      </c>
-      <c r="K272" s="6">
-        <v>64283</v>
-      </c>
-      <c r="L272" s="6">
-        <v>68694</v>
-      </c>
-      <c r="M272" s="6">
-        <v>60135</v>
-      </c>
-      <c r="N272" s="6">
-        <v>46337</v>
-      </c>
-      <c r="O272" s="6">
-        <v>50289</v>
-      </c>
-      <c r="P272" s="6">
-        <v>104107</v>
-      </c>
-      <c r="Q272" s="6">
-        <v>201963</v>
-      </c>
-      <c r="R272" s="6">
-        <v>84506</v>
-      </c>
-      <c r="S272" s="6">
-        <v>295948</v>
-      </c>
-      <c r="T272" s="6">
-        <v>123796</v>
-      </c>
-      <c r="U272" s="6">
-        <v>104040</v>
+        <v>36</v>
+      </c>
+      <c r="G272" s="4">
+        <v>65.7</v>
+      </c>
+      <c r="H272" s="4">
+        <v>64.8</v>
+      </c>
+      <c r="I272" s="4">
+        <v>67.400000000000006</v>
+      </c>
+      <c r="J272" s="4">
+        <v>69.8</v>
+      </c>
+      <c r="K272" s="4">
+        <v>70.5</v>
+      </c>
+      <c r="L272" s="4">
+        <v>70.900000000000006</v>
+      </c>
+      <c r="M272" s="4">
+        <v>71.400000000000006</v>
+      </c>
+      <c r="N272" s="4">
+        <v>72.5</v>
+      </c>
+      <c r="O272" s="4">
+        <v>73.2</v>
+      </c>
+      <c r="P272" s="4">
+        <v>73.900000000000006</v>
+      </c>
+      <c r="Q272" s="4">
+        <v>73.3</v>
+      </c>
+      <c r="R272" s="4">
+        <v>72.8</v>
+      </c>
+      <c r="S272" s="4">
+        <v>76.3</v>
+      </c>
+      <c r="T272" s="4">
+        <v>78.099999999999994</v>
+      </c>
+      <c r="U272" s="4">
+        <v>78.599999999999994</v>
       </c>
       <c r="V272" s="3"/>
       <c r="W272" s="2" t="s">
@@ -18674,7 +18684,7 @@
         <v>375</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D273" s="2" t="s">
         <v>27</v>
@@ -18683,52 +18693,52 @@
         <v>28</v>
       </c>
       <c r="F273" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G273" s="4">
-        <v>2.9</v>
-      </c>
-      <c r="H273" s="4">
-        <v>3.8</v>
-      </c>
-      <c r="I273" s="4">
-        <v>6</v>
-      </c>
-      <c r="J273" s="4">
-        <v>4.3</v>
-      </c>
-      <c r="K273" s="4">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="L273" s="4">
-        <v>4.2</v>
-      </c>
-      <c r="M273" s="4">
-        <v>3.1</v>
-      </c>
-      <c r="N273" s="4">
-        <v>3</v>
-      </c>
-      <c r="O273" s="4">
-        <v>3.2</v>
-      </c>
-      <c r="P273" s="4">
-        <v>3.4</v>
-      </c>
-      <c r="Q273" s="4">
-        <v>3.2</v>
-      </c>
-      <c r="R273" s="4">
-        <v>4.5</v>
-      </c>
-      <c r="S273" s="4">
-        <v>6.6</v>
-      </c>
-      <c r="T273" s="4">
-        <v>5.8</v>
-      </c>
-      <c r="U273" s="4">
-        <v>4.5</v>
+        <v>377</v>
+      </c>
+      <c r="G273" s="6">
+        <v>70108</v>
+      </c>
+      <c r="H273" s="6">
+        <v>248240</v>
+      </c>
+      <c r="I273" s="6">
+        <v>168221</v>
+      </c>
+      <c r="J273" s="6">
+        <v>72837</v>
+      </c>
+      <c r="K273" s="6">
+        <v>64283</v>
+      </c>
+      <c r="L273" s="6">
+        <v>68694</v>
+      </c>
+      <c r="M273" s="6">
+        <v>60135</v>
+      </c>
+      <c r="N273" s="6">
+        <v>46337</v>
+      </c>
+      <c r="O273" s="6">
+        <v>50289</v>
+      </c>
+      <c r="P273" s="6">
+        <v>104107</v>
+      </c>
+      <c r="Q273" s="6">
+        <v>201963</v>
+      </c>
+      <c r="R273" s="6">
+        <v>84506</v>
+      </c>
+      <c r="S273" s="6">
+        <v>295948</v>
+      </c>
+      <c r="T273" s="6">
+        <v>123796</v>
+      </c>
+      <c r="U273" s="6">
+        <v>104040</v>
       </c>
       <c r="V273" s="3"/>
       <c r="W273" s="2" t="s">
@@ -18737,13 +18747,13 @@
     </row>
     <row r="274" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
-        <v>379</v>
+        <v>363</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D274" s="2" t="s">
         <v>27</v>
@@ -18754,56 +18764,54 @@
       <c r="F274" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G274" s="6">
-        <v>70</v>
-      </c>
-      <c r="H274" s="6">
-        <v>75</v>
-      </c>
-      <c r="I274" s="6">
-        <v>66</v>
-      </c>
-      <c r="J274" s="6">
-        <v>64</v>
-      </c>
-      <c r="K274" s="6">
-        <v>70</v>
-      </c>
-      <c r="L274" s="6">
-        <v>66</v>
-      </c>
-      <c r="M274" s="6">
-        <v>80</v>
-      </c>
-      <c r="N274" s="6">
-        <v>89</v>
-      </c>
-      <c r="O274" s="6">
-        <v>86</v>
-      </c>
-      <c r="P274" s="6">
-        <v>89</v>
-      </c>
-      <c r="Q274" s="6">
-        <v>85</v>
-      </c>
-      <c r="R274" s="6">
-        <v>82</v>
-      </c>
-      <c r="S274" s="6">
-        <v>83</v>
-      </c>
-      <c r="T274" s="6">
-        <v>88</v>
-      </c>
-      <c r="U274" s="6">
-        <v>88</v>
-      </c>
-      <c r="V274" s="6">
-        <v>86</v>
-      </c>
+      <c r="G274" s="4">
+        <v>2.9</v>
+      </c>
+      <c r="H274" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="I274" s="4">
+        <v>6</v>
+      </c>
+      <c r="J274" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="K274" s="4">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="L274" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="M274" s="4">
+        <v>3.1</v>
+      </c>
+      <c r="N274" s="4">
+        <v>3</v>
+      </c>
+      <c r="O274" s="4">
+        <v>3.2</v>
+      </c>
+      <c r="P274" s="4">
+        <v>3.4</v>
+      </c>
+      <c r="Q274" s="4">
+        <v>3.2</v>
+      </c>
+      <c r="R274" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="S274" s="4">
+        <v>6.6</v>
+      </c>
+      <c r="T274" s="4">
+        <v>5.8</v>
+      </c>
+      <c r="U274" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="V274" s="3"/>
       <c r="W274" s="2" t="s">
-        <v>382</v>
+        <v>30</v>
       </c>
     </row>
     <row r="275" spans="1:23" ht="27" x14ac:dyDescent="0.25">
@@ -18814,7 +18822,7 @@
         <v>380</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D275" s="2" t="s">
         <v>27</v>
@@ -18826,37 +18834,53 @@
         <v>36</v>
       </c>
       <c r="G275" s="6">
-        <v>55</v>
-      </c>
-      <c r="H275" s="3"/>
+        <v>70</v>
+      </c>
+      <c r="H275" s="6">
+        <v>75</v>
+      </c>
       <c r="I275" s="6">
-        <v>58</v>
-      </c>
-      <c r="J275" s="3"/>
+        <v>66</v>
+      </c>
+      <c r="J275" s="6">
+        <v>64</v>
+      </c>
       <c r="K275" s="6">
-        <v>60</v>
-      </c>
-      <c r="L275" s="3"/>
+        <v>70</v>
+      </c>
+      <c r="L275" s="6">
+        <v>66</v>
+      </c>
       <c r="M275" s="6">
-        <v>64</v>
-      </c>
-      <c r="N275" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="N275" s="6">
+        <v>89</v>
+      </c>
       <c r="O275" s="6">
-        <v>65</v>
-      </c>
-      <c r="P275" s="3"/>
+        <v>86</v>
+      </c>
+      <c r="P275" s="6">
+        <v>89</v>
+      </c>
       <c r="Q275" s="6">
-        <v>74</v>
-      </c>
-      <c r="R275" s="3"/>
+        <v>85</v>
+      </c>
+      <c r="R275" s="6">
+        <v>82</v>
+      </c>
       <c r="S275" s="6">
-        <v>63</v>
-      </c>
-      <c r="T275" s="3"/>
+        <v>83</v>
+      </c>
+      <c r="T275" s="6">
+        <v>88</v>
+      </c>
       <c r="U275" s="6">
-        <v>71</v>
-      </c>
-      <c r="V275" s="3"/>
+        <v>88</v>
+      </c>
+      <c r="V275" s="6">
+        <v>86</v>
+      </c>
       <c r="W275" s="2" t="s">
         <v>382</v>
       </c>
@@ -18866,10 +18890,10 @@
         <v>379</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D276" s="2" t="s">
         <v>27</v>
@@ -18878,56 +18902,42 @@
         <v>28</v>
       </c>
       <c r="F276" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="G276" s="5">
-        <v>1.02</v>
-      </c>
-      <c r="H276" s="5">
-        <v>0.96</v>
-      </c>
-      <c r="I276" s="5">
-        <v>1</v>
-      </c>
-      <c r="J276" s="5">
-        <v>1.05</v>
-      </c>
-      <c r="K276" s="5">
-        <v>1.06</v>
-      </c>
-      <c r="L276" s="5">
-        <v>0.95</v>
-      </c>
-      <c r="M276" s="5">
-        <v>0.91</v>
-      </c>
-      <c r="N276" s="5">
-        <v>0.81</v>
-      </c>
-      <c r="O276" s="5">
-        <v>0.87</v>
-      </c>
-      <c r="P276" s="5">
-        <v>1.01</v>
-      </c>
-      <c r="Q276" s="5">
-        <v>0.85</v>
-      </c>
-      <c r="R276" s="5">
-        <v>0.83</v>
-      </c>
-      <c r="S276" s="5">
-        <v>0.72</v>
-      </c>
-      <c r="T276" s="5">
-        <v>0.78</v>
-      </c>
-      <c r="U276" s="5">
-        <v>0.69</v>
+        <v>36</v>
+      </c>
+      <c r="G276" s="6">
+        <v>55</v>
+      </c>
+      <c r="H276" s="3"/>
+      <c r="I276" s="6">
+        <v>58</v>
+      </c>
+      <c r="J276" s="3"/>
+      <c r="K276" s="6">
+        <v>60</v>
+      </c>
+      <c r="L276" s="3"/>
+      <c r="M276" s="6">
+        <v>64</v>
+      </c>
+      <c r="N276" s="3"/>
+      <c r="O276" s="6">
+        <v>65</v>
+      </c>
+      <c r="P276" s="3"/>
+      <c r="Q276" s="6">
+        <v>74</v>
+      </c>
+      <c r="R276" s="3"/>
+      <c r="S276" s="6">
+        <v>63</v>
+      </c>
+      <c r="T276" s="3"/>
+      <c r="U276" s="6">
+        <v>71</v>
       </c>
       <c r="V276" s="3"/>
       <c r="W276" s="2" t="s">
-        <v>202</v>
+        <v>382</v>
       </c>
     </row>
     <row r="277" spans="1:23" ht="27" x14ac:dyDescent="0.25">
@@ -18935,10 +18945,10 @@
         <v>379</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D277" s="2" t="s">
         <v>27</v>
@@ -18947,56 +18957,56 @@
         <v>28</v>
       </c>
       <c r="F277" s="3" t="s">
-        <v>36</v>
+        <v>250</v>
       </c>
       <c r="G277" s="5">
-        <v>1.84</v>
+        <v>1.02</v>
       </c>
       <c r="H277" s="5">
-        <v>1.79</v>
+        <v>0.96</v>
       </c>
       <c r="I277" s="5">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J277" s="5">
-        <v>1.79</v>
+        <v>1.05</v>
       </c>
       <c r="K277" s="5">
-        <v>1.86</v>
+        <v>1.06</v>
       </c>
       <c r="L277" s="5">
-        <v>2.21</v>
+        <v>0.95</v>
       </c>
       <c r="M277" s="5">
-        <v>1.99</v>
+        <v>0.91</v>
       </c>
       <c r="N277" s="5">
-        <v>1.88</v>
+        <v>0.81</v>
       </c>
       <c r="O277" s="5">
-        <v>2</v>
+        <v>0.87</v>
       </c>
       <c r="P277" s="5">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="Q277" s="5">
-        <v>2.21</v>
+        <v>0.85</v>
       </c>
       <c r="R277" s="5">
-        <v>2.19</v>
+        <v>0.83</v>
       </c>
       <c r="S277" s="5">
-        <v>2.21</v>
+        <v>0.72</v>
       </c>
       <c r="T277" s="5">
-        <v>3.27</v>
+        <v>0.78</v>
       </c>
       <c r="U277" s="5">
-        <v>4.07</v>
+        <v>0.69</v>
       </c>
       <c r="V277" s="3"/>
       <c r="W277" s="2" t="s">
-        <v>388</v>
+        <v>202</v>
       </c>
     </row>
     <row r="278" spans="1:23" ht="27" x14ac:dyDescent="0.25">
@@ -19004,13 +19014,13 @@
         <v>379</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="E278" s="3" t="s">
         <v>28</v>
@@ -19018,48 +19028,54 @@
       <c r="F278" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G278" s="6">
-        <v>10</v>
-      </c>
-      <c r="H278" s="6">
-        <v>9</v>
-      </c>
-      <c r="I278" s="6">
-        <v>11</v>
-      </c>
-      <c r="J278" s="6">
-        <v>11</v>
-      </c>
-      <c r="K278" s="6">
-        <v>15</v>
-      </c>
-      <c r="L278" s="6">
-        <v>16</v>
-      </c>
-      <c r="M278" s="6">
-        <v>19</v>
-      </c>
-      <c r="N278" s="6">
-        <v>21</v>
-      </c>
-      <c r="O278" s="6">
-        <v>25</v>
-      </c>
-      <c r="P278" s="6">
-        <v>31</v>
-      </c>
-      <c r="Q278" s="6">
-        <v>34</v>
-      </c>
-      <c r="R278" s="6">
-        <v>40</v>
-      </c>
-      <c r="S278" s="3"/>
-      <c r="T278" s="3"/>
-      <c r="U278" s="3"/>
+      <c r="G278" s="5">
+        <v>1.84</v>
+      </c>
+      <c r="H278" s="5">
+        <v>1.79</v>
+      </c>
+      <c r="I278" s="5">
+        <v>1.8</v>
+      </c>
+      <c r="J278" s="5">
+        <v>1.79</v>
+      </c>
+      <c r="K278" s="5">
+        <v>1.86</v>
+      </c>
+      <c r="L278" s="5">
+        <v>2.21</v>
+      </c>
+      <c r="M278" s="5">
+        <v>1.99</v>
+      </c>
+      <c r="N278" s="5">
+        <v>1.88</v>
+      </c>
+      <c r="O278" s="5">
+        <v>2</v>
+      </c>
+      <c r="P278" s="5">
+        <v>1.96</v>
+      </c>
+      <c r="Q278" s="5">
+        <v>2.21</v>
+      </c>
+      <c r="R278" s="5">
+        <v>2.19</v>
+      </c>
+      <c r="S278" s="5">
+        <v>2.21</v>
+      </c>
+      <c r="T278" s="5">
+        <v>3.27</v>
+      </c>
+      <c r="U278" s="5">
+        <v>4.07</v>
+      </c>
       <c r="V278" s="3"/>
       <c r="W278" s="2" t="s">
-        <v>30</v>
+        <v>388</v>
       </c>
     </row>
     <row r="279" spans="1:23" ht="27" x14ac:dyDescent="0.25">
@@ -19076,7 +19092,7 @@
         <v>62</v>
       </c>
       <c r="E279" s="3" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="F279" s="3" t="s">
         <v>36</v>
@@ -19091,13 +19107,13 @@
         <v>11</v>
       </c>
       <c r="J279" s="6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K279" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L279" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M279" s="6">
         <v>19</v>
@@ -19106,16 +19122,16 @@
         <v>21</v>
       </c>
       <c r="O279" s="6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P279" s="6">
         <v>31</v>
       </c>
       <c r="Q279" s="6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R279" s="6">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S279" s="3"/>
       <c r="T279" s="3"/>
@@ -19139,7 +19155,7 @@
         <v>62</v>
       </c>
       <c r="E280" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F280" s="3" t="s">
         <v>36</v>
@@ -19151,16 +19167,16 @@
         <v>9</v>
       </c>
       <c r="I280" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J280" s="6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K280" s="6">
+        <v>14</v>
+      </c>
+      <c r="L280" s="6">
         <v>15</v>
-      </c>
-      <c r="L280" s="6">
-        <v>16</v>
       </c>
       <c r="M280" s="6">
         <v>19</v>
@@ -19169,16 +19185,16 @@
         <v>21</v>
       </c>
       <c r="O280" s="6">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="P280" s="6">
+        <v>31</v>
+      </c>
+      <c r="Q280" s="6">
         <v>32</v>
       </c>
-      <c r="Q280" s="6">
-        <v>35</v>
-      </c>
       <c r="R280" s="6">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="S280" s="3"/>
       <c r="T280" s="3"/>
@@ -19199,49 +19215,49 @@
         <v>390</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="E281" s="3" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="F281" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G281" s="6">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H281" s="6">
+        <v>9</v>
+      </c>
+      <c r="I281" s="6">
+        <v>10</v>
+      </c>
+      <c r="J281" s="6">
         <v>11</v>
       </c>
-      <c r="I281" s="6">
-        <v>13</v>
-      </c>
-      <c r="J281" s="6">
+      <c r="K281" s="6">
         <v>15</v>
       </c>
-      <c r="K281" s="6">
-        <v>18</v>
-      </c>
       <c r="L281" s="6">
+        <v>16</v>
+      </c>
+      <c r="M281" s="6">
         <v>19</v>
       </c>
-      <c r="M281" s="6">
-        <v>23</v>
-      </c>
       <c r="N281" s="6">
+        <v>21</v>
+      </c>
+      <c r="O281" s="6">
         <v>26</v>
       </c>
-      <c r="O281" s="6">
-        <v>30</v>
-      </c>
       <c r="P281" s="6">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="Q281" s="6">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="R281" s="6">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="S281" s="3"/>
       <c r="T281" s="3"/>
@@ -19265,46 +19281,46 @@
         <v>35</v>
       </c>
       <c r="E282" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F282" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G282" s="6">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H282" s="6">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I282" s="6">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J282" s="6">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="K282" s="6">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="L282" s="6">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="M282" s="6">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="N282" s="6">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="O282" s="6">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="P282" s="6">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="Q282" s="6">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="R282" s="6">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="S282" s="3"/>
       <c r="T282" s="3"/>
@@ -19325,49 +19341,49 @@
         <v>390</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="E283" s="3" t="s">
-        <v>139</v>
+        <v>39</v>
       </c>
       <c r="F283" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G283" s="6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H283" s="6">
+        <v>5</v>
+      </c>
+      <c r="I283" s="6">
         <v>6</v>
       </c>
-      <c r="I283" s="6">
-        <v>8</v>
-      </c>
       <c r="J283" s="6">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K283" s="6">
         <v>9</v>
       </c>
       <c r="L283" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M283" s="6">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="N283" s="6">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O283" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P283" s="6">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Q283" s="6">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="R283" s="6">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="S283" s="3"/>
       <c r="T283" s="3"/>
@@ -19391,46 +19407,46 @@
         <v>80</v>
       </c>
       <c r="E284" s="3" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="F284" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G284" s="6">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H284" s="6">
+        <v>6</v>
+      </c>
+      <c r="I284" s="6">
+        <v>8</v>
+      </c>
+      <c r="J284" s="6">
+        <v>9</v>
+      </c>
+      <c r="K284" s="6">
+        <v>9</v>
+      </c>
+      <c r="L284" s="6">
+        <v>8</v>
+      </c>
+      <c r="M284" s="6">
+        <v>9</v>
+      </c>
+      <c r="N284" s="6">
+        <v>11</v>
+      </c>
+      <c r="O284" s="6">
         <v>16</v>
       </c>
-      <c r="I284" s="6">
-        <v>19</v>
-      </c>
-      <c r="J284" s="6">
-        <v>20</v>
-      </c>
-      <c r="K284" s="6">
-        <v>28</v>
-      </c>
-      <c r="L284" s="6">
-        <v>28</v>
-      </c>
-      <c r="M284" s="6">
-        <v>32</v>
-      </c>
-      <c r="N284" s="6">
-        <v>35</v>
-      </c>
-      <c r="O284" s="6">
-        <v>39</v>
-      </c>
       <c r="P284" s="6">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="Q284" s="6">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="R284" s="6">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="S284" s="3"/>
       <c r="T284" s="3"/>
@@ -19454,46 +19470,46 @@
         <v>80</v>
       </c>
       <c r="E285" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F285" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G285" s="6">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H285" s="6">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I285" s="6">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J285" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K285" s="6">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="L285" s="6">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M285" s="6">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="N285" s="6">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="O285" s="6">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="P285" s="6">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q285" s="6">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="R285" s="6">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="S285" s="3"/>
       <c r="T285" s="3"/>
@@ -19517,46 +19533,46 @@
         <v>80</v>
       </c>
       <c r="E286" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F286" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G286" s="6">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H286" s="6">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I286" s="6">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="J286" s="6">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="K286" s="6">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="L286" s="6">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="M286" s="6">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="N286" s="6">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="O286" s="6">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="P286" s="6">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="Q286" s="6">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="R286" s="6">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="S286" s="3"/>
       <c r="T286" s="3"/>
@@ -19580,46 +19596,46 @@
         <v>80</v>
       </c>
       <c r="E287" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F287" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G287" s="6">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H287" s="6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I287" s="6">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J287" s="6">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K287" s="6">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="L287" s="6">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M287" s="6">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="N287" s="6">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="O287" s="6">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="P287" s="6">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="Q287" s="6">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R287" s="6">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="S287" s="3"/>
       <c r="T287" s="3"/>
@@ -19643,46 +19659,46 @@
         <v>80</v>
       </c>
       <c r="E288" s="3" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="F288" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G288" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H288" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I288" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J288" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K288" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L288" s="6">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M288" s="6">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="N288" s="6">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="O288" s="6">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="P288" s="6">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="Q288" s="6">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="R288" s="6">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="S288" s="3"/>
       <c r="T288" s="3"/>
@@ -19703,49 +19719,49 @@
         <v>390</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>141</v>
+        <v>80</v>
       </c>
       <c r="E289" s="3" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="F289" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G289" s="6">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="H289" s="6">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="I289" s="6">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="J289" s="6">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="K289" s="6">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="L289" s="6">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="M289" s="6">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="N289" s="6">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="O289" s="6">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="P289" s="6">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="Q289" s="6">
-        <v>62</v>
+        <v>9</v>
       </c>
       <c r="R289" s="6">
-        <v>71</v>
+        <v>11</v>
       </c>
       <c r="S289" s="3"/>
       <c r="T289" s="3"/>
@@ -19769,46 +19785,46 @@
         <v>141</v>
       </c>
       <c r="E290" s="3" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="F290" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G290" s="6">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="H290" s="6">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="I290" s="6">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="J290" s="6">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="K290" s="6">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="L290" s="6">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="M290" s="6">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="N290" s="6">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="O290" s="6">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="P290" s="6">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="Q290" s="6">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="R290" s="6">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="S290" s="3"/>
       <c r="T290" s="3"/>
@@ -19832,46 +19848,46 @@
         <v>141</v>
       </c>
       <c r="E291" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F291" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G291" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H291" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I291" s="6">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J291" s="6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K291" s="6">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L291" s="6">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="M291" s="6">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="N291" s="6">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="O291" s="6">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="P291" s="6">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="Q291" s="6">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="R291" s="6">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="S291" s="3"/>
       <c r="T291" s="3"/>
@@ -19892,49 +19908,49 @@
         <v>390</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E292" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F292" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G292" s="6">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H292" s="6">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I292" s="6">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="J292" s="6">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="K292" s="6">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="L292" s="6">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="M292" s="6">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="N292" s="6">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="O292" s="6">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="P292" s="6">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="Q292" s="6">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="R292" s="6">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="S292" s="3"/>
       <c r="T292" s="3"/>
@@ -19958,46 +19974,46 @@
         <v>144</v>
       </c>
       <c r="E293" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F293" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G293" s="6">
+        <v>14</v>
+      </c>
+      <c r="H293" s="6">
+        <v>13</v>
+      </c>
+      <c r="I293" s="6">
         <v>15</v>
       </c>
-      <c r="H293" s="6">
-        <v>14</v>
-      </c>
-      <c r="I293" s="6">
-        <v>16</v>
-      </c>
       <c r="J293" s="6">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K293" s="6">
+        <v>21</v>
+      </c>
+      <c r="L293" s="6">
         <v>23</v>
       </c>
-      <c r="L293" s="6">
+      <c r="M293" s="6">
         <v>25</v>
       </c>
-      <c r="M293" s="6">
-        <v>27</v>
-      </c>
       <c r="N293" s="6">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O293" s="6">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P293" s="6">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q293" s="6">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="R293" s="6">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="S293" s="3"/>
       <c r="T293" s="3"/>
@@ -20021,46 +20037,46 @@
         <v>144</v>
       </c>
       <c r="E294" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F294" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G294" s="6">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H294" s="6">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I294" s="6">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J294" s="6">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="K294" s="6">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="L294" s="6">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="M294" s="6">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="N294" s="6">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="O294" s="6">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="P294" s="6">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="Q294" s="6">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="R294" s="6">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="S294" s="3"/>
       <c r="T294" s="3"/>
@@ -20084,46 +20100,46 @@
         <v>144</v>
       </c>
       <c r="E295" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F295" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G295" s="6">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H295" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I295" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J295" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K295" s="6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L295" s="6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M295" s="6">
         <v>7</v>
       </c>
       <c r="N295" s="6">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O295" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P295" s="6">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="Q295" s="6">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="R295" s="6">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="S295" s="3"/>
       <c r="T295" s="3"/>
@@ -20138,81 +20154,73 @@
         <v>379</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>27</v>
+        <v>144</v>
       </c>
       <c r="E296" s="3" t="s">
-        <v>28</v>
+        <v>148</v>
       </c>
       <c r="F296" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G296" s="4">
-        <v>5.7</v>
-      </c>
-      <c r="H296" s="4">
-        <v>6</v>
-      </c>
-      <c r="I296" s="4">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="J296" s="4">
-        <v>4.3</v>
-      </c>
-      <c r="K296" s="4">
-        <v>4.7</v>
-      </c>
-      <c r="L296" s="4">
-        <v>4.5</v>
-      </c>
-      <c r="M296" s="4">
-        <v>3.3</v>
-      </c>
-      <c r="N296" s="4">
-        <v>3.8</v>
-      </c>
-      <c r="O296" s="4">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="P296" s="4">
-        <v>4.3</v>
-      </c>
-      <c r="Q296" s="4">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="R296" s="4">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="S296" s="4">
-        <v>3.8</v>
-      </c>
-      <c r="T296" s="4">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="U296" s="4">
-        <v>4.8</v>
-      </c>
-      <c r="V296" s="4">
-        <v>5.2</v>
-      </c>
+      <c r="G296" s="6">
+        <v>4</v>
+      </c>
+      <c r="H296" s="6">
+        <v>3</v>
+      </c>
+      <c r="I296" s="6">
+        <v>5</v>
+      </c>
+      <c r="J296" s="6">
+        <v>4</v>
+      </c>
+      <c r="K296" s="6">
+        <v>5</v>
+      </c>
+      <c r="L296" s="6">
+        <v>5</v>
+      </c>
+      <c r="M296" s="6">
+        <v>7</v>
+      </c>
+      <c r="N296" s="6">
+        <v>8</v>
+      </c>
+      <c r="O296" s="6">
+        <v>9</v>
+      </c>
+      <c r="P296" s="6">
+        <v>12</v>
+      </c>
+      <c r="Q296" s="6">
+        <v>14</v>
+      </c>
+      <c r="R296" s="6">
+        <v>17</v>
+      </c>
+      <c r="S296" s="3"/>
+      <c r="T296" s="3"/>
+      <c r="U296" s="3"/>
+      <c r="V296" s="3"/>
       <c r="W296" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="297" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
-        <v>393</v>
+        <v>379</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D297" s="2" t="s">
         <v>27</v>
@@ -20221,56 +20229,58 @@
         <v>28</v>
       </c>
       <c r="F297" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="G297" s="5">
-        <v>377.75</v>
-      </c>
-      <c r="H297" s="5">
-        <v>417.47</v>
-      </c>
-      <c r="I297" s="5">
-        <v>421.06</v>
-      </c>
-      <c r="J297" s="5">
-        <v>487.12</v>
-      </c>
-      <c r="K297" s="5">
-        <v>451.84</v>
-      </c>
-      <c r="L297" s="5">
-        <v>440.89</v>
-      </c>
-      <c r="M297" s="5">
-        <v>662.95</v>
-      </c>
-      <c r="N297" s="5">
-        <v>679.46</v>
-      </c>
-      <c r="O297" s="5">
-        <v>766.04</v>
-      </c>
-      <c r="P297" s="5">
-        <v>776.56</v>
-      </c>
-      <c r="Q297" s="5">
-        <v>829.27</v>
-      </c>
-      <c r="R297" s="5">
-        <v>983.51</v>
-      </c>
-      <c r="S297" s="5">
-        <v>3494.39</v>
-      </c>
-      <c r="T297" s="5">
-        <v>2580.38</v>
-      </c>
-      <c r="U297" s="5">
-        <v>1840.15</v>
-      </c>
-      <c r="V297" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="G297" s="4">
+        <v>5.7</v>
+      </c>
+      <c r="H297" s="4">
+        <v>6</v>
+      </c>
+      <c r="I297" s="4">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="J297" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="K297" s="4">
+        <v>4.7</v>
+      </c>
+      <c r="L297" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="M297" s="4">
+        <v>3.3</v>
+      </c>
+      <c r="N297" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="O297" s="4">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="P297" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="Q297" s="4">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="R297" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="S297" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="T297" s="4">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="U297" s="4">
+        <v>4.8</v>
+      </c>
+      <c r="V297" s="4">
+        <v>5.2</v>
+      </c>
       <c r="W297" s="2" t="s">
-        <v>397</v>
+        <v>30</v>
       </c>
     </row>
     <row r="298" spans="1:23" ht="36" x14ac:dyDescent="0.25">
@@ -20278,10 +20288,10 @@
         <v>393</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="D298" s="2" t="s">
         <v>27</v>
@@ -20293,64 +20303,64 @@
         <v>396</v>
       </c>
       <c r="G298" s="5">
-        <v>96.04</v>
+        <v>377.75</v>
       </c>
       <c r="H298" s="5">
-        <v>90.68</v>
+        <v>417.47</v>
       </c>
       <c r="I298" s="5">
-        <v>111.55</v>
+        <v>421.06</v>
       </c>
       <c r="J298" s="5">
-        <v>127.11</v>
+        <v>487.12</v>
       </c>
       <c r="K298" s="5">
-        <v>82.28</v>
+        <v>451.84</v>
       </c>
       <c r="L298" s="5">
-        <v>100.19</v>
+        <v>440.89</v>
       </c>
       <c r="M298" s="5">
-        <v>148.99</v>
+        <v>662.95</v>
       </c>
       <c r="N298" s="5">
-        <v>222.11</v>
+        <v>679.46</v>
       </c>
       <c r="O298" s="5">
-        <v>244.93</v>
+        <v>766.04</v>
       </c>
       <c r="P298" s="5">
-        <v>223.31</v>
+        <v>776.56</v>
       </c>
       <c r="Q298" s="5">
-        <v>225.08</v>
+        <v>829.27</v>
       </c>
       <c r="R298" s="5">
-        <v>296.20999999999998</v>
+        <v>983.51</v>
       </c>
       <c r="S298" s="5">
-        <v>2661.32</v>
+        <v>3494.39</v>
       </c>
       <c r="T298" s="5">
-        <v>1701.94</v>
+        <v>2580.38</v>
       </c>
       <c r="U298" s="5">
-        <v>705.25</v>
+        <v>1840.15</v>
       </c>
       <c r="V298" s="3"/>
       <c r="W298" s="2" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="299" spans="1:23" ht="72" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
         <v>393</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D299" s="2" t="s">
         <v>27</v>
@@ -20359,67 +20369,67 @@
         <v>28</v>
       </c>
       <c r="F299" s="3" t="s">
-        <v>36</v>
+        <v>396</v>
       </c>
       <c r="G299" s="5">
-        <v>0.08</v>
+        <v>96.04</v>
       </c>
       <c r="H299" s="5">
-        <v>0.08</v>
+        <v>90.68</v>
       </c>
       <c r="I299" s="5">
-        <v>0.09</v>
+        <v>111.55</v>
       </c>
       <c r="J299" s="5">
-        <v>0.1</v>
+        <v>127.11</v>
       </c>
       <c r="K299" s="5">
-        <v>0.09</v>
+        <v>82.28</v>
       </c>
       <c r="L299" s="5">
-        <v>0.1</v>
+        <v>100.19</v>
       </c>
       <c r="M299" s="5">
-        <v>0.15</v>
+        <v>148.99</v>
       </c>
       <c r="N299" s="5">
-        <v>0.13</v>
+        <v>222.11</v>
       </c>
       <c r="O299" s="5">
-        <v>0.14000000000000001</v>
+        <v>244.93</v>
       </c>
       <c r="P299" s="5">
-        <v>0.14000000000000001</v>
+        <v>223.31</v>
       </c>
       <c r="Q299" s="5">
-        <v>0.14000000000000001</v>
+        <v>225.08</v>
       </c>
       <c r="R299" s="5">
-        <v>0.15</v>
+        <v>296.20999999999998</v>
       </c>
       <c r="S299" s="5">
-        <v>0.53</v>
+        <v>2661.32</v>
       </c>
       <c r="T299" s="5">
-        <v>0.33</v>
+        <v>1701.94</v>
       </c>
       <c r="U299" s="5">
-        <v>0.21</v>
+        <v>705.25</v>
       </c>
       <c r="V299" s="3"/>
       <c r="W299" s="2" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="300" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:23" ht="72" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
         <v>393</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D300" s="2" t="s">
         <v>27</v>
@@ -20428,52 +20438,56 @@
         <v>28</v>
       </c>
       <c r="F300" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="G300" s="3"/>
-      <c r="H300" s="3"/>
-      <c r="I300" s="3"/>
-      <c r="J300" s="7">
-        <v>2.2850000000000001</v>
-      </c>
-      <c r="K300" s="7">
-        <v>1.1160000000000001</v>
-      </c>
-      <c r="L300" s="7">
-        <v>1.55</v>
-      </c>
-      <c r="M300" s="7">
-        <v>3.7469999999999999</v>
-      </c>
-      <c r="N300" s="7">
-        <v>3.8530000000000002</v>
-      </c>
-      <c r="O300" s="7">
-        <v>3.367</v>
-      </c>
-      <c r="P300" s="7">
-        <v>6.8940000000000001</v>
-      </c>
-      <c r="Q300" s="7">
-        <v>4.077</v>
-      </c>
-      <c r="R300" s="7">
-        <v>4.49</v>
-      </c>
-      <c r="S300" s="7">
-        <v>11.999000000000001</v>
-      </c>
-      <c r="T300" s="7">
-        <v>16.606000000000002</v>
-      </c>
-      <c r="U300" s="7">
-        <v>20.382000000000001</v>
-      </c>
-      <c r="V300" s="7">
-        <v>5.3920000000000003</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G300" s="5">
+        <v>0.08</v>
+      </c>
+      <c r="H300" s="5">
+        <v>0.08</v>
+      </c>
+      <c r="I300" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="J300" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="K300" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="L300" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="M300" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="N300" s="5">
+        <v>0.13</v>
+      </c>
+      <c r="O300" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="P300" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="Q300" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="R300" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="S300" s="5">
+        <v>0.53</v>
+      </c>
+      <c r="T300" s="5">
+        <v>0.33</v>
+      </c>
+      <c r="U300" s="5">
+        <v>0.21</v>
+      </c>
+      <c r="V300" s="3"/>
       <c r="W300" s="2" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
     </row>
     <row r="301" spans="1:23" ht="27" x14ac:dyDescent="0.25">
@@ -20484,7 +20498,7 @@
         <v>402</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D301" s="2" t="s">
         <v>27</v>
@@ -20498,45 +20512,47 @@
       <c r="G301" s="3"/>
       <c r="H301" s="3"/>
       <c r="I301" s="3"/>
-      <c r="J301" s="5">
-        <v>8.07</v>
-      </c>
-      <c r="K301" s="5">
-        <v>3.54</v>
-      </c>
-      <c r="L301" s="5">
-        <v>2.98</v>
-      </c>
-      <c r="M301" s="5">
-        <v>2.44</v>
-      </c>
-      <c r="N301" s="5">
-        <v>2.25</v>
-      </c>
-      <c r="O301" s="5">
-        <v>63.36</v>
-      </c>
-      <c r="P301" s="5">
-        <v>7.61</v>
-      </c>
-      <c r="Q301" s="5">
-        <v>6.64</v>
-      </c>
-      <c r="R301" s="5">
-        <v>3.65</v>
-      </c>
-      <c r="S301" s="5">
-        <v>9.59</v>
-      </c>
-      <c r="T301" s="5">
-        <v>4.2699999999999996</v>
-      </c>
-      <c r="U301" s="5">
-        <v>8.32</v>
-      </c>
-      <c r="V301" s="3"/>
+      <c r="J301" s="7">
+        <v>2.2850000000000001</v>
+      </c>
+      <c r="K301" s="7">
+        <v>1.1160000000000001</v>
+      </c>
+      <c r="L301" s="7">
+        <v>1.55</v>
+      </c>
+      <c r="M301" s="7">
+        <v>3.7469999999999999</v>
+      </c>
+      <c r="N301" s="7">
+        <v>3.8530000000000002</v>
+      </c>
+      <c r="O301" s="7">
+        <v>3.367</v>
+      </c>
+      <c r="P301" s="7">
+        <v>6.8940000000000001</v>
+      </c>
+      <c r="Q301" s="7">
+        <v>4.077</v>
+      </c>
+      <c r="R301" s="7">
+        <v>4.49</v>
+      </c>
+      <c r="S301" s="7">
+        <v>11.999000000000001</v>
+      </c>
+      <c r="T301" s="7">
+        <v>16.606000000000002</v>
+      </c>
+      <c r="U301" s="7">
+        <v>20.382000000000001</v>
+      </c>
+      <c r="V301" s="7">
+        <v>5.3920000000000003</v>
+      </c>
       <c r="W301" s="2" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
     </row>
     <row r="302" spans="1:23" ht="27" x14ac:dyDescent="0.25">
@@ -20544,10 +20560,10 @@
         <v>393</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D302" s="2" t="s">
         <v>27</v>
@@ -20556,44 +20572,50 @@
         <v>28</v>
       </c>
       <c r="F302" s="3" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="G302" s="3"/>
       <c r="H302" s="3"/>
       <c r="I302" s="3"/>
-      <c r="J302" s="3"/>
-      <c r="K302" s="6">
-        <v>1</v>
-      </c>
-      <c r="L302" s="6">
-        <v>1</v>
-      </c>
-      <c r="M302" s="6">
-        <v>8</v>
-      </c>
-      <c r="N302" s="6">
-        <v>2</v>
-      </c>
-      <c r="O302" s="3"/>
-      <c r="P302" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q302" s="6">
-        <v>2</v>
-      </c>
-      <c r="R302" s="3"/>
-      <c r="S302" s="3"/>
-      <c r="T302" s="6">
-        <v>8</v>
-      </c>
-      <c r="U302" s="6">
-        <v>7</v>
-      </c>
-      <c r="V302" s="6">
-        <v>2</v>
-      </c>
+      <c r="J302" s="5">
+        <v>8.07</v>
+      </c>
+      <c r="K302" s="5">
+        <v>3.54</v>
+      </c>
+      <c r="L302" s="5">
+        <v>2.98</v>
+      </c>
+      <c r="M302" s="5">
+        <v>2.44</v>
+      </c>
+      <c r="N302" s="5">
+        <v>2.25</v>
+      </c>
+      <c r="O302" s="5">
+        <v>63.36</v>
+      </c>
+      <c r="P302" s="5">
+        <v>7.61</v>
+      </c>
+      <c r="Q302" s="5">
+        <v>6.64</v>
+      </c>
+      <c r="R302" s="5">
+        <v>3.65</v>
+      </c>
+      <c r="S302" s="5">
+        <v>9.59</v>
+      </c>
+      <c r="T302" s="5">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="U302" s="5">
+        <v>8.32</v>
+      </c>
+      <c r="V302" s="3"/>
       <c r="W302" s="2" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
     </row>
     <row r="303" spans="1:23" ht="27" x14ac:dyDescent="0.25">
@@ -20601,10 +20623,10 @@
         <v>393</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="D303" s="2" t="s">
         <v>27</v>
@@ -20617,12 +20639,8 @@
       </c>
       <c r="G303" s="3"/>
       <c r="H303" s="3"/>
-      <c r="I303" s="6">
-        <v>2</v>
-      </c>
-      <c r="J303" s="6">
-        <v>2</v>
-      </c>
+      <c r="I303" s="3"/>
+      <c r="J303" s="3"/>
       <c r="K303" s="6">
         <v>1</v>
       </c>
@@ -20630,31 +20648,25 @@
         <v>1</v>
       </c>
       <c r="M303" s="6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N303" s="6">
-        <v>1</v>
-      </c>
-      <c r="O303" s="6">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="O303" s="3"/>
       <c r="P303" s="6">
         <v>1</v>
       </c>
       <c r="Q303" s="6">
-        <v>4</v>
-      </c>
-      <c r="R303" s="6">
-        <v>1</v>
-      </c>
-      <c r="S303" s="6">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="R303" s="3"/>
+      <c r="S303" s="3"/>
       <c r="T303" s="6">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U303" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V303" s="6">
         <v>2</v>
@@ -20668,10 +20680,10 @@
         <v>393</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D304" s="2" t="s">
         <v>27</v>
@@ -20680,61 +20692,65 @@
         <v>28</v>
       </c>
       <c r="F304" s="3" t="s">
-        <v>32</v>
+        <v>408</v>
       </c>
       <c r="G304" s="3"/>
       <c r="H304" s="3"/>
-      <c r="I304" s="3"/>
-      <c r="J304" s="3"/>
+      <c r="I304" s="6">
+        <v>2</v>
+      </c>
+      <c r="J304" s="6">
+        <v>2</v>
+      </c>
       <c r="K304" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L304" s="6">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="M304" s="6">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="N304" s="6">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="O304" s="6">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="P304" s="6">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="Q304" s="6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="R304" s="6">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="S304" s="6">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="T304" s="6">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="U304" s="6">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="V304" s="6">
-        <v>69</v>
+        <v>2</v>
       </c>
       <c r="W304" s="2" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="305" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
         <v>393</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D305" s="2" t="s">
         <v>27</v>
@@ -20749,47 +20765,112 @@
       <c r="H305" s="3"/>
       <c r="I305" s="3"/>
       <c r="J305" s="3"/>
-      <c r="K305" s="3"/>
-      <c r="L305" s="3"/>
-      <c r="M305" s="3"/>
-      <c r="N305" s="3"/>
-      <c r="O305" s="3"/>
-      <c r="P305" s="3"/>
-      <c r="Q305" s="3"/>
-      <c r="R305" s="3"/>
-      <c r="S305" s="3"/>
+      <c r="K305" s="6">
+        <v>5</v>
+      </c>
+      <c r="L305" s="6">
+        <v>13</v>
+      </c>
+      <c r="M305" s="6">
+        <v>19</v>
+      </c>
+      <c r="N305" s="6">
+        <v>18</v>
+      </c>
+      <c r="O305" s="6">
+        <v>15</v>
+      </c>
+      <c r="P305" s="6">
+        <v>15</v>
+      </c>
+      <c r="Q305" s="6">
+        <v>8</v>
+      </c>
+      <c r="R305" s="6">
+        <v>28</v>
+      </c>
+      <c r="S305" s="6">
+        <v>53</v>
+      </c>
       <c r="T305" s="6">
+        <v>65</v>
+      </c>
+      <c r="U305" s="6">
+        <v>70</v>
+      </c>
+      <c r="V305" s="6">
+        <v>69</v>
+      </c>
+      <c r="W305" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="306" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+      <c r="A306" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B306" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="C306" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="D306" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E306" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F306" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G306" s="3"/>
+      <c r="H306" s="3"/>
+      <c r="I306" s="3"/>
+      <c r="J306" s="3"/>
+      <c r="K306" s="3"/>
+      <c r="L306" s="3"/>
+      <c r="M306" s="3"/>
+      <c r="N306" s="3"/>
+      <c r="O306" s="3"/>
+      <c r="P306" s="3"/>
+      <c r="Q306" s="3"/>
+      <c r="R306" s="3"/>
+      <c r="S306" s="3"/>
+      <c r="T306" s="6">
         <v>114</v>
       </c>
-      <c r="U305" s="6">
+      <c r="U306" s="6">
         <v>61</v>
       </c>
-      <c r="V305" s="6">
+      <c r="V306" s="6">
         <v>97</v>
       </c>
-      <c r="W305" s="2" t="s">
+      <c r="W306" s="2" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="306" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="307" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A307" s="10" t="s">
+    <row r="307" spans="1:23" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A309" s="10" t="s">
         <v>417</v>
       </c>
-      <c r="B307" s="8"/>
-    </row>
+      <c r="B309" s="8"/>
+    </row>
+    <row r="310" spans="1:23" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <autoFilter ref="A3:C3" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A307:B307"/>
+    <mergeCell ref="A309:B309"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.39370078740157499" right="0.39370078740157499" top="0.39370078740157499" bottom="0.39370078740157499" header="0.39370078740157499" footer="0.39370078740157499"/>
-  <pageSetup paperSize="9" scale="58" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="57" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId3"/>
 </worksheet>

--- a/assets/excel/en/national_sdg_indicators.xlsx
+++ b/assets/excel/en/national_sdg_indicators.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dregerj\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CA1097A-0CA5-4189-81F6-E370B3FC423A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07996D36-05AC-4A7F-8C3C-9DEF7472F8D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SDGs_1-17" sheetId="1" r:id="rId1"/>
@@ -1303,7 +1303,7 @@
     <t>The Ministry of Economic Development and Technology / The Chancellery of the  Prime Minister</t>
   </si>
   <si>
-    <t>Last update: 23-07-2026, 08:10</t>
+    <t>Last update: 23-07-2026, 12:34</t>
   </si>
 </sst>
 </file>
@@ -7836,52 +7836,52 @@
         <v>34</v>
       </c>
       <c r="G100" s="4">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H100" s="4">
-        <v>23.4</v>
+        <v>11.7</v>
       </c>
       <c r="I100" s="4">
-        <v>24.2</v>
+        <v>12.1</v>
       </c>
       <c r="J100" s="4">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="K100" s="4">
-        <v>24.4</v>
+        <v>12.2</v>
       </c>
       <c r="L100" s="4">
-        <v>22.4</v>
+        <v>11.2</v>
       </c>
       <c r="M100" s="4">
-        <v>21.6</v>
+        <v>10.8</v>
       </c>
       <c r="N100" s="4">
-        <v>19.399999999999999</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="O100" s="4">
-        <v>17.600000000000001</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="P100" s="4">
-        <v>15.8</v>
+        <v>7.9</v>
       </c>
       <c r="Q100" s="4">
-        <v>17.2</v>
+        <v>8.6</v>
       </c>
       <c r="R100" s="4">
-        <v>22.4</v>
+        <v>11.2</v>
       </c>
       <c r="S100" s="4">
-        <v>16.2</v>
+        <v>8.1</v>
       </c>
       <c r="T100" s="4">
-        <v>13.8</v>
+        <v>6.9</v>
       </c>
       <c r="U100" s="4">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="V100" s="4">
-        <v>14.2</v>
+        <v>7.1</v>
       </c>
       <c r="W100" s="2" t="s">
         <v>30</v>
@@ -7901,58 +7901,58 @@
         <v>66</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G101" s="4">
-        <v>22</v>
+        <v>10.9</v>
       </c>
       <c r="H101" s="4">
-        <v>23.5</v>
+        <v>11.7</v>
       </c>
       <c r="I101" s="4">
-        <v>24.2</v>
+        <v>12.2</v>
       </c>
       <c r="J101" s="4">
-        <v>25</v>
+        <v>12.4</v>
       </c>
       <c r="K101" s="4">
-        <v>24.4</v>
+        <v>12</v>
       </c>
       <c r="L101" s="4">
-        <v>22.4</v>
+        <v>10.9</v>
       </c>
       <c r="M101" s="4">
-        <v>21.6</v>
+        <v>11.2</v>
       </c>
       <c r="N101" s="4">
-        <v>19.5</v>
+        <v>10.7</v>
       </c>
       <c r="O101" s="4">
-        <v>17.5</v>
+        <v>10.1</v>
       </c>
       <c r="P101" s="4">
-        <v>15.9</v>
+        <v>9.1</v>
       </c>
       <c r="Q101" s="4">
-        <v>17.2</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="R101" s="4">
-        <v>22.4</v>
+        <v>11.8</v>
       </c>
       <c r="S101" s="4">
-        <v>16.100000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="T101" s="4">
-        <v>13.8</v>
+        <v>6.7</v>
       </c>
       <c r="U101" s="4">
-        <v>13.9</v>
+        <v>6.9</v>
       </c>
       <c r="V101" s="4">
-        <v>14.3</v>
+        <v>7.6</v>
       </c>
       <c r="W101" s="2" t="s">
         <v>30</v>
@@ -7972,58 +7972,58 @@
         <v>66</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G102" s="4">
-        <v>22</v>
+        <v>11.1</v>
       </c>
       <c r="H102" s="4">
-        <v>23.5</v>
+        <v>11.8</v>
       </c>
       <c r="I102" s="4">
-        <v>24.2</v>
+        <v>12</v>
       </c>
       <c r="J102" s="4">
-        <v>25</v>
+        <v>12.6</v>
       </c>
       <c r="K102" s="4">
-        <v>24.4</v>
+        <v>12.4</v>
       </c>
       <c r="L102" s="4">
-        <v>22.4</v>
+        <v>11.5</v>
       </c>
       <c r="M102" s="4">
-        <v>21.6</v>
+        <v>10.4</v>
       </c>
       <c r="N102" s="4">
-        <v>19.5</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="O102" s="4">
-        <v>17.5</v>
+        <v>7.4</v>
       </c>
       <c r="P102" s="4">
-        <v>15.9</v>
+        <v>6.8</v>
       </c>
       <c r="Q102" s="4">
-        <v>17.2</v>
+        <v>7.9</v>
       </c>
       <c r="R102" s="4">
-        <v>22.4</v>
+        <v>10.6</v>
       </c>
       <c r="S102" s="4">
-        <v>16.100000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="T102" s="4">
-        <v>13.8</v>
+        <v>7.1</v>
       </c>
       <c r="U102" s="4">
-        <v>13.9</v>
+        <v>7</v>
       </c>
       <c r="V102" s="4">
-        <v>14.3</v>
+        <v>6.7</v>
       </c>
       <c r="W102" s="2" t="s">
         <v>30</v>
@@ -13816,7 +13816,7 @@
         <v>66</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F194" s="3" t="s">
         <v>34</v>
@@ -13887,7 +13887,7 @@
         <v>66</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F195" s="3" t="s">
         <v>34</v>

--- a/assets/excel/en/national_sdg_indicators.xlsx
+++ b/assets/excel/en/national_sdg_indicators.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sidwab\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99B2E980-4D98-4B6F-9C86-8E946190C44C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{296A1576-BDF5-4D45-95D6-CB0104835314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2132" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="426">
   <si>
     <t>sdg.gov.pl/en</t>
   </si>
@@ -841,39 +841,15 @@
     <t>11.1.a Population living in households considering that they suffer from noise</t>
   </si>
   <si>
-    <t>11.1.b Average useful floor area of dwelling per capita in urban areas</t>
+    <t>11.1.b Share of strolling-recreational parks and green areas in the total area of the city</t>
+  </si>
+  <si>
+    <t>11.1.c Area of strolling-recreational parks and green areas per capita in the city</t>
   </si>
   <si>
     <t>m2</t>
   </si>
   <si>
-    <t>11.1.c Share of total population in urban areas living in a dwelling with a leaking roof, damp walls, floors or foundation, or rot in window frames or floor</t>
-  </si>
-  <si>
-    <t>11.1.d Share of buses powered by alternative fuels in the total number of buses serving urban transport</t>
-  </si>
-  <si>
-    <t>11.1.e Transport of passengers per 1 inhabitant of urban areas</t>
-  </si>
-  <si>
-    <t>11.1.f Proportion of municipal waste generated according to the treatment operation to total municipal generated</t>
-  </si>
-  <si>
-    <t>by treatment operation</t>
-  </si>
-  <si>
-    <t>recycling</t>
-  </si>
-  <si>
-    <t>composting or fermentation</t>
-  </si>
-  <si>
-    <t>incineration</t>
-  </si>
-  <si>
-    <t>landfilling</t>
-  </si>
-  <si>
     <t>Supporting cities in dealing with sudden changes, crises, both socio-economic and environmental, and guaranteeing safety and high quality of life for inhabitants</t>
   </si>
   <si>
@@ -886,7 +862,7 @@
     <t>11.2.c Share of inhabitants connected to water supply system in urban areas</t>
   </si>
   <si>
-    <t>11.2.d Share of population living in areas covered by revitalization processes in the total population in urban areas</t>
+    <t>11.2.d Share of population living in areas covered by revitalization processes in the total population in urban gminas</t>
   </si>
   <si>
     <t>11.2.e Share of degraded areas in the total area of urban gminas</t>
@@ -898,18 +874,6 @@
     <t>11.3.a Share of area covered by local-land development plans in urban gminas</t>
   </si>
   <si>
-    <t>11.3.b Relation of the length of public transport lines in rural areas to the length of public transport lines in urban areas</t>
-  </si>
-  <si>
-    <t>11.3.c Range of the Index of Multimodal Accessibility of Transport in Functional Urban Areas</t>
-  </si>
-  <si>
-    <t>[-]</t>
-  </si>
-  <si>
-    <t>Ministry of Funds and Regional Policy</t>
-  </si>
-  <si>
     <t>Building a sustainable, publicly accessible, safe and affordable transport system, especially through the development and prioritization of public transport</t>
   </si>
   <si>
@@ -928,6 +892,9 @@
     <t>11.4.c Number of passenger transport per 1 inhabitant of urban area</t>
   </si>
   <si>
+    <t>11.4.d Share of buses powered by alternative fuels in the total number of buses serving urban transport</t>
+  </si>
+  <si>
     <t>Fulfillment of housing needs of urban population by building a universal and accessible housing market, including the development of social housing</t>
   </si>
   <si>
@@ -952,7 +919,16 @@
     <t>tonnes</t>
   </si>
   <si>
-    <t>11.6.b Total capacity of installed devices and installations to reduce pollution in cities with powiat status</t>
+    <t>11.6.b Share of pollutants retained or neutralised in pollutant reduction systems in plants particularly noxious in cities with powiat status</t>
+  </si>
+  <si>
+    <t>by type of pollutants</t>
+  </si>
+  <si>
+    <t>gaseous (without CO2)</t>
+  </si>
+  <si>
+    <t>particulate</t>
   </si>
   <si>
     <t>11.6.c Number of agglomerations and cities with over 100 thous. inhabitants, where the value of average exposure indicator does not exceed the concentration threshold of exposure to PM 2.5 at 20 µg/m3</t>
@@ -1330,7 +1306,7 @@
     <t>The Ministry of Economic Development and Technology / The Chancellery of the  Prime Minister</t>
   </si>
   <si>
-    <t>Last update: 05-08-2026, 07:42</t>
+    <t>Last update: 05-08-2026, 10:54</t>
   </si>
 </sst>
 </file>
@@ -1876,7 +1852,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W308"/>
+  <dimension ref="A1:W300"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" customWidth="1"/>
@@ -15181,52 +15157,52 @@
         <v>28</v>
       </c>
       <c r="F215" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="G215" s="4">
-        <v>24.7</v>
-      </c>
-      <c r="H215" s="4">
-        <v>25</v>
-      </c>
-      <c r="I215" s="4">
-        <v>25.4</v>
-      </c>
-      <c r="J215" s="4">
-        <v>25.7</v>
-      </c>
-      <c r="K215" s="4">
-        <v>26.1</v>
-      </c>
-      <c r="L215" s="4">
-        <v>26.4</v>
-      </c>
-      <c r="M215" s="4">
-        <v>26.8</v>
-      </c>
-      <c r="N215" s="4">
-        <v>27.2</v>
-      </c>
-      <c r="O215" s="4">
-        <v>27.7</v>
-      </c>
-      <c r="P215" s="4">
-        <v>28.1</v>
-      </c>
-      <c r="Q215" s="4">
-        <v>29.2</v>
-      </c>
-      <c r="R215" s="4">
-        <v>29.8</v>
-      </c>
-      <c r="S215" s="4">
-        <v>30.4</v>
-      </c>
-      <c r="T215" s="4">
-        <v>31</v>
-      </c>
-      <c r="U215" s="4">
-        <v>31.6</v>
+        <v>34</v>
+      </c>
+      <c r="G215" s="5">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="H215" s="5">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="I215" s="5">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="J215" s="5">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="K215" s="5">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="L215" s="5">
+        <v>1.18</v>
+      </c>
+      <c r="M215" s="5">
+        <v>1.18</v>
+      </c>
+      <c r="N215" s="5">
+        <v>1.18</v>
+      </c>
+      <c r="O215" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="P215" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="Q215" s="5">
+        <v>1.22</v>
+      </c>
+      <c r="R215" s="5">
+        <v>1.24</v>
+      </c>
+      <c r="S215" s="5">
+        <v>1.24</v>
+      </c>
+      <c r="T215" s="5">
+        <v>1.21</v>
+      </c>
+      <c r="U215" s="5">
+        <v>1.21</v>
       </c>
       <c r="V215" s="3"/>
       <c r="W215" s="2" t="s">
@@ -15241,7 +15217,7 @@
         <v>268</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>27</v>
@@ -15250,61 +15226,67 @@
         <v>28</v>
       </c>
       <c r="F216" s="3" t="s">
-        <v>34</v>
+        <v>272</v>
       </c>
       <c r="G216" s="4">
+        <v>10.5</v>
+      </c>
+      <c r="H216" s="4">
+        <v>10.5</v>
+      </c>
+      <c r="I216" s="4">
+        <v>10.5</v>
+      </c>
+      <c r="J216" s="4">
+        <v>10.5</v>
+      </c>
+      <c r="K216" s="4">
+        <v>10.7</v>
+      </c>
+      <c r="L216" s="4">
+        <v>11.1</v>
+      </c>
+      <c r="M216" s="4">
+        <v>11.1</v>
+      </c>
+      <c r="N216" s="4">
+        <v>11.2</v>
+      </c>
+      <c r="O216" s="4">
+        <v>11.4</v>
+      </c>
+      <c r="P216" s="4">
+        <v>11.8</v>
+      </c>
+      <c r="Q216" s="4">
+        <v>11.9</v>
+      </c>
+      <c r="R216" s="4">
+        <v>12.3</v>
+      </c>
+      <c r="S216" s="4">
+        <v>12.4</v>
+      </c>
+      <c r="T216" s="4">
+        <v>12.7</v>
+      </c>
+      <c r="U216" s="4">
         <v>13</v>
       </c>
-      <c r="H216" s="4">
-        <v>10.3</v>
-      </c>
-      <c r="I216" s="4">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="J216" s="4">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="K216" s="4">
-        <v>8.9</v>
-      </c>
-      <c r="L216" s="4">
-        <v>10.6</v>
-      </c>
-      <c r="M216" s="4">
-        <v>10.1</v>
-      </c>
-      <c r="N216" s="4">
-        <v>10.5</v>
-      </c>
-      <c r="O216" s="4">
-        <v>10.5</v>
-      </c>
-      <c r="P216" s="4">
-        <v>10.4</v>
-      </c>
-      <c r="Q216" s="4">
-        <v>5.7</v>
-      </c>
-      <c r="R216" s="3"/>
-      <c r="S216" s="3"/>
-      <c r="T216" s="4">
-        <v>6.1</v>
-      </c>
-      <c r="U216" s="3"/>
       <c r="V216" s="3"/>
       <c r="W216" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="217" spans="1:23" ht="54" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>267</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>27</v>
@@ -15313,67 +15295,39 @@
         <v>28</v>
       </c>
       <c r="F217" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G217" s="4">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="H217" s="4">
-        <v>2.8</v>
-      </c>
-      <c r="I217" s="4">
-        <v>2.7</v>
-      </c>
-      <c r="J217" s="4">
-        <v>3.1</v>
-      </c>
-      <c r="K217" s="4">
-        <v>2.9</v>
-      </c>
-      <c r="L217" s="4">
-        <v>3.6</v>
-      </c>
-      <c r="M217" s="4">
-        <v>3.8</v>
-      </c>
-      <c r="N217" s="4">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="O217" s="4">
-        <v>7</v>
-      </c>
-      <c r="P217" s="4">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="Q217" s="4">
-        <v>12.2</v>
-      </c>
-      <c r="R217" s="4">
-        <v>15.4</v>
-      </c>
-      <c r="S217" s="4">
-        <v>17.399999999999999</v>
-      </c>
-      <c r="T217" s="4">
-        <v>21.6</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="G217" s="3"/>
+      <c r="H217" s="3"/>
+      <c r="I217" s="3"/>
+      <c r="J217" s="3"/>
+      <c r="K217" s="3"/>
+      <c r="L217" s="3"/>
+      <c r="M217" s="3"/>
+      <c r="N217" s="3"/>
+      <c r="O217" s="3"/>
+      <c r="P217" s="3"/>
+      <c r="Q217" s="3"/>
+      <c r="R217" s="3"/>
+      <c r="S217" s="3"/>
+      <c r="T217" s="3"/>
       <c r="U217" s="4">
-        <v>24.2</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="V217" s="3"/>
       <c r="W217" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="218" spans="1:23" ht="54" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="218" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>267</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>27</v>
@@ -15382,335 +15336,295 @@
         <v>28</v>
       </c>
       <c r="F218" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G218" s="4">
-        <v>166.5</v>
+        <v>88</v>
       </c>
       <c r="H218" s="4">
-        <v>166.2</v>
+        <v>88.4</v>
       </c>
       <c r="I218" s="4">
-        <v>165.6</v>
+        <v>91.7</v>
       </c>
       <c r="J218" s="4">
-        <v>155.5</v>
+        <v>93.3</v>
       </c>
       <c r="K218" s="4">
-        <v>159.69999999999999</v>
+        <v>93.9</v>
       </c>
       <c r="L218" s="4">
-        <v>158.30000000000001</v>
+        <v>94.6</v>
       </c>
       <c r="M218" s="4">
-        <v>162.69999999999999</v>
+        <v>94.8</v>
       </c>
       <c r="N218" s="4">
-        <v>161.69999999999999</v>
+        <v>94.5</v>
       </c>
       <c r="O218" s="4">
-        <v>163.4</v>
+        <v>94.6</v>
       </c>
       <c r="P218" s="4">
-        <v>167.6</v>
+        <v>94.8</v>
       </c>
       <c r="Q218" s="4">
-        <v>99.3</v>
+        <v>94.7</v>
       </c>
       <c r="R218" s="4">
-        <v>110.1</v>
+        <v>94.6</v>
       </c>
       <c r="S218" s="4">
-        <v>135.6</v>
+        <v>95</v>
       </c>
       <c r="T218" s="4">
-        <v>144.6</v>
+        <v>94.8</v>
       </c>
       <c r="U218" s="4">
-        <v>152.19999999999999</v>
+        <v>94.6</v>
       </c>
       <c r="V218" s="3"/>
       <c r="W218" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="219" spans="1:23" ht="54" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="219" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>267</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>276</v>
+        <v>27</v>
       </c>
       <c r="E219" s="3" t="s">
-        <v>277</v>
+        <v>28</v>
       </c>
       <c r="F219" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G219" s="5">
-        <v>14.82</v>
-      </c>
-      <c r="H219" s="5">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="I219" s="5">
-        <v>10.3</v>
-      </c>
-      <c r="J219" s="5">
-        <v>13.27</v>
-      </c>
-      <c r="K219" s="5">
-        <v>21.1</v>
-      </c>
-      <c r="L219" s="5">
-        <v>26.39</v>
-      </c>
-      <c r="M219" s="5">
-        <v>27.84</v>
-      </c>
-      <c r="N219" s="5">
-        <v>26.73</v>
-      </c>
-      <c r="O219" s="5">
-        <v>26.18</v>
-      </c>
-      <c r="P219" s="5">
-        <v>25.03</v>
-      </c>
-      <c r="Q219" s="5">
-        <v>26.68</v>
-      </c>
-      <c r="R219" s="5">
-        <v>26.92</v>
-      </c>
-      <c r="S219" s="5">
-        <v>26.72</v>
-      </c>
-      <c r="T219" s="5">
-        <v>15.76</v>
-      </c>
-      <c r="U219" s="5">
-        <v>18.34</v>
+      <c r="G219" s="4">
+        <v>95.3</v>
+      </c>
+      <c r="H219" s="4">
+        <v>95.4</v>
+      </c>
+      <c r="I219" s="4">
+        <v>95.4</v>
+      </c>
+      <c r="J219" s="4">
+        <v>95.5</v>
+      </c>
+      <c r="K219" s="4">
+        <v>96.4</v>
+      </c>
+      <c r="L219" s="4">
+        <v>96.5</v>
+      </c>
+      <c r="M219" s="4">
+        <v>96.5</v>
+      </c>
+      <c r="N219" s="4">
+        <v>96.6</v>
+      </c>
+      <c r="O219" s="4">
+        <v>96.6</v>
+      </c>
+      <c r="P219" s="4">
+        <v>96.6</v>
+      </c>
+      <c r="Q219" s="4">
+        <v>96.7</v>
+      </c>
+      <c r="R219" s="4">
+        <v>96.7</v>
+      </c>
+      <c r="S219" s="4">
+        <v>96.7</v>
+      </c>
+      <c r="T219" s="4">
+        <v>96.8</v>
+      </c>
+      <c r="U219" s="4">
+        <v>96.8</v>
       </c>
       <c r="V219" s="3"/>
       <c r="W219" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="220" spans="1:23" ht="54" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>267</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>276</v>
+        <v>27</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>278</v>
+        <v>28</v>
       </c>
       <c r="F220" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G220" s="5">
-        <v>1.5</v>
-      </c>
-      <c r="H220" s="5">
-        <v>1.73</v>
-      </c>
-      <c r="I220" s="5">
-        <v>1.67</v>
-      </c>
-      <c r="J220" s="5">
-        <v>1.88</v>
-      </c>
-      <c r="K220" s="5">
-        <v>5.42</v>
-      </c>
-      <c r="L220" s="5">
-        <v>6.09</v>
-      </c>
-      <c r="M220" s="5">
-        <v>6.99</v>
-      </c>
-      <c r="N220" s="5">
-        <v>7.08</v>
-      </c>
-      <c r="O220" s="5">
-        <v>8.11</v>
-      </c>
-      <c r="P220" s="5">
-        <v>9.0399999999999991</v>
-      </c>
-      <c r="Q220" s="5">
-        <v>12.03</v>
-      </c>
-      <c r="R220" s="5">
-        <v>13.34</v>
-      </c>
-      <c r="S220" s="5">
-        <v>14.15</v>
-      </c>
-      <c r="T220" s="5">
-        <v>11.79</v>
-      </c>
-      <c r="U220" s="5">
-        <v>12.81</v>
+      <c r="G220" s="3"/>
+      <c r="H220" s="3"/>
+      <c r="I220" s="3"/>
+      <c r="J220" s="3"/>
+      <c r="K220" s="3"/>
+      <c r="L220" s="3"/>
+      <c r="M220" s="3"/>
+      <c r="N220" s="3"/>
+      <c r="O220" s="3"/>
+      <c r="P220" s="3"/>
+      <c r="Q220" s="4">
+        <v>5.4</v>
+      </c>
+      <c r="R220" s="4">
+        <v>5.3</v>
+      </c>
+      <c r="S220" s="4">
+        <v>5.2</v>
+      </c>
+      <c r="T220" s="4">
+        <v>6.6</v>
+      </c>
+      <c r="U220" s="4">
+        <v>10.7</v>
       </c>
       <c r="V220" s="3"/>
       <c r="W220" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="221" spans="1:23" ht="54" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>267</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>276</v>
+        <v>27</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>279</v>
+        <v>28</v>
       </c>
       <c r="F221" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G221" s="5">
-        <v>0.32</v>
-      </c>
-      <c r="H221" s="5">
-        <v>0.37</v>
-      </c>
-      <c r="I221" s="5">
-        <v>0.42</v>
-      </c>
-      <c r="J221" s="5">
-        <v>6.78</v>
-      </c>
-      <c r="K221" s="5">
-        <v>15.1</v>
-      </c>
-      <c r="L221" s="5">
-        <v>13.25</v>
-      </c>
-      <c r="M221" s="5">
-        <v>19.440000000000001</v>
-      </c>
-      <c r="N221" s="5">
-        <v>24.41</v>
-      </c>
-      <c r="O221" s="5">
-        <v>24.13</v>
-      </c>
-      <c r="P221" s="5">
-        <v>22.9</v>
-      </c>
-      <c r="Q221" s="5">
-        <v>21.52</v>
-      </c>
-      <c r="R221" s="5">
-        <v>21.01</v>
-      </c>
-      <c r="S221" s="5">
-        <v>21.07</v>
-      </c>
-      <c r="T221" s="5">
-        <v>20.66</v>
-      </c>
-      <c r="U221" s="5">
-        <v>21.92</v>
+      <c r="G221" s="3"/>
+      <c r="H221" s="3"/>
+      <c r="I221" s="3"/>
+      <c r="J221" s="3"/>
+      <c r="K221" s="3"/>
+      <c r="L221" s="3"/>
+      <c r="M221" s="3"/>
+      <c r="N221" s="3"/>
+      <c r="O221" s="3"/>
+      <c r="P221" s="3"/>
+      <c r="Q221" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="R221" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="S221" s="4">
+        <v>5</v>
+      </c>
+      <c r="T221" s="4">
+        <v>7.3</v>
+      </c>
+      <c r="U221" s="4">
+        <v>14.5</v>
       </c>
       <c r="V221" s="3"/>
       <c r="W221" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="222" spans="1:23" ht="54" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>267</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>276</v>
+        <v>27</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>280</v>
+        <v>28</v>
       </c>
       <c r="F222" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G222" s="5">
-        <v>66.8</v>
-      </c>
-      <c r="H222" s="5">
-        <v>69.260000000000005</v>
-      </c>
-      <c r="I222" s="5">
-        <v>66.91</v>
-      </c>
-      <c r="J222" s="5">
-        <v>61.95</v>
-      </c>
-      <c r="K222" s="5">
-        <v>58.38</v>
-      </c>
-      <c r="L222" s="5">
-        <v>54.29</v>
-      </c>
-      <c r="M222" s="5">
-        <v>45.74</v>
-      </c>
-      <c r="N222" s="5">
-        <v>41.77</v>
-      </c>
-      <c r="O222" s="5">
-        <v>41.58</v>
-      </c>
-      <c r="P222" s="5">
-        <v>43.03</v>
-      </c>
-      <c r="Q222" s="5">
-        <v>39.78</v>
-      </c>
-      <c r="R222" s="5">
-        <v>38.729999999999997</v>
-      </c>
-      <c r="S222" s="5">
-        <v>38.06</v>
-      </c>
-      <c r="T222" s="5">
-        <v>30.24</v>
-      </c>
-      <c r="U222" s="5">
-        <v>30.07</v>
+      <c r="G222" s="4">
+        <v>41.6</v>
+      </c>
+      <c r="H222" s="4">
+        <v>44.7</v>
+      </c>
+      <c r="I222" s="4">
+        <v>46.5</v>
+      </c>
+      <c r="J222" s="4">
+        <v>48.2</v>
+      </c>
+      <c r="K222" s="4">
+        <v>49.6</v>
+      </c>
+      <c r="L222" s="4">
+        <v>49.8</v>
+      </c>
+      <c r="M222" s="4">
+        <v>50.6</v>
+      </c>
+      <c r="N222" s="4">
+        <v>51.2</v>
+      </c>
+      <c r="O222" s="4">
+        <v>52.4</v>
+      </c>
+      <c r="P222" s="4">
+        <v>53.4</v>
+      </c>
+      <c r="Q222" s="4">
+        <v>53.9</v>
+      </c>
+      <c r="R222" s="4">
+        <v>54.8</v>
+      </c>
+      <c r="S222" s="4">
+        <v>55.8</v>
+      </c>
+      <c r="T222" s="4">
+        <v>53.6</v>
+      </c>
+      <c r="U222" s="4">
+        <v>54.5</v>
       </c>
       <c r="V222" s="3"/>
       <c r="W222" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="223" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>267</v>
       </c>
@@ -15727,31 +15641,55 @@
         <v>28</v>
       </c>
       <c r="F223" s="3" t="s">
-        <v>27</v>
+        <v>283</v>
       </c>
       <c r="G223" s="3"/>
       <c r="H223" s="3"/>
-      <c r="I223" s="3"/>
-      <c r="J223" s="3"/>
-      <c r="K223" s="3"/>
-      <c r="L223" s="3"/>
-      <c r="M223" s="3"/>
-      <c r="N223" s="3"/>
-      <c r="O223" s="3"/>
-      <c r="P223" s="3"/>
-      <c r="Q223" s="3"/>
-      <c r="R223" s="3"/>
-      <c r="S223" s="3"/>
-      <c r="T223" s="3"/>
-      <c r="U223" s="4">
-        <v>5.0999999999999996</v>
+      <c r="I223" s="5">
+        <v>1.39</v>
+      </c>
+      <c r="J223" s="5">
+        <v>1.41</v>
+      </c>
+      <c r="K223" s="5">
+        <v>1.43</v>
+      </c>
+      <c r="L223" s="5">
+        <v>1.48</v>
+      </c>
+      <c r="M223" s="5">
+        <v>1.47</v>
+      </c>
+      <c r="N223" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="O223" s="5">
+        <v>1.53</v>
+      </c>
+      <c r="P223" s="5">
+        <v>1.57</v>
+      </c>
+      <c r="Q223" s="5">
+        <v>1.58</v>
+      </c>
+      <c r="R223" s="5">
+        <v>1.58</v>
+      </c>
+      <c r="S223" s="5">
+        <v>1.54</v>
+      </c>
+      <c r="T223" s="5">
+        <v>1.57</v>
+      </c>
+      <c r="U223" s="5">
+        <v>1.62</v>
       </c>
       <c r="V223" s="3"/>
       <c r="W223" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="224" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="224" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>267</v>
       </c>
@@ -15759,7 +15697,7 @@
         <v>281</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>27</v>
@@ -15768,59 +15706,49 @@
         <v>28</v>
       </c>
       <c r="F224" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G224" s="4">
-        <v>88</v>
-      </c>
-      <c r="H224" s="4">
-        <v>88.4</v>
-      </c>
-      <c r="I224" s="4">
-        <v>91.7</v>
-      </c>
-      <c r="J224" s="4">
-        <v>93.3</v>
-      </c>
-      <c r="K224" s="4">
-        <v>93.9</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="G224" s="3"/>
+      <c r="H224" s="3"/>
+      <c r="I224" s="3"/>
+      <c r="J224" s="3"/>
+      <c r="K224" s="3"/>
       <c r="L224" s="4">
-        <v>94.6</v>
+        <v>12.1</v>
       </c>
       <c r="M224" s="4">
-        <v>94.8</v>
+        <v>12.7</v>
       </c>
       <c r="N224" s="4">
-        <v>94.5</v>
+        <v>11.6</v>
       </c>
       <c r="O224" s="4">
-        <v>94.6</v>
+        <v>11.4</v>
       </c>
       <c r="P224" s="4">
-        <v>94.8</v>
+        <v>10.6</v>
       </c>
       <c r="Q224" s="4">
-        <v>94.7</v>
+        <v>9</v>
       </c>
       <c r="R224" s="4">
-        <v>94.6</v>
+        <v>7.8</v>
       </c>
       <c r="S224" s="4">
-        <v>95</v>
+        <v>7.6</v>
       </c>
       <c r="T224" s="4">
-        <v>94.8</v>
+        <v>7.6</v>
       </c>
       <c r="U224" s="4">
-        <v>94.6</v>
+        <v>7.7</v>
       </c>
       <c r="V224" s="3"/>
       <c r="W224" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="225" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="225" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>267</v>
       </c>
@@ -15828,7 +15756,7 @@
         <v>281</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D225" s="2" t="s">
         <v>27</v>
@@ -15837,59 +15765,59 @@
         <v>28</v>
       </c>
       <c r="F225" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G225" s="4">
-        <v>95.3</v>
+        <v>166.5</v>
       </c>
       <c r="H225" s="4">
-        <v>95.4</v>
+        <v>166.2</v>
       </c>
       <c r="I225" s="4">
-        <v>95.4</v>
+        <v>165.6</v>
       </c>
       <c r="J225" s="4">
-        <v>95.5</v>
+        <v>155.5</v>
       </c>
       <c r="K225" s="4">
-        <v>96.4</v>
+        <v>159.69999999999999</v>
       </c>
       <c r="L225" s="4">
-        <v>96.5</v>
+        <v>158.30000000000001</v>
       </c>
       <c r="M225" s="4">
-        <v>96.5</v>
+        <v>162.69999999999999</v>
       </c>
       <c r="N225" s="4">
-        <v>96.6</v>
+        <v>161.69999999999999</v>
       </c>
       <c r="O225" s="4">
-        <v>96.6</v>
+        <v>163.4</v>
       </c>
       <c r="P225" s="4">
-        <v>96.6</v>
+        <v>167.6</v>
       </c>
       <c r="Q225" s="4">
-        <v>96.7</v>
+        <v>99.3</v>
       </c>
       <c r="R225" s="4">
-        <v>96.7</v>
+        <v>110.1</v>
       </c>
       <c r="S225" s="4">
-        <v>96.7</v>
+        <v>135.6</v>
       </c>
       <c r="T225" s="4">
-        <v>96.8</v>
+        <v>144.6</v>
       </c>
       <c r="U225" s="4">
-        <v>96.8</v>
+        <v>152.19999999999999</v>
       </c>
       <c r="V225" s="3"/>
       <c r="W225" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="226" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>267</v>
       </c>
@@ -15897,7 +15825,7 @@
         <v>281</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D226" s="2" t="s">
         <v>27</v>
@@ -15908,45 +15836,65 @@
       <c r="F226" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G226" s="3"/>
-      <c r="H226" s="3"/>
-      <c r="I226" s="3"/>
-      <c r="J226" s="3"/>
-      <c r="K226" s="3"/>
-      <c r="L226" s="3"/>
-      <c r="M226" s="3"/>
-      <c r="N226" s="3"/>
-      <c r="O226" s="3"/>
-      <c r="P226" s="3"/>
+      <c r="G226" s="4">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="H226" s="4">
+        <v>2.8</v>
+      </c>
+      <c r="I226" s="4">
+        <v>2.7</v>
+      </c>
+      <c r="J226" s="4">
+        <v>3.1</v>
+      </c>
+      <c r="K226" s="4">
+        <v>2.9</v>
+      </c>
+      <c r="L226" s="4">
+        <v>3.6</v>
+      </c>
+      <c r="M226" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="N226" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="O226" s="4">
+        <v>7</v>
+      </c>
+      <c r="P226" s="4">
+        <v>9.6999999999999993</v>
+      </c>
       <c r="Q226" s="4">
-        <v>5.4</v>
+        <v>12.2</v>
       </c>
       <c r="R226" s="4">
-        <v>5.3</v>
+        <v>15.4</v>
       </c>
       <c r="S226" s="4">
-        <v>5.2</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="T226" s="4">
-        <v>6.6</v>
+        <v>21.6</v>
       </c>
       <c r="U226" s="4">
-        <v>10.7</v>
+        <v>24.2</v>
       </c>
       <c r="V226" s="3"/>
       <c r="W226" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="227" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>267</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D227" s="2" t="s">
         <v>27</v>
@@ -15955,47 +15903,69 @@
         <v>28</v>
       </c>
       <c r="F227" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G227" s="3"/>
-      <c r="H227" s="3"/>
-      <c r="I227" s="3"/>
-      <c r="J227" s="3"/>
-      <c r="K227" s="3"/>
-      <c r="L227" s="3"/>
-      <c r="M227" s="3"/>
-      <c r="N227" s="3"/>
-      <c r="O227" s="3"/>
-      <c r="P227" s="3"/>
+        <v>264</v>
+      </c>
+      <c r="G227" s="4">
+        <v>3.7</v>
+      </c>
+      <c r="H227" s="4">
+        <v>3.4</v>
+      </c>
+      <c r="I227" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="J227" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="K227" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="L227" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="M227" s="4">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="N227" s="4">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="O227" s="4">
+        <v>5.4</v>
+      </c>
+      <c r="P227" s="4">
+        <v>6.1</v>
+      </c>
       <c r="Q227" s="4">
-        <v>3.9</v>
+        <v>6.5</v>
       </c>
       <c r="R227" s="4">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="S227" s="4">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="T227" s="4">
-        <v>7.3</v>
+        <v>6.3</v>
       </c>
       <c r="U227" s="4">
-        <v>14.5</v>
-      </c>
-      <c r="V227" s="3"/>
+        <v>5.8</v>
+      </c>
+      <c r="V227" s="4">
+        <v>6</v>
+      </c>
       <c r="W227" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="228" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>267</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D228" s="2" t="s">
         <v>27</v>
@@ -16004,67 +15974,69 @@
         <v>28</v>
       </c>
       <c r="F228" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G228" s="4">
-        <v>41.6</v>
-      </c>
-      <c r="H228" s="4">
-        <v>44.7</v>
-      </c>
-      <c r="I228" s="4">
-        <v>46.5</v>
-      </c>
-      <c r="J228" s="4">
-        <v>48.2</v>
-      </c>
-      <c r="K228" s="4">
-        <v>49.6</v>
-      </c>
-      <c r="L228" s="4">
-        <v>49.8</v>
-      </c>
-      <c r="M228" s="4">
-        <v>50.6</v>
-      </c>
-      <c r="N228" s="4">
-        <v>51.2</v>
-      </c>
-      <c r="O228" s="4">
-        <v>52.4</v>
-      </c>
-      <c r="P228" s="4">
-        <v>53.4</v>
-      </c>
-      <c r="Q228" s="4">
-        <v>53.9</v>
-      </c>
-      <c r="R228" s="4">
-        <v>54.8</v>
-      </c>
-      <c r="S228" s="4">
-        <v>55.8</v>
-      </c>
-      <c r="T228" s="4">
-        <v>53.6</v>
-      </c>
-      <c r="U228" s="4">
-        <v>54.5</v>
-      </c>
-      <c r="V228" s="3"/>
+        <v>264</v>
+      </c>
+      <c r="G228" s="5">
+        <v>0.26</v>
+      </c>
+      <c r="H228" s="5">
+        <v>0.18</v>
+      </c>
+      <c r="I228" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J228" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="K228" s="5">
+        <v>0.16</v>
+      </c>
+      <c r="L228" s="5">
+        <v>0.11</v>
+      </c>
+      <c r="M228" s="5">
+        <v>0.12</v>
+      </c>
+      <c r="N228" s="5">
+        <v>0.13</v>
+      </c>
+      <c r="O228" s="5">
+        <v>0.13</v>
+      </c>
+      <c r="P228" s="5">
+        <v>0.18</v>
+      </c>
+      <c r="Q228" s="5">
+        <v>0.11</v>
+      </c>
+      <c r="R228" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="S228" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="T228" s="5">
+        <v>0.13</v>
+      </c>
+      <c r="U228" s="5">
+        <v>0.18</v>
+      </c>
+      <c r="V228" s="5">
+        <v>0.25</v>
+      </c>
       <c r="W228" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="229" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>267</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D229" s="2" t="s">
         <v>27</v>
@@ -16073,63 +16045,49 @@
         <v>28</v>
       </c>
       <c r="F229" s="3" t="s">
-        <v>34</v>
+        <v>264</v>
       </c>
       <c r="G229" s="3"/>
       <c r="H229" s="3"/>
-      <c r="I229" s="4">
-        <v>29.8</v>
-      </c>
-      <c r="J229" s="4">
-        <v>31.1</v>
-      </c>
-      <c r="K229" s="4">
-        <v>30.3</v>
-      </c>
-      <c r="L229" s="4">
-        <v>32.299999999999997</v>
-      </c>
-      <c r="M229" s="4">
-        <v>34.700000000000003</v>
-      </c>
-      <c r="N229" s="4">
-        <v>35.6</v>
-      </c>
-      <c r="O229" s="4">
-        <v>37.5</v>
-      </c>
-      <c r="P229" s="4">
-        <v>35.9</v>
-      </c>
-      <c r="Q229" s="4">
-        <v>36.6</v>
-      </c>
-      <c r="R229" s="4">
-        <v>36.1</v>
-      </c>
-      <c r="S229" s="4">
-        <v>35.4</v>
-      </c>
-      <c r="T229" s="4">
-        <v>35.6</v>
-      </c>
-      <c r="U229" s="4">
-        <v>35.4</v>
+      <c r="I229" s="3"/>
+      <c r="J229" s="3"/>
+      <c r="K229" s="3"/>
+      <c r="L229" s="3"/>
+      <c r="M229" s="3"/>
+      <c r="N229" s="3"/>
+      <c r="O229" s="3"/>
+      <c r="P229" s="6">
+        <v>74110</v>
+      </c>
+      <c r="Q229" s="6">
+        <v>68436</v>
+      </c>
+      <c r="R229" s="6">
+        <v>65117</v>
+      </c>
+      <c r="S229" s="6">
+        <v>64070</v>
+      </c>
+      <c r="T229" s="6">
+        <v>61349</v>
+      </c>
+      <c r="U229" s="6">
+        <v>59560</v>
       </c>
       <c r="V229" s="3"/>
       <c r="W229" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="230" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>267</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D230" s="2" t="s">
         <v>27</v>
@@ -16138,28 +16096,40 @@
         <v>28</v>
       </c>
       <c r="F230" s="3" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="G230" s="3"/>
       <c r="H230" s="3"/>
       <c r="I230" s="3"/>
-      <c r="J230" s="3"/>
+      <c r="J230" s="6">
+        <v>546870</v>
+      </c>
       <c r="K230" s="3"/>
-      <c r="L230" s="3"/>
-      <c r="M230" s="3"/>
+      <c r="L230" s="6">
+        <v>512116</v>
+      </c>
+      <c r="M230" s="6">
+        <v>501544</v>
+      </c>
       <c r="N230" s="3"/>
-      <c r="O230" s="3"/>
+      <c r="O230" s="6">
+        <v>487452</v>
+      </c>
       <c r="P230" s="3"/>
-      <c r="Q230" s="5">
-        <v>83.49</v>
+      <c r="Q230" s="6">
+        <v>469607</v>
       </c>
       <c r="R230" s="3"/>
-      <c r="S230" s="3"/>
+      <c r="S230" s="6">
+        <v>457891</v>
+      </c>
       <c r="T230" s="3"/>
-      <c r="U230" s="3"/>
+      <c r="U230" s="6">
+        <v>446959</v>
+      </c>
       <c r="V230" s="3"/>
       <c r="W230" s="2" t="s">
-        <v>292</v>
+        <v>30</v>
       </c>
     </row>
     <row r="231" spans="1:23" ht="27" x14ac:dyDescent="0.25">
@@ -16181,46 +16151,50 @@
       <c r="F231" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="G231" s="3"/>
-      <c r="H231" s="3"/>
-      <c r="I231" s="5">
-        <v>1.39</v>
-      </c>
-      <c r="J231" s="5">
-        <v>1.41</v>
-      </c>
-      <c r="K231" s="5">
-        <v>1.43</v>
-      </c>
-      <c r="L231" s="5">
-        <v>1.48</v>
-      </c>
-      <c r="M231" s="5">
-        <v>1.47</v>
-      </c>
-      <c r="N231" s="5">
-        <v>1.5</v>
-      </c>
-      <c r="O231" s="5">
-        <v>1.53</v>
-      </c>
-      <c r="P231" s="5">
-        <v>1.57</v>
-      </c>
-      <c r="Q231" s="5">
-        <v>1.58</v>
-      </c>
-      <c r="R231" s="5">
-        <v>1.58</v>
-      </c>
-      <c r="S231" s="5">
-        <v>1.54</v>
-      </c>
-      <c r="T231" s="5">
-        <v>1.57</v>
-      </c>
-      <c r="U231" s="5">
-        <v>1.62</v>
+      <c r="G231" s="6">
+        <v>22795</v>
+      </c>
+      <c r="H231" s="6">
+        <v>21359</v>
+      </c>
+      <c r="I231" s="6">
+        <v>20022</v>
+      </c>
+      <c r="J231" s="6">
+        <v>19636</v>
+      </c>
+      <c r="K231" s="6">
+        <v>18137</v>
+      </c>
+      <c r="L231" s="6">
+        <v>16793</v>
+      </c>
+      <c r="M231" s="6">
+        <v>15086</v>
+      </c>
+      <c r="N231" s="6">
+        <v>14505</v>
+      </c>
+      <c r="O231" s="6">
+        <v>14165</v>
+      </c>
+      <c r="P231" s="6">
+        <v>11466</v>
+      </c>
+      <c r="Q231" s="6">
+        <v>8767</v>
+      </c>
+      <c r="R231" s="6">
+        <v>8374</v>
+      </c>
+      <c r="S231" s="6">
+        <v>7344</v>
+      </c>
+      <c r="T231" s="6">
+        <v>5553</v>
+      </c>
+      <c r="U231" s="6">
+        <v>5297</v>
       </c>
       <c r="V231" s="3"/>
       <c r="W231" s="2" t="s">
@@ -16238,52 +16212,62 @@
         <v>296</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>27</v>
+        <v>297</v>
       </c>
       <c r="E232" s="3" t="s">
-        <v>28</v>
+        <v>298</v>
       </c>
       <c r="F232" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G232" s="3"/>
-      <c r="H232" s="3"/>
-      <c r="I232" s="3"/>
-      <c r="J232" s="3"/>
-      <c r="K232" s="3"/>
+        <v>34</v>
+      </c>
+      <c r="G232" s="4">
+        <v>99.6</v>
+      </c>
+      <c r="H232" s="4">
+        <v>99.6</v>
+      </c>
+      <c r="I232" s="4">
+        <v>99.6</v>
+      </c>
+      <c r="J232" s="4">
+        <v>99.6</v>
+      </c>
+      <c r="K232" s="4">
+        <v>99.6</v>
+      </c>
       <c r="L232" s="4">
-        <v>12.1</v>
+        <v>99.6</v>
       </c>
       <c r="M232" s="4">
-        <v>12.7</v>
+        <v>99.7</v>
       </c>
       <c r="N232" s="4">
-        <v>11.6</v>
+        <v>99.7</v>
       </c>
       <c r="O232" s="4">
-        <v>11.4</v>
+        <v>99.7</v>
       </c>
       <c r="P232" s="4">
-        <v>10.6</v>
+        <v>99.7</v>
       </c>
       <c r="Q232" s="4">
-        <v>9</v>
+        <v>99.8</v>
       </c>
       <c r="R232" s="4">
-        <v>7.8</v>
+        <v>99.8</v>
       </c>
       <c r="S232" s="4">
-        <v>7.6</v>
+        <v>99.8</v>
       </c>
       <c r="T232" s="4">
-        <v>7.6</v>
+        <v>99.8</v>
       </c>
       <c r="U232" s="4">
-        <v>7.7</v>
+        <v>99.8</v>
       </c>
       <c r="V232" s="3"/>
       <c r="W232" s="2" t="s">
-        <v>297</v>
+        <v>30</v>
       </c>
     </row>
     <row r="233" spans="1:23" ht="27" x14ac:dyDescent="0.25">
@@ -16294,73 +16278,73 @@
         <v>293</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>27</v>
+        <v>297</v>
       </c>
       <c r="E233" s="3" t="s">
-        <v>28</v>
+        <v>299</v>
       </c>
       <c r="F233" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G233" s="4">
-        <v>166.5</v>
+        <v>43.4</v>
       </c>
       <c r="H233" s="4">
-        <v>166.2</v>
+        <v>46.5</v>
       </c>
       <c r="I233" s="4">
-        <v>165.6</v>
+        <v>47.2</v>
       </c>
       <c r="J233" s="4">
-        <v>155.5</v>
+        <v>47.8</v>
       </c>
       <c r="K233" s="4">
-        <v>159.69999999999999</v>
+        <v>46.4</v>
       </c>
       <c r="L233" s="4">
-        <v>158.30000000000001</v>
+        <v>46.5</v>
       </c>
       <c r="M233" s="4">
-        <v>162.69999999999999</v>
+        <v>51.4</v>
       </c>
       <c r="N233" s="4">
-        <v>161.69999999999999</v>
+        <v>53.8</v>
       </c>
       <c r="O233" s="4">
-        <v>163.4</v>
+        <v>54</v>
       </c>
       <c r="P233" s="4">
-        <v>167.6</v>
+        <v>54.3</v>
       </c>
       <c r="Q233" s="4">
-        <v>99.3</v>
+        <v>58.5</v>
       </c>
       <c r="R233" s="4">
-        <v>110.1</v>
+        <v>61.4</v>
       </c>
       <c r="S233" s="4">
-        <v>135.6</v>
+        <v>60</v>
       </c>
       <c r="T233" s="4">
-        <v>144.6</v>
+        <v>62.3</v>
       </c>
       <c r="U233" s="4">
-        <v>152.19999999999999</v>
+        <v>59.6</v>
       </c>
       <c r="V233" s="3"/>
       <c r="W233" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="234" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
         <v>267</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="C234" s="2" t="s">
         <v>300</v>
@@ -16374,67 +16358,65 @@
       <c r="F234" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="G234" s="4">
-        <v>3.7</v>
-      </c>
-      <c r="H234" s="4">
-        <v>3.4</v>
-      </c>
-      <c r="I234" s="4">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="J234" s="4">
-        <v>3.8</v>
-      </c>
-      <c r="K234" s="4">
-        <v>3.9</v>
-      </c>
-      <c r="L234" s="4">
-        <v>3.9</v>
-      </c>
-      <c r="M234" s="4">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="N234" s="4">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="O234" s="4">
-        <v>5.4</v>
-      </c>
-      <c r="P234" s="4">
-        <v>6.1</v>
-      </c>
-      <c r="Q234" s="4">
-        <v>6.5</v>
-      </c>
-      <c r="R234" s="4">
-        <v>6.6</v>
-      </c>
-      <c r="S234" s="4">
-        <v>6.6</v>
-      </c>
-      <c r="T234" s="4">
-        <v>6.3</v>
-      </c>
-      <c r="U234" s="4">
-        <v>5.8</v>
-      </c>
-      <c r="V234" s="4">
+      <c r="G234" s="6">
         <v>6</v>
       </c>
+      <c r="H234" s="6">
+        <v>8</v>
+      </c>
+      <c r="I234" s="6">
+        <v>8</v>
+      </c>
+      <c r="J234" s="6">
+        <v>10</v>
+      </c>
+      <c r="K234" s="6">
+        <v>9</v>
+      </c>
+      <c r="L234" s="6">
+        <v>10</v>
+      </c>
+      <c r="M234" s="6">
+        <v>11</v>
+      </c>
+      <c r="N234" s="6">
+        <v>13</v>
+      </c>
+      <c r="O234" s="6">
+        <v>12</v>
+      </c>
+      <c r="P234" s="6">
+        <v>16</v>
+      </c>
+      <c r="Q234" s="6">
+        <v>21</v>
+      </c>
+      <c r="R234" s="6">
+        <v>24</v>
+      </c>
+      <c r="S234" s="6">
+        <v>25</v>
+      </c>
+      <c r="T234" s="6">
+        <v>26</v>
+      </c>
+      <c r="U234" s="6">
+        <v>21</v>
+      </c>
+      <c r="V234" s="3"/>
       <c r="W234" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="235" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="235" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D235" s="2" t="s">
         <v>27</v>
@@ -16443,69 +16425,67 @@
         <v>28</v>
       </c>
       <c r="F235" s="3" t="s">
-        <v>264</v>
+        <v>304</v>
       </c>
       <c r="G235" s="5">
-        <v>0.26</v>
+        <v>0.59</v>
       </c>
       <c r="H235" s="5">
-        <v>0.18</v>
+        <v>0.5</v>
       </c>
       <c r="I235" s="5">
-        <v>0.14000000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="J235" s="5">
-        <v>0.14000000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="K235" s="5">
-        <v>0.16</v>
+        <v>0.66</v>
       </c>
       <c r="L235" s="5">
-        <v>0.11</v>
+        <v>0.69</v>
       </c>
       <c r="M235" s="5">
-        <v>0.12</v>
+        <v>0.69</v>
       </c>
       <c r="N235" s="5">
-        <v>0.13</v>
+        <v>0.69</v>
       </c>
       <c r="O235" s="5">
-        <v>0.13</v>
+        <v>0.71</v>
       </c>
       <c r="P235" s="5">
-        <v>0.18</v>
+        <v>0.78</v>
       </c>
       <c r="Q235" s="5">
-        <v>0.11</v>
+        <v>0.77</v>
       </c>
       <c r="R235" s="5">
-        <v>0.1</v>
+        <v>0.81</v>
       </c>
       <c r="S235" s="5">
-        <v>0.09</v>
+        <v>0.85</v>
       </c>
       <c r="T235" s="5">
-        <v>0.13</v>
+        <v>0.9</v>
       </c>
       <c r="U235" s="5">
-        <v>0.18</v>
-      </c>
-      <c r="V235" s="5">
-        <v>0.25</v>
-      </c>
+        <v>0.97</v>
+      </c>
+      <c r="V235" s="3"/>
       <c r="W235" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="236" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="236" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D236" s="2" t="s">
         <v>27</v>
@@ -16514,49 +16494,67 @@
         <v>28</v>
       </c>
       <c r="F236" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="G236" s="3"/>
-      <c r="H236" s="3"/>
-      <c r="I236" s="3"/>
-      <c r="J236" s="3"/>
-      <c r="K236" s="3"/>
-      <c r="L236" s="3"/>
-      <c r="M236" s="3"/>
-      <c r="N236" s="3"/>
-      <c r="O236" s="3"/>
-      <c r="P236" s="6">
-        <v>74110</v>
-      </c>
-      <c r="Q236" s="6">
-        <v>68436</v>
-      </c>
-      <c r="R236" s="6">
-        <v>65117</v>
-      </c>
-      <c r="S236" s="6">
-        <v>64070</v>
-      </c>
-      <c r="T236" s="6">
-        <v>61349</v>
-      </c>
-      <c r="U236" s="6">
-        <v>59560</v>
+        <v>295</v>
+      </c>
+      <c r="G236" s="5">
+        <v>16.5</v>
+      </c>
+      <c r="H236" s="5">
+        <v>20.43</v>
+      </c>
+      <c r="I236" s="5">
+        <v>17.52</v>
+      </c>
+      <c r="J236" s="5">
+        <v>16.72</v>
+      </c>
+      <c r="K236" s="5">
+        <v>16.579999999999998</v>
+      </c>
+      <c r="L236" s="5">
+        <v>16.47</v>
+      </c>
+      <c r="M236" s="5">
+        <v>16.920000000000002</v>
+      </c>
+      <c r="N236" s="5">
+        <v>18.010000000000002</v>
+      </c>
+      <c r="O236" s="5">
+        <v>18.47</v>
+      </c>
+      <c r="P236" s="5">
+        <v>17.59</v>
+      </c>
+      <c r="Q236" s="5">
+        <v>17.579999999999998</v>
+      </c>
+      <c r="R236" s="5">
+        <v>18.25</v>
+      </c>
+      <c r="S236" s="5">
+        <v>18.309999999999999</v>
+      </c>
+      <c r="T236" s="5">
+        <v>17.34</v>
+      </c>
+      <c r="U236" s="5">
+        <v>16.68</v>
       </c>
       <c r="V236" s="3"/>
       <c r="W236" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="237" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="237" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D237" s="2" t="s">
         <v>27</v>
@@ -16565,51 +16563,67 @@
         <v>28</v>
       </c>
       <c r="F237" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="G237" s="3"/>
-      <c r="H237" s="3"/>
-      <c r="I237" s="3"/>
-      <c r="J237" s="6">
-        <v>546870</v>
-      </c>
-      <c r="K237" s="3"/>
-      <c r="L237" s="6">
-        <v>512116</v>
-      </c>
-      <c r="M237" s="6">
-        <v>501544</v>
-      </c>
-      <c r="N237" s="3"/>
-      <c r="O237" s="6">
-        <v>487452</v>
-      </c>
-      <c r="P237" s="3"/>
-      <c r="Q237" s="6">
-        <v>469607</v>
-      </c>
-      <c r="R237" s="3"/>
-      <c r="S237" s="6">
-        <v>457891</v>
-      </c>
-      <c r="T237" s="3"/>
-      <c r="U237" s="6">
-        <v>446959</v>
+        <v>34</v>
+      </c>
+      <c r="G237" s="4">
+        <v>11.1</v>
+      </c>
+      <c r="H237" s="4">
+        <v>9.4</v>
+      </c>
+      <c r="I237" s="4">
+        <v>11</v>
+      </c>
+      <c r="J237" s="4">
+        <v>12.2</v>
+      </c>
+      <c r="K237" s="4">
+        <v>13</v>
+      </c>
+      <c r="L237" s="4">
+        <v>11.9</v>
+      </c>
+      <c r="M237" s="4">
+        <v>10.6</v>
+      </c>
+      <c r="N237" s="4">
+        <v>10.4</v>
+      </c>
+      <c r="O237" s="4">
+        <v>10.5</v>
+      </c>
+      <c r="P237" s="4">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="Q237" s="4">
+        <v>7.4</v>
+      </c>
+      <c r="R237" s="4">
+        <v>7</v>
+      </c>
+      <c r="S237" s="4">
+        <v>6.7</v>
+      </c>
+      <c r="T237" s="4">
+        <v>7.8</v>
+      </c>
+      <c r="U237" s="4">
+        <v>7.7</v>
       </c>
       <c r="V237" s="3"/>
       <c r="W237" s="2" t="s">
-        <v>30</v>
+        <v>87</v>
       </c>
     </row>
     <row r="238" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D238" s="2" t="s">
         <v>27</v>
@@ -16618,67 +16632,61 @@
         <v>28</v>
       </c>
       <c r="F238" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="G238" s="6">
-        <v>22795</v>
-      </c>
-      <c r="H238" s="6">
-        <v>21359</v>
-      </c>
-      <c r="I238" s="6">
-        <v>20022</v>
-      </c>
-      <c r="J238" s="6">
-        <v>19636</v>
-      </c>
-      <c r="K238" s="6">
-        <v>18137</v>
-      </c>
-      <c r="L238" s="6">
-        <v>16793</v>
-      </c>
-      <c r="M238" s="6">
-        <v>15086</v>
-      </c>
-      <c r="N238" s="6">
-        <v>14505</v>
-      </c>
-      <c r="O238" s="6">
-        <v>14165</v>
-      </c>
-      <c r="P238" s="6">
-        <v>11466</v>
-      </c>
-      <c r="Q238" s="6">
-        <v>8767</v>
-      </c>
-      <c r="R238" s="6">
-        <v>8374</v>
-      </c>
-      <c r="S238" s="6">
-        <v>7344</v>
-      </c>
-      <c r="T238" s="6">
-        <v>5553</v>
-      </c>
-      <c r="U238" s="6">
-        <v>5297</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="G238" s="5">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="H238" s="5">
+        <v>2.48</v>
+      </c>
+      <c r="I238" s="5">
+        <v>3.05</v>
+      </c>
+      <c r="J238" s="5">
+        <v>3.37</v>
+      </c>
+      <c r="K238" s="5">
+        <v>3.82</v>
+      </c>
+      <c r="L238" s="5">
+        <v>3.45</v>
+      </c>
+      <c r="M238" s="5">
+        <v>2.96</v>
+      </c>
+      <c r="N238" s="5">
+        <v>2.62</v>
+      </c>
+      <c r="O238" s="5">
+        <v>2.48</v>
+      </c>
+      <c r="P238" s="5">
+        <v>2.66</v>
+      </c>
+      <c r="Q238" s="5">
+        <v>2.68</v>
+      </c>
+      <c r="R238" s="3"/>
+      <c r="S238" s="3"/>
+      <c r="T238" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="U238" s="3"/>
       <c r="V238" s="3"/>
       <c r="W238" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="239" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="239" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
-        <v>267</v>
+        <v>309</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="D239" s="2" t="s">
         <v>27</v>
@@ -16687,67 +16695,67 @@
         <v>28</v>
       </c>
       <c r="F239" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="G239" s="6">
-        <v>961</v>
-      </c>
-      <c r="H239" s="6">
-        <v>136730</v>
-      </c>
-      <c r="I239" s="6">
-        <v>11553</v>
-      </c>
-      <c r="J239" s="6">
-        <v>15701</v>
-      </c>
-      <c r="K239" s="6">
-        <v>2758</v>
-      </c>
-      <c r="L239" s="6">
-        <v>69422</v>
-      </c>
-      <c r="M239" s="6">
-        <v>44764</v>
-      </c>
-      <c r="N239" s="6">
-        <v>78118</v>
-      </c>
-      <c r="O239" s="6">
-        <v>14958</v>
-      </c>
-      <c r="P239" s="6">
-        <v>68943</v>
-      </c>
-      <c r="Q239" s="6">
-        <v>57788</v>
-      </c>
-      <c r="R239" s="6">
-        <v>27276</v>
-      </c>
-      <c r="S239" s="6">
-        <v>256675</v>
-      </c>
-      <c r="T239" s="6">
-        <v>211015</v>
-      </c>
-      <c r="U239" s="6">
-        <v>1435</v>
+        <v>312</v>
+      </c>
+      <c r="G239" s="4">
+        <v>100</v>
+      </c>
+      <c r="H239" s="4">
+        <v>99.8</v>
+      </c>
+      <c r="I239" s="4">
+        <v>97.5</v>
+      </c>
+      <c r="J239" s="4">
+        <v>96.3</v>
+      </c>
+      <c r="K239" s="4">
+        <v>92.6</v>
+      </c>
+      <c r="L239" s="4">
+        <v>93.6</v>
+      </c>
+      <c r="M239" s="4">
+        <v>96.8</v>
+      </c>
+      <c r="N239" s="4">
+        <v>100.7</v>
+      </c>
+      <c r="O239" s="4">
+        <v>100.5</v>
+      </c>
+      <c r="P239" s="4">
+        <v>95</v>
+      </c>
+      <c r="Q239" s="4">
+        <v>90.4</v>
+      </c>
+      <c r="R239" s="4">
+        <v>99</v>
+      </c>
+      <c r="S239" s="4">
+        <v>94.2</v>
+      </c>
+      <c r="T239" s="4">
+        <v>84.9</v>
+      </c>
+      <c r="U239" s="4">
+        <v>83.4</v>
       </c>
       <c r="V239" s="3"/>
       <c r="W239" s="2" t="s">
-        <v>30</v>
+        <v>313</v>
       </c>
     </row>
     <row r="240" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
-        <v>267</v>
+        <v>309</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="D240" s="2" t="s">
         <v>27</v>
@@ -16756,259 +16764,259 @@
         <v>28</v>
       </c>
       <c r="F240" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="G240" s="6">
-        <v>6</v>
-      </c>
-      <c r="H240" s="6">
-        <v>8</v>
-      </c>
-      <c r="I240" s="6">
-        <v>8</v>
-      </c>
-      <c r="J240" s="6">
-        <v>10</v>
-      </c>
-      <c r="K240" s="6">
-        <v>9</v>
-      </c>
-      <c r="L240" s="6">
-        <v>10</v>
-      </c>
-      <c r="M240" s="6">
-        <v>11</v>
-      </c>
-      <c r="N240" s="6">
-        <v>13</v>
-      </c>
-      <c r="O240" s="6">
-        <v>12</v>
-      </c>
-      <c r="P240" s="6">
-        <v>16</v>
-      </c>
-      <c r="Q240" s="6">
-        <v>21</v>
-      </c>
-      <c r="R240" s="6">
-        <v>24</v>
-      </c>
-      <c r="S240" s="6">
-        <v>25</v>
-      </c>
-      <c r="T240" s="6">
-        <v>26</v>
-      </c>
-      <c r="U240" s="6">
-        <v>21</v>
+        <v>315</v>
+      </c>
+      <c r="G240" s="4">
+        <v>100</v>
+      </c>
+      <c r="H240" s="4">
+        <v>99.7</v>
+      </c>
+      <c r="I240" s="4">
+        <v>97.8</v>
+      </c>
+      <c r="J240" s="4">
+        <v>96.7</v>
+      </c>
+      <c r="K240" s="4">
+        <v>93.6</v>
+      </c>
+      <c r="L240" s="4">
+        <v>94.3</v>
+      </c>
+      <c r="M240" s="4">
+        <v>96.9</v>
+      </c>
+      <c r="N240" s="4">
+        <v>100.5</v>
+      </c>
+      <c r="O240" s="4">
+        <v>100.4</v>
+      </c>
+      <c r="P240" s="4">
+        <v>94.9</v>
+      </c>
+      <c r="Q240" s="4">
+        <v>91.2</v>
+      </c>
+      <c r="R240" s="4">
+        <v>98.2</v>
+      </c>
+      <c r="S240" s="4">
+        <v>93.6</v>
+      </c>
+      <c r="T240" s="4">
+        <v>85.7</v>
+      </c>
+      <c r="U240" s="4">
+        <v>84.2</v>
       </c>
       <c r="V240" s="3"/>
       <c r="W240" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="241" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="241" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
         <v>309</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>27</v>
+        <v>187</v>
       </c>
       <c r="E241" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F241" s="3" t="s">
-        <v>312</v>
+        <v>34</v>
       </c>
       <c r="G241" s="5">
-        <v>0.59</v>
+        <v>9.2799999999999994</v>
       </c>
       <c r="H241" s="5">
-        <v>0.5</v>
+        <v>10.34</v>
       </c>
       <c r="I241" s="5">
-        <v>0.59</v>
+        <v>10.96</v>
       </c>
       <c r="J241" s="5">
-        <v>0.63</v>
+        <v>11.45</v>
       </c>
       <c r="K241" s="5">
-        <v>0.66</v>
+        <v>11.61</v>
       </c>
       <c r="L241" s="5">
-        <v>0.69</v>
+        <v>11.88</v>
       </c>
       <c r="M241" s="5">
-        <v>0.69</v>
+        <v>11.4</v>
       </c>
       <c r="N241" s="5">
-        <v>0.69</v>
+        <v>11.06</v>
       </c>
       <c r="O241" s="5">
-        <v>0.71</v>
+        <v>14.94</v>
       </c>
       <c r="P241" s="5">
-        <v>0.78</v>
+        <v>15.38</v>
       </c>
       <c r="Q241" s="5">
-        <v>0.77</v>
+        <v>16.100000000000001</v>
       </c>
       <c r="R241" s="5">
-        <v>0.81</v>
+        <v>15.6</v>
       </c>
       <c r="S241" s="5">
-        <v>0.85</v>
+        <v>16.64</v>
       </c>
       <c r="T241" s="5">
-        <v>0.9</v>
+        <v>16.649999999999999</v>
       </c>
       <c r="U241" s="5">
-        <v>0.97</v>
+        <v>17.77</v>
       </c>
       <c r="V241" s="3"/>
       <c r="W241" s="2" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="242" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
         <v>309</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>27</v>
+        <v>187</v>
       </c>
       <c r="E242" s="3" t="s">
-        <v>28</v>
+        <v>188</v>
       </c>
       <c r="F242" s="3" t="s">
-        <v>306</v>
+        <v>34</v>
       </c>
       <c r="G242" s="5">
-        <v>16.5</v>
+        <v>6.64</v>
       </c>
       <c r="H242" s="5">
-        <v>20.43</v>
+        <v>6.92</v>
       </c>
       <c r="I242" s="5">
-        <v>17.52</v>
+        <v>6.53</v>
       </c>
       <c r="J242" s="5">
-        <v>16.72</v>
+        <v>6.67</v>
       </c>
       <c r="K242" s="5">
-        <v>16.579999999999998</v>
+        <v>6.32</v>
       </c>
       <c r="L242" s="5">
-        <v>16.47</v>
+        <v>5.69</v>
       </c>
       <c r="M242" s="5">
-        <v>16.920000000000002</v>
+        <v>3.97</v>
       </c>
       <c r="N242" s="5">
-        <v>18.010000000000002</v>
+        <v>4.2300000000000004</v>
       </c>
       <c r="O242" s="5">
-        <v>18.47</v>
+        <v>5.72</v>
       </c>
       <c r="P242" s="5">
-        <v>17.59</v>
+        <v>6.2</v>
       </c>
       <c r="Q242" s="5">
-        <v>17.579999999999998</v>
+        <v>6.58</v>
       </c>
       <c r="R242" s="5">
-        <v>18.25</v>
+        <v>5.67</v>
       </c>
       <c r="S242" s="5">
-        <v>18.309999999999999</v>
+        <v>5.79</v>
       </c>
       <c r="T242" s="5">
-        <v>17.34</v>
+        <v>6.34</v>
       </c>
       <c r="U242" s="5">
-        <v>16.68</v>
+        <v>6.03</v>
       </c>
       <c r="V242" s="3"/>
       <c r="W242" s="2" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="243" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
         <v>309</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>27</v>
+        <v>187</v>
       </c>
       <c r="E243" s="3" t="s">
-        <v>28</v>
+        <v>189</v>
       </c>
       <c r="F243" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G243" s="4">
-        <v>11.1</v>
-      </c>
-      <c r="H243" s="4">
-        <v>9.4</v>
-      </c>
-      <c r="I243" s="4">
-        <v>11</v>
-      </c>
-      <c r="J243" s="4">
-        <v>12.2</v>
-      </c>
-      <c r="K243" s="4">
-        <v>13</v>
-      </c>
-      <c r="L243" s="4">
-        <v>11.9</v>
-      </c>
-      <c r="M243" s="4">
-        <v>10.6</v>
-      </c>
-      <c r="N243" s="4">
-        <v>10.4</v>
-      </c>
-      <c r="O243" s="4">
-        <v>10.5</v>
-      </c>
-      <c r="P243" s="4">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="Q243" s="4">
-        <v>7.4</v>
-      </c>
-      <c r="R243" s="4">
-        <v>7</v>
-      </c>
-      <c r="S243" s="4">
-        <v>6.7</v>
-      </c>
-      <c r="T243" s="4">
-        <v>7.8</v>
-      </c>
-      <c r="U243" s="4">
-        <v>7.7</v>
+      <c r="G243" s="5">
+        <v>6.55</v>
+      </c>
+      <c r="H243" s="5">
+        <v>8.08</v>
+      </c>
+      <c r="I243" s="5">
+        <v>10.61</v>
+      </c>
+      <c r="J243" s="5">
+        <v>10.68</v>
+      </c>
+      <c r="K243" s="5">
+        <v>12.36</v>
+      </c>
+      <c r="L243" s="5">
+        <v>13.4</v>
+      </c>
+      <c r="M243" s="5">
+        <v>13.34</v>
+      </c>
+      <c r="N243" s="5">
+        <v>13.08</v>
+      </c>
+      <c r="O243" s="5">
+        <v>13.03</v>
+      </c>
+      <c r="P243" s="5">
+        <v>14.36</v>
+      </c>
+      <c r="Q243" s="5">
+        <v>16.239999999999998</v>
+      </c>
+      <c r="R243" s="5">
+        <v>17.170000000000002</v>
+      </c>
+      <c r="S243" s="5">
+        <v>21.01</v>
+      </c>
+      <c r="T243" s="5">
+        <v>25.79</v>
+      </c>
+      <c r="U243" s="5">
+        <v>30.37</v>
       </c>
       <c r="V243" s="3"/>
       <c r="W243" s="2" t="s">
@@ -17020,694 +17028,698 @@
         <v>309</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>27</v>
+        <v>187</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>28</v>
+        <v>190</v>
       </c>
       <c r="F244" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G244" s="5">
-        <v>2.0699999999999998</v>
+        <v>11.81</v>
       </c>
       <c r="H244" s="5">
-        <v>2.48</v>
+        <v>13.24</v>
       </c>
       <c r="I244" s="5">
-        <v>3.05</v>
+        <v>13.5</v>
       </c>
       <c r="J244" s="5">
-        <v>3.37</v>
+        <v>14.27</v>
       </c>
       <c r="K244" s="5">
-        <v>3.82</v>
+        <v>14.24</v>
       </c>
       <c r="L244" s="5">
-        <v>3.45</v>
+        <v>14.8</v>
       </c>
       <c r="M244" s="5">
-        <v>2.96</v>
+        <v>14.92</v>
       </c>
       <c r="N244" s="5">
-        <v>2.62</v>
+        <v>14.78</v>
       </c>
       <c r="O244" s="5">
-        <v>2.48</v>
+        <v>21.47</v>
       </c>
       <c r="P244" s="5">
-        <v>2.66</v>
+        <v>22.01</v>
       </c>
       <c r="Q244" s="5">
-        <v>2.68</v>
-      </c>
-      <c r="R244" s="3"/>
-      <c r="S244" s="3"/>
+        <v>22.14</v>
+      </c>
+      <c r="R244" s="5">
+        <v>20.98</v>
+      </c>
+      <c r="S244" s="5">
+        <v>22.1</v>
+      </c>
       <c r="T244" s="5">
-        <v>3.1</v>
-      </c>
-      <c r="U244" s="3"/>
+        <v>20.61</v>
+      </c>
+      <c r="U244" s="5">
+        <v>21.29</v>
+      </c>
       <c r="V244" s="3"/>
       <c r="W244" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="245" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="245" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="B245" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C245" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="C245" s="2" t="s">
-        <v>319</v>
-      </c>
       <c r="D245" s="2" t="s">
-        <v>27</v>
+        <v>187</v>
       </c>
       <c r="E245" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F245" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="G245" s="4">
-        <v>100</v>
-      </c>
-      <c r="H245" s="4">
-        <v>99.8</v>
-      </c>
-      <c r="I245" s="4">
-        <v>97.5</v>
-      </c>
-      <c r="J245" s="4">
-        <v>96.3</v>
-      </c>
-      <c r="K245" s="4">
-        <v>92.6</v>
-      </c>
-      <c r="L245" s="4">
-        <v>93.6</v>
-      </c>
-      <c r="M245" s="4">
-        <v>96.8</v>
-      </c>
-      <c r="N245" s="4">
-        <v>100.7</v>
-      </c>
-      <c r="O245" s="4">
-        <v>100.5</v>
-      </c>
-      <c r="P245" s="4">
-        <v>95</v>
-      </c>
-      <c r="Q245" s="4">
-        <v>90.4</v>
-      </c>
-      <c r="R245" s="4">
-        <v>99</v>
-      </c>
-      <c r="S245" s="4">
-        <v>94.2</v>
-      </c>
-      <c r="T245" s="4">
-        <v>84.9</v>
-      </c>
-      <c r="U245" s="4">
-        <v>83.4</v>
+        <v>319</v>
+      </c>
+      <c r="G245" s="6">
+        <v>563</v>
+      </c>
+      <c r="H245" s="6">
+        <v>531</v>
+      </c>
+      <c r="I245" s="6">
+        <v>661</v>
+      </c>
+      <c r="J245" s="6">
+        <v>778</v>
+      </c>
+      <c r="K245" s="6">
+        <v>847</v>
+      </c>
+      <c r="L245" s="6">
+        <v>909</v>
+      </c>
+      <c r="M245" s="6">
+        <v>930</v>
+      </c>
+      <c r="N245" s="6">
+        <v>946</v>
+      </c>
+      <c r="O245" s="6">
+        <v>991</v>
+      </c>
+      <c r="P245" s="6">
+        <v>1050</v>
+      </c>
+      <c r="Q245" s="6">
+        <v>1073</v>
+      </c>
+      <c r="R245" s="6">
+        <v>1189</v>
+      </c>
+      <c r="S245" s="6">
+        <v>1318</v>
+      </c>
+      <c r="T245" s="6">
+        <v>1372</v>
+      </c>
+      <c r="U245" s="6">
+        <v>1556</v>
       </c>
       <c r="V245" s="3"/>
       <c r="W245" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="246" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="246" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="B246" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C246" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="C246" s="2" t="s">
-        <v>322</v>
-      </c>
       <c r="D246" s="2" t="s">
-        <v>27</v>
+        <v>187</v>
       </c>
       <c r="E246" s="3" t="s">
-        <v>28</v>
+        <v>320</v>
       </c>
       <c r="F246" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="G246" s="4">
-        <v>100</v>
-      </c>
-      <c r="H246" s="4">
-        <v>99.7</v>
-      </c>
-      <c r="I246" s="4">
-        <v>97.8</v>
-      </c>
-      <c r="J246" s="4">
-        <v>96.7</v>
-      </c>
-      <c r="K246" s="4">
-        <v>93.6</v>
-      </c>
-      <c r="L246" s="4">
-        <v>94.3</v>
-      </c>
-      <c r="M246" s="4">
-        <v>96.9</v>
-      </c>
-      <c r="N246" s="4">
-        <v>100.5</v>
-      </c>
-      <c r="O246" s="4">
-        <v>100.4</v>
-      </c>
-      <c r="P246" s="4">
-        <v>94.9</v>
-      </c>
-      <c r="Q246" s="4">
-        <v>91.2</v>
-      </c>
-      <c r="R246" s="4">
-        <v>98.2</v>
-      </c>
-      <c r="S246" s="4">
-        <v>93.6</v>
-      </c>
-      <c r="T246" s="4">
-        <v>85.7</v>
-      </c>
-      <c r="U246" s="4">
-        <v>84.2</v>
+        <v>319</v>
+      </c>
+      <c r="G246" s="6">
+        <v>440</v>
+      </c>
+      <c r="H246" s="6">
+        <v>101</v>
+      </c>
+      <c r="I246" s="6">
+        <v>151</v>
+      </c>
+      <c r="J246" s="6">
+        <v>217</v>
+      </c>
+      <c r="K246" s="6">
+        <v>239</v>
+      </c>
+      <c r="L246" s="6">
+        <v>674</v>
+      </c>
+      <c r="M246" s="6">
+        <v>705</v>
+      </c>
+      <c r="N246" s="6">
+        <v>712</v>
+      </c>
+      <c r="O246" s="6">
+        <v>743</v>
+      </c>
+      <c r="P246" s="6">
+        <v>788</v>
+      </c>
+      <c r="Q246" s="6">
+        <v>805</v>
+      </c>
+      <c r="R246" s="6">
+        <v>892</v>
+      </c>
+      <c r="S246" s="6">
+        <v>988</v>
+      </c>
+      <c r="T246" s="6">
+        <v>1029</v>
+      </c>
+      <c r="U246" s="6">
+        <v>1167</v>
       </c>
       <c r="V246" s="3"/>
       <c r="W246" s="2" t="s">
-        <v>321</v>
+        <v>30</v>
       </c>
     </row>
     <row r="247" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="D247" s="2" t="s">
         <v>187</v>
       </c>
       <c r="E247" s="3" t="s">
-        <v>28</v>
+        <v>321</v>
       </c>
       <c r="F247" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G247" s="5">
-        <v>9.2799999999999994</v>
-      </c>
-      <c r="H247" s="5">
-        <v>10.34</v>
-      </c>
-      <c r="I247" s="5">
-        <v>10.96</v>
-      </c>
-      <c r="J247" s="5">
-        <v>11.45</v>
-      </c>
-      <c r="K247" s="5">
-        <v>11.61</v>
-      </c>
-      <c r="L247" s="5">
-        <v>11.88</v>
-      </c>
-      <c r="M247" s="5">
-        <v>11.4</v>
-      </c>
-      <c r="N247" s="5">
-        <v>11.06</v>
-      </c>
-      <c r="O247" s="5">
-        <v>14.94</v>
-      </c>
-      <c r="P247" s="5">
-        <v>15.38</v>
-      </c>
-      <c r="Q247" s="5">
-        <v>16.100000000000001</v>
-      </c>
-      <c r="R247" s="5">
-        <v>15.6</v>
-      </c>
-      <c r="S247" s="5">
-        <v>16.64</v>
-      </c>
-      <c r="T247" s="5">
-        <v>16.649999999999999</v>
-      </c>
-      <c r="U247" s="5">
-        <v>17.77</v>
+        <v>319</v>
+      </c>
+      <c r="G247" s="6">
+        <v>123</v>
+      </c>
+      <c r="H247" s="6">
+        <v>101</v>
+      </c>
+      <c r="I247" s="6">
+        <v>151</v>
+      </c>
+      <c r="J247" s="6">
+        <v>217</v>
+      </c>
+      <c r="K247" s="6">
+        <v>239</v>
+      </c>
+      <c r="L247" s="6">
+        <v>235</v>
+      </c>
+      <c r="M247" s="6">
+        <v>225</v>
+      </c>
+      <c r="N247" s="6">
+        <v>234</v>
+      </c>
+      <c r="O247" s="6">
+        <v>248</v>
+      </c>
+      <c r="P247" s="6">
+        <v>263</v>
+      </c>
+      <c r="Q247" s="6">
+        <v>268</v>
+      </c>
+      <c r="R247" s="6">
+        <v>297</v>
+      </c>
+      <c r="S247" s="6">
+        <v>329</v>
+      </c>
+      <c r="T247" s="6">
+        <v>343</v>
+      </c>
+      <c r="U247" s="6">
+        <v>389</v>
       </c>
       <c r="V247" s="3"/>
       <c r="W247" s="2" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
     </row>
     <row r="248" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="B248" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C248" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D248" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E248" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F248" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="G248" s="6">
+        <v>2218</v>
+      </c>
+      <c r="H248" s="6">
+        <v>3117</v>
+      </c>
+      <c r="I248" s="6">
+        <v>4139</v>
+      </c>
+      <c r="J248" s="6">
+        <v>5205</v>
+      </c>
+      <c r="K248" s="6">
+        <v>5793</v>
+      </c>
+      <c r="L248" s="6">
+        <v>7105</v>
+      </c>
+      <c r="M248" s="6">
+        <v>8017</v>
+      </c>
+      <c r="N248" s="6">
+        <v>8195</v>
+      </c>
+      <c r="O248" s="6">
+        <v>8486</v>
+      </c>
+      <c r="P248" s="6">
+        <v>9547</v>
+      </c>
+      <c r="Q248" s="6">
+        <v>12490</v>
+      </c>
+      <c r="R248" s="6">
+        <v>16935</v>
+      </c>
+      <c r="S248" s="6">
+        <v>22670</v>
+      </c>
+      <c r="T248" s="6">
+        <v>28779</v>
+      </c>
+      <c r="U248" s="6">
+        <v>33623</v>
+      </c>
+      <c r="V248" s="6">
+        <v>37777</v>
+      </c>
+      <c r="W248" s="2" t="s">
         <v>324</v>
-      </c>
-      <c r="C248" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="D248" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="E248" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="F248" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G248" s="5">
-        <v>6.64</v>
-      </c>
-      <c r="H248" s="5">
-        <v>6.92</v>
-      </c>
-      <c r="I248" s="5">
-        <v>6.53</v>
-      </c>
-      <c r="J248" s="5">
-        <v>6.67</v>
-      </c>
-      <c r="K248" s="5">
-        <v>6.32</v>
-      </c>
-      <c r="L248" s="5">
-        <v>5.69</v>
-      </c>
-      <c r="M248" s="5">
-        <v>3.97</v>
-      </c>
-      <c r="N248" s="5">
-        <v>4.2300000000000004</v>
-      </c>
-      <c r="O248" s="5">
-        <v>5.72</v>
-      </c>
-      <c r="P248" s="5">
-        <v>6.2</v>
-      </c>
-      <c r="Q248" s="5">
-        <v>6.58</v>
-      </c>
-      <c r="R248" s="5">
-        <v>5.67</v>
-      </c>
-      <c r="S248" s="5">
-        <v>5.79</v>
-      </c>
-      <c r="T248" s="5">
-        <v>6.34</v>
-      </c>
-      <c r="U248" s="5">
-        <v>6.03</v>
-      </c>
-      <c r="V248" s="3"/>
-      <c r="W248" s="2" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="249" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>187</v>
+        <v>27</v>
       </c>
       <c r="E249" s="3" t="s">
-        <v>189</v>
+        <v>28</v>
       </c>
       <c r="F249" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G249" s="5">
-        <v>6.55</v>
-      </c>
-      <c r="H249" s="5">
-        <v>8.08</v>
-      </c>
-      <c r="I249" s="5">
-        <v>10.61</v>
-      </c>
-      <c r="J249" s="5">
-        <v>10.68</v>
-      </c>
-      <c r="K249" s="5">
-        <v>12.36</v>
-      </c>
-      <c r="L249" s="5">
-        <v>13.4</v>
-      </c>
-      <c r="M249" s="5">
-        <v>13.34</v>
-      </c>
-      <c r="N249" s="5">
-        <v>13.08</v>
-      </c>
-      <c r="O249" s="5">
-        <v>13.03</v>
-      </c>
-      <c r="P249" s="5">
-        <v>14.36</v>
-      </c>
-      <c r="Q249" s="5">
-        <v>16.239999999999998</v>
-      </c>
-      <c r="R249" s="5">
-        <v>17.170000000000002</v>
-      </c>
-      <c r="S249" s="5">
-        <v>21.01</v>
-      </c>
-      <c r="T249" s="5">
-        <v>25.79</v>
-      </c>
-      <c r="U249" s="5">
-        <v>30.37</v>
-      </c>
+      <c r="G249" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="H249" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="I249" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="J249" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="K249" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="L249" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="M249" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="N249" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="O249" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="P249" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="Q249" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="R249" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="S249" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="T249" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="U249" s="3"/>
       <c r="V249" s="3"/>
       <c r="W249" s="2" t="s">
-        <v>87</v>
+        <v>27</v>
       </c>
     </row>
     <row r="250" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>187</v>
+        <v>27</v>
       </c>
       <c r="E250" s="3" t="s">
-        <v>190</v>
+        <v>328</v>
       </c>
       <c r="F250" s="3" t="s">
-        <v>34</v>
+        <v>329</v>
       </c>
       <c r="G250" s="5">
-        <v>11.81</v>
+        <v>137.94999999999999</v>
       </c>
       <c r="H250" s="5">
-        <v>13.24</v>
+        <v>0</v>
       </c>
       <c r="I250" s="5">
-        <v>13.5</v>
+        <v>0.18</v>
       </c>
       <c r="J250" s="5">
-        <v>14.27</v>
+        <v>0</v>
       </c>
       <c r="K250" s="5">
-        <v>14.24</v>
+        <v>0</v>
       </c>
       <c r="L250" s="5">
-        <v>14.8</v>
+        <v>0</v>
       </c>
       <c r="M250" s="5">
-        <v>14.92</v>
+        <v>0</v>
       </c>
       <c r="N250" s="5">
-        <v>14.78</v>
+        <v>2.29</v>
       </c>
       <c r="O250" s="5">
-        <v>21.47</v>
+        <v>25.44</v>
       </c>
       <c r="P250" s="5">
-        <v>22.01</v>
+        <v>0</v>
       </c>
       <c r="Q250" s="5">
-        <v>22.14</v>
+        <v>12.02</v>
       </c>
       <c r="R250" s="5">
-        <v>20.98</v>
+        <v>0.89</v>
       </c>
       <c r="S250" s="5">
-        <v>22.1</v>
+        <v>0.03</v>
       </c>
       <c r="T250" s="5">
-        <v>20.61</v>
+        <v>0.03</v>
       </c>
       <c r="U250" s="5">
-        <v>21.29</v>
+        <v>80.36</v>
       </c>
       <c r="V250" s="3"/>
       <c r="W250" s="2" t="s">
-        <v>87</v>
+        <v>27</v>
       </c>
     </row>
     <row r="251" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>187</v>
+        <v>27</v>
       </c>
       <c r="E251" s="3" t="s">
-        <v>28</v>
+        <v>330</v>
       </c>
       <c r="F251" s="3" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G251" s="6">
-        <v>563</v>
+        <v>5248</v>
       </c>
       <c r="H251" s="6">
-        <v>531</v>
+        <v>0</v>
       </c>
       <c r="I251" s="6">
-        <v>661</v>
+        <v>7</v>
       </c>
       <c r="J251" s="6">
-        <v>778</v>
+        <v>0</v>
       </c>
       <c r="K251" s="6">
-        <v>847</v>
+        <v>0</v>
       </c>
       <c r="L251" s="6">
-        <v>909</v>
+        <v>0</v>
       </c>
       <c r="M251" s="6">
-        <v>930</v>
+        <v>0</v>
       </c>
       <c r="N251" s="6">
-        <v>946</v>
+        <v>87</v>
       </c>
       <c r="O251" s="6">
-        <v>991</v>
+        <v>966</v>
       </c>
       <c r="P251" s="6">
-        <v>1050</v>
+        <v>0</v>
       </c>
       <c r="Q251" s="6">
-        <v>1073</v>
+        <v>451</v>
       </c>
       <c r="R251" s="6">
-        <v>1189</v>
+        <v>33</v>
       </c>
       <c r="S251" s="6">
-        <v>1318</v>
+        <v>1</v>
       </c>
       <c r="T251" s="6">
-        <v>1372</v>
+        <v>1</v>
       </c>
       <c r="U251" s="6">
-        <v>1556</v>
+        <v>2938</v>
       </c>
       <c r="V251" s="3"/>
       <c r="W251" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="252" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="252" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>187</v>
+        <v>27</v>
       </c>
       <c r="E252" s="3" t="s">
-        <v>328</v>
+        <v>28</v>
       </c>
       <c r="F252" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="G252" s="6">
-        <v>440</v>
-      </c>
-      <c r="H252" s="6">
-        <v>101</v>
-      </c>
-      <c r="I252" s="6">
-        <v>151</v>
-      </c>
-      <c r="J252" s="6">
-        <v>217</v>
-      </c>
-      <c r="K252" s="6">
-        <v>239</v>
-      </c>
-      <c r="L252" s="6">
-        <v>674</v>
-      </c>
-      <c r="M252" s="6">
-        <v>705</v>
-      </c>
-      <c r="N252" s="6">
-        <v>712</v>
-      </c>
-      <c r="O252" s="6">
-        <v>743</v>
-      </c>
-      <c r="P252" s="6">
-        <v>788</v>
-      </c>
-      <c r="Q252" s="6">
-        <v>805</v>
-      </c>
-      <c r="R252" s="6">
-        <v>892</v>
-      </c>
-      <c r="S252" s="6">
-        <v>988</v>
-      </c>
-      <c r="T252" s="6">
-        <v>1029</v>
-      </c>
-      <c r="U252" s="6">
-        <v>1167</v>
+        <v>34</v>
+      </c>
+      <c r="G252" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="H252" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="I252" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J252" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="K252" s="5">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="L252" s="5">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="M252" s="5">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="N252" s="5">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="O252" s="5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="P252" s="5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="Q252" s="5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="R252" s="5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="S252" s="5">
+        <v>0.59</v>
+      </c>
+      <c r="T252" s="5">
+        <v>0.59</v>
+      </c>
+      <c r="U252" s="5">
+        <v>0.59</v>
       </c>
       <c r="V252" s="3"/>
       <c r="W252" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="253" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>187</v>
+        <v>27</v>
       </c>
       <c r="E253" s="3" t="s">
-        <v>329</v>
+        <v>28</v>
       </c>
       <c r="F253" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="G253" s="6">
-        <v>123</v>
-      </c>
-      <c r="H253" s="6">
-        <v>101</v>
-      </c>
-      <c r="I253" s="6">
-        <v>151</v>
-      </c>
-      <c r="J253" s="6">
-        <v>217</v>
-      </c>
-      <c r="K253" s="6">
-        <v>239</v>
-      </c>
-      <c r="L253" s="6">
-        <v>235</v>
-      </c>
-      <c r="M253" s="6">
-        <v>225</v>
-      </c>
-      <c r="N253" s="6">
-        <v>234</v>
-      </c>
-      <c r="O253" s="6">
-        <v>248</v>
-      </c>
-      <c r="P253" s="6">
-        <v>263</v>
-      </c>
-      <c r="Q253" s="6">
-        <v>268</v>
-      </c>
-      <c r="R253" s="6">
-        <v>297</v>
-      </c>
-      <c r="S253" s="6">
-        <v>329</v>
-      </c>
-      <c r="T253" s="6">
-        <v>343</v>
-      </c>
-      <c r="U253" s="6">
-        <v>389</v>
+        <v>169</v>
+      </c>
+      <c r="G253" s="4">
+        <v>732401.6</v>
+      </c>
+      <c r="H253" s="4">
+        <v>740630</v>
+      </c>
+      <c r="I253" s="4">
+        <v>753624</v>
+      </c>
+      <c r="J253" s="4">
+        <v>752240.3</v>
+      </c>
+      <c r="K253" s="4">
+        <v>804401.8</v>
+      </c>
+      <c r="L253" s="4">
+        <v>830309.8</v>
+      </c>
+      <c r="M253" s="4">
+        <v>826034.2</v>
+      </c>
+      <c r="N253" s="3"/>
+      <c r="O253" s="4">
+        <v>846693.5</v>
+      </c>
+      <c r="P253" s="4">
+        <v>839607.4</v>
+      </c>
+      <c r="Q253" s="4">
+        <v>852978.8</v>
+      </c>
+      <c r="R253" s="4">
+        <v>855928.1</v>
+      </c>
+      <c r="S253" s="4">
+        <v>859996.9</v>
+      </c>
+      <c r="T253" s="4">
+        <v>870987.2</v>
+      </c>
+      <c r="U253" s="4">
+        <v>881284.3</v>
       </c>
       <c r="V253" s="3"/>
       <c r="W253" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="254" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="254" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D254" s="2" t="s">
         <v>27</v>
@@ -17716,69 +17728,59 @@
         <v>28</v>
       </c>
       <c r="F254" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="G254" s="6">
-        <v>2218</v>
-      </c>
-      <c r="H254" s="6">
-        <v>3117</v>
-      </c>
-      <c r="I254" s="6">
-        <v>4139</v>
-      </c>
-      <c r="J254" s="6">
-        <v>5205</v>
-      </c>
-      <c r="K254" s="6">
-        <v>5793</v>
-      </c>
-      <c r="L254" s="6">
-        <v>7105</v>
-      </c>
-      <c r="M254" s="6">
-        <v>8017</v>
-      </c>
-      <c r="N254" s="6">
-        <v>8195</v>
-      </c>
-      <c r="O254" s="6">
-        <v>8486</v>
-      </c>
-      <c r="P254" s="6">
-        <v>9547</v>
-      </c>
-      <c r="Q254" s="6">
-        <v>12490</v>
-      </c>
-      <c r="R254" s="6">
-        <v>16935</v>
-      </c>
-      <c r="S254" s="6">
-        <v>22670</v>
-      </c>
-      <c r="T254" s="6">
-        <v>28779</v>
-      </c>
-      <c r="U254" s="6">
-        <v>33623</v>
-      </c>
-      <c r="V254" s="6">
-        <v>37777</v>
+        <v>335</v>
+      </c>
+      <c r="G254" s="3"/>
+      <c r="H254" s="3"/>
+      <c r="I254" s="3"/>
+      <c r="J254" s="3"/>
+      <c r="K254" s="3"/>
+      <c r="L254" s="5">
+        <v>6.6</v>
+      </c>
+      <c r="M254" s="5">
+        <v>7.58</v>
+      </c>
+      <c r="N254" s="5">
+        <v>7.54</v>
+      </c>
+      <c r="O254" s="5">
+        <v>10.15</v>
+      </c>
+      <c r="P254" s="5">
+        <v>12.38</v>
+      </c>
+      <c r="Q254" s="5">
+        <v>12.53</v>
+      </c>
+      <c r="R254" s="5">
+        <v>5.95</v>
+      </c>
+      <c r="S254" s="5">
+        <v>4.7300000000000004</v>
+      </c>
+      <c r="T254" s="5">
+        <v>6.25</v>
+      </c>
+      <c r="U254" s="5">
+        <v>5.6</v>
+      </c>
+      <c r="V254" s="5">
+        <v>5.95</v>
       </c>
       <c r="W254" s="2" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="255" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="255" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D255" s="2" t="s">
         <v>27</v>
@@ -17789,453 +17791,423 @@
       <c r="F255" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G255" s="4">
-        <v>0.4</v>
-      </c>
-      <c r="H255" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="I255" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="J255" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="K255" s="4">
-        <v>0.7</v>
-      </c>
-      <c r="L255" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="M255" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="N255" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="O255" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="P255" s="4">
-        <v>0.7</v>
-      </c>
-      <c r="Q255" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="R255" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="S255" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="T255" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="U255" s="3"/>
-      <c r="V255" s="3"/>
+      <c r="G255" s="3"/>
+      <c r="H255" s="3"/>
+      <c r="I255" s="3"/>
+      <c r="J255" s="3"/>
+      <c r="K255" s="3"/>
+      <c r="L255" s="3"/>
+      <c r="M255" s="3"/>
+      <c r="N255" s="3"/>
+      <c r="O255" s="6">
+        <v>1</v>
+      </c>
+      <c r="P255" s="6">
+        <v>54</v>
+      </c>
+      <c r="Q255" s="6">
+        <v>63</v>
+      </c>
+      <c r="R255" s="6">
+        <v>66</v>
+      </c>
+      <c r="S255" s="6">
+        <v>70</v>
+      </c>
+      <c r="T255" s="6">
+        <v>75</v>
+      </c>
+      <c r="U255" s="6">
+        <v>80</v>
+      </c>
+      <c r="V255" s="6">
+        <v>86</v>
+      </c>
       <c r="W255" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="256" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="256" spans="1:23" ht="99" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="D256" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E256" s="3" t="s">
-        <v>336</v>
+        <v>28</v>
       </c>
       <c r="F256" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="G256" s="5">
-        <v>137.94999999999999</v>
-      </c>
-      <c r="H256" s="5">
-        <v>0</v>
-      </c>
-      <c r="I256" s="5">
-        <v>0.18</v>
-      </c>
-      <c r="J256" s="5">
-        <v>0</v>
-      </c>
-      <c r="K256" s="5">
-        <v>0</v>
-      </c>
-      <c r="L256" s="5">
-        <v>0</v>
-      </c>
-      <c r="M256" s="5">
-        <v>0</v>
-      </c>
-      <c r="N256" s="5">
-        <v>2.29</v>
-      </c>
-      <c r="O256" s="5">
-        <v>25.44</v>
-      </c>
-      <c r="P256" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q256" s="5">
-        <v>12.02</v>
-      </c>
-      <c r="R256" s="5">
-        <v>0.89</v>
-      </c>
-      <c r="S256" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="T256" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="U256" s="5">
-        <v>80.36</v>
-      </c>
-      <c r="V256" s="3"/>
+        <v>264</v>
+      </c>
+      <c r="G256" s="3"/>
+      <c r="H256" s="3"/>
+      <c r="I256" s="3"/>
+      <c r="J256" s="3"/>
+      <c r="K256" s="3"/>
+      <c r="L256" s="3"/>
+      <c r="M256" s="3"/>
+      <c r="N256" s="3"/>
+      <c r="O256" s="3"/>
+      <c r="P256" s="3"/>
+      <c r="Q256" s="3"/>
+      <c r="R256" s="3"/>
+      <c r="S256" s="6">
+        <v>16</v>
+      </c>
+      <c r="T256" s="6">
+        <v>7</v>
+      </c>
+      <c r="U256" s="6">
+        <v>6</v>
+      </c>
+      <c r="V256" s="6">
+        <v>4</v>
+      </c>
       <c r="W256" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="257" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="257" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="D257" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E257" s="3" t="s">
-        <v>338</v>
+        <v>28</v>
       </c>
       <c r="F257" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="G257" s="6">
-        <v>5248</v>
-      </c>
-      <c r="H257" s="6">
-        <v>0</v>
-      </c>
-      <c r="I257" s="6">
-        <v>7</v>
-      </c>
-      <c r="J257" s="6">
-        <v>0</v>
-      </c>
-      <c r="K257" s="6">
-        <v>0</v>
-      </c>
-      <c r="L257" s="6">
-        <v>0</v>
-      </c>
-      <c r="M257" s="6">
-        <v>0</v>
-      </c>
-      <c r="N257" s="6">
-        <v>87</v>
-      </c>
-      <c r="O257" s="6">
-        <v>966</v>
-      </c>
-      <c r="P257" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q257" s="6">
-        <v>451</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="G257" s="3"/>
+      <c r="H257" s="3"/>
+      <c r="I257" s="3"/>
+      <c r="J257" s="3"/>
+      <c r="K257" s="3"/>
+      <c r="L257" s="3"/>
+      <c r="M257" s="3"/>
+      <c r="N257" s="3"/>
+      <c r="O257" s="3"/>
+      <c r="P257" s="3"/>
+      <c r="Q257" s="3"/>
       <c r="R257" s="6">
-        <v>33</v>
+        <v>133</v>
       </c>
       <c r="S257" s="6">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="T257" s="6">
-        <v>1</v>
+        <v>97</v>
       </c>
       <c r="U257" s="6">
-        <v>2938</v>
-      </c>
-      <c r="V257" s="3"/>
+        <v>44</v>
+      </c>
+      <c r="V257" s="6">
+        <v>89</v>
+      </c>
       <c r="W257" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="258" spans="1:23" ht="18" x14ac:dyDescent="0.25">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="258" spans="1:23" ht="72" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
-        <v>317</v>
+        <v>345</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>27</v>
+        <v>348</v>
       </c>
       <c r="E258" s="3" t="s">
-        <v>28</v>
+        <v>349</v>
       </c>
       <c r="F258" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G258" s="5">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="H258" s="5">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="I258" s="5">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="J258" s="5">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="K258" s="5">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="L258" s="5">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="M258" s="5">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="N258" s="5">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="O258" s="5">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="P258" s="5">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="Q258" s="5">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="R258" s="5">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="S258" s="5">
-        <v>0.59</v>
-      </c>
-      <c r="T258" s="5">
-        <v>0.59</v>
-      </c>
-      <c r="U258" s="5">
-        <v>0.59</v>
+      <c r="G258" s="6">
+        <v>40</v>
+      </c>
+      <c r="H258" s="6">
+        <v>60</v>
+      </c>
+      <c r="I258" s="6">
+        <v>40</v>
+      </c>
+      <c r="J258" s="6">
+        <v>40</v>
+      </c>
+      <c r="K258" s="6">
+        <v>40</v>
+      </c>
+      <c r="L258" s="6">
+        <v>40</v>
+      </c>
+      <c r="M258" s="6">
+        <v>60</v>
+      </c>
+      <c r="N258" s="6">
+        <v>40</v>
+      </c>
+      <c r="O258" s="6">
+        <v>40</v>
+      </c>
+      <c r="P258" s="6">
+        <v>40</v>
+      </c>
+      <c r="Q258" s="6">
+        <v>60</v>
+      </c>
+      <c r="R258" s="6">
+        <v>67</v>
+      </c>
+      <c r="S258" s="6">
+        <v>50</v>
+      </c>
+      <c r="T258" s="6">
+        <v>67</v>
+      </c>
+      <c r="U258" s="6">
+        <v>67</v>
       </c>
       <c r="V258" s="3"/>
       <c r="W258" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="259" spans="1:23" ht="18" x14ac:dyDescent="0.25">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="259" spans="1:23" ht="72" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
-        <v>317</v>
+        <v>345</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>27</v>
+        <v>348</v>
       </c>
       <c r="E259" s="3" t="s">
-        <v>28</v>
+        <v>351</v>
       </c>
       <c r="F259" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="G259" s="4">
-        <v>732401.6</v>
-      </c>
-      <c r="H259" s="4">
-        <v>740630</v>
-      </c>
-      <c r="I259" s="4">
-        <v>753624</v>
-      </c>
-      <c r="J259" s="4">
-        <v>752240.3</v>
-      </c>
-      <c r="K259" s="4">
-        <v>804401.8</v>
-      </c>
-      <c r="L259" s="4">
-        <v>830309.8</v>
-      </c>
-      <c r="M259" s="4">
-        <v>826034.2</v>
-      </c>
-      <c r="N259" s="3"/>
-      <c r="O259" s="4">
-        <v>846693.5</v>
-      </c>
-      <c r="P259" s="4">
-        <v>839607.4</v>
-      </c>
-      <c r="Q259" s="4">
-        <v>852978.8</v>
-      </c>
-      <c r="R259" s="4">
-        <v>855928.1</v>
-      </c>
-      <c r="S259" s="4">
-        <v>859996.9</v>
-      </c>
-      <c r="T259" s="4">
-        <v>870987.2</v>
-      </c>
-      <c r="U259" s="4">
-        <v>881284.3</v>
+        <v>34</v>
+      </c>
+      <c r="G259" s="6">
+        <v>40</v>
+      </c>
+      <c r="H259" s="6">
+        <v>60</v>
+      </c>
+      <c r="I259" s="6">
+        <v>20</v>
+      </c>
+      <c r="J259" s="6">
+        <v>20</v>
+      </c>
+      <c r="K259" s="6">
+        <v>20</v>
+      </c>
+      <c r="L259" s="6">
+        <v>40</v>
+      </c>
+      <c r="M259" s="6">
+        <v>60</v>
+      </c>
+      <c r="N259" s="6">
+        <v>40</v>
+      </c>
+      <c r="O259" s="6">
+        <v>25</v>
+      </c>
+      <c r="P259" s="6">
+        <v>25</v>
+      </c>
+      <c r="Q259" s="6">
+        <v>20</v>
+      </c>
+      <c r="R259" s="6">
+        <v>17</v>
+      </c>
+      <c r="S259" s="6">
+        <v>0</v>
+      </c>
+      <c r="T259" s="6">
+        <v>17</v>
+      </c>
+      <c r="U259" s="6">
+        <v>0</v>
       </c>
       <c r="V259" s="3"/>
       <c r="W259" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="260" spans="1:23" ht="18" x14ac:dyDescent="0.25">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="260" spans="1:23" ht="72" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
-        <v>317</v>
+        <v>345</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>27</v>
+        <v>348</v>
       </c>
       <c r="E260" s="3" t="s">
-        <v>28</v>
+        <v>352</v>
       </c>
       <c r="F260" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="G260" s="3"/>
-      <c r="H260" s="3"/>
-      <c r="I260" s="3"/>
-      <c r="J260" s="3"/>
-      <c r="K260" s="3"/>
-      <c r="L260" s="5">
-        <v>6.6</v>
-      </c>
-      <c r="M260" s="5">
-        <v>7.58</v>
-      </c>
-      <c r="N260" s="5">
-        <v>7.54</v>
-      </c>
-      <c r="O260" s="5">
-        <v>10.15</v>
-      </c>
-      <c r="P260" s="5">
-        <v>12.38</v>
-      </c>
-      <c r="Q260" s="5">
-        <v>12.53</v>
-      </c>
-      <c r="R260" s="5">
-        <v>5.95</v>
-      </c>
-      <c r="S260" s="5">
-        <v>4.7300000000000004</v>
-      </c>
-      <c r="T260" s="5">
-        <v>6.25</v>
-      </c>
-      <c r="U260" s="5">
-        <v>5.6</v>
-      </c>
-      <c r="V260" s="5">
-        <v>5.95</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="G260" s="6">
+        <v>0</v>
+      </c>
+      <c r="H260" s="6">
+        <v>0</v>
+      </c>
+      <c r="I260" s="6">
+        <v>20</v>
+      </c>
+      <c r="J260" s="6">
+        <v>20</v>
+      </c>
+      <c r="K260" s="6">
+        <v>20</v>
+      </c>
+      <c r="L260" s="6">
+        <v>0</v>
+      </c>
+      <c r="M260" s="6">
+        <v>0</v>
+      </c>
+      <c r="N260" s="6">
+        <v>0</v>
+      </c>
+      <c r="O260" s="6">
+        <v>0</v>
+      </c>
+      <c r="P260" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q260" s="6">
+        <v>40</v>
+      </c>
+      <c r="R260" s="6">
+        <v>17</v>
+      </c>
+      <c r="S260" s="6">
+        <v>17</v>
+      </c>
+      <c r="T260" s="6">
+        <v>17</v>
+      </c>
+      <c r="U260" s="6">
+        <v>50</v>
+      </c>
+      <c r="V260" s="3"/>
       <c r="W260" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="261" spans="1:23" ht="18" x14ac:dyDescent="0.25">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="261" spans="1:23" ht="72" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
-        <v>317</v>
+        <v>345</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>27</v>
+        <v>348</v>
       </c>
       <c r="E261" s="3" t="s">
-        <v>28</v>
+        <v>353</v>
       </c>
       <c r="F261" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G261" s="3"/>
-      <c r="H261" s="3"/>
-      <c r="I261" s="3"/>
-      <c r="J261" s="3"/>
-      <c r="K261" s="3"/>
-      <c r="L261" s="3"/>
-      <c r="M261" s="3"/>
-      <c r="N261" s="3"/>
+      <c r="G261" s="6">
+        <v>60</v>
+      </c>
+      <c r="H261" s="6">
+        <v>40</v>
+      </c>
+      <c r="I261" s="6">
+        <v>60</v>
+      </c>
+      <c r="J261" s="6">
+        <v>60</v>
+      </c>
+      <c r="K261" s="6">
+        <v>60</v>
+      </c>
+      <c r="L261" s="6">
+        <v>60</v>
+      </c>
+      <c r="M261" s="6">
+        <v>40</v>
+      </c>
+      <c r="N261" s="6">
+        <v>60</v>
+      </c>
       <c r="O261" s="6">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="P261" s="6">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="Q261" s="6">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="R261" s="6">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="S261" s="6">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="T261" s="6">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="U261" s="6">
-        <v>80</v>
-      </c>
-      <c r="V261" s="6">
-        <v>86</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="V261" s="3"/>
       <c r="W261" s="2" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="262" spans="1:23" ht="99" x14ac:dyDescent="0.25">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="262" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
-        <v>317</v>
+        <v>345</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="D262" s="2" t="s">
         <v>27</v>
@@ -18244,45 +18216,67 @@
         <v>28</v>
       </c>
       <c r="F262" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="G262" s="3"/>
-      <c r="H262" s="3"/>
-      <c r="I262" s="3"/>
-      <c r="J262" s="3"/>
-      <c r="K262" s="3"/>
-      <c r="L262" s="3"/>
-      <c r="M262" s="3"/>
-      <c r="N262" s="3"/>
-      <c r="O262" s="3"/>
-      <c r="P262" s="3"/>
-      <c r="Q262" s="3"/>
-      <c r="R262" s="3"/>
-      <c r="S262" s="6">
-        <v>16</v>
-      </c>
-      <c r="T262" s="6">
-        <v>7</v>
-      </c>
-      <c r="U262" s="6">
-        <v>6</v>
-      </c>
-      <c r="V262" s="6">
-        <v>4</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="G262" s="4">
+        <v>100</v>
+      </c>
+      <c r="H262" s="4">
+        <v>100.8</v>
+      </c>
+      <c r="I262" s="4">
+        <v>99.9</v>
+      </c>
+      <c r="J262" s="4">
+        <v>101.8</v>
+      </c>
+      <c r="K262" s="4">
+        <v>104.9</v>
+      </c>
+      <c r="L262" s="4">
+        <v>106</v>
+      </c>
+      <c r="M262" s="4">
+        <v>119.9</v>
+      </c>
+      <c r="N262" s="4">
+        <v>119.4</v>
+      </c>
+      <c r="O262" s="4">
+        <v>130</v>
+      </c>
+      <c r="P262" s="4">
+        <v>189.5</v>
+      </c>
+      <c r="Q262" s="4">
+        <v>186.6</v>
+      </c>
+      <c r="R262" s="4">
+        <v>190.1</v>
+      </c>
+      <c r="S262" s="4">
+        <v>200.8</v>
+      </c>
+      <c r="T262" s="4">
+        <v>205.6</v>
+      </c>
+      <c r="U262" s="4">
+        <v>208.5</v>
+      </c>
+      <c r="V262" s="3"/>
       <c r="W262" s="2" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="263" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="263" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
-        <v>317</v>
+        <v>345</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="D263" s="2" t="s">
         <v>27</v>
@@ -18291,446 +18285,466 @@
         <v>28</v>
       </c>
       <c r="F263" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="G263" s="3"/>
-      <c r="H263" s="3"/>
-      <c r="I263" s="3"/>
-      <c r="J263" s="3"/>
-      <c r="K263" s="3"/>
-      <c r="L263" s="3"/>
-      <c r="M263" s="3"/>
-      <c r="N263" s="3"/>
-      <c r="O263" s="3"/>
-      <c r="P263" s="3"/>
-      <c r="Q263" s="3"/>
-      <c r="R263" s="6">
-        <v>133</v>
-      </c>
-      <c r="S263" s="6">
-        <v>80</v>
-      </c>
-      <c r="T263" s="6">
-        <v>97</v>
-      </c>
-      <c r="U263" s="6">
-        <v>44</v>
-      </c>
-      <c r="V263" s="6">
-        <v>89</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="G263" s="4">
+        <v>59.5</v>
+      </c>
+      <c r="H263" s="4">
+        <v>57.7</v>
+      </c>
+      <c r="I263" s="4">
+        <v>58.8</v>
+      </c>
+      <c r="J263" s="4">
+        <v>64.3</v>
+      </c>
+      <c r="K263" s="4">
+        <v>68.7</v>
+      </c>
+      <c r="L263" s="4">
+        <v>69.5</v>
+      </c>
+      <c r="M263" s="4">
+        <v>72.900000000000006</v>
+      </c>
+      <c r="N263" s="4">
+        <v>78.099999999999994</v>
+      </c>
+      <c r="O263" s="4">
+        <v>91.8</v>
+      </c>
+      <c r="P263" s="4">
+        <v>93.9</v>
+      </c>
+      <c r="Q263" s="4">
+        <v>88.5</v>
+      </c>
+      <c r="R263" s="4">
+        <v>96.7</v>
+      </c>
+      <c r="S263" s="4">
+        <v>119</v>
+      </c>
+      <c r="T263" s="4">
+        <v>136.4</v>
+      </c>
+      <c r="U263" s="4">
+        <v>124.2</v>
+      </c>
+      <c r="V263" s="3"/>
       <c r="W263" s="2" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="264" spans="1:23" ht="72" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="264" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>356</v>
+        <v>27</v>
       </c>
       <c r="E264" s="3" t="s">
-        <v>357</v>
+        <v>28</v>
       </c>
       <c r="F264" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G264" s="6">
-        <v>40</v>
-      </c>
-      <c r="H264" s="6">
-        <v>60</v>
-      </c>
-      <c r="I264" s="6">
-        <v>40</v>
-      </c>
-      <c r="J264" s="6">
-        <v>40</v>
-      </c>
-      <c r="K264" s="6">
-        <v>40</v>
-      </c>
-      <c r="L264" s="6">
-        <v>40</v>
-      </c>
-      <c r="M264" s="6">
-        <v>60</v>
-      </c>
-      <c r="N264" s="6">
-        <v>40</v>
-      </c>
-      <c r="O264" s="6">
-        <v>40</v>
-      </c>
-      <c r="P264" s="6">
-        <v>40</v>
-      </c>
-      <c r="Q264" s="6">
-        <v>60</v>
-      </c>
-      <c r="R264" s="6">
-        <v>67</v>
-      </c>
-      <c r="S264" s="6">
-        <v>50</v>
-      </c>
-      <c r="T264" s="6">
-        <v>67</v>
-      </c>
-      <c r="U264" s="6">
-        <v>67</v>
+        <v>362</v>
+      </c>
+      <c r="G264" s="4">
+        <v>90.8</v>
+      </c>
+      <c r="H264" s="4">
+        <v>88.8</v>
+      </c>
+      <c r="I264" s="4">
+        <v>86.5</v>
+      </c>
+      <c r="J264" s="4">
+        <v>87</v>
+      </c>
+      <c r="K264" s="4">
+        <v>85</v>
+      </c>
+      <c r="L264" s="4">
+        <v>87.4</v>
+      </c>
+      <c r="M264" s="4">
+        <v>88.7</v>
+      </c>
+      <c r="N264" s="4">
+        <v>84.6</v>
+      </c>
+      <c r="O264" s="4">
+        <v>77.3</v>
+      </c>
+      <c r="P264" s="4">
+        <v>79.7</v>
+      </c>
+      <c r="Q264" s="4">
+        <v>81.900000000000006</v>
+      </c>
+      <c r="R264" s="4">
+        <v>74.8</v>
+      </c>
+      <c r="S264" s="4">
+        <v>77</v>
+      </c>
+      <c r="T264" s="4">
+        <v>77.2</v>
+      </c>
+      <c r="U264" s="4">
+        <v>76.3</v>
       </c>
       <c r="V264" s="3"/>
       <c r="W264" s="2" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="265" spans="1:23" ht="72" x14ac:dyDescent="0.25">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="265" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>356</v>
+        <v>27</v>
       </c>
       <c r="E265" s="3" t="s">
-        <v>359</v>
+        <v>28</v>
       </c>
       <c r="F265" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G265" s="6">
-        <v>40</v>
-      </c>
-      <c r="H265" s="6">
-        <v>60</v>
-      </c>
-      <c r="I265" s="6">
-        <v>20</v>
-      </c>
-      <c r="J265" s="6">
-        <v>20</v>
-      </c>
-      <c r="K265" s="6">
-        <v>20</v>
-      </c>
-      <c r="L265" s="6">
-        <v>40</v>
-      </c>
-      <c r="M265" s="6">
-        <v>60</v>
-      </c>
-      <c r="N265" s="6">
-        <v>40</v>
-      </c>
-      <c r="O265" s="6">
-        <v>25</v>
-      </c>
-      <c r="P265" s="6">
-        <v>25</v>
-      </c>
-      <c r="Q265" s="6">
-        <v>20</v>
-      </c>
-      <c r="R265" s="6">
-        <v>17</v>
-      </c>
-      <c r="S265" s="6">
-        <v>0</v>
-      </c>
-      <c r="T265" s="6">
-        <v>17</v>
-      </c>
-      <c r="U265" s="6">
-        <v>0</v>
+      <c r="G265" s="7">
+        <v>0.19600000000000001</v>
+      </c>
+      <c r="H265" s="7">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="I265" s="7">
+        <v>0.20599999999999999</v>
+      </c>
+      <c r="J265" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="K265" s="7">
+        <v>0.20100000000000001</v>
+      </c>
+      <c r="L265" s="7">
+        <v>0.20300000000000001</v>
+      </c>
+      <c r="M265" s="7">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="N265" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="O265" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="P265" s="7">
+        <v>0.19900000000000001</v>
+      </c>
+      <c r="Q265" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="R265" s="7">
+        <v>0.19900000000000001</v>
+      </c>
+      <c r="S265" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="T265" s="7">
+        <v>0.192</v>
+      </c>
+      <c r="U265" s="7">
+        <v>0.192</v>
       </c>
       <c r="V265" s="3"/>
       <c r="W265" s="2" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="266" spans="1:23" ht="72" x14ac:dyDescent="0.25">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="266" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>356</v>
+        <v>27</v>
       </c>
       <c r="E266" s="3" t="s">
-        <v>360</v>
+        <v>28</v>
       </c>
       <c r="F266" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G266" s="6">
-        <v>0</v>
-      </c>
-      <c r="H266" s="6">
-        <v>0</v>
-      </c>
-      <c r="I266" s="6">
-        <v>20</v>
-      </c>
-      <c r="J266" s="6">
-        <v>20</v>
-      </c>
-      <c r="K266" s="6">
-        <v>20</v>
-      </c>
-      <c r="L266" s="6">
-        <v>0</v>
-      </c>
-      <c r="M266" s="6">
-        <v>0</v>
-      </c>
-      <c r="N266" s="6">
-        <v>0</v>
-      </c>
-      <c r="O266" s="6">
-        <v>0</v>
-      </c>
-      <c r="P266" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q266" s="6">
-        <v>40</v>
-      </c>
-      <c r="R266" s="6">
-        <v>17</v>
-      </c>
-      <c r="S266" s="6">
-        <v>17</v>
-      </c>
-      <c r="T266" s="6">
-        <v>17</v>
-      </c>
-      <c r="U266" s="6">
-        <v>50</v>
+      <c r="G266" s="4">
+        <v>30.5</v>
+      </c>
+      <c r="H266" s="4">
+        <v>30.5</v>
+      </c>
+      <c r="I266" s="4">
+        <v>30.6</v>
+      </c>
+      <c r="J266" s="4">
+        <v>30.6</v>
+      </c>
+      <c r="K266" s="4">
+        <v>30.7</v>
+      </c>
+      <c r="L266" s="4">
+        <v>30.8</v>
+      </c>
+      <c r="M266" s="4">
+        <v>30.8</v>
+      </c>
+      <c r="N266" s="4">
+        <v>30.9</v>
+      </c>
+      <c r="O266" s="4">
+        <v>30.9</v>
+      </c>
+      <c r="P266" s="4">
+        <v>30.9</v>
+      </c>
+      <c r="Q266" s="4">
+        <v>30.9</v>
+      </c>
+      <c r="R266" s="4">
+        <v>30.9</v>
+      </c>
+      <c r="S266" s="4">
+        <v>31</v>
+      </c>
+      <c r="T266" s="4">
+        <v>31</v>
+      </c>
+      <c r="U266" s="4">
+        <v>31</v>
       </c>
       <c r="V266" s="3"/>
       <c r="W266" s="2" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="267" spans="1:23" ht="72" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="267" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>356</v>
+        <v>27</v>
       </c>
       <c r="E267" s="3" t="s">
-        <v>361</v>
+        <v>28</v>
       </c>
       <c r="F267" s="3" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="G267" s="6">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="H267" s="6">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="I267" s="6">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="J267" s="6">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="K267" s="6">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="L267" s="6">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="M267" s="6">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="N267" s="6">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="O267" s="6">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="P267" s="6">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="Q267" s="6">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="R267" s="6">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="S267" s="6">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="T267" s="6">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U267" s="6">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="V267" s="3"/>
       <c r="W267" s="2" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="268" spans="1:23" ht="18" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="268" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E268" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F268" s="3" t="s">
-        <v>323</v>
+        <v>34</v>
       </c>
       <c r="G268" s="4">
-        <v>100</v>
+        <v>64.7</v>
       </c>
       <c r="H268" s="4">
-        <v>100.8</v>
+        <v>65.7</v>
       </c>
       <c r="I268" s="4">
-        <v>99.9</v>
+        <v>68.599999999999994</v>
       </c>
       <c r="J268" s="4">
-        <v>101.8</v>
+        <v>70.3</v>
       </c>
       <c r="K268" s="4">
-        <v>104.9</v>
+        <v>71.5</v>
       </c>
       <c r="L268" s="4">
-        <v>106</v>
+        <v>72.7</v>
       </c>
       <c r="M268" s="4">
-        <v>119.9</v>
+        <v>73.5</v>
       </c>
       <c r="N268" s="4">
-        <v>119.4</v>
+        <v>73.599999999999994</v>
       </c>
       <c r="O268" s="4">
-        <v>130</v>
+        <v>74</v>
       </c>
       <c r="P268" s="4">
-        <v>189.5</v>
+        <v>74.5</v>
       </c>
       <c r="Q268" s="4">
-        <v>186.6</v>
+        <v>74.900000000000006</v>
       </c>
       <c r="R268" s="4">
-        <v>190.1</v>
+        <v>75.2</v>
       </c>
       <c r="S268" s="4">
-        <v>200.8</v>
+        <v>75.7</v>
       </c>
       <c r="T268" s="4">
-        <v>205.6</v>
+        <v>75.900000000000006</v>
       </c>
       <c r="U268" s="4">
-        <v>208.5</v>
+        <v>76.2</v>
       </c>
       <c r="V268" s="3"/>
       <c r="W268" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="269" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E269" s="3" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F269" s="3" t="s">
-        <v>366</v>
+        <v>34</v>
       </c>
       <c r="G269" s="4">
-        <v>59.5</v>
+        <v>88</v>
       </c>
       <c r="H269" s="4">
-        <v>57.7</v>
+        <v>88.4</v>
       </c>
       <c r="I269" s="4">
-        <v>58.8</v>
+        <v>91.7</v>
       </c>
       <c r="J269" s="4">
-        <v>64.3</v>
+        <v>93.3</v>
       </c>
       <c r="K269" s="4">
-        <v>68.7</v>
+        <v>93.9</v>
       </c>
       <c r="L269" s="4">
-        <v>69.5</v>
+        <v>94.6</v>
       </c>
       <c r="M269" s="4">
-        <v>72.900000000000006</v>
+        <v>94.8</v>
       </c>
       <c r="N269" s="4">
-        <v>78.099999999999994</v>
+        <v>94.5</v>
       </c>
       <c r="O269" s="4">
-        <v>91.8</v>
+        <v>94.6</v>
       </c>
       <c r="P269" s="4">
-        <v>93.9</v>
+        <v>94.8</v>
       </c>
       <c r="Q269" s="4">
-        <v>88.5</v>
+        <v>94.7</v>
       </c>
       <c r="R269" s="4">
-        <v>96.7</v>
+        <v>94.6</v>
       </c>
       <c r="S269" s="4">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="T269" s="4">
-        <v>136.4</v>
+        <v>94.8</v>
       </c>
       <c r="U269" s="4">
-        <v>124.2</v>
+        <v>94.6</v>
       </c>
       <c r="V269" s="3"/>
       <c r="W269" s="2" t="s">
@@ -18739,82 +18753,82 @@
     </row>
     <row r="270" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B270" s="2" t="s">
         <v>367</v>
-      </c>
-      <c r="B270" s="2" t="s">
-        <v>368</v>
       </c>
       <c r="C270" s="2" t="s">
         <v>369</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E270" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="F270" s="3" t="s">
-        <v>370</v>
+        <v>34</v>
       </c>
       <c r="G270" s="4">
-        <v>90.8</v>
+        <v>28.5</v>
       </c>
       <c r="H270" s="4">
-        <v>88.8</v>
+        <v>30.6</v>
       </c>
       <c r="I270" s="4">
-        <v>86.5</v>
+        <v>33.1</v>
       </c>
       <c r="J270" s="4">
-        <v>87</v>
+        <v>35.299999999999997</v>
       </c>
       <c r="K270" s="4">
-        <v>85</v>
+        <v>37.4</v>
       </c>
       <c r="L270" s="4">
-        <v>87.4</v>
+        <v>39.6</v>
       </c>
       <c r="M270" s="4">
-        <v>88.7</v>
+        <v>41.2</v>
       </c>
       <c r="N270" s="4">
-        <v>84.6</v>
+        <v>42</v>
       </c>
       <c r="O270" s="4">
-        <v>77.3</v>
+        <v>42.9</v>
       </c>
       <c r="P270" s="4">
-        <v>79.7</v>
+        <v>44</v>
       </c>
       <c r="Q270" s="4">
-        <v>81.900000000000006</v>
+        <v>45.4</v>
       </c>
       <c r="R270" s="4">
-        <v>74.8</v>
+        <v>46.5</v>
       </c>
       <c r="S270" s="4">
-        <v>77</v>
+        <v>47.2</v>
       </c>
       <c r="T270" s="4">
-        <v>77.2</v>
+        <v>48.2</v>
       </c>
       <c r="U270" s="4">
-        <v>76.3</v>
+        <v>49.3</v>
       </c>
       <c r="V270" s="3"/>
       <c r="W270" s="2" t="s">
-        <v>371</v>
+        <v>30</v>
       </c>
     </row>
     <row r="271" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B271" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="B271" s="2" t="s">
-        <v>368</v>
-      </c>
       <c r="C271" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D271" s="2" t="s">
         <v>27</v>
@@ -18825,65 +18839,65 @@
       <c r="F271" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G271" s="7">
-        <v>0.19600000000000001</v>
-      </c>
-      <c r="H271" s="7">
-        <v>0.20499999999999999</v>
-      </c>
-      <c r="I271" s="7">
-        <v>0.20599999999999999</v>
-      </c>
-      <c r="J271" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="K271" s="7">
-        <v>0.20100000000000001</v>
-      </c>
-      <c r="L271" s="7">
-        <v>0.20300000000000001</v>
-      </c>
-      <c r="M271" s="7">
-        <v>0.20699999999999999</v>
-      </c>
-      <c r="N271" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="O271" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="P271" s="7">
-        <v>0.19900000000000001</v>
-      </c>
-      <c r="Q271" s="7">
-        <v>0.2</v>
-      </c>
-      <c r="R271" s="7">
-        <v>0.19900000000000001</v>
-      </c>
-      <c r="S271" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="T271" s="7">
-        <v>0.192</v>
-      </c>
-      <c r="U271" s="7">
-        <v>0.192</v>
+      <c r="G271" s="4">
+        <v>65.7</v>
+      </c>
+      <c r="H271" s="4">
+        <v>64.8</v>
+      </c>
+      <c r="I271" s="4">
+        <v>67.400000000000006</v>
+      </c>
+      <c r="J271" s="4">
+        <v>69.8</v>
+      </c>
+      <c r="K271" s="4">
+        <v>70.5</v>
+      </c>
+      <c r="L271" s="4">
+        <v>70.900000000000006</v>
+      </c>
+      <c r="M271" s="4">
+        <v>71.400000000000006</v>
+      </c>
+      <c r="N271" s="4">
+        <v>72.5</v>
+      </c>
+      <c r="O271" s="4">
+        <v>73.2</v>
+      </c>
+      <c r="P271" s="4">
+        <v>73.900000000000006</v>
+      </c>
+      <c r="Q271" s="4">
+        <v>73.3</v>
+      </c>
+      <c r="R271" s="4">
+        <v>72.8</v>
+      </c>
+      <c r="S271" s="4">
+        <v>76.3</v>
+      </c>
+      <c r="T271" s="4">
+        <v>78.099999999999994</v>
+      </c>
+      <c r="U271" s="4">
+        <v>78.599999999999994</v>
       </c>
       <c r="V271" s="3"/>
       <c r="W271" s="2" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="272" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="272" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D272" s="2" t="s">
         <v>27</v>
@@ -18892,67 +18906,67 @@
         <v>28</v>
       </c>
       <c r="F272" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G272" s="4">
-        <v>30.5</v>
-      </c>
-      <c r="H272" s="4">
-        <v>30.5</v>
-      </c>
-      <c r="I272" s="4">
-        <v>30.6</v>
-      </c>
-      <c r="J272" s="4">
-        <v>30.6</v>
-      </c>
-      <c r="K272" s="4">
-        <v>30.7</v>
-      </c>
-      <c r="L272" s="4">
-        <v>30.8</v>
-      </c>
-      <c r="M272" s="4">
-        <v>30.8</v>
-      </c>
-      <c r="N272" s="4">
-        <v>30.9</v>
-      </c>
-      <c r="O272" s="4">
-        <v>30.9</v>
-      </c>
-      <c r="P272" s="4">
-        <v>30.9</v>
-      </c>
-      <c r="Q272" s="4">
-        <v>30.9</v>
-      </c>
-      <c r="R272" s="4">
-        <v>30.9</v>
-      </c>
-      <c r="S272" s="4">
-        <v>31</v>
-      </c>
-      <c r="T272" s="4">
-        <v>31</v>
-      </c>
-      <c r="U272" s="4">
-        <v>31</v>
+        <v>373</v>
+      </c>
+      <c r="G272" s="6">
+        <v>70108</v>
+      </c>
+      <c r="H272" s="6">
+        <v>248240</v>
+      </c>
+      <c r="I272" s="6">
+        <v>168221</v>
+      </c>
+      <c r="J272" s="6">
+        <v>72837</v>
+      </c>
+      <c r="K272" s="6">
+        <v>64283</v>
+      </c>
+      <c r="L272" s="6">
+        <v>68694</v>
+      </c>
+      <c r="M272" s="6">
+        <v>60135</v>
+      </c>
+      <c r="N272" s="6">
+        <v>46337</v>
+      </c>
+      <c r="O272" s="6">
+        <v>50289</v>
+      </c>
+      <c r="P272" s="6">
+        <v>104107</v>
+      </c>
+      <c r="Q272" s="6">
+        <v>201963</v>
+      </c>
+      <c r="R272" s="6">
+        <v>84506</v>
+      </c>
+      <c r="S272" s="6">
+        <v>295948</v>
+      </c>
+      <c r="T272" s="6">
+        <v>123796</v>
+      </c>
+      <c r="U272" s="6">
+        <v>104040</v>
       </c>
       <c r="V272" s="3"/>
       <c r="W272" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="273" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D273" s="2" t="s">
         <v>27</v>
@@ -18961,70 +18975,70 @@
         <v>28</v>
       </c>
       <c r="F273" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="G273" s="6">
-        <v>28</v>
-      </c>
-      <c r="H273" s="6">
-        <v>27</v>
-      </c>
-      <c r="I273" s="6">
-        <v>26</v>
-      </c>
-      <c r="J273" s="6">
-        <v>25</v>
-      </c>
-      <c r="K273" s="6">
-        <v>24</v>
-      </c>
-      <c r="L273" s="6">
-        <v>23</v>
-      </c>
-      <c r="M273" s="6">
-        <v>22</v>
-      </c>
-      <c r="N273" s="6">
-        <v>22</v>
-      </c>
-      <c r="O273" s="6">
-        <v>22</v>
-      </c>
-      <c r="P273" s="6">
-        <v>21</v>
-      </c>
-      <c r="Q273" s="6">
-        <v>19</v>
-      </c>
-      <c r="R273" s="6">
-        <v>17</v>
-      </c>
-      <c r="S273" s="6">
-        <v>16</v>
-      </c>
-      <c r="T273" s="6">
-        <v>16</v>
-      </c>
-      <c r="U273" s="6">
-        <v>15</v>
+        <v>34</v>
+      </c>
+      <c r="G273" s="4">
+        <v>2.9</v>
+      </c>
+      <c r="H273" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="I273" s="4">
+        <v>6</v>
+      </c>
+      <c r="J273" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="K273" s="4">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="L273" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="M273" s="4">
+        <v>3.1</v>
+      </c>
+      <c r="N273" s="4">
+        <v>3</v>
+      </c>
+      <c r="O273" s="4">
+        <v>3.2</v>
+      </c>
+      <c r="P273" s="4">
+        <v>3.4</v>
+      </c>
+      <c r="Q273" s="4">
+        <v>3.2</v>
+      </c>
+      <c r="R273" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="S273" s="4">
+        <v>6.6</v>
+      </c>
+      <c r="T273" s="4">
+        <v>5.8</v>
+      </c>
+      <c r="U273" s="4">
+        <v>4.5</v>
       </c>
       <c r="V273" s="3"/>
       <c r="W273" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="274" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="274" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C274" s="2" t="s">
         <v>377</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E274" s="3" t="s">
         <v>28</v>
@@ -19032,203 +19046,165 @@
       <c r="F274" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G274" s="4">
-        <v>64.7</v>
-      </c>
-      <c r="H274" s="4">
-        <v>65.7</v>
-      </c>
-      <c r="I274" s="4">
-        <v>68.599999999999994</v>
-      </c>
-      <c r="J274" s="4">
-        <v>70.3</v>
-      </c>
-      <c r="K274" s="4">
-        <v>71.5</v>
-      </c>
-      <c r="L274" s="4">
-        <v>72.7</v>
-      </c>
-      <c r="M274" s="4">
-        <v>73.5</v>
-      </c>
-      <c r="N274" s="4">
-        <v>73.599999999999994</v>
-      </c>
-      <c r="O274" s="4">
-        <v>74</v>
-      </c>
-      <c r="P274" s="4">
-        <v>74.5</v>
-      </c>
-      <c r="Q274" s="4">
-        <v>74.900000000000006</v>
-      </c>
-      <c r="R274" s="4">
-        <v>75.2</v>
-      </c>
-      <c r="S274" s="4">
-        <v>75.7</v>
-      </c>
-      <c r="T274" s="4">
-        <v>75.900000000000006</v>
-      </c>
-      <c r="U274" s="4">
-        <v>76.2</v>
-      </c>
-      <c r="V274" s="3"/>
+      <c r="G274" s="6">
+        <v>70</v>
+      </c>
+      <c r="H274" s="6">
+        <v>75</v>
+      </c>
+      <c r="I274" s="6">
+        <v>66</v>
+      </c>
+      <c r="J274" s="6">
+        <v>64</v>
+      </c>
+      <c r="K274" s="6">
+        <v>70</v>
+      </c>
+      <c r="L274" s="6">
+        <v>66</v>
+      </c>
+      <c r="M274" s="6">
+        <v>80</v>
+      </c>
+      <c r="N274" s="6">
+        <v>89</v>
+      </c>
+      <c r="O274" s="6">
+        <v>86</v>
+      </c>
+      <c r="P274" s="6">
+        <v>89</v>
+      </c>
+      <c r="Q274" s="6">
+        <v>85</v>
+      </c>
+      <c r="R274" s="6">
+        <v>82</v>
+      </c>
+      <c r="S274" s="6">
+        <v>83</v>
+      </c>
+      <c r="T274" s="6">
+        <v>88</v>
+      </c>
+      <c r="U274" s="6">
+        <v>88</v>
+      </c>
+      <c r="V274" s="6">
+        <v>86</v>
+      </c>
       <c r="W274" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="275" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="275" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E275" s="3" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="F275" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G275" s="4">
-        <v>88</v>
-      </c>
-      <c r="H275" s="4">
-        <v>88.4</v>
-      </c>
-      <c r="I275" s="4">
-        <v>91.7</v>
-      </c>
-      <c r="J275" s="4">
-        <v>93.3</v>
-      </c>
-      <c r="K275" s="4">
-        <v>93.9</v>
-      </c>
-      <c r="L275" s="4">
-        <v>94.6</v>
-      </c>
-      <c r="M275" s="4">
-        <v>94.8</v>
-      </c>
-      <c r="N275" s="4">
-        <v>94.5</v>
-      </c>
-      <c r="O275" s="4">
-        <v>94.6</v>
-      </c>
-      <c r="P275" s="4">
-        <v>94.8</v>
-      </c>
-      <c r="Q275" s="4">
-        <v>94.7</v>
-      </c>
-      <c r="R275" s="4">
-        <v>94.6</v>
-      </c>
-      <c r="S275" s="4">
-        <v>95</v>
-      </c>
-      <c r="T275" s="4">
-        <v>94.8</v>
-      </c>
-      <c r="U275" s="4">
-        <v>94.6</v>
+      <c r="G275" s="6">
+        <v>55</v>
+      </c>
+      <c r="H275" s="3"/>
+      <c r="I275" s="6">
+        <v>58</v>
+      </c>
+      <c r="J275" s="3"/>
+      <c r="K275" s="6">
+        <v>60</v>
+      </c>
+      <c r="L275" s="3"/>
+      <c r="M275" s="6">
+        <v>64</v>
+      </c>
+      <c r="N275" s="3"/>
+      <c r="O275" s="6">
+        <v>65</v>
+      </c>
+      <c r="P275" s="3"/>
+      <c r="Q275" s="6">
+        <v>74</v>
+      </c>
+      <c r="R275" s="3"/>
+      <c r="S275" s="6">
+        <v>63</v>
+      </c>
+      <c r="T275" s="3"/>
+      <c r="U275" s="6">
+        <v>71</v>
       </c>
       <c r="V275" s="3"/>
       <c r="W275" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="276" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="276" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E276" s="3" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="F276" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G276" s="4">
-        <v>28.5</v>
-      </c>
-      <c r="H276" s="4">
-        <v>30.6</v>
-      </c>
-      <c r="I276" s="4">
-        <v>33.1</v>
-      </c>
-      <c r="J276" s="4">
-        <v>35.299999999999997</v>
-      </c>
-      <c r="K276" s="4">
-        <v>37.4</v>
-      </c>
-      <c r="L276" s="4">
-        <v>39.6</v>
-      </c>
-      <c r="M276" s="4">
-        <v>41.2</v>
-      </c>
-      <c r="N276" s="4">
         <v>42</v>
       </c>
-      <c r="O276" s="4">
-        <v>42.9</v>
-      </c>
-      <c r="P276" s="4">
-        <v>44</v>
-      </c>
-      <c r="Q276" s="4">
-        <v>45.4</v>
-      </c>
-      <c r="R276" s="4">
-        <v>46.5</v>
-      </c>
-      <c r="S276" s="4">
-        <v>47.2</v>
-      </c>
-      <c r="T276" s="4">
-        <v>48.2</v>
-      </c>
-      <c r="U276" s="4">
-        <v>49.3</v>
-      </c>
+      <c r="G276" s="3"/>
+      <c r="H276" s="3"/>
+      <c r="I276" s="3"/>
+      <c r="J276" s="3"/>
+      <c r="K276" s="3"/>
+      <c r="L276" s="3"/>
+      <c r="M276" s="3"/>
+      <c r="N276" s="3"/>
+      <c r="O276" s="3"/>
+      <c r="P276" s="3"/>
+      <c r="Q276" s="3"/>
+      <c r="R276" s="3"/>
+      <c r="S276" s="5">
+        <v>33109.31</v>
+      </c>
+      <c r="T276" s="5">
+        <v>33829.39</v>
+      </c>
+      <c r="U276" s="3"/>
       <c r="V276" s="3"/>
       <c r="W276" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="277" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="277" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D277" s="2" t="s">
         <v>27</v>
@@ -19237,67 +19213,67 @@
         <v>28</v>
       </c>
       <c r="F277" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G277" s="4">
-        <v>65.7</v>
-      </c>
-      <c r="H277" s="4">
-        <v>64.8</v>
-      </c>
-      <c r="I277" s="4">
-        <v>67.400000000000006</v>
-      </c>
-      <c r="J277" s="4">
-        <v>69.8</v>
-      </c>
-      <c r="K277" s="4">
-        <v>70.5</v>
-      </c>
-      <c r="L277" s="4">
-        <v>70.900000000000006</v>
-      </c>
-      <c r="M277" s="4">
-        <v>71.400000000000006</v>
-      </c>
-      <c r="N277" s="4">
-        <v>72.5</v>
-      </c>
-      <c r="O277" s="4">
-        <v>73.2</v>
-      </c>
-      <c r="P277" s="4">
-        <v>73.900000000000006</v>
-      </c>
-      <c r="Q277" s="4">
-        <v>73.3</v>
-      </c>
-      <c r="R277" s="4">
-        <v>72.8</v>
-      </c>
-      <c r="S277" s="4">
-        <v>76.3</v>
-      </c>
-      <c r="T277" s="4">
-        <v>78.099999999999994</v>
-      </c>
-      <c r="U277" s="4">
-        <v>78.599999999999994</v>
+        <v>205</v>
+      </c>
+      <c r="G277" s="5">
+        <v>1.02</v>
+      </c>
+      <c r="H277" s="5">
+        <v>0.96</v>
+      </c>
+      <c r="I277" s="5">
+        <v>1</v>
+      </c>
+      <c r="J277" s="5">
+        <v>1.05</v>
+      </c>
+      <c r="K277" s="5">
+        <v>1.06</v>
+      </c>
+      <c r="L277" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="M277" s="5">
+        <v>0.91</v>
+      </c>
+      <c r="N277" s="5">
+        <v>0.81</v>
+      </c>
+      <c r="O277" s="5">
+        <v>0.87</v>
+      </c>
+      <c r="P277" s="5">
+        <v>1.01</v>
+      </c>
+      <c r="Q277" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="R277" s="5">
+        <v>0.83</v>
+      </c>
+      <c r="S277" s="5">
+        <v>0.72</v>
+      </c>
+      <c r="T277" s="5">
+        <v>0.78</v>
+      </c>
+      <c r="U277" s="5">
+        <v>0.69</v>
       </c>
       <c r="V277" s="3"/>
       <c r="W277" s="2" t="s">
-        <v>30</v>
+        <v>206</v>
       </c>
     </row>
     <row r="278" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D278" s="2" t="s">
         <v>27</v>
@@ -19306,67 +19282,67 @@
         <v>28</v>
       </c>
       <c r="F278" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="G278" s="6">
-        <v>70108</v>
-      </c>
-      <c r="H278" s="6">
-        <v>248240</v>
-      </c>
-      <c r="I278" s="6">
-        <v>168221</v>
-      </c>
-      <c r="J278" s="6">
-        <v>72837</v>
-      </c>
-      <c r="K278" s="6">
-        <v>64283</v>
-      </c>
-      <c r="L278" s="6">
-        <v>68694</v>
-      </c>
-      <c r="M278" s="6">
-        <v>60135</v>
-      </c>
-      <c r="N278" s="6">
-        <v>46337</v>
-      </c>
-      <c r="O278" s="6">
-        <v>50289</v>
-      </c>
-      <c r="P278" s="6">
-        <v>104107</v>
-      </c>
-      <c r="Q278" s="6">
-        <v>201963</v>
-      </c>
-      <c r="R278" s="6">
-        <v>84506</v>
-      </c>
-      <c r="S278" s="6">
-        <v>295948</v>
-      </c>
-      <c r="T278" s="6">
-        <v>123796</v>
-      </c>
-      <c r="U278" s="6">
-        <v>104040</v>
+        <v>34</v>
+      </c>
+      <c r="G278" s="5">
+        <v>1.84</v>
+      </c>
+      <c r="H278" s="5">
+        <v>1.79</v>
+      </c>
+      <c r="I278" s="5">
+        <v>1.8</v>
+      </c>
+      <c r="J278" s="5">
+        <v>1.79</v>
+      </c>
+      <c r="K278" s="5">
+        <v>1.86</v>
+      </c>
+      <c r="L278" s="5">
+        <v>2.21</v>
+      </c>
+      <c r="M278" s="5">
+        <v>1.99</v>
+      </c>
+      <c r="N278" s="5">
+        <v>1.88</v>
+      </c>
+      <c r="O278" s="5">
+        <v>2</v>
+      </c>
+      <c r="P278" s="5">
+        <v>1.96</v>
+      </c>
+      <c r="Q278" s="5">
+        <v>2.21</v>
+      </c>
+      <c r="R278" s="5">
+        <v>2.19</v>
+      </c>
+      <c r="S278" s="5">
+        <v>2.21</v>
+      </c>
+      <c r="T278" s="5">
+        <v>3.27</v>
+      </c>
+      <c r="U278" s="5">
+        <v>4.07</v>
       </c>
       <c r="V278" s="3"/>
       <c r="W278" s="2" t="s">
-        <v>30</v>
+        <v>385</v>
       </c>
     </row>
     <row r="279" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="D279" s="2" t="s">
         <v>27</v>
@@ -19377,68 +19353,42 @@
       <c r="F279" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G279" s="4">
-        <v>2.9</v>
-      </c>
-      <c r="H279" s="4">
-        <v>3.8</v>
-      </c>
-      <c r="I279" s="4">
-        <v>6</v>
-      </c>
-      <c r="J279" s="4">
-        <v>4.3</v>
-      </c>
-      <c r="K279" s="4">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="L279" s="4">
-        <v>4.2</v>
-      </c>
-      <c r="M279" s="4">
-        <v>3.1</v>
-      </c>
-      <c r="N279" s="4">
-        <v>3</v>
-      </c>
-      <c r="O279" s="4">
-        <v>3.2</v>
-      </c>
-      <c r="P279" s="4">
-        <v>3.4</v>
-      </c>
-      <c r="Q279" s="4">
-        <v>3.2</v>
-      </c>
-      <c r="R279" s="4">
-        <v>4.5</v>
-      </c>
-      <c r="S279" s="4">
-        <v>6.6</v>
-      </c>
-      <c r="T279" s="4">
-        <v>5.8</v>
-      </c>
+      <c r="G279" s="3"/>
+      <c r="H279" s="3"/>
+      <c r="I279" s="3"/>
+      <c r="J279" s="3"/>
+      <c r="K279" s="3"/>
+      <c r="L279" s="3"/>
+      <c r="M279" s="3"/>
+      <c r="N279" s="3"/>
+      <c r="O279" s="3"/>
+      <c r="P279" s="3"/>
+      <c r="Q279" s="3"/>
+      <c r="R279" s="3"/>
+      <c r="S279" s="3"/>
+      <c r="T279" s="3"/>
       <c r="U279" s="4">
-        <v>4.5</v>
-      </c>
-      <c r="V279" s="3"/>
+        <v>30.2</v>
+      </c>
+      <c r="V279" s="4">
+        <v>51.3</v>
+      </c>
       <c r="W279" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="280" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="E280" s="3" t="s">
         <v>28</v>
@@ -19446,332 +19396,408 @@
       <c r="F280" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G280" s="6">
-        <v>70</v>
-      </c>
-      <c r="H280" s="6">
-        <v>75</v>
-      </c>
-      <c r="I280" s="6">
-        <v>66</v>
-      </c>
-      <c r="J280" s="6">
-        <v>64</v>
-      </c>
-      <c r="K280" s="6">
-        <v>70</v>
-      </c>
-      <c r="L280" s="6">
-        <v>66</v>
-      </c>
-      <c r="M280" s="6">
-        <v>80</v>
-      </c>
-      <c r="N280" s="6">
-        <v>89</v>
-      </c>
-      <c r="O280" s="6">
-        <v>86</v>
-      </c>
-      <c r="P280" s="6">
-        <v>89</v>
-      </c>
-      <c r="Q280" s="6">
-        <v>85</v>
-      </c>
-      <c r="R280" s="6">
-        <v>82</v>
-      </c>
-      <c r="S280" s="6">
-        <v>83</v>
-      </c>
-      <c r="T280" s="6">
-        <v>88</v>
-      </c>
-      <c r="U280" s="6">
-        <v>88</v>
-      </c>
-      <c r="V280" s="6">
-        <v>86</v>
+      <c r="G280" s="4">
+        <v>28.1</v>
+      </c>
+      <c r="H280" s="4">
+        <v>27.6</v>
+      </c>
+      <c r="I280" s="4">
+        <v>31.6</v>
+      </c>
+      <c r="J280" s="4">
+        <v>22.6</v>
+      </c>
+      <c r="K280" s="4">
+        <v>26.9</v>
+      </c>
+      <c r="L280" s="4">
+        <v>26.6</v>
+      </c>
+      <c r="M280" s="4">
+        <v>30.2</v>
+      </c>
+      <c r="N280" s="4">
+        <v>30.8</v>
+      </c>
+      <c r="O280" s="4">
+        <v>35.5</v>
+      </c>
+      <c r="P280" s="4">
+        <v>40.4</v>
+      </c>
+      <c r="Q280" s="4">
+        <v>41.9</v>
+      </c>
+      <c r="R280" s="4">
+        <v>47.5</v>
+      </c>
+      <c r="S280" s="4">
+        <v>55.4</v>
+      </c>
+      <c r="T280" s="4">
+        <v>58.5</v>
+      </c>
+      <c r="U280" s="4">
+        <v>61</v>
+      </c>
+      <c r="V280" s="4">
+        <v>61.1</v>
       </c>
       <c r="W280" s="2" t="s">
-        <v>386</v>
+        <v>30</v>
       </c>
     </row>
     <row r="281" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="E281" s="3" t="s">
-        <v>28</v>
+        <v>389</v>
       </c>
       <c r="F281" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G281" s="6">
-        <v>55</v>
-      </c>
-      <c r="H281" s="3"/>
-      <c r="I281" s="6">
-        <v>58</v>
-      </c>
-      <c r="J281" s="3"/>
-      <c r="K281" s="6">
-        <v>60</v>
-      </c>
-      <c r="L281" s="3"/>
-      <c r="M281" s="6">
-        <v>64</v>
-      </c>
-      <c r="N281" s="3"/>
-      <c r="O281" s="6">
-        <v>65</v>
-      </c>
-      <c r="P281" s="3"/>
-      <c r="Q281" s="6">
-        <v>74</v>
-      </c>
-      <c r="R281" s="3"/>
-      <c r="S281" s="6">
-        <v>63</v>
-      </c>
-      <c r="T281" s="3"/>
-      <c r="U281" s="6">
-        <v>71</v>
-      </c>
-      <c r="V281" s="3"/>
+      <c r="G281" s="4">
+        <v>31.5</v>
+      </c>
+      <c r="H281" s="4">
+        <v>27.9</v>
+      </c>
+      <c r="I281" s="4">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="J281" s="4">
+        <v>20.2</v>
+      </c>
+      <c r="K281" s="4">
+        <v>23.9</v>
+      </c>
+      <c r="L281" s="4">
+        <v>20.8</v>
+      </c>
+      <c r="M281" s="4">
+        <v>20.5</v>
+      </c>
+      <c r="N281" s="4">
+        <v>22.4</v>
+      </c>
+      <c r="O281" s="4">
+        <v>29.5</v>
+      </c>
+      <c r="P281" s="4">
+        <v>29.8</v>
+      </c>
+      <c r="Q281" s="4">
+        <v>30.9</v>
+      </c>
+      <c r="R281" s="4">
+        <v>35.6</v>
+      </c>
+      <c r="S281" s="4">
+        <v>42.1</v>
+      </c>
+      <c r="T281" s="4">
+        <v>44</v>
+      </c>
+      <c r="U281" s="4">
+        <v>47.7</v>
+      </c>
+      <c r="V281" s="4">
+        <v>48.9</v>
+      </c>
       <c r="W281" s="2" t="s">
-        <v>386</v>
+        <v>30</v>
       </c>
     </row>
     <row r="282" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C282" s="2" t="s">
         <v>388</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="E282" s="3" t="s">
-        <v>28</v>
+        <v>390</v>
       </c>
       <c r="F282" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G282" s="3"/>
-      <c r="H282" s="3"/>
-      <c r="I282" s="3"/>
-      <c r="J282" s="3"/>
-      <c r="K282" s="3"/>
-      <c r="L282" s="3"/>
-      <c r="M282" s="3"/>
-      <c r="N282" s="3"/>
-      <c r="O282" s="3"/>
-      <c r="P282" s="3"/>
-      <c r="Q282" s="3"/>
-      <c r="R282" s="3"/>
-      <c r="S282" s="5">
-        <v>33109.31</v>
-      </c>
-      <c r="T282" s="5">
-        <v>33829.39</v>
-      </c>
-      <c r="U282" s="3"/>
-      <c r="V282" s="3"/>
+        <v>34</v>
+      </c>
+      <c r="G282" s="4">
+        <v>47.6</v>
+      </c>
+      <c r="H282" s="4">
+        <v>46.2</v>
+      </c>
+      <c r="I282" s="4">
+        <v>50.6</v>
+      </c>
+      <c r="J282" s="4">
+        <v>39</v>
+      </c>
+      <c r="K282" s="4">
+        <v>46</v>
+      </c>
+      <c r="L282" s="4">
+        <v>45</v>
+      </c>
+      <c r="M282" s="4">
+        <v>48.1</v>
+      </c>
+      <c r="N282" s="4">
+        <v>48.1</v>
+      </c>
+      <c r="O282" s="4">
+        <v>53</v>
+      </c>
+      <c r="P282" s="4">
+        <v>58.6</v>
+      </c>
+      <c r="Q282" s="4">
+        <v>59.9</v>
+      </c>
+      <c r="R282" s="4">
+        <v>68.3</v>
+      </c>
+      <c r="S282" s="4">
+        <v>75.2</v>
+      </c>
+      <c r="T282" s="4">
+        <v>81</v>
+      </c>
+      <c r="U282" s="4">
+        <v>81.2</v>
+      </c>
+      <c r="V282" s="4">
+        <v>81.8</v>
+      </c>
       <c r="W282" s="2" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
     </row>
     <row r="283" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="E283" s="3" t="s">
-        <v>28</v>
+        <v>391</v>
       </c>
       <c r="F283" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="G283" s="5">
-        <v>1.02</v>
-      </c>
-      <c r="H283" s="5">
-        <v>0.96</v>
-      </c>
-      <c r="I283" s="5">
-        <v>1</v>
-      </c>
-      <c r="J283" s="5">
-        <v>1.05</v>
-      </c>
-      <c r="K283" s="5">
-        <v>1.06</v>
-      </c>
-      <c r="L283" s="5">
-        <v>0.95</v>
-      </c>
-      <c r="M283" s="5">
-        <v>0.91</v>
-      </c>
-      <c r="N283" s="5">
-        <v>0.81</v>
-      </c>
-      <c r="O283" s="5">
-        <v>0.87</v>
-      </c>
-      <c r="P283" s="5">
-        <v>1.01</v>
-      </c>
-      <c r="Q283" s="5">
-        <v>0.85</v>
-      </c>
-      <c r="R283" s="5">
-        <v>0.83</v>
-      </c>
-      <c r="S283" s="5">
-        <v>0.72</v>
-      </c>
-      <c r="T283" s="5">
-        <v>0.78</v>
-      </c>
-      <c r="U283" s="5">
-        <v>0.69</v>
-      </c>
-      <c r="V283" s="3"/>
+        <v>34</v>
+      </c>
+      <c r="G283" s="4">
+        <v>37.6</v>
+      </c>
+      <c r="H283" s="4">
+        <v>36.9</v>
+      </c>
+      <c r="I283" s="4">
+        <v>45.3</v>
+      </c>
+      <c r="J283" s="4">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="K283" s="4">
+        <v>40.1</v>
+      </c>
+      <c r="L283" s="4">
+        <v>38.6</v>
+      </c>
+      <c r="M283" s="4">
+        <v>40.5</v>
+      </c>
+      <c r="N283" s="4">
+        <v>45</v>
+      </c>
+      <c r="O283" s="4">
+        <v>49.6</v>
+      </c>
+      <c r="P283" s="4">
+        <v>57.6</v>
+      </c>
+      <c r="Q283" s="4">
+        <v>59.4</v>
+      </c>
+      <c r="R283" s="4">
+        <v>65.900000000000006</v>
+      </c>
+      <c r="S283" s="4">
+        <v>75.599999999999994</v>
+      </c>
+      <c r="T283" s="4">
+        <v>78.3</v>
+      </c>
+      <c r="U283" s="4">
+        <v>81.099999999999994</v>
+      </c>
+      <c r="V283" s="4">
+        <v>78.3</v>
+      </c>
       <c r="W283" s="2" t="s">
-        <v>206</v>
+        <v>30</v>
       </c>
     </row>
     <row r="284" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="C284" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="D284" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E284" s="3" t="s">
         <v>392</v>
-      </c>
-      <c r="D284" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E284" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="F284" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G284" s="5">
-        <v>1.84</v>
-      </c>
-      <c r="H284" s="5">
-        <v>1.79</v>
-      </c>
-      <c r="I284" s="5">
-        <v>1.8</v>
-      </c>
-      <c r="J284" s="5">
-        <v>1.79</v>
-      </c>
-      <c r="K284" s="5">
-        <v>1.86</v>
-      </c>
-      <c r="L284" s="5">
-        <v>2.21</v>
-      </c>
-      <c r="M284" s="5">
-        <v>1.99</v>
-      </c>
-      <c r="N284" s="5">
-        <v>1.88</v>
-      </c>
-      <c r="O284" s="5">
-        <v>2</v>
-      </c>
-      <c r="P284" s="5">
-        <v>1.96</v>
-      </c>
-      <c r="Q284" s="5">
-        <v>2.21</v>
-      </c>
-      <c r="R284" s="5">
-        <v>2.19</v>
-      </c>
-      <c r="S284" s="5">
-        <v>2.21</v>
-      </c>
-      <c r="T284" s="5">
-        <v>3.27</v>
-      </c>
-      <c r="U284" s="5">
-        <v>4.07</v>
-      </c>
-      <c r="V284" s="3"/>
+      <c r="G284" s="4">
+        <v>26.2</v>
+      </c>
+      <c r="H284" s="4">
+        <v>26.3</v>
+      </c>
+      <c r="I284" s="4">
+        <v>28.7</v>
+      </c>
+      <c r="J284" s="4">
+        <v>21.5</v>
+      </c>
+      <c r="K284" s="4">
+        <v>26.2</v>
+      </c>
+      <c r="L284" s="4">
+        <v>26</v>
+      </c>
+      <c r="M284" s="4">
+        <v>30</v>
+      </c>
+      <c r="N284" s="4">
+        <v>28</v>
+      </c>
+      <c r="O284" s="4">
+        <v>35</v>
+      </c>
+      <c r="P284" s="4">
+        <v>41.4</v>
+      </c>
+      <c r="Q284" s="4">
+        <v>45.1</v>
+      </c>
+      <c r="R284" s="4">
+        <v>51.7</v>
+      </c>
+      <c r="S284" s="4">
+        <v>62.4</v>
+      </c>
+      <c r="T284" s="4">
+        <v>65.7</v>
+      </c>
+      <c r="U284" s="4">
+        <v>68.8</v>
+      </c>
+      <c r="V284" s="4">
+        <v>69.900000000000006</v>
+      </c>
       <c r="W284" s="2" t="s">
-        <v>393</v>
+        <v>30</v>
       </c>
     </row>
     <row r="285" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="D285" s="2" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="E285" s="3" t="s">
-        <v>28</v>
+        <v>393</v>
       </c>
       <c r="F285" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G285" s="3"/>
-      <c r="H285" s="3"/>
-      <c r="I285" s="3"/>
-      <c r="J285" s="3"/>
-      <c r="K285" s="3"/>
-      <c r="L285" s="3"/>
-      <c r="M285" s="3"/>
-      <c r="N285" s="3"/>
-      <c r="O285" s="3"/>
-      <c r="P285" s="3"/>
-      <c r="Q285" s="3"/>
-      <c r="R285" s="3"/>
-      <c r="S285" s="3"/>
-      <c r="T285" s="3"/>
+      <c r="G285" s="4">
+        <v>13.5</v>
+      </c>
+      <c r="H285" s="4">
+        <v>15.7</v>
+      </c>
+      <c r="I285" s="4">
+        <v>17.2</v>
+      </c>
+      <c r="J285" s="4">
+        <v>12.7</v>
+      </c>
+      <c r="K285" s="4">
+        <v>15.5</v>
+      </c>
+      <c r="L285" s="4">
+        <v>18.3</v>
+      </c>
+      <c r="M285" s="4">
+        <v>19.8</v>
+      </c>
+      <c r="N285" s="4">
+        <v>18.8</v>
+      </c>
+      <c r="O285" s="4">
+        <v>22.4</v>
+      </c>
+      <c r="P285" s="4">
+        <v>28.5</v>
+      </c>
+      <c r="Q285" s="4">
+        <v>29.4</v>
+      </c>
+      <c r="R285" s="4">
+        <v>35</v>
+      </c>
+      <c r="S285" s="4">
+        <v>39.5</v>
+      </c>
+      <c r="T285" s="4">
+        <v>44.4</v>
+      </c>
       <c r="U285" s="4">
-        <v>30.2</v>
+        <v>50.8</v>
       </c>
       <c r="V285" s="4">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
       <c r="W285" s="2" t="s">
         <v>30</v>
@@ -19779,70 +19805,70 @@
     </row>
     <row r="286" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="D286" s="2" t="s">
         <v>90</v>
       </c>
       <c r="E286" s="3" t="s">
-        <v>28</v>
+        <v>394</v>
       </c>
       <c r="F286" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G286" s="4">
-        <v>28.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="H286" s="4">
+        <v>5</v>
+      </c>
+      <c r="I286" s="4">
+        <v>6.8</v>
+      </c>
+      <c r="J286" s="4">
+        <v>3.7</v>
+      </c>
+      <c r="K286" s="4">
+        <v>6.6</v>
+      </c>
+      <c r="L286" s="4">
+        <v>6</v>
+      </c>
+      <c r="M286" s="4">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="N286" s="4">
+        <v>8.4</v>
+      </c>
+      <c r="O286" s="4">
+        <v>10.9</v>
+      </c>
+      <c r="P286" s="4">
+        <v>12.2</v>
+      </c>
+      <c r="Q286" s="4">
+        <v>13.5</v>
+      </c>
+      <c r="R286" s="4">
+        <v>15.8</v>
+      </c>
+      <c r="S286" s="4">
+        <v>23.6</v>
+      </c>
+      <c r="T286" s="4">
+        <v>26.1</v>
+      </c>
+      <c r="U286" s="4">
+        <v>27.4</v>
+      </c>
+      <c r="V286" s="4">
         <v>27.6</v>
-      </c>
-      <c r="I286" s="4">
-        <v>31.6</v>
-      </c>
-      <c r="J286" s="4">
-        <v>22.6</v>
-      </c>
-      <c r="K286" s="4">
-        <v>26.9</v>
-      </c>
-      <c r="L286" s="4">
-        <v>26.6</v>
-      </c>
-      <c r="M286" s="4">
-        <v>30.2</v>
-      </c>
-      <c r="N286" s="4">
-        <v>30.8</v>
-      </c>
-      <c r="O286" s="4">
-        <v>35.5</v>
-      </c>
-      <c r="P286" s="4">
-        <v>40.4</v>
-      </c>
-      <c r="Q286" s="4">
-        <v>41.9</v>
-      </c>
-      <c r="R286" s="4">
-        <v>47.5</v>
-      </c>
-      <c r="S286" s="4">
-        <v>55.4</v>
-      </c>
-      <c r="T286" s="4">
-        <v>58.5</v>
-      </c>
-      <c r="U286" s="4">
-        <v>61</v>
-      </c>
-      <c r="V286" s="4">
-        <v>61.1</v>
       </c>
       <c r="W286" s="2" t="s">
         <v>30</v>
@@ -19850,439 +19876,407 @@
     </row>
     <row r="287" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C287" s="2" t="s">
         <v>396</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="E287" s="3" t="s">
-        <v>397</v>
+        <v>28</v>
       </c>
       <c r="F287" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G287" s="4">
-        <v>31.5</v>
+        <v>5.7</v>
       </c>
       <c r="H287" s="4">
-        <v>27.9</v>
+        <v>6</v>
       </c>
       <c r="I287" s="4">
-        <v>36.799999999999997</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="J287" s="4">
-        <v>20.2</v>
+        <v>4.3</v>
       </c>
       <c r="K287" s="4">
-        <v>23.9</v>
+        <v>4.7</v>
       </c>
       <c r="L287" s="4">
-        <v>20.8</v>
+        <v>4.5</v>
       </c>
       <c r="M287" s="4">
-        <v>20.5</v>
+        <v>3.3</v>
       </c>
       <c r="N287" s="4">
-        <v>22.4</v>
+        <v>3.8</v>
       </c>
       <c r="O287" s="4">
-        <v>29.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="P287" s="4">
-        <v>29.8</v>
+        <v>4.3</v>
       </c>
       <c r="Q287" s="4">
-        <v>30.9</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="R287" s="4">
-        <v>35.6</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="S287" s="4">
-        <v>42.1</v>
+        <v>3.8</v>
       </c>
       <c r="T287" s="4">
-        <v>44</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="U287" s="4">
-        <v>47.7</v>
+        <v>4.8</v>
       </c>
       <c r="V287" s="4">
-        <v>48.9</v>
+        <v>5.2</v>
       </c>
       <c r="W287" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="288" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="E288" s="3" t="s">
-        <v>398</v>
+        <v>28</v>
       </c>
       <c r="F288" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G288" s="4">
-        <v>47.6</v>
-      </c>
-      <c r="H288" s="4">
-        <v>46.2</v>
-      </c>
-      <c r="I288" s="4">
-        <v>50.6</v>
-      </c>
-      <c r="J288" s="4">
-        <v>39</v>
-      </c>
-      <c r="K288" s="4">
-        <v>46</v>
-      </c>
-      <c r="L288" s="4">
-        <v>45</v>
-      </c>
-      <c r="M288" s="4">
-        <v>48.1</v>
-      </c>
-      <c r="N288" s="4">
-        <v>48.1</v>
-      </c>
-      <c r="O288" s="4">
-        <v>53</v>
-      </c>
-      <c r="P288" s="4">
-        <v>58.6</v>
-      </c>
-      <c r="Q288" s="4">
-        <v>59.9</v>
-      </c>
-      <c r="R288" s="4">
-        <v>68.3</v>
-      </c>
-      <c r="S288" s="4">
-        <v>75.2</v>
-      </c>
-      <c r="T288" s="4">
-        <v>81</v>
-      </c>
-      <c r="U288" s="4">
-        <v>81.2</v>
-      </c>
-      <c r="V288" s="4">
-        <v>81.8</v>
+        <v>42</v>
+      </c>
+      <c r="G288" s="6">
+        <v>674</v>
+      </c>
+      <c r="H288" s="6">
+        <v>605</v>
+      </c>
+      <c r="I288" s="6">
+        <v>1082</v>
+      </c>
+      <c r="J288" s="6">
+        <v>1219</v>
+      </c>
+      <c r="K288" s="6">
+        <v>1282</v>
+      </c>
+      <c r="L288" s="6">
+        <v>1456</v>
+      </c>
+      <c r="M288" s="6">
+        <v>1926</v>
+      </c>
+      <c r="N288" s="6">
+        <v>3182</v>
+      </c>
+      <c r="O288" s="6">
+        <v>3739</v>
+      </c>
+      <c r="P288" s="6">
+        <v>6484</v>
+      </c>
+      <c r="Q288" s="6">
+        <v>10420</v>
+      </c>
+      <c r="R288" s="6">
+        <v>29483</v>
+      </c>
+      <c r="S288" s="6">
+        <v>39683</v>
+      </c>
+      <c r="T288" s="6">
+        <v>80267</v>
+      </c>
+      <c r="U288" s="6">
+        <v>103449</v>
+      </c>
+      <c r="V288" s="6">
+        <v>260783</v>
       </c>
       <c r="W288" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="289" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="289" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="E289" s="3" t="s">
-        <v>399</v>
+        <v>28</v>
       </c>
       <c r="F289" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G289" s="4">
-        <v>37.6</v>
-      </c>
-      <c r="H289" s="4">
-        <v>36.9</v>
-      </c>
-      <c r="I289" s="4">
-        <v>45.3</v>
-      </c>
-      <c r="J289" s="4">
-        <v>35.200000000000003</v>
-      </c>
-      <c r="K289" s="4">
-        <v>40.1</v>
-      </c>
-      <c r="L289" s="4">
-        <v>38.6</v>
-      </c>
-      <c r="M289" s="4">
-        <v>40.5</v>
-      </c>
-      <c r="N289" s="4">
-        <v>45</v>
-      </c>
-      <c r="O289" s="4">
-        <v>49.6</v>
-      </c>
-      <c r="P289" s="4">
-        <v>57.6</v>
-      </c>
-      <c r="Q289" s="4">
-        <v>59.4</v>
-      </c>
-      <c r="R289" s="4">
-        <v>65.900000000000006</v>
-      </c>
-      <c r="S289" s="4">
-        <v>75.599999999999994</v>
-      </c>
-      <c r="T289" s="4">
-        <v>78.3</v>
-      </c>
-      <c r="U289" s="4">
-        <v>81.099999999999994</v>
-      </c>
-      <c r="V289" s="4">
-        <v>78.3</v>
+      <c r="G289" s="3"/>
+      <c r="H289" s="3"/>
+      <c r="I289" s="3"/>
+      <c r="J289" s="3"/>
+      <c r="K289" s="3"/>
+      <c r="L289" s="3"/>
+      <c r="M289" s="3"/>
+      <c r="N289" s="3"/>
+      <c r="O289" s="3"/>
+      <c r="P289" s="3"/>
+      <c r="Q289" s="3"/>
+      <c r="R289" s="5">
+        <v>18.93</v>
+      </c>
+      <c r="S289" s="3"/>
+      <c r="T289" s="5">
+        <v>21.3</v>
+      </c>
+      <c r="U289" s="3"/>
+      <c r="V289" s="5">
+        <v>23.01</v>
       </c>
       <c r="W289" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="290" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="290" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
-        <v>383</v>
+        <v>401</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="E290" s="3" t="s">
-        <v>400</v>
+        <v>28</v>
       </c>
       <c r="F290" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G290" s="4">
-        <v>26.2</v>
-      </c>
-      <c r="H290" s="4">
-        <v>26.3</v>
-      </c>
-      <c r="I290" s="4">
-        <v>28.7</v>
-      </c>
-      <c r="J290" s="4">
-        <v>21.5</v>
-      </c>
-      <c r="K290" s="4">
-        <v>26.2</v>
-      </c>
-      <c r="L290" s="4">
-        <v>26</v>
-      </c>
-      <c r="M290" s="4">
-        <v>30</v>
-      </c>
-      <c r="N290" s="4">
+        <v>404</v>
+      </c>
+      <c r="G290" s="5">
+        <v>377.75</v>
+      </c>
+      <c r="H290" s="5">
+        <v>417.47</v>
+      </c>
+      <c r="I290" s="5">
+        <v>421.06</v>
+      </c>
+      <c r="J290" s="5">
+        <v>487.12</v>
+      </c>
+      <c r="K290" s="5">
+        <v>451.84</v>
+      </c>
+      <c r="L290" s="5">
+        <v>440.89</v>
+      </c>
+      <c r="M290" s="5">
+        <v>662.95</v>
+      </c>
+      <c r="N290" s="5">
+        <v>679.46</v>
+      </c>
+      <c r="O290" s="5">
+        <v>766.04</v>
+      </c>
+      <c r="P290" s="5">
+        <v>776.56</v>
+      </c>
+      <c r="Q290" s="5">
+        <v>829.27</v>
+      </c>
+      <c r="R290" s="5">
+        <v>983.51</v>
+      </c>
+      <c r="S290" s="5">
+        <v>3494.39</v>
+      </c>
+      <c r="T290" s="5">
+        <v>2580.38</v>
+      </c>
+      <c r="U290" s="5">
+        <v>1840.15</v>
+      </c>
+      <c r="V290" s="3"/>
+      <c r="W290" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="291" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+      <c r="A291" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B291" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="C291" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="D291" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E291" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="O290" s="4">
-        <v>35</v>
-      </c>
-      <c r="P290" s="4">
-        <v>41.4</v>
-      </c>
-      <c r="Q290" s="4">
-        <v>45.1</v>
-      </c>
-      <c r="R290" s="4">
-        <v>51.7</v>
-      </c>
-      <c r="S290" s="4">
-        <v>62.4</v>
-      </c>
-      <c r="T290" s="4">
-        <v>65.7</v>
-      </c>
-      <c r="U290" s="4">
-        <v>68.8</v>
-      </c>
-      <c r="V290" s="4">
-        <v>69.900000000000006</v>
-      </c>
-      <c r="W290" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="291" spans="1:23" ht="27" x14ac:dyDescent="0.25">
-      <c r="A291" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="B291" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="C291" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="D291" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E291" s="3" t="s">
+      <c r="F291" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="G291" s="5">
+        <v>96.04</v>
+      </c>
+      <c r="H291" s="5">
+        <v>90.68</v>
+      </c>
+      <c r="I291" s="5">
+        <v>111.55</v>
+      </c>
+      <c r="J291" s="5">
+        <v>127.11</v>
+      </c>
+      <c r="K291" s="5">
+        <v>82.28</v>
+      </c>
+      <c r="L291" s="5">
+        <v>100.19</v>
+      </c>
+      <c r="M291" s="5">
+        <v>148.99</v>
+      </c>
+      <c r="N291" s="5">
+        <v>222.11</v>
+      </c>
+      <c r="O291" s="5">
+        <v>244.93</v>
+      </c>
+      <c r="P291" s="5">
+        <v>223.31</v>
+      </c>
+      <c r="Q291" s="5">
+        <v>225.08</v>
+      </c>
+      <c r="R291" s="5">
+        <v>296.20999999999998</v>
+      </c>
+      <c r="S291" s="5">
+        <v>2661.32</v>
+      </c>
+      <c r="T291" s="5">
+        <v>1701.94</v>
+      </c>
+      <c r="U291" s="5">
+        <v>705.25</v>
+      </c>
+      <c r="V291" s="3"/>
+      <c r="W291" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="292" spans="1:23" ht="72" x14ac:dyDescent="0.25">
+      <c r="A292" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="F291" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G291" s="4">
-        <v>13.5</v>
-      </c>
-      <c r="H291" s="4">
-        <v>15.7</v>
-      </c>
-      <c r="I291" s="4">
-        <v>17.2</v>
-      </c>
-      <c r="J291" s="4">
-        <v>12.7</v>
-      </c>
-      <c r="K291" s="4">
-        <v>15.5</v>
-      </c>
-      <c r="L291" s="4">
-        <v>18.3</v>
-      </c>
-      <c r="M291" s="4">
-        <v>19.8</v>
-      </c>
-      <c r="N291" s="4">
-        <v>18.8</v>
-      </c>
-      <c r="O291" s="4">
-        <v>22.4</v>
-      </c>
-      <c r="P291" s="4">
-        <v>28.5</v>
-      </c>
-      <c r="Q291" s="4">
-        <v>29.4</v>
-      </c>
-      <c r="R291" s="4">
-        <v>35</v>
-      </c>
-      <c r="S291" s="4">
-        <v>39.5</v>
-      </c>
-      <c r="T291" s="4">
-        <v>44.4</v>
-      </c>
-      <c r="U291" s="4">
-        <v>50.8</v>
-      </c>
-      <c r="V291" s="4">
-        <v>51.4</v>
-      </c>
-      <c r="W291" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="292" spans="1:23" ht="27" x14ac:dyDescent="0.25">
-      <c r="A292" s="2" t="s">
-        <v>383</v>
-      </c>
       <c r="B292" s="2" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="E292" s="3" t="s">
-        <v>402</v>
+        <v>28</v>
       </c>
       <c r="F292" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G292" s="4">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="H292" s="4">
-        <v>5</v>
-      </c>
-      <c r="I292" s="4">
-        <v>6.8</v>
-      </c>
-      <c r="J292" s="4">
-        <v>3.7</v>
-      </c>
-      <c r="K292" s="4">
-        <v>6.6</v>
-      </c>
-      <c r="L292" s="4">
-        <v>6</v>
-      </c>
-      <c r="M292" s="4">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="N292" s="4">
-        <v>8.4</v>
-      </c>
-      <c r="O292" s="4">
-        <v>10.9</v>
-      </c>
-      <c r="P292" s="4">
-        <v>12.2</v>
-      </c>
-      <c r="Q292" s="4">
-        <v>13.5</v>
-      </c>
-      <c r="R292" s="4">
-        <v>15.8</v>
-      </c>
-      <c r="S292" s="4">
-        <v>23.6</v>
-      </c>
-      <c r="T292" s="4">
-        <v>26.1</v>
-      </c>
-      <c r="U292" s="4">
-        <v>27.4</v>
-      </c>
-      <c r="V292" s="4">
-        <v>27.6</v>
-      </c>
+      <c r="G292" s="5">
+        <v>0.08</v>
+      </c>
+      <c r="H292" s="5">
+        <v>0.08</v>
+      </c>
+      <c r="I292" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="J292" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="K292" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="L292" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="M292" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="N292" s="5">
+        <v>0.13</v>
+      </c>
+      <c r="O292" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="P292" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="Q292" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="R292" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="S292" s="5">
+        <v>0.53</v>
+      </c>
+      <c r="T292" s="5">
+        <v>0.33</v>
+      </c>
+      <c r="U292" s="5">
+        <v>0.21</v>
+      </c>
+      <c r="V292" s="3"/>
       <c r="W292" s="2" t="s">
-        <v>30</v>
+        <v>405</v>
       </c>
     </row>
     <row r="293" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
-        <v>383</v>
+        <v>401</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="D293" s="2" t="s">
         <v>27</v>
@@ -20291,69 +20285,63 @@
         <v>28</v>
       </c>
       <c r="F293" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G293" s="4">
-        <v>5.7</v>
-      </c>
-      <c r="H293" s="4">
-        <v>6</v>
-      </c>
-      <c r="I293" s="4">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="J293" s="4">
-        <v>4.3</v>
-      </c>
-      <c r="K293" s="4">
-        <v>4.7</v>
-      </c>
-      <c r="L293" s="4">
-        <v>4.5</v>
-      </c>
-      <c r="M293" s="4">
-        <v>3.3</v>
-      </c>
-      <c r="N293" s="4">
-        <v>3.8</v>
-      </c>
-      <c r="O293" s="4">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="P293" s="4">
-        <v>4.3</v>
-      </c>
-      <c r="Q293" s="4">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="R293" s="4">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="S293" s="4">
-        <v>3.8</v>
-      </c>
-      <c r="T293" s="4">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="U293" s="4">
-        <v>4.8</v>
-      </c>
-      <c r="V293" s="4">
-        <v>5.2</v>
+        <v>404</v>
+      </c>
+      <c r="G293" s="3"/>
+      <c r="H293" s="3"/>
+      <c r="I293" s="3"/>
+      <c r="J293" s="7">
+        <v>2.2850000000000001</v>
+      </c>
+      <c r="K293" s="7">
+        <v>1.1160000000000001</v>
+      </c>
+      <c r="L293" s="7">
+        <v>1.55</v>
+      </c>
+      <c r="M293" s="7">
+        <v>3.7469999999999999</v>
+      </c>
+      <c r="N293" s="7">
+        <v>3.8530000000000002</v>
+      </c>
+      <c r="O293" s="7">
+        <v>3.367</v>
+      </c>
+      <c r="P293" s="7">
+        <v>6.8940000000000001</v>
+      </c>
+      <c r="Q293" s="7">
+        <v>4.077</v>
+      </c>
+      <c r="R293" s="7">
+        <v>4.49</v>
+      </c>
+      <c r="S293" s="7">
+        <v>11.999000000000001</v>
+      </c>
+      <c r="T293" s="7">
+        <v>16.606000000000002</v>
+      </c>
+      <c r="U293" s="7">
+        <v>20.382000000000001</v>
+      </c>
+      <c r="V293" s="7">
+        <v>5.3920000000000003</v>
       </c>
       <c r="W293" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="294" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="294" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
-        <v>383</v>
+        <v>401</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="D294" s="2" t="s">
         <v>27</v>
@@ -20362,69 +20350,61 @@
         <v>28</v>
       </c>
       <c r="F294" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G294" s="6">
-        <v>674</v>
-      </c>
-      <c r="H294" s="6">
-        <v>605</v>
-      </c>
-      <c r="I294" s="6">
-        <v>1082</v>
-      </c>
-      <c r="J294" s="6">
-        <v>1219</v>
-      </c>
-      <c r="K294" s="6">
-        <v>1282</v>
-      </c>
-      <c r="L294" s="6">
-        <v>1456</v>
-      </c>
-      <c r="M294" s="6">
-        <v>1926</v>
-      </c>
-      <c r="N294" s="6">
-        <v>3182</v>
-      </c>
-      <c r="O294" s="6">
-        <v>3739</v>
-      </c>
-      <c r="P294" s="6">
-        <v>6484</v>
-      </c>
-      <c r="Q294" s="6">
-        <v>10420</v>
-      </c>
-      <c r="R294" s="6">
-        <v>29483</v>
-      </c>
-      <c r="S294" s="6">
-        <v>39683</v>
-      </c>
-      <c r="T294" s="6">
-        <v>80267</v>
-      </c>
-      <c r="U294" s="6">
-        <v>103449</v>
-      </c>
-      <c r="V294" s="6">
-        <v>260783</v>
-      </c>
+        <v>404</v>
+      </c>
+      <c r="G294" s="3"/>
+      <c r="H294" s="3"/>
+      <c r="I294" s="3"/>
+      <c r="J294" s="5">
+        <v>8.07</v>
+      </c>
+      <c r="K294" s="5">
+        <v>3.54</v>
+      </c>
+      <c r="L294" s="5">
+        <v>2.98</v>
+      </c>
+      <c r="M294" s="5">
+        <v>2.44</v>
+      </c>
+      <c r="N294" s="5">
+        <v>2.25</v>
+      </c>
+      <c r="O294" s="5">
+        <v>63.36</v>
+      </c>
+      <c r="P294" s="5">
+        <v>7.61</v>
+      </c>
+      <c r="Q294" s="5">
+        <v>6.64</v>
+      </c>
+      <c r="R294" s="5">
+        <v>3.65</v>
+      </c>
+      <c r="S294" s="5">
+        <v>9.59</v>
+      </c>
+      <c r="T294" s="5">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="U294" s="5">
+        <v>8.32</v>
+      </c>
+      <c r="V294" s="3"/>
       <c r="W294" s="2" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="295" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="295" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
-        <v>383</v>
+        <v>401</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="D295" s="2" t="s">
         <v>27</v>
@@ -20433,43 +20413,55 @@
         <v>28</v>
       </c>
       <c r="F295" s="3" t="s">
-        <v>34</v>
+        <v>416</v>
       </c>
       <c r="G295" s="3"/>
       <c r="H295" s="3"/>
       <c r="I295" s="3"/>
       <c r="J295" s="3"/>
-      <c r="K295" s="3"/>
-      <c r="L295" s="3"/>
-      <c r="M295" s="3"/>
-      <c r="N295" s="3"/>
+      <c r="K295" s="6">
+        <v>1</v>
+      </c>
+      <c r="L295" s="6">
+        <v>1</v>
+      </c>
+      <c r="M295" s="6">
+        <v>8</v>
+      </c>
+      <c r="N295" s="6">
+        <v>2</v>
+      </c>
       <c r="O295" s="3"/>
-      <c r="P295" s="3"/>
-      <c r="Q295" s="3"/>
-      <c r="R295" s="5">
-        <v>18.93</v>
-      </c>
+      <c r="P295" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q295" s="6">
+        <v>2</v>
+      </c>
+      <c r="R295" s="3"/>
       <c r="S295" s="3"/>
-      <c r="T295" s="5">
-        <v>21.3</v>
-      </c>
-      <c r="U295" s="3"/>
-      <c r="V295" s="5">
-        <v>23.01</v>
+      <c r="T295" s="6">
+        <v>8</v>
+      </c>
+      <c r="U295" s="6">
+        <v>7</v>
+      </c>
+      <c r="V295" s="6">
+        <v>2</v>
       </c>
       <c r="W295" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="296" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="296" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="D296" s="2" t="s">
         <v>27</v>
@@ -20478,67 +20470,65 @@
         <v>28</v>
       </c>
       <c r="F296" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="G296" s="5">
-        <v>377.75</v>
-      </c>
-      <c r="H296" s="5">
-        <v>417.47</v>
-      </c>
-      <c r="I296" s="5">
-        <v>421.06</v>
-      </c>
-      <c r="J296" s="5">
-        <v>487.12</v>
-      </c>
-      <c r="K296" s="5">
-        <v>451.84</v>
-      </c>
-      <c r="L296" s="5">
-        <v>440.89</v>
-      </c>
-      <c r="M296" s="5">
-        <v>662.95</v>
-      </c>
-      <c r="N296" s="5">
-        <v>679.46</v>
-      </c>
-      <c r="O296" s="5">
-        <v>766.04</v>
-      </c>
-      <c r="P296" s="5">
-        <v>776.56</v>
-      </c>
-      <c r="Q296" s="5">
-        <v>829.27</v>
-      </c>
-      <c r="R296" s="5">
-        <v>983.51</v>
-      </c>
-      <c r="S296" s="5">
-        <v>3494.39</v>
-      </c>
-      <c r="T296" s="5">
-        <v>2580.38</v>
-      </c>
-      <c r="U296" s="5">
-        <v>1840.15</v>
-      </c>
-      <c r="V296" s="3"/>
+        <v>416</v>
+      </c>
+      <c r="G296" s="3"/>
+      <c r="H296" s="3"/>
+      <c r="I296" s="6">
+        <v>2</v>
+      </c>
+      <c r="J296" s="6">
+        <v>2</v>
+      </c>
+      <c r="K296" s="6">
+        <v>1</v>
+      </c>
+      <c r="L296" s="6">
+        <v>1</v>
+      </c>
+      <c r="M296" s="6">
+        <v>1</v>
+      </c>
+      <c r="N296" s="6">
+        <v>1</v>
+      </c>
+      <c r="O296" s="6">
+        <v>1</v>
+      </c>
+      <c r="P296" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q296" s="6">
+        <v>4</v>
+      </c>
+      <c r="R296" s="6">
+        <v>1</v>
+      </c>
+      <c r="S296" s="6">
+        <v>1</v>
+      </c>
+      <c r="T296" s="6">
+        <v>0</v>
+      </c>
+      <c r="U296" s="6">
+        <v>4</v>
+      </c>
+      <c r="V296" s="6">
+        <v>2</v>
+      </c>
       <c r="W296" s="2" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="297" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="297" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="D297" s="2" t="s">
         <v>27</v>
@@ -20547,67 +20537,61 @@
         <v>28</v>
       </c>
       <c r="F297" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="G297" s="5">
-        <v>96.04</v>
-      </c>
-      <c r="H297" s="5">
-        <v>90.68</v>
-      </c>
-      <c r="I297" s="5">
-        <v>111.55</v>
-      </c>
-      <c r="J297" s="5">
-        <v>127.11</v>
-      </c>
-      <c r="K297" s="5">
-        <v>82.28</v>
-      </c>
-      <c r="L297" s="5">
-        <v>100.19</v>
-      </c>
-      <c r="M297" s="5">
-        <v>148.99</v>
-      </c>
-      <c r="N297" s="5">
-        <v>222.11</v>
-      </c>
-      <c r="O297" s="5">
-        <v>244.93</v>
-      </c>
-      <c r="P297" s="5">
-        <v>223.31</v>
-      </c>
-      <c r="Q297" s="5">
-        <v>225.08</v>
-      </c>
-      <c r="R297" s="5">
-        <v>296.20999999999998</v>
-      </c>
-      <c r="S297" s="5">
-        <v>2661.32</v>
-      </c>
-      <c r="T297" s="5">
-        <v>1701.94</v>
-      </c>
-      <c r="U297" s="5">
-        <v>705.25</v>
-      </c>
-      <c r="V297" s="3"/>
+        <v>32</v>
+      </c>
+      <c r="G297" s="3"/>
+      <c r="H297" s="3"/>
+      <c r="I297" s="3"/>
+      <c r="J297" s="3"/>
+      <c r="K297" s="6">
+        <v>5</v>
+      </c>
+      <c r="L297" s="6">
+        <v>13</v>
+      </c>
+      <c r="M297" s="6">
+        <v>19</v>
+      </c>
+      <c r="N297" s="6">
+        <v>18</v>
+      </c>
+      <c r="O297" s="6">
+        <v>15</v>
+      </c>
+      <c r="P297" s="6">
+        <v>15</v>
+      </c>
+      <c r="Q297" s="6">
+        <v>8</v>
+      </c>
+      <c r="R297" s="6">
+        <v>28</v>
+      </c>
+      <c r="S297" s="6">
+        <v>53</v>
+      </c>
+      <c r="T297" s="6">
+        <v>65</v>
+      </c>
+      <c r="U297" s="6">
+        <v>70</v>
+      </c>
+      <c r="V297" s="6">
+        <v>69</v>
+      </c>
       <c r="W297" s="2" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="298" spans="1:23" ht="72" x14ac:dyDescent="0.25">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="298" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="D298" s="2" t="s">
         <v>27</v>
@@ -20616,433 +20600,47 @@
         <v>28</v>
       </c>
       <c r="F298" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G298" s="5">
-        <v>0.08</v>
-      </c>
-      <c r="H298" s="5">
-        <v>0.08</v>
-      </c>
-      <c r="I298" s="5">
-        <v>0.09</v>
-      </c>
-      <c r="J298" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="K298" s="5">
-        <v>0.09</v>
-      </c>
-      <c r="L298" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="M298" s="5">
-        <v>0.15</v>
-      </c>
-      <c r="N298" s="5">
-        <v>0.13</v>
-      </c>
-      <c r="O298" s="5">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="P298" s="5">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="Q298" s="5">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="R298" s="5">
-        <v>0.15</v>
-      </c>
-      <c r="S298" s="5">
-        <v>0.53</v>
-      </c>
-      <c r="T298" s="5">
-        <v>0.33</v>
-      </c>
-      <c r="U298" s="5">
-        <v>0.21</v>
-      </c>
-      <c r="V298" s="3"/>
+        <v>32</v>
+      </c>
+      <c r="G298" s="3"/>
+      <c r="H298" s="3"/>
+      <c r="I298" s="3"/>
+      <c r="J298" s="3"/>
+      <c r="K298" s="3"/>
+      <c r="L298" s="3"/>
+      <c r="M298" s="3"/>
+      <c r="N298" s="3"/>
+      <c r="O298" s="3"/>
+      <c r="P298" s="3"/>
+      <c r="Q298" s="3"/>
+      <c r="R298" s="3"/>
+      <c r="S298" s="3"/>
+      <c r="T298" s="6">
+        <v>114</v>
+      </c>
+      <c r="U298" s="6">
+        <v>61</v>
+      </c>
+      <c r="V298" s="6">
+        <v>97</v>
+      </c>
       <c r="W298" s="2" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="299" spans="1:23" ht="27" x14ac:dyDescent="0.25">
-      <c r="A299" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="B299" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="C299" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="D299" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E299" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F299" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="G299" s="3"/>
-      <c r="H299" s="3"/>
-      <c r="I299" s="3"/>
-      <c r="J299" s="7">
-        <v>2.2850000000000001</v>
-      </c>
-      <c r="K299" s="7">
-        <v>1.1160000000000001</v>
-      </c>
-      <c r="L299" s="7">
-        <v>1.55</v>
-      </c>
-      <c r="M299" s="7">
-        <v>3.7469999999999999</v>
-      </c>
-      <c r="N299" s="7">
-        <v>3.8530000000000002</v>
-      </c>
-      <c r="O299" s="7">
-        <v>3.367</v>
-      </c>
-      <c r="P299" s="7">
-        <v>6.8940000000000001</v>
-      </c>
-      <c r="Q299" s="7">
-        <v>4.077</v>
-      </c>
-      <c r="R299" s="7">
-        <v>4.49</v>
-      </c>
-      <c r="S299" s="7">
-        <v>11.999000000000001</v>
-      </c>
-      <c r="T299" s="7">
-        <v>16.606000000000002</v>
-      </c>
-      <c r="U299" s="7">
-        <v>20.382000000000001</v>
-      </c>
-      <c r="V299" s="7">
-        <v>5.3920000000000003</v>
-      </c>
-      <c r="W299" s="2" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="300" spans="1:23" ht="27" x14ac:dyDescent="0.25">
-      <c r="A300" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="B300" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="C300" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="D300" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E300" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F300" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="G300" s="3"/>
-      <c r="H300" s="3"/>
-      <c r="I300" s="3"/>
-      <c r="J300" s="5">
-        <v>8.07</v>
-      </c>
-      <c r="K300" s="5">
-        <v>3.54</v>
-      </c>
-      <c r="L300" s="5">
-        <v>2.98</v>
-      </c>
-      <c r="M300" s="5">
-        <v>2.44</v>
-      </c>
-      <c r="N300" s="5">
-        <v>2.25</v>
-      </c>
-      <c r="O300" s="5">
-        <v>63.36</v>
-      </c>
-      <c r="P300" s="5">
-        <v>7.61</v>
-      </c>
-      <c r="Q300" s="5">
-        <v>6.64</v>
-      </c>
-      <c r="R300" s="5">
-        <v>3.65</v>
-      </c>
-      <c r="S300" s="5">
-        <v>9.59</v>
-      </c>
-      <c r="T300" s="5">
-        <v>4.2699999999999996</v>
-      </c>
-      <c r="U300" s="5">
-        <v>8.32</v>
-      </c>
-      <c r="V300" s="3"/>
-      <c r="W300" s="2" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="301" spans="1:23" ht="27" x14ac:dyDescent="0.25">
-      <c r="A301" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="B301" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="C301" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="D301" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E301" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F301" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="G301" s="3"/>
-      <c r="H301" s="3"/>
-      <c r="I301" s="3"/>
-      <c r="J301" s="3"/>
-      <c r="K301" s="6">
-        <v>1</v>
-      </c>
-      <c r="L301" s="6">
-        <v>1</v>
-      </c>
-      <c r="M301" s="6">
-        <v>8</v>
-      </c>
-      <c r="N301" s="6">
-        <v>2</v>
-      </c>
-      <c r="O301" s="3"/>
-      <c r="P301" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q301" s="6">
-        <v>2</v>
-      </c>
-      <c r="R301" s="3"/>
-      <c r="S301" s="3"/>
-      <c r="T301" s="6">
-        <v>8</v>
-      </c>
-      <c r="U301" s="6">
-        <v>7</v>
-      </c>
-      <c r="V301" s="6">
-        <v>2</v>
-      </c>
-      <c r="W301" s="2" t="s">
+    </row>
+    <row r="299" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A300" s="10" t="s">
         <v>425</v>
       </c>
-    </row>
-    <row r="302" spans="1:23" ht="27" x14ac:dyDescent="0.25">
-      <c r="A302" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="B302" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="C302" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="D302" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E302" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F302" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="G302" s="3"/>
-      <c r="H302" s="3"/>
-      <c r="I302" s="6">
-        <v>2</v>
-      </c>
-      <c r="J302" s="6">
-        <v>2</v>
-      </c>
-      <c r="K302" s="6">
-        <v>1</v>
-      </c>
-      <c r="L302" s="6">
-        <v>1</v>
-      </c>
-      <c r="M302" s="6">
-        <v>1</v>
-      </c>
-      <c r="N302" s="6">
-        <v>1</v>
-      </c>
-      <c r="O302" s="6">
-        <v>1</v>
-      </c>
-      <c r="P302" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q302" s="6">
-        <v>4</v>
-      </c>
-      <c r="R302" s="6">
-        <v>1</v>
-      </c>
-      <c r="S302" s="6">
-        <v>1</v>
-      </c>
-      <c r="T302" s="6">
-        <v>0</v>
-      </c>
-      <c r="U302" s="6">
-        <v>4</v>
-      </c>
-      <c r="V302" s="6">
-        <v>2</v>
-      </c>
-      <c r="W302" s="2" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="303" spans="1:23" ht="27" x14ac:dyDescent="0.25">
-      <c r="A303" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="B303" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="C303" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="D303" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E303" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F303" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G303" s="3"/>
-      <c r="H303" s="3"/>
-      <c r="I303" s="3"/>
-      <c r="J303" s="3"/>
-      <c r="K303" s="6">
-        <v>5</v>
-      </c>
-      <c r="L303" s="6">
-        <v>13</v>
-      </c>
-      <c r="M303" s="6">
-        <v>19</v>
-      </c>
-      <c r="N303" s="6">
-        <v>18</v>
-      </c>
-      <c r="O303" s="6">
-        <v>15</v>
-      </c>
-      <c r="P303" s="6">
-        <v>15</v>
-      </c>
-      <c r="Q303" s="6">
-        <v>8</v>
-      </c>
-      <c r="R303" s="6">
-        <v>28</v>
-      </c>
-      <c r="S303" s="6">
-        <v>53</v>
-      </c>
-      <c r="T303" s="6">
-        <v>65</v>
-      </c>
-      <c r="U303" s="6">
-        <v>70</v>
-      </c>
-      <c r="V303" s="6">
-        <v>69</v>
-      </c>
-      <c r="W303" s="2" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="304" spans="1:23" ht="45" x14ac:dyDescent="0.25">
-      <c r="A304" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="B304" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="C304" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="D304" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E304" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F304" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G304" s="3"/>
-      <c r="H304" s="3"/>
-      <c r="I304" s="3"/>
-      <c r="J304" s="3"/>
-      <c r="K304" s="3"/>
-      <c r="L304" s="3"/>
-      <c r="M304" s="3"/>
-      <c r="N304" s="3"/>
-      <c r="O304" s="3"/>
-      <c r="P304" s="3"/>
-      <c r="Q304" s="3"/>
-      <c r="R304" s="3"/>
-      <c r="S304" s="3"/>
-      <c r="T304" s="6">
-        <v>114</v>
-      </c>
-      <c r="U304" s="6">
-        <v>61</v>
-      </c>
-      <c r="V304" s="6">
-        <v>97</v>
-      </c>
-      <c r="W304" s="2" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="305" spans="1:2" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="306" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="307" spans="1:2" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A307" s="10" t="s">
-        <v>433</v>
-      </c>
-      <c r="B307" s="8"/>
-    </row>
-    <row r="308" spans="1:2" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="B300" s="8"/>
+    </row>
   </sheetData>
   <autoFilter ref="A3:C3" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A307:B307"/>
+    <mergeCell ref="A300:B300"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>

--- a/assets/excel/en/national_sdg_indicators.xlsx
+++ b/assets/excel/en/national_sdg_indicators.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sidwab\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{296A1576-BDF5-4D45-95D6-CB0104835314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C68FBFFF-6B7A-4C44-A574-432027A15113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2104" uniqueCount="431">
   <si>
     <t>sdg.gov.pl/en</t>
   </si>
@@ -952,12 +952,27 @@
     <t>12.1.c Circular material use rate</t>
   </si>
   <si>
+    <t>12.1.d Amount of food wasted per capita</t>
+  </si>
+  <si>
+    <t>kg</t>
+  </si>
+  <si>
     <t>Development of ecological agriculture</t>
   </si>
   <si>
     <t>12.2.a Share of certified agricultural land area of organic farms in total agricultural land area of farms</t>
   </si>
   <si>
+    <t>12.2.b Number of organic farms</t>
+  </si>
+  <si>
+    <t>thous.</t>
+  </si>
+  <si>
+    <t>Chief Inspectorate of Commercial Quality of Agri-food Products (GIJHARS)</t>
+  </si>
+  <si>
     <t>Goal 13. Climate action</t>
   </si>
   <si>
@@ -1306,7 +1321,7 @@
     <t>The Ministry of Economic Development and Technology / The Chancellery of the  Prime Minister</t>
   </si>
   <si>
-    <t>Last update: 05-08-2026, 10:54</t>
+    <t>Last update: 05-08-2026, 13:23</t>
   </si>
 </sst>
 </file>
@@ -1852,7 +1867,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W300"/>
+  <dimension ref="A1:W302"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" customWidth="1"/>
@@ -16615,15 +16630,15 @@
         <v>87</v>
       </c>
     </row>
-    <row r="238" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
         <v>301</v>
       </c>
       <c r="B238" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C238" s="2" t="s">
         <v>307</v>
-      </c>
-      <c r="C238" s="2" t="s">
-        <v>308</v>
       </c>
       <c r="D238" s="2" t="s">
         <v>27</v>
@@ -16632,61 +16647,45 @@
         <v>28</v>
       </c>
       <c r="F238" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G238" s="5">
-        <v>2.0699999999999998</v>
-      </c>
-      <c r="H238" s="5">
-        <v>2.48</v>
-      </c>
-      <c r="I238" s="5">
-        <v>3.05</v>
-      </c>
-      <c r="J238" s="5">
-        <v>3.37</v>
-      </c>
-      <c r="K238" s="5">
-        <v>3.82</v>
-      </c>
-      <c r="L238" s="5">
-        <v>3.45</v>
-      </c>
-      <c r="M238" s="5">
-        <v>2.96</v>
-      </c>
-      <c r="N238" s="5">
-        <v>2.62</v>
-      </c>
-      <c r="O238" s="5">
-        <v>2.48</v>
-      </c>
-      <c r="P238" s="5">
-        <v>2.66</v>
-      </c>
-      <c r="Q238" s="5">
-        <v>2.68</v>
-      </c>
-      <c r="R238" s="3"/>
-      <c r="S238" s="3"/>
-      <c r="T238" s="5">
-        <v>3.1</v>
+        <v>308</v>
+      </c>
+      <c r="G238" s="3"/>
+      <c r="H238" s="3"/>
+      <c r="I238" s="3"/>
+      <c r="J238" s="3"/>
+      <c r="K238" s="3"/>
+      <c r="L238" s="3"/>
+      <c r="M238" s="3"/>
+      <c r="N238" s="3"/>
+      <c r="O238" s="3"/>
+      <c r="P238" s="3"/>
+      <c r="Q238" s="6">
+        <v>120</v>
+      </c>
+      <c r="R238" s="6">
+        <v>122</v>
+      </c>
+      <c r="S238" s="6">
+        <v>123</v>
+      </c>
+      <c r="T238" s="6">
+        <v>127</v>
       </c>
       <c r="U238" s="3"/>
       <c r="V238" s="3"/>
       <c r="W238" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="239" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="239" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B239" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="B239" s="2" t="s">
+      <c r="C239" s="2" t="s">
         <v>310</v>
-      </c>
-      <c r="C239" s="2" t="s">
-        <v>311</v>
       </c>
       <c r="D239" s="2" t="s">
         <v>27</v>
@@ -16695,67 +16694,61 @@
         <v>28</v>
       </c>
       <c r="F239" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="G239" s="4">
-        <v>100</v>
-      </c>
-      <c r="H239" s="4">
-        <v>99.8</v>
-      </c>
-      <c r="I239" s="4">
-        <v>97.5</v>
-      </c>
-      <c r="J239" s="4">
-        <v>96.3</v>
-      </c>
-      <c r="K239" s="4">
-        <v>92.6</v>
-      </c>
-      <c r="L239" s="4">
-        <v>93.6</v>
-      </c>
-      <c r="M239" s="4">
-        <v>96.8</v>
-      </c>
-      <c r="N239" s="4">
-        <v>100.7</v>
-      </c>
-      <c r="O239" s="4">
-        <v>100.5</v>
-      </c>
-      <c r="P239" s="4">
-        <v>95</v>
-      </c>
-      <c r="Q239" s="4">
-        <v>90.4</v>
-      </c>
-      <c r="R239" s="4">
-        <v>99</v>
-      </c>
-      <c r="S239" s="4">
-        <v>94.2</v>
-      </c>
-      <c r="T239" s="4">
-        <v>84.9</v>
-      </c>
-      <c r="U239" s="4">
-        <v>83.4</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="G239" s="5">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="H239" s="5">
+        <v>2.48</v>
+      </c>
+      <c r="I239" s="5">
+        <v>3.05</v>
+      </c>
+      <c r="J239" s="5">
+        <v>3.37</v>
+      </c>
+      <c r="K239" s="5">
+        <v>3.82</v>
+      </c>
+      <c r="L239" s="5">
+        <v>3.45</v>
+      </c>
+      <c r="M239" s="5">
+        <v>2.96</v>
+      </c>
+      <c r="N239" s="5">
+        <v>2.62</v>
+      </c>
+      <c r="O239" s="5">
+        <v>2.48</v>
+      </c>
+      <c r="P239" s="5">
+        <v>2.66</v>
+      </c>
+      <c r="Q239" s="5">
+        <v>2.68</v>
+      </c>
+      <c r="R239" s="3"/>
+      <c r="S239" s="3"/>
+      <c r="T239" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="U239" s="3"/>
       <c r="V239" s="3"/>
       <c r="W239" s="2" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="240" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="240" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B240" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="B240" s="2" t="s">
-        <v>310</v>
-      </c>
       <c r="C240" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D240" s="2" t="s">
         <v>27</v>
@@ -16764,259 +16757,259 @@
         <v>28</v>
       </c>
       <c r="F240" s="3" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="G240" s="4">
-        <v>100</v>
+        <v>20.6</v>
       </c>
       <c r="H240" s="4">
-        <v>99.7</v>
+        <v>23.4</v>
       </c>
       <c r="I240" s="4">
-        <v>97.8</v>
+        <v>25.9</v>
       </c>
       <c r="J240" s="4">
-        <v>96.7</v>
+        <v>26.6</v>
       </c>
       <c r="K240" s="4">
-        <v>93.6</v>
+        <v>24.8</v>
       </c>
       <c r="L240" s="4">
-        <v>94.3</v>
+        <v>22.3</v>
       </c>
       <c r="M240" s="4">
-        <v>96.9</v>
+        <v>22.4</v>
       </c>
       <c r="N240" s="4">
-        <v>100.5</v>
+        <v>20.3</v>
       </c>
       <c r="O240" s="4">
-        <v>100.4</v>
+        <v>19.2</v>
       </c>
       <c r="P240" s="4">
-        <v>94.9</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="Q240" s="4">
-        <v>91.2</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="R240" s="4">
-        <v>98.2</v>
+        <v>20</v>
       </c>
       <c r="S240" s="4">
-        <v>93.6</v>
+        <v>21.2</v>
       </c>
       <c r="T240" s="4">
-        <v>85.7</v>
+        <v>22.4</v>
       </c>
       <c r="U240" s="4">
-        <v>84.2</v>
+        <v>23.2</v>
       </c>
       <c r="V240" s="3"/>
       <c r="W240" s="2" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="241" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B241" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C241" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="C241" s="2" t="s">
-        <v>317</v>
-      </c>
       <c r="D241" s="2" t="s">
-        <v>187</v>
+        <v>27</v>
       </c>
       <c r="E241" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F241" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G241" s="5">
-        <v>9.2799999999999994</v>
-      </c>
-      <c r="H241" s="5">
-        <v>10.34</v>
-      </c>
-      <c r="I241" s="5">
-        <v>10.96</v>
-      </c>
-      <c r="J241" s="5">
-        <v>11.45</v>
-      </c>
-      <c r="K241" s="5">
-        <v>11.61</v>
-      </c>
-      <c r="L241" s="5">
-        <v>11.88</v>
-      </c>
-      <c r="M241" s="5">
-        <v>11.4</v>
-      </c>
-      <c r="N241" s="5">
-        <v>11.06</v>
-      </c>
-      <c r="O241" s="5">
-        <v>14.94</v>
-      </c>
-      <c r="P241" s="5">
-        <v>15.38</v>
-      </c>
-      <c r="Q241" s="5">
-        <v>16.100000000000001</v>
-      </c>
-      <c r="R241" s="5">
-        <v>15.6</v>
-      </c>
-      <c r="S241" s="5">
-        <v>16.64</v>
-      </c>
-      <c r="T241" s="5">
-        <v>16.649999999999999</v>
-      </c>
-      <c r="U241" s="5">
-        <v>17.77</v>
+        <v>317</v>
+      </c>
+      <c r="G241" s="4">
+        <v>100</v>
+      </c>
+      <c r="H241" s="4">
+        <v>99.8</v>
+      </c>
+      <c r="I241" s="4">
+        <v>97.5</v>
+      </c>
+      <c r="J241" s="4">
+        <v>96.3</v>
+      </c>
+      <c r="K241" s="4">
+        <v>92.6</v>
+      </c>
+      <c r="L241" s="4">
+        <v>93.6</v>
+      </c>
+      <c r="M241" s="4">
+        <v>96.8</v>
+      </c>
+      <c r="N241" s="4">
+        <v>100.7</v>
+      </c>
+      <c r="O241" s="4">
+        <v>100.5</v>
+      </c>
+      <c r="P241" s="4">
+        <v>95</v>
+      </c>
+      <c r="Q241" s="4">
+        <v>90.4</v>
+      </c>
+      <c r="R241" s="4">
+        <v>99</v>
+      </c>
+      <c r="S241" s="4">
+        <v>94.2</v>
+      </c>
+      <c r="T241" s="4">
+        <v>84.9</v>
+      </c>
+      <c r="U241" s="4">
+        <v>83.4</v>
       </c>
       <c r="V241" s="3"/>
       <c r="W241" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="242" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="242" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>187</v>
+        <v>27</v>
       </c>
       <c r="E242" s="3" t="s">
-        <v>188</v>
+        <v>28</v>
       </c>
       <c r="F242" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G242" s="5">
-        <v>6.64</v>
-      </c>
-      <c r="H242" s="5">
-        <v>6.92</v>
-      </c>
-      <c r="I242" s="5">
-        <v>6.53</v>
-      </c>
-      <c r="J242" s="5">
-        <v>6.67</v>
-      </c>
-      <c r="K242" s="5">
-        <v>6.32</v>
-      </c>
-      <c r="L242" s="5">
-        <v>5.69</v>
-      </c>
-      <c r="M242" s="5">
-        <v>3.97</v>
-      </c>
-      <c r="N242" s="5">
-        <v>4.2300000000000004</v>
-      </c>
-      <c r="O242" s="5">
-        <v>5.72</v>
-      </c>
-      <c r="P242" s="5">
-        <v>6.2</v>
-      </c>
-      <c r="Q242" s="5">
-        <v>6.58</v>
-      </c>
-      <c r="R242" s="5">
-        <v>5.67</v>
-      </c>
-      <c r="S242" s="5">
-        <v>5.79</v>
-      </c>
-      <c r="T242" s="5">
-        <v>6.34</v>
-      </c>
-      <c r="U242" s="5">
-        <v>6.03</v>
+        <v>320</v>
+      </c>
+      <c r="G242" s="4">
+        <v>100</v>
+      </c>
+      <c r="H242" s="4">
+        <v>99.7</v>
+      </c>
+      <c r="I242" s="4">
+        <v>97.8</v>
+      </c>
+      <c r="J242" s="4">
+        <v>96.7</v>
+      </c>
+      <c r="K242" s="4">
+        <v>93.6</v>
+      </c>
+      <c r="L242" s="4">
+        <v>94.3</v>
+      </c>
+      <c r="M242" s="4">
+        <v>96.9</v>
+      </c>
+      <c r="N242" s="4">
+        <v>100.5</v>
+      </c>
+      <c r="O242" s="4">
+        <v>100.4</v>
+      </c>
+      <c r="P242" s="4">
+        <v>94.9</v>
+      </c>
+      <c r="Q242" s="4">
+        <v>91.2</v>
+      </c>
+      <c r="R242" s="4">
+        <v>98.2</v>
+      </c>
+      <c r="S242" s="4">
+        <v>93.6</v>
+      </c>
+      <c r="T242" s="4">
+        <v>85.7</v>
+      </c>
+      <c r="U242" s="4">
+        <v>84.2</v>
       </c>
       <c r="V242" s="3"/>
       <c r="W242" s="2" t="s">
-        <v>87</v>
+        <v>318</v>
       </c>
     </row>
     <row r="243" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="D243" s="2" t="s">
         <v>187</v>
       </c>
       <c r="E243" s="3" t="s">
-        <v>189</v>
+        <v>28</v>
       </c>
       <c r="F243" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G243" s="5">
-        <v>6.55</v>
+        <v>9.2799999999999994</v>
       </c>
       <c r="H243" s="5">
-        <v>8.08</v>
+        <v>10.34</v>
       </c>
       <c r="I243" s="5">
-        <v>10.61</v>
+        <v>10.96</v>
       </c>
       <c r="J243" s="5">
-        <v>10.68</v>
+        <v>11.45</v>
       </c>
       <c r="K243" s="5">
-        <v>12.36</v>
+        <v>11.61</v>
       </c>
       <c r="L243" s="5">
-        <v>13.4</v>
+        <v>11.88</v>
       </c>
       <c r="M243" s="5">
-        <v>13.34</v>
+        <v>11.4</v>
       </c>
       <c r="N243" s="5">
-        <v>13.08</v>
+        <v>11.06</v>
       </c>
       <c r="O243" s="5">
-        <v>13.03</v>
+        <v>14.94</v>
       </c>
       <c r="P243" s="5">
-        <v>14.36</v>
+        <v>15.38</v>
       </c>
       <c r="Q243" s="5">
-        <v>16.239999999999998</v>
+        <v>16.100000000000001</v>
       </c>
       <c r="R243" s="5">
-        <v>17.170000000000002</v>
+        <v>15.6</v>
       </c>
       <c r="S243" s="5">
-        <v>21.01</v>
+        <v>16.64</v>
       </c>
       <c r="T243" s="5">
-        <v>25.79</v>
+        <v>16.649999999999999</v>
       </c>
       <c r="U243" s="5">
-        <v>30.37</v>
+        <v>17.77</v>
       </c>
       <c r="V243" s="3"/>
       <c r="W243" s="2" t="s">
@@ -17025,67 +17018,67 @@
     </row>
     <row r="244" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="D244" s="2" t="s">
         <v>187</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F244" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G244" s="5">
-        <v>11.81</v>
+        <v>6.64</v>
       </c>
       <c r="H244" s="5">
-        <v>13.24</v>
+        <v>6.92</v>
       </c>
       <c r="I244" s="5">
-        <v>13.5</v>
+        <v>6.53</v>
       </c>
       <c r="J244" s="5">
-        <v>14.27</v>
+        <v>6.67</v>
       </c>
       <c r="K244" s="5">
-        <v>14.24</v>
+        <v>6.32</v>
       </c>
       <c r="L244" s="5">
-        <v>14.8</v>
+        <v>5.69</v>
       </c>
       <c r="M244" s="5">
-        <v>14.92</v>
+        <v>3.97</v>
       </c>
       <c r="N244" s="5">
-        <v>14.78</v>
+        <v>4.2300000000000004</v>
       </c>
       <c r="O244" s="5">
-        <v>21.47</v>
+        <v>5.72</v>
       </c>
       <c r="P244" s="5">
-        <v>22.01</v>
+        <v>6.2</v>
       </c>
       <c r="Q244" s="5">
-        <v>22.14</v>
+        <v>6.58</v>
       </c>
       <c r="R244" s="5">
-        <v>20.98</v>
+        <v>5.67</v>
       </c>
       <c r="S244" s="5">
-        <v>22.1</v>
+        <v>5.79</v>
       </c>
       <c r="T244" s="5">
-        <v>20.61</v>
+        <v>6.34</v>
       </c>
       <c r="U244" s="5">
-        <v>21.29</v>
+        <v>6.03</v>
       </c>
       <c r="V244" s="3"/>
       <c r="W244" s="2" t="s">
@@ -17094,205 +17087,205 @@
     </row>
     <row r="245" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="D245" s="2" t="s">
         <v>187</v>
       </c>
       <c r="E245" s="3" t="s">
-        <v>28</v>
+        <v>189</v>
       </c>
       <c r="F245" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="G245" s="6">
-        <v>563</v>
-      </c>
-      <c r="H245" s="6">
-        <v>531</v>
-      </c>
-      <c r="I245" s="6">
-        <v>661</v>
-      </c>
-      <c r="J245" s="6">
-        <v>778</v>
-      </c>
-      <c r="K245" s="6">
-        <v>847</v>
-      </c>
-      <c r="L245" s="6">
-        <v>909</v>
-      </c>
-      <c r="M245" s="6">
-        <v>930</v>
-      </c>
-      <c r="N245" s="6">
-        <v>946</v>
-      </c>
-      <c r="O245" s="6">
-        <v>991</v>
-      </c>
-      <c r="P245" s="6">
-        <v>1050</v>
-      </c>
-      <c r="Q245" s="6">
-        <v>1073</v>
-      </c>
-      <c r="R245" s="6">
-        <v>1189</v>
-      </c>
-      <c r="S245" s="6">
-        <v>1318</v>
-      </c>
-      <c r="T245" s="6">
-        <v>1372</v>
-      </c>
-      <c r="U245" s="6">
-        <v>1556</v>
+        <v>34</v>
+      </c>
+      <c r="G245" s="5">
+        <v>6.55</v>
+      </c>
+      <c r="H245" s="5">
+        <v>8.08</v>
+      </c>
+      <c r="I245" s="5">
+        <v>10.61</v>
+      </c>
+      <c r="J245" s="5">
+        <v>10.68</v>
+      </c>
+      <c r="K245" s="5">
+        <v>12.36</v>
+      </c>
+      <c r="L245" s="5">
+        <v>13.4</v>
+      </c>
+      <c r="M245" s="5">
+        <v>13.34</v>
+      </c>
+      <c r="N245" s="5">
+        <v>13.08</v>
+      </c>
+      <c r="O245" s="5">
+        <v>13.03</v>
+      </c>
+      <c r="P245" s="5">
+        <v>14.36</v>
+      </c>
+      <c r="Q245" s="5">
+        <v>16.239999999999998</v>
+      </c>
+      <c r="R245" s="5">
+        <v>17.170000000000002</v>
+      </c>
+      <c r="S245" s="5">
+        <v>21.01</v>
+      </c>
+      <c r="T245" s="5">
+        <v>25.79</v>
+      </c>
+      <c r="U245" s="5">
+        <v>30.37</v>
       </c>
       <c r="V245" s="3"/>
       <c r="W245" s="2" t="s">
-        <v>30</v>
+        <v>87</v>
       </c>
     </row>
     <row r="246" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="D246" s="2" t="s">
         <v>187</v>
       </c>
       <c r="E246" s="3" t="s">
-        <v>320</v>
+        <v>190</v>
       </c>
       <c r="F246" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="G246" s="6">
-        <v>440</v>
-      </c>
-      <c r="H246" s="6">
-        <v>101</v>
-      </c>
-      <c r="I246" s="6">
-        <v>151</v>
-      </c>
-      <c r="J246" s="6">
-        <v>217</v>
-      </c>
-      <c r="K246" s="6">
-        <v>239</v>
-      </c>
-      <c r="L246" s="6">
-        <v>674</v>
-      </c>
-      <c r="M246" s="6">
-        <v>705</v>
-      </c>
-      <c r="N246" s="6">
-        <v>712</v>
-      </c>
-      <c r="O246" s="6">
-        <v>743</v>
-      </c>
-      <c r="P246" s="6">
-        <v>788</v>
-      </c>
-      <c r="Q246" s="6">
-        <v>805</v>
-      </c>
-      <c r="R246" s="6">
-        <v>892</v>
-      </c>
-      <c r="S246" s="6">
-        <v>988</v>
-      </c>
-      <c r="T246" s="6">
-        <v>1029</v>
-      </c>
-      <c r="U246" s="6">
-        <v>1167</v>
+        <v>34</v>
+      </c>
+      <c r="G246" s="5">
+        <v>11.81</v>
+      </c>
+      <c r="H246" s="5">
+        <v>13.24</v>
+      </c>
+      <c r="I246" s="5">
+        <v>13.5</v>
+      </c>
+      <c r="J246" s="5">
+        <v>14.27</v>
+      </c>
+      <c r="K246" s="5">
+        <v>14.24</v>
+      </c>
+      <c r="L246" s="5">
+        <v>14.8</v>
+      </c>
+      <c r="M246" s="5">
+        <v>14.92</v>
+      </c>
+      <c r="N246" s="5">
+        <v>14.78</v>
+      </c>
+      <c r="O246" s="5">
+        <v>21.47</v>
+      </c>
+      <c r="P246" s="5">
+        <v>22.01</v>
+      </c>
+      <c r="Q246" s="5">
+        <v>22.14</v>
+      </c>
+      <c r="R246" s="5">
+        <v>20.98</v>
+      </c>
+      <c r="S246" s="5">
+        <v>22.1</v>
+      </c>
+      <c r="T246" s="5">
+        <v>20.61</v>
+      </c>
+      <c r="U246" s="5">
+        <v>21.29</v>
       </c>
       <c r="V246" s="3"/>
       <c r="W246" s="2" t="s">
-        <v>30</v>
+        <v>87</v>
       </c>
     </row>
     <row r="247" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="D247" s="2" t="s">
         <v>187</v>
       </c>
       <c r="E247" s="3" t="s">
-        <v>321</v>
+        <v>28</v>
       </c>
       <c r="F247" s="3" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="G247" s="6">
-        <v>123</v>
+        <v>563</v>
       </c>
       <c r="H247" s="6">
-        <v>101</v>
+        <v>531</v>
       </c>
       <c r="I247" s="6">
-        <v>151</v>
+        <v>661</v>
       </c>
       <c r="J247" s="6">
-        <v>217</v>
+        <v>778</v>
       </c>
       <c r="K247" s="6">
-        <v>239</v>
+        <v>847</v>
       </c>
       <c r="L247" s="6">
-        <v>235</v>
+        <v>909</v>
       </c>
       <c r="M247" s="6">
-        <v>225</v>
+        <v>930</v>
       </c>
       <c r="N247" s="6">
-        <v>234</v>
+        <v>946</v>
       </c>
       <c r="O247" s="6">
-        <v>248</v>
+        <v>991</v>
       </c>
       <c r="P247" s="6">
-        <v>263</v>
+        <v>1050</v>
       </c>
       <c r="Q247" s="6">
-        <v>268</v>
+        <v>1073</v>
       </c>
       <c r="R247" s="6">
-        <v>297</v>
+        <v>1189</v>
       </c>
       <c r="S247" s="6">
-        <v>329</v>
+        <v>1318</v>
       </c>
       <c r="T247" s="6">
-        <v>343</v>
+        <v>1372</v>
       </c>
       <c r="U247" s="6">
-        <v>389</v>
+        <v>1556</v>
       </c>
       <c r="V247" s="3"/>
       <c r="W247" s="2" t="s">
@@ -17301,148 +17294,148 @@
     </row>
     <row r="248" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>27</v>
+        <v>187</v>
       </c>
       <c r="E248" s="3" t="s">
-        <v>28</v>
+        <v>325</v>
       </c>
       <c r="F248" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G248" s="6">
-        <v>2218</v>
+        <v>440</v>
       </c>
       <c r="H248" s="6">
-        <v>3117</v>
+        <v>101</v>
       </c>
       <c r="I248" s="6">
-        <v>4139</v>
+        <v>151</v>
       </c>
       <c r="J248" s="6">
-        <v>5205</v>
+        <v>217</v>
       </c>
       <c r="K248" s="6">
-        <v>5793</v>
+        <v>239</v>
       </c>
       <c r="L248" s="6">
-        <v>7105</v>
+        <v>674</v>
       </c>
       <c r="M248" s="6">
-        <v>8017</v>
+        <v>705</v>
       </c>
       <c r="N248" s="6">
-        <v>8195</v>
+        <v>712</v>
       </c>
       <c r="O248" s="6">
-        <v>8486</v>
+        <v>743</v>
       </c>
       <c r="P248" s="6">
-        <v>9547</v>
+        <v>788</v>
       </c>
       <c r="Q248" s="6">
-        <v>12490</v>
+        <v>805</v>
       </c>
       <c r="R248" s="6">
-        <v>16935</v>
+        <v>892</v>
       </c>
       <c r="S248" s="6">
-        <v>22670</v>
+        <v>988</v>
       </c>
       <c r="T248" s="6">
-        <v>28779</v>
+        <v>1029</v>
       </c>
       <c r="U248" s="6">
-        <v>33623</v>
-      </c>
-      <c r="V248" s="6">
-        <v>37777</v>
-      </c>
+        <v>1167</v>
+      </c>
+      <c r="V248" s="3"/>
       <c r="W248" s="2" t="s">
-        <v>324</v>
+        <v>30</v>
       </c>
     </row>
     <row r="249" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C249" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D249" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E249" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="D249" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E249" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="F249" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G249" s="4">
-        <v>0.4</v>
-      </c>
-      <c r="H249" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="I249" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="J249" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="K249" s="4">
-        <v>0.7</v>
-      </c>
-      <c r="L249" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="M249" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="N249" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="O249" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="P249" s="4">
-        <v>0.7</v>
-      </c>
-      <c r="Q249" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="R249" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="S249" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="T249" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="U249" s="3"/>
+        <v>324</v>
+      </c>
+      <c r="G249" s="6">
+        <v>123</v>
+      </c>
+      <c r="H249" s="6">
+        <v>101</v>
+      </c>
+      <c r="I249" s="6">
+        <v>151</v>
+      </c>
+      <c r="J249" s="6">
+        <v>217</v>
+      </c>
+      <c r="K249" s="6">
+        <v>239</v>
+      </c>
+      <c r="L249" s="6">
+        <v>235</v>
+      </c>
+      <c r="M249" s="6">
+        <v>225</v>
+      </c>
+      <c r="N249" s="6">
+        <v>234</v>
+      </c>
+      <c r="O249" s="6">
+        <v>248</v>
+      </c>
+      <c r="P249" s="6">
+        <v>263</v>
+      </c>
+      <c r="Q249" s="6">
+        <v>268</v>
+      </c>
+      <c r="R249" s="6">
+        <v>297</v>
+      </c>
+      <c r="S249" s="6">
+        <v>329</v>
+      </c>
+      <c r="T249" s="6">
+        <v>343</v>
+      </c>
+      <c r="U249" s="6">
+        <v>389</v>
+      </c>
       <c r="V249" s="3"/>
       <c r="W249" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="250" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C250" s="2" t="s">
         <v>327</v>
@@ -17451,136 +17444,136 @@
         <v>27</v>
       </c>
       <c r="E250" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F250" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="F250" s="3" t="s">
+      <c r="G250" s="6">
+        <v>2218</v>
+      </c>
+      <c r="H250" s="6">
+        <v>3117</v>
+      </c>
+      <c r="I250" s="6">
+        <v>4139</v>
+      </c>
+      <c r="J250" s="6">
+        <v>5205</v>
+      </c>
+      <c r="K250" s="6">
+        <v>5793</v>
+      </c>
+      <c r="L250" s="6">
+        <v>7105</v>
+      </c>
+      <c r="M250" s="6">
+        <v>8017</v>
+      </c>
+      <c r="N250" s="6">
+        <v>8195</v>
+      </c>
+      <c r="O250" s="6">
+        <v>8486</v>
+      </c>
+      <c r="P250" s="6">
+        <v>9547</v>
+      </c>
+      <c r="Q250" s="6">
+        <v>12490</v>
+      </c>
+      <c r="R250" s="6">
+        <v>16935</v>
+      </c>
+      <c r="S250" s="6">
+        <v>22670</v>
+      </c>
+      <c r="T250" s="6">
+        <v>28779</v>
+      </c>
+      <c r="U250" s="6">
+        <v>33623</v>
+      </c>
+      <c r="V250" s="6">
+        <v>37777</v>
+      </c>
+      <c r="W250" s="2" t="s">
         <v>329</v>
-      </c>
-      <c r="G250" s="5">
-        <v>137.94999999999999</v>
-      </c>
-      <c r="H250" s="5">
-        <v>0</v>
-      </c>
-      <c r="I250" s="5">
-        <v>0.18</v>
-      </c>
-      <c r="J250" s="5">
-        <v>0</v>
-      </c>
-      <c r="K250" s="5">
-        <v>0</v>
-      </c>
-      <c r="L250" s="5">
-        <v>0</v>
-      </c>
-      <c r="M250" s="5">
-        <v>0</v>
-      </c>
-      <c r="N250" s="5">
-        <v>2.29</v>
-      </c>
-      <c r="O250" s="5">
-        <v>25.44</v>
-      </c>
-      <c r="P250" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q250" s="5">
-        <v>12.02</v>
-      </c>
-      <c r="R250" s="5">
-        <v>0.89</v>
-      </c>
-      <c r="S250" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="T250" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="U250" s="5">
-        <v>80.36</v>
-      </c>
-      <c r="V250" s="3"/>
-      <c r="W250" s="2" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="251" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D251" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E251" s="3" t="s">
-        <v>330</v>
+        <v>28</v>
       </c>
       <c r="F251" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="G251" s="6">
-        <v>5248</v>
-      </c>
-      <c r="H251" s="6">
-        <v>0</v>
-      </c>
-      <c r="I251" s="6">
-        <v>7</v>
-      </c>
-      <c r="J251" s="6">
-        <v>0</v>
-      </c>
-      <c r="K251" s="6">
-        <v>0</v>
-      </c>
-      <c r="L251" s="6">
-        <v>0</v>
-      </c>
-      <c r="M251" s="6">
-        <v>0</v>
-      </c>
-      <c r="N251" s="6">
-        <v>87</v>
-      </c>
-      <c r="O251" s="6">
-        <v>966</v>
-      </c>
-      <c r="P251" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q251" s="6">
-        <v>451</v>
-      </c>
-      <c r="R251" s="6">
-        <v>33</v>
-      </c>
-      <c r="S251" s="6">
-        <v>1</v>
-      </c>
-      <c r="T251" s="6">
-        <v>1</v>
-      </c>
-      <c r="U251" s="6">
-        <v>2938</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="G251" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="H251" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="I251" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="J251" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="K251" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="L251" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="M251" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="N251" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="O251" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="P251" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="Q251" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="R251" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="S251" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="T251" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="U251" s="3"/>
       <c r="V251" s="3"/>
       <c r="W251" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="252" spans="1:23" ht="18" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C252" s="2" t="s">
         <v>332</v>
@@ -17589,137 +17582,139 @@
         <v>27</v>
       </c>
       <c r="E252" s="3" t="s">
-        <v>28</v>
+        <v>333</v>
       </c>
       <c r="F252" s="3" t="s">
-        <v>34</v>
+        <v>334</v>
       </c>
       <c r="G252" s="5">
-        <v>0.55000000000000004</v>
+        <v>137.94999999999999</v>
       </c>
       <c r="H252" s="5">
-        <v>0.55000000000000004</v>
+        <v>0</v>
       </c>
       <c r="I252" s="5">
-        <v>0.55000000000000004</v>
+        <v>0.18</v>
       </c>
       <c r="J252" s="5">
-        <v>0.55000000000000004</v>
+        <v>0</v>
       </c>
       <c r="K252" s="5">
-        <v>0.56000000000000005</v>
+        <v>0</v>
       </c>
       <c r="L252" s="5">
-        <v>0.56000000000000005</v>
+        <v>0</v>
       </c>
       <c r="M252" s="5">
-        <v>0.56999999999999995</v>
+        <v>0</v>
       </c>
       <c r="N252" s="5">
-        <v>0.56999999999999995</v>
+        <v>2.29</v>
       </c>
       <c r="O252" s="5">
-        <v>0.57999999999999996</v>
+        <v>25.44</v>
       </c>
       <c r="P252" s="5">
-        <v>0.57999999999999996</v>
+        <v>0</v>
       </c>
       <c r="Q252" s="5">
-        <v>0.57999999999999996</v>
+        <v>12.02</v>
       </c>
       <c r="R252" s="5">
-        <v>0.57999999999999996</v>
+        <v>0.89</v>
       </c>
       <c r="S252" s="5">
-        <v>0.59</v>
+        <v>0.03</v>
       </c>
       <c r="T252" s="5">
-        <v>0.59</v>
+        <v>0.03</v>
       </c>
       <c r="U252" s="5">
-        <v>0.59</v>
+        <v>80.36</v>
       </c>
       <c r="V252" s="3"/>
       <c r="W252" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="253" spans="1:23" ht="18" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="253" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D253" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E253" s="3" t="s">
-        <v>28</v>
+        <v>335</v>
       </c>
       <c r="F253" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="G253" s="4">
-        <v>732401.6</v>
-      </c>
-      <c r="H253" s="4">
-        <v>740630</v>
-      </c>
-      <c r="I253" s="4">
-        <v>753624</v>
-      </c>
-      <c r="J253" s="4">
-        <v>752240.3</v>
-      </c>
-      <c r="K253" s="4">
-        <v>804401.8</v>
-      </c>
-      <c r="L253" s="4">
-        <v>830309.8</v>
-      </c>
-      <c r="M253" s="4">
-        <v>826034.2</v>
-      </c>
-      <c r="N253" s="3"/>
-      <c r="O253" s="4">
-        <v>846693.5</v>
-      </c>
-      <c r="P253" s="4">
-        <v>839607.4</v>
-      </c>
-      <c r="Q253" s="4">
-        <v>852978.8</v>
-      </c>
-      <c r="R253" s="4">
-        <v>855928.1</v>
-      </c>
-      <c r="S253" s="4">
-        <v>859996.9</v>
-      </c>
-      <c r="T253" s="4">
-        <v>870987.2</v>
-      </c>
-      <c r="U253" s="4">
-        <v>881284.3</v>
+        <v>334</v>
+      </c>
+      <c r="G253" s="6">
+        <v>5248</v>
+      </c>
+      <c r="H253" s="6">
+        <v>0</v>
+      </c>
+      <c r="I253" s="6">
+        <v>7</v>
+      </c>
+      <c r="J253" s="6">
+        <v>0</v>
+      </c>
+      <c r="K253" s="6">
+        <v>0</v>
+      </c>
+      <c r="L253" s="6">
+        <v>0</v>
+      </c>
+      <c r="M253" s="6">
+        <v>0</v>
+      </c>
+      <c r="N253" s="6">
+        <v>87</v>
+      </c>
+      <c r="O253" s="6">
+        <v>966</v>
+      </c>
+      <c r="P253" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q253" s="6">
+        <v>451</v>
+      </c>
+      <c r="R253" s="6">
+        <v>33</v>
+      </c>
+      <c r="S253" s="6">
+        <v>1</v>
+      </c>
+      <c r="T253" s="6">
+        <v>1</v>
+      </c>
+      <c r="U253" s="6">
+        <v>2938</v>
       </c>
       <c r="V253" s="3"/>
       <c r="W253" s="2" t="s">
-        <v>170</v>
+        <v>27</v>
       </c>
     </row>
     <row r="254" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D254" s="2" t="s">
         <v>27</v>
@@ -17728,59 +17723,67 @@
         <v>28</v>
       </c>
       <c r="F254" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="G254" s="3"/>
-      <c r="H254" s="3"/>
-      <c r="I254" s="3"/>
-      <c r="J254" s="3"/>
-      <c r="K254" s="3"/>
+        <v>34</v>
+      </c>
+      <c r="G254" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="H254" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="I254" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J254" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="K254" s="5">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="L254" s="5">
-        <v>6.6</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="M254" s="5">
-        <v>7.58</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="N254" s="5">
-        <v>7.54</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="O254" s="5">
-        <v>10.15</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="P254" s="5">
-        <v>12.38</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="Q254" s="5">
-        <v>12.53</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="R254" s="5">
-        <v>5.95</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="S254" s="5">
-        <v>4.7300000000000004</v>
+        <v>0.59</v>
       </c>
       <c r="T254" s="5">
-        <v>6.25</v>
+        <v>0.59</v>
       </c>
       <c r="U254" s="5">
-        <v>5.6</v>
-      </c>
-      <c r="V254" s="5">
-        <v>5.95</v>
-      </c>
+        <v>0.59</v>
+      </c>
+      <c r="V254" s="3"/>
       <c r="W254" s="2" t="s">
-        <v>170</v>
+        <v>30</v>
       </c>
     </row>
     <row r="255" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B255" s="2" t="s">
         <v>336</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D255" s="2" t="s">
         <v>27</v>
@@ -17789,53 +17792,65 @@
         <v>28</v>
       </c>
       <c r="F255" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G255" s="3"/>
-      <c r="H255" s="3"/>
-      <c r="I255" s="3"/>
-      <c r="J255" s="3"/>
-      <c r="K255" s="3"/>
-      <c r="L255" s="3"/>
-      <c r="M255" s="3"/>
+        <v>169</v>
+      </c>
+      <c r="G255" s="4">
+        <v>732401.6</v>
+      </c>
+      <c r="H255" s="4">
+        <v>740630</v>
+      </c>
+      <c r="I255" s="4">
+        <v>753624</v>
+      </c>
+      <c r="J255" s="4">
+        <v>752240.3</v>
+      </c>
+      <c r="K255" s="4">
+        <v>804401.8</v>
+      </c>
+      <c r="L255" s="4">
+        <v>830309.8</v>
+      </c>
+      <c r="M255" s="4">
+        <v>826034.2</v>
+      </c>
       <c r="N255" s="3"/>
-      <c r="O255" s="6">
-        <v>1</v>
-      </c>
-      <c r="P255" s="6">
-        <v>54</v>
-      </c>
-      <c r="Q255" s="6">
-        <v>63</v>
-      </c>
-      <c r="R255" s="6">
-        <v>66</v>
-      </c>
-      <c r="S255" s="6">
-        <v>70</v>
-      </c>
-      <c r="T255" s="6">
-        <v>75</v>
-      </c>
-      <c r="U255" s="6">
-        <v>80</v>
-      </c>
-      <c r="V255" s="6">
-        <v>86</v>
-      </c>
+      <c r="O255" s="4">
+        <v>846693.5</v>
+      </c>
+      <c r="P255" s="4">
+        <v>839607.4</v>
+      </c>
+      <c r="Q255" s="4">
+        <v>852978.8</v>
+      </c>
+      <c r="R255" s="4">
+        <v>855928.1</v>
+      </c>
+      <c r="S255" s="4">
+        <v>859996.9</v>
+      </c>
+      <c r="T255" s="4">
+        <v>870987.2</v>
+      </c>
+      <c r="U255" s="4">
+        <v>881284.3</v>
+      </c>
+      <c r="V255" s="3"/>
       <c r="W255" s="2" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="256" spans="1:23" ht="99" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="256" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B256" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="C256" s="2" t="s">
         <v>339</v>
-      </c>
-      <c r="C256" s="2" t="s">
-        <v>340</v>
       </c>
       <c r="D256" s="2" t="s">
         <v>27</v>
@@ -17844,42 +17859,56 @@
         <v>28</v>
       </c>
       <c r="F256" s="3" t="s">
-        <v>264</v>
+        <v>340</v>
       </c>
       <c r="G256" s="3"/>
       <c r="H256" s="3"/>
       <c r="I256" s="3"/>
       <c r="J256" s="3"/>
       <c r="K256" s="3"/>
-      <c r="L256" s="3"/>
-      <c r="M256" s="3"/>
-      <c r="N256" s="3"/>
-      <c r="O256" s="3"/>
-      <c r="P256" s="3"/>
-      <c r="Q256" s="3"/>
-      <c r="R256" s="3"/>
-      <c r="S256" s="6">
-        <v>16</v>
-      </c>
-      <c r="T256" s="6">
-        <v>7</v>
-      </c>
-      <c r="U256" s="6">
-        <v>6</v>
-      </c>
-      <c r="V256" s="6">
-        <v>4</v>
+      <c r="L256" s="5">
+        <v>6.6</v>
+      </c>
+      <c r="M256" s="5">
+        <v>7.58</v>
+      </c>
+      <c r="N256" s="5">
+        <v>7.54</v>
+      </c>
+      <c r="O256" s="5">
+        <v>10.15</v>
+      </c>
+      <c r="P256" s="5">
+        <v>12.38</v>
+      </c>
+      <c r="Q256" s="5">
+        <v>12.53</v>
+      </c>
+      <c r="R256" s="5">
+        <v>5.95</v>
+      </c>
+      <c r="S256" s="5">
+        <v>4.7300000000000004</v>
+      </c>
+      <c r="T256" s="5">
+        <v>6.25</v>
+      </c>
+      <c r="U256" s="5">
+        <v>5.6</v>
+      </c>
+      <c r="V256" s="5">
+        <v>5.95</v>
       </c>
       <c r="W256" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="257" spans="1:23" ht="18" x14ac:dyDescent="0.25">
+      <c r="A257" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B257" s="2" t="s">
         <v>341</v>
-      </c>
-    </row>
-    <row r="257" spans="1:23" ht="36" x14ac:dyDescent="0.25">
-      <c r="A257" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="B257" s="2" t="s">
-        <v>339</v>
       </c>
       <c r="C257" s="2" t="s">
         <v>342</v>
@@ -17891,7 +17920,7 @@
         <v>28</v>
       </c>
       <c r="F257" s="3" t="s">
-        <v>343</v>
+        <v>34</v>
       </c>
       <c r="G257" s="3"/>
       <c r="H257" s="3"/>
@@ -17901,451 +17930,415 @@
       <c r="L257" s="3"/>
       <c r="M257" s="3"/>
       <c r="N257" s="3"/>
-      <c r="O257" s="3"/>
-      <c r="P257" s="3"/>
-      <c r="Q257" s="3"/>
+      <c r="O257" s="6">
+        <v>1</v>
+      </c>
+      <c r="P257" s="6">
+        <v>54</v>
+      </c>
+      <c r="Q257" s="6">
+        <v>63</v>
+      </c>
       <c r="R257" s="6">
-        <v>133</v>
+        <v>66</v>
       </c>
       <c r="S257" s="6">
+        <v>70</v>
+      </c>
+      <c r="T257" s="6">
+        <v>75</v>
+      </c>
+      <c r="U257" s="6">
         <v>80</v>
       </c>
-      <c r="T257" s="6">
-        <v>97</v>
-      </c>
-      <c r="U257" s="6">
-        <v>44</v>
-      </c>
       <c r="V257" s="6">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="W257" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="258" spans="1:23" ht="99" x14ac:dyDescent="0.25">
+      <c r="A258" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B258" s="2" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="258" spans="1:23" ht="72" x14ac:dyDescent="0.25">
-      <c r="A258" s="2" t="s">
+      <c r="C258" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="B258" s="2" t="s">
+      <c r="D258" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E258" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F258" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="G258" s="3"/>
+      <c r="H258" s="3"/>
+      <c r="I258" s="3"/>
+      <c r="J258" s="3"/>
+      <c r="K258" s="3"/>
+      <c r="L258" s="3"/>
+      <c r="M258" s="3"/>
+      <c r="N258" s="3"/>
+      <c r="O258" s="3"/>
+      <c r="P258" s="3"/>
+      <c r="Q258" s="3"/>
+      <c r="R258" s="3"/>
+      <c r="S258" s="6">
+        <v>16</v>
+      </c>
+      <c r="T258" s="6">
+        <v>7</v>
+      </c>
+      <c r="U258" s="6">
+        <v>6</v>
+      </c>
+      <c r="V258" s="6">
+        <v>4</v>
+      </c>
+      <c r="W258" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="C258" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="D258" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="E258" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="F258" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G258" s="6">
-        <v>40</v>
-      </c>
-      <c r="H258" s="6">
-        <v>60</v>
-      </c>
-      <c r="I258" s="6">
-        <v>40</v>
-      </c>
-      <c r="J258" s="6">
-        <v>40</v>
-      </c>
-      <c r="K258" s="6">
-        <v>40</v>
-      </c>
-      <c r="L258" s="6">
-        <v>40</v>
-      </c>
-      <c r="M258" s="6">
-        <v>60</v>
-      </c>
-      <c r="N258" s="6">
-        <v>40</v>
-      </c>
-      <c r="O258" s="6">
-        <v>40</v>
-      </c>
-      <c r="P258" s="6">
-        <v>40</v>
-      </c>
-      <c r="Q258" s="6">
-        <v>60</v>
-      </c>
-      <c r="R258" s="6">
-        <v>67</v>
-      </c>
-      <c r="S258" s="6">
-        <v>50</v>
-      </c>
-      <c r="T258" s="6">
-        <v>67</v>
-      </c>
-      <c r="U258" s="6">
-        <v>67</v>
-      </c>
-      <c r="V258" s="3"/>
-      <c r="W258" s="2" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="259" spans="1:23" ht="72" x14ac:dyDescent="0.25">
+    </row>
+    <row r="259" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
-        <v>345</v>
+        <v>314</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C259" s="2" t="s">
         <v>347</v>
       </c>
       <c r="D259" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E259" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F259" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="E259" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="F259" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G259" s="6">
-        <v>40</v>
-      </c>
-      <c r="H259" s="6">
-        <v>60</v>
-      </c>
-      <c r="I259" s="6">
-        <v>20</v>
-      </c>
-      <c r="J259" s="6">
-        <v>20</v>
-      </c>
-      <c r="K259" s="6">
-        <v>20</v>
-      </c>
-      <c r="L259" s="6">
-        <v>40</v>
-      </c>
-      <c r="M259" s="6">
-        <v>60</v>
-      </c>
-      <c r="N259" s="6">
-        <v>40</v>
-      </c>
-      <c r="O259" s="6">
-        <v>25</v>
-      </c>
-      <c r="P259" s="6">
-        <v>25</v>
-      </c>
-      <c r="Q259" s="6">
-        <v>20</v>
-      </c>
+      <c r="G259" s="3"/>
+      <c r="H259" s="3"/>
+      <c r="I259" s="3"/>
+      <c r="J259" s="3"/>
+      <c r="K259" s="3"/>
+      <c r="L259" s="3"/>
+      <c r="M259" s="3"/>
+      <c r="N259" s="3"/>
+      <c r="O259" s="3"/>
+      <c r="P259" s="3"/>
+      <c r="Q259" s="3"/>
       <c r="R259" s="6">
-        <v>17</v>
+        <v>133</v>
       </c>
       <c r="S259" s="6">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="T259" s="6">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="U259" s="6">
-        <v>0</v>
-      </c>
-      <c r="V259" s="3"/>
+        <v>44</v>
+      </c>
+      <c r="V259" s="6">
+        <v>89</v>
+      </c>
       <c r="W259" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="260" spans="1:23" ht="72" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E260" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F260" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G260" s="6">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H260" s="6">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I260" s="6">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="J260" s="6">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K260" s="6">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L260" s="6">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M260" s="6">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N260" s="6">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="O260" s="6">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="P260" s="6">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Q260" s="6">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="R260" s="6">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="S260" s="6">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="T260" s="6">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="U260" s="6">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="V260" s="3"/>
       <c r="W260" s="2" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="261" spans="1:23" ht="72" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E261" s="3" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F261" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G261" s="6">
+        <v>40</v>
+      </c>
+      <c r="H261" s="6">
         <v>60</v>
       </c>
-      <c r="H261" s="6">
+      <c r="I261" s="6">
+        <v>20</v>
+      </c>
+      <c r="J261" s="6">
+        <v>20</v>
+      </c>
+      <c r="K261" s="6">
+        <v>20</v>
+      </c>
+      <c r="L261" s="6">
         <v>40</v>
       </c>
-      <c r="I261" s="6">
+      <c r="M261" s="6">
         <v>60</v>
       </c>
-      <c r="J261" s="6">
-        <v>60</v>
-      </c>
-      <c r="K261" s="6">
-        <v>60</v>
-      </c>
-      <c r="L261" s="6">
-        <v>60</v>
-      </c>
-      <c r="M261" s="6">
+      <c r="N261" s="6">
         <v>40</v>
       </c>
-      <c r="N261" s="6">
-        <v>60</v>
-      </c>
       <c r="O261" s="6">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="P261" s="6">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="Q261" s="6">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="R261" s="6">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="S261" s="6">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="T261" s="6">
         <v>17</v>
       </c>
       <c r="U261" s="6">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="V261" s="3"/>
       <c r="W261" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="262" spans="1:23" ht="72" x14ac:dyDescent="0.25">
+      <c r="A262" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="262" spans="1:23" ht="18" x14ac:dyDescent="0.25">
-      <c r="A262" s="2" t="s">
-        <v>345</v>
-      </c>
       <c r="B262" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>27</v>
+        <v>353</v>
       </c>
       <c r="E262" s="3" t="s">
-        <v>28</v>
+        <v>357</v>
       </c>
       <c r="F262" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="G262" s="4">
-        <v>100</v>
-      </c>
-      <c r="H262" s="4">
-        <v>100.8</v>
-      </c>
-      <c r="I262" s="4">
-        <v>99.9</v>
-      </c>
-      <c r="J262" s="4">
-        <v>101.8</v>
-      </c>
-      <c r="K262" s="4">
-        <v>104.9</v>
-      </c>
-      <c r="L262" s="4">
-        <v>106</v>
-      </c>
-      <c r="M262" s="4">
-        <v>119.9</v>
-      </c>
-      <c r="N262" s="4">
-        <v>119.4</v>
-      </c>
-      <c r="O262" s="4">
-        <v>130</v>
-      </c>
-      <c r="P262" s="4">
-        <v>189.5</v>
-      </c>
-      <c r="Q262" s="4">
-        <v>186.6</v>
-      </c>
-      <c r="R262" s="4">
-        <v>190.1</v>
-      </c>
-      <c r="S262" s="4">
-        <v>200.8</v>
-      </c>
-      <c r="T262" s="4">
-        <v>205.6</v>
-      </c>
-      <c r="U262" s="4">
-        <v>208.5</v>
+        <v>34</v>
+      </c>
+      <c r="G262" s="6">
+        <v>0</v>
+      </c>
+      <c r="H262" s="6">
+        <v>0</v>
+      </c>
+      <c r="I262" s="6">
+        <v>20</v>
+      </c>
+      <c r="J262" s="6">
+        <v>20</v>
+      </c>
+      <c r="K262" s="6">
+        <v>20</v>
+      </c>
+      <c r="L262" s="6">
+        <v>0</v>
+      </c>
+      <c r="M262" s="6">
+        <v>0</v>
+      </c>
+      <c r="N262" s="6">
+        <v>0</v>
+      </c>
+      <c r="O262" s="6">
+        <v>0</v>
+      </c>
+      <c r="P262" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q262" s="6">
+        <v>40</v>
+      </c>
+      <c r="R262" s="6">
+        <v>17</v>
+      </c>
+      <c r="S262" s="6">
+        <v>17</v>
+      </c>
+      <c r="T262" s="6">
+        <v>17</v>
+      </c>
+      <c r="U262" s="6">
+        <v>50</v>
       </c>
       <c r="V262" s="3"/>
       <c r="W262" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="263" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="263" spans="1:23" ht="72" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>27</v>
+        <v>353</v>
       </c>
       <c r="E263" s="3" t="s">
-        <v>28</v>
+        <v>358</v>
       </c>
       <c r="F263" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="G263" s="4">
-        <v>59.5</v>
-      </c>
-      <c r="H263" s="4">
-        <v>57.7</v>
-      </c>
-      <c r="I263" s="4">
-        <v>58.8</v>
-      </c>
-      <c r="J263" s="4">
-        <v>64.3</v>
-      </c>
-      <c r="K263" s="4">
-        <v>68.7</v>
-      </c>
-      <c r="L263" s="4">
-        <v>69.5</v>
-      </c>
-      <c r="M263" s="4">
-        <v>72.900000000000006</v>
-      </c>
-      <c r="N263" s="4">
-        <v>78.099999999999994</v>
-      </c>
-      <c r="O263" s="4">
-        <v>91.8</v>
-      </c>
-      <c r="P263" s="4">
-        <v>93.9</v>
-      </c>
-      <c r="Q263" s="4">
-        <v>88.5</v>
-      </c>
-      <c r="R263" s="4">
-        <v>96.7</v>
-      </c>
-      <c r="S263" s="4">
-        <v>119</v>
-      </c>
-      <c r="T263" s="4">
-        <v>136.4</v>
-      </c>
-      <c r="U263" s="4">
-        <v>124.2</v>
+        <v>34</v>
+      </c>
+      <c r="G263" s="6">
+        <v>60</v>
+      </c>
+      <c r="H263" s="6">
+        <v>40</v>
+      </c>
+      <c r="I263" s="6">
+        <v>60</v>
+      </c>
+      <c r="J263" s="6">
+        <v>60</v>
+      </c>
+      <c r="K263" s="6">
+        <v>60</v>
+      </c>
+      <c r="L263" s="6">
+        <v>60</v>
+      </c>
+      <c r="M263" s="6">
+        <v>40</v>
+      </c>
+      <c r="N263" s="6">
+        <v>60</v>
+      </c>
+      <c r="O263" s="6">
+        <v>75</v>
+      </c>
+      <c r="P263" s="6">
+        <v>75</v>
+      </c>
+      <c r="Q263" s="6">
+        <v>40</v>
+      </c>
+      <c r="R263" s="6">
+        <v>33</v>
+      </c>
+      <c r="S263" s="6">
+        <v>50</v>
+      </c>
+      <c r="T263" s="6">
+        <v>17</v>
+      </c>
+      <c r="U263" s="6">
+        <v>25</v>
       </c>
       <c r="V263" s="3"/>
       <c r="W263" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="264" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="264" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B264" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="B264" s="2" t="s">
+      <c r="C264" s="2" t="s">
         <v>360</v>
-      </c>
-      <c r="C264" s="2" t="s">
-        <v>361</v>
       </c>
       <c r="D264" s="2" t="s">
         <v>27</v>
@@ -18354,67 +18347,67 @@
         <v>28</v>
       </c>
       <c r="F264" s="3" t="s">
-        <v>362</v>
+        <v>320</v>
       </c>
       <c r="G264" s="4">
-        <v>90.8</v>
+        <v>100</v>
       </c>
       <c r="H264" s="4">
-        <v>88.8</v>
+        <v>100.8</v>
       </c>
       <c r="I264" s="4">
-        <v>86.5</v>
+        <v>99.9</v>
       </c>
       <c r="J264" s="4">
-        <v>87</v>
+        <v>101.8</v>
       </c>
       <c r="K264" s="4">
-        <v>85</v>
+        <v>104.9</v>
       </c>
       <c r="L264" s="4">
-        <v>87.4</v>
+        <v>106</v>
       </c>
       <c r="M264" s="4">
-        <v>88.7</v>
+        <v>119.9</v>
       </c>
       <c r="N264" s="4">
-        <v>84.6</v>
+        <v>119.4</v>
       </c>
       <c r="O264" s="4">
-        <v>77.3</v>
+        <v>130</v>
       </c>
       <c r="P264" s="4">
-        <v>79.7</v>
+        <v>189.5</v>
       </c>
       <c r="Q264" s="4">
-        <v>81.900000000000006</v>
+        <v>186.6</v>
       </c>
       <c r="R264" s="4">
-        <v>74.8</v>
+        <v>190.1</v>
       </c>
       <c r="S264" s="4">
-        <v>77</v>
+        <v>200.8</v>
       </c>
       <c r="T264" s="4">
-        <v>77.2</v>
+        <v>205.6</v>
       </c>
       <c r="U264" s="4">
-        <v>76.3</v>
+        <v>208.5</v>
       </c>
       <c r="V264" s="3"/>
       <c r="W264" s="2" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="265" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="265" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D265" s="2" t="s">
         <v>27</v>
@@ -18423,64 +18416,64 @@
         <v>28</v>
       </c>
       <c r="F265" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G265" s="7">
-        <v>0.19600000000000001</v>
-      </c>
-      <c r="H265" s="7">
-        <v>0.20499999999999999</v>
-      </c>
-      <c r="I265" s="7">
-        <v>0.20599999999999999</v>
-      </c>
-      <c r="J265" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="K265" s="7">
-        <v>0.20100000000000001</v>
-      </c>
-      <c r="L265" s="7">
-        <v>0.20300000000000001</v>
-      </c>
-      <c r="M265" s="7">
-        <v>0.20699999999999999</v>
-      </c>
-      <c r="N265" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="O265" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="P265" s="7">
-        <v>0.19900000000000001</v>
-      </c>
-      <c r="Q265" s="7">
-        <v>0.2</v>
-      </c>
-      <c r="R265" s="7">
-        <v>0.19900000000000001</v>
-      </c>
-      <c r="S265" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="T265" s="7">
-        <v>0.192</v>
-      </c>
-      <c r="U265" s="7">
-        <v>0.192</v>
+        <v>363</v>
+      </c>
+      <c r="G265" s="4">
+        <v>59.5</v>
+      </c>
+      <c r="H265" s="4">
+        <v>57.7</v>
+      </c>
+      <c r="I265" s="4">
+        <v>58.8</v>
+      </c>
+      <c r="J265" s="4">
+        <v>64.3</v>
+      </c>
+      <c r="K265" s="4">
+        <v>68.7</v>
+      </c>
+      <c r="L265" s="4">
+        <v>69.5</v>
+      </c>
+      <c r="M265" s="4">
+        <v>72.900000000000006</v>
+      </c>
+      <c r="N265" s="4">
+        <v>78.099999999999994</v>
+      </c>
+      <c r="O265" s="4">
+        <v>91.8</v>
+      </c>
+      <c r="P265" s="4">
+        <v>93.9</v>
+      </c>
+      <c r="Q265" s="4">
+        <v>88.5</v>
+      </c>
+      <c r="R265" s="4">
+        <v>96.7</v>
+      </c>
+      <c r="S265" s="4">
+        <v>119</v>
+      </c>
+      <c r="T265" s="4">
+        <v>136.4</v>
+      </c>
+      <c r="U265" s="4">
+        <v>124.2</v>
       </c>
       <c r="V265" s="3"/>
       <c r="W265" s="2" t="s">
-        <v>365</v>
+        <v>30</v>
       </c>
     </row>
     <row r="266" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="C266" s="2" t="s">
         <v>366</v>
@@ -18492,67 +18485,67 @@
         <v>28</v>
       </c>
       <c r="F266" s="3" t="s">
-        <v>34</v>
+        <v>367</v>
       </c>
       <c r="G266" s="4">
-        <v>30.5</v>
+        <v>90.8</v>
       </c>
       <c r="H266" s="4">
-        <v>30.5</v>
+        <v>88.8</v>
       </c>
       <c r="I266" s="4">
-        <v>30.6</v>
+        <v>86.5</v>
       </c>
       <c r="J266" s="4">
-        <v>30.6</v>
+        <v>87</v>
       </c>
       <c r="K266" s="4">
-        <v>30.7</v>
+        <v>85</v>
       </c>
       <c r="L266" s="4">
-        <v>30.8</v>
+        <v>87.4</v>
       </c>
       <c r="M266" s="4">
-        <v>30.8</v>
+        <v>88.7</v>
       </c>
       <c r="N266" s="4">
-        <v>30.9</v>
+        <v>84.6</v>
       </c>
       <c r="O266" s="4">
-        <v>30.9</v>
+        <v>77.3</v>
       </c>
       <c r="P266" s="4">
-        <v>30.9</v>
+        <v>79.7</v>
       </c>
       <c r="Q266" s="4">
-        <v>30.9</v>
+        <v>81.900000000000006</v>
       </c>
       <c r="R266" s="4">
-        <v>30.9</v>
+        <v>74.8</v>
       </c>
       <c r="S266" s="4">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="T266" s="4">
-        <v>31</v>
+        <v>77.2</v>
       </c>
       <c r="U266" s="4">
-        <v>31</v>
+        <v>76.3</v>
       </c>
       <c r="V266" s="3"/>
       <c r="W266" s="2" t="s">
-        <v>30</v>
+        <v>368</v>
       </c>
     </row>
     <row r="267" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D267" s="2" t="s">
         <v>27</v>
@@ -18561,70 +18554,70 @@
         <v>28</v>
       </c>
       <c r="F267" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="G267" s="6">
-        <v>28</v>
-      </c>
-      <c r="H267" s="6">
-        <v>27</v>
-      </c>
-      <c r="I267" s="6">
-        <v>26</v>
-      </c>
-      <c r="J267" s="6">
-        <v>25</v>
-      </c>
-      <c r="K267" s="6">
-        <v>24</v>
-      </c>
-      <c r="L267" s="6">
-        <v>23</v>
-      </c>
-      <c r="M267" s="6">
-        <v>22</v>
-      </c>
-      <c r="N267" s="6">
-        <v>22</v>
-      </c>
-      <c r="O267" s="6">
-        <v>22</v>
-      </c>
-      <c r="P267" s="6">
-        <v>21</v>
-      </c>
-      <c r="Q267" s="6">
-        <v>19</v>
-      </c>
-      <c r="R267" s="6">
-        <v>17</v>
-      </c>
-      <c r="S267" s="6">
-        <v>16</v>
-      </c>
-      <c r="T267" s="6">
-        <v>16</v>
-      </c>
-      <c r="U267" s="6">
-        <v>15</v>
+        <v>34</v>
+      </c>
+      <c r="G267" s="7">
+        <v>0.19600000000000001</v>
+      </c>
+      <c r="H267" s="7">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="I267" s="7">
+        <v>0.20599999999999999</v>
+      </c>
+      <c r="J267" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="K267" s="7">
+        <v>0.20100000000000001</v>
+      </c>
+      <c r="L267" s="7">
+        <v>0.20300000000000001</v>
+      </c>
+      <c r="M267" s="7">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="N267" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="O267" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="P267" s="7">
+        <v>0.19900000000000001</v>
+      </c>
+      <c r="Q267" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="R267" s="7">
+        <v>0.19900000000000001</v>
+      </c>
+      <c r="S267" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="T267" s="7">
+        <v>0.192</v>
+      </c>
+      <c r="U267" s="7">
+        <v>0.192</v>
       </c>
       <c r="V267" s="3"/>
       <c r="W267" s="2" t="s">
-        <v>107</v>
+        <v>370</v>
       </c>
     </row>
     <row r="268" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E268" s="3" t="s">
         <v>28</v>
@@ -18633,49 +18626,49 @@
         <v>34</v>
       </c>
       <c r="G268" s="4">
-        <v>64.7</v>
+        <v>30.5</v>
       </c>
       <c r="H268" s="4">
-        <v>65.7</v>
+        <v>30.5</v>
       </c>
       <c r="I268" s="4">
-        <v>68.599999999999994</v>
+        <v>30.6</v>
       </c>
       <c r="J268" s="4">
-        <v>70.3</v>
+        <v>30.6</v>
       </c>
       <c r="K268" s="4">
-        <v>71.5</v>
+        <v>30.7</v>
       </c>
       <c r="L268" s="4">
-        <v>72.7</v>
+        <v>30.8</v>
       </c>
       <c r="M268" s="4">
-        <v>73.5</v>
+        <v>30.8</v>
       </c>
       <c r="N268" s="4">
-        <v>73.599999999999994</v>
+        <v>30.9</v>
       </c>
       <c r="O268" s="4">
-        <v>74</v>
+        <v>30.9</v>
       </c>
       <c r="P268" s="4">
-        <v>74.5</v>
+        <v>30.9</v>
       </c>
       <c r="Q268" s="4">
-        <v>74.900000000000006</v>
+        <v>30.9</v>
       </c>
       <c r="R268" s="4">
-        <v>75.2</v>
+        <v>30.9</v>
       </c>
       <c r="S268" s="4">
-        <v>75.7</v>
+        <v>31</v>
       </c>
       <c r="T268" s="4">
-        <v>75.900000000000006</v>
+        <v>31</v>
       </c>
       <c r="U268" s="4">
-        <v>76.2</v>
+        <v>31</v>
       </c>
       <c r="V268" s="3"/>
       <c r="W268" s="2" t="s">
@@ -18684,136 +18677,136 @@
     </row>
     <row r="269" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E269" s="3" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="F269" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G269" s="4">
-        <v>88</v>
-      </c>
-      <c r="H269" s="4">
-        <v>88.4</v>
-      </c>
-      <c r="I269" s="4">
-        <v>91.7</v>
-      </c>
-      <c r="J269" s="4">
-        <v>93.3</v>
-      </c>
-      <c r="K269" s="4">
-        <v>93.9</v>
-      </c>
-      <c r="L269" s="4">
-        <v>94.6</v>
-      </c>
-      <c r="M269" s="4">
-        <v>94.8</v>
-      </c>
-      <c r="N269" s="4">
-        <v>94.5</v>
-      </c>
-      <c r="O269" s="4">
-        <v>94.6</v>
-      </c>
-      <c r="P269" s="4">
-        <v>94.8</v>
-      </c>
-      <c r="Q269" s="4">
-        <v>94.7</v>
-      </c>
-      <c r="R269" s="4">
-        <v>94.6</v>
-      </c>
-      <c r="S269" s="4">
-        <v>95</v>
-      </c>
-      <c r="T269" s="4">
-        <v>94.8</v>
-      </c>
-      <c r="U269" s="4">
-        <v>94.6</v>
+        <v>106</v>
+      </c>
+      <c r="G269" s="6">
+        <v>28</v>
+      </c>
+      <c r="H269" s="6">
+        <v>27</v>
+      </c>
+      <c r="I269" s="6">
+        <v>26</v>
+      </c>
+      <c r="J269" s="6">
+        <v>25</v>
+      </c>
+      <c r="K269" s="6">
+        <v>24</v>
+      </c>
+      <c r="L269" s="6">
+        <v>23</v>
+      </c>
+      <c r="M269" s="6">
+        <v>22</v>
+      </c>
+      <c r="N269" s="6">
+        <v>22</v>
+      </c>
+      <c r="O269" s="6">
+        <v>22</v>
+      </c>
+      <c r="P269" s="6">
+        <v>21</v>
+      </c>
+      <c r="Q269" s="6">
+        <v>19</v>
+      </c>
+      <c r="R269" s="6">
+        <v>17</v>
+      </c>
+      <c r="S269" s="6">
+        <v>16</v>
+      </c>
+      <c r="T269" s="6">
+        <v>16</v>
+      </c>
+      <c r="U269" s="6">
+        <v>15</v>
       </c>
       <c r="V269" s="3"/>
       <c r="W269" s="2" t="s">
-        <v>30</v>
+        <v>107</v>
       </c>
     </row>
     <row r="270" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="D270" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E270" s="3" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="F270" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G270" s="4">
-        <v>28.5</v>
+        <v>64.7</v>
       </c>
       <c r="H270" s="4">
-        <v>30.6</v>
+        <v>65.7</v>
       </c>
       <c r="I270" s="4">
-        <v>33.1</v>
+        <v>68.599999999999994</v>
       </c>
       <c r="J270" s="4">
-        <v>35.299999999999997</v>
+        <v>70.3</v>
       </c>
       <c r="K270" s="4">
-        <v>37.4</v>
+        <v>71.5</v>
       </c>
       <c r="L270" s="4">
-        <v>39.6</v>
+        <v>72.7</v>
       </c>
       <c r="M270" s="4">
-        <v>41.2</v>
+        <v>73.5</v>
       </c>
       <c r="N270" s="4">
-        <v>42</v>
+        <v>73.599999999999994</v>
       </c>
       <c r="O270" s="4">
-        <v>42.9</v>
+        <v>74</v>
       </c>
       <c r="P270" s="4">
-        <v>44</v>
+        <v>74.5</v>
       </c>
       <c r="Q270" s="4">
-        <v>45.4</v>
+        <v>74.900000000000006</v>
       </c>
       <c r="R270" s="4">
-        <v>46.5</v>
+        <v>75.2</v>
       </c>
       <c r="S270" s="4">
-        <v>47.2</v>
+        <v>75.7</v>
       </c>
       <c r="T270" s="4">
-        <v>48.2</v>
+        <v>75.900000000000006</v>
       </c>
       <c r="U270" s="4">
-        <v>49.3</v>
+        <v>76.2</v>
       </c>
       <c r="V270" s="3"/>
       <c r="W270" s="2" t="s">
@@ -18822,151 +18815,151 @@
     </row>
     <row r="271" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E271" s="3" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F271" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G271" s="4">
-        <v>65.7</v>
+        <v>88</v>
       </c>
       <c r="H271" s="4">
-        <v>64.8</v>
+        <v>88.4</v>
       </c>
       <c r="I271" s="4">
-        <v>67.400000000000006</v>
+        <v>91.7</v>
       </c>
       <c r="J271" s="4">
-        <v>69.8</v>
+        <v>93.3</v>
       </c>
       <c r="K271" s="4">
-        <v>70.5</v>
+        <v>93.9</v>
       </c>
       <c r="L271" s="4">
-        <v>70.900000000000006</v>
+        <v>94.6</v>
       </c>
       <c r="M271" s="4">
-        <v>71.400000000000006</v>
+        <v>94.8</v>
       </c>
       <c r="N271" s="4">
-        <v>72.5</v>
+        <v>94.5</v>
       </c>
       <c r="O271" s="4">
-        <v>73.2</v>
+        <v>94.6</v>
       </c>
       <c r="P271" s="4">
-        <v>73.900000000000006</v>
+        <v>94.8</v>
       </c>
       <c r="Q271" s="4">
-        <v>73.3</v>
+        <v>94.7</v>
       </c>
       <c r="R271" s="4">
-        <v>72.8</v>
+        <v>94.6</v>
       </c>
       <c r="S271" s="4">
-        <v>76.3</v>
+        <v>95</v>
       </c>
       <c r="T271" s="4">
-        <v>78.099999999999994</v>
+        <v>94.8</v>
       </c>
       <c r="U271" s="4">
-        <v>78.599999999999994</v>
+        <v>94.6</v>
       </c>
       <c r="V271" s="3"/>
       <c r="W271" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="272" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E272" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="F272" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="G272" s="6">
-        <v>70108</v>
-      </c>
-      <c r="H272" s="6">
-        <v>248240</v>
-      </c>
-      <c r="I272" s="6">
-        <v>168221</v>
-      </c>
-      <c r="J272" s="6">
-        <v>72837</v>
-      </c>
-      <c r="K272" s="6">
-        <v>64283</v>
-      </c>
-      <c r="L272" s="6">
-        <v>68694</v>
-      </c>
-      <c r="M272" s="6">
-        <v>60135</v>
-      </c>
-      <c r="N272" s="6">
-        <v>46337</v>
-      </c>
-      <c r="O272" s="6">
-        <v>50289</v>
-      </c>
-      <c r="P272" s="6">
-        <v>104107</v>
-      </c>
-      <c r="Q272" s="6">
-        <v>201963</v>
-      </c>
-      <c r="R272" s="6">
-        <v>84506</v>
-      </c>
-      <c r="S272" s="6">
-        <v>295948</v>
-      </c>
-      <c r="T272" s="6">
-        <v>123796</v>
-      </c>
-      <c r="U272" s="6">
-        <v>104040</v>
+        <v>34</v>
+      </c>
+      <c r="G272" s="4">
+        <v>28.5</v>
+      </c>
+      <c r="H272" s="4">
+        <v>30.6</v>
+      </c>
+      <c r="I272" s="4">
+        <v>33.1</v>
+      </c>
+      <c r="J272" s="4">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="K272" s="4">
+        <v>37.4</v>
+      </c>
+      <c r="L272" s="4">
+        <v>39.6</v>
+      </c>
+      <c r="M272" s="4">
+        <v>41.2</v>
+      </c>
+      <c r="N272" s="4">
+        <v>42</v>
+      </c>
+      <c r="O272" s="4">
+        <v>42.9</v>
+      </c>
+      <c r="P272" s="4">
+        <v>44</v>
+      </c>
+      <c r="Q272" s="4">
+        <v>45.4</v>
+      </c>
+      <c r="R272" s="4">
+        <v>46.5</v>
+      </c>
+      <c r="S272" s="4">
+        <v>47.2</v>
+      </c>
+      <c r="T272" s="4">
+        <v>48.2</v>
+      </c>
+      <c r="U272" s="4">
+        <v>49.3</v>
       </c>
       <c r="V272" s="3"/>
       <c r="W272" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="273" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D273" s="2" t="s">
         <v>27</v>
@@ -18978,49 +18971,49 @@
         <v>34</v>
       </c>
       <c r="G273" s="4">
-        <v>2.9</v>
+        <v>65.7</v>
       </c>
       <c r="H273" s="4">
-        <v>3.8</v>
+        <v>64.8</v>
       </c>
       <c r="I273" s="4">
-        <v>6</v>
+        <v>67.400000000000006</v>
       </c>
       <c r="J273" s="4">
-        <v>4.3</v>
+        <v>69.8</v>
       </c>
       <c r="K273" s="4">
-        <v>4.5999999999999996</v>
+        <v>70.5</v>
       </c>
       <c r="L273" s="4">
-        <v>4.2</v>
+        <v>70.900000000000006</v>
       </c>
       <c r="M273" s="4">
-        <v>3.1</v>
+        <v>71.400000000000006</v>
       </c>
       <c r="N273" s="4">
-        <v>3</v>
+        <v>72.5</v>
       </c>
       <c r="O273" s="4">
-        <v>3.2</v>
+        <v>73.2</v>
       </c>
       <c r="P273" s="4">
-        <v>3.4</v>
+        <v>73.900000000000006</v>
       </c>
       <c r="Q273" s="4">
-        <v>3.2</v>
+        <v>73.3</v>
       </c>
       <c r="R273" s="4">
-        <v>4.5</v>
+        <v>72.8</v>
       </c>
       <c r="S273" s="4">
-        <v>6.6</v>
+        <v>76.3</v>
       </c>
       <c r="T273" s="4">
-        <v>5.8</v>
+        <v>78.099999999999994</v>
       </c>
       <c r="U273" s="4">
-        <v>4.5</v>
+        <v>78.599999999999994</v>
       </c>
       <c r="V273" s="3"/>
       <c r="W273" s="2" t="s">
@@ -19029,7 +19022,7 @@
     </row>
     <row r="274" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="B274" s="2" t="s">
         <v>376</v>
@@ -19044,63 +19037,61 @@
         <v>28</v>
       </c>
       <c r="F274" s="3" t="s">
-        <v>34</v>
+        <v>378</v>
       </c>
       <c r="G274" s="6">
-        <v>70</v>
+        <v>70108</v>
       </c>
       <c r="H274" s="6">
-        <v>75</v>
+        <v>248240</v>
       </c>
       <c r="I274" s="6">
-        <v>66</v>
+        <v>168221</v>
       </c>
       <c r="J274" s="6">
-        <v>64</v>
+        <v>72837</v>
       </c>
       <c r="K274" s="6">
-        <v>70</v>
+        <v>64283</v>
       </c>
       <c r="L274" s="6">
-        <v>66</v>
+        <v>68694</v>
       </c>
       <c r="M274" s="6">
-        <v>80</v>
+        <v>60135</v>
       </c>
       <c r="N274" s="6">
-        <v>89</v>
+        <v>46337</v>
       </c>
       <c r="O274" s="6">
-        <v>86</v>
+        <v>50289</v>
       </c>
       <c r="P274" s="6">
-        <v>89</v>
+        <v>104107</v>
       </c>
       <c r="Q274" s="6">
-        <v>85</v>
+        <v>201963</v>
       </c>
       <c r="R274" s="6">
-        <v>82</v>
+        <v>84506</v>
       </c>
       <c r="S274" s="6">
-        <v>83</v>
+        <v>295948</v>
       </c>
       <c r="T274" s="6">
-        <v>88</v>
+        <v>123796</v>
       </c>
       <c r="U274" s="6">
-        <v>88</v>
-      </c>
-      <c r="V274" s="6">
-        <v>86</v>
-      </c>
+        <v>104040</v>
+      </c>
+      <c r="V274" s="3"/>
       <c r="W274" s="2" t="s">
-        <v>378</v>
+        <v>30</v>
       </c>
     </row>
     <row r="275" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="B275" s="2" t="s">
         <v>376</v>
@@ -19117,51 +19108,65 @@
       <c r="F275" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G275" s="6">
-        <v>55</v>
-      </c>
-      <c r="H275" s="3"/>
-      <c r="I275" s="6">
-        <v>58</v>
-      </c>
-      <c r="J275" s="3"/>
-      <c r="K275" s="6">
-        <v>60</v>
-      </c>
-      <c r="L275" s="3"/>
-      <c r="M275" s="6">
-        <v>64</v>
-      </c>
-      <c r="N275" s="3"/>
-      <c r="O275" s="6">
-        <v>65</v>
-      </c>
-      <c r="P275" s="3"/>
-      <c r="Q275" s="6">
-        <v>74</v>
-      </c>
-      <c r="R275" s="3"/>
-      <c r="S275" s="6">
-        <v>63</v>
-      </c>
-      <c r="T275" s="3"/>
-      <c r="U275" s="6">
-        <v>71</v>
+      <c r="G275" s="4">
+        <v>2.9</v>
+      </c>
+      <c r="H275" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="I275" s="4">
+        <v>6</v>
+      </c>
+      <c r="J275" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="K275" s="4">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="L275" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="M275" s="4">
+        <v>3.1</v>
+      </c>
+      <c r="N275" s="4">
+        <v>3</v>
+      </c>
+      <c r="O275" s="4">
+        <v>3.2</v>
+      </c>
+      <c r="P275" s="4">
+        <v>3.4</v>
+      </c>
+      <c r="Q275" s="4">
+        <v>3.2</v>
+      </c>
+      <c r="R275" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="S275" s="4">
+        <v>6.6</v>
+      </c>
+      <c r="T275" s="4">
+        <v>5.8</v>
+      </c>
+      <c r="U275" s="4">
+        <v>4.5</v>
       </c>
       <c r="V275" s="3"/>
       <c r="W275" s="2" t="s">
-        <v>378</v>
+        <v>30</v>
       </c>
     </row>
     <row r="276" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="D276" s="2" t="s">
         <v>27</v>
@@ -19170,41 +19175,69 @@
         <v>28</v>
       </c>
       <c r="F276" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G276" s="3"/>
-      <c r="H276" s="3"/>
-      <c r="I276" s="3"/>
-      <c r="J276" s="3"/>
-      <c r="K276" s="3"/>
-      <c r="L276" s="3"/>
-      <c r="M276" s="3"/>
-      <c r="N276" s="3"/>
-      <c r="O276" s="3"/>
-      <c r="P276" s="3"/>
-      <c r="Q276" s="3"/>
-      <c r="R276" s="3"/>
-      <c r="S276" s="5">
-        <v>33109.31</v>
-      </c>
-      <c r="T276" s="5">
-        <v>33829.39</v>
-      </c>
-      <c r="U276" s="3"/>
-      <c r="V276" s="3"/>
+        <v>34</v>
+      </c>
+      <c r="G276" s="6">
+        <v>70</v>
+      </c>
+      <c r="H276" s="6">
+        <v>75</v>
+      </c>
+      <c r="I276" s="6">
+        <v>66</v>
+      </c>
+      <c r="J276" s="6">
+        <v>64</v>
+      </c>
+      <c r="K276" s="6">
+        <v>70</v>
+      </c>
+      <c r="L276" s="6">
+        <v>66</v>
+      </c>
+      <c r="M276" s="6">
+        <v>80</v>
+      </c>
+      <c r="N276" s="6">
+        <v>89</v>
+      </c>
+      <c r="O276" s="6">
+        <v>86</v>
+      </c>
+      <c r="P276" s="6">
+        <v>89</v>
+      </c>
+      <c r="Q276" s="6">
+        <v>85</v>
+      </c>
+      <c r="R276" s="6">
+        <v>82</v>
+      </c>
+      <c r="S276" s="6">
+        <v>83</v>
+      </c>
+      <c r="T276" s="6">
+        <v>88</v>
+      </c>
+      <c r="U276" s="6">
+        <v>88</v>
+      </c>
+      <c r="V276" s="6">
+        <v>86</v>
+      </c>
       <c r="W276" s="2" t="s">
-        <v>87</v>
+        <v>383</v>
       </c>
     </row>
     <row r="277" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B277" s="2" t="s">
         <v>381</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D277" s="2" t="s">
         <v>27</v>
@@ -19213,67 +19246,53 @@
         <v>28</v>
       </c>
       <c r="F277" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="G277" s="5">
-        <v>1.02</v>
-      </c>
-      <c r="H277" s="5">
-        <v>0.96</v>
-      </c>
-      <c r="I277" s="5">
-        <v>1</v>
-      </c>
-      <c r="J277" s="5">
-        <v>1.05</v>
-      </c>
-      <c r="K277" s="5">
-        <v>1.06</v>
-      </c>
-      <c r="L277" s="5">
-        <v>0.95</v>
-      </c>
-      <c r="M277" s="5">
-        <v>0.91</v>
-      </c>
-      <c r="N277" s="5">
-        <v>0.81</v>
-      </c>
-      <c r="O277" s="5">
-        <v>0.87</v>
-      </c>
-      <c r="P277" s="5">
-        <v>1.01</v>
-      </c>
-      <c r="Q277" s="5">
-        <v>0.85</v>
-      </c>
-      <c r="R277" s="5">
-        <v>0.83</v>
-      </c>
-      <c r="S277" s="5">
-        <v>0.72</v>
-      </c>
-      <c r="T277" s="5">
-        <v>0.78</v>
-      </c>
-      <c r="U277" s="5">
-        <v>0.69</v>
+        <v>34</v>
+      </c>
+      <c r="G277" s="6">
+        <v>55</v>
+      </c>
+      <c r="H277" s="3"/>
+      <c r="I277" s="6">
+        <v>58</v>
+      </c>
+      <c r="J277" s="3"/>
+      <c r="K277" s="6">
+        <v>60</v>
+      </c>
+      <c r="L277" s="3"/>
+      <c r="M277" s="6">
+        <v>64</v>
+      </c>
+      <c r="N277" s="3"/>
+      <c r="O277" s="6">
+        <v>65</v>
+      </c>
+      <c r="P277" s="3"/>
+      <c r="Q277" s="6">
+        <v>74</v>
+      </c>
+      <c r="R277" s="3"/>
+      <c r="S277" s="6">
+        <v>63</v>
+      </c>
+      <c r="T277" s="3"/>
+      <c r="U277" s="6">
+        <v>71</v>
       </c>
       <c r="V277" s="3"/>
       <c r="W277" s="2" t="s">
-        <v>206</v>
+        <v>383</v>
       </c>
     </row>
     <row r="278" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D278" s="2" t="s">
         <v>27</v>
@@ -19282,61 +19301,35 @@
         <v>28</v>
       </c>
       <c r="F278" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G278" s="5">
-        <v>1.84</v>
-      </c>
-      <c r="H278" s="5">
-        <v>1.79</v>
-      </c>
-      <c r="I278" s="5">
-        <v>1.8</v>
-      </c>
-      <c r="J278" s="5">
-        <v>1.79</v>
-      </c>
-      <c r="K278" s="5">
-        <v>1.86</v>
-      </c>
-      <c r="L278" s="5">
-        <v>2.21</v>
-      </c>
-      <c r="M278" s="5">
-        <v>1.99</v>
-      </c>
-      <c r="N278" s="5">
-        <v>1.88</v>
-      </c>
-      <c r="O278" s="5">
-        <v>2</v>
-      </c>
-      <c r="P278" s="5">
-        <v>1.96</v>
-      </c>
-      <c r="Q278" s="5">
-        <v>2.21</v>
-      </c>
-      <c r="R278" s="5">
-        <v>2.19</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="G278" s="3"/>
+      <c r="H278" s="3"/>
+      <c r="I278" s="3"/>
+      <c r="J278" s="3"/>
+      <c r="K278" s="3"/>
+      <c r="L278" s="3"/>
+      <c r="M278" s="3"/>
+      <c r="N278" s="3"/>
+      <c r="O278" s="3"/>
+      <c r="P278" s="3"/>
+      <c r="Q278" s="3"/>
+      <c r="R278" s="3"/>
       <c r="S278" s="5">
-        <v>2.21</v>
+        <v>33109.31</v>
       </c>
       <c r="T278" s="5">
-        <v>3.27</v>
-      </c>
-      <c r="U278" s="5">
-        <v>4.07</v>
-      </c>
+        <v>33829.39</v>
+      </c>
+      <c r="U278" s="3"/>
       <c r="V278" s="3"/>
       <c r="W278" s="2" t="s">
-        <v>385</v>
+        <v>87</v>
       </c>
     </row>
     <row r="279" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B279" s="2" t="s">
         <v>386</v>
@@ -19351,44 +19344,70 @@
         <v>28</v>
       </c>
       <c r="F279" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G279" s="3"/>
-      <c r="H279" s="3"/>
-      <c r="I279" s="3"/>
-      <c r="J279" s="3"/>
-      <c r="K279" s="3"/>
-      <c r="L279" s="3"/>
-      <c r="M279" s="3"/>
-      <c r="N279" s="3"/>
-      <c r="O279" s="3"/>
-      <c r="P279" s="3"/>
-      <c r="Q279" s="3"/>
-      <c r="R279" s="3"/>
-      <c r="S279" s="3"/>
-      <c r="T279" s="3"/>
-      <c r="U279" s="4">
-        <v>30.2</v>
-      </c>
-      <c r="V279" s="4">
-        <v>51.3</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="G279" s="5">
+        <v>1.02</v>
+      </c>
+      <c r="H279" s="5">
+        <v>0.96</v>
+      </c>
+      <c r="I279" s="5">
+        <v>1</v>
+      </c>
+      <c r="J279" s="5">
+        <v>1.05</v>
+      </c>
+      <c r="K279" s="5">
+        <v>1.06</v>
+      </c>
+      <c r="L279" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="M279" s="5">
+        <v>0.91</v>
+      </c>
+      <c r="N279" s="5">
+        <v>0.81</v>
+      </c>
+      <c r="O279" s="5">
+        <v>0.87</v>
+      </c>
+      <c r="P279" s="5">
+        <v>1.01</v>
+      </c>
+      <c r="Q279" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="R279" s="5">
+        <v>0.83</v>
+      </c>
+      <c r="S279" s="5">
+        <v>0.72</v>
+      </c>
+      <c r="T279" s="5">
+        <v>0.78</v>
+      </c>
+      <c r="U279" s="5">
+        <v>0.69</v>
+      </c>
+      <c r="V279" s="3"/>
       <c r="W279" s="2" t="s">
-        <v>30</v>
+        <v>206</v>
       </c>
     </row>
     <row r="280" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="E280" s="3" t="s">
         <v>28</v>
@@ -19396,124 +19415,94 @@
       <c r="F280" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G280" s="4">
-        <v>28.1</v>
-      </c>
-      <c r="H280" s="4">
-        <v>27.6</v>
-      </c>
-      <c r="I280" s="4">
-        <v>31.6</v>
-      </c>
-      <c r="J280" s="4">
-        <v>22.6</v>
-      </c>
-      <c r="K280" s="4">
-        <v>26.9</v>
-      </c>
-      <c r="L280" s="4">
-        <v>26.6</v>
-      </c>
-      <c r="M280" s="4">
-        <v>30.2</v>
-      </c>
-      <c r="N280" s="4">
-        <v>30.8</v>
-      </c>
-      <c r="O280" s="4">
-        <v>35.5</v>
-      </c>
-      <c r="P280" s="4">
-        <v>40.4</v>
-      </c>
-      <c r="Q280" s="4">
-        <v>41.9</v>
-      </c>
-      <c r="R280" s="4">
-        <v>47.5</v>
-      </c>
-      <c r="S280" s="4">
-        <v>55.4</v>
-      </c>
-      <c r="T280" s="4">
-        <v>58.5</v>
-      </c>
-      <c r="U280" s="4">
-        <v>61</v>
-      </c>
-      <c r="V280" s="4">
-        <v>61.1</v>
-      </c>
+      <c r="G280" s="5">
+        <v>1.84</v>
+      </c>
+      <c r="H280" s="5">
+        <v>1.79</v>
+      </c>
+      <c r="I280" s="5">
+        <v>1.8</v>
+      </c>
+      <c r="J280" s="5">
+        <v>1.79</v>
+      </c>
+      <c r="K280" s="5">
+        <v>1.86</v>
+      </c>
+      <c r="L280" s="5">
+        <v>2.21</v>
+      </c>
+      <c r="M280" s="5">
+        <v>1.99</v>
+      </c>
+      <c r="N280" s="5">
+        <v>1.88</v>
+      </c>
+      <c r="O280" s="5">
+        <v>2</v>
+      </c>
+      <c r="P280" s="5">
+        <v>1.96</v>
+      </c>
+      <c r="Q280" s="5">
+        <v>2.21</v>
+      </c>
+      <c r="R280" s="5">
+        <v>2.19</v>
+      </c>
+      <c r="S280" s="5">
+        <v>2.21</v>
+      </c>
+      <c r="T280" s="5">
+        <v>3.27</v>
+      </c>
+      <c r="U280" s="5">
+        <v>4.07</v>
+      </c>
+      <c r="V280" s="3"/>
       <c r="W280" s="2" t="s">
-        <v>30</v>
+        <v>390</v>
       </c>
     </row>
     <row r="281" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="E281" s="3" t="s">
-        <v>389</v>
+        <v>28</v>
       </c>
       <c r="F281" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G281" s="4">
-        <v>31.5</v>
-      </c>
-      <c r="H281" s="4">
-        <v>27.9</v>
-      </c>
-      <c r="I281" s="4">
-        <v>36.799999999999997</v>
-      </c>
-      <c r="J281" s="4">
-        <v>20.2</v>
-      </c>
-      <c r="K281" s="4">
-        <v>23.9</v>
-      </c>
-      <c r="L281" s="4">
-        <v>20.8</v>
-      </c>
-      <c r="M281" s="4">
-        <v>20.5</v>
-      </c>
-      <c r="N281" s="4">
-        <v>22.4</v>
-      </c>
-      <c r="O281" s="4">
-        <v>29.5</v>
-      </c>
-      <c r="P281" s="4">
-        <v>29.8</v>
-      </c>
-      <c r="Q281" s="4">
-        <v>30.9</v>
-      </c>
-      <c r="R281" s="4">
-        <v>35.6</v>
-      </c>
-      <c r="S281" s="4">
-        <v>42.1</v>
-      </c>
-      <c r="T281" s="4">
-        <v>44</v>
-      </c>
+      <c r="G281" s="3"/>
+      <c r="H281" s="3"/>
+      <c r="I281" s="3"/>
+      <c r="J281" s="3"/>
+      <c r="K281" s="3"/>
+      <c r="L281" s="3"/>
+      <c r="M281" s="3"/>
+      <c r="N281" s="3"/>
+      <c r="O281" s="3"/>
+      <c r="P281" s="3"/>
+      <c r="Q281" s="3"/>
+      <c r="R281" s="3"/>
+      <c r="S281" s="3"/>
+      <c r="T281" s="3"/>
       <c r="U281" s="4">
-        <v>47.7</v>
+        <v>30.2</v>
       </c>
       <c r="V281" s="4">
-        <v>48.9</v>
+        <v>51.3</v>
       </c>
       <c r="W281" s="2" t="s">
         <v>30</v>
@@ -19521,70 +19510,70 @@
     </row>
     <row r="282" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="D282" s="2" t="s">
         <v>90</v>
       </c>
       <c r="E282" s="3" t="s">
-        <v>390</v>
+        <v>28</v>
       </c>
       <c r="F282" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G282" s="4">
-        <v>47.6</v>
+        <v>28.1</v>
       </c>
       <c r="H282" s="4">
-        <v>46.2</v>
+        <v>27.6</v>
       </c>
       <c r="I282" s="4">
-        <v>50.6</v>
+        <v>31.6</v>
       </c>
       <c r="J282" s="4">
-        <v>39</v>
+        <v>22.6</v>
       </c>
       <c r="K282" s="4">
-        <v>46</v>
+        <v>26.9</v>
       </c>
       <c r="L282" s="4">
-        <v>45</v>
+        <v>26.6</v>
       </c>
       <c r="M282" s="4">
-        <v>48.1</v>
+        <v>30.2</v>
       </c>
       <c r="N282" s="4">
-        <v>48.1</v>
+        <v>30.8</v>
       </c>
       <c r="O282" s="4">
-        <v>53</v>
+        <v>35.5</v>
       </c>
       <c r="P282" s="4">
-        <v>58.6</v>
+        <v>40.4</v>
       </c>
       <c r="Q282" s="4">
-        <v>59.9</v>
+        <v>41.9</v>
       </c>
       <c r="R282" s="4">
-        <v>68.3</v>
+        <v>47.5</v>
       </c>
       <c r="S282" s="4">
-        <v>75.2</v>
+        <v>55.4</v>
       </c>
       <c r="T282" s="4">
-        <v>81</v>
+        <v>58.5</v>
       </c>
       <c r="U282" s="4">
-        <v>81.2</v>
+        <v>61</v>
       </c>
       <c r="V282" s="4">
-        <v>81.8</v>
+        <v>61.1</v>
       </c>
       <c r="W282" s="2" t="s">
         <v>30</v>
@@ -19592,70 +19581,70 @@
     </row>
     <row r="283" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="D283" s="2" t="s">
         <v>90</v>
       </c>
       <c r="E283" s="3" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="F283" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G283" s="4">
-        <v>37.6</v>
+        <v>31.5</v>
       </c>
       <c r="H283" s="4">
-        <v>36.9</v>
+        <v>27.9</v>
       </c>
       <c r="I283" s="4">
-        <v>45.3</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="J283" s="4">
-        <v>35.200000000000003</v>
+        <v>20.2</v>
       </c>
       <c r="K283" s="4">
-        <v>40.1</v>
+        <v>23.9</v>
       </c>
       <c r="L283" s="4">
-        <v>38.6</v>
+        <v>20.8</v>
       </c>
       <c r="M283" s="4">
-        <v>40.5</v>
+        <v>20.5</v>
       </c>
       <c r="N283" s="4">
-        <v>45</v>
+        <v>22.4</v>
       </c>
       <c r="O283" s="4">
-        <v>49.6</v>
+        <v>29.5</v>
       </c>
       <c r="P283" s="4">
-        <v>57.6</v>
+        <v>29.8</v>
       </c>
       <c r="Q283" s="4">
-        <v>59.4</v>
+        <v>30.9</v>
       </c>
       <c r="R283" s="4">
-        <v>65.900000000000006</v>
+        <v>35.6</v>
       </c>
       <c r="S283" s="4">
-        <v>75.599999999999994</v>
+        <v>42.1</v>
       </c>
       <c r="T283" s="4">
-        <v>78.3</v>
+        <v>44</v>
       </c>
       <c r="U283" s="4">
-        <v>81.099999999999994</v>
+        <v>47.7</v>
       </c>
       <c r="V283" s="4">
-        <v>78.3</v>
+        <v>48.9</v>
       </c>
       <c r="W283" s="2" t="s">
         <v>30</v>
@@ -19663,70 +19652,70 @@
     </row>
     <row r="284" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="D284" s="2" t="s">
         <v>90</v>
       </c>
       <c r="E284" s="3" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="F284" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G284" s="4">
-        <v>26.2</v>
+        <v>47.6</v>
       </c>
       <c r="H284" s="4">
-        <v>26.3</v>
+        <v>46.2</v>
       </c>
       <c r="I284" s="4">
-        <v>28.7</v>
+        <v>50.6</v>
       </c>
       <c r="J284" s="4">
-        <v>21.5</v>
+        <v>39</v>
       </c>
       <c r="K284" s="4">
-        <v>26.2</v>
+        <v>46</v>
       </c>
       <c r="L284" s="4">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="M284" s="4">
-        <v>30</v>
+        <v>48.1</v>
       </c>
       <c r="N284" s="4">
-        <v>28</v>
+        <v>48.1</v>
       </c>
       <c r="O284" s="4">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="P284" s="4">
-        <v>41.4</v>
+        <v>58.6</v>
       </c>
       <c r="Q284" s="4">
-        <v>45.1</v>
+        <v>59.9</v>
       </c>
       <c r="R284" s="4">
-        <v>51.7</v>
+        <v>68.3</v>
       </c>
       <c r="S284" s="4">
-        <v>62.4</v>
+        <v>75.2</v>
       </c>
       <c r="T284" s="4">
-        <v>65.7</v>
+        <v>81</v>
       </c>
       <c r="U284" s="4">
-        <v>68.8</v>
+        <v>81.2</v>
       </c>
       <c r="V284" s="4">
-        <v>69.900000000000006</v>
+        <v>81.8</v>
       </c>
       <c r="W284" s="2" t="s">
         <v>30</v>
@@ -19734,70 +19723,70 @@
     </row>
     <row r="285" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="D285" s="2" t="s">
         <v>90</v>
       </c>
       <c r="E285" s="3" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F285" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G285" s="4">
-        <v>13.5</v>
+        <v>37.6</v>
       </c>
       <c r="H285" s="4">
-        <v>15.7</v>
+        <v>36.9</v>
       </c>
       <c r="I285" s="4">
-        <v>17.2</v>
+        <v>45.3</v>
       </c>
       <c r="J285" s="4">
-        <v>12.7</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="K285" s="4">
-        <v>15.5</v>
+        <v>40.1</v>
       </c>
       <c r="L285" s="4">
-        <v>18.3</v>
+        <v>38.6</v>
       </c>
       <c r="M285" s="4">
-        <v>19.8</v>
+        <v>40.5</v>
       </c>
       <c r="N285" s="4">
-        <v>18.8</v>
+        <v>45</v>
       </c>
       <c r="O285" s="4">
-        <v>22.4</v>
+        <v>49.6</v>
       </c>
       <c r="P285" s="4">
-        <v>28.5</v>
+        <v>57.6</v>
       </c>
       <c r="Q285" s="4">
-        <v>29.4</v>
+        <v>59.4</v>
       </c>
       <c r="R285" s="4">
-        <v>35</v>
+        <v>65.900000000000006</v>
       </c>
       <c r="S285" s="4">
-        <v>39.5</v>
+        <v>75.599999999999994</v>
       </c>
       <c r="T285" s="4">
-        <v>44.4</v>
+        <v>78.3</v>
       </c>
       <c r="U285" s="4">
-        <v>50.8</v>
+        <v>81.099999999999994</v>
       </c>
       <c r="V285" s="4">
-        <v>51.4</v>
+        <v>78.3</v>
       </c>
       <c r="W285" s="2" t="s">
         <v>30</v>
@@ -19805,70 +19794,70 @@
     </row>
     <row r="286" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="D286" s="2" t="s">
         <v>90</v>
       </c>
       <c r="E286" s="3" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="F286" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G286" s="4">
-        <v>4.0999999999999996</v>
+        <v>26.2</v>
       </c>
       <c r="H286" s="4">
-        <v>5</v>
+        <v>26.3</v>
       </c>
       <c r="I286" s="4">
-        <v>6.8</v>
+        <v>28.7</v>
       </c>
       <c r="J286" s="4">
-        <v>3.7</v>
+        <v>21.5</v>
       </c>
       <c r="K286" s="4">
-        <v>6.6</v>
+        <v>26.2</v>
       </c>
       <c r="L286" s="4">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="M286" s="4">
-        <v>8.6999999999999993</v>
+        <v>30</v>
       </c>
       <c r="N286" s="4">
-        <v>8.4</v>
+        <v>28</v>
       </c>
       <c r="O286" s="4">
-        <v>10.9</v>
+        <v>35</v>
       </c>
       <c r="P286" s="4">
-        <v>12.2</v>
+        <v>41.4</v>
       </c>
       <c r="Q286" s="4">
-        <v>13.5</v>
+        <v>45.1</v>
       </c>
       <c r="R286" s="4">
-        <v>15.8</v>
+        <v>51.7</v>
       </c>
       <c r="S286" s="4">
-        <v>23.6</v>
+        <v>62.4</v>
       </c>
       <c r="T286" s="4">
-        <v>26.1</v>
+        <v>65.7</v>
       </c>
       <c r="U286" s="4">
-        <v>27.4</v>
+        <v>68.8</v>
       </c>
       <c r="V286" s="4">
-        <v>27.6</v>
+        <v>69.900000000000006</v>
       </c>
       <c r="W286" s="2" t="s">
         <v>30</v>
@@ -19876,155 +19865,155 @@
     </row>
     <row r="287" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="E287" s="3" t="s">
-        <v>28</v>
+        <v>398</v>
       </c>
       <c r="F287" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G287" s="4">
-        <v>5.7</v>
+        <v>13.5</v>
       </c>
       <c r="H287" s="4">
-        <v>6</v>
+        <v>15.7</v>
       </c>
       <c r="I287" s="4">
-        <v>4.9000000000000004</v>
+        <v>17.2</v>
       </c>
       <c r="J287" s="4">
-        <v>4.3</v>
+        <v>12.7</v>
       </c>
       <c r="K287" s="4">
-        <v>4.7</v>
+        <v>15.5</v>
       </c>
       <c r="L287" s="4">
-        <v>4.5</v>
+        <v>18.3</v>
       </c>
       <c r="M287" s="4">
-        <v>3.3</v>
+        <v>19.8</v>
       </c>
       <c r="N287" s="4">
-        <v>3.8</v>
+        <v>18.8</v>
       </c>
       <c r="O287" s="4">
-        <v>4.5999999999999996</v>
+        <v>22.4</v>
       </c>
       <c r="P287" s="4">
-        <v>4.3</v>
+        <v>28.5</v>
       </c>
       <c r="Q287" s="4">
-        <v>4.4000000000000004</v>
+        <v>29.4</v>
       </c>
       <c r="R287" s="4">
-        <v>4.0999999999999996</v>
+        <v>35</v>
       </c>
       <c r="S287" s="4">
-        <v>3.8</v>
+        <v>39.5</v>
       </c>
       <c r="T287" s="4">
-        <v>5.0999999999999996</v>
+        <v>44.4</v>
       </c>
       <c r="U287" s="4">
-        <v>4.8</v>
+        <v>50.8</v>
       </c>
       <c r="V287" s="4">
-        <v>5.2</v>
+        <v>51.4</v>
       </c>
       <c r="W287" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="288" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="E288" s="3" t="s">
-        <v>28</v>
+        <v>399</v>
       </c>
       <c r="F288" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G288" s="6">
-        <v>674</v>
-      </c>
-      <c r="H288" s="6">
-        <v>605</v>
-      </c>
-      <c r="I288" s="6">
-        <v>1082</v>
-      </c>
-      <c r="J288" s="6">
-        <v>1219</v>
-      </c>
-      <c r="K288" s="6">
-        <v>1282</v>
-      </c>
-      <c r="L288" s="6">
-        <v>1456</v>
-      </c>
-      <c r="M288" s="6">
-        <v>1926</v>
-      </c>
-      <c r="N288" s="6">
-        <v>3182</v>
-      </c>
-      <c r="O288" s="6">
-        <v>3739</v>
-      </c>
-      <c r="P288" s="6">
-        <v>6484</v>
-      </c>
-      <c r="Q288" s="6">
-        <v>10420</v>
-      </c>
-      <c r="R288" s="6">
-        <v>29483</v>
-      </c>
-      <c r="S288" s="6">
-        <v>39683</v>
-      </c>
-      <c r="T288" s="6">
-        <v>80267</v>
-      </c>
-      <c r="U288" s="6">
-        <v>103449</v>
-      </c>
-      <c r="V288" s="6">
-        <v>260783</v>
+        <v>34</v>
+      </c>
+      <c r="G288" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H288" s="4">
+        <v>5</v>
+      </c>
+      <c r="I288" s="4">
+        <v>6.8</v>
+      </c>
+      <c r="J288" s="4">
+        <v>3.7</v>
+      </c>
+      <c r="K288" s="4">
+        <v>6.6</v>
+      </c>
+      <c r="L288" s="4">
+        <v>6</v>
+      </c>
+      <c r="M288" s="4">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="N288" s="4">
+        <v>8.4</v>
+      </c>
+      <c r="O288" s="4">
+        <v>10.9</v>
+      </c>
+      <c r="P288" s="4">
+        <v>12.2</v>
+      </c>
+      <c r="Q288" s="4">
+        <v>13.5</v>
+      </c>
+      <c r="R288" s="4">
+        <v>15.8</v>
+      </c>
+      <c r="S288" s="4">
+        <v>23.6</v>
+      </c>
+      <c r="T288" s="4">
+        <v>26.1</v>
+      </c>
+      <c r="U288" s="4">
+        <v>27.4</v>
+      </c>
+      <c r="V288" s="4">
+        <v>27.6</v>
       </c>
       <c r="W288" s="2" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="289" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="289" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D289" s="2" t="s">
         <v>27</v>
@@ -20035,35 +20024,61 @@
       <c r="F289" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G289" s="3"/>
-      <c r="H289" s="3"/>
-      <c r="I289" s="3"/>
-      <c r="J289" s="3"/>
-      <c r="K289" s="3"/>
-      <c r="L289" s="3"/>
-      <c r="M289" s="3"/>
-      <c r="N289" s="3"/>
-      <c r="O289" s="3"/>
-      <c r="P289" s="3"/>
-      <c r="Q289" s="3"/>
-      <c r="R289" s="5">
-        <v>18.93</v>
-      </c>
-      <c r="S289" s="3"/>
-      <c r="T289" s="5">
-        <v>21.3</v>
-      </c>
-      <c r="U289" s="3"/>
-      <c r="V289" s="5">
-        <v>23.01</v>
+      <c r="G289" s="4">
+        <v>5.7</v>
+      </c>
+      <c r="H289" s="4">
+        <v>6</v>
+      </c>
+      <c r="I289" s="4">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="J289" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="K289" s="4">
+        <v>4.7</v>
+      </c>
+      <c r="L289" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="M289" s="4">
+        <v>3.3</v>
+      </c>
+      <c r="N289" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="O289" s="4">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="P289" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="Q289" s="4">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="R289" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="S289" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="T289" s="4">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="U289" s="4">
+        <v>4.8</v>
+      </c>
+      <c r="V289" s="4">
+        <v>5.2</v>
       </c>
       <c r="W289" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="290" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="290" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
-        <v>401</v>
+        <v>380</v>
       </c>
       <c r="B290" s="2" t="s">
         <v>402</v>
@@ -20078,67 +20093,69 @@
         <v>28</v>
       </c>
       <c r="F290" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G290" s="6">
+        <v>674</v>
+      </c>
+      <c r="H290" s="6">
+        <v>605</v>
+      </c>
+      <c r="I290" s="6">
+        <v>1082</v>
+      </c>
+      <c r="J290" s="6">
+        <v>1219</v>
+      </c>
+      <c r="K290" s="6">
+        <v>1282</v>
+      </c>
+      <c r="L290" s="6">
+        <v>1456</v>
+      </c>
+      <c r="M290" s="6">
+        <v>1926</v>
+      </c>
+      <c r="N290" s="6">
+        <v>3182</v>
+      </c>
+      <c r="O290" s="6">
+        <v>3739</v>
+      </c>
+      <c r="P290" s="6">
+        <v>6484</v>
+      </c>
+      <c r="Q290" s="6">
+        <v>10420</v>
+      </c>
+      <c r="R290" s="6">
+        <v>29483</v>
+      </c>
+      <c r="S290" s="6">
+        <v>39683</v>
+      </c>
+      <c r="T290" s="6">
+        <v>80267</v>
+      </c>
+      <c r="U290" s="6">
+        <v>103449</v>
+      </c>
+      <c r="V290" s="6">
+        <v>260783</v>
+      </c>
+      <c r="W290" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="G290" s="5">
-        <v>377.75</v>
-      </c>
-      <c r="H290" s="5">
-        <v>417.47</v>
-      </c>
-      <c r="I290" s="5">
-        <v>421.06</v>
-      </c>
-      <c r="J290" s="5">
-        <v>487.12</v>
-      </c>
-      <c r="K290" s="5">
-        <v>451.84</v>
-      </c>
-      <c r="L290" s="5">
-        <v>440.89</v>
-      </c>
-      <c r="M290" s="5">
-        <v>662.95</v>
-      </c>
-      <c r="N290" s="5">
-        <v>679.46</v>
-      </c>
-      <c r="O290" s="5">
-        <v>766.04</v>
-      </c>
-      <c r="P290" s="5">
-        <v>776.56</v>
-      </c>
-      <c r="Q290" s="5">
-        <v>829.27</v>
-      </c>
-      <c r="R290" s="5">
-        <v>983.51</v>
-      </c>
-      <c r="S290" s="5">
-        <v>3494.39</v>
-      </c>
-      <c r="T290" s="5">
-        <v>2580.38</v>
-      </c>
-      <c r="U290" s="5">
-        <v>1840.15</v>
-      </c>
-      <c r="V290" s="3"/>
-      <c r="W290" s="2" t="s">
+    </row>
+    <row r="291" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+      <c r="A291" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B291" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="C291" s="2" t="s">
         <v>405</v>
-      </c>
-    </row>
-    <row r="291" spans="1:23" ht="36" x14ac:dyDescent="0.25">
-      <c r="A291" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="B291" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="C291" s="2" t="s">
-        <v>407</v>
       </c>
       <c r="D291" s="2" t="s">
         <v>27</v>
@@ -20147,67 +20164,43 @@
         <v>28</v>
       </c>
       <c r="F291" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="G291" s="5">
-        <v>96.04</v>
-      </c>
-      <c r="H291" s="5">
-        <v>90.68</v>
-      </c>
-      <c r="I291" s="5">
-        <v>111.55</v>
-      </c>
-      <c r="J291" s="5">
-        <v>127.11</v>
-      </c>
-      <c r="K291" s="5">
-        <v>82.28</v>
-      </c>
-      <c r="L291" s="5">
-        <v>100.19</v>
-      </c>
-      <c r="M291" s="5">
-        <v>148.99</v>
-      </c>
-      <c r="N291" s="5">
-        <v>222.11</v>
-      </c>
-      <c r="O291" s="5">
-        <v>244.93</v>
-      </c>
-      <c r="P291" s="5">
-        <v>223.31</v>
-      </c>
-      <c r="Q291" s="5">
-        <v>225.08</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="G291" s="3"/>
+      <c r="H291" s="3"/>
+      <c r="I291" s="3"/>
+      <c r="J291" s="3"/>
+      <c r="K291" s="3"/>
+      <c r="L291" s="3"/>
+      <c r="M291" s="3"/>
+      <c r="N291" s="3"/>
+      <c r="O291" s="3"/>
+      <c r="P291" s="3"/>
+      <c r="Q291" s="3"/>
       <c r="R291" s="5">
-        <v>296.20999999999998</v>
-      </c>
-      <c r="S291" s="5">
-        <v>2661.32</v>
-      </c>
+        <v>18.93</v>
+      </c>
+      <c r="S291" s="3"/>
       <c r="T291" s="5">
-        <v>1701.94</v>
-      </c>
-      <c r="U291" s="5">
-        <v>705.25</v>
-      </c>
-      <c r="V291" s="3"/>
+        <v>21.3</v>
+      </c>
+      <c r="U291" s="3"/>
+      <c r="V291" s="5">
+        <v>23.01</v>
+      </c>
       <c r="W291" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="292" spans="1:23" ht="72" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="292" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="B292" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C292" s="2" t="s">
         <v>408</v>
-      </c>
-      <c r="C292" s="2" t="s">
-        <v>409</v>
       </c>
       <c r="D292" s="2" t="s">
         <v>27</v>
@@ -20216,67 +20209,67 @@
         <v>28</v>
       </c>
       <c r="F292" s="3" t="s">
-        <v>34</v>
+        <v>409</v>
       </c>
       <c r="G292" s="5">
-        <v>0.08</v>
+        <v>377.75</v>
       </c>
       <c r="H292" s="5">
-        <v>0.08</v>
+        <v>417.47</v>
       </c>
       <c r="I292" s="5">
-        <v>0.09</v>
+        <v>421.06</v>
       </c>
       <c r="J292" s="5">
-        <v>0.1</v>
+        <v>487.12</v>
       </c>
       <c r="K292" s="5">
-        <v>0.09</v>
+        <v>451.84</v>
       </c>
       <c r="L292" s="5">
-        <v>0.1</v>
+        <v>440.89</v>
       </c>
       <c r="M292" s="5">
-        <v>0.15</v>
+        <v>662.95</v>
       </c>
       <c r="N292" s="5">
-        <v>0.13</v>
+        <v>679.46</v>
       </c>
       <c r="O292" s="5">
-        <v>0.14000000000000001</v>
+        <v>766.04</v>
       </c>
       <c r="P292" s="5">
-        <v>0.14000000000000001</v>
+        <v>776.56</v>
       </c>
       <c r="Q292" s="5">
-        <v>0.14000000000000001</v>
+        <v>829.27</v>
       </c>
       <c r="R292" s="5">
-        <v>0.15</v>
+        <v>983.51</v>
       </c>
       <c r="S292" s="5">
-        <v>0.53</v>
+        <v>3494.39</v>
       </c>
       <c r="T292" s="5">
-        <v>0.33</v>
+        <v>2580.38</v>
       </c>
       <c r="U292" s="5">
-        <v>0.21</v>
+        <v>1840.15</v>
       </c>
       <c r="V292" s="3"/>
       <c r="W292" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="293" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="293" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D293" s="2" t="s">
         <v>27</v>
@@ -20285,63 +20278,67 @@
         <v>28</v>
       </c>
       <c r="F293" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="G293" s="3"/>
-      <c r="H293" s="3"/>
-      <c r="I293" s="3"/>
-      <c r="J293" s="7">
-        <v>2.2850000000000001</v>
-      </c>
-      <c r="K293" s="7">
-        <v>1.1160000000000001</v>
-      </c>
-      <c r="L293" s="7">
-        <v>1.55</v>
-      </c>
-      <c r="M293" s="7">
-        <v>3.7469999999999999</v>
-      </c>
-      <c r="N293" s="7">
-        <v>3.8530000000000002</v>
-      </c>
-      <c r="O293" s="7">
-        <v>3.367</v>
-      </c>
-      <c r="P293" s="7">
-        <v>6.8940000000000001</v>
-      </c>
-      <c r="Q293" s="7">
-        <v>4.077</v>
-      </c>
-      <c r="R293" s="7">
-        <v>4.49</v>
-      </c>
-      <c r="S293" s="7">
-        <v>11.999000000000001</v>
-      </c>
-      <c r="T293" s="7">
-        <v>16.606000000000002</v>
-      </c>
-      <c r="U293" s="7">
-        <v>20.382000000000001</v>
-      </c>
-      <c r="V293" s="7">
-        <v>5.3920000000000003</v>
-      </c>
+        <v>409</v>
+      </c>
+      <c r="G293" s="5">
+        <v>96.04</v>
+      </c>
+      <c r="H293" s="5">
+        <v>90.68</v>
+      </c>
+      <c r="I293" s="5">
+        <v>111.55</v>
+      </c>
+      <c r="J293" s="5">
+        <v>127.11</v>
+      </c>
+      <c r="K293" s="5">
+        <v>82.28</v>
+      </c>
+      <c r="L293" s="5">
+        <v>100.19</v>
+      </c>
+      <c r="M293" s="5">
+        <v>148.99</v>
+      </c>
+      <c r="N293" s="5">
+        <v>222.11</v>
+      </c>
+      <c r="O293" s="5">
+        <v>244.93</v>
+      </c>
+      <c r="P293" s="5">
+        <v>223.31</v>
+      </c>
+      <c r="Q293" s="5">
+        <v>225.08</v>
+      </c>
+      <c r="R293" s="5">
+        <v>296.20999999999998</v>
+      </c>
+      <c r="S293" s="5">
+        <v>2661.32</v>
+      </c>
+      <c r="T293" s="5">
+        <v>1701.94</v>
+      </c>
+      <c r="U293" s="5">
+        <v>705.25</v>
+      </c>
+      <c r="V293" s="3"/>
       <c r="W293" s="2" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="294" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="294" spans="1:23" ht="72" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D294" s="2" t="s">
         <v>27</v>
@@ -20350,61 +20347,67 @@
         <v>28</v>
       </c>
       <c r="F294" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="G294" s="3"/>
-      <c r="H294" s="3"/>
-      <c r="I294" s="3"/>
+        <v>34</v>
+      </c>
+      <c r="G294" s="5">
+        <v>0.08</v>
+      </c>
+      <c r="H294" s="5">
+        <v>0.08</v>
+      </c>
+      <c r="I294" s="5">
+        <v>0.09</v>
+      </c>
       <c r="J294" s="5">
-        <v>8.07</v>
+        <v>0.1</v>
       </c>
       <c r="K294" s="5">
-        <v>3.54</v>
+        <v>0.09</v>
       </c>
       <c r="L294" s="5">
-        <v>2.98</v>
+        <v>0.1</v>
       </c>
       <c r="M294" s="5">
-        <v>2.44</v>
+        <v>0.15</v>
       </c>
       <c r="N294" s="5">
-        <v>2.25</v>
+        <v>0.13</v>
       </c>
       <c r="O294" s="5">
-        <v>63.36</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="P294" s="5">
-        <v>7.61</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="Q294" s="5">
-        <v>6.64</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="R294" s="5">
-        <v>3.65</v>
+        <v>0.15</v>
       </c>
       <c r="S294" s="5">
-        <v>9.59</v>
+        <v>0.53</v>
       </c>
       <c r="T294" s="5">
-        <v>4.2699999999999996</v>
+        <v>0.33</v>
       </c>
       <c r="U294" s="5">
-        <v>8.32</v>
+        <v>0.21</v>
       </c>
       <c r="V294" s="3"/>
       <c r="W294" s="2" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
     </row>
     <row r="295" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D295" s="2" t="s">
         <v>27</v>
@@ -20413,41 +20416,49 @@
         <v>28</v>
       </c>
       <c r="F295" s="3" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="G295" s="3"/>
       <c r="H295" s="3"/>
       <c r="I295" s="3"/>
-      <c r="J295" s="3"/>
-      <c r="K295" s="6">
-        <v>1</v>
-      </c>
-      <c r="L295" s="6">
-        <v>1</v>
-      </c>
-      <c r="M295" s="6">
-        <v>8</v>
-      </c>
-      <c r="N295" s="6">
-        <v>2</v>
-      </c>
-      <c r="O295" s="3"/>
-      <c r="P295" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q295" s="6">
-        <v>2</v>
-      </c>
-      <c r="R295" s="3"/>
-      <c r="S295" s="3"/>
-      <c r="T295" s="6">
-        <v>8</v>
-      </c>
-      <c r="U295" s="6">
-        <v>7</v>
-      </c>
-      <c r="V295" s="6">
-        <v>2</v>
+      <c r="J295" s="7">
+        <v>2.2850000000000001</v>
+      </c>
+      <c r="K295" s="7">
+        <v>1.1160000000000001</v>
+      </c>
+      <c r="L295" s="7">
+        <v>1.55</v>
+      </c>
+      <c r="M295" s="7">
+        <v>3.7469999999999999</v>
+      </c>
+      <c r="N295" s="7">
+        <v>3.8530000000000002</v>
+      </c>
+      <c r="O295" s="7">
+        <v>3.367</v>
+      </c>
+      <c r="P295" s="7">
+        <v>6.8940000000000001</v>
+      </c>
+      <c r="Q295" s="7">
+        <v>4.077</v>
+      </c>
+      <c r="R295" s="7">
+        <v>4.49</v>
+      </c>
+      <c r="S295" s="7">
+        <v>11.999000000000001</v>
+      </c>
+      <c r="T295" s="7">
+        <v>16.606000000000002</v>
+      </c>
+      <c r="U295" s="7">
+        <v>20.382000000000001</v>
+      </c>
+      <c r="V295" s="7">
+        <v>5.3920000000000003</v>
       </c>
       <c r="W295" s="2" t="s">
         <v>417</v>
@@ -20455,13 +20466,13 @@
     </row>
     <row r="296" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="B296" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="C296" s="2" t="s">
         <v>418</v>
-      </c>
-      <c r="C296" s="2" t="s">
-        <v>419</v>
       </c>
       <c r="D296" s="2" t="s">
         <v>27</v>
@@ -20470,65 +20481,61 @@
         <v>28</v>
       </c>
       <c r="F296" s="3" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="G296" s="3"/>
       <c r="H296" s="3"/>
-      <c r="I296" s="6">
-        <v>2</v>
-      </c>
-      <c r="J296" s="6">
-        <v>2</v>
-      </c>
-      <c r="K296" s="6">
-        <v>1</v>
-      </c>
-      <c r="L296" s="6">
-        <v>1</v>
-      </c>
-      <c r="M296" s="6">
-        <v>1</v>
-      </c>
-      <c r="N296" s="6">
-        <v>1</v>
-      </c>
-      <c r="O296" s="6">
-        <v>1</v>
-      </c>
-      <c r="P296" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q296" s="6">
-        <v>4</v>
-      </c>
-      <c r="R296" s="6">
-        <v>1</v>
-      </c>
-      <c r="S296" s="6">
-        <v>1</v>
-      </c>
-      <c r="T296" s="6">
-        <v>0</v>
-      </c>
-      <c r="U296" s="6">
-        <v>4</v>
-      </c>
-      <c r="V296" s="6">
-        <v>2</v>
-      </c>
+      <c r="I296" s="3"/>
+      <c r="J296" s="5">
+        <v>8.07</v>
+      </c>
+      <c r="K296" s="5">
+        <v>3.54</v>
+      </c>
+      <c r="L296" s="5">
+        <v>2.98</v>
+      </c>
+      <c r="M296" s="5">
+        <v>2.44</v>
+      </c>
+      <c r="N296" s="5">
+        <v>2.25</v>
+      </c>
+      <c r="O296" s="5">
+        <v>63.36</v>
+      </c>
+      <c r="P296" s="5">
+        <v>7.61</v>
+      </c>
+      <c r="Q296" s="5">
+        <v>6.64</v>
+      </c>
+      <c r="R296" s="5">
+        <v>3.65</v>
+      </c>
+      <c r="S296" s="5">
+        <v>9.59</v>
+      </c>
+      <c r="T296" s="5">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="U296" s="5">
+        <v>8.32</v>
+      </c>
+      <c r="V296" s="3"/>
       <c r="W296" s="2" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
     </row>
     <row r="297" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="B297" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="C297" s="2" t="s">
         <v>420</v>
-      </c>
-      <c r="C297" s="2" t="s">
-        <v>421</v>
       </c>
       <c r="D297" s="2" t="s">
         <v>27</v>
@@ -20537,61 +20544,55 @@
         <v>28</v>
       </c>
       <c r="F297" s="3" t="s">
-        <v>32</v>
+        <v>421</v>
       </c>
       <c r="G297" s="3"/>
       <c r="H297" s="3"/>
       <c r="I297" s="3"/>
       <c r="J297" s="3"/>
       <c r="K297" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L297" s="6">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="M297" s="6">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="N297" s="6">
-        <v>18</v>
-      </c>
-      <c r="O297" s="6">
-        <v>15</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="O297" s="3"/>
       <c r="P297" s="6">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="Q297" s="6">
+        <v>2</v>
+      </c>
+      <c r="R297" s="3"/>
+      <c r="S297" s="3"/>
+      <c r="T297" s="6">
         <v>8</v>
       </c>
-      <c r="R297" s="6">
-        <v>28</v>
-      </c>
-      <c r="S297" s="6">
-        <v>53</v>
-      </c>
-      <c r="T297" s="6">
-        <v>65</v>
-      </c>
       <c r="U297" s="6">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="V297" s="6">
-        <v>69</v>
+        <v>2</v>
       </c>
       <c r="W297" s="2" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="298" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="298" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D298" s="2" t="s">
         <v>27</v>
@@ -20600,47 +20601,177 @@
         <v>28</v>
       </c>
       <c r="F298" s="3" t="s">
-        <v>32</v>
+        <v>421</v>
       </c>
       <c r="G298" s="3"/>
       <c r="H298" s="3"/>
-      <c r="I298" s="3"/>
-      <c r="J298" s="3"/>
-      <c r="K298" s="3"/>
-      <c r="L298" s="3"/>
-      <c r="M298" s="3"/>
-      <c r="N298" s="3"/>
-      <c r="O298" s="3"/>
-      <c r="P298" s="3"/>
-      <c r="Q298" s="3"/>
-      <c r="R298" s="3"/>
-      <c r="S298" s="3"/>
+      <c r="I298" s="6">
+        <v>2</v>
+      </c>
+      <c r="J298" s="6">
+        <v>2</v>
+      </c>
+      <c r="K298" s="6">
+        <v>1</v>
+      </c>
+      <c r="L298" s="6">
+        <v>1</v>
+      </c>
+      <c r="M298" s="6">
+        <v>1</v>
+      </c>
+      <c r="N298" s="6">
+        <v>1</v>
+      </c>
+      <c r="O298" s="6">
+        <v>1</v>
+      </c>
+      <c r="P298" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q298" s="6">
+        <v>4</v>
+      </c>
+      <c r="R298" s="6">
+        <v>1</v>
+      </c>
+      <c r="S298" s="6">
+        <v>1</v>
+      </c>
       <c r="T298" s="6">
+        <v>0</v>
+      </c>
+      <c r="U298" s="6">
+        <v>4</v>
+      </c>
+      <c r="V298" s="6">
+        <v>2</v>
+      </c>
+      <c r="W298" s="2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="299" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+      <c r="A299" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="B299" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="C299" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="D299" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E299" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F299" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G299" s="3"/>
+      <c r="H299" s="3"/>
+      <c r="I299" s="3"/>
+      <c r="J299" s="3"/>
+      <c r="K299" s="6">
+        <v>5</v>
+      </c>
+      <c r="L299" s="6">
+        <v>13</v>
+      </c>
+      <c r="M299" s="6">
+        <v>19</v>
+      </c>
+      <c r="N299" s="6">
+        <v>18</v>
+      </c>
+      <c r="O299" s="6">
+        <v>15</v>
+      </c>
+      <c r="P299" s="6">
+        <v>15</v>
+      </c>
+      <c r="Q299" s="6">
+        <v>8</v>
+      </c>
+      <c r="R299" s="6">
+        <v>28</v>
+      </c>
+      <c r="S299" s="6">
+        <v>53</v>
+      </c>
+      <c r="T299" s="6">
+        <v>65</v>
+      </c>
+      <c r="U299" s="6">
+        <v>70</v>
+      </c>
+      <c r="V299" s="6">
+        <v>69</v>
+      </c>
+      <c r="W299" s="2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="300" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+      <c r="A300" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="B300" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="C300" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="D300" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E300" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F300" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G300" s="3"/>
+      <c r="H300" s="3"/>
+      <c r="I300" s="3"/>
+      <c r="J300" s="3"/>
+      <c r="K300" s="3"/>
+      <c r="L300" s="3"/>
+      <c r="M300" s="3"/>
+      <c r="N300" s="3"/>
+      <c r="O300" s="3"/>
+      <c r="P300" s="3"/>
+      <c r="Q300" s="3"/>
+      <c r="R300" s="3"/>
+      <c r="S300" s="3"/>
+      <c r="T300" s="6">
         <v>114</v>
       </c>
-      <c r="U298" s="6">
+      <c r="U300" s="6">
         <v>61</v>
       </c>
-      <c r="V298" s="6">
+      <c r="V300" s="6">
         <v>97</v>
       </c>
-      <c r="W298" s="2" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="299" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="300" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A300" s="10" t="s">
-        <v>425</v>
-      </c>
-      <c r="B300" s="8"/>
+      <c r="W300" s="2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="301" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A302" s="10" t="s">
+        <v>430</v>
+      </c>
+      <c r="B302" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:C3" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A300:B300"/>
+    <mergeCell ref="A302:B302"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>

--- a/assets/excel/en/national_sdg_indicators.xlsx
+++ b/assets/excel/en/national_sdg_indicators.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sidwab\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C68FBFFF-6B7A-4C44-A574-432027A15113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A037913B-D2A7-433F-86BC-9F6E5E42A691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2104" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2153" uniqueCount="441">
   <si>
     <t>sdg.gov.pl/en</t>
   </si>
@@ -1108,10 +1108,25 @@
     <t>proportion of stocks overexploited on the Baltic Sea</t>
   </si>
   <si>
+    <t>14.1.b Share of marine protected areas</t>
+  </si>
+  <si>
     <t>Increase of maritime economy share in GDP and increase of employment in maritime economy</t>
   </si>
   <si>
-    <t>14.2.a Indices of average employment in maritime economy (2010=100)</t>
+    <t>14.2.a Indices of average employment in the maritime economy (previous year = 100)</t>
+  </si>
+  <si>
+    <t>private</t>
+  </si>
+  <si>
+    <t>previous year = 100</t>
+  </si>
+  <si>
+    <t>public</t>
+  </si>
+  <si>
+    <t>14.2.b Share of the maritime economy in the gross value of fixed assets of the national economy</t>
   </si>
   <si>
     <t>Enhancement of Polish seaports position, increase in competitiveness of sea transport and ensurance of sea security</t>
@@ -1123,6 +1138,21 @@
     <t xml:space="preserve">million tonnes [mln t] </t>
   </si>
   <si>
+    <t>14.3.b Domestic passenger traffic in seaports</t>
+  </si>
+  <si>
+    <t>by passenger traffic</t>
+  </si>
+  <si>
+    <t>arrivals</t>
+  </si>
+  <si>
+    <t>departures</t>
+  </si>
+  <si>
+    <t>14.3.c International passenger traffic in seaports</t>
+  </si>
+  <si>
     <t>Goal 15. Life on land</t>
   </si>
   <si>
@@ -1321,7 +1351,7 @@
     <t>The Ministry of Economic Development and Technology / The Chancellery of the  Prime Minister</t>
   </si>
   <si>
-    <t>Last update: 05-08-2026, 13:23</t>
+    <t>Last update: 07-08-2026, 10:19</t>
   </si>
 </sst>
 </file>
@@ -1867,7 +1897,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W302"/>
+  <dimension ref="A1:W309"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" customWidth="1"/>
@@ -18330,15 +18360,15 @@
         <v>355</v>
       </c>
     </row>
-    <row r="264" spans="1:23" ht="18" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:23" ht="72" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
         <v>350</v>
       </c>
       <c r="B264" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="C264" s="2" t="s">
         <v>359</v>
-      </c>
-      <c r="C264" s="2" t="s">
-        <v>360</v>
       </c>
       <c r="D264" s="2" t="s">
         <v>27</v>
@@ -18347,205 +18377,183 @@
         <v>28</v>
       </c>
       <c r="F264" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="G264" s="4">
-        <v>100</v>
-      </c>
-      <c r="H264" s="4">
-        <v>100.8</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="G264" s="3"/>
+      <c r="H264" s="3"/>
       <c r="I264" s="4">
-        <v>99.9</v>
-      </c>
-      <c r="J264" s="4">
-        <v>101.8</v>
-      </c>
-      <c r="K264" s="4">
-        <v>104.9</v>
-      </c>
-      <c r="L264" s="4">
-        <v>106</v>
-      </c>
+        <v>21.8</v>
+      </c>
+      <c r="J264" s="3"/>
+      <c r="K264" s="3"/>
+      <c r="L264" s="3"/>
       <c r="M264" s="4">
-        <v>119.9</v>
-      </c>
-      <c r="N264" s="4">
-        <v>119.4</v>
-      </c>
-      <c r="O264" s="4">
-        <v>130</v>
-      </c>
+        <v>21.8</v>
+      </c>
+      <c r="N264" s="3"/>
+      <c r="O264" s="3"/>
       <c r="P264" s="4">
-        <v>189.5</v>
-      </c>
-      <c r="Q264" s="4">
-        <v>186.6</v>
-      </c>
+        <v>21.8</v>
+      </c>
+      <c r="Q264" s="3"/>
       <c r="R264" s="4">
-        <v>190.1</v>
+        <v>21.9</v>
       </c>
       <c r="S264" s="4">
-        <v>200.8</v>
+        <v>21.9</v>
       </c>
       <c r="T264" s="4">
-        <v>205.6</v>
-      </c>
-      <c r="U264" s="4">
-        <v>208.5</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="U264" s="3"/>
       <c r="V264" s="3"/>
       <c r="W264" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="265" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="265" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
         <v>350</v>
       </c>
       <c r="B265" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="C265" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="C265" s="2" t="s">
+      <c r="D265" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E265" s="3" t="s">
         <v>362</v>
-      </c>
-      <c r="D265" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E265" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="F265" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="G265" s="4">
-        <v>59.5</v>
-      </c>
+      <c r="G265" s="3"/>
       <c r="H265" s="4">
-        <v>57.7</v>
+        <v>101.8</v>
       </c>
       <c r="I265" s="4">
-        <v>58.8</v>
+        <v>100</v>
       </c>
       <c r="J265" s="4">
-        <v>64.3</v>
+        <v>101.8</v>
       </c>
       <c r="K265" s="4">
-        <v>68.7</v>
+        <v>103.2</v>
       </c>
       <c r="L265" s="4">
-        <v>69.5</v>
+        <v>101.8</v>
       </c>
       <c r="M265" s="4">
-        <v>72.900000000000006</v>
+        <v>115.4</v>
       </c>
       <c r="N265" s="4">
-        <v>78.099999999999994</v>
+        <v>98.6</v>
       </c>
       <c r="O265" s="4">
-        <v>91.8</v>
+        <v>110.3</v>
       </c>
       <c r="P265" s="4">
-        <v>93.9</v>
+        <v>149.6</v>
       </c>
       <c r="Q265" s="4">
-        <v>88.5</v>
+        <v>98.5</v>
       </c>
       <c r="R265" s="4">
-        <v>96.7</v>
+        <v>102.3</v>
       </c>
       <c r="S265" s="4">
-        <v>119</v>
+        <v>106.1</v>
       </c>
       <c r="T265" s="4">
-        <v>136.4</v>
+        <v>102.7</v>
       </c>
       <c r="U265" s="4">
-        <v>124.2</v>
+        <v>101</v>
       </c>
       <c r="V265" s="3"/>
       <c r="W265" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="266" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B266" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="C266" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D266" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E266" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="B266" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="C266" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="D266" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E266" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="F266" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="G266" s="4">
-        <v>90.8</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="G266" s="3"/>
       <c r="H266" s="4">
-        <v>88.8</v>
+        <v>95.6</v>
       </c>
       <c r="I266" s="4">
-        <v>86.5</v>
+        <v>94.8</v>
       </c>
       <c r="J266" s="4">
-        <v>87</v>
+        <v>102.6</v>
       </c>
       <c r="K266" s="4">
-        <v>85</v>
+        <v>102.1</v>
       </c>
       <c r="L266" s="4">
-        <v>87.4</v>
+        <v>96.9</v>
       </c>
       <c r="M266" s="4">
-        <v>88.7</v>
+        <v>99.7</v>
       </c>
       <c r="N266" s="4">
-        <v>84.6</v>
+        <v>106.1</v>
       </c>
       <c r="O266" s="4">
-        <v>77.3</v>
+        <v>100.5</v>
       </c>
       <c r="P266" s="4">
-        <v>79.7</v>
+        <v>119</v>
       </c>
       <c r="Q266" s="4">
-        <v>81.900000000000006</v>
+        <v>98.4</v>
       </c>
       <c r="R266" s="4">
-        <v>74.8</v>
+        <v>98.1</v>
       </c>
       <c r="S266" s="4">
-        <v>77</v>
+        <v>101.5</v>
       </c>
       <c r="T266" s="4">
-        <v>77.2</v>
+        <v>98.9</v>
       </c>
       <c r="U266" s="4">
-        <v>76.3</v>
+        <v>105.5</v>
       </c>
       <c r="V266" s="3"/>
       <c r="W266" s="2" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="267" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="267" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="B267" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="C267" s="2" t="s">
         <v>365</v>
-      </c>
-      <c r="C267" s="2" t="s">
-        <v>369</v>
       </c>
       <c r="D267" s="2" t="s">
         <v>27</v>
@@ -18556,65 +18564,65 @@
       <c r="F267" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G267" s="7">
-        <v>0.19600000000000001</v>
-      </c>
-      <c r="H267" s="7">
-        <v>0.20499999999999999</v>
-      </c>
-      <c r="I267" s="7">
-        <v>0.20599999999999999</v>
-      </c>
-      <c r="J267" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="K267" s="7">
-        <v>0.20100000000000001</v>
-      </c>
-      <c r="L267" s="7">
-        <v>0.20300000000000001</v>
-      </c>
-      <c r="M267" s="7">
-        <v>0.20699999999999999</v>
-      </c>
-      <c r="N267" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="O267" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="P267" s="7">
-        <v>0.19900000000000001</v>
-      </c>
-      <c r="Q267" s="7">
-        <v>0.2</v>
-      </c>
-      <c r="R267" s="7">
-        <v>0.19900000000000001</v>
-      </c>
-      <c r="S267" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="T267" s="7">
-        <v>0.192</v>
-      </c>
-      <c r="U267" s="7">
-        <v>0.192</v>
+      <c r="G267" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="H267" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="I267" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="J267" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="K267" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="L267" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="M267" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="N267" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="O267" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="P267" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="Q267" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="R267" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="S267" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="T267" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="U267" s="4">
+        <v>0.8</v>
       </c>
       <c r="V267" s="3"/>
       <c r="W267" s="2" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="268" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="268" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="D268" s="2" t="s">
         <v>27</v>
@@ -18623,343 +18631,351 @@
         <v>28</v>
       </c>
       <c r="F268" s="3" t="s">
-        <v>34</v>
+        <v>368</v>
       </c>
       <c r="G268" s="4">
-        <v>30.5</v>
+        <v>59.5</v>
       </c>
       <c r="H268" s="4">
-        <v>30.5</v>
+        <v>57.7</v>
       </c>
       <c r="I268" s="4">
-        <v>30.6</v>
+        <v>58.8</v>
       </c>
       <c r="J268" s="4">
-        <v>30.6</v>
+        <v>64.3</v>
       </c>
       <c r="K268" s="4">
-        <v>30.7</v>
+        <v>68.7</v>
       </c>
       <c r="L268" s="4">
-        <v>30.8</v>
+        <v>69.5</v>
       </c>
       <c r="M268" s="4">
-        <v>30.8</v>
+        <v>72.900000000000006</v>
       </c>
       <c r="N268" s="4">
-        <v>30.9</v>
+        <v>78.099999999999994</v>
       </c>
       <c r="O268" s="4">
-        <v>30.9</v>
+        <v>91.8</v>
       </c>
       <c r="P268" s="4">
-        <v>30.9</v>
+        <v>93.9</v>
       </c>
       <c r="Q268" s="4">
-        <v>30.9</v>
+        <v>88.5</v>
       </c>
       <c r="R268" s="4">
-        <v>30.9</v>
+        <v>96.7</v>
       </c>
       <c r="S268" s="4">
-        <v>31</v>
+        <v>119</v>
       </c>
       <c r="T268" s="4">
-        <v>31</v>
+        <v>136.4</v>
       </c>
       <c r="U268" s="4">
-        <v>31</v>
+        <v>124.2</v>
       </c>
       <c r="V268" s="3"/>
       <c r="W268" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="269" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="B269" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="C269" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D269" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E269" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="F269" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G269" s="6">
+        <v>493249</v>
+      </c>
+      <c r="H269" s="6">
+        <v>474154</v>
+      </c>
+      <c r="I269" s="6">
+        <v>372834</v>
+      </c>
+      <c r="J269" s="6">
+        <v>302421</v>
+      </c>
+      <c r="K269" s="6">
+        <v>232736</v>
+      </c>
+      <c r="L269" s="6">
+        <v>284915</v>
+      </c>
+      <c r="M269" s="6">
+        <v>334020</v>
+      </c>
+      <c r="N269" s="6">
+        <v>279852</v>
+      </c>
+      <c r="O269" s="6">
+        <v>330941</v>
+      </c>
+      <c r="P269" s="6">
+        <v>351775</v>
+      </c>
+      <c r="Q269" s="6">
+        <v>176029</v>
+      </c>
+      <c r="R269" s="6">
+        <v>275628</v>
+      </c>
+      <c r="S269" s="6">
+        <v>257955</v>
+      </c>
+      <c r="T269" s="6">
+        <v>261424</v>
+      </c>
+      <c r="U269" s="6">
+        <v>353616</v>
+      </c>
+      <c r="V269" s="6">
+        <v>303091</v>
+      </c>
+      <c r="W269" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="270" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+      <c r="A270" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B270" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="C270" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D270" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E270" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="C269" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="D269" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E269" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F269" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="G269" s="6">
-        <v>28</v>
-      </c>
-      <c r="H269" s="6">
-        <v>27</v>
-      </c>
-      <c r="I269" s="6">
-        <v>26</v>
-      </c>
-      <c r="J269" s="6">
-        <v>25</v>
-      </c>
-      <c r="K269" s="6">
-        <v>24</v>
-      </c>
-      <c r="L269" s="6">
-        <v>23</v>
-      </c>
-      <c r="M269" s="6">
-        <v>22</v>
-      </c>
-      <c r="N269" s="6">
-        <v>22</v>
-      </c>
-      <c r="O269" s="6">
-        <v>22</v>
-      </c>
-      <c r="P269" s="6">
-        <v>21</v>
-      </c>
-      <c r="Q269" s="6">
-        <v>19</v>
-      </c>
-      <c r="R269" s="6">
-        <v>17</v>
-      </c>
-      <c r="S269" s="6">
-        <v>16</v>
-      </c>
-      <c r="T269" s="6">
-        <v>16</v>
-      </c>
-      <c r="U269" s="6">
-        <v>15</v>
-      </c>
-      <c r="V269" s="3"/>
-      <c r="W269" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="270" spans="1:23" ht="36" x14ac:dyDescent="0.25">
-      <c r="A270" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="B270" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="C270" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="D270" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E270" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="F270" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G270" s="4">
-        <v>64.7</v>
-      </c>
-      <c r="H270" s="4">
-        <v>65.7</v>
-      </c>
-      <c r="I270" s="4">
-        <v>68.599999999999994</v>
-      </c>
-      <c r="J270" s="4">
-        <v>70.3</v>
-      </c>
-      <c r="K270" s="4">
-        <v>71.5</v>
-      </c>
-      <c r="L270" s="4">
-        <v>72.7</v>
-      </c>
-      <c r="M270" s="4">
-        <v>73.5</v>
-      </c>
-      <c r="N270" s="4">
-        <v>73.599999999999994</v>
-      </c>
-      <c r="O270" s="4">
-        <v>74</v>
-      </c>
-      <c r="P270" s="4">
-        <v>74.5</v>
-      </c>
-      <c r="Q270" s="4">
-        <v>74.900000000000006</v>
-      </c>
-      <c r="R270" s="4">
-        <v>75.2</v>
-      </c>
-      <c r="S270" s="4">
-        <v>75.7</v>
-      </c>
-      <c r="T270" s="4">
-        <v>75.900000000000006</v>
-      </c>
-      <c r="U270" s="4">
-        <v>76.2</v>
-      </c>
-      <c r="V270" s="3"/>
+        <v>32</v>
+      </c>
+      <c r="G270" s="6">
+        <v>485152</v>
+      </c>
+      <c r="H270" s="6">
+        <v>474731</v>
+      </c>
+      <c r="I270" s="6">
+        <v>372768</v>
+      </c>
+      <c r="J270" s="6">
+        <v>301883</v>
+      </c>
+      <c r="K270" s="6">
+        <v>233889</v>
+      </c>
+      <c r="L270" s="6">
+        <v>285054</v>
+      </c>
+      <c r="M270" s="6">
+        <v>334120</v>
+      </c>
+      <c r="N270" s="6">
+        <v>279520</v>
+      </c>
+      <c r="O270" s="6">
+        <v>330602</v>
+      </c>
+      <c r="P270" s="6">
+        <v>351685</v>
+      </c>
+      <c r="Q270" s="6">
+        <v>175421</v>
+      </c>
+      <c r="R270" s="6">
+        <v>276413</v>
+      </c>
+      <c r="S270" s="6">
+        <v>262425</v>
+      </c>
+      <c r="T270" s="6">
+        <v>256157</v>
+      </c>
+      <c r="U270" s="6">
+        <v>346671</v>
+      </c>
+      <c r="V270" s="6">
+        <v>299556</v>
+      </c>
       <c r="W270" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="271" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>37</v>
+        <v>370</v>
       </c>
       <c r="E271" s="3" t="s">
-        <v>39</v>
+        <v>371</v>
       </c>
       <c r="F271" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G271" s="4">
-        <v>88</v>
-      </c>
-      <c r="H271" s="4">
-        <v>88.4</v>
-      </c>
-      <c r="I271" s="4">
-        <v>91.7</v>
-      </c>
-      <c r="J271" s="4">
-        <v>93.3</v>
-      </c>
-      <c r="K271" s="4">
-        <v>93.9</v>
-      </c>
-      <c r="L271" s="4">
-        <v>94.6</v>
-      </c>
-      <c r="M271" s="4">
-        <v>94.8</v>
-      </c>
-      <c r="N271" s="4">
-        <v>94.5</v>
-      </c>
-      <c r="O271" s="4">
-        <v>94.6</v>
-      </c>
-      <c r="P271" s="4">
-        <v>94.8</v>
-      </c>
-      <c r="Q271" s="4">
-        <v>94.7</v>
-      </c>
-      <c r="R271" s="4">
-        <v>94.6</v>
-      </c>
-      <c r="S271" s="4">
-        <v>95</v>
-      </c>
-      <c r="T271" s="4">
-        <v>94.8</v>
-      </c>
-      <c r="U271" s="4">
-        <v>94.6</v>
-      </c>
-      <c r="V271" s="3"/>
+        <v>32</v>
+      </c>
+      <c r="G271" s="6">
+        <v>759502</v>
+      </c>
+      <c r="H271" s="6">
+        <v>781353</v>
+      </c>
+      <c r="I271" s="6">
+        <v>802702</v>
+      </c>
+      <c r="J271" s="6">
+        <v>787070</v>
+      </c>
+      <c r="K271" s="6">
+        <v>875518</v>
+      </c>
+      <c r="L271" s="6">
+        <v>919666</v>
+      </c>
+      <c r="M271" s="6">
+        <v>962501</v>
+      </c>
+      <c r="N271" s="6">
+        <v>1011758</v>
+      </c>
+      <c r="O271" s="6">
+        <v>1029218</v>
+      </c>
+      <c r="P271" s="6">
+        <v>1057440</v>
+      </c>
+      <c r="Q271" s="6">
+        <v>780543</v>
+      </c>
+      <c r="R271" s="6">
+        <v>882463</v>
+      </c>
+      <c r="S271" s="6">
+        <v>885794</v>
+      </c>
+      <c r="T271" s="6">
+        <v>871811</v>
+      </c>
+      <c r="U271" s="6">
+        <v>872944</v>
+      </c>
+      <c r="V271" s="6">
+        <v>884918</v>
+      </c>
       <c r="W271" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="272" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="B272" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="C272" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="D272" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E272" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="C272" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="D272" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E272" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="F272" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G272" s="4">
-        <v>28.5</v>
-      </c>
-      <c r="H272" s="4">
-        <v>30.6</v>
-      </c>
-      <c r="I272" s="4">
-        <v>33.1</v>
-      </c>
-      <c r="J272" s="4">
-        <v>35.299999999999997</v>
-      </c>
-      <c r="K272" s="4">
-        <v>37.4</v>
-      </c>
-      <c r="L272" s="4">
-        <v>39.6</v>
-      </c>
-      <c r="M272" s="4">
-        <v>41.2</v>
-      </c>
-      <c r="N272" s="4">
-        <v>42</v>
-      </c>
-      <c r="O272" s="4">
-        <v>42.9</v>
-      </c>
-      <c r="P272" s="4">
-        <v>44</v>
-      </c>
-      <c r="Q272" s="4">
-        <v>45.4</v>
-      </c>
-      <c r="R272" s="4">
-        <v>46.5</v>
-      </c>
-      <c r="S272" s="4">
-        <v>47.2</v>
-      </c>
-      <c r="T272" s="4">
-        <v>48.2</v>
-      </c>
-      <c r="U272" s="4">
-        <v>49.3</v>
-      </c>
-      <c r="V272" s="3"/>
+        <v>32</v>
+      </c>
+      <c r="G272" s="6">
+        <v>781553</v>
+      </c>
+      <c r="H272" s="6">
+        <v>802785</v>
+      </c>
+      <c r="I272" s="6">
+        <v>809836</v>
+      </c>
+      <c r="J272" s="6">
+        <v>809712</v>
+      </c>
+      <c r="K272" s="6">
+        <v>878045</v>
+      </c>
+      <c r="L272" s="6">
+        <v>931632</v>
+      </c>
+      <c r="M272" s="6">
+        <v>970959</v>
+      </c>
+      <c r="N272" s="6">
+        <v>1013639</v>
+      </c>
+      <c r="O272" s="6">
+        <v>1029660</v>
+      </c>
+      <c r="P272" s="6">
+        <v>1026283</v>
+      </c>
+      <c r="Q272" s="6">
+        <v>773182</v>
+      </c>
+      <c r="R272" s="6">
+        <v>881969</v>
+      </c>
+      <c r="S272" s="6">
+        <v>929215</v>
+      </c>
+      <c r="T272" s="6">
+        <v>862113</v>
+      </c>
+      <c r="U272" s="6">
+        <v>853481</v>
+      </c>
+      <c r="V272" s="6">
+        <v>873943</v>
+      </c>
       <c r="W272" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="273" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D273" s="2" t="s">
         <v>27</v>
@@ -18968,67 +18984,67 @@
         <v>28</v>
       </c>
       <c r="F273" s="3" t="s">
-        <v>34</v>
+        <v>377</v>
       </c>
       <c r="G273" s="4">
-        <v>65.7</v>
+        <v>90.8</v>
       </c>
       <c r="H273" s="4">
-        <v>64.8</v>
+        <v>88.8</v>
       </c>
       <c r="I273" s="4">
-        <v>67.400000000000006</v>
+        <v>86.5</v>
       </c>
       <c r="J273" s="4">
-        <v>69.8</v>
+        <v>87</v>
       </c>
       <c r="K273" s="4">
-        <v>70.5</v>
+        <v>85</v>
       </c>
       <c r="L273" s="4">
-        <v>70.900000000000006</v>
+        <v>87.4</v>
       </c>
       <c r="M273" s="4">
-        <v>71.400000000000006</v>
+        <v>88.7</v>
       </c>
       <c r="N273" s="4">
-        <v>72.5</v>
+        <v>84.6</v>
       </c>
       <c r="O273" s="4">
-        <v>73.2</v>
+        <v>77.3</v>
       </c>
       <c r="P273" s="4">
-        <v>73.900000000000006</v>
+        <v>79.7</v>
       </c>
       <c r="Q273" s="4">
-        <v>73.3</v>
+        <v>81.900000000000006</v>
       </c>
       <c r="R273" s="4">
-        <v>72.8</v>
+        <v>74.8</v>
       </c>
       <c r="S273" s="4">
+        <v>77</v>
+      </c>
+      <c r="T273" s="4">
+        <v>77.2</v>
+      </c>
+      <c r="U273" s="4">
         <v>76.3</v>
-      </c>
-      <c r="T273" s="4">
-        <v>78.099999999999994</v>
-      </c>
-      <c r="U273" s="4">
-        <v>78.599999999999994</v>
       </c>
       <c r="V273" s="3"/>
       <c r="W273" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="274" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="274" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D274" s="2" t="s">
         <v>27</v>
@@ -19037,67 +19053,67 @@
         <v>28</v>
       </c>
       <c r="F274" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="G274" s="6">
-        <v>70108</v>
-      </c>
-      <c r="H274" s="6">
-        <v>248240</v>
-      </c>
-      <c r="I274" s="6">
-        <v>168221</v>
-      </c>
-      <c r="J274" s="6">
-        <v>72837</v>
-      </c>
-      <c r="K274" s="6">
-        <v>64283</v>
-      </c>
-      <c r="L274" s="6">
-        <v>68694</v>
-      </c>
-      <c r="M274" s="6">
-        <v>60135</v>
-      </c>
-      <c r="N274" s="6">
-        <v>46337</v>
-      </c>
-      <c r="O274" s="6">
-        <v>50289</v>
-      </c>
-      <c r="P274" s="6">
-        <v>104107</v>
-      </c>
-      <c r="Q274" s="6">
-        <v>201963</v>
-      </c>
-      <c r="R274" s="6">
-        <v>84506</v>
-      </c>
-      <c r="S274" s="6">
-        <v>295948</v>
-      </c>
-      <c r="T274" s="6">
-        <v>123796</v>
-      </c>
-      <c r="U274" s="6">
-        <v>104040</v>
+        <v>34</v>
+      </c>
+      <c r="G274" s="7">
+        <v>0.19600000000000001</v>
+      </c>
+      <c r="H274" s="7">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="I274" s="7">
+        <v>0.20599999999999999</v>
+      </c>
+      <c r="J274" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="K274" s="7">
+        <v>0.20100000000000001</v>
+      </c>
+      <c r="L274" s="7">
+        <v>0.20300000000000001</v>
+      </c>
+      <c r="M274" s="7">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="N274" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="O274" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="P274" s="7">
+        <v>0.19900000000000001</v>
+      </c>
+      <c r="Q274" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="R274" s="7">
+        <v>0.19900000000000001</v>
+      </c>
+      <c r="S274" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="T274" s="7">
+        <v>0.192</v>
+      </c>
+      <c r="U274" s="7">
+        <v>0.192</v>
       </c>
       <c r="V274" s="3"/>
       <c r="W274" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="275" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="275" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D275" s="2" t="s">
         <v>27</v>
@@ -19109,64 +19125,64 @@
         <v>34</v>
       </c>
       <c r="G275" s="4">
-        <v>2.9</v>
+        <v>30.5</v>
       </c>
       <c r="H275" s="4">
-        <v>3.8</v>
+        <v>30.5</v>
       </c>
       <c r="I275" s="4">
-        <v>6</v>
+        <v>30.6</v>
       </c>
       <c r="J275" s="4">
-        <v>4.3</v>
+        <v>30.6</v>
       </c>
       <c r="K275" s="4">
-        <v>4.5999999999999996</v>
+        <v>30.7</v>
       </c>
       <c r="L275" s="4">
-        <v>4.2</v>
+        <v>30.8</v>
       </c>
       <c r="M275" s="4">
-        <v>3.1</v>
+        <v>30.8</v>
       </c>
       <c r="N275" s="4">
-        <v>3</v>
+        <v>30.9</v>
       </c>
       <c r="O275" s="4">
-        <v>3.2</v>
+        <v>30.9</v>
       </c>
       <c r="P275" s="4">
-        <v>3.4</v>
+        <v>30.9</v>
       </c>
       <c r="Q275" s="4">
-        <v>3.2</v>
+        <v>30.9</v>
       </c>
       <c r="R275" s="4">
-        <v>4.5</v>
+        <v>30.9</v>
       </c>
       <c r="S275" s="4">
-        <v>6.6</v>
+        <v>31</v>
       </c>
       <c r="T275" s="4">
-        <v>5.8</v>
+        <v>31</v>
       </c>
       <c r="U275" s="4">
-        <v>4.5</v>
+        <v>31</v>
       </c>
       <c r="V275" s="3"/>
       <c r="W275" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="276" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D276" s="2" t="s">
         <v>27</v>
@@ -19175,72 +19191,70 @@
         <v>28</v>
       </c>
       <c r="F276" s="3" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="G276" s="6">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="H276" s="6">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="I276" s="6">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="J276" s="6">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="K276" s="6">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="L276" s="6">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="M276" s="6">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="N276" s="6">
-        <v>89</v>
+        <v>22</v>
       </c>
       <c r="O276" s="6">
-        <v>86</v>
+        <v>22</v>
       </c>
       <c r="P276" s="6">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="Q276" s="6">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="R276" s="6">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="S276" s="6">
-        <v>83</v>
+        <v>16</v>
       </c>
       <c r="T276" s="6">
-        <v>88</v>
+        <v>16</v>
       </c>
       <c r="U276" s="6">
-        <v>88</v>
-      </c>
-      <c r="V276" s="6">
-        <v>86</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="V276" s="3"/>
       <c r="W276" s="2" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="277" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="277" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C277" s="2" t="s">
         <v>384</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E277" s="3" t="s">
         <v>28</v>
@@ -19248,163 +19262,203 @@
       <c r="F277" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G277" s="6">
-        <v>55</v>
-      </c>
-      <c r="H277" s="3"/>
-      <c r="I277" s="6">
-        <v>58</v>
-      </c>
-      <c r="J277" s="3"/>
-      <c r="K277" s="6">
-        <v>60</v>
-      </c>
-      <c r="L277" s="3"/>
-      <c r="M277" s="6">
-        <v>64</v>
-      </c>
-      <c r="N277" s="3"/>
-      <c r="O277" s="6">
-        <v>65</v>
-      </c>
-      <c r="P277" s="3"/>
-      <c r="Q277" s="6">
+      <c r="G277" s="4">
+        <v>64.7</v>
+      </c>
+      <c r="H277" s="4">
+        <v>65.7</v>
+      </c>
+      <c r="I277" s="4">
+        <v>68.599999999999994</v>
+      </c>
+      <c r="J277" s="4">
+        <v>70.3</v>
+      </c>
+      <c r="K277" s="4">
+        <v>71.5</v>
+      </c>
+      <c r="L277" s="4">
+        <v>72.7</v>
+      </c>
+      <c r="M277" s="4">
+        <v>73.5</v>
+      </c>
+      <c r="N277" s="4">
+        <v>73.599999999999994</v>
+      </c>
+      <c r="O277" s="4">
         <v>74</v>
       </c>
-      <c r="R277" s="3"/>
-      <c r="S277" s="6">
-        <v>63</v>
-      </c>
-      <c r="T277" s="3"/>
-      <c r="U277" s="6">
-        <v>71</v>
+      <c r="P277" s="4">
+        <v>74.5</v>
+      </c>
+      <c r="Q277" s="4">
+        <v>74.900000000000006</v>
+      </c>
+      <c r="R277" s="4">
+        <v>75.2</v>
+      </c>
+      <c r="S277" s="4">
+        <v>75.7</v>
+      </c>
+      <c r="T277" s="4">
+        <v>75.900000000000006</v>
+      </c>
+      <c r="U277" s="4">
+        <v>76.2</v>
       </c>
       <c r="V277" s="3"/>
       <c r="W277" s="2" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="278" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="278" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E278" s="3" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F278" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G278" s="3"/>
-      <c r="H278" s="3"/>
-      <c r="I278" s="3"/>
-      <c r="J278" s="3"/>
-      <c r="K278" s="3"/>
-      <c r="L278" s="3"/>
-      <c r="M278" s="3"/>
-      <c r="N278" s="3"/>
-      <c r="O278" s="3"/>
-      <c r="P278" s="3"/>
-      <c r="Q278" s="3"/>
-      <c r="R278" s="3"/>
-      <c r="S278" s="5">
-        <v>33109.31</v>
-      </c>
-      <c r="T278" s="5">
-        <v>33829.39</v>
-      </c>
-      <c r="U278" s="3"/>
+        <v>34</v>
+      </c>
+      <c r="G278" s="4">
+        <v>88</v>
+      </c>
+      <c r="H278" s="4">
+        <v>88.4</v>
+      </c>
+      <c r="I278" s="4">
+        <v>91.7</v>
+      </c>
+      <c r="J278" s="4">
+        <v>93.3</v>
+      </c>
+      <c r="K278" s="4">
+        <v>93.9</v>
+      </c>
+      <c r="L278" s="4">
+        <v>94.6</v>
+      </c>
+      <c r="M278" s="4">
+        <v>94.8</v>
+      </c>
+      <c r="N278" s="4">
+        <v>94.5</v>
+      </c>
+      <c r="O278" s="4">
+        <v>94.6</v>
+      </c>
+      <c r="P278" s="4">
+        <v>94.8</v>
+      </c>
+      <c r="Q278" s="4">
+        <v>94.7</v>
+      </c>
+      <c r="R278" s="4">
+        <v>94.6</v>
+      </c>
+      <c r="S278" s="4">
+        <v>95</v>
+      </c>
+      <c r="T278" s="4">
+        <v>94.8</v>
+      </c>
+      <c r="U278" s="4">
+        <v>94.6</v>
+      </c>
       <c r="V278" s="3"/>
       <c r="W278" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="279" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="279" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E279" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="F279" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="G279" s="5">
-        <v>1.02</v>
-      </c>
-      <c r="H279" s="5">
-        <v>0.96</v>
-      </c>
-      <c r="I279" s="5">
-        <v>1</v>
-      </c>
-      <c r="J279" s="5">
-        <v>1.05</v>
-      </c>
-      <c r="K279" s="5">
-        <v>1.06</v>
-      </c>
-      <c r="L279" s="5">
-        <v>0.95</v>
-      </c>
-      <c r="M279" s="5">
-        <v>0.91</v>
-      </c>
-      <c r="N279" s="5">
-        <v>0.81</v>
-      </c>
-      <c r="O279" s="5">
-        <v>0.87</v>
-      </c>
-      <c r="P279" s="5">
-        <v>1.01</v>
-      </c>
-      <c r="Q279" s="5">
-        <v>0.85</v>
-      </c>
-      <c r="R279" s="5">
-        <v>0.83</v>
-      </c>
-      <c r="S279" s="5">
-        <v>0.72</v>
-      </c>
-      <c r="T279" s="5">
-        <v>0.78</v>
-      </c>
-      <c r="U279" s="5">
-        <v>0.69</v>
+        <v>34</v>
+      </c>
+      <c r="G279" s="4">
+        <v>28.5</v>
+      </c>
+      <c r="H279" s="4">
+        <v>30.6</v>
+      </c>
+      <c r="I279" s="4">
+        <v>33.1</v>
+      </c>
+      <c r="J279" s="4">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="K279" s="4">
+        <v>37.4</v>
+      </c>
+      <c r="L279" s="4">
+        <v>39.6</v>
+      </c>
+      <c r="M279" s="4">
+        <v>41.2</v>
+      </c>
+      <c r="N279" s="4">
+        <v>42</v>
+      </c>
+      <c r="O279" s="4">
+        <v>42.9</v>
+      </c>
+      <c r="P279" s="4">
+        <v>44</v>
+      </c>
+      <c r="Q279" s="4">
+        <v>45.4</v>
+      </c>
+      <c r="R279" s="4">
+        <v>46.5</v>
+      </c>
+      <c r="S279" s="4">
+        <v>47.2</v>
+      </c>
+      <c r="T279" s="4">
+        <v>48.2</v>
+      </c>
+      <c r="U279" s="4">
+        <v>49.3</v>
       </c>
       <c r="V279" s="3"/>
       <c r="W279" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="280" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="280" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="D280" s="2" t="s">
         <v>27</v>
@@ -19415,65 +19469,65 @@
       <c r="F280" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G280" s="5">
-        <v>1.84</v>
-      </c>
-      <c r="H280" s="5">
-        <v>1.79</v>
-      </c>
-      <c r="I280" s="5">
-        <v>1.8</v>
-      </c>
-      <c r="J280" s="5">
-        <v>1.79</v>
-      </c>
-      <c r="K280" s="5">
-        <v>1.86</v>
-      </c>
-      <c r="L280" s="5">
-        <v>2.21</v>
-      </c>
-      <c r="M280" s="5">
-        <v>1.99</v>
-      </c>
-      <c r="N280" s="5">
-        <v>1.88</v>
-      </c>
-      <c r="O280" s="5">
-        <v>2</v>
-      </c>
-      <c r="P280" s="5">
-        <v>1.96</v>
-      </c>
-      <c r="Q280" s="5">
-        <v>2.21</v>
-      </c>
-      <c r="R280" s="5">
-        <v>2.19</v>
-      </c>
-      <c r="S280" s="5">
-        <v>2.21</v>
-      </c>
-      <c r="T280" s="5">
-        <v>3.27</v>
-      </c>
-      <c r="U280" s="5">
-        <v>4.07</v>
+      <c r="G280" s="4">
+        <v>65.7</v>
+      </c>
+      <c r="H280" s="4">
+        <v>64.8</v>
+      </c>
+      <c r="I280" s="4">
+        <v>67.400000000000006</v>
+      </c>
+      <c r="J280" s="4">
+        <v>69.8</v>
+      </c>
+      <c r="K280" s="4">
+        <v>70.5</v>
+      </c>
+      <c r="L280" s="4">
+        <v>70.900000000000006</v>
+      </c>
+      <c r="M280" s="4">
+        <v>71.400000000000006</v>
+      </c>
+      <c r="N280" s="4">
+        <v>72.5</v>
+      </c>
+      <c r="O280" s="4">
+        <v>73.2</v>
+      </c>
+      <c r="P280" s="4">
+        <v>73.900000000000006</v>
+      </c>
+      <c r="Q280" s="4">
+        <v>73.3</v>
+      </c>
+      <c r="R280" s="4">
+        <v>72.8</v>
+      </c>
+      <c r="S280" s="4">
+        <v>76.3</v>
+      </c>
+      <c r="T280" s="4">
+        <v>78.099999999999994</v>
+      </c>
+      <c r="U280" s="4">
+        <v>78.599999999999994</v>
       </c>
       <c r="V280" s="3"/>
       <c r="W280" s="2" t="s">
-        <v>390</v>
+        <v>30</v>
       </c>
     </row>
     <row r="281" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="D281" s="2" t="s">
         <v>27</v>
@@ -19482,44 +19536,70 @@
         <v>28</v>
       </c>
       <c r="F281" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G281" s="3"/>
-      <c r="H281" s="3"/>
-      <c r="I281" s="3"/>
-      <c r="J281" s="3"/>
-      <c r="K281" s="3"/>
-      <c r="L281" s="3"/>
-      <c r="M281" s="3"/>
-      <c r="N281" s="3"/>
-      <c r="O281" s="3"/>
-      <c r="P281" s="3"/>
-      <c r="Q281" s="3"/>
-      <c r="R281" s="3"/>
-      <c r="S281" s="3"/>
-      <c r="T281" s="3"/>
-      <c r="U281" s="4">
-        <v>30.2</v>
-      </c>
-      <c r="V281" s="4">
-        <v>51.3</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="G281" s="6">
+        <v>70108</v>
+      </c>
+      <c r="H281" s="6">
+        <v>248240</v>
+      </c>
+      <c r="I281" s="6">
+        <v>168221</v>
+      </c>
+      <c r="J281" s="6">
+        <v>72837</v>
+      </c>
+      <c r="K281" s="6">
+        <v>64283</v>
+      </c>
+      <c r="L281" s="6">
+        <v>68694</v>
+      </c>
+      <c r="M281" s="6">
+        <v>60135</v>
+      </c>
+      <c r="N281" s="6">
+        <v>46337</v>
+      </c>
+      <c r="O281" s="6">
+        <v>50289</v>
+      </c>
+      <c r="P281" s="6">
+        <v>104107</v>
+      </c>
+      <c r="Q281" s="6">
+        <v>201963</v>
+      </c>
+      <c r="R281" s="6">
+        <v>84506</v>
+      </c>
+      <c r="S281" s="6">
+        <v>295948</v>
+      </c>
+      <c r="T281" s="6">
+        <v>123796</v>
+      </c>
+      <c r="U281" s="6">
+        <v>104040</v>
+      </c>
+      <c r="V281" s="3"/>
       <c r="W281" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="282" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="E282" s="3" t="s">
         <v>28</v>
@@ -19528,478 +19608,400 @@
         <v>34</v>
       </c>
       <c r="G282" s="4">
-        <v>28.1</v>
+        <v>2.9</v>
       </c>
       <c r="H282" s="4">
-        <v>27.6</v>
+        <v>3.8</v>
       </c>
       <c r="I282" s="4">
-        <v>31.6</v>
+        <v>6</v>
       </c>
       <c r="J282" s="4">
-        <v>22.6</v>
+        <v>4.3</v>
       </c>
       <c r="K282" s="4">
-        <v>26.9</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L282" s="4">
-        <v>26.6</v>
+        <v>4.2</v>
       </c>
       <c r="M282" s="4">
-        <v>30.2</v>
+        <v>3.1</v>
       </c>
       <c r="N282" s="4">
-        <v>30.8</v>
+        <v>3</v>
       </c>
       <c r="O282" s="4">
-        <v>35.5</v>
+        <v>3.2</v>
       </c>
       <c r="P282" s="4">
-        <v>40.4</v>
+        <v>3.4</v>
       </c>
       <c r="Q282" s="4">
-        <v>41.9</v>
+        <v>3.2</v>
       </c>
       <c r="R282" s="4">
-        <v>47.5</v>
+        <v>4.5</v>
       </c>
       <c r="S282" s="4">
-        <v>55.4</v>
+        <v>6.6</v>
       </c>
       <c r="T282" s="4">
-        <v>58.5</v>
+        <v>5.8</v>
       </c>
       <c r="U282" s="4">
-        <v>61</v>
-      </c>
-      <c r="V282" s="4">
-        <v>61.1</v>
-      </c>
+        <v>4.5</v>
+      </c>
+      <c r="V282" s="3"/>
       <c r="W282" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="283" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="B283" s="2" t="s">
         <v>391</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="E283" s="3" t="s">
-        <v>394</v>
+        <v>28</v>
       </c>
       <c r="F283" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G283" s="4">
-        <v>31.5</v>
-      </c>
-      <c r="H283" s="4">
-        <v>27.9</v>
-      </c>
-      <c r="I283" s="4">
-        <v>36.799999999999997</v>
-      </c>
-      <c r="J283" s="4">
-        <v>20.2</v>
-      </c>
-      <c r="K283" s="4">
-        <v>23.9</v>
-      </c>
-      <c r="L283" s="4">
-        <v>20.8</v>
-      </c>
-      <c r="M283" s="4">
-        <v>20.5</v>
-      </c>
-      <c r="N283" s="4">
-        <v>22.4</v>
-      </c>
-      <c r="O283" s="4">
-        <v>29.5</v>
-      </c>
-      <c r="P283" s="4">
-        <v>29.8</v>
-      </c>
-      <c r="Q283" s="4">
-        <v>30.9</v>
-      </c>
-      <c r="R283" s="4">
-        <v>35.6</v>
-      </c>
-      <c r="S283" s="4">
-        <v>42.1</v>
-      </c>
-      <c r="T283" s="4">
-        <v>44</v>
-      </c>
-      <c r="U283" s="4">
-        <v>47.7</v>
-      </c>
-      <c r="V283" s="4">
-        <v>48.9</v>
+      <c r="G283" s="6">
+        <v>70</v>
+      </c>
+      <c r="H283" s="6">
+        <v>75</v>
+      </c>
+      <c r="I283" s="6">
+        <v>66</v>
+      </c>
+      <c r="J283" s="6">
+        <v>64</v>
+      </c>
+      <c r="K283" s="6">
+        <v>70</v>
+      </c>
+      <c r="L283" s="6">
+        <v>66</v>
+      </c>
+      <c r="M283" s="6">
+        <v>80</v>
+      </c>
+      <c r="N283" s="6">
+        <v>89</v>
+      </c>
+      <c r="O283" s="6">
+        <v>86</v>
+      </c>
+      <c r="P283" s="6">
+        <v>89</v>
+      </c>
+      <c r="Q283" s="6">
+        <v>85</v>
+      </c>
+      <c r="R283" s="6">
+        <v>82</v>
+      </c>
+      <c r="S283" s="6">
+        <v>83</v>
+      </c>
+      <c r="T283" s="6">
+        <v>88</v>
+      </c>
+      <c r="U283" s="6">
+        <v>88</v>
+      </c>
+      <c r="V283" s="6">
+        <v>86</v>
       </c>
       <c r="W283" s="2" t="s">
-        <v>30</v>
+        <v>393</v>
       </c>
     </row>
     <row r="284" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="B284" s="2" t="s">
         <v>391</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="E284" s="3" t="s">
-        <v>395</v>
+        <v>28</v>
       </c>
       <c r="F284" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G284" s="4">
-        <v>47.6</v>
-      </c>
-      <c r="H284" s="4">
-        <v>46.2</v>
-      </c>
-      <c r="I284" s="4">
-        <v>50.6</v>
-      </c>
-      <c r="J284" s="4">
-        <v>39</v>
-      </c>
-      <c r="K284" s="4">
-        <v>46</v>
-      </c>
-      <c r="L284" s="4">
-        <v>45</v>
-      </c>
-      <c r="M284" s="4">
-        <v>48.1</v>
-      </c>
-      <c r="N284" s="4">
-        <v>48.1</v>
-      </c>
-      <c r="O284" s="4">
-        <v>53</v>
-      </c>
-      <c r="P284" s="4">
-        <v>58.6</v>
-      </c>
-      <c r="Q284" s="4">
-        <v>59.9</v>
-      </c>
-      <c r="R284" s="4">
-        <v>68.3</v>
-      </c>
-      <c r="S284" s="4">
-        <v>75.2</v>
-      </c>
-      <c r="T284" s="4">
-        <v>81</v>
-      </c>
-      <c r="U284" s="4">
-        <v>81.2</v>
-      </c>
-      <c r="V284" s="4">
-        <v>81.8</v>
-      </c>
+      <c r="G284" s="6">
+        <v>55</v>
+      </c>
+      <c r="H284" s="3"/>
+      <c r="I284" s="6">
+        <v>58</v>
+      </c>
+      <c r="J284" s="3"/>
+      <c r="K284" s="6">
+        <v>60</v>
+      </c>
+      <c r="L284" s="3"/>
+      <c r="M284" s="6">
+        <v>64</v>
+      </c>
+      <c r="N284" s="3"/>
+      <c r="O284" s="6">
+        <v>65</v>
+      </c>
+      <c r="P284" s="3"/>
+      <c r="Q284" s="6">
+        <v>74</v>
+      </c>
+      <c r="R284" s="3"/>
+      <c r="S284" s="6">
+        <v>63</v>
+      </c>
+      <c r="T284" s="3"/>
+      <c r="U284" s="6">
+        <v>71</v>
+      </c>
+      <c r="V284" s="3"/>
       <c r="W284" s="2" t="s">
-        <v>30</v>
+        <v>393</v>
       </c>
     </row>
     <row r="285" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="B285" s="2" t="s">
         <v>391</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D285" s="2" t="s">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="E285" s="3" t="s">
-        <v>396</v>
+        <v>28</v>
       </c>
       <c r="F285" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G285" s="4">
-        <v>37.6</v>
-      </c>
-      <c r="H285" s="4">
-        <v>36.9</v>
-      </c>
-      <c r="I285" s="4">
-        <v>45.3</v>
-      </c>
-      <c r="J285" s="4">
-        <v>35.200000000000003</v>
-      </c>
-      <c r="K285" s="4">
-        <v>40.1</v>
-      </c>
-      <c r="L285" s="4">
-        <v>38.6</v>
-      </c>
-      <c r="M285" s="4">
-        <v>40.5</v>
-      </c>
-      <c r="N285" s="4">
-        <v>45</v>
-      </c>
-      <c r="O285" s="4">
-        <v>49.6</v>
-      </c>
-      <c r="P285" s="4">
-        <v>57.6</v>
-      </c>
-      <c r="Q285" s="4">
-        <v>59.4</v>
-      </c>
-      <c r="R285" s="4">
-        <v>65.900000000000006</v>
-      </c>
-      <c r="S285" s="4">
-        <v>75.599999999999994</v>
-      </c>
-      <c r="T285" s="4">
-        <v>78.3</v>
-      </c>
-      <c r="U285" s="4">
-        <v>81.099999999999994</v>
-      </c>
-      <c r="V285" s="4">
-        <v>78.3</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="G285" s="3"/>
+      <c r="H285" s="3"/>
+      <c r="I285" s="3"/>
+      <c r="J285" s="3"/>
+      <c r="K285" s="3"/>
+      <c r="L285" s="3"/>
+      <c r="M285" s="3"/>
+      <c r="N285" s="3"/>
+      <c r="O285" s="3"/>
+      <c r="P285" s="3"/>
+      <c r="Q285" s="3"/>
+      <c r="R285" s="3"/>
+      <c r="S285" s="5">
+        <v>33109.31</v>
+      </c>
+      <c r="T285" s="5">
+        <v>33829.39</v>
+      </c>
+      <c r="U285" s="3"/>
+      <c r="V285" s="3"/>
       <c r="W285" s="2" t="s">
-        <v>30</v>
+        <v>87</v>
       </c>
     </row>
     <row r="286" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="E286" s="3" t="s">
-        <v>397</v>
+        <v>28</v>
       </c>
       <c r="F286" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G286" s="4">
-        <v>26.2</v>
-      </c>
-      <c r="H286" s="4">
-        <v>26.3</v>
-      </c>
-      <c r="I286" s="4">
-        <v>28.7</v>
-      </c>
-      <c r="J286" s="4">
-        <v>21.5</v>
-      </c>
-      <c r="K286" s="4">
-        <v>26.2</v>
-      </c>
-      <c r="L286" s="4">
-        <v>26</v>
-      </c>
-      <c r="M286" s="4">
-        <v>30</v>
-      </c>
-      <c r="N286" s="4">
-        <v>28</v>
-      </c>
-      <c r="O286" s="4">
-        <v>35</v>
-      </c>
-      <c r="P286" s="4">
-        <v>41.4</v>
-      </c>
-      <c r="Q286" s="4">
-        <v>45.1</v>
-      </c>
-      <c r="R286" s="4">
-        <v>51.7</v>
-      </c>
-      <c r="S286" s="4">
-        <v>62.4</v>
-      </c>
-      <c r="T286" s="4">
-        <v>65.7</v>
-      </c>
-      <c r="U286" s="4">
-        <v>68.8</v>
-      </c>
-      <c r="V286" s="4">
-        <v>69.900000000000006</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="G286" s="5">
+        <v>1.02</v>
+      </c>
+      <c r="H286" s="5">
+        <v>0.96</v>
+      </c>
+      <c r="I286" s="5">
+        <v>1</v>
+      </c>
+      <c r="J286" s="5">
+        <v>1.05</v>
+      </c>
+      <c r="K286" s="5">
+        <v>1.06</v>
+      </c>
+      <c r="L286" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="M286" s="5">
+        <v>0.91</v>
+      </c>
+      <c r="N286" s="5">
+        <v>0.81</v>
+      </c>
+      <c r="O286" s="5">
+        <v>0.87</v>
+      </c>
+      <c r="P286" s="5">
+        <v>1.01</v>
+      </c>
+      <c r="Q286" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="R286" s="5">
+        <v>0.83</v>
+      </c>
+      <c r="S286" s="5">
+        <v>0.72</v>
+      </c>
+      <c r="T286" s="5">
+        <v>0.78</v>
+      </c>
+      <c r="U286" s="5">
+        <v>0.69</v>
+      </c>
+      <c r="V286" s="3"/>
       <c r="W286" s="2" t="s">
-        <v>30</v>
+        <v>206</v>
       </c>
     </row>
     <row r="287" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="E287" s="3" t="s">
-        <v>398</v>
+        <v>28</v>
       </c>
       <c r="F287" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G287" s="4">
-        <v>13.5</v>
-      </c>
-      <c r="H287" s="4">
-        <v>15.7</v>
-      </c>
-      <c r="I287" s="4">
-        <v>17.2</v>
-      </c>
-      <c r="J287" s="4">
-        <v>12.7</v>
-      </c>
-      <c r="K287" s="4">
-        <v>15.5</v>
-      </c>
-      <c r="L287" s="4">
-        <v>18.3</v>
-      </c>
-      <c r="M287" s="4">
-        <v>19.8</v>
-      </c>
-      <c r="N287" s="4">
-        <v>18.8</v>
-      </c>
-      <c r="O287" s="4">
-        <v>22.4</v>
-      </c>
-      <c r="P287" s="4">
-        <v>28.5</v>
-      </c>
-      <c r="Q287" s="4">
-        <v>29.4</v>
-      </c>
-      <c r="R287" s="4">
-        <v>35</v>
-      </c>
-      <c r="S287" s="4">
-        <v>39.5</v>
-      </c>
-      <c r="T287" s="4">
-        <v>44.4</v>
-      </c>
-      <c r="U287" s="4">
-        <v>50.8</v>
-      </c>
-      <c r="V287" s="4">
-        <v>51.4</v>
-      </c>
+      <c r="G287" s="5">
+        <v>1.84</v>
+      </c>
+      <c r="H287" s="5">
+        <v>1.79</v>
+      </c>
+      <c r="I287" s="5">
+        <v>1.8</v>
+      </c>
+      <c r="J287" s="5">
+        <v>1.79</v>
+      </c>
+      <c r="K287" s="5">
+        <v>1.86</v>
+      </c>
+      <c r="L287" s="5">
+        <v>2.21</v>
+      </c>
+      <c r="M287" s="5">
+        <v>1.99</v>
+      </c>
+      <c r="N287" s="5">
+        <v>1.88</v>
+      </c>
+      <c r="O287" s="5">
+        <v>2</v>
+      </c>
+      <c r="P287" s="5">
+        <v>1.96</v>
+      </c>
+      <c r="Q287" s="5">
+        <v>2.21</v>
+      </c>
+      <c r="R287" s="5">
+        <v>2.19</v>
+      </c>
+      <c r="S287" s="5">
+        <v>2.21</v>
+      </c>
+      <c r="T287" s="5">
+        <v>3.27</v>
+      </c>
+      <c r="U287" s="5">
+        <v>4.07</v>
+      </c>
+      <c r="V287" s="3"/>
       <c r="W287" s="2" t="s">
-        <v>30</v>
+        <v>400</v>
       </c>
     </row>
     <row r="288" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="E288" s="3" t="s">
-        <v>399</v>
+        <v>28</v>
       </c>
       <c r="F288" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G288" s="4">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="H288" s="4">
-        <v>5</v>
-      </c>
-      <c r="I288" s="4">
-        <v>6.8</v>
-      </c>
-      <c r="J288" s="4">
-        <v>3.7</v>
-      </c>
-      <c r="K288" s="4">
-        <v>6.6</v>
-      </c>
-      <c r="L288" s="4">
-        <v>6</v>
-      </c>
-      <c r="M288" s="4">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="N288" s="4">
-        <v>8.4</v>
-      </c>
-      <c r="O288" s="4">
-        <v>10.9</v>
-      </c>
-      <c r="P288" s="4">
-        <v>12.2</v>
-      </c>
-      <c r="Q288" s="4">
-        <v>13.5</v>
-      </c>
-      <c r="R288" s="4">
-        <v>15.8</v>
-      </c>
-      <c r="S288" s="4">
-        <v>23.6</v>
-      </c>
-      <c r="T288" s="4">
-        <v>26.1</v>
-      </c>
+      <c r="G288" s="3"/>
+      <c r="H288" s="3"/>
+      <c r="I288" s="3"/>
+      <c r="J288" s="3"/>
+      <c r="K288" s="3"/>
+      <c r="L288" s="3"/>
+      <c r="M288" s="3"/>
+      <c r="N288" s="3"/>
+      <c r="O288" s="3"/>
+      <c r="P288" s="3"/>
+      <c r="Q288" s="3"/>
+      <c r="R288" s="3"/>
+      <c r="S288" s="3"/>
+      <c r="T288" s="3"/>
       <c r="U288" s="4">
-        <v>27.4</v>
+        <v>30.2</v>
       </c>
       <c r="V288" s="4">
-        <v>27.6</v>
+        <v>51.3</v>
       </c>
       <c r="W288" s="2" t="s">
         <v>30</v>
@@ -20007,16 +20009,16 @@
     </row>
     <row r="289" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="E289" s="3" t="s">
         <v>28</v>
@@ -20025,454 +20027,492 @@
         <v>34</v>
       </c>
       <c r="G289" s="4">
-        <v>5.7</v>
+        <v>28.1</v>
       </c>
       <c r="H289" s="4">
-        <v>6</v>
+        <v>27.6</v>
       </c>
       <c r="I289" s="4">
-        <v>4.9000000000000004</v>
+        <v>31.6</v>
       </c>
       <c r="J289" s="4">
-        <v>4.3</v>
+        <v>22.6</v>
       </c>
       <c r="K289" s="4">
-        <v>4.7</v>
+        <v>26.9</v>
       </c>
       <c r="L289" s="4">
-        <v>4.5</v>
+        <v>26.6</v>
       </c>
       <c r="M289" s="4">
-        <v>3.3</v>
+        <v>30.2</v>
       </c>
       <c r="N289" s="4">
-        <v>3.8</v>
+        <v>30.8</v>
       </c>
       <c r="O289" s="4">
-        <v>4.5999999999999996</v>
+        <v>35.5</v>
       </c>
       <c r="P289" s="4">
-        <v>4.3</v>
+        <v>40.4</v>
       </c>
       <c r="Q289" s="4">
-        <v>4.4000000000000004</v>
+        <v>41.9</v>
       </c>
       <c r="R289" s="4">
-        <v>4.0999999999999996</v>
+        <v>47.5</v>
       </c>
       <c r="S289" s="4">
-        <v>3.8</v>
+        <v>55.4</v>
       </c>
       <c r="T289" s="4">
-        <v>5.0999999999999996</v>
+        <v>58.5</v>
       </c>
       <c r="U289" s="4">
-        <v>4.8</v>
+        <v>61</v>
       </c>
       <c r="V289" s="4">
-        <v>5.2</v>
+        <v>61.1</v>
       </c>
       <c r="W289" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="290" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C290" s="2" t="s">
         <v>403</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="E290" s="3" t="s">
-        <v>28</v>
+        <v>404</v>
       </c>
       <c r="F290" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G290" s="6">
-        <v>674</v>
-      </c>
-      <c r="H290" s="6">
-        <v>605</v>
-      </c>
-      <c r="I290" s="6">
-        <v>1082</v>
-      </c>
-      <c r="J290" s="6">
-        <v>1219</v>
-      </c>
-      <c r="K290" s="6">
-        <v>1282</v>
-      </c>
-      <c r="L290" s="6">
-        <v>1456</v>
-      </c>
-      <c r="M290" s="6">
-        <v>1926</v>
-      </c>
-      <c r="N290" s="6">
-        <v>3182</v>
-      </c>
-      <c r="O290" s="6">
-        <v>3739</v>
-      </c>
-      <c r="P290" s="6">
-        <v>6484</v>
-      </c>
-      <c r="Q290" s="6">
-        <v>10420</v>
-      </c>
-      <c r="R290" s="6">
-        <v>29483</v>
-      </c>
-      <c r="S290" s="6">
-        <v>39683</v>
-      </c>
-      <c r="T290" s="6">
-        <v>80267</v>
-      </c>
-      <c r="U290" s="6">
-        <v>103449</v>
-      </c>
-      <c r="V290" s="6">
-        <v>260783</v>
+        <v>34</v>
+      </c>
+      <c r="G290" s="4">
+        <v>31.5</v>
+      </c>
+      <c r="H290" s="4">
+        <v>27.9</v>
+      </c>
+      <c r="I290" s="4">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="J290" s="4">
+        <v>20.2</v>
+      </c>
+      <c r="K290" s="4">
+        <v>23.9</v>
+      </c>
+      <c r="L290" s="4">
+        <v>20.8</v>
+      </c>
+      <c r="M290" s="4">
+        <v>20.5</v>
+      </c>
+      <c r="N290" s="4">
+        <v>22.4</v>
+      </c>
+      <c r="O290" s="4">
+        <v>29.5</v>
+      </c>
+      <c r="P290" s="4">
+        <v>29.8</v>
+      </c>
+      <c r="Q290" s="4">
+        <v>30.9</v>
+      </c>
+      <c r="R290" s="4">
+        <v>35.6</v>
+      </c>
+      <c r="S290" s="4">
+        <v>42.1</v>
+      </c>
+      <c r="T290" s="4">
+        <v>44</v>
+      </c>
+      <c r="U290" s="4">
+        <v>47.7</v>
+      </c>
+      <c r="V290" s="4">
+        <v>48.9</v>
       </c>
       <c r="W290" s="2" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="291" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="291" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C291" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="D291" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E291" s="3" t="s">
         <v>405</v>
-      </c>
-      <c r="D291" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E291" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="F291" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G291" s="3"/>
-      <c r="H291" s="3"/>
-      <c r="I291" s="3"/>
-      <c r="J291" s="3"/>
-      <c r="K291" s="3"/>
-      <c r="L291" s="3"/>
-      <c r="M291" s="3"/>
-      <c r="N291" s="3"/>
-      <c r="O291" s="3"/>
-      <c r="P291" s="3"/>
-      <c r="Q291" s="3"/>
-      <c r="R291" s="5">
-        <v>18.93</v>
-      </c>
-      <c r="S291" s="3"/>
-      <c r="T291" s="5">
-        <v>21.3</v>
-      </c>
-      <c r="U291" s="3"/>
-      <c r="V291" s="5">
-        <v>23.01</v>
+      <c r="G291" s="4">
+        <v>47.6</v>
+      </c>
+      <c r="H291" s="4">
+        <v>46.2</v>
+      </c>
+      <c r="I291" s="4">
+        <v>50.6</v>
+      </c>
+      <c r="J291" s="4">
+        <v>39</v>
+      </c>
+      <c r="K291" s="4">
+        <v>46</v>
+      </c>
+      <c r="L291" s="4">
+        <v>45</v>
+      </c>
+      <c r="M291" s="4">
+        <v>48.1</v>
+      </c>
+      <c r="N291" s="4">
+        <v>48.1</v>
+      </c>
+      <c r="O291" s="4">
+        <v>53</v>
+      </c>
+      <c r="P291" s="4">
+        <v>58.6</v>
+      </c>
+      <c r="Q291" s="4">
+        <v>59.9</v>
+      </c>
+      <c r="R291" s="4">
+        <v>68.3</v>
+      </c>
+      <c r="S291" s="4">
+        <v>75.2</v>
+      </c>
+      <c r="T291" s="4">
+        <v>81</v>
+      </c>
+      <c r="U291" s="4">
+        <v>81.2</v>
+      </c>
+      <c r="V291" s="4">
+        <v>81.8</v>
       </c>
       <c r="W291" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="292" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="292" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B292" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="C292" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="D292" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E292" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="B292" s="2" t="s">
+      <c r="F292" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G292" s="4">
+        <v>37.6</v>
+      </c>
+      <c r="H292" s="4">
+        <v>36.9</v>
+      </c>
+      <c r="I292" s="4">
+        <v>45.3</v>
+      </c>
+      <c r="J292" s="4">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="K292" s="4">
+        <v>40.1</v>
+      </c>
+      <c r="L292" s="4">
+        <v>38.6</v>
+      </c>
+      <c r="M292" s="4">
+        <v>40.5</v>
+      </c>
+      <c r="N292" s="4">
+        <v>45</v>
+      </c>
+      <c r="O292" s="4">
+        <v>49.6</v>
+      </c>
+      <c r="P292" s="4">
+        <v>57.6</v>
+      </c>
+      <c r="Q292" s="4">
+        <v>59.4</v>
+      </c>
+      <c r="R292" s="4">
+        <v>65.900000000000006</v>
+      </c>
+      <c r="S292" s="4">
+        <v>75.599999999999994</v>
+      </c>
+      <c r="T292" s="4">
+        <v>78.3</v>
+      </c>
+      <c r="U292" s="4">
+        <v>81.099999999999994</v>
+      </c>
+      <c r="V292" s="4">
+        <v>78.3</v>
+      </c>
+      <c r="W292" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="293" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+      <c r="A293" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B293" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="C293" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="D293" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E293" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="C292" s="2" t="s">
+      <c r="F293" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G293" s="4">
+        <v>26.2</v>
+      </c>
+      <c r="H293" s="4">
+        <v>26.3</v>
+      </c>
+      <c r="I293" s="4">
+        <v>28.7</v>
+      </c>
+      <c r="J293" s="4">
+        <v>21.5</v>
+      </c>
+      <c r="K293" s="4">
+        <v>26.2</v>
+      </c>
+      <c r="L293" s="4">
+        <v>26</v>
+      </c>
+      <c r="M293" s="4">
+        <v>30</v>
+      </c>
+      <c r="N293" s="4">
+        <v>28</v>
+      </c>
+      <c r="O293" s="4">
+        <v>35</v>
+      </c>
+      <c r="P293" s="4">
+        <v>41.4</v>
+      </c>
+      <c r="Q293" s="4">
+        <v>45.1</v>
+      </c>
+      <c r="R293" s="4">
+        <v>51.7</v>
+      </c>
+      <c r="S293" s="4">
+        <v>62.4</v>
+      </c>
+      <c r="T293" s="4">
+        <v>65.7</v>
+      </c>
+      <c r="U293" s="4">
+        <v>68.8</v>
+      </c>
+      <c r="V293" s="4">
+        <v>69.900000000000006</v>
+      </c>
+      <c r="W293" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="294" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+      <c r="A294" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B294" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="C294" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="D294" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E294" s="3" t="s">
         <v>408</v>
-      </c>
-      <c r="D292" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E292" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F292" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="G292" s="5">
-        <v>377.75</v>
-      </c>
-      <c r="H292" s="5">
-        <v>417.47</v>
-      </c>
-      <c r="I292" s="5">
-        <v>421.06</v>
-      </c>
-      <c r="J292" s="5">
-        <v>487.12</v>
-      </c>
-      <c r="K292" s="5">
-        <v>451.84</v>
-      </c>
-      <c r="L292" s="5">
-        <v>440.89</v>
-      </c>
-      <c r="M292" s="5">
-        <v>662.95</v>
-      </c>
-      <c r="N292" s="5">
-        <v>679.46</v>
-      </c>
-      <c r="O292" s="5">
-        <v>766.04</v>
-      </c>
-      <c r="P292" s="5">
-        <v>776.56</v>
-      </c>
-      <c r="Q292" s="5">
-        <v>829.27</v>
-      </c>
-      <c r="R292" s="5">
-        <v>983.51</v>
-      </c>
-      <c r="S292" s="5">
-        <v>3494.39</v>
-      </c>
-      <c r="T292" s="5">
-        <v>2580.38</v>
-      </c>
-      <c r="U292" s="5">
-        <v>1840.15</v>
-      </c>
-      <c r="V292" s="3"/>
-      <c r="W292" s="2" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="293" spans="1:23" ht="36" x14ac:dyDescent="0.25">
-      <c r="A293" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="B293" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="C293" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="D293" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E293" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F293" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="G293" s="5">
-        <v>96.04</v>
-      </c>
-      <c r="H293" s="5">
-        <v>90.68</v>
-      </c>
-      <c r="I293" s="5">
-        <v>111.55</v>
-      </c>
-      <c r="J293" s="5">
-        <v>127.11</v>
-      </c>
-      <c r="K293" s="5">
-        <v>82.28</v>
-      </c>
-      <c r="L293" s="5">
-        <v>100.19</v>
-      </c>
-      <c r="M293" s="5">
-        <v>148.99</v>
-      </c>
-      <c r="N293" s="5">
-        <v>222.11</v>
-      </c>
-      <c r="O293" s="5">
-        <v>244.93</v>
-      </c>
-      <c r="P293" s="5">
-        <v>223.31</v>
-      </c>
-      <c r="Q293" s="5">
-        <v>225.08</v>
-      </c>
-      <c r="R293" s="5">
-        <v>296.20999999999998</v>
-      </c>
-      <c r="S293" s="5">
-        <v>2661.32</v>
-      </c>
-      <c r="T293" s="5">
-        <v>1701.94</v>
-      </c>
-      <c r="U293" s="5">
-        <v>705.25</v>
-      </c>
-      <c r="V293" s="3"/>
-      <c r="W293" s="2" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="294" spans="1:23" ht="72" x14ac:dyDescent="0.25">
-      <c r="A294" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="B294" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="C294" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="D294" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E294" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="F294" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G294" s="5">
-        <v>0.08</v>
-      </c>
-      <c r="H294" s="5">
-        <v>0.08</v>
-      </c>
-      <c r="I294" s="5">
-        <v>0.09</v>
-      </c>
-      <c r="J294" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="K294" s="5">
-        <v>0.09</v>
-      </c>
-      <c r="L294" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="M294" s="5">
-        <v>0.15</v>
-      </c>
-      <c r="N294" s="5">
-        <v>0.13</v>
-      </c>
-      <c r="O294" s="5">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="P294" s="5">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="Q294" s="5">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="R294" s="5">
-        <v>0.15</v>
-      </c>
-      <c r="S294" s="5">
-        <v>0.53</v>
-      </c>
-      <c r="T294" s="5">
-        <v>0.33</v>
-      </c>
-      <c r="U294" s="5">
-        <v>0.21</v>
-      </c>
-      <c r="V294" s="3"/>
+      <c r="G294" s="4">
+        <v>13.5</v>
+      </c>
+      <c r="H294" s="4">
+        <v>15.7</v>
+      </c>
+      <c r="I294" s="4">
+        <v>17.2</v>
+      </c>
+      <c r="J294" s="4">
+        <v>12.7</v>
+      </c>
+      <c r="K294" s="4">
+        <v>15.5</v>
+      </c>
+      <c r="L294" s="4">
+        <v>18.3</v>
+      </c>
+      <c r="M294" s="4">
+        <v>19.8</v>
+      </c>
+      <c r="N294" s="4">
+        <v>18.8</v>
+      </c>
+      <c r="O294" s="4">
+        <v>22.4</v>
+      </c>
+      <c r="P294" s="4">
+        <v>28.5</v>
+      </c>
+      <c r="Q294" s="4">
+        <v>29.4</v>
+      </c>
+      <c r="R294" s="4">
+        <v>35</v>
+      </c>
+      <c r="S294" s="4">
+        <v>39.5</v>
+      </c>
+      <c r="T294" s="4">
+        <v>44.4</v>
+      </c>
+      <c r="U294" s="4">
+        <v>50.8</v>
+      </c>
+      <c r="V294" s="4">
+        <v>51.4</v>
+      </c>
       <c r="W294" s="2" t="s">
-        <v>410</v>
+        <v>30</v>
       </c>
     </row>
     <row r="295" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
-        <v>406</v>
+        <v>390</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>415</v>
+        <v>401</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="E295" s="3" t="s">
-        <v>28</v>
+        <v>409</v>
       </c>
       <c r="F295" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="G295" s="3"/>
-      <c r="H295" s="3"/>
-      <c r="I295" s="3"/>
-      <c r="J295" s="7">
-        <v>2.2850000000000001</v>
-      </c>
-      <c r="K295" s="7">
-        <v>1.1160000000000001</v>
-      </c>
-      <c r="L295" s="7">
-        <v>1.55</v>
-      </c>
-      <c r="M295" s="7">
-        <v>3.7469999999999999</v>
-      </c>
-      <c r="N295" s="7">
-        <v>3.8530000000000002</v>
-      </c>
-      <c r="O295" s="7">
-        <v>3.367</v>
-      </c>
-      <c r="P295" s="7">
-        <v>6.8940000000000001</v>
-      </c>
-      <c r="Q295" s="7">
-        <v>4.077</v>
-      </c>
-      <c r="R295" s="7">
-        <v>4.49</v>
-      </c>
-      <c r="S295" s="7">
-        <v>11.999000000000001</v>
-      </c>
-      <c r="T295" s="7">
-        <v>16.606000000000002</v>
-      </c>
-      <c r="U295" s="7">
-        <v>20.382000000000001</v>
-      </c>
-      <c r="V295" s="7">
-        <v>5.3920000000000003</v>
+        <v>34</v>
+      </c>
+      <c r="G295" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H295" s="4">
+        <v>5</v>
+      </c>
+      <c r="I295" s="4">
+        <v>6.8</v>
+      </c>
+      <c r="J295" s="4">
+        <v>3.7</v>
+      </c>
+      <c r="K295" s="4">
+        <v>6.6</v>
+      </c>
+      <c r="L295" s="4">
+        <v>6</v>
+      </c>
+      <c r="M295" s="4">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="N295" s="4">
+        <v>8.4</v>
+      </c>
+      <c r="O295" s="4">
+        <v>10.9</v>
+      </c>
+      <c r="P295" s="4">
+        <v>12.2</v>
+      </c>
+      <c r="Q295" s="4">
+        <v>13.5</v>
+      </c>
+      <c r="R295" s="4">
+        <v>15.8</v>
+      </c>
+      <c r="S295" s="4">
+        <v>23.6</v>
+      </c>
+      <c r="T295" s="4">
+        <v>26.1</v>
+      </c>
+      <c r="U295" s="4">
+        <v>27.4</v>
+      </c>
+      <c r="V295" s="4">
+        <v>27.6</v>
       </c>
       <c r="W295" s="2" t="s">
-        <v>417</v>
+        <v>30</v>
       </c>
     </row>
     <row r="296" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
-        <v>406</v>
+        <v>390</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="D296" s="2" t="s">
         <v>27</v>
@@ -20481,61 +20521,69 @@
         <v>28</v>
       </c>
       <c r="F296" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="G296" s="3"/>
-      <c r="H296" s="3"/>
-      <c r="I296" s="3"/>
-      <c r="J296" s="5">
-        <v>8.07</v>
-      </c>
-      <c r="K296" s="5">
-        <v>3.54</v>
-      </c>
-      <c r="L296" s="5">
-        <v>2.98</v>
-      </c>
-      <c r="M296" s="5">
-        <v>2.44</v>
-      </c>
-      <c r="N296" s="5">
-        <v>2.25</v>
-      </c>
-      <c r="O296" s="5">
-        <v>63.36</v>
-      </c>
-      <c r="P296" s="5">
-        <v>7.61</v>
-      </c>
-      <c r="Q296" s="5">
-        <v>6.64</v>
-      </c>
-      <c r="R296" s="5">
-        <v>3.65</v>
-      </c>
-      <c r="S296" s="5">
-        <v>9.59</v>
-      </c>
-      <c r="T296" s="5">
-        <v>4.2699999999999996</v>
-      </c>
-      <c r="U296" s="5">
-        <v>8.32</v>
-      </c>
-      <c r="V296" s="3"/>
+        <v>34</v>
+      </c>
+      <c r="G296" s="4">
+        <v>5.7</v>
+      </c>
+      <c r="H296" s="4">
+        <v>6</v>
+      </c>
+      <c r="I296" s="4">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="J296" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="K296" s="4">
+        <v>4.7</v>
+      </c>
+      <c r="L296" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="M296" s="4">
+        <v>3.3</v>
+      </c>
+      <c r="N296" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="O296" s="4">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="P296" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="Q296" s="4">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="R296" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="S296" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="T296" s="4">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="U296" s="4">
+        <v>4.8</v>
+      </c>
+      <c r="V296" s="4">
+        <v>5.2</v>
+      </c>
       <c r="W296" s="2" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="297" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="297" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
-        <v>406</v>
+        <v>390</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="D297" s="2" t="s">
         <v>27</v>
@@ -20544,55 +20592,69 @@
         <v>28</v>
       </c>
       <c r="F297" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="G297" s="3"/>
-      <c r="H297" s="3"/>
-      <c r="I297" s="3"/>
-      <c r="J297" s="3"/>
+        <v>42</v>
+      </c>
+      <c r="G297" s="6">
+        <v>674</v>
+      </c>
+      <c r="H297" s="6">
+        <v>605</v>
+      </c>
+      <c r="I297" s="6">
+        <v>1082</v>
+      </c>
+      <c r="J297" s="6">
+        <v>1219</v>
+      </c>
       <c r="K297" s="6">
-        <v>1</v>
+        <v>1282</v>
       </c>
       <c r="L297" s="6">
-        <v>1</v>
+        <v>1456</v>
       </c>
       <c r="M297" s="6">
-        <v>8</v>
+        <v>1926</v>
       </c>
       <c r="N297" s="6">
-        <v>2</v>
-      </c>
-      <c r="O297" s="3"/>
+        <v>3182</v>
+      </c>
+      <c r="O297" s="6">
+        <v>3739</v>
+      </c>
       <c r="P297" s="6">
-        <v>1</v>
+        <v>6484</v>
       </c>
       <c r="Q297" s="6">
-        <v>2</v>
-      </c>
-      <c r="R297" s="3"/>
-      <c r="S297" s="3"/>
+        <v>10420</v>
+      </c>
+      <c r="R297" s="6">
+        <v>29483</v>
+      </c>
+      <c r="S297" s="6">
+        <v>39683</v>
+      </c>
       <c r="T297" s="6">
-        <v>8</v>
+        <v>80267</v>
       </c>
       <c r="U297" s="6">
-        <v>7</v>
+        <v>103449</v>
       </c>
       <c r="V297" s="6">
-        <v>2</v>
+        <v>260783</v>
       </c>
       <c r="W297" s="2" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="298" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="298" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
-        <v>406</v>
+        <v>390</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="D298" s="2" t="s">
         <v>27</v>
@@ -20601,65 +20663,43 @@
         <v>28</v>
       </c>
       <c r="F298" s="3" t="s">
-        <v>421</v>
+        <v>34</v>
       </c>
       <c r="G298" s="3"/>
       <c r="H298" s="3"/>
-      <c r="I298" s="6">
-        <v>2</v>
-      </c>
-      <c r="J298" s="6">
-        <v>2</v>
-      </c>
-      <c r="K298" s="6">
-        <v>1</v>
-      </c>
-      <c r="L298" s="6">
-        <v>1</v>
-      </c>
-      <c r="M298" s="6">
-        <v>1</v>
-      </c>
-      <c r="N298" s="6">
-        <v>1</v>
-      </c>
-      <c r="O298" s="6">
-        <v>1</v>
-      </c>
-      <c r="P298" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q298" s="6">
-        <v>4</v>
-      </c>
-      <c r="R298" s="6">
-        <v>1</v>
-      </c>
-      <c r="S298" s="6">
-        <v>1</v>
-      </c>
-      <c r="T298" s="6">
-        <v>0</v>
-      </c>
-      <c r="U298" s="6">
-        <v>4</v>
-      </c>
-      <c r="V298" s="6">
-        <v>2</v>
+      <c r="I298" s="3"/>
+      <c r="J298" s="3"/>
+      <c r="K298" s="3"/>
+      <c r="L298" s="3"/>
+      <c r="M298" s="3"/>
+      <c r="N298" s="3"/>
+      <c r="O298" s="3"/>
+      <c r="P298" s="3"/>
+      <c r="Q298" s="3"/>
+      <c r="R298" s="5">
+        <v>18.93</v>
+      </c>
+      <c r="S298" s="3"/>
+      <c r="T298" s="5">
+        <v>21.3</v>
+      </c>
+      <c r="U298" s="3"/>
+      <c r="V298" s="5">
+        <v>23.01</v>
       </c>
       <c r="W298" s="2" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="299" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="299" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="D299" s="2" t="s">
         <v>27</v>
@@ -20668,61 +20708,67 @@
         <v>28</v>
       </c>
       <c r="F299" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G299" s="3"/>
-      <c r="H299" s="3"/>
-      <c r="I299" s="3"/>
-      <c r="J299" s="3"/>
-      <c r="K299" s="6">
-        <v>5</v>
-      </c>
-      <c r="L299" s="6">
-        <v>13</v>
-      </c>
-      <c r="M299" s="6">
-        <v>19</v>
-      </c>
-      <c r="N299" s="6">
-        <v>18</v>
-      </c>
-      <c r="O299" s="6">
-        <v>15</v>
-      </c>
-      <c r="P299" s="6">
-        <v>15</v>
-      </c>
-      <c r="Q299" s="6">
-        <v>8</v>
-      </c>
-      <c r="R299" s="6">
-        <v>28</v>
-      </c>
-      <c r="S299" s="6">
-        <v>53</v>
-      </c>
-      <c r="T299" s="6">
-        <v>65</v>
-      </c>
-      <c r="U299" s="6">
-        <v>70</v>
-      </c>
-      <c r="V299" s="6">
-        <v>69</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="G299" s="5">
+        <v>377.75</v>
+      </c>
+      <c r="H299" s="5">
+        <v>417.47</v>
+      </c>
+      <c r="I299" s="5">
+        <v>421.06</v>
+      </c>
+      <c r="J299" s="5">
+        <v>487.12</v>
+      </c>
+      <c r="K299" s="5">
+        <v>451.84</v>
+      </c>
+      <c r="L299" s="5">
+        <v>440.89</v>
+      </c>
+      <c r="M299" s="5">
+        <v>662.95</v>
+      </c>
+      <c r="N299" s="5">
+        <v>679.46</v>
+      </c>
+      <c r="O299" s="5">
+        <v>766.04</v>
+      </c>
+      <c r="P299" s="5">
+        <v>776.56</v>
+      </c>
+      <c r="Q299" s="5">
+        <v>829.27</v>
+      </c>
+      <c r="R299" s="5">
+        <v>983.51</v>
+      </c>
+      <c r="S299" s="5">
+        <v>3494.39</v>
+      </c>
+      <c r="T299" s="5">
+        <v>2580.38</v>
+      </c>
+      <c r="U299" s="5">
+        <v>1840.15</v>
+      </c>
+      <c r="V299" s="3"/>
       <c r="W299" s="2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="300" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+      <c r="A300" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="B300" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="C300" s="2" t="s">
         <v>422</v>
-      </c>
-    </row>
-    <row r="300" spans="1:23" ht="45" x14ac:dyDescent="0.25">
-      <c r="A300" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="B300" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="C300" s="2" t="s">
-        <v>428</v>
       </c>
       <c r="D300" s="2" t="s">
         <v>27</v>
@@ -20731,47 +20777,500 @@
         <v>28</v>
       </c>
       <c r="F300" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="G300" s="5">
+        <v>96.04</v>
+      </c>
+      <c r="H300" s="5">
+        <v>90.68</v>
+      </c>
+      <c r="I300" s="5">
+        <v>111.55</v>
+      </c>
+      <c r="J300" s="5">
+        <v>127.11</v>
+      </c>
+      <c r="K300" s="5">
+        <v>82.28</v>
+      </c>
+      <c r="L300" s="5">
+        <v>100.19</v>
+      </c>
+      <c r="M300" s="5">
+        <v>148.99</v>
+      </c>
+      <c r="N300" s="5">
+        <v>222.11</v>
+      </c>
+      <c r="O300" s="5">
+        <v>244.93</v>
+      </c>
+      <c r="P300" s="5">
+        <v>223.31</v>
+      </c>
+      <c r="Q300" s="5">
+        <v>225.08</v>
+      </c>
+      <c r="R300" s="5">
+        <v>296.20999999999998</v>
+      </c>
+      <c r="S300" s="5">
+        <v>2661.32</v>
+      </c>
+      <c r="T300" s="5">
+        <v>1701.94</v>
+      </c>
+      <c r="U300" s="5">
+        <v>705.25</v>
+      </c>
+      <c r="V300" s="3"/>
+      <c r="W300" s="2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="301" spans="1:23" ht="72" x14ac:dyDescent="0.25">
+      <c r="A301" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="B301" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="C301" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="D301" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E301" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F301" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G301" s="5">
+        <v>0.08</v>
+      </c>
+      <c r="H301" s="5">
+        <v>0.08</v>
+      </c>
+      <c r="I301" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="J301" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="K301" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="L301" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="M301" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="N301" s="5">
+        <v>0.13</v>
+      </c>
+      <c r="O301" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="P301" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="Q301" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="R301" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="S301" s="5">
+        <v>0.53</v>
+      </c>
+      <c r="T301" s="5">
+        <v>0.33</v>
+      </c>
+      <c r="U301" s="5">
+        <v>0.21</v>
+      </c>
+      <c r="V301" s="3"/>
+      <c r="W301" s="2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="302" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+      <c r="A302" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="B302" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="C302" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="D302" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E302" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F302" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="G302" s="3"/>
+      <c r="H302" s="3"/>
+      <c r="I302" s="3"/>
+      <c r="J302" s="7">
+        <v>2.2850000000000001</v>
+      </c>
+      <c r="K302" s="7">
+        <v>1.1160000000000001</v>
+      </c>
+      <c r="L302" s="7">
+        <v>1.55</v>
+      </c>
+      <c r="M302" s="7">
+        <v>3.7469999999999999</v>
+      </c>
+      <c r="N302" s="7">
+        <v>3.8530000000000002</v>
+      </c>
+      <c r="O302" s="7">
+        <v>3.367</v>
+      </c>
+      <c r="P302" s="7">
+        <v>6.8940000000000001</v>
+      </c>
+      <c r="Q302" s="7">
+        <v>4.077</v>
+      </c>
+      <c r="R302" s="7">
+        <v>4.49</v>
+      </c>
+      <c r="S302" s="7">
+        <v>11.999000000000001</v>
+      </c>
+      <c r="T302" s="7">
+        <v>16.606000000000002</v>
+      </c>
+      <c r="U302" s="7">
+        <v>20.382000000000001</v>
+      </c>
+      <c r="V302" s="7">
+        <v>5.3920000000000003</v>
+      </c>
+      <c r="W302" s="2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="303" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+      <c r="A303" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="B303" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="C303" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="D303" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E303" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F303" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="G303" s="3"/>
+      <c r="H303" s="3"/>
+      <c r="I303" s="3"/>
+      <c r="J303" s="5">
+        <v>8.07</v>
+      </c>
+      <c r="K303" s="5">
+        <v>3.54</v>
+      </c>
+      <c r="L303" s="5">
+        <v>2.98</v>
+      </c>
+      <c r="M303" s="5">
+        <v>2.44</v>
+      </c>
+      <c r="N303" s="5">
+        <v>2.25</v>
+      </c>
+      <c r="O303" s="5">
+        <v>63.36</v>
+      </c>
+      <c r="P303" s="5">
+        <v>7.61</v>
+      </c>
+      <c r="Q303" s="5">
+        <v>6.64</v>
+      </c>
+      <c r="R303" s="5">
+        <v>3.65</v>
+      </c>
+      <c r="S303" s="5">
+        <v>9.59</v>
+      </c>
+      <c r="T303" s="5">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="U303" s="5">
+        <v>8.32</v>
+      </c>
+      <c r="V303" s="3"/>
+      <c r="W303" s="2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="304" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+      <c r="A304" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="B304" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="C304" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="D304" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E304" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F304" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="G304" s="3"/>
+      <c r="H304" s="3"/>
+      <c r="I304" s="3"/>
+      <c r="J304" s="3"/>
+      <c r="K304" s="6">
+        <v>1</v>
+      </c>
+      <c r="L304" s="6">
+        <v>1</v>
+      </c>
+      <c r="M304" s="6">
+        <v>8</v>
+      </c>
+      <c r="N304" s="6">
+        <v>2</v>
+      </c>
+      <c r="O304" s="3"/>
+      <c r="P304" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q304" s="6">
+        <v>2</v>
+      </c>
+      <c r="R304" s="3"/>
+      <c r="S304" s="3"/>
+      <c r="T304" s="6">
+        <v>8</v>
+      </c>
+      <c r="U304" s="6">
+        <v>7</v>
+      </c>
+      <c r="V304" s="6">
+        <v>2</v>
+      </c>
+      <c r="W304" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="305" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+      <c r="A305" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="B305" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="C305" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="D305" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E305" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F305" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="G305" s="3"/>
+      <c r="H305" s="3"/>
+      <c r="I305" s="6">
+        <v>2</v>
+      </c>
+      <c r="J305" s="6">
+        <v>2</v>
+      </c>
+      <c r="K305" s="6">
+        <v>1</v>
+      </c>
+      <c r="L305" s="6">
+        <v>1</v>
+      </c>
+      <c r="M305" s="6">
+        <v>1</v>
+      </c>
+      <c r="N305" s="6">
+        <v>1</v>
+      </c>
+      <c r="O305" s="6">
+        <v>1</v>
+      </c>
+      <c r="P305" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q305" s="6">
+        <v>4</v>
+      </c>
+      <c r="R305" s="6">
+        <v>1</v>
+      </c>
+      <c r="S305" s="6">
+        <v>1</v>
+      </c>
+      <c r="T305" s="6">
+        <v>0</v>
+      </c>
+      <c r="U305" s="6">
+        <v>4</v>
+      </c>
+      <c r="V305" s="6">
+        <v>2</v>
+      </c>
+      <c r="W305" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="306" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+      <c r="A306" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="B306" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="C306" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="D306" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E306" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F306" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G300" s="3"/>
-      <c r="H300" s="3"/>
-      <c r="I300" s="3"/>
-      <c r="J300" s="3"/>
-      <c r="K300" s="3"/>
-      <c r="L300" s="3"/>
-      <c r="M300" s="3"/>
-      <c r="N300" s="3"/>
-      <c r="O300" s="3"/>
-      <c r="P300" s="3"/>
-      <c r="Q300" s="3"/>
-      <c r="R300" s="3"/>
-      <c r="S300" s="3"/>
-      <c r="T300" s="6">
+      <c r="G306" s="3"/>
+      <c r="H306" s="3"/>
+      <c r="I306" s="3"/>
+      <c r="J306" s="3"/>
+      <c r="K306" s="6">
+        <v>5</v>
+      </c>
+      <c r="L306" s="6">
+        <v>13</v>
+      </c>
+      <c r="M306" s="6">
+        <v>19</v>
+      </c>
+      <c r="N306" s="6">
+        <v>18</v>
+      </c>
+      <c r="O306" s="6">
+        <v>15</v>
+      </c>
+      <c r="P306" s="6">
+        <v>15</v>
+      </c>
+      <c r="Q306" s="6">
+        <v>8</v>
+      </c>
+      <c r="R306" s="6">
+        <v>28</v>
+      </c>
+      <c r="S306" s="6">
+        <v>53</v>
+      </c>
+      <c r="T306" s="6">
+        <v>65</v>
+      </c>
+      <c r="U306" s="6">
+        <v>70</v>
+      </c>
+      <c r="V306" s="6">
+        <v>69</v>
+      </c>
+      <c r="W306" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="307" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+      <c r="A307" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="B307" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C307" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="D307" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E307" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F307" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G307" s="3"/>
+      <c r="H307" s="3"/>
+      <c r="I307" s="3"/>
+      <c r="J307" s="3"/>
+      <c r="K307" s="3"/>
+      <c r="L307" s="3"/>
+      <c r="M307" s="3"/>
+      <c r="N307" s="3"/>
+      <c r="O307" s="3"/>
+      <c r="P307" s="3"/>
+      <c r="Q307" s="3"/>
+      <c r="R307" s="3"/>
+      <c r="S307" s="3"/>
+      <c r="T307" s="6">
         <v>114</v>
       </c>
-      <c r="U300" s="6">
+      <c r="U307" s="6">
         <v>61</v>
       </c>
-      <c r="V300" s="6">
+      <c r="V307" s="6">
         <v>97</v>
       </c>
-      <c r="W300" s="2" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="301" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="302" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A302" s="10" t="s">
-        <v>430</v>
-      </c>
-      <c r="B302" s="8"/>
+      <c r="W307" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="308" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A309" s="10" t="s">
+        <v>440</v>
+      </c>
+      <c r="B309" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:C3" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A302:B302"/>
+    <mergeCell ref="A309:B309"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>

--- a/assets/excel/en/national_sdg_indicators.xlsx
+++ b/assets/excel/en/national_sdg_indicators.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sidwab\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A037913B-D2A7-433F-86BC-9F6E5E42A691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC813D9E-950E-4268-BAE3-7577D0BB9491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1351,7 +1351,7 @@
     <t>The Ministry of Economic Development and Technology / The Chancellery of the  Prime Minister</t>
   </si>
   <si>
-    <t>Last update: 07-08-2026, 10:19</t>
+    <t>Last update: 07-08-2026, 12:58</t>
   </si>
 </sst>
 </file>
@@ -16266,49 +16266,49 @@
         <v>34</v>
       </c>
       <c r="G232" s="4">
-        <v>99.6</v>
+        <v>43.4</v>
       </c>
       <c r="H232" s="4">
-        <v>99.6</v>
+        <v>46.5</v>
       </c>
       <c r="I232" s="4">
-        <v>99.6</v>
+        <v>47.2</v>
       </c>
       <c r="J232" s="4">
-        <v>99.6</v>
+        <v>47.8</v>
       </c>
       <c r="K232" s="4">
-        <v>99.6</v>
+        <v>46.4</v>
       </c>
       <c r="L232" s="4">
-        <v>99.6</v>
+        <v>46.5</v>
       </c>
       <c r="M232" s="4">
-        <v>99.7</v>
+        <v>51.4</v>
       </c>
       <c r="N232" s="4">
-        <v>99.7</v>
+        <v>53.8</v>
       </c>
       <c r="O232" s="4">
-        <v>99.7</v>
+        <v>54</v>
       </c>
       <c r="P232" s="4">
-        <v>99.7</v>
+        <v>54.3</v>
       </c>
       <c r="Q232" s="4">
-        <v>99.8</v>
+        <v>58.5</v>
       </c>
       <c r="R232" s="4">
-        <v>99.8</v>
+        <v>61.4</v>
       </c>
       <c r="S232" s="4">
-        <v>99.8</v>
+        <v>60</v>
       </c>
       <c r="T232" s="4">
-        <v>99.8</v>
+        <v>62.3</v>
       </c>
       <c r="U232" s="4">
-        <v>99.8</v>
+        <v>59.6</v>
       </c>
       <c r="V232" s="3"/>
       <c r="W232" s="2" t="s">
@@ -16335,49 +16335,49 @@
         <v>34</v>
       </c>
       <c r="G233" s="4">
-        <v>43.4</v>
+        <v>99.6</v>
       </c>
       <c r="H233" s="4">
-        <v>46.5</v>
+        <v>99.6</v>
       </c>
       <c r="I233" s="4">
-        <v>47.2</v>
+        <v>99.6</v>
       </c>
       <c r="J233" s="4">
-        <v>47.8</v>
+        <v>99.6</v>
       </c>
       <c r="K233" s="4">
-        <v>46.4</v>
+        <v>99.6</v>
       </c>
       <c r="L233" s="4">
-        <v>46.5</v>
+        <v>99.6</v>
       </c>
       <c r="M233" s="4">
-        <v>51.4</v>
+        <v>99.7</v>
       </c>
       <c r="N233" s="4">
-        <v>53.8</v>
+        <v>99.7</v>
       </c>
       <c r="O233" s="4">
-        <v>54</v>
+        <v>99.7</v>
       </c>
       <c r="P233" s="4">
-        <v>54.3</v>
+        <v>99.7</v>
       </c>
       <c r="Q233" s="4">
-        <v>58.5</v>
+        <v>99.8</v>
       </c>
       <c r="R233" s="4">
-        <v>61.4</v>
+        <v>99.8</v>
       </c>
       <c r="S233" s="4">
-        <v>60</v>
+        <v>99.8</v>
       </c>
       <c r="T233" s="4">
-        <v>62.3</v>
+        <v>99.8</v>
       </c>
       <c r="U233" s="4">
-        <v>59.6</v>
+        <v>99.8</v>
       </c>
       <c r="V233" s="3"/>
       <c r="W233" s="2" t="s">
